--- a/spreadsheet.xlsx
+++ b/spreadsheet.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="305">
   <si>
     <t>product_id</t>
   </si>
@@ -31,70 +31,73 @@
     <t>image_url</t>
   </si>
   <si>
-    <t>price_history</t>
+    <t>13992938</t>
   </si>
   <si>
     <t>13991986</t>
   </si>
   <si>
-    <t>13992938</t>
+    <t>13991988</t>
+  </si>
+  <si>
+    <t>13992940</t>
+  </si>
+  <si>
+    <t>13993095</t>
   </si>
   <si>
     <t>13992951</t>
   </si>
   <si>
-    <t>13993095</t>
-  </si>
-  <si>
-    <t>13991988</t>
+    <t>13993244</t>
+  </si>
+  <si>
+    <t>13993093</t>
+  </si>
+  <si>
+    <t>12547939</t>
+  </si>
+  <si>
+    <t>12755140</t>
+  </si>
+  <si>
+    <t>13991952</t>
+  </si>
+  <si>
+    <t>12534144</t>
   </si>
   <si>
     <t>12547936</t>
   </si>
   <si>
-    <t>13992940</t>
-  </si>
-  <si>
-    <t>13993244</t>
-  </si>
-  <si>
-    <t>12534144</t>
-  </si>
-  <si>
-    <t>12755140</t>
-  </si>
-  <si>
-    <t>12547939</t>
-  </si>
-  <si>
-    <t>13991952</t>
-  </si>
-  <si>
-    <t>13993093</t>
-  </si>
-  <si>
     <t>13538152</t>
   </si>
   <si>
+    <t>13993381</t>
+  </si>
+  <si>
+    <t>13993243</t>
+  </si>
+  <si>
     <t>13570649</t>
   </si>
   <si>
-    <t>13993381</t>
+    <t>13564531</t>
+  </si>
+  <si>
+    <t>13994392</t>
+  </si>
+  <si>
+    <t>13561997</t>
   </si>
   <si>
     <t>13991985</t>
   </si>
   <si>
-    <t>13993243</t>
-  </si>
-  <si>
-    <t>13994392</t>
-  </si>
-  <si>
-    <t>13561997</t>
-  </si>
-  <si>
-    <t>13564531</t>
+    <t>13994199</t>
+  </si>
+  <si>
+    <t>13991987</t>
   </si>
   <si>
     <t>13993303</t>
@@ -103,61 +106,67 @@
     <t>13992308</t>
   </si>
   <si>
+    <t>13994348</t>
+  </si>
+  <si>
     <t>12534152</t>
   </si>
   <si>
-    <t>13991987</t>
+    <t>13567220</t>
+  </si>
+  <si>
+    <t>13992942</t>
+  </si>
+  <si>
+    <t>13994192</t>
+  </si>
+  <si>
+    <t>13382394</t>
+  </si>
+  <si>
+    <t>12755141</t>
   </si>
   <si>
     <t>13340189</t>
   </si>
   <si>
-    <t>13994199</t>
+    <t>13991991</t>
+  </si>
+  <si>
+    <t>13992135</t>
+  </si>
+  <si>
+    <t>13186208</t>
+  </si>
+  <si>
+    <t>12474762</t>
   </si>
   <si>
     <t>13340176</t>
   </si>
   <si>
-    <t>13994348</t>
+    <t>13994393</t>
+  </si>
+  <si>
+    <t>13994264</t>
+  </si>
+  <si>
+    <t>13994235</t>
+  </si>
+  <si>
+    <t>12481774</t>
+  </si>
+  <si>
+    <t>13993126</t>
+  </si>
+  <si>
+    <t>13994236</t>
   </si>
   <si>
     <t>13994245</t>
   </si>
   <si>
-    <t>13567220</t>
-  </si>
-  <si>
-    <t>12474762</t>
-  </si>
-  <si>
-    <t>13991991</t>
-  </si>
-  <si>
-    <t>13993126</t>
-  </si>
-  <si>
-    <t>12755141</t>
-  </si>
-  <si>
-    <t>13994393</t>
-  </si>
-  <si>
-    <t>13992942</t>
-  </si>
-  <si>
-    <t>13994236</t>
-  </si>
-  <si>
-    <t>13382394</t>
-  </si>
-  <si>
-    <t>13186208</t>
-  </si>
-  <si>
-    <t>12481774</t>
-  </si>
-  <si>
-    <t>13992135</t>
+    <t>13992383</t>
   </si>
   <si>
     <t>13994350</t>
@@ -166,115 +175,109 @@
     <t>13994352</t>
   </si>
   <si>
-    <t>13992383</t>
+    <t>13993089</t>
+  </si>
+  <si>
+    <t>13994360</t>
+  </si>
+  <si>
+    <t>13645640</t>
+  </si>
+  <si>
+    <t>13341614</t>
+  </si>
+  <si>
+    <t>12481790</t>
+  </si>
+  <si>
+    <t>13340173</t>
+  </si>
+  <si>
+    <t>13992139</t>
+  </si>
+  <si>
+    <t>12547997</t>
   </si>
   <si>
     <t>13340177</t>
   </si>
   <si>
-    <t>13341614</t>
-  </si>
-  <si>
-    <t>13992139</t>
-  </si>
-  <si>
-    <t>13994264</t>
-  </si>
-  <si>
-    <t>13994235</t>
+    <t>13992941</t>
+  </si>
+  <si>
+    <t>13992144</t>
   </si>
   <si>
     <t>13341612</t>
   </si>
   <si>
-    <t>13994360</t>
-  </si>
-  <si>
-    <t>13645640</t>
-  </si>
-  <si>
-    <t>13340173</t>
-  </si>
-  <si>
-    <t>12481790</t>
-  </si>
-  <si>
-    <t>12547997</t>
-  </si>
-  <si>
-    <t>13994349</t>
-  </si>
-  <si>
-    <t>12534149</t>
-  </si>
-  <si>
-    <t>13994064</t>
-  </si>
-  <si>
-    <t>13992144</t>
+    <t>iPhone 17 256GB</t>
   </si>
   <si>
     <t>Celular Samsung Galaxy A56 5G 256GB 8 GB</t>
   </si>
   <si>
-    <t>iPhone 17 256GB</t>
+    <t>Celular Samsung Galaxy A36 5G 256GB 8 GB</t>
+  </si>
+  <si>
+    <t>iPhone 17 Pro Max 256GB</t>
+  </si>
+  <si>
+    <t>Celular Samsung Galaxy S25 FE 5G 128GB 8 GB</t>
   </si>
   <si>
     <t>Celular Samsung Galaxy A17 5G 256GB 8 GB</t>
   </si>
   <si>
-    <t>Celular Samsung Galaxy S25 FE 5G 128GB 8 GB</t>
-  </si>
-  <si>
-    <t>Celular Samsung Galaxy A36 5G 256GB 8 GB</t>
+    <t>Celular Samsung Galaxy A07 4G 128GB 4 GB</t>
+  </si>
+  <si>
+    <t>Celular Samsung Galaxy S25 FE 5G 256GB 8 GB</t>
+  </si>
+  <si>
+    <t>Celular Samsung Galaxy S24 Ultra 5G 256GB 12 GB</t>
+  </si>
+  <si>
+    <t>iPhone 16 128GB</t>
+  </si>
+  <si>
+    <t>iPhone 16e 128GB 8 GB</t>
+  </si>
+  <si>
+    <t>iPhone 15 128GB 6GB</t>
   </si>
   <si>
     <t>Celular Samsung Galaxy S24 5G 256GB 8 GB</t>
   </si>
   <si>
-    <t>iPhone 17 Pro Max 256GB</t>
-  </si>
-  <si>
-    <t>Celular Samsung Galaxy A07 4G 128GB 4 GB</t>
-  </si>
-  <si>
-    <t>iPhone 15 128GB 6GB</t>
-  </si>
-  <si>
-    <t>iPhone 16 128GB</t>
-  </si>
-  <si>
-    <t>Celular Samsung Galaxy S24 Ultra 5G 256GB 12 GB</t>
-  </si>
-  <si>
-    <t>iPhone 16e 128GB 8 GB</t>
-  </si>
-  <si>
-    <t>Celular Samsung Galaxy S25 FE 5G 256GB 8 GB</t>
-  </si>
-  <si>
     <t>Celular Samsung Galaxy S25 Plus 5G 256GB 12 GB</t>
   </si>
   <si>
+    <t>Celular Motorola Moto G G86 5G 256GB 8 GB</t>
+  </si>
+  <si>
+    <t>Celular Samsung Galaxy A07 4G 256GB 8 GB</t>
+  </si>
+  <si>
     <t>Celular Samsung Galaxy S25 5G 256GB 12 GB</t>
   </si>
   <si>
-    <t>Celular Motorola Moto G G86 5G 256GB 8 GB</t>
+    <t>Celular Samsung Galaxy S25 Ultra 5G 256GB 12 GB</t>
+  </si>
+  <si>
+    <t>Celular Samsung A57 256GB 8 GB</t>
+  </si>
+  <si>
+    <t>Celular Samsung Galaxy S25 Plus 5G 512GB 12 GB</t>
   </si>
   <si>
     <t>Celular Samsung Galaxy A56 5G 128GB 8 GB</t>
   </si>
   <si>
-    <t>Celular Samsung Galaxy A07 4G 256GB 8 GB</t>
-  </si>
-  <si>
-    <t>Celular Samsung A57 256GB 8 GB</t>
-  </si>
-  <si>
-    <t>Celular Samsung Galaxy S25 Plus 5G 512GB 12 GB</t>
-  </si>
-  <si>
-    <t>Celular Samsung Galaxy S25 Ultra 5G 256GB 12 GB</t>
+    <t>Celular Samsung Galaxy S26 5G 256GB 12 GB</t>
+  </si>
+  <si>
+    <t>Celular Samsung Galaxy A36 5G SM-A366E 128GB 6 GB</t>
   </si>
   <si>
     <t>Celular Xiaomi Redmi 15 256GB 8 GB</t>
@@ -283,61 +286,67 @@
     <t>Celular Motorola Moto Edge 60 Pro 5G 256GB 12 GB</t>
   </si>
   <si>
+    <t>Celular Xiaomi Pocophone Poco X8 Pro 256GB 8 GB</t>
+  </si>
+  <si>
     <t>iPhone 15 Pro Max 8 GB 256GB</t>
   </si>
   <si>
-    <t>Celular Samsung Galaxy A36 5G SM-A366E 128GB 6 GB</t>
+    <t>Celular Samsung Galaxy S25 Ultra 5G SM-S938B 512GB 12 GB</t>
+  </si>
+  <si>
+    <t>iPhone 17 Pro 256GB</t>
+  </si>
+  <si>
+    <t>Celular Samsung Galaxy S26 Ultra 5G 256GB 12 GB</t>
+  </si>
+  <si>
+    <t>Celular Xiaomi Poco X7 5G 256GB 8 GB</t>
+  </si>
+  <si>
+    <t>iPhone 16 256GB</t>
   </si>
   <si>
     <t>Celular Samsung Galaxy A25 5G 256GB 8 GB</t>
   </si>
   <si>
-    <t>Celular Samsung Galaxy S26 5G 256GB 12 GB</t>
+    <t>Celular Samsung Galaxy A26 5G SM-A266M 256GB 8 GB</t>
+  </si>
+  <si>
+    <t>Celular Motorola Moto Edge 60 Fusion 5G 256GB 8 GB</t>
+  </si>
+  <si>
+    <t>Celular Samsung Galaxy S24 FE 5G 256GB 8 GB</t>
+  </si>
+  <si>
+    <t>iPhone 13 4 GB 256GB</t>
   </si>
   <si>
     <t>Celular Motorola Moto G35 5G 128GB 12 GB</t>
   </si>
   <si>
-    <t>Celular Xiaomi Pocophone Poco X8 Pro 256GB 8 GB</t>
+    <t>Celular Samsung A57 128GB 8 GB</t>
+  </si>
+  <si>
+    <t>Celular Motorola Edge 70 Fusion 5G 256GB 8 GB</t>
+  </si>
+  <si>
+    <t>Celular Samsung Galaxy A17 4G 128GB 4 GB</t>
+  </si>
+  <si>
+    <t>iPhone 14 Plus 256GB 6GB</t>
+  </si>
+  <si>
+    <t>Celular Xiaomi Poco C85 256GB 8 GB</t>
+  </si>
+  <si>
+    <t>Celular Samsung Galaxy A17 4G 256GB 8 GB</t>
   </si>
   <si>
     <t>Celular Apple iPhone 17e 5G 256GB</t>
   </si>
   <si>
-    <t>Celular Samsung Galaxy S25 Ultra 5G SM-S938B 512GB 12 GB</t>
-  </si>
-  <si>
-    <t>iPhone 13 4 GB 256GB</t>
-  </si>
-  <si>
-    <t>Celular Samsung Galaxy A26 5G SM-A266M 256GB 8 GB</t>
-  </si>
-  <si>
-    <t>Celular Xiaomi Poco C85 256GB 8 GB</t>
-  </si>
-  <si>
-    <t>iPhone 16 256GB</t>
-  </si>
-  <si>
-    <t>Celular Samsung A57 128GB 8 GB</t>
-  </si>
-  <si>
-    <t>iPhone 17 Pro 256GB</t>
-  </si>
-  <si>
-    <t>Celular Samsung Galaxy A17 4G 256GB 8 GB</t>
-  </si>
-  <si>
-    <t>Celular Xiaomi Poco X7 5G 256GB 8 GB</t>
-  </si>
-  <si>
-    <t>Celular Samsung Galaxy S24 FE 5G 256GB 8 GB</t>
-  </si>
-  <si>
-    <t>iPhone 14 Plus 256GB 6GB</t>
-  </si>
-  <si>
-    <t>Celular Motorola Moto Edge 60 Fusion 5G 256GB 8 GB</t>
+    <t>Celular Motorola Moto G G56 5G 256GB 8 GB</t>
   </si>
   <si>
     <t>Celular Xiaomi Pocophone Poco X8 Pro 512GB 12 GB</t>
@@ -346,115 +355,109 @@
     <t>Celular Xiaomi Pocophone Poco X8 Pro Max 512GB 12 GB</t>
   </si>
   <si>
-    <t>Celular Motorola Moto G G56 5G 256GB 8 GB</t>
+    <t>Celular Motorola Moto G G06 128GB 4 GB</t>
+  </si>
+  <si>
+    <t>Celular Xiaomi Redmi Note 15 Pro 5G 256GB 8 GB</t>
+  </si>
+  <si>
+    <t>Celular Xiaomi Redmi Note 14 256GB 8 GB</t>
+  </si>
+  <si>
+    <t>Celular Xiaomi Poco X7 Pro 5G 512GB 12GB</t>
+  </si>
+  <si>
+    <t>Celular Apple iPhone 14 Pro 256GB 6 GB</t>
+  </si>
+  <si>
+    <t>Celular Motorola Moto G35 5G 256GB 12 GB</t>
+  </si>
+  <si>
+    <t>Celular Motorola Edge 60 5G XT2505-4 512GB 12 GB</t>
+  </si>
+  <si>
+    <t>Celular Samsung Galaxy A05s 128GB 6 GB</t>
   </si>
   <si>
     <t>Celular Motorola Moto G75 5G XT2437-2 256GB 16 GB</t>
   </si>
   <si>
-    <t>Celular Xiaomi Poco X7 Pro 5G 512GB 12GB</t>
-  </si>
-  <si>
-    <t>Celular Motorola Edge 60 5G XT2505-4 512GB 12 GB</t>
-  </si>
-  <si>
-    <t>Celular Motorola Edge 70 Fusion 5G 256GB 8 GB</t>
-  </si>
-  <si>
-    <t>Celular Samsung Galaxy A17 4G 128GB 4 GB</t>
+    <t>iPhone 17 Pro Max 512GB</t>
+  </si>
+  <si>
+    <t>Celular Motorola Moto Edge 60 Pro 5G 512GB 12 GB</t>
   </si>
   <si>
     <t>Celular Xiaomi Poco X7 Pro 5G 256GB 8 GB</t>
   </si>
   <si>
-    <t>Celular Xiaomi Redmi Note 15 Pro 5G 256GB 8 GB</t>
-  </si>
-  <si>
-    <t>Celular Xiaomi Redmi Note 14 256GB 8 GB</t>
-  </si>
-  <si>
-    <t>Celular Motorola Moto G35 5G 256GB 12 GB</t>
-  </si>
-  <si>
-    <t>Celular Apple iPhone 14 Pro 256GB 6 GB</t>
-  </si>
-  <si>
-    <t>Celular Samsung Galaxy A05s 128GB 6 GB</t>
-  </si>
-  <si>
-    <t>Celular Xiaomi Pocophone Poco X8 Pro 512GB 8 GB</t>
-  </si>
-  <si>
-    <t>Celular Apple iPhone 15 Plus 256GB 6 GB</t>
-  </si>
-  <si>
-    <t>Celular Xiaomi Redmi Note 15 Pro 5G 512GB 8 GB</t>
-  </si>
-  <si>
-    <t>Celular Motorola Moto Edge 60 Pro 5G 512GB 12 GB</t>
+    <t>/celular/celular-apple-iphone-17-256gb?_lc=11</t>
   </si>
   <si>
     <t>/celular/celular-samsung-galaxy-a56-5g-256gb-8-gb?_lc=11</t>
   </si>
   <si>
-    <t>/celular/celular-apple-iphone-17-256gb?_lc=11</t>
+    <t>/celular/celular-samsung-galaxy-a36-5g-256gb-8-gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-apple-iphone-17-pro-max-256gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-samsung-galaxy-s25-fe-5g-128gb-8-gb?_lc=11</t>
   </si>
   <si>
     <t>/celular/celular-samsung-galaxy-a17-256gb-8-gb?_lc=11</t>
   </si>
   <si>
-    <t>/celular/celular-samsung-galaxy-s25-fe-5g-128gb-8-gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-samsung-galaxy-a36-5g-256gb-8-gb?_lc=11</t>
+    <t>/celular/celular-samsung-galaxy-a07-4g-128gb-4-gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-samsung-galaxy-s25-fe-5g-256gb-8-gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/smartphone-samsung-galaxy-s24-ultra-5g-256gb-camera-quadrupla?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/smartphone-apple-iphone-16-128gb-camera-dupla?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-apple-iphone-16e-128gb-8-gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/smartphone-apple-iphone-15-128gb-camera-dupla?_lc=11</t>
   </si>
   <si>
     <t>/celular/smartphone-samsung-galaxy-s24-5g-256gb?_lc=11</t>
   </si>
   <si>
-    <t>/celular/celular-apple-iphone-17-pro-max-256gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-samsung-galaxy-a07-4g-128gb-4-gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/smartphone-apple-iphone-15-128gb-camera-dupla?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/smartphone-apple-iphone-16-128gb-camera-dupla?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/smartphone-samsung-galaxy-s24-ultra-5g-256gb-camera-quadrupla?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-apple-iphone-16e-128gb-8-gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-samsung-galaxy-s25-fe-5g-256gb-8-gb?_lc=11</t>
-  </si>
-  <si>
     <t>/celular/celular-samsung-galaxy-s25-plus-5g-256gb-12-gb?_lc=11</t>
   </si>
   <si>
+    <t>/celular/celular-motorola-moto-g86-5g-256gb-8-gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-samsung-galaxy-a07-4g-256gb-8-gb?_lc=11</t>
+  </si>
+  <si>
     <t>/celular/celular-samsung-galaxy-s25-5g-256gb-12-gb?_lc=11</t>
   </si>
   <si>
-    <t>/celular/celular-motorola-moto-g86-5g-256gb-8-gb?_lc=11</t>
+    <t>/celular/celular-samsung-galaxy-s25-ultra-5g-256gb-12-gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-samsung-a57-256gb-8-gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-samsung-galaxy-s25-plus-5g-512gb-12-gb?_lc=11</t>
   </si>
   <si>
     <t>/celular/celular-samsung-galaxy-a56-5g-128gb-8-gb?_lc=11</t>
   </si>
   <si>
-    <t>/celular/celular-samsung-galaxy-a07-4g-256gb-8-gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-samsung-a57-256gb-8-gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-samsung-galaxy-s25-plus-5g-512gb-12-gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-samsung-galaxy-s25-ultra-5g-256gb-12-gb?_lc=11</t>
+    <t>/celular/celular-samsung-galaxy-s26-5g-256gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-samsung-galaxy-a36-5g-128gb-6-gb?_lc=11</t>
   </si>
   <si>
     <t>/celular/celular-xiaomi-redmi-15-256gb-8-gb?_lc=11</t>
@@ -463,61 +466,67 @@
     <t>/celular/celular-motorola-moto-edge-60-pro-5g-256gb-12-gb?_lc=11</t>
   </si>
   <si>
+    <t>/celular/celular-xiaomi-x8-poco-pro-256gb-8-gb?_lc=11</t>
+  </si>
+  <si>
     <t>/celular/smartphone-apple-iphone-15-pro-max-256gb-camera-tripla?_lc=11</t>
   </si>
   <si>
-    <t>/celular/celular-samsung-galaxy-a36-5g-128gb-6-gb?_lc=11</t>
+    <t>/celular/celular-samsung-galaxy-s25-ultra-5g-512gb-12-gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-apple-iphone-17-pro-256gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-samsung-galaxy-s26-ultra-5g-256gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-xiaomi-pocophone-poco-x7-256gb-8-gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/smartphone-apple-iphone-16-256gb-camera-dupla?_lc=11</t>
   </si>
   <si>
     <t>/celular/celular-samsung-galaxy-a25-5g-256gb-8-gb?_lc=11</t>
   </si>
   <si>
-    <t>/celular/celular-samsung-galaxy-s26-5g-256gb?_lc=11</t>
+    <t>/celular/celular-samsung-galaxy-a26-256gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-motorola-edge-60-fusion-5g-256gb-8-gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-samsung-galaxy-s24-fe-5g-256gb-8-gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/smartphone-apple-iphone-13-256gb-ios?_lc=11</t>
   </si>
   <si>
     <t>/celular/celular-motorola-moto-g35-5g-128gb-12-gb?_lc=11</t>
   </si>
   <si>
-    <t>/celular/celular-xiaomi-x8-poco-pro-256gb-8-gb?_lc=11</t>
+    <t>/celular/celular-samsung-a57-128gb-8-gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-motorola-edge-70-fusion-5g-256gb-8-gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-samsung-galaxy-a17-4g-128gb-4-gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/smartphone-apple-iphone-14-plus-256gb-camera-dupla?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-xiaomi-poco-c85-256gb-8-gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-samsung-galaxy-a17-4g-256gb-8-gb?_lc=11</t>
   </si>
   <si>
     <t>/celular/celular-apple-iphone-17e-5g-256gb?_lc=11</t>
   </si>
   <si>
-    <t>/celular/celular-samsung-galaxy-s25-ultra-5g-512gb-12-gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/smartphone-apple-iphone-13-256gb-ios?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-samsung-galaxy-a26-256gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-xiaomi-poco-c85-256gb-8-gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/smartphone-apple-iphone-16-256gb-camera-dupla?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-samsung-a57-128gb-8-gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-apple-iphone-17-pro-256gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-samsung-galaxy-a17-4g-256gb-8-gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-xiaomi-pocophone-poco-x7-256gb-8-gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-samsung-galaxy-s24-fe-5g-256gb-8-gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/smartphone-apple-iphone-14-plus-256gb-camera-dupla?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-motorola-edge-60-fusion-5g-256gb-8-gb?_lc=11</t>
+    <t>/celular/celular-motorola-moto-g56-256gb-8-gb?_lc=11</t>
   </si>
   <si>
     <t>/celular/celular-xiaomi-x8-poco-pro-512gb-12-gb?_lc=11</t>
@@ -526,292 +535,289 @@
     <t>/celular/celular-xiaomi-x8-poco-pro-max-512gb-12-gb?_lc=11</t>
   </si>
   <si>
-    <t>/celular/celular-motorola-moto-g56-256gb-8-gb?_lc=11</t>
+    <t>/celular/celular-motorola-moto-g-g06-128gb-4-gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-xiaomi-redmi-note-15-pro-5g-256gb-8-gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-xiaomi-redmi-note-14-256gb-8-gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-xiaomi-pocophone-poco-x7-pro-5g-512gb-12-gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/smartphone-apple-iphone-14-pro-256gb-camera-tripla?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-motorola-moto-g35-5g-256gb-12-gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-motorola-edge-60-5g-512gb-12-gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/smartphone-samsung-galaxy-a05s-128gb-camera-tripla?_lc=11</t>
   </si>
   <si>
     <t>/celular/celular-motorola-moto-g75-5g-256gb-16-gb?_lc=11</t>
   </si>
   <si>
-    <t>/celular/celular-xiaomi-pocophone-poco-x7-pro-5g-512gb-12-gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-motorola-edge-60-5g-512gb-12-gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-motorola-edge-70-fusion-5g-256gb-8-gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-samsung-galaxy-a17-4g-128gb-4-gb?_lc=11</t>
+    <t>/celular/celular-apple-iphone-17-pro-max-512gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-motorola-edge-60-pro-512gb-12-gb?_lc=11</t>
   </si>
   <si>
     <t>/celular/celular-xiaomi-pocophone-poco-x7-pro-5g-256gb-8-gb?_lc=11</t>
   </si>
   <si>
-    <t>/celular/celular-xiaomi-redmi-note-15-pro-5g-256gb-8-gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-xiaomi-redmi-note-14-256gb-8-gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-motorola-moto-g35-5g-256gb-12-gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/smartphone-apple-iphone-14-pro-256gb-camera-tripla?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/smartphone-samsung-galaxy-a05s-128gb-camera-tripla?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-xiaomi-x8-poco-pro-512gb-8-gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/smartphone-apple-iphone-15-plus-iphone-256gb-camera-dupla?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-xiaomi-redmi-note-15-pro-5g-512gb-8-gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-motorola-edge-60-pro-512gb-12-gb?_lc=11</t>
+    <t>5578</t>
   </si>
   <si>
     <t>2287</t>
   </si>
   <si>
-    <t>5449</t>
+    <t>1519</t>
+  </si>
+  <si>
+    <t>8261</t>
+  </si>
+  <si>
+    <t>2638</t>
   </si>
   <si>
     <t>1374</t>
   </si>
   <si>
-    <t>2557</t>
-  </si>
-  <si>
-    <t>1688</t>
-  </si>
-  <si>
-    <t>2559</t>
-  </si>
-  <si>
-    <t>8499</t>
-  </si>
-  <si>
     <t>594</t>
   </si>
   <si>
-    <t>3851</t>
-  </si>
-  <si>
-    <t>4829</t>
+    <t>3123</t>
   </si>
   <si>
     <t>4249</t>
   </si>
   <si>
+    <t>4599</t>
+  </si>
+  <si>
     <t>3498</t>
   </si>
   <si>
-    <t>3124</t>
+    <t>4099</t>
+  </si>
+  <si>
+    <t>2347</t>
   </si>
   <si>
     <t>4047</t>
   </si>
   <si>
+    <t>1494</t>
+  </si>
+  <si>
+    <t>789</t>
+  </si>
+  <si>
     <t>3758</t>
   </si>
   <si>
-    <t>1495</t>
+    <t>5199</t>
+  </si>
+  <si>
+    <t>2443</t>
+  </si>
+  <si>
+    <t>4311</t>
   </si>
   <si>
     <t>1999</t>
   </si>
   <si>
-    <t>799</t>
-  </si>
-  <si>
-    <t>2443</t>
-  </si>
-  <si>
-    <t>4311</t>
-  </si>
-  <si>
-    <t>5549</t>
-  </si>
-  <si>
-    <t>915</t>
+    <t>4192</t>
+  </si>
+  <si>
+    <t>1399</t>
+  </si>
+  <si>
+    <t>1175</t>
   </si>
   <si>
     <t>2591</t>
   </si>
   <si>
+    <t>2199</t>
+  </si>
+  <si>
     <t>5642</t>
   </si>
   <si>
-    <t>1399</t>
+    <t>5865</t>
+  </si>
+  <si>
+    <t>7892</t>
+  </si>
+  <si>
+    <t>6652</t>
+  </si>
+  <si>
+    <t>1699</t>
+  </si>
+  <si>
+    <t>5399</t>
   </si>
   <si>
     <t>1131</t>
   </si>
   <si>
-    <t>4197</t>
-  </si>
-  <si>
-    <t>789</t>
-  </si>
-  <si>
-    <t>2294</t>
-  </si>
-  <si>
-    <t>4699</t>
-  </si>
-  <si>
-    <t>5865</t>
-  </si>
-  <si>
-    <t>2512</t>
-  </si>
-  <si>
     <t>1421</t>
   </si>
   <si>
+    <t>1715</t>
+  </si>
+  <si>
+    <t>2775</t>
+  </si>
+  <si>
+    <t>3009</t>
+  </si>
+  <si>
+    <t>917</t>
+  </si>
+  <si>
+    <t>1954</t>
+  </si>
+  <si>
+    <t>1847</t>
+  </si>
+  <si>
+    <t>729</t>
+  </si>
+  <si>
+    <t>3325</t>
+  </si>
+  <si>
     <t>939</t>
   </si>
   <si>
-    <t>5299</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>8776</t>
-  </si>
-  <si>
     <t>1164</t>
   </si>
   <si>
-    <t>1699</t>
-  </si>
-  <si>
-    <t>2775</t>
+    <t>4499</t>
+  </si>
+  <si>
+    <t>1359</t>
+  </si>
+  <si>
+    <t>2649</t>
   </si>
   <si>
     <t>3499</t>
   </si>
   <si>
-    <t>1754</t>
-  </si>
-  <si>
-    <t>2719</t>
-  </si>
-  <si>
-    <t>3399</t>
-  </si>
-  <si>
-    <t>1359</t>
+    <t>598</t>
+  </si>
+  <si>
+    <t>1919</t>
+  </si>
+  <si>
+    <t>1210</t>
+  </si>
+  <si>
+    <t>2407</t>
+  </si>
+  <si>
+    <t>4084</t>
+  </si>
+  <si>
+    <t>999</t>
+  </si>
+  <si>
+    <t>2124</t>
+  </si>
+  <si>
+    <t>635</t>
   </si>
   <si>
     <t>1785</t>
   </si>
   <si>
-    <t>2407</t>
-  </si>
-  <si>
-    <t>1847</t>
-  </si>
-  <si>
-    <t>749</t>
+    <t>10169</t>
+  </si>
+  <si>
+    <t>2999</t>
   </si>
   <si>
     <t>2100</t>
   </si>
   <si>
-    <t>1954</t>
-  </si>
-  <si>
-    <t>1210</t>
-  </si>
-  <si>
-    <t>1019</t>
-  </si>
-  <si>
-    <t>4008</t>
-  </si>
-  <si>
-    <t>635</t>
-  </si>
-  <si>
-    <t>2537</t>
-  </si>
-  <si>
-    <t>4949</t>
-  </si>
-  <si>
-    <t>2188</t>
-  </si>
-  <si>
-    <t>2999</t>
+    <t>https://i.zst.com.br/thumbs/45/15/19/-1584053110.jpg</t>
   </si>
   <si>
     <t>https://i.zst.com.br/thumbs/45/1e/30/-1482643704.jpg</t>
   </si>
   <si>
-    <t>https://i.zst.com.br/thumbs/45/15/19/-1584053110.jpg</t>
+    <t>https://i.zst.com.br/thumbs/45/15/16/-1533149317.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/2c/3a/-1584066151.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/39/14/-1591251808.jpg</t>
   </si>
   <si>
     <t>https://i.zst.com.br/thumbs/45/16/30/-1584401187.jpg</t>
   </si>
   <si>
-    <t>https://i.zst.com.br/thumbs/45/39/14/-1591251808.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/15/16/-1533149317.jpg</t>
+    <t>https://i.zst.com.br/thumbs/45/f/35/-1597645208.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/30/14/-1591252595.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/30/17/-1202498267.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/16/f/-1346812222.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/12/32/-1472883387.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/19/31/-1113972290.jpg</t>
   </si>
   <si>
     <t>https://i.zst.com.br/thumbs/45/3d/11/-1202542340.jpg</t>
   </si>
   <si>
-    <t>https://i.zst.com.br/thumbs/45/2c/3a/-1584066151.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/f/35/-1597645208.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/19/31/-1113972290.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/16/f/-1346812222.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/30/17/-1202498267.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/12/32/-1472883387.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/30/14/-1591252595.jpg</t>
-  </si>
-  <si>
     <t>https://i.zst.com.br/thumbs/45/37/2f/-1451536322.jpg</t>
   </si>
   <si>
+    <t>https://i.zst.com.br/thumbs/45/2e/2d/-1603821631.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/2c/35/-1597643414.jpg</t>
+  </si>
+  <si>
     <t>https://i.zst.com.br/thumbs/45/37/3b/-1449465281.jpg</t>
   </si>
   <si>
-    <t>https://i.zst.com.br/thumbs/45/2e/2d/-1603821631.jpg</t>
+    <t>https://i.zst.com.br/thumbs/45/18/3d/-1449484750.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/24/14/-1693348668.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/b/10/-1451545519.jpg</t>
   </si>
   <si>
     <t>https://i.zst.com.br/thumbs/45/32/30/-1482641322.jpg</t>
   </si>
   <si>
-    <t>https://i.zst.com.br/thumbs/45/2c/35/-1597643414.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/24/14/-1693348668.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/b/10/-1451545519.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/18/3d/-1449484750.jpg</t>
+    <t>https://i.zst.com.br/thumbs/45/2b/0/-1678192945.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/11/f/-1524507737.jpg</t>
   </si>
   <si>
     <t>https://i.zst.com.br/thumbs/45/3a/3a/-1598683126.jpg</t>
@@ -820,61 +826,67 @@
     <t>https://i.zst.com.br/thumbs/45/1a/1c/-1529478118.jpg</t>
   </si>
   <si>
+    <t>https://i.zst.com.br/thumbs/45/2/12/-1683989765.jpg</t>
+  </si>
+  <si>
     <t>https://i.zst.com.br/thumbs/45/a/13/-1114650735.jpg</t>
   </si>
   <si>
-    <t>https://i.zst.com.br/thumbs/45/11/f/-1524507737.jpg</t>
+    <t>https://i.zst.com.br/thumbs/45/1c/14/-1449500134.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/3f/1b/-1584074872.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/2a/1b/-1678471943.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/1b/1d/-1448497225.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/1c/37/-1347442557.jpg</t>
   </si>
   <si>
     <t>https://i.zst.com.br/thumbs/45/29/33/-1421244724.jpg</t>
   </si>
   <si>
-    <t>https://i.zst.com.br/thumbs/45/2b/0/-1678192945.jpg</t>
+    <t>https://i.zst.com.br/thumbs/45/30/33/-1475648263.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/d/13/-1500036474.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/5/15/-1358966033.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/23/11/-747056146.jpg</t>
   </si>
   <si>
     <t>https://i.zst.com.br/thumbs/45/29/2e/-1554937995.jpg</t>
   </si>
   <si>
-    <t>https://i.zst.com.br/thumbs/45/2/12/-1683989765.jpg</t>
+    <t>https://i.zst.com.br/thumbs/45/15/14/-1693349843.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/d/15/-1680059930.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/39/30/-1678916430.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/31/1c/-871936652.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/14/37/-1591284000.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/35/30/-1678917590.jpg</t>
   </si>
   <si>
     <t>https://i.zst.com.br/thumbs/45/11/12/-1679706169.jpg</t>
   </si>
   <si>
-    <t>https://i.zst.com.br/thumbs/45/1c/14/-1449500134.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/23/11/-747056146.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/30/33/-1475648263.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/14/37/-1591284000.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/1c/37/-1347442557.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/15/14/-1693349843.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/3f/1b/-1584074872.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/35/30/-1678917590.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/1b/1d/-1448497225.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/5/15/-1358966033.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/31/1c/-871936652.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/d/13/-1500036474.jpg</t>
+    <t>https://i.zst.com.br/thumbs/45/10/30/-1532643273.jpg</t>
   </si>
   <si>
     <t>https://i.zst.com.br/thumbs/45/3e/33/-1683990601.jpg</t>
@@ -883,232 +895,40 @@
     <t>https://i.zst.com.br/thumbs/45/d/33/-1683996479.jpg</t>
   </si>
   <si>
-    <t>https://i.zst.com.br/thumbs/45/10/30/-1532643273.jpg</t>
+    <t>https://i.zst.com.br/thumbs/45/11/11/-1590231539.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/2b/3f/-1687085680.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/34/1e/-1449381969.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/33/19/-1446255064.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/12/11/-845276527.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/b/14/-1533234478.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/3a/1a/-1505387439.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/3f/15/-1206545191.jpg</t>
   </si>
   <si>
     <t>https://i.zst.com.br/thumbs/45/1e/36/-1420399903.jpg</t>
   </si>
   <si>
-    <t>https://i.zst.com.br/thumbs/45/33/19/-1446255064.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/3a/1a/-1505387439.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/d/15/-1680059930.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/39/30/-1678916430.jpg</t>
+    <t>https://i.zst.com.br/thumbs/45/3/1b/-1584070252.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/2a/33/-1505424683.jpg</t>
   </si>
   <si>
     <t>https://i.zst.com.br/thumbs/45/6/f/-1532413784.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/2b/3f/-1687085680.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/34/1e/-1449381969.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/b/14/-1533234478.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/12/11/-845276527.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/3f/15/-1206545191.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/4/33/-1683990402.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/15/1d/-1114090902.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/3b/31/-1661334126.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/2a/33/-1505424683.jpg</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13991986, 'date': '2025-07-07', 'price': 2193.0, 'merchantId': 34}, {'prodId': 13991986, 'date': '2025-07-08', 'price': 2249.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2025-07-09', 'price': 2099.0, 'merchantId': 10763}, {'prodId': 13991986, 'date': '2025-07-10', 'price': 2099.0, 'merchantId': 10763}, {'prodId': 13991986, 'date': '2025-07-11', 'price': 2249.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2025-07-12', 'price': 2099.0, 'merchantId': 10763}, {'prodId': 13991986, 'date': '2025-07-13', 'price': 2249.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2025-07-14', 'price': 2249.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2025-07-15', 'price': 2199.0, 'merchantId': 10763}, {'prodId': 13991986, 'date': '2025-07-16', 'price': 2199.0, 'merchantId': 10763}, {'prodId': 13991986, 'date': '2025-07-17', 'price': 2199.0, 'merchantId': 10763}, {'prodId': 13991986, 'date': '2025-07-18', 'price': 2199.0, 'merchantId': 10763}, {'prodId': 13991986, 'date': '2025-07-19', 'price': 2199.0, 'merchantId': 10763}, {'prodId': 13991986, 'date': '2025-07-20', 'price': 2199.0, 'merchantId': 10763}, {'prodId': 13991986, 'date': '2025-07-21', 'price': 2199.0, 'merchantId': 10763}, {'prodId': 13991986, 'date': '2025-07-22', 'price': 2199.0, 'merchantId': 10763}, {'prodId': 13991986, 'date': '2025-07-23', 'price': 2199.0, 'merchantId': 10763}, {'prodId': 13991986, 'date': '2025-07-24', 'price': 2199.0, 'merchantId': 10763}, {'prodId': 13991986, 'date': '2025-07-25', 'price': 2199.0, 'merchantId': 10763}, {'prodId': 13991986, 'date': '2025-07-26', 'price': 2249.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2025-07-27', 'price': 2249.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2025-07-28', 'price': 2239.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2025-07-29', 'price': 2239.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2025-07-30', 'price': 2159.1, 'merchantId': 1582}, {'prodId': 13991986, 'date': '2025-07-31', 'price': 2159.1, 'merchantId': 1582}, {'prodId': 13991986, 'date': '2025-08-01', 'price': 2239.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2025-08-02', 'price': 2039.15, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2025-08-03', 'price': 2039.15, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2025-08-04', 'price': 2239.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2025-08-05', 'price': 2039.15, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2025-08-06', 'price': 2239.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2025-08-07', 'price': 2239.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2025-08-08', 'price': 2224.11, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2025-08-09', 'price': 2224.11, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2025-08-10', 'price': 2224.11, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2025-08-11', 'price': 2224.11, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2025-08-12', 'price': 2224.11, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2025-08-13', 'price': 1999.0, 'merchantId': 22902}, {'prodId': 13991986, 'date': '2025-08-14', 'price': 1999.0, 'merchantId': 22902}, {'prodId': 13991986, 'date': '2025-08-15', 'price': 1999.0, 'merchantId': 22902}, {'prodId': 13991986, 'date': '2025-08-16', 'price': 1999.0, 'merchantId': 22902}, {'prodId': 13991986, 'date': '2025-08-17', 'price': 1999.0, 'merchantId': 22902}, {'prodId': 13991986, 'date': '2025-08-18', 'price': 1999.0, 'merchantId': 22902}, {'prodId': 13991986, 'date': '2025-08-19', 'price': 1999.0, 'merchantId': 22902}, {'prodId': 13991986, 'date': '2025-08-20', 'price': 2226.9, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2025-08-21', 'price': 2216.9, 'merchantId': 1582}, {'prodId': 13991986, 'date': '2025-08-22', 'price': 2159.1, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2025-08-23', 'price': 2159.1, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2025-08-24', 'price': 2159.1, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2025-08-25', 'price': 2159.1, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2025-08-26', 'price': 2239.0, 'merchantId': 23254}, {'prodId': 13991986, 'date': '2025-08-27', 'price': 2149.2, 'merchantId': 4}, {'prodId': 13991986, 'date': '2025-08-28', 'price': 2149.2, 'merchantId': 4}, {'prodId': 13991986, 'date': '2025-08-29', 'price': 2149.2, 'merchantId': 4}, {'prodId': 13991986, 'date': '2025-08-30', 'price': 2149.2, 'merchantId': 4}, {'prodId': 13991986, 'date': '2025-08-31', 'price': 1655.93, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2025-09-01', 'price': 1983.24, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2025-09-02', 'price': 2148.3, 'merchantId': 22902}, {'prodId': 13991986, 'date': '2025-09-03', 'price': 2067.12, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2025-09-04', 'price': 2067.12, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2025-09-05', 'price': 2021.18, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2025-09-06', 'price': 2067.12, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2025-09-07', 'price': 2067.12, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2025-09-08', 'price': 1999.9, 'merchantId': 5}, {'prodId': 13991986, 'date': '2025-09-09', 'price': 2067.12, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2025-09-10', 'price': 2056.16, 'merchantId': 5}, {'prodId': 13991986, 'date': '2025-09-11', 'price': 2056.16, 'merchantId': 5}, {'prodId': 13991986, 'date': '2025-09-12', 'price': 2056.16, 'merchantId': 5}, {'prodId': 13991986, 'date': '2025-09-13', 'price': 2056.16, 'merchantId': 5}, {'prodId': 13991986, 'date': '2025-09-14', 'price': 2056.16, 'merchantId': 5}, {'prodId': 13991986, 'date': '2025-09-15', 'price': 2149.2, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2025-09-16', 'price': 2109.9, 'merchantId': 16108}, {'prodId': 13991986, 'date': '2025-09-17', 'price': 2109.9, 'merchantId': 16108}, {'prodId': 13991986, 'date': '2025-09-18', 'price': 2109.9, 'merchantId': 16108}, {'prodId': 13991986, 'date': '2025-09-19', 'price': 1969.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2025-09-20', 'price': 1969.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2025-09-21', 'price': 1969.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2025-09-22', 'price': 2137.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2025-09-23', 'price': 1938.0, 'merchantId': 1582}, {'prodId': 13991986, 'date': '2025-09-24', 'price': 1938.0, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2025-09-25', 'price': 2090.0, 'merchantId': 20612}, {'prodId': 13991986, 'date': '2025-09-26', 'price': 2090.0, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2025-09-27', 'price': 2090.0, 'merchantId': 20612}, {'prodId': 13991986, 'date': '2025-09-28', 'price': 2090.0, 'merchantId': 23254}, {'prodId': 13991986, 'date': '2025-09-29', 'price': 2090.0, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2025-09-30', 'price': 2090.0, 'merchantId': 20609}, {'prodId': 13991986, 'date': '2025-10-01', 'price': 2139.9, 'merchantId': 16108}, {'prodId': 13991986, 'date': '2025-10-02', 'price': 2139.9, 'merchantId': 16108}, {'prodId': 13991986, 'date': '2025-10-03', 'price': 2149.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2025-10-04', 'price': 2149.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2025-10-05', 'price': 2149.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2025-10-06', 'price': 2149.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2025-10-07', 'price': 2149.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2025-10-08', 'price': 2069.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2025-10-09', 'price': 2068.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2025-10-10', 'price': 2068.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2025-10-11', 'price': 2068.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2025-10-12', 'price': 2068.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2025-10-13', 'price': 2068.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2025-10-14', 'price': 2068.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2025-10-15', 'price': 2042.31, 'merchantId': 245}, {'prodId': 13991986, 'date': '2025-10-16', 'price': 2042.31, 'merchantId': 245}, {'prodId': 13991986, 'date': '2025-10-17', 'price': 2042.31, 'merchantId': 245}, {'prodId': 13991986, 'date': '2025-10-18', 'price': 2042.31, 'merchantId': 245}, {'prodId': 13991986, 'date': '2025-10-19', 'price': 2042.31, 'merchantId': 245}, {'prodId': 13991986, 'date': '2025-10-20', 'price': 1999.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2025-10-21', 'price': 1998.99, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2025-10-22', 'price': 1999.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2025-10-23', 'price': 2042.31, 'merchantId': 245}, {'prodId': 13991986, 'date': '2025-10-24', 'price': 2042.31, 'merchantId': 245}, {'prodId': 13991986, 'date': '2025-10-25', 'price': 2042.31, 'merchantId': 245}, {'prodId': 13991986, 'date': '2025-10-26', 'price': 2042.31, 'merchantId': 245}, {'prodId': 13991986, 'date': '2025-10-27', 'price': 2042.31, 'merchantId': 245}, {'prodId': 13991986, 'date': '2025-10-28', 'price': 2144.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2025-10-29', 'price': 2144.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2025-10-30', 'price': 2144.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2025-10-31', 'price': 2044.43, 'merchantId': 23254}, {'prodId': 13991986, 'date': '2025-11-01', 'price': 1999.0, 'merchantId': 23254}, {'prodId': 13991986, 'date': '2025-11-02', 'price': 1999.0, 'merchantId': 23254}, {'prodId': 13991986, 'date': '2025-11-03', 'price': 1999.0, 'merchantId': 20612}, {'prodId': 13991986, 'date': '2025-11-04', 'price': 1970.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2025-11-05', 'price': 1970.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2025-11-06', 'price': 1913.08, 'merchantId': 245}, {'prodId': 13991986, 'date': '2025-11-07', 'price': 1871.5, 'merchantId': 245}, {'prodId': 13991986, 'date': '2025-11-08', 'price': 1970.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2025-11-09', 'price': 1970.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2025-11-10', 'price': 1970.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2025-11-11', 'price': 1970.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2025-11-12', 'price': 1970.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2025-11-13', 'price': 1970.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2025-11-14', 'price': 1970.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2025-11-15', 'price': 1970.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2025-11-16', 'price': 1970.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2025-11-17', 'price': 1970.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2025-11-18', 'price': 1999.0, 'merchantId': 20612}, {'prodId': 13991986, 'date': '2025-11-19', 'price': 1871.5, 'merchantId': 245}, {'prodId': 13991986, 'date': '2025-11-20', 'price': 1871.5, 'merchantId': 245}, {'prodId': 13991986, 'date': '2025-11-21', 'price': 1871.5, 'merchantId': 245}, {'prodId': 13991986, 'date': '2025-11-22', 'price': 1913.08, 'merchantId': 245}, {'prodId': 13991986, 'date': '2025-11-23', 'price': 1913.08, 'merchantId': 245}, {'prodId': 13991986, 'date': '2025-11-24', 'price': 1913.08, 'merchantId': 245}, {'prodId': 13991986, 'date': '2025-11-25', 'price': 1941.16, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2025-11-26', 'price': 1941.08, 'merchantId': 23326}, {'prodId': 13991986, 'date': '2025-11-27', 'price': 1919.59, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2025-11-28', 'price': 1897.1, 'merchantId': 23326}, {'prodId': 13991986, 'date': '2025-11-29', 'price': 1889.1, 'merchantId': 1582}, {'prodId': 13991986, 'date': '2025-11-30', 'price': 1919.59, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2025-12-01', 'price': 1889.1, 'merchantId': 1582}, {'prodId': 13991986, 'date': '2025-12-02', 'price': 1919.59, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2025-12-03', 'price': 1919.59, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2025-12-04', 'price': 1919.59, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2025-12-05', 'price': 1934.0, 'merchantId': 23326}, {'prodId': 13991986, 'date': '2025-12-06', 'price': 1934.0, 'merchantId': 23326}, {'prodId': 13991986, 'date': '2025-12-07', 'price': 1934.0, 'merchantId': 23326}, {'prodId': 13991986, 'date': '2025-12-08', 'price': 1934.0, 'merchantId': 23326}, {'prodId': 13991986, 'date': '2025-12-09', 'price': 1941.16, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2025-12-10', 'price': 1941.16, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2025-12-11', 'price': 1941.16, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2025-12-12', 'price': 1941.16, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2025-12-13', 'price': 1941.16, 'merchantId': 20612}, {'prodId': 13991986, 'date': '2025-12-14', 'price': 1941.16, 'merchantId': 20612}, {'prodId': 13991986, 'date': '2025-12-15', 'price': 1941.16, 'merchantId': 20612}, {'prodId': 13991986, 'date': '2025-12-16', 'price': 2018.79, 'merchantId': 20612}, {'prodId': 13991986, 'date': '2025-12-17', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2025-12-18', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2025-12-19', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2025-12-20', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2025-12-21', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2025-12-22', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2025-12-23', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2025-12-24', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2025-12-25', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2025-12-26', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2025-12-27', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2025-12-28', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2025-12-29', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2025-12-30', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2025-12-31', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-01', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-02', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-03', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-04', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-05', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-06', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-07', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-08', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-09', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-10', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-11', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-12', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-13', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-14', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-15', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-16', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-17', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-18', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-19', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-20', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-21', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-22', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-23', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-24', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-25', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-26', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-27', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-28', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-29', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-30', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-01-31', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-02-01', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-02-02', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-02-03', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-02-04', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-02-05', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-02-06', 'price': 2049.0, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-02-07', 'price': 2298.9, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2026-02-08', 'price': 2298.9, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2026-02-09', 'price': 2298.9, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2026-02-10', 'price': 2298.9, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2026-02-11', 'price': 2298.9, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2026-02-12', 'price': 2298.9, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2026-02-13', 'price': 2298.9, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2026-02-14', 'price': 2298.9, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2026-02-15', 'price': 2298.9, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2026-02-16', 'price': 2298.9, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2026-02-17', 'price': 2298.9, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2026-02-18', 'price': 2298.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2026-02-19', 'price': 2297.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2026-02-20', 'price': 2296.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2026-02-21', 'price': 2296.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2026-02-22', 'price': 2289.0, 'merchantId': 34}, {'prodId': 13991986, 'date': '2026-02-23', 'price': 2288.9, 'merchantId': 4}, {'prodId': 13991986, 'date': '2026-02-24', 'price': 2288.9, 'merchantId': 4}, {'prodId': 13991986, 'date': '2026-02-25', 'price': 2288.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2026-02-26', 'price': 2287.0, 'merchantId': 23326}, {'prodId': 13991986, 'date': '2026-02-27', 'price': 2286.0, 'merchantId': 23326}, {'prodId': 13991986, 'date': '2026-02-28', 'price': 2210.52, 'merchantId': 1582}, {'prodId': 13991986, 'date': '2026-03-01', 'price': 2279.0, 'merchantId': 23326}, {'prodId': 13991986, 'date': '2026-03-02', 'price': 2279.0, 'merchantId': 23326}, {'prodId': 13991986, 'date': '2026-03-03', 'price': 2249.1, 'merchantId': 22902}, {'prodId': 13991986, 'date': '2026-03-04', 'price': 2210.52, 'merchantId': 1582}, {'prodId': 13991986, 'date': '2026-03-05', 'price': 2248.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2026-03-06', 'price': 2247.3, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2026-03-07', 'price': 2247.3, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2026-03-08', 'price': 2296.8, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2026-03-09', 'price': 2249.1, 'merchantId': 16108}, {'prodId': 13991986, 'date': '2026-03-10', 'price': 2210.52, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2026-03-11', 'price': 2229.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2026-03-12', 'price': 2129.9, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2026-03-13', 'price': 2229.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2026-03-14', 'price': 2229.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2026-03-15', 'price': 2229.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2026-03-16', 'price': 2229.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2026-03-17', 'price': 2229.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2026-03-18', 'price': 2229.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2026-03-19', 'price': 2229.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2026-03-20', 'price': 2229.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2026-03-21', 'price': 2229.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2026-03-22', 'price': 2229.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2026-03-23', 'price': 2229.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2026-03-24', 'price': 2229.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2026-03-25', 'price': 2229.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2026-03-26', 'price': 2229.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2026-03-27', 'price': 2099.9, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2026-03-28', 'price': 2135.9, 'merchantId': 1582}, {'prodId': 13991986, 'date': '2026-03-29', 'price': 2229.0, 'merchantId': 21628}, {'prodId': 13991986, 'date': '2026-03-30', 'price': 2159.0, 'merchantId': 23326}, {'prodId': 13991986, 'date': '2026-03-31', 'price': 2135.11, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2026-04-01', 'price': 2135.11, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2026-04-02', 'price': 2099.9, 'merchantId': 1582}, {'prodId': 13991986, 'date': '2026-04-03', 'price': 2158.0, 'merchantId': 23326}, {'prodId': 13991986, 'date': '2026-04-04', 'price': 2158.0, 'merchantId': 23326}, {'prodId': 13991986, 'date': '2026-04-05', 'price': 2158.0, 'merchantId': 23326}, {'prodId': 13991986, 'date': '2026-04-06', 'price': 2098.1, 'merchantId': 23326}, {'prodId': 13991986, 'date': '2026-04-07', 'price': 2098.1, 'merchantId': 23326}, {'prodId': 13991986, 'date': '2026-04-08', 'price': 2098.0, 'merchantId': 23326}, {'prodId': 13991986, 'date': '2026-04-09', 'price': 2097.9, 'merchantId': 23326}, {'prodId': 13991986, 'date': '2026-04-10', 'price': 2097.0, 'merchantId': 23326}, {'prodId': 13991986, 'date': '2026-04-11', 'price': 2097.0, 'merchantId': 23326}, {'prodId': 13991986, 'date': '2026-04-12', 'price': 2050.4, 'merchantId': 245}, {'prodId': 13991986, 'date': '2026-04-13', 'price': 2050.4, 'merchantId': 245}, {'prodId': 13991986, 'date': '2026-04-14', 'price': 1954.58, 'merchantId': 245}, {'prodId': 13991986, 'date': '2026-04-15', 'price': 1953.6, 'merchantId': 245}, {'prodId': 13991986, 'date': '2026-04-16', 'price': 1953.5, 'merchantId': 245}, {'prodId': 13991986, 'date': '2026-04-17', 'price': 1953.5, 'merchantId': 245}, {'prodId': 13991986, 'date': '2026-04-18', 'price': 1976.69, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2026-04-19', 'price': 1976.69, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2026-04-20', 'price': 1976.69, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2026-04-21', 'price': 1954.48, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-04-22', 'price': 1954.48, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-04-23', 'price': 1954.48, 'merchantId': 22905}, {'prodId': 13991986, 'date': '2026-04-24', 'price': 1898.9, 'merchantId': 4}, {'prodId': 13991986, 'date': '2026-04-25', 'price': 1898.9, 'merchantId': 4}, {'prodId': 13991986, 'date': '2026-04-26', 'price': 1898.9, 'merchantId': 245}, {'prodId': 13991986, 'date': '2026-04-27', 'price': 1898.9, 'merchantId': 245}, {'prodId': 13991986, 'date': '2026-04-28', 'price': 1997.9, 'merchantId': 245}, {'prodId': 13991986, 'date': '2026-04-29', 'price': 1997.9, 'merchantId': 4}, {'prodId': 13991986, 'date': '2026-04-30', 'price': 1997.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2026-05-01', 'price': 1954.58, 'merchantId': 245}, {'prodId': 13991986, 'date': '2026-05-02', 'price': 1954.58, 'merchantId': 245}, {'prodId': 13991986, 'date': '2026-05-03', 'price': 1954.58, 'merchantId': 245}, {'prodId': 13991986, 'date': '2026-05-04', 'price': 1935.0, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2026-05-05', 'price': 1935.0, 'merchantId': 34}, {'prodId': 13991986, 'date': '2026-05-06', 'price': 1944.9, 'merchantId': 1582}, {'prodId': 13991986, 'date': '2026-05-07', 'price': 1944.9, 'merchantId': 1582}, {'prodId': 13991986, 'date': '2026-05-08', 'price': 1954.58, 'merchantId': 23326}, {'prodId': 13991986, 'date': '2026-05-09', 'price': 1954.58, 'merchantId': 23326}, {'prodId': 13991986, 'date': '2026-05-10', 'price': 1954.58, 'merchantId': 23326}, {'prodId': 13991986, 'date': '2026-05-11', 'price': 1954.37, 'merchantId': 23326}, {'prodId': 13991986, 'date': '2026-05-12', 'price': 1954.37, 'merchantId': 23326}, {'prodId': 13991986, 'date': '2026-05-13', 'price': 1841.93, 'merchantId': 1582}, {'prodId': 13991986, 'date': '2026-05-14', 'price': 1998.79, 'merchantId': 4}, {'prodId': 13991986, 'date': '2026-05-15', 'price': 1998.79, 'merchantId': 4}, {'prodId': 13991986, 'date': '2026-05-16', 'price': 1998.79, 'merchantId': 4}, {'prodId': 13991986, 'date': '2026-05-17', 'price': 1998.79, 'merchantId': 34}, {'prodId': 13991986, 'date': '2026-05-18', 'price': 1998.79, 'merchantId': 34}, {'prodId': 13991986, 'date': '2026-05-19', 'price': 1841.93, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2026-05-20', 'price': 1841.93, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2026-05-21', 'price': 1998.79, 'merchantId': 4}, {'prodId': 13991986, 'date': '2026-05-22', 'price': 1954.58, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2026-05-23', 'price': 1841.93, 'merchantId': 1582}, {'prodId': 13991986, 'date': '2026-05-24', 'price': 1998.79, 'merchantId': 4}, {'prodId': 13991986, 'date': '2026-05-25', 'price': 1998.79, 'merchantId': 4}, {'prodId': 13991986, 'date': '2026-05-26', 'price': 1998.79, 'merchantId': 4}, {'prodId': 13991986, 'date': '2026-05-27', 'price': 1954.58, 'merchantId': 20583}, {'prodId': 13991986, 'date': '2026-05-28', 'price': 1998.0, 'merchantId': 4}, {'prodId': 13991986, 'date': '2026-05-29', 'price': 1997.9, 'merchantId': 4}, {'prodId': 13991986, 'date': '2026-05-30', 'price': 1997.9, 'merchantId': 2}, {'prodId': 13991986, 'date': '2026-05-31', 'price': 1997.9, 'merchantId': 4}, {'prodId': 13991986, 'date': '2026-06-01', 'price': 1709.95, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2026-06-02', 'price': 1709.95, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2026-06-03', 'price': 1709.0, 'merchantId': 1582}, {'prodId': 13991986, 'date': '2026-06-04', 'price': 1709.0, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2026-06-05', 'price': 1549.0, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2026-06-06', 'price': 1549.0, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2026-06-07', 'price': 1549.0, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2026-06-08', 'price': 1599.0, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2026-06-09', 'price': 1997.9, 'merchantId': 4}, {'prodId': 13991986, 'date': '2026-06-10', 'price': 1997.9, 'merchantId': 4}, {'prodId': 13991986, 'date': '2026-06-11', 'price': 1599.0, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2026-06-12', 'price': 1997.9, 'merchantId': 4}, {'prodId': 13991986, 'date': '2026-06-13', 'price': 1998.9, 'merchantId': 23254}, {'prodId': 13991986, 'date': '2026-06-14', 'price': 1998.9, 'merchantId': 23254}, {'prodId': 13991986, 'date': '2026-06-15', 'price': 1998.9, 'merchantId': 23254}, {'prodId': 13991986, 'date': '2026-06-16', 'price': 1998.0, 'merchantId': 22902}, {'prodId': 13991986, 'date': '2026-06-17', 'price': 1998.9, 'merchantId': 23254}, {'prodId': 13991986, 'date': '2026-06-18', 'price': 1998.9, 'merchantId': 23254}, {'prodId': 13991986, 'date': '2026-06-19', 'price': 1998.9, 'merchantId': 23254}, {'prodId': 13991986, 'date': '2026-06-20', 'price': 1998.9, 'merchantId': 23254}, {'prodId': 13991986, 'date': '2026-06-21', 'price': 1998.9, 'merchantId': 23254}, {'prodId': 13991986, 'date': '2026-06-22', 'price': 1998.9, 'merchantId': 23254}, {'prodId': 13991986, 'date': '2026-06-23', 'price': 1998.79, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2026-06-24', 'price': 1998.9, 'merchantId': 23254}, {'prodId': 13991986, 'date': '2026-06-25', 'price': 1998.9, 'merchantId': 23254}, {'prodId': 13991986, 'date': '2026-06-26', 'price': 1239.0, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2026-06-27', 'price': 1888.0, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2026-06-28', 'price': 1998.9, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2026-06-29', 'price': 1649.0, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2026-06-30', 'price': 1998.9, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2026-07-01', 'price': 1887.78, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2026-07-02', 'price': 1734.0, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2026-07-03', 'price': 1619.0, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2026-07-04', 'price': 1151.24, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2026-07-05', 'price': 1151.24, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2026-07-06', 'price': 1688.0, 'merchantId': 9385}, {'prodId': 13991986, 'date': '2026-07-07', 'price': 1998.9, 'merchantId': 9385}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13992938, 'date': '2025-09-16', 'price': 7199.1, 'merchantId': 22902}, {'prodId': 13992938, 'date': '2025-09-17', 'price': 7199.1, 'merchantId': 22902}, {'prodId': 13992938, 'date': '2025-09-18', 'price': 7199.1, 'merchantId': 22902}, {'prodId': 13992938, 'date': '2025-09-19', 'price': 7199.1, 'merchantId': 22902}, {'prodId': 13992938, 'date': '2025-09-20', 'price': 7199.1, 'merchantId': 22902}, {'prodId': 13992938, 'date': '2025-09-21', 'price': 7199.1, 'merchantId': 22902}, {'prodId': 13992938, 'date': '2025-09-22', 'price': 7199.1, 'merchantId': 22902}, {'prodId': 13992938, 'date': '2025-09-23', 'price': 7199.1, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-09-24', 'price': 7199.1, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-09-25', 'price': 7199.1, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-09-26', 'price': 7198.95, 'merchantId': 9385}, {'prodId': 13992938, 'date': '2025-09-27', 'price': 7198.95, 'merchantId': 1582}, {'prodId': 13992938, 'date': '2025-09-28', 'price': 7198.95, 'merchantId': 1582}, {'prodId': 13992938, 'date': '2025-09-29', 'price': 7198.95, 'merchantId': 1582}, {'prodId': 13992938, 'date': '2025-09-30', 'price': 7198.95, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2025-10-01', 'price': 7198.95, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2025-10-02', 'price': 7039.12, 'merchantId': 23326}, {'prodId': 13992938, 'date': '2025-10-03', 'price': 7039.12, 'merchantId': 23326}, {'prodId': 13992938, 'date': '2025-10-04', 'price': 7039.12, 'merchantId': 23326}, {'prodId': 13992938, 'date': '2025-10-05', 'price': 7039.12, 'merchantId': 23326}, {'prodId': 13992938, 'date': '2025-10-06', 'price': 7039.12, 'merchantId': 23326}, {'prodId': 13992938, 'date': '2025-10-07', 'price': 7039.12, 'merchantId': 23326}, {'prodId': 13992938, 'date': '2025-10-08', 'price': 7039.12, 'merchantId': 23326}, {'prodId': 13992938, 'date': '2025-10-09', 'price': 7039.12, 'merchantId': 23326}, {'prodId': 13992938, 'date': '2025-10-10', 'price': 7039.12, 'merchantId': 23326}, {'prodId': 13992938, 'date': '2025-10-11', 'price': 7039.12, 'merchantId': 23326}, {'prodId': 13992938, 'date': '2025-10-12', 'price': 7199.0, 'merchantId': 2}, {'prodId': 13992938, 'date': '2025-10-13', 'price': 7198.95, 'merchantId': 21628}, {'prodId': 13992938, 'date': '2025-10-14', 'price': 7198.95, 'merchantId': 21628}, {'prodId': 13992938, 'date': '2025-10-15', 'price': 7198.95, 'merchantId': 9385}, {'prodId': 13992938, 'date': '2025-10-16', 'price': 7198.95, 'merchantId': 9385}, {'prodId': 13992938, 'date': '2025-10-17', 'price': 7198.95, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2025-10-18', 'price': 7039.12, 'merchantId': 23326}, {'prodId': 13992938, 'date': '2025-10-19', 'price': 7039.12, 'merchantId': 23326}, {'prodId': 13992938, 'date': '2025-10-20', 'price': 7039.12, 'merchantId': 23326}, {'prodId': 13992938, 'date': '2025-10-21', 'price': 7198.95, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2025-10-22', 'price': 7198.95, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2025-10-23', 'price': 7039.12, 'merchantId': 23326}, {'prodId': 13992938, 'date': '2025-10-24', 'price': 7198.95, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2025-10-25', 'price': 6799.15, 'merchantId': 23326}, {'prodId': 13992938, 'date': '2025-10-26', 'price': 6799.15, 'merchantId': 23326}, {'prodId': 13992938, 'date': '2025-10-27', 'price': 7198.95, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2025-10-28', 'price': 7198.95, 'merchantId': 1582}, {'prodId': 13992938, 'date': '2025-10-29', 'price': 7198.95, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2025-10-30', 'price': 6799.15, 'merchantId': 23326}, {'prodId': 13992938, 'date': '2025-10-31', 'price': 6799.15, 'merchantId': 23326}, {'prodId': 13992938, 'date': '2025-11-01', 'price': 6799.15, 'merchantId': 23326}, {'prodId': 13992938, 'date': '2025-11-02', 'price': 6799.15, 'merchantId': 23326}, {'prodId': 13992938, 'date': '2025-11-03', 'price': 6799.15, 'merchantId': 23326}, {'prodId': 13992938, 'date': '2025-11-04', 'price': 7198.95, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2025-11-05', 'price': 7198.95, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2025-11-06', 'price': 6799.0, 'merchantId': 20609}, {'prodId': 13992938, 'date': '2025-11-07', 'price': 6799.0, 'merchantId': 20609}, {'prodId': 13992938, 'date': '2025-11-08', 'price': 6799.0, 'merchantId': 20609}, {'prodId': 13992938, 'date': '2025-11-09', 'price': 6799.0, 'merchantId': 20609}, {'prodId': 13992938, 'date': '2025-11-10', 'price': 6799.0, 'merchantId': 20609}, {'prodId': 13992938, 'date': '2025-11-11', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-11-12', 'price': 7198.0, 'merchantId': 21627}, {'prodId': 13992938, 'date': '2025-11-13', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-11-14', 'price': 7198.0, 'merchantId': 23326}, {'prodId': 13992938, 'date': '2025-11-15', 'price': 7198.0, 'merchantId': 23326}, {'prodId': 13992938, 'date': '2025-11-16', 'price': 7198.0, 'merchantId': 21627}, {'prodId': 13992938, 'date': '2025-11-17', 'price': 7198.0, 'merchantId': 21627}, {'prodId': 13992938, 'date': '2025-11-18', 'price': 7198.0, 'merchantId': 21627}, {'prodId': 13992938, 'date': '2025-11-19', 'price': 6499.1, 'merchantId': 21}, {'prodId': 13992938, 'date': '2025-11-20', 'price': 6499.1, 'merchantId': 21}, {'prodId': 13992938, 'date': '2025-11-21', 'price': 6699.1, 'merchantId': 21}, {'prodId': 13992938, 'date': '2025-11-22', 'price': 7198.0, 'merchantId': 21627}, {'prodId': 13992938, 'date': '2025-11-23', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-11-24', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-11-25', 'price': 6899.1, 'merchantId': 21}, {'prodId': 13992938, 'date': '2025-11-26', 'price': 7198.0, 'merchantId': 21627}, {'prodId': 13992938, 'date': '2025-11-27', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-11-28', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-11-29', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-11-30', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-12-01', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-12-02', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-12-03', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-12-04', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-12-05', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-12-06', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-12-07', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-12-08', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-12-09', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-12-10', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-12-11', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-12-12', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-12-13', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-12-14', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-12-15', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-12-16', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-12-17', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-12-18', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-12-19', 'price': 7199.1, 'merchantId': 22905}, {'prodId': 13992938, 'date': '2025-12-20', 'price': 6775.12, 'merchantId': 23326}, {'prodId': 13992938, 'date': '2025-12-21', 'price': 6775.12, 'merchantId': 23326}, {'prodId': 13992938, 'date': '2025-12-22', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-12-23', 'price': 7199.1, 'merchantId': 22905}, {'prodId': 13992938, 'date': '2025-12-24', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-12-25', 'price': 7199.1, 'merchantId': 22905}, {'prodId': 13992938, 'date': '2025-12-26', 'price': 7199.1, 'merchantId': 22905}, {'prodId': 13992938, 'date': '2025-12-27', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2025-12-28', 'price': 7198.0, 'merchantId': 245}, {'prodId': 13992938, 'date': '2025-12-29', 'price': 7198.0, 'merchantId': 245}, {'prodId': 13992938, 'date': '2025-12-30', 'price': 7198.0, 'merchantId': 245}, {'prodId': 13992938, 'date': '2025-12-31', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2026-01-01', 'price': 7198.0, 'merchantId': 2}, {'prodId': 13992938, 'date': '2026-01-02', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2026-01-03', 'price': 7198.0, 'merchantId': 2}, {'prodId': 13992938, 'date': '2026-01-04', 'price': 7199.1, 'merchantId': 22905}, {'prodId': 13992938, 'date': '2026-01-05', 'price': 7199.0, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-01-06', 'price': 7198.0, 'merchantId': 2}, {'prodId': 13992938, 'date': '2026-01-07', 'price': 7199.0, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-01-08', 'price': 7198.0, 'merchantId': 2}, {'prodId': 13992938, 'date': '2026-01-09', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2026-01-10', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2026-01-11', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2026-01-12', 'price': 7198.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2026-01-13', 'price': 6499.1, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-01-14', 'price': 6543.21, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-01-15', 'price': 6789.1, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-01-16', 'price': 6789.1, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-01-17', 'price': 6543.21, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-01-18', 'price': 6789.1, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-01-19', 'price': 6789.1, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-01-20', 'price': 6543.21, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-01-21', 'price': 6543.21, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-01-22', 'price': 6543.21, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-01-23', 'price': 6543.21, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-01-24', 'price': 6899.9, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-01-25', 'price': 7197.9, 'merchantId': 245}, {'prodId': 13992938, 'date': '2026-01-26', 'price': 6479.1, 'merchantId': 22902}, {'prodId': 13992938, 'date': '2026-01-27', 'price': 6478.99, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-01-28', 'price': 6478.99, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-01-29', 'price': 6399.9, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-01-30', 'price': 6399.9, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-01-31', 'price': 6428.0, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2026-02-01', 'price': 6428.0, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2026-02-02', 'price': 6192.9, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-02-03', 'price': 6192.9, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-02-04', 'price': 6428.0, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2026-02-05', 'price': 6428.0, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2026-02-06', 'price': 6428.0, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2026-02-07', 'price': 6428.0, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2026-02-08', 'price': 6428.0, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2026-02-09', 'price': 6428.0, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2026-02-10', 'price': 6399.9, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-02-11', 'price': 6428.0, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2026-02-12', 'price': 6428.0, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2026-02-13', 'price': 6428.0, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2026-02-14', 'price': 6428.0, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2026-02-15', 'price': 6428.0, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2026-02-16', 'price': 6428.0, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2026-02-17', 'price': 6428.0, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2026-02-18', 'price': 6428.0, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2026-02-19', 'price': 6428.0, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2026-02-20', 'price': 6428.0, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2026-02-21', 'price': 6428.0, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2026-02-22', 'price': 6428.0, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2026-02-23', 'price': 6428.0, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2026-02-24', 'price': 6428.0, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2026-02-25', 'price': 6428.0, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2026-02-26', 'price': 6395.0, 'merchantId': 9385}, {'prodId': 13992938, 'date': '2026-02-27', 'price': 6428.0, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2026-02-28', 'price': 6428.0, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2026-03-01', 'price': 6428.0, 'merchantId': 21629}, {'prodId': 13992938, 'date': '2026-03-02', 'price': 6389.1, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-03', 'price': 6349.9, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-04', 'price': 6349.9, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-05', 'price': 6349.9, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-06', 'price': 6349.9, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-07', 'price': 6349.9, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-08', 'price': 6349.9, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-09', 'price': 6349.9, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-10', 'price': 6349.9, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-11', 'price': 6349.9, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-12', 'price': 6349.91, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-13', 'price': 6349.91, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-14', 'price': 6349.91, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-15', 'price': 6349.91, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-16', 'price': 6349.91, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-17', 'price': 6349.91, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-18', 'price': 6349.91, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-19', 'price': 6349.91, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-20', 'price': 6349.91, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-21', 'price': 6349.91, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-22', 'price': 6349.91, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-23', 'price': 6349.91, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-24', 'price': 6349.91, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-25', 'price': 6349.91, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-26', 'price': 6349.91, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-27', 'price': 6349.91, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-28', 'price': 6349.91, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-29', 'price': 6349.91, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-30', 'price': 6349.91, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-03-31', 'price': 6349.91, 'merchantId': 21}, {'prodId': 13992938, 'date': '2026-04-01', 'price': 6299.1, 'merchantId': 22902}, {'prodId': 13992938, 'date': '2026-04-02', 'price': 6299.1, 'merchantId': 22902}, {'prodId': 13992938, 'date': '2026-04-03', 'price': 6298.0, 'merchantId': 4}, {'prodId': 13992938, 'date': '2026-04-04', 'price': 6029.1, 'merchantId': 9385}, {'prodId': 13992938, 'date': '2026-04-05', 'price': 6029.1, 'merchantId': 9385}, {'prodId': 13992938, 'date': '2026-04-06', 'price': 6298.0, 'merchantId': 2}, {'prodId': 13992938, 'date': '2026-04-07', 'price': 6295.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-04-08', 'price': 6027.13, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-04-09', 'price': 6295.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-04-10', 'price': 6203.29, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-04-11', 'price': 6203.29, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-04-12', 'price': 6203.29, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-04-13', 'price': 6203.29, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-04-14', 'price': 6333.34, 'merchantId': 20904}, {'prodId': 13992938, 'date': '2026-04-15', 'price': 6333.34, 'merchantId': 20904}, {'prodId': 13992938, 'date': '2026-04-16', 'price': 6333.34, 'merchantId': 20904}, {'prodId': 13992938, 'date': '2026-04-17', 'price': 6333.34, 'merchantId': 20904}, {'prodId': 13992938, 'date': '2026-04-18', 'price': 6333.34, 'merchantId': 20904}, {'prodId': 13992938, 'date': '2026-04-19', 'price': 6299.1, 'merchantId': 22902}, {'prodId': 13992938, 'date': '2026-04-20', 'price': 6299.1, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-04-21', 'price': 6299.1, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-04-22', 'price': 6147.03, 'merchantId': 22905}, {'prodId': 13992938, 'date': '2026-04-23', 'price': 6147.03, 'merchantId': 22905}, {'prodId': 13992938, 'date': '2026-04-24', 'price': 5999.0, 'merchantId': 16623}, {'prodId': 13992938, 'date': '2026-04-25', 'price': 5999.0, 'merchantId': 16623}, {'prodId': 13992938, 'date': '2026-04-26', 'price': 5999.0, 'merchantId': 16623}, {'prodId': 13992938, 'date': '2026-04-27', 'price': 5999.0, 'merchantId': 16623}, {'prodId': 13992938, 'date': '2026-04-28', 'price': 5999.0, 'merchantId': 16623}, {'prodId': 13992938, 'date': '2026-04-29', 'price': 5999.0, 'merchantId': 16623}, {'prodId': 13992938, 'date': '2026-04-30', 'price': 5999.0, 'merchantId': 16623}, {'prodId': 13992938, 'date': '2026-05-01', 'price': 5999.0, 'merchantId': 16623}, {'prodId': 13992938, 'date': '2026-05-02', 'price': 5999.0, 'merchantId': 16623}, {'prodId': 13992938, 'date': '2026-05-03', 'price': 5999.0, 'merchantId': 16623}, {'prodId': 13992938, 'date': '2026-05-04', 'price': 5999.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-05-05', 'price': 5999.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-05-06', 'price': 5999.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-05-07', 'price': 5899.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-05-08', 'price': 5999.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-05-09', 'price': 5999.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-05-10', 'price': 5999.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-05-11', 'price': 5999.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-05-12', 'price': 5999.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-05-13', 'price': 5999.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-05-14', 'price': 5999.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-05-15', 'price': 5999.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-05-16', 'price': 5999.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-05-17', 'price': 5999.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-05-18', 'price': 5999.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-05-19', 'price': 5999.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-05-20', 'price': 5999.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-05-21', 'price': 5999.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-05-22', 'price': 5999.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-05-23', 'price': 5895.12, 'merchantId': 22905}, {'prodId': 13992938, 'date': '2026-05-24', 'price': 5895.12, 'merchantId': 22905}, {'prodId': 13992938, 'date': '2026-05-25', 'price': 5749.0, 'merchantId': 16623}, {'prodId': 13992938, 'date': '2026-05-26', 'price': 5749.0, 'merchantId': 16623}, {'prodId': 13992938, 'date': '2026-05-27', 'price': 5749.0, 'merchantId': 16623}, {'prodId': 13992938, 'date': '2026-05-28', 'price': 5749.0, 'merchantId': 16623}, {'prodId': 13992938, 'date': '2026-05-29', 'price': 5749.0, 'merchantId': 16623}, {'prodId': 13992938, 'date': '2026-05-30', 'price': 5749.0, 'merchantId': 16623}, {'prodId': 13992938, 'date': '2026-05-31', 'price': 5749.0, 'merchantId': 16623}, {'prodId': 13992938, 'date': '2026-06-01', 'price': 5749.0, 'merchantId': 16623}, {'prodId': 13992938, 'date': '2026-06-02', 'price': 5749.0, 'merchantId': 16623}, {'prodId': 13992938, 'date': '2026-06-03', 'price': 5749.0, 'merchantId': 16623}, {'prodId': 13992938, 'date': '2026-06-04', 'price': 5749.0, 'merchantId': 16623}, {'prodId': 13992938, 'date': '2026-06-05', 'price': 5749.0, 'merchantId': 16623}, {'prodId': 13992938, 'date': '2026-06-06', 'price': 5749.0, 'merchantId': 16623}, {'prodId': 13992938, 'date': '2026-06-07', 'price': 5749.0, 'merchantId': 16623}, {'prodId': 13992938, 'date': '2026-06-08', 'price': 5749.0, 'merchantId': 16623}, {'prodId': 13992938, 'date': '2026-06-09', 'price': 5499.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-06-10', 'price': 5499.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-06-11', 'price': 5613.84, 'merchantId': 16108}, {'prodId': 13992938, 'date': '2026-06-12', 'price': 5613.84, 'merchantId': 16108}, {'prodId': 13992938, 'date': '2026-06-13', 'price': 5599.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-06-14', 'price': 5599.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-06-15', 'price': 5599.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-06-16', 'price': 5599.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-06-17', 'price': 5749.0, 'merchantId': 16623}, {'prodId': 13992938, 'date': '2026-06-18', 'price': 5309.1, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-06-19', 'price': 5499.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-06-20', 'price': 5499.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-06-21', 'price': 5309.1, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-06-22', 'price': 5309.1, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-06-23', 'price': 5599.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-06-24', 'price': 5599.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-06-25', 'price': 5599.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-06-26', 'price': 5599.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-06-27', 'price': 5599.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-06-28', 'price': 5649.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-06-29', 'price': 5649.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-06-30', 'price': 5649.0, 'merchantId': 5}, {'prodId': 13992938, 'date': '2026-07-01', 'price': 5799.0, 'merchantId': 22902}, {'prodId': 13992938, 'date': '2026-07-02', 'price': 5449.0, 'merchantId': 22902}, {'prodId': 13992938, 'date': '2026-07-03', 'price': 5449.0, 'merchantId': 22902}, {'prodId': 13992938, 'date': '2026-07-04', 'price': 5449.0, 'merchantId': 22902}, {'prodId': 13992938, 'date': '2026-07-05', 'price': 5449.0, 'merchantId': 22902}, {'prodId': 13992938, 'date': '2026-07-06', 'price': 5449.0, 'merchantId': 22902}, {'prodId': 13992938, 'date': '2026-07-07', 'price': 5449.0, 'merchantId': 22902}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13992951, 'date': '2025-09-10', 'price': 1756.55, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-09-11', 'price': 1756.55, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-09-12', 'price': 1756.55, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-09-13', 'price': 1756.55, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-09-14', 'price': 1756.55, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-09-15', 'price': 1756.55, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-09-16', 'price': 1756.55, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-09-17', 'price': 1756.55, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-09-18', 'price': 1519.05, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-09-19', 'price': 1519.05, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-09-20', 'price': 1519.05, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-09-21', 'price': 1519.05, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-09-22', 'price': 1519.05, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-09-23', 'price': 1519.05, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-09-24', 'price': 1519.05, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-09-25', 'price': 1519.05, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-09-26', 'price': 1519.05, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-09-27', 'price': 1519.05, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-09-28', 'price': 1519.05, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-09-29', 'price': 1519.05, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-09-30', 'price': 1519.05, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-10-01', 'price': 1519.05, 'merchantId': 20612}, {'prodId': 13992951, 'date': '2025-10-02', 'price': 1519.05, 'merchantId': 20612}, {'prodId': 13992951, 'date': '2025-10-03', 'price': 1519.05, 'merchantId': 20612}, {'prodId': 13992951, 'date': '2025-10-04', 'price': 1519.05, 'merchantId': 20612}, {'prodId': 13992951, 'date': '2025-10-05', 'price': 1599.0, 'merchantId': 1582}, {'prodId': 13992951, 'date': '2025-10-06', 'price': 1583.01, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-10-07', 'price': 1519.05, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-10-08', 'price': 1439.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-10-09', 'price': 1439.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-10-10', 'price': 1439.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-10-11', 'price': 1439.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-10-12', 'price': 1439.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-10-13', 'price': 1439.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-10-14', 'price': 1434.56, 'merchantId': 9385}, {'prodId': 13992951, 'date': '2025-10-15', 'price': 1434.56, 'merchantId': 9385}, {'prodId': 13992951, 'date': '2025-10-16', 'price': 1439.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-10-17', 'price': 1439.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-10-18', 'price': 1439.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-10-19', 'price': 1439.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-10-20', 'price': 1439.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-10-21', 'price': 1439.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-10-22', 'price': 1439.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-10-23', 'price': 1439.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-10-24', 'price': 1299.0, 'merchantId': 1582}, {'prodId': 13992951, 'date': '2025-10-25', 'price': 1439.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-10-26', 'price': 1439.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-10-27', 'price': 1439.0, 'merchantId': 34}, {'prodId': 13992951, 'date': '2025-10-28', 'price': 1439.0, 'merchantId': 34}, {'prodId': 13992951, 'date': '2025-10-29', 'price': 1439.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-10-30', 'price': 1439.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-10-31', 'price': 1259.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-11-01', 'price': 1259.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-11-02', 'price': 1259.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-11-03', 'price': 1259.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-11-04', 'price': 1259.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-11-05', 'price': 1439.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-11-06', 'price': 1439.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-11-07', 'price': 1439.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-11-08', 'price': 1439.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-11-09', 'price': 1439.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-11-10', 'price': 1439.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-11-11', 'price': 1439.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-11-12', 'price': 1439.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-11-13', 'price': 1439.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2025-11-14', 'price': 1399.0, 'merchantId': 20583}, {'prodId': 13992951, 'date': '2025-11-15', 'price': 1399.0, 'merchantId': 20583}, {'prodId': 13992951, 'date': '2025-11-16', 'price': 1399.0, 'merchantId': 20583}, {'prodId': 13992951, 'date': '2025-11-17', 'price': 1399.0, 'merchantId': 20583}, {'prodId': 13992951, 'date': '2025-11-18', 'price': 1396.11, 'merchantId': 9385}, {'prodId': 13992951, 'date': '2025-11-19', 'price': 1396.11, 'merchantId': 9385}, {'prodId': 13992951, 'date': '2025-11-20', 'price': 1396.11, 'merchantId': 9385}, {'prodId': 13992951, 'date': '2025-11-21', 'price': 1396.11, 'merchantId': 9385}, {'prodId': 13992951, 'date': '2025-11-22', 'price': 1396.11, 'merchantId': 1582}, {'prodId': 13992951, 'date': '2025-11-23', 'price': 1396.11, 'merchantId': 1582}, {'prodId': 13992951, 'date': '2025-11-24', 'price': 1198.99, 'merchantId': 1582}, {'prodId': 13992951, 'date': '2025-11-25', 'price': 1198.8, 'merchantId': 9385}, {'prodId': 13992951, 'date': '2025-11-26', 'price': 1198.8, 'merchantId': 9385}, {'prodId': 13992951, 'date': '2025-11-27', 'price': 1198.8, 'merchantId': 9385}, {'prodId': 13992951, 'date': '2025-11-28', 'price': 1198.8, 'merchantId': 9385}, {'prodId': 13992951, 'date': '2025-11-29', 'price': 1198.8, 'merchantId': 9385}, {'prodId': 13992951, 'date': '2025-11-30', 'price': 1198.8, 'merchantId': 9385}, {'prodId': 13992951, 'date': '2025-12-01', 'price': 1198.8, 'merchantId': 9385}, {'prodId': 13992951, 'date': '2025-12-02', 'price': 1198.96, 'merchantId': 1582}, {'prodId': 13992951, 'date': '2025-12-03', 'price': 1198.96, 'merchantId': 1582}, {'prodId': 13992951, 'date': '2025-12-04', 'price': 1198.96, 'merchantId': 1582}, {'prodId': 13992951, 'date': '2025-12-05', 'price': 1198.96, 'merchantId': 1582}, {'prodId': 13992951, 'date': '2025-12-06', 'price': 1198.96, 'merchantId': 1582}, {'prodId': 13992951, 'date': '2025-12-07', 'price': 1198.96, 'merchantId': 1582}, {'prodId': 13992951, 'date': '2025-12-08', 'price': 1198.8, 'merchantId': 23254}, {'prodId': 13992951, 'date': '2025-12-09', 'price': 1198.0, 'merchantId': 2}, {'prodId': 13992951, 'date': '2025-12-10', 'price': 1198.0, 'merchantId': 2}, {'prodId': 13992951, 'date': '2025-12-11', 'price': 1198.0, 'merchantId': 2}, {'prodId': 13992951, 'date': '2025-12-12', 'price': 1198.0, 'merchantId': 2}, {'prodId': 13992951, 'date': '2025-12-13', 'price': 1198.0, 'merchantId': 2}, {'prodId': 13992951, 'date': '2025-12-14', 'price': 1198.0, 'merchantId': 2}, {'prodId': 13992951, 'date': '2025-12-15', 'price': 1198.0, 'merchantId': 2}, {'prodId': 13992951, 'date': '2025-12-16', 'price': 1198.8, 'merchantId': 23254}, {'prodId': 13992951, 'date': '2025-12-17', 'price': 1198.8, 'merchantId': 23254}, {'prodId': 13992951, 'date': '2025-12-18', 'price': 1198.8, 'merchantId': 23254}, {'prodId': 13992951, 'date': '2025-12-19', 'price': 1198.8, 'merchantId': 23254}, {'prodId': 13992951, 'date': '2025-12-20', 'price': 1198.8, 'merchantId': 23254}, {'prodId': 13992951, 'date': '2025-12-21', 'price': 1198.8, 'merchantId': 23254}, {'prodId': 13992951, 'date': '2025-12-22', 'price': 1198.8, 'merchantId': 23254}, {'prodId': 13992951, 'date': '2025-12-23', 'price': 1198.8, 'merchantId': 23254}, {'prodId': 13992951, 'date': '2025-12-24', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-12-25', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-12-26', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-12-27', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-12-28', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-12-29', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-12-30', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2025-12-31', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-01-01', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-01-02', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-01-03', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-01-04', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-01-05', 'price': 1198.8, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-01-06', 'price': 1198.8, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-01-07', 'price': 1198.8, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-01-08', 'price': 1197.0, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-01-09', 'price': 1160.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-01-10', 'price': 1160.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-01-11', 'price': 1160.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-01-12', 'price': 1160.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-01-13', 'price': 1198.8, 'merchantId': 23254}, {'prodId': 13992951, 'date': '2026-01-14', 'price': 1198.8, 'merchantId': 23254}, {'prodId': 13992951, 'date': '2026-01-15', 'price': 1198.8, 'merchantId': 23254}, {'prodId': 13992951, 'date': '2026-01-16', 'price': 1198.8, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-01-17', 'price': 1198.8, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-01-18', 'price': 1198.8, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-01-19', 'price': 1198.8, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-01-20', 'price': 1198.8, 'merchantId': 23254}, {'prodId': 13992951, 'date': '2026-01-21', 'price': 1198.8, 'merchantId': 23254}, {'prodId': 13992951, 'date': '2026-01-22', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-01-23', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-01-24', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-01-25', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-01-26', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-01-27', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-01-28', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-01-29', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-01-30', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-01-31', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-02-01', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-02-02', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-02-03', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-02-04', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-02-05', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-02-06', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-02-07', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-02-08', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-02-09', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-02-10', 'price': 1184.65, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-02-11', 'price': 1184.65, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-02-12', 'price': 1184.65, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-02-13', 'price': 1184.65, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-02-14', 'price': 1184.65, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-02-15', 'price': 1184.65, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-02-16', 'price': 1184.65, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-02-17', 'price': 1184.65, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-02-18', 'price': 1184.65, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-02-19', 'price': 1184.65, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-02-20', 'price': 1184.65, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-02-21', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-02-22', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-02-23', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-02-24', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-02-25', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-02-26', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-02-27', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-02-28', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-03-01', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-03-02', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-03-03', 'price': 1169.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-03-04', 'price': 1169.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-03-05', 'price': 1169.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-03-06', 'price': 1169.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-03-07', 'price': 1169.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-03-08', 'price': 1169.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-03-09', 'price': 1169.1, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-03-10', 'price': 1284.2, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-03-11', 'price': 1284.2, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-03-12', 'price': 1284.2, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-03-13', 'price': 1284.2, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-03-14', 'price': 1284.2, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-03-15', 'price': 1284.2, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-03-16', 'price': 1284.2, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-03-17', 'price': 1284.2, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-03-18', 'price': 1284.2, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-03-19', 'price': 1284.2, 'merchantId': 20612}, {'prodId': 13992951, 'date': '2026-03-20', 'price': 1426.9, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-03-21', 'price': 1426.9, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-03-22', 'price': 1426.9, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-03-23', 'price': 1274.0, 'merchantId': 20583}, {'prodId': 13992951, 'date': '2026-03-24', 'price': 1358.9, 'merchantId': 20583}, {'prodId': 13992951, 'date': '2026-03-25', 'price': 1358.9, 'merchantId': 20583}, {'prodId': 13992951, 'date': '2026-03-26', 'price': 1358.9, 'merchantId': 20583}, {'prodId': 13992951, 'date': '2026-03-27', 'price': 1358.9, 'merchantId': 20583}, {'prodId': 13992951, 'date': '2026-03-28', 'price': 1358.9, 'merchantId': 20583}, {'prodId': 13992951, 'date': '2026-03-29', 'price': 1358.9, 'merchantId': 20583}, {'prodId': 13992951, 'date': '2026-03-30', 'price': 1222.9, 'merchantId': 20583}, {'prodId': 13992951, 'date': '2026-03-31', 'price': 1222.9, 'merchantId': 20583}, {'prodId': 13992951, 'date': '2026-04-01', 'price': 1222.9, 'merchantId': 20583}, {'prodId': 13992951, 'date': '2026-04-02', 'price': 1222.9, 'merchantId': 20583}, {'prodId': 13992951, 'date': '2026-04-03', 'price': 1222.9, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-04-04', 'price': 1078.9, 'merchantId': 1582}, {'prodId': 13992951, 'date': '2026-04-05', 'price': 1198.78, 'merchantId': 1582}, {'prodId': 13992951, 'date': '2026-04-06', 'price': 1222.9, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-04-07', 'price': 1199.0, 'merchantId': 9385}, {'prodId': 13992951, 'date': '2026-04-08', 'price': 1199.0, 'merchantId': 9385}, {'prodId': 13992951, 'date': '2026-04-09', 'price': 1222.9, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-04-10', 'price': 1223.0, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-04-11', 'price': 1223.0, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-04-12', 'price': 1223.0, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-04-13', 'price': 1223.0, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-04-14', 'price': 1223.0, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-04-15', 'price': 1223.0, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-04-16', 'price': 1079.1, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-04-17', 'price': 1079.1, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-04-18', 'price': 1079.1, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-04-19', 'price': 1079.1, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-04-20', 'price': 1079.1, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-04-21', 'price': 1079.1, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-04-22', 'price': 1079.1, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-04-23', 'price': 1079.1, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-04-24', 'price': 1079.1, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-04-25', 'price': 1079.1, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-04-26', 'price': 1079.1, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-04-27', 'price': 1079.1, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-04-28', 'price': 1079.1, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-04-29', 'price': 1169.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-04-30', 'price': 1169.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-05-01', 'price': 1169.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-05-02', 'price': 1169.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-05-03', 'price': 1169.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-05-04', 'price': 1169.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-05-05', 'price': 1169.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-05-06', 'price': 1169.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-05-07', 'price': 1169.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-05-08', 'price': 1258.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-05-09', 'price': 1258.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-05-10', 'price': 1298.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-05-11', 'price': 1298.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-05-12', 'price': 1079.1, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-05-13', 'price': 1079.1, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-05-14', 'price': 1223.0, 'merchantId': 20583}, {'prodId': 13992951, 'date': '2026-05-15', 'price': 1079.1, 'merchantId': 20583}, {'prodId': 13992951, 'date': '2026-05-16', 'price': 1079.1, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-05-17', 'price': 1079.1, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-05-18', 'price': 1079.1, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-05-19', 'price': 1079.1, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-05-20', 'price': 1079.1, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-05-21', 'price': 1079.1, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-05-22', 'price': 1079.1, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-05-23', 'price': 1267.97, 'merchantId': 23326}, {'prodId': 13992951, 'date': '2026-05-24', 'price': 1267.97, 'merchantId': 23326}, {'prodId': 13992951, 'date': '2026-05-25', 'price': 1231.2, 'merchantId': 9385}, {'prodId': 13992951, 'date': '2026-05-26', 'price': 1267.97, 'merchantId': 23326}, {'prodId': 13992951, 'date': '2026-05-27', 'price': 1080.0, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-05-28', 'price': 1080.0, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-05-29', 'price': 1080.0, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-05-30', 'price': 1080.0, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-05-31', 'price': 1080.0, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-06-01', 'price': 1080.0, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-06-02', 'price': 1080.0, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-06-03', 'price': 1080.0, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-06-04', 'price': 1080.0, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-06-05', 'price': 1080.0, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-06-06', 'price': 1080.0, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-06-07', 'price': 1080.0, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-06-08', 'price': 1080.0, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-06-09', 'price': 1080.0, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-06-10', 'price': 1080.0, 'merchantId': 22902}, {'prodId': 13992951, 'date': '2026-06-11', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-06-12', 'price': 1291.95, 'merchantId': 245}, {'prodId': 13992951, 'date': '2026-06-13', 'price': 1291.95, 'merchantId': 245}, {'prodId': 13992951, 'date': '2026-06-14', 'price': 1291.95, 'merchantId': 245}, {'prodId': 13992951, 'date': '2026-06-15', 'price': 1291.95, 'merchantId': 245}, {'prodId': 13992951, 'date': '2026-06-16', 'price': 1324.9, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-06-17', 'price': 1324.9, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-06-18', 'price': 1324.9, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-06-19', 'price': 1324.9, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-06-20', 'price': 1324.9, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-06-21', 'price': 1324.9, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-06-22', 'price': 1324.9, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-06-23', 'price': 1324.9, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-06-24', 'price': 1324.9, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-06-25', 'price': 1324.9, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-06-26', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-06-27', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-06-28', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-06-29', 'price': 1199.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-06-30', 'price': 1149.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-07-01', 'price': 1149.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-07-02', 'price': 1149.0, 'merchantId': 22905}, {'prodId': 13992951, 'date': '2026-07-03', 'price': 1258.8, 'merchantId': 20583}, {'prodId': 13992951, 'date': '2026-07-04', 'price': 1324.9, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-07-05', 'price': 1324.9, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-07-06', 'price': 1324.9, 'merchantId': 20609}, {'prodId': 13992951, 'date': '2026-07-07', 'price': 1208.91, 'merchantId': 22905}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13993095, 'date': '2025-11-20', 'price': 3819.1, 'merchantId': 21629}, {'prodId': 13993095, 'date': '2025-11-21', 'price': 3819.1, 'merchantId': 21629}, {'prodId': 13993095, 'date': '2025-11-22', 'price': 3819.1, 'merchantId': 21629}, {'prodId': 13993095, 'date': '2025-11-23', 'price': 3819.1, 'merchantId': 21629}, {'prodId': 13993095, 'date': '2025-11-24', 'price': 3819.1, 'merchantId': 21629}, {'prodId': 13993095, 'date': '2025-11-25', 'price': 3819.1, 'merchantId': 21629}, {'prodId': 13993095, 'date': '2025-11-26', 'price': 3299.0, 'merchantId': 21629}, {'prodId': 13993095, 'date': '2025-11-27', 'price': 3299.0, 'merchantId': 21629}, {'prodId': 13993095, 'date': '2025-11-28', 'price': 3099.0, 'merchantId': 21628}, {'prodId': 13993095, 'date': '2025-11-29', 'price': 3099.0, 'merchantId': 21628}, {'prodId': 13993095, 'date': '2025-11-30', 'price': 3099.0, 'merchantId': 21628}, {'prodId': 13993095, 'date': '2025-12-01', 'price': 3099.0, 'merchantId': 21628}, {'prodId': 13993095, 'date': '2025-12-02', 'price': 3099.0, 'merchantId': 21628}, {'prodId': 13993095, 'date': '2025-12-03', 'price': 3238.2, 'merchantId': 20612}, {'prodId': 13993095, 'date': '2025-12-04', 'price': 3199.0, 'merchantId': 21628}, {'prodId': 13993095, 'date': '2025-12-05', 'price': 3199.0, 'merchantId': 21628}, {'prodId': 13993095, 'date': '2025-12-06', 'price': 3199.0, 'merchantId': 21628}, {'prodId': 13993095, 'date': '2025-12-07', 'price': 3199.0, 'merchantId': 21628}, {'prodId': 13993095, 'date': '2025-12-08', 'price': 3099.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2025-12-09', 'price': 3098.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2025-12-10', 'price': 3098.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2025-12-11', 'price': 3098.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2025-12-12', 'price': 2932.45, 'merchantId': 20609}, {'prodId': 13993095, 'date': '2025-12-13', 'price': 2932.45, 'merchantId': 20609}, {'prodId': 13993095, 'date': '2025-12-14', 'price': 2932.45, 'merchantId': 20609}, {'prodId': 13993095, 'date': '2025-12-15', 'price': 2932.45, 'merchantId': 20609}, {'prodId': 13993095, 'date': '2025-12-16', 'price': 3098.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2025-12-17', 'price': 3098.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2025-12-18', 'price': 3098.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2025-12-19', 'price': 2754.66, 'merchantId': 20609}, {'prodId': 13993095, 'date': '2025-12-20', 'price': 2754.66, 'merchantId': 20583}, {'prodId': 13993095, 'date': '2025-12-21', 'price': 2754.66, 'merchantId': 20583}, {'prodId': 13993095, 'date': '2025-12-22', 'price': 2754.66, 'merchantId': 20583}, {'prodId': 13993095, 'date': '2025-12-23', 'price': 2754.66, 'merchantId': 20583}, {'prodId': 13993095, 'date': '2025-12-24', 'price': 2754.66, 'merchantId': 20583}, {'prodId': 13993095, 'date': '2025-12-25', 'price': 2754.66, 'merchantId': 20583}, {'prodId': 13993095, 'date': '2025-12-26', 'price': 2754.66, 'merchantId': 20583}, {'prodId': 13993095, 'date': '2025-12-27', 'price': 2754.66, 'merchantId': 20612}, {'prodId': 13993095, 'date': '2025-12-28', 'price': 3098.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2025-12-29', 'price': 3097.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2025-12-30', 'price': 3097.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2025-12-31', 'price': 3097.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-01-01', 'price': 3097.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-01-02', 'price': 3096.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-01-03', 'price': 3096.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-01-04', 'price': 3096.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-01-05', 'price': 2699.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-01-06', 'price': 2699.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-01-07', 'price': 2699.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-01-08', 'price': 2699.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-01-09', 'price': 2639.12, 'merchantId': 20583}, {'prodId': 13993095, 'date': '2026-01-10', 'price': 2639.12, 'merchantId': 20583}, {'prodId': 13993095, 'date': '2026-01-11', 'price': 2639.12, 'merchantId': 20583}, {'prodId': 13993095, 'date': '2026-01-12', 'price': 2639.12, 'merchantId': 20583}, {'prodId': 13993095, 'date': '2026-01-13', 'price': 2639.12, 'merchantId': 20583}, {'prodId': 13993095, 'date': '2026-01-14', 'price': 2699.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-01-15', 'price': 2699.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-01-16', 'price': 2699.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-01-17', 'price': 2699.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-01-18', 'price': 2699.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-01-19', 'price': 2698.1, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-01-20', 'price': 2698.1, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-01-21', 'price': 2749.0, 'merchantId': 21627}, {'prodId': 13993095, 'date': '2026-01-22', 'price': 2749.0, 'merchantId': 21627}, {'prodId': 13993095, 'date': '2026-01-23', 'price': 2749.0, 'merchantId': 21627}, {'prodId': 13993095, 'date': '2026-01-24', 'price': 2749.0, 'merchantId': 21627}, {'prodId': 13993095, 'date': '2026-01-25', 'price': 2749.0, 'merchantId': 21627}, {'prodId': 13993095, 'date': '2026-01-26', 'price': 2749.0, 'merchantId': 21627}, {'prodId': 13993095, 'date': '2026-01-27', 'price': 2749.0, 'merchantId': 21627}, {'prodId': 13993095, 'date': '2026-01-28', 'price': 2749.0, 'merchantId': 21627}, {'prodId': 13993095, 'date': '2026-01-29', 'price': 2749.0, 'merchantId': 21627}, {'prodId': 13993095, 'date': '2026-01-30', 'price': 2749.0, 'merchantId': 21627}, {'prodId': 13993095, 'date': '2026-01-31', 'price': 2749.0, 'merchantId': 21627}, {'prodId': 13993095, 'date': '2026-02-01', 'price': 2749.0, 'merchantId': 21627}, {'prodId': 13993095, 'date': '2026-02-02', 'price': 2699.0, 'merchantId': 34}, {'prodId': 13993095, 'date': '2026-02-03', 'price': 2699.0, 'merchantId': 23326}, {'prodId': 13993095, 'date': '2026-02-04', 'price': 2587.73, 'merchantId': 23326}, {'prodId': 13993095, 'date': '2026-02-05', 'price': 2587.73, 'merchantId': 23326}, {'prodId': 13993095, 'date': '2026-02-06', 'price': 2587.73, 'merchantId': 23326}, {'prodId': 13993095, 'date': '2026-02-07', 'price': 2749.0, 'merchantId': 21627}, {'prodId': 13993095, 'date': '2026-02-08', 'price': 2749.0, 'merchantId': 21627}, {'prodId': 13993095, 'date': '2026-02-09', 'price': 2749.0, 'merchantId': 21627}, {'prodId': 13993095, 'date': '2026-02-10', 'price': 2749.0, 'merchantId': 21627}, {'prodId': 13993095, 'date': '2026-02-11', 'price': 2749.0, 'merchantId': 21628}, {'prodId': 13993095, 'date': '2026-02-12', 'price': 2749.0, 'merchantId': 21628}, {'prodId': 13993095, 'date': '2026-02-13', 'price': 2749.0, 'merchantId': 21628}, {'prodId': 13993095, 'date': '2026-02-14', 'price': 2749.0, 'merchantId': 21628}, {'prodId': 13993095, 'date': '2026-02-15', 'price': 2749.0, 'merchantId': 21628}, {'prodId': 13993095, 'date': '2026-02-16', 'price': 2749.0, 'merchantId': 21628}, {'prodId': 13993095, 'date': '2026-02-17', 'price': 2749.0, 'merchantId': 21628}, {'prodId': 13993095, 'date': '2026-02-18', 'price': 2749.0, 'merchantId': 21628}, {'prodId': 13993095, 'date': '2026-02-19', 'price': 2749.0, 'merchantId': 21628}, {'prodId': 13993095, 'date': '2026-02-20', 'price': 2749.0, 'merchantId': 21628}, {'prodId': 13993095, 'date': '2026-02-21', 'price': 2749.0, 'merchantId': 21627}, {'prodId': 13993095, 'date': '2026-02-22', 'price': 2783.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-02-23', 'price': 2783.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-02-24', 'price': 2783.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-02-25', 'price': 2749.0, 'merchantId': 21628}, {'prodId': 13993095, 'date': '2026-02-26', 'price': 2749.0, 'merchantId': 21628}, {'prodId': 13993095, 'date': '2026-02-27', 'price': 2749.0, 'merchantId': 21628}, {'prodId': 13993095, 'date': '2026-02-28', 'price': 2749.0, 'merchantId': 21628}, {'prodId': 13993095, 'date': '2026-03-01', 'price': 2749.0, 'merchantId': 21628}, {'prodId': 13993095, 'date': '2026-03-02', 'price': 2787.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-03-03', 'price': 2599.0, 'merchantId': 22902}, {'prodId': 13993095, 'date': '2026-03-04', 'price': 2599.0, 'merchantId': 22902}, {'prodId': 13993095, 'date': '2026-03-05', 'price': 2599.0, 'merchantId': 22902}, {'prodId': 13993095, 'date': '2026-03-06', 'price': 2599.0, 'merchantId': 22902}, {'prodId': 13993095, 'date': '2026-03-07', 'price': 2599.0, 'merchantId': 22902}, {'prodId': 13993095, 'date': '2026-03-08', 'price': 2599.0, 'merchantId': 22902}, {'prodId': 13993095, 'date': '2026-03-09', 'price': 2598.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-03-10', 'price': 2597.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-03-11', 'price': 2596.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-03-12', 'price': 2596.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-03-13', 'price': 2594.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-03-14', 'price': 2594.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-03-15', 'price': 2594.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-03-16', 'price': 2593.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-03-17', 'price': 2659.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-03-18', 'price': 2599.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-03-19', 'price': 2598.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-03-20', 'price': 2598.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-03-21', 'price': 2598.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-03-22', 'price': 2598.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-03-23', 'price': 2598.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-03-24', 'price': 2597.0, 'merchantId': 2}, {'prodId': 13993095, 'date': '2026-03-25', 'price': 2596.9, 'merchantId': 2}, {'prodId': 13993095, 'date': '2026-03-26', 'price': 2609.0, 'merchantId': 23326}, {'prodId': 13993095, 'date': '2026-03-27', 'price': 2596.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-03-28', 'price': 2596.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-03-29', 'price': 2596.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-03-30', 'price': 2596.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-03-31', 'price': 2595.6, 'merchantId': 20583}, {'prodId': 13993095, 'date': '2026-04-01', 'price': 2595.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-04-02', 'price': 2464.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-04-03', 'price': 2464.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-04-04', 'price': 2464.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-04-05', 'price': 2464.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-04-06', 'price': 2464.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-04-07', 'price': 2597.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-04-08', 'price': 2679.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-04-09', 'price': 2678.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-04-10', 'price': 2678.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-04-11', 'price': 2678.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-04-12', 'price': 2678.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-04-13', 'price': 2618.49, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-04-14', 'price': 2618.39, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-04-15', 'price': 2618.39, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-04-16', 'price': 2802.31, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-04-17', 'price': 2736.7, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-04-18', 'price': 2798.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-04-19', 'price': 2798.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-04-20', 'price': 2798.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-04-21', 'price': 2798.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-04-22', 'price': 2797.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-04-23', 'price': 2797.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-04-24', 'price': 2712.98, 'merchantId': 9385}, {'prodId': 13993095, 'date': '2026-04-25', 'price': 2796.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-04-26', 'price': 2796.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-04-27', 'price': 2796.0, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-04-28', 'price': 2796.0, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-04-29', 'price': 2611.55, 'merchantId': 34}, {'prodId': 13993095, 'date': '2026-04-30', 'price': 2611.55, 'merchantId': 34}, {'prodId': 13993095, 'date': '2026-05-01', 'price': 2611.54, 'merchantId': 9385}, {'prodId': 13993095, 'date': '2026-05-02', 'price': 2611.54, 'merchantId': 9385}, {'prodId': 13993095, 'date': '2026-05-03', 'price': 2611.54, 'merchantId': 1582}, {'prodId': 13993095, 'date': '2026-05-04', 'price': 2611.54, 'merchantId': 1582}, {'prodId': 13993095, 'date': '2026-05-05', 'price': 2699.0, 'merchantId': 2}, {'prodId': 13993095, 'date': '2026-05-06', 'price': 2517.3, 'merchantId': 9385}, {'prodId': 13993095, 'date': '2026-05-07', 'price': 2517.3, 'merchantId': 9385}, {'prodId': 13993095, 'date': '2026-05-08', 'price': 2702.7, 'merchantId': 22902}, {'prodId': 13993095, 'date': '2026-05-09', 'price': 2774.92, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-05-10', 'price': 2774.92, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-05-11', 'price': 2519.1, 'merchantId': 23254}, {'prodId': 13993095, 'date': '2026-05-12', 'price': 2519.1, 'merchantId': 23254}, {'prodId': 13993095, 'date': '2026-05-13', 'price': 2519.1, 'merchantId': 23254}, {'prodId': 13993095, 'date': '2026-05-14', 'price': 2519.1, 'merchantId': 23254}, {'prodId': 13993095, 'date': '2026-05-15', 'price': 2519.1, 'merchantId': 23254}, {'prodId': 13993095, 'date': '2026-05-16', 'price': 2519.1, 'merchantId': 23254}, {'prodId': 13993095, 'date': '2026-05-17', 'price': 2519.1, 'merchantId': 23254}, {'prodId': 13993095, 'date': '2026-05-18', 'price': 2499.0, 'merchantId': 22902}, {'prodId': 13993095, 'date': '2026-05-19', 'price': 2443.47, 'merchantId': 23326}, {'prodId': 13993095, 'date': '2026-05-20', 'price': 2443.47, 'merchantId': 23326}, {'prodId': 13993095, 'date': '2026-05-21', 'price': 2498.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-05-22', 'price': 2199.0, 'merchantId': 9385}, {'prodId': 13993095, 'date': '2026-05-23', 'price': 2361.6, 'merchantId': 9385}, {'prodId': 13993095, 'date': '2026-05-24', 'price': 2499.0, 'merchantId': 1582}, {'prodId': 13993095, 'date': '2026-05-25', 'price': 2471.14, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-05-26', 'price': 2470.25, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-05-27', 'price': 2470.25, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-05-28', 'price': 2386.88, 'merchantId': 23326}, {'prodId': 13993095, 'date': '2026-05-29', 'price': 2386.88, 'merchantId': 23326}, {'prodId': 13993095, 'date': '2026-05-30', 'price': 2470.14, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-05-31', 'price': 2470.14, 'merchantId': 23326}, {'prodId': 13993095, 'date': '2026-06-01', 'price': 2442.38, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-06-02', 'price': 2442.38, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-06-03', 'price': 2637.07, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-06-04', 'price': 2637.07, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-06-05', 'price': 2636.98, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-06-06', 'price': 2636.98, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-06-07', 'price': 2636.98, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-06-08', 'price': 2639.12, 'merchantId': 20583}, {'prodId': 13993095, 'date': '2026-06-09', 'price': 2636.1, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-06-10', 'price': 2635.98, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-06-11', 'price': 2635.1, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-06-12', 'price': 2485.39, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-06-13', 'price': 2485.39, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-06-14', 'price': 2639.12, 'merchantId': 20583}, {'prodId': 13993095, 'date': '2026-06-15', 'price': 2484.46, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-06-16', 'price': 2618.02, 'merchantId': 9385}, {'prodId': 13993095, 'date': '2026-06-17', 'price': 2618.02, 'merchantId': 9385}, {'prodId': 13993095, 'date': '2026-06-18', 'price': 2617.99, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-06-19', 'price': 2617.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-06-20', 'price': 2617.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-06-21', 'price': 2617.9, 'merchantId': 2}, {'prodId': 13993095, 'date': '2026-06-22', 'price': 2617.9, 'merchantId': 2}, {'prodId': 13993095, 'date': '2026-06-23', 'price': 2617.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-06-24', 'price': 2617.9, 'merchantId': 4}, {'prodId': 13993095, 'date': '2026-06-25', 'price': 2559.73, 'merchantId': 23326}, {'prodId': 13993095, 'date': '2026-06-26', 'price': 2482.36, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-06-27', 'price': 2481.6, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-06-28', 'price': 2481.6, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-06-29', 'price': 2602.9, 'merchantId': 9385}, {'prodId': 13993095, 'date': '2026-06-30', 'price': 2616.9, 'merchantId': 2}, {'prodId': 13993095, 'date': '2026-07-01', 'price': 2602.9, 'merchantId': 9385}, {'prodId': 13993095, 'date': '2026-07-02', 'price': 2558.75, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-07-03', 'price': 2557.78, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-07-04', 'price': 2557.78, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-07-05', 'price': 2557.78, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-07-06', 'price': 2557.78, 'merchantId': 245}, {'prodId': 13993095, 'date': '2026-07-07', 'price': 2557.78, 'merchantId': 245}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13991988, 'date': '2025-07-07', 'price': 1914.3, 'merchantId': 5}, {'prodId': 13991988, 'date': '2025-07-08', 'price': 1969.0, 'merchantId': 20583}, {'prodId': 13991988, 'date': '2025-07-09', 'price': 1969.0, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2025-07-10', 'price': 1649.9, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2025-07-11', 'price': 1648.8, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2025-07-12', 'price': 1669.0, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2025-07-13', 'price': 1669.0, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2025-07-14', 'price': 1669.0, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2025-07-15', 'price': 1669.0, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2025-07-16', 'price': 1669.0, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2025-07-17', 'price': 1669.0, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2025-07-18', 'price': 1669.0, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2025-07-19', 'price': 1669.0, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2025-07-20', 'price': 1669.0, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2025-07-21', 'price': 1669.0, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2025-07-22', 'price': 1669.0, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2025-07-23', 'price': 1669.0, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2025-07-24', 'price': 1669.0, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2025-07-25', 'price': 1669.0, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2025-07-26', 'price': 1669.0, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2025-07-27', 'price': 1669.0, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2025-07-28', 'price': 1669.0, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2025-07-29', 'price': 1669.0, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2025-07-30', 'price': 1698.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-07-31', 'price': 1698.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-08-01', 'price': 1698.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-08-02', 'price': 1671.12, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2025-08-03', 'price': 1799.0, 'merchantId': 5}, {'prodId': 13991988, 'date': '2025-08-04', 'price': 1648.8, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2025-08-05', 'price': 1647.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-08-06', 'price': 1647.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-08-07', 'price': 1647.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-08-08', 'price': 1647.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-08-09', 'price': 1647.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-08-10', 'price': 1647.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-08-11', 'price': 1647.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-08-12', 'price': 1698.99, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2025-08-13', 'price': 1709.1, 'merchantId': 20583}, {'prodId': 13991988, 'date': '2025-08-14', 'price': 1709.1, 'merchantId': 20583}, {'prodId': 13991988, 'date': '2025-08-15', 'price': 1709.1, 'merchantId': 20583}, {'prodId': 13991988, 'date': '2025-08-16', 'price': 1709.1, 'merchantId': 20583}, {'prodId': 13991988, 'date': '2025-08-17', 'price': 1709.1, 'merchantId': 20583}, {'prodId': 13991988, 'date': '2025-08-18', 'price': 1709.1, 'merchantId': 20583}, {'prodId': 13991988, 'date': '2025-08-19', 'price': 1709.1, 'merchantId': 20583}, {'prodId': 13991988, 'date': '2025-08-20', 'price': 1709.1, 'merchantId': 20583}, {'prodId': 13991988, 'date': '2025-08-21', 'price': 1709.1, 'merchantId': 20583}, {'prodId': 13991988, 'date': '2025-08-22', 'price': 1709.1, 'merchantId': 20583}, {'prodId': 13991988, 'date': '2025-08-23', 'price': 1709.1, 'merchantId': 20583}, {'prodId': 13991988, 'date': '2025-08-24', 'price': 1709.1, 'merchantId': 20583}, {'prodId': 13991988, 'date': '2025-08-25', 'price': 1698.99, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2025-08-26', 'price': 1698.99, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2025-08-27', 'price': 1599.3, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2025-08-28', 'price': 1599.3, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2025-08-29', 'price': 1599.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-08-30', 'price': 1599.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-08-31', 'price': 1599.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-09-01', 'price': 1599.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-09-02', 'price': 1599.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-09-03', 'price': 1599.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-09-04', 'price': 1599.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-09-05', 'price': 1599.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-09-06', 'price': 1599.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-09-07', 'price': 1599.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-09-08', 'price': 1599.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-09-09', 'price': 1599.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-09-10', 'price': 1565.69, 'merchantId': 5}, {'prodId': 13991988, 'date': '2025-09-11', 'price': 1565.69, 'merchantId': 5}, {'prodId': 13991988, 'date': '2025-09-12', 'price': 1565.69, 'merchantId': 5}, {'prodId': 13991988, 'date': '2025-09-13', 'price': 1565.69, 'merchantId': 5}, {'prodId': 13991988, 'date': '2025-09-14', 'price': 1565.69, 'merchantId': 5}, {'prodId': 13991988, 'date': '2025-09-15', 'price': 1565.69, 'merchantId': 5}, {'prodId': 13991988, 'date': '2025-09-16', 'price': 1565.69, 'merchantId': 5}, {'prodId': 13991988, 'date': '2025-09-17', 'price': 1614.65, 'merchantId': 5}, {'prodId': 13991988, 'date': '2025-09-18', 'price': 1463.2, 'merchantId': 20583}, {'prodId': 13991988, 'date': '2025-09-19', 'price': 1463.2, 'merchantId': 20583}, {'prodId': 13991988, 'date': '2025-09-20', 'price': 1463.2, 'merchantId': 20583}, {'prodId': 13991988, 'date': '2025-09-21', 'price': 1463.2, 'merchantId': 20583}, {'prodId': 13991988, 'date': '2025-09-22', 'price': 1463.2, 'merchantId': 20583}, {'prodId': 13991988, 'date': '2025-09-23', 'price': 1463.2, 'merchantId': 20612}, {'prodId': 13991988, 'date': '2025-09-24', 'price': 1463.2, 'merchantId': 20612}, {'prodId': 13991988, 'date': '2025-09-25', 'price': 1463.2, 'merchantId': 20612}, {'prodId': 13991988, 'date': '2025-09-26', 'price': 1609.08, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-09-27', 'price': 1609.08, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-09-28', 'price': 1609.08, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-09-29', 'price': 1609.08, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-09-30', 'price': 1609.08, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-10-01', 'price': 1566.55, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2025-10-02', 'price': 1566.55, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2025-10-03', 'price': 1566.55, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2025-10-04', 'price': 1566.55, 'merchantId': 1582}, {'prodId': 13991988, 'date': '2025-10-05', 'price': 1566.55, 'merchantId': 1582}, {'prodId': 13991988, 'date': '2025-10-06', 'price': 1566.55, 'merchantId': 1582}, {'prodId': 13991988, 'date': '2025-10-07', 'price': 1609.9, 'merchantId': 1582}, {'prodId': 13991988, 'date': '2025-10-08', 'price': 1626.57, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-10-09', 'price': 1626.57, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-10-10', 'price': 1626.57, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-10-11', 'price': 1585.55, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2025-10-12', 'price': 1585.55, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2025-10-13', 'price': 1609.08, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-10-14', 'price': 1609.08, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-10-15', 'price': 1626.57, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-10-16', 'price': 1626.57, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-10-17', 'price': 1626.57, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-10-18', 'price': 1626.57, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-10-19', 'price': 1626.57, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-10-20', 'price': 1626.57, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-10-21', 'price': 1626.57, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-10-22', 'price': 1626.57, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-10-23', 'price': 1626.57, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-10-24', 'price': 1634.54, 'merchantId': 245}, {'prodId': 13991988, 'date': '2025-10-25', 'price': 1626.57, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-10-26', 'price': 1626.57, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-10-27', 'price': 1609.08, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-10-28', 'price': 1626.57, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-10-29', 'price': 1626.57, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-10-30', 'price': 1626.57, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-10-31', 'price': 1617.27, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-11-01', 'price': 1617.27, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-11-02', 'price': 1617.27, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-11-03', 'price': 1599.88, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-11-04', 'price': 1530.32, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-11-05', 'price': 1590.68, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-11-06', 'price': 1590.68, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-11-07', 'price': 1590.68, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-11-08', 'price': 1590.68, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-11-09', 'price': 1590.68, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-11-10', 'price': 1590.68, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-11-11', 'price': 1590.68, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-11-12', 'price': 1590.68, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-11-13', 'price': 1590.68, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-11-14', 'price': 1590.68, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-11-15', 'price': 1601.1, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2025-11-16', 'price': 1601.1, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2025-11-17', 'price': 1590.68, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-11-18', 'price': 1521.52, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-11-19', 'price': 1521.52, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-11-20', 'price': 1590.68, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-11-21', 'price': 1590.68, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-11-22', 'price': 1590.68, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-11-23', 'price': 1590.68, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-11-24', 'price': 1590.68, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-11-25', 'price': 1601.1, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2025-11-26', 'price': 1590.68, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-11-27', 'price': 1691.1, 'merchantId': 20583}, {'prodId': 13991988, 'date': '2025-11-28', 'price': 1691.1, 'merchantId': 20583}, {'prodId': 13991988, 'date': '2025-11-29', 'price': 1590.68, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-11-30', 'price': 1590.68, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-12-01', 'price': 1590.68, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-12-02', 'price': 1590.68, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-12-03', 'price': 1590.68, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-12-04', 'price': 1590.68, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-12-05', 'price': 1590.68, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-12-06', 'price': 1708.92, 'merchantId': 1582}, {'prodId': 13991988, 'date': '2025-12-07', 'price': 1708.92, 'merchantId': 1582}, {'prodId': 13991988, 'date': '2025-12-08', 'price': 1708.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-12-09', 'price': 1707.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-12-10', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13991988, 'date': '2025-12-11', 'price': 1707.0, 'merchantId': 245}, {'prodId': 13991988, 'date': '2025-12-12', 'price': 1707.0, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-12-13', 'price': 1707.0, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-12-14', 'price': 1707.0, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2025-12-15', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13991988, 'date': '2025-12-16', 'price': 1761.8, 'merchantId': 20583}, {'prodId': 13991988, 'date': '2025-12-17', 'price': 1761.8, 'merchantId': 20583}, {'prodId': 13991988, 'date': '2025-12-18', 'price': 1761.8, 'merchantId': 20583}, {'prodId': 13991988, 'date': '2025-12-19', 'price': 1708.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-12-20', 'price': 1708.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-12-21', 'price': 1708.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-12-22', 'price': 1708.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-12-23', 'price': 1708.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-12-24', 'price': 1708.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-12-25', 'price': 1708.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-12-26', 'price': 1708.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-12-27', 'price': 1708.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-12-28', 'price': 1708.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-12-29', 'price': 1708.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-12-30', 'price': 1708.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2025-12-31', 'price': 1708.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-01-01', 'price': 1708.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-01-02', 'price': 1708.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-01-03', 'price': 1708.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-01-04', 'price': 1708.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-01-05', 'price': 1708.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-01-06', 'price': 1708.0, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2026-01-07', 'price': 1729.0, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2026-01-08', 'price': 1699.0, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-01-09', 'price': 1521.52, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2026-01-10', 'price': 1521.52, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2026-01-11', 'price': 1521.52, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2026-01-12', 'price': 1521.52, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2026-01-13', 'price': 1530.32, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2026-01-14', 'price': 1530.32, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2026-01-15', 'price': 1530.32, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2026-01-16', 'price': 1664.0, 'merchantId': 245}, {'prodId': 13991988, 'date': '2026-01-17', 'price': 1699.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-01-18', 'price': 1699.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-01-19', 'price': 1699.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-01-20', 'price': 1699.0, 'merchantId': 245}, {'prodId': 13991988, 'date': '2026-01-21', 'price': 1799.0, 'merchantId': 21628}, {'prodId': 13991988, 'date': '2026-01-22', 'price': 1799.0, 'merchantId': 21628}, {'prodId': 13991988, 'date': '2026-01-23', 'price': 1799.0, 'merchantId': 21628}, {'prodId': 13991988, 'date': '2026-01-24', 'price': 1799.0, 'merchantId': 21628}, {'prodId': 13991988, 'date': '2026-01-25', 'price': 1799.0, 'merchantId': 21628}, {'prodId': 13991988, 'date': '2026-01-26', 'price': 1799.0, 'merchantId': 21628}, {'prodId': 13991988, 'date': '2026-01-27', 'price': 1799.0, 'merchantId': 21628}, {'prodId': 13991988, 'date': '2026-01-28', 'price': 1799.0, 'merchantId': 21628}, {'prodId': 13991988, 'date': '2026-01-29', 'price': 1799.0, 'merchantId': 21628}, {'prodId': 13991988, 'date': '2026-01-30', 'price': 1799.0, 'merchantId': 21628}, {'prodId': 13991988, 'date': '2026-01-31', 'price': 1799.0, 'merchantId': 21628}, {'prodId': 13991988, 'date': '2026-02-01', 'price': 1799.0, 'merchantId': 21628}, {'prodId': 13991988, 'date': '2026-02-02', 'price': 1799.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-02-03', 'price': 1798.9, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-02-04', 'price': 1708.96, 'merchantId': 245}, {'prodId': 13991988, 'date': '2026-02-05', 'price': 1798.9, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-02-06', 'price': 1798.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-02-07', 'price': 1798.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-02-08', 'price': 1798.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-02-09', 'price': 1797.9, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-02-10', 'price': 1797.79, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-02-11', 'price': 1797.74, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-02-12', 'price': 1797.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-02-13', 'price': 1796.9, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-02-14', 'price': 1796.9, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-02-15', 'price': 1796.9, 'merchantId': 2}, {'prodId': 13991988, 'date': '2026-02-16', 'price': 1796.9, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-02-17', 'price': 1796.9, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-02-18', 'price': 1708.9, 'merchantId': 2}, {'prodId': 13991988, 'date': '2026-02-19', 'price': 1708.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-02-20', 'price': 1708.0, 'merchantId': 2}, {'prodId': 13991988, 'date': '2026-02-21', 'price': 1708.0, 'merchantId': 2}, {'prodId': 13991988, 'date': '2026-02-22', 'price': 1708.0, 'merchantId': 2}, {'prodId': 13991988, 'date': '2026-02-23', 'price': 1708.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-02-24', 'price': 1708.0, 'merchantId': 34}, {'prodId': 13991988, 'date': '2026-02-25', 'price': 1789.99, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-02-26', 'price': 1789.99, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-02-27', 'price': 1796.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-02-28', 'price': 1796.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-03-01', 'price': 1796.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-03-02', 'price': 1619.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-03-03', 'price': 1618.9, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-03-04', 'price': 1619.1, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-03-05', 'price': 1619.1, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-03-06', 'price': 1619.1, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-03-07', 'price': 1619.1, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-03-08', 'price': 1619.1, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-03-09', 'price': 1619.1, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-03-10', 'price': 1619.1, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-03-11', 'price': 1664.1, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-03-12', 'price': 999.0, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-03-13', 'price': 999.0, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-03-14', 'price': 1709.05, 'merchantId': 2584}, {'prodId': 13991988, 'date': '2026-03-15', 'price': 1709.05, 'merchantId': 2584}, {'prodId': 13991988, 'date': '2026-03-16', 'price': 1709.05, 'merchantId': 2584}, {'prodId': 13991988, 'date': '2026-03-17', 'price': 1521.52, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2026-03-18', 'price': 1625.26, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2026-03-19', 'price': 1736.9, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-03-20', 'price': 1736.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-03-21', 'price': 1736.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-03-22', 'price': 1736.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-03-23', 'price': 1736.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-03-24', 'price': 1729.9, 'merchantId': 16108}, {'prodId': 13991988, 'date': '2026-03-25', 'price': 1729.9, 'merchantId': 16108}, {'prodId': 13991988, 'date': '2026-03-26', 'price': 1729.9, 'merchantId': 16108}, {'prodId': 13991988, 'date': '2026-03-27', 'price': 1729.9, 'merchantId': 16108}, {'prodId': 13991988, 'date': '2026-03-28', 'price': 1729.9, 'merchantId': 16108}, {'prodId': 13991988, 'date': '2026-03-29', 'price': 1729.9, 'merchantId': 16108}, {'prodId': 13991988, 'date': '2026-03-30', 'price': 1709.1, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-03-31', 'price': 1709.0, 'merchantId': 16108}, {'prodId': 13991988, 'date': '2026-04-01', 'price': 1708.9, 'merchantId': 2}, {'prodId': 13991988, 'date': '2026-04-02', 'price': 1559.0, 'merchantId': 2}, {'prodId': 13991988, 'date': '2026-04-03', 'price': 1558.99, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-04-04', 'price': 1558.99, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-04-05', 'price': 1558.99, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-04-06', 'price': 1558.99, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-04-07', 'price': 1708.0, 'merchantId': 2}, {'prodId': 13991988, 'date': '2026-04-08', 'price': 1707.9, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-04-09', 'price': 1446.56, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-04-10', 'price': 1707.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-04-11', 'price': 1669.07, 'merchantId': 245}, {'prodId': 13991988, 'date': '2026-04-12', 'price': 1669.07, 'merchantId': 245}, {'prodId': 13991988, 'date': '2026-04-13', 'price': 1668.09, 'merchantId': 245}, {'prodId': 13991988, 'date': '2026-04-14', 'price': 1661.25, 'merchantId': 245}, {'prodId': 13991988, 'date': '2026-04-15', 'price': 1661.25, 'merchantId': 245}, {'prodId': 13991988, 'date': '2026-04-16', 'price': 1660.17, 'merchantId': 245}, {'prodId': 13991988, 'date': '2026-04-17', 'price': 1659.29, 'merchantId': 245}, {'prodId': 13991988, 'date': '2026-04-18', 'price': 1690.9, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-04-19', 'price': 1529.68, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-04-20', 'price': 1690.9, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-04-21', 'price': 1690.9, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-04-22', 'price': 1549.25, 'merchantId': 1582}, {'prodId': 13991988, 'date': '2026-04-23', 'price': 1599.0, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-04-24', 'price': 1529.75, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-04-25', 'price': 1598.9, 'merchantId': 2}, {'prodId': 13991988, 'date': '2026-04-26', 'price': 1598.9, 'merchantId': 2}, {'prodId': 13991988, 'date': '2026-04-27', 'price': 1598.9, 'merchantId': 2}, {'prodId': 13991988, 'date': '2026-04-28', 'price': 1598.9, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2026-04-29', 'price': 1629.0, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-04-30', 'price': 1629.0, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-05-01', 'price': 1439.47, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-05-02', 'price': 1629.03, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-05-03', 'price': 1629.03, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-05-04', 'price': 1553.37, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-05-05', 'price': 1447.86, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-05-06', 'price': 1477.8, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-05-07', 'price': 1609.91, 'merchantId': 245}, {'prodId': 13991988, 'date': '2026-05-08', 'price': 1625.0, 'merchantId': 16108}, {'prodId': 13991988, 'date': '2026-05-09', 'price': 1625.0, 'merchantId': 16108}, {'prodId': 13991988, 'date': '2026-05-10', 'price': 1543.5, 'merchantId': 1582}, {'prodId': 13991988, 'date': '2026-05-11', 'price': 1625.0, 'merchantId': 16108}, {'prodId': 13991988, 'date': '2026-05-12', 'price': 1625.0, 'merchantId': 16108}, {'prodId': 13991988, 'date': '2026-05-13', 'price': 1625.0, 'merchantId': 16108}, {'prodId': 13991988, 'date': '2026-05-14', 'price': 1625.0, 'merchantId': 16108}, {'prodId': 13991988, 'date': '2026-05-15', 'price': 1625.0, 'merchantId': 16108}, {'prodId': 13991988, 'date': '2026-05-16', 'price': 1625.0, 'merchantId': 16108}, {'prodId': 13991988, 'date': '2026-05-17', 'price': 1636.8, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2026-05-18', 'price': 1538.19, 'merchantId': 16108}, {'prodId': 13991988, 'date': '2026-05-19', 'price': 1538.19, 'merchantId': 16108}, {'prodId': 13991988, 'date': '2026-05-20', 'price': 1599.0, 'merchantId': 4}, {'prodId': 13991988, 'date': '2026-05-21', 'price': 1538.19, 'merchantId': 16108}, {'prodId': 13991988, 'date': '2026-05-22', 'price': 1538.19, 'merchantId': 16108}, {'prodId': 13991988, 'date': '2026-05-23', 'price': 1518.1, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-05-24', 'price': 1562.49, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2026-05-25', 'price': 1562.49, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2026-05-26', 'price': 1562.49, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2026-05-27', 'price': 1551.36, 'merchantId': 245}, {'prodId': 13991988, 'date': '2026-05-28', 'price': 1498.31, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2026-05-29', 'price': 1498.31, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2026-05-30', 'price': 1550.48, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2026-05-31', 'price': 1550.48, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2026-06-01', 'price': 1533.06, 'merchantId': 23326}, {'prodId': 13991988, 'date': '2026-06-02', 'price': 1533.06, 'merchantId': 245}, {'prodId': 13991988, 'date': '2026-06-03', 'price': 1599.0, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-06-04', 'price': 1504.14, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2026-06-05', 'price': 1538.54, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2026-06-06', 'price': 1538.54, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2026-06-07', 'price': 1538.54, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2026-06-08', 'price': 1538.54, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2026-06-09', 'price': 1538.54, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2026-06-10', 'price': 1599.0, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-06-11', 'price': 1599.0, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-06-12', 'price': 1599.0, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-06-13', 'price': 1599.0, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-06-14', 'price': 1594.0, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-06-15', 'price': 1260.9, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2026-06-16', 'price': 1599.0, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-06-17', 'price': 1538.54, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2026-06-18', 'price': 1599.0, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-06-19', 'price': 1599.0, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-06-20', 'price': 1599.0, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-06-21', 'price': 1599.0, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-06-22', 'price': 1599.0, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-06-23', 'price': 1599.0, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-06-24', 'price': 1538.54, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2026-06-25', 'price': 1439.1, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-06-26', 'price': 1599.0, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-06-27', 'price': 1599.0, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-06-28', 'price': 1599.0, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-06-29', 'price': 1599.0, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-06-30', 'price': 1599.0, 'merchantId': 22902}, {'prodId': 13991988, 'date': '2026-07-01', 'price': 1538.54, 'merchantId': 22905}, {'prodId': 13991988, 'date': '2026-07-02', 'price': 1661.25, 'merchantId': 20583}, {'prodId': 13991988, 'date': '2026-07-03', 'price': 1661.25, 'merchantId': 20583}, {'prodId': 13991988, 'date': '2026-07-04', 'price': 1519.2, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-07-05', 'price': 1519.2, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-07-06', 'price': 1519.2, 'merchantId': 9385}, {'prodId': 13991988, 'date': '2026-07-07', 'price': 1519.2, 'merchantId': 9385}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 12547936, 'date': '2025-07-07', 'price': 2999.0, 'merchantId': 22902}, {'prodId': 12547936, 'date': '2025-07-08', 'price': 2999.0, 'merchantId': 22902}, {'prodId': 12547936, 'date': '2025-07-09', 'price': 2999.0, 'merchantId': 22902}, {'prodId': 12547936, 'date': '2025-07-10', 'price': 2998.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-07-11', 'price': 2913.06, 'merchantId': 20583}, {'prodId': 12547936, 'date': '2025-07-12', 'price': 2913.06, 'merchantId': 20583}, {'prodId': 12547936, 'date': '2025-07-13', 'price': 2998.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-07-14', 'price': 2913.06, 'merchantId': 20583}, {'prodId': 12547936, 'date': '2025-07-15', 'price': 2998.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-07-16', 'price': 2998.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-07-17', 'price': 2998.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-07-18', 'price': 2998.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-07-19', 'price': 2998.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-07-20', 'price': 2998.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-07-21', 'price': 2998.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-07-22', 'price': 2998.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-07-23', 'price': 3149.0, 'merchantId': 21629}, {'prodId': 12547936, 'date': '2025-07-24', 'price': 3149.0, 'merchantId': 21629}, {'prodId': 12547936, 'date': '2025-07-25', 'price': 3149.0, 'merchantId': 21629}, {'prodId': 12547936, 'date': '2025-07-26', 'price': 3149.0, 'merchantId': 21629}, {'prodId': 12547936, 'date': '2025-07-27', 'price': 3099.0, 'merchantId': 20609}, {'prodId': 12547936, 'date': '2025-07-28', 'price': 3099.0, 'merchantId': 20609}, {'prodId': 12547936, 'date': '2025-07-29', 'price': 2878.54, 'merchantId': 9385}, {'prodId': 12547936, 'date': '2025-07-30', 'price': 2878.54, 'merchantId': 9385}, {'prodId': 12547936, 'date': '2025-07-31', 'price': 2878.54, 'merchantId': 9385}, {'prodId': 12547936, 'date': '2025-08-01', 'price': 2978.99, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2025-08-02', 'price': 2999.0, 'merchantId': 20609}, {'prodId': 12547936, 'date': '2025-08-03', 'price': 2999.0, 'merchantId': 20609}, {'prodId': 12547936, 'date': '2025-08-04', 'price': 2979.0, 'merchantId': 22902}, {'prodId': 12547936, 'date': '2025-08-05', 'price': 2979.0, 'merchantId': 9385}, {'prodId': 12547936, 'date': '2025-08-06', 'price': 2979.0, 'merchantId': 9385}, {'prodId': 12547936, 'date': '2025-08-07', 'price': 2979.0, 'merchantId': 9385}, {'prodId': 12547936, 'date': '2025-08-08', 'price': 2979.0, 'merchantId': 9385}, {'prodId': 12547936, 'date': '2025-08-09', 'price': 2979.0, 'merchantId': 9385}, {'prodId': 12547936, 'date': '2025-08-10', 'price': 2979.0, 'merchantId': 9385}, {'prodId': 12547936, 'date': '2025-08-11', 'price': 2979.0, 'merchantId': 9385}, {'prodId': 12547936, 'date': '2025-08-12', 'price': 2999.0, 'merchantId': 20609}, {'prodId': 12547936, 'date': '2025-08-13', 'price': 2999.0, 'merchantId': 20609}, {'prodId': 12547936, 'date': '2025-08-14', 'price': 2999.0, 'merchantId': 20609}, {'prodId': 12547936, 'date': '2025-08-15', 'price': 2999.0, 'merchantId': 20609}, {'prodId': 12547936, 'date': '2025-08-16', 'price': 2999.0, 'merchantId': 20609}, {'prodId': 12547936, 'date': '2025-08-17', 'price': 2999.0, 'merchantId': 20609}, {'prodId': 12547936, 'date': '2025-08-18', 'price': 2999.0, 'merchantId': 20609}, {'prodId': 12547936, 'date': '2025-08-19', 'price': 2999.0, 'merchantId': 20609}, {'prodId': 12547936, 'date': '2025-08-20', 'price': 2999.0, 'merchantId': 20609}, {'prodId': 12547936, 'date': '2025-08-21', 'price': 2999.0, 'merchantId': 20609}, {'prodId': 12547936, 'date': '2025-08-22', 'price': 2999.0, 'merchantId': 20609}, {'prodId': 12547936, 'date': '2025-08-23', 'price': 2999.0, 'merchantId': 20609}, {'prodId': 12547936, 'date': '2025-08-24', 'price': 2999.0, 'merchantId': 20609}, {'prodId': 12547936, 'date': '2025-08-25', 'price': 2999.0, 'merchantId': 20609}, {'prodId': 12547936, 'date': '2025-08-26', 'price': 2999.0, 'merchantId': 20609}, {'prodId': 12547936, 'date': '2025-08-27', 'price': 2999.0, 'merchantId': 20609}, {'prodId': 12547936, 'date': '2025-08-28', 'price': 2999.0, 'merchantId': 20609}, {'prodId': 12547936, 'date': '2025-08-29', 'price': 2998.8, 'merchantId': 22902}, {'prodId': 12547936, 'date': '2025-08-30', 'price': 2998.8, 'merchantId': 22902}, {'prodId': 12547936, 'date': '2025-08-31', 'price': 2998.8, 'merchantId': 22902}, {'prodId': 12547936, 'date': '2025-09-01', 'price': 2998.8, 'merchantId': 22902}, {'prodId': 12547936, 'date': '2025-09-02', 'price': 2999.0, 'merchantId': 20609}, {'prodId': 12547936, 'date': '2025-09-03', 'price': 2999.0, 'merchantId': 20609}, {'prodId': 12547936, 'date': '2025-09-04', 'price': 2899.0, 'merchantId': 16108}, {'prodId': 12547936, 'date': '2025-09-05', 'price': 2899.0, 'merchantId': 16108}, {'prodId': 12547936, 'date': '2025-09-06', 'price': 2999.0, 'merchantId': 20609}, {'prodId': 12547936, 'date': '2025-09-07', 'price': 2999.0, 'merchantId': 20609}, {'prodId': 12547936, 'date': '2025-09-08', 'price': 2999.0, 'merchantId': 20609}, {'prodId': 12547936, 'date': '2025-09-09', 'price': 2999.0, 'merchantId': 20609}, {'prodId': 12547936, 'date': '2025-09-10', 'price': 2699.1, 'merchantId': 16108}, {'prodId': 12547936, 'date': '2025-09-11', 'price': 2699.1, 'merchantId': 16108}, {'prodId': 12547936, 'date': '2025-09-12', 'price': 2699.1, 'merchantId': 16108}, {'prodId': 12547936, 'date': '2025-09-13', 'price': 2998.89, 'merchantId': 21629}, {'prodId': 12547936, 'date': '2025-09-14', 'price': 2998.89, 'merchantId': 21629}, {'prodId': 12547936, 'date': '2025-09-15', 'price': 2998.89, 'merchantId': 21629}, {'prodId': 12547936, 'date': '2025-09-16', 'price': 2999.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-09-17', 'price': 2998.8, 'merchantId': 21629}, {'prodId': 12547936, 'date': '2025-09-18', 'price': 2964.9, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2025-09-19', 'price': 2964.9, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2025-09-20', 'price': 2964.9, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2025-09-21', 'price': 2964.9, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2025-09-22', 'price': 2964.9, 'merchantId': 9385}, {'prodId': 12547936, 'date': '2025-09-23', 'price': 2964.9, 'merchantId': 9385}, {'prodId': 12547936, 'date': '2025-09-24', 'price': 2964.9, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2025-09-25', 'price': 2999.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-09-26', 'price': 2999.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-09-27', 'price': 2999.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-09-28', 'price': 2973.93, 'merchantId': 9385}, {'prodId': 12547936, 'date': '2025-09-29', 'price': 2973.93, 'merchantId': 9385}, {'prodId': 12547936, 'date': '2025-09-30', 'price': 2999.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-10-01', 'price': 2999.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-10-02', 'price': 2998.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-10-03', 'price': 2998.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-10-04', 'price': 2998.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-10-05', 'price': 2998.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-10-06', 'price': 2989.9, 'merchantId': 21}, {'prodId': 12547936, 'date': '2025-10-07', 'price': 2989.9, 'merchantId': 21}, {'prodId': 12547936, 'date': '2025-10-08', 'price': 2997.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-10-09', 'price': 2997.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-10-10', 'price': 2997.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-10-11', 'price': 2997.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-10-12', 'price': 2997.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-10-13', 'price': 2997.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-10-14', 'price': 2997.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-10-15', 'price': 2997.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-10-16', 'price': 2997.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-10-17', 'price': 2932.16, 'merchantId': 9385}, {'prodId': 12547936, 'date': '2025-10-18', 'price': 2930.4, 'merchantId': 9385}, {'prodId': 12547936, 'date': '2025-10-19', 'price': 2899.0, 'merchantId': 9385}, {'prodId': 12547936, 'date': '2025-10-20', 'price': 2929.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-10-21', 'price': 2832.39, 'merchantId': 9385}, {'prodId': 12547936, 'date': '2025-10-22', 'price': 2929.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-10-23', 'price': 2929.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-10-24', 'price': 2929.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-10-25', 'price': 2929.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-10-26', 'price': 2929.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-10-27', 'price': 2929.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-10-28', 'price': 2929.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-10-29', 'price': 2929.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-10-30', 'price': 2929.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-10-31', 'price': 2899.0, 'merchantId': 9385}, {'prodId': 12547936, 'date': '2025-11-01', 'price': 2929.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-11-02', 'price': 2929.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-11-03', 'price': 2929.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-11-04', 'price': 2929.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-11-05', 'price': 2980.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-11-06', 'price': 2978.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-11-07', 'price': 2978.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-11-08', 'price': 2978.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-11-09', 'price': 2978.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-11-10', 'price': 2978.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-11-11', 'price': 2978.0, 'merchantId': 245}, {'prodId': 12547936, 'date': '2025-11-12', 'price': 2998.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-11-13', 'price': 2998.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-11-14', 'price': 2998.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-11-15', 'price': 2998.8, 'merchantId': 20583}, {'prodId': 12547936, 'date': '2025-11-16', 'price': 2998.8, 'merchantId': 20583}, {'prodId': 12547936, 'date': '2025-11-17', 'price': 2977.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-11-18', 'price': 2977.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-11-19', 'price': 2976.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-11-20', 'price': 2965.48, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-11-21', 'price': 2965.48, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-11-22', 'price': 2976.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-11-23', 'price': 2965.48, 'merchantId': 20583}, {'prodId': 12547936, 'date': '2025-11-24', 'price': 2669.01, 'merchantId': 20583}, {'prodId': 12547936, 'date': '2025-11-25', 'price': 2669.01, 'merchantId': 20612}, {'prodId': 12547936, 'date': '2025-11-26', 'price': 2669.01, 'merchantId': 20612}, {'prodId': 12547936, 'date': '2025-11-27', 'price': 2698.9, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-11-28', 'price': 2638.93, 'merchantId': 23326}, {'prodId': 12547936, 'date': '2025-11-29', 'price': 2698.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-11-30', 'price': 2698.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-12-01', 'price': 2697.9, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-12-02', 'price': 2697.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-12-03', 'price': 2696.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-12-04', 'price': 2696.0, 'merchantId': 23326}, {'prodId': 12547936, 'date': '2025-12-05', 'price': 2696.0, 'merchantId': 23326}, {'prodId': 12547936, 'date': '2025-12-06', 'price': 2696.0, 'merchantId': 23326}, {'prodId': 12547936, 'date': '2025-12-07', 'price': 2696.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-12-08', 'price': 2696.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2025-12-09', 'price': 2697.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-12-10', 'price': 2697.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-12-11', 'price': 2697.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-12-12', 'price': 2697.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-12-13', 'price': 2697.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-12-14', 'price': 2697.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-12-15', 'price': 2697.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-12-16', 'price': 2697.0, 'merchantId': 4}, {'prodId': 12547936, 'date': '2025-12-17', 'price': 2697.0, 'merchantId': 4}, {'prodId': 12547936, 'date': '2025-12-18', 'price': 2697.0, 'merchantId': 34}, {'prodId': 12547936, 'date': '2025-12-19', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2025-12-20', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2025-12-21', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2025-12-22', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2025-12-23', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2025-12-24', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2025-12-25', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2025-12-26', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2025-12-27', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2025-12-28', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2025-12-29', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2025-12-30', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2025-12-31', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-01', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-02', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-03', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-04', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-05', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-06', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-07', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-08', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-09', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-10', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-11', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-12', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-13', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-14', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-15', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-16', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-17', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-18', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-19', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-20', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-21', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-22', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-23', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-24', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-25', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-26', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-27', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-28', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-29', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-30', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-01-31', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-01', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-02', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-03', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-04', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-05', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-06', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-07', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-08', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-09', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-10', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-11', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-12', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-13', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-14', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-15', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-16', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-17', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-18', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-19', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-20', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-21', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-22', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-23', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-24', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-25', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-26', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-27', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-02-28', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-03-01', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-03-02', 'price': 2399.9, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-03-03', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-03-04', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-03-05', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-03-06', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-03-07', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-03-08', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-03-09', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-03-10', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-03-11', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-03-12', 'price': 2699.0, 'merchantId': 22905}, {'prodId': 12547936, 'date': '2026-03-13', 'price': 2924.1, 'merchantId': 22902}, {'prodId': 12547936, 'date': '2026-03-14', 'price': 2924.1, 'merchantId': 22902}, {'prodId': 12547936, 'date': '2026-03-15', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-03-16', 'price': 3104.1, 'merchantId': 16108}, {'prodId': 12547936, 'date': '2026-03-17', 'price': 2969.1, 'merchantId': 22902}, {'prodId': 12547936, 'date': '2026-03-18', 'price': 3104.1, 'merchantId': 16108}, {'prodId': 12547936, 'date': '2026-03-19', 'price': 2969.1, 'merchantId': 22902}, {'prodId': 12547936, 'date': '2026-03-20', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-03-21', 'price': 2969.1, 'merchantId': 22902}, {'prodId': 12547936, 'date': '2026-03-22', 'price': 3104.1, 'merchantId': 16108}, {'prodId': 12547936, 'date': '2026-03-23', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-03-24', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-03-25', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-03-26', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-03-27', 'price': 2399.9, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-03-28', 'price': 2399.9, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-03-29', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-03-30', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-03-31', 'price': 2399.9, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-04-01', 'price': 2399.9, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-04-02', 'price': 2399.9, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-04-03', 'price': 2399.9, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-04-04', 'price': 2399.9, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-04-05', 'price': 3599.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2026-04-06', 'price': 3599.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2026-04-07', 'price': 3599.0, 'merchantId': 2}, {'prodId': 12547936, 'date': '2026-04-08', 'price': 2399.9, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-04-09', 'price': 2399.9, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-04-10', 'price': 2924.17, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-04-11', 'price': 2399.9, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-04-12', 'price': 2924.17, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-04-13', 'price': 2924.17, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-04-14', 'price': 2924.17, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-04-15', 'price': 2789.99, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-04-16', 'price': 2789.99, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-04-17', 'price': 2679.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-04-18', 'price': 2839.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-04-19', 'price': 2839.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-04-20', 'price': 2679.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-04-21', 'price': 2679.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-04-22', 'price': 3059.1, 'merchantId': 22902}, {'prodId': 12547936, 'date': '2026-04-23', 'price': 3059.1, 'merchantId': 16108}, {'prodId': 12547936, 'date': '2026-04-24', 'price': 3059.1, 'merchantId': 16108}, {'prodId': 12547936, 'date': '2026-04-25', 'price': 4033.35, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-04-26', 'price': 4031.8, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-04-27', 'price': 3059.1, 'merchantId': 22902}, {'prodId': 12547936, 'date': '2026-04-28', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-04-29', 'price': 3059.1, 'merchantId': 22902}, {'prodId': 12547936, 'date': '2026-04-30', 'price': 3599.0, 'merchantId': 245}, {'prodId': 12547936, 'date': '2026-05-01', 'price': 3599.0, 'merchantId': 245}, {'prodId': 12547936, 'date': '2026-05-02', 'price': 2153.4, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-05-03', 'price': 3599.0, 'merchantId': 245}, {'prodId': 12547936, 'date': '2026-05-04', 'price': 3599.0, 'merchantId': 245}, {'prodId': 12547936, 'date': '2026-05-05', 'price': 2718.17, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-05-06', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-05-07', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-05-08', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-05-09', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-05-10', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-05-11', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-05-12', 'price': 2718.17, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-05-13', 'price': 2399.9, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-05-14', 'price': 2399.9, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-05-15', 'price': 2399.9, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-05-16', 'price': 2399.9, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-05-17', 'price': 2399.9, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-05-18', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-05-19', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-05-20', 'price': 2789.99, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-05-21', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-05-22', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-05-23', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-05-24', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-05-25', 'price': 4074.62, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-05-26', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-05-27', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-05-28', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-05-29', 'price': 2789.99, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-05-30', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-05-31', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-06-01', 'price': 2879.1, 'merchantId': 22902}, {'prodId': 12547936, 'date': '2026-06-02', 'price': 2687.27, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-06-03', 'price': 2687.27, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-06-04', 'price': 2879.1, 'merchantId': 22902}, {'prodId': 12547936, 'date': '2026-06-05', 'price': 2879.1, 'merchantId': 22902}, {'prodId': 12547936, 'date': '2026-06-06', 'price': 2879.1, 'merchantId': 22902}, {'prodId': 12547936, 'date': '2026-06-07', 'price': 2879.1, 'merchantId': 22902}, {'prodId': 12547936, 'date': '2026-06-08', 'price': 2879.1, 'merchantId': 22902}, {'prodId': 12547936, 'date': '2026-06-09', 'price': 2789.1, 'merchantId': 22902}, {'prodId': 12547936, 'date': '2026-06-10', 'price': 2687.27, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-06-11', 'price': 2687.27, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-06-12', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-06-13', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-06-14', 'price': 5579.0, 'merchantId': 20612}, {'prodId': 12547936, 'date': '2026-06-15', 'price': 3599.0, 'merchantId': 21628}, {'prodId': 12547936, 'date': '2026-06-16', 'price': 2789.1, 'merchantId': 22902}, {'prodId': 12547936, 'date': '2026-06-17', 'price': 2789.1, 'merchantId': 22902}, {'prodId': 12547936, 'date': '2026-06-18', 'price': 2501.87, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-06-19', 'price': 2687.27, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-06-20', 'price': 2687.27, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-06-21', 'price': 2687.27, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-06-22', 'price': 2687.27, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-06-23', 'price': 2687.27, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-06-24', 'price': 2687.27, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-06-25', 'price': 2687.27, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-06-26', 'price': 2789.1, 'merchantId': 22902}, {'prodId': 12547936, 'date': '2026-06-27', 'price': 2789.1, 'merchantId': 22902}, {'prodId': 12547936, 'date': '2026-06-28', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-06-29', 'price': 2929.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-06-30', 'price': 2553.37, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-07-01', 'price': 2553.37, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-07-02', 'price': 2789.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-07-03', 'price': 2559.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-07-04', 'price': 2559.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-07-05', 'price': 2559.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-07-06', 'price': 2559.0, 'merchantId': 1582}, {'prodId': 12547936, 'date': '2026-07-07', 'price': 2559.0, 'merchantId': 1582}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13992940, 'date': '2025-09-16', 'price': 11249.1, 'merchantId': 22902}, {'prodId': 13992940, 'date': '2025-09-17', 'price': 11249.1, 'merchantId': 22902}, {'prodId': 13992940, 'date': '2025-09-18', 'price': 11249.1, 'merchantId': 22902}, {'prodId': 13992940, 'date': '2025-09-19', 'price': 11249.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-09-20', 'price': 11249.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-09-21', 'price': 11249.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-09-22', 'price': 11249.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-09-23', 'price': 11249.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-09-24', 'price': 11249.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-09-25', 'price': 11249.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-09-26', 'price': 11249.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-09-27', 'price': 11249.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-09-28', 'price': 11249.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-09-29', 'price': 11249.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-09-30', 'price': 11249.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-10-01', 'price': 11249.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-10-02', 'price': 10999.12, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-10-03', 'price': 10999.12, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-10-04', 'price': 10999.12, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-10-05', 'price': 10999.12, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-10-06', 'price': 10999.12, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-10-07', 'price': 10999.12, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-10-08', 'price': 10999.12, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-10-09', 'price': 10999.12, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-10-10', 'price': 10999.12, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-10-11', 'price': 11249.1, 'merchantId': 22902}, {'prodId': 13992940, 'date': '2025-10-12', 'price': 11249.1, 'merchantId': 22902}, {'prodId': 13992940, 'date': '2025-10-13', 'price': 11249.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-10-14', 'price': 11249.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-10-15', 'price': 11249.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-10-16', 'price': 11249.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-10-17', 'price': 11249.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-10-18', 'price': 10999.12, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-10-19', 'price': 10999.12, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-10-20', 'price': 10999.12, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-10-21', 'price': 11249.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-10-22', 'price': 11249.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-10-23', 'price': 10999.12, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-10-24', 'price': 11249.1, 'merchantId': 22902}, {'prodId': 13992940, 'date': '2025-10-25', 'price': 10624.15, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-10-26', 'price': 10624.15, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-10-27', 'price': 11249.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2025-10-28', 'price': 11249.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2025-10-29', 'price': 11249.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2025-10-30', 'price': 10624.15, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-10-31', 'price': 10624.15, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-11-01', 'price': 10624.15, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-11-02', 'price': 10624.15, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-11-03', 'price': 10624.15, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-11-04', 'price': 10624.15, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-11-05', 'price': 10624.15, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-11-06', 'price': 11249.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2025-11-07', 'price': 10624.15, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-11-08', 'price': 11249.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2025-11-09', 'price': 11249.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2025-11-10', 'price': 11249.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2025-11-11', 'price': 11249.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2025-11-12', 'price': 11249.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2025-11-13', 'price': 11248.95, 'merchantId': 9385}, {'prodId': 13992940, 'date': '2025-11-14', 'price': 10249.1, 'merchantId': 21}, {'prodId': 13992940, 'date': '2025-11-15', 'price': 10249.1, 'merchantId': 21}, {'prodId': 13992940, 'date': '2025-11-16', 'price': 10249.1, 'merchantId': 21}, {'prodId': 13992940, 'date': '2025-11-17', 'price': 10249.1, 'merchantId': 21}, {'prodId': 13992940, 'date': '2025-11-18', 'price': 10249.1, 'merchantId': 21}, {'prodId': 13992940, 'date': '2025-11-19', 'price': 10249.1, 'merchantId': 21}, {'prodId': 13992940, 'date': '2025-11-20', 'price': 10249.1, 'merchantId': 21}, {'prodId': 13992940, 'date': '2025-11-21', 'price': 10249.1, 'merchantId': 21}, {'prodId': 13992940, 'date': '2025-11-22', 'price': 10249.1, 'merchantId': 21}, {'prodId': 13992940, 'date': '2025-11-23', 'price': 10249.1, 'merchantId': 9385}, {'prodId': 13992940, 'date': '2025-11-24', 'price': 10249.09, 'merchantId': 9385}, {'prodId': 13992940, 'date': '2025-11-25', 'price': 10249.1, 'merchantId': 21}, {'prodId': 13992940, 'date': '2025-11-26', 'price': 10601.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-11-27', 'price': 10601.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-11-28', 'price': 10749.14, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-11-29', 'price': 10190.14, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-11-30', 'price': 10427.12, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-12-01', 'price': 10427.12, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-12-02', 'price': 10999.12, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-12-03', 'price': 10999.12, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-12-04', 'price': 10999.12, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-12-05', 'price': 11249.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2025-12-06', 'price': 10894.5, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-12-07', 'price': 10894.5, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-12-08', 'price': 10894.5, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-12-09', 'price': 11249.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2025-12-10', 'price': 11249.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2025-12-11', 'price': 10674.58, 'merchantId': 5}, {'prodId': 13992940, 'date': '2025-12-12', 'price': 10674.58, 'merchantId': 5}, {'prodId': 13992940, 'date': '2025-12-13', 'price': 10894.5, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-12-14', 'price': 10894.5, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-12-15', 'price': 10894.5, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-12-16', 'price': 10894.5, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-12-17', 'price': 10894.5, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-12-18', 'price': 11249.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2025-12-19', 'price': 11249.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2025-12-20', 'price': 10576.72, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-12-21', 'price': 10576.72, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-12-22', 'price': 10817.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-12-23', 'price': 10817.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-12-24', 'price': 10817.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-12-25', 'price': 10817.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-12-26', 'price': 10817.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2025-12-27', 'price': 11249.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2025-12-28', 'price': 11249.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2025-12-29', 'price': 11249.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2025-12-30', 'price': 11249.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2025-12-31', 'price': 11249.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2026-01-01', 'price': 11249.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2026-01-02', 'price': 11249.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2026-01-03', 'price': 11249.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2026-01-04', 'price': 11249.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2026-01-05', 'price': 11249.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2026-01-06', 'price': 11249.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2026-01-07', 'price': 11249.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2026-01-08', 'price': 10817.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2026-01-09', 'price': 11249.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2026-01-10', 'price': 10349.0, 'merchantId': 245}, {'prodId': 13992940, 'date': '2026-01-11', 'price': 10817.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2026-01-12', 'price': 10817.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2026-01-13', 'price': 10249.1, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-01-14', 'price': 10249.1, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-01-15', 'price': 10249.1, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-01-16', 'price': 10249.1, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-01-17', 'price': 10249.1, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-01-18', 'price': 9999.99, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-01-19', 'price': 9999.99, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-01-20', 'price': 9999.99, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-01-21', 'price': 9999.9, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-01-22', 'price': 9999.9, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-01-23', 'price': 9999.9, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-01-24', 'price': 10249.1, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-01-25', 'price': 10249.1, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-01-26', 'price': 10124.1, 'merchantId': 22902}, {'prodId': 13992940, 'date': '2026-01-27', 'price': 9999.9, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-01-28', 'price': 9999.9, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-01-29', 'price': 9999.9, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-01-30', 'price': 9999.9, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-01-31', 'price': 9999.9, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-02-01', 'price': 9999.9, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-02-02', 'price': 9999.9, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-02-03', 'price': 9999.9, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-02-04', 'price': 10123.0, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2026-02-05', 'price': 10817.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2026-02-06', 'price': 10817.1, 'merchantId': 23326}, {'prodId': 13992940, 'date': '2026-02-07', 'price': 11248.0, 'merchantId': 21629}, {'prodId': 13992940, 'date': '2026-02-08', 'price': 11248.0, 'merchantId': 21629}, {'prodId': 13992940, 'date': '2026-02-09', 'price': 11248.0, 'merchantId': 21629}, {'prodId': 13992940, 'date': '2026-02-10', 'price': 9999.9, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-02-11', 'price': 11222.1, 'merchantId': 20583}, {'prodId': 13992940, 'date': '2026-02-12', 'price': 11222.1, 'merchantId': 20583}, {'prodId': 13992940, 'date': '2026-02-13', 'price': 11222.1, 'merchantId': 20612}, {'prodId': 13992940, 'date': '2026-02-14', 'price': 11033.1, 'merchantId': 20583}, {'prodId': 13992940, 'date': '2026-02-15', 'price': 11033.1, 'merchantId': 20583}, {'prodId': 13992940, 'date': '2026-02-16', 'price': 11033.1, 'merchantId': 20583}, {'prodId': 13992940, 'date': '2026-02-17', 'price': 11033.1, 'merchantId': 20583}, {'prodId': 13992940, 'date': '2026-02-18', 'price': 11033.1, 'merchantId': 20583}, {'prodId': 13992940, 'date': '2026-02-19', 'price': 11033.1, 'merchantId': 20583}, {'prodId': 13992940, 'date': '2026-02-20', 'price': 11248.0, 'merchantId': 21629}, {'prodId': 13992940, 'date': '2026-02-21', 'price': 11248.0, 'merchantId': 21629}, {'prodId': 13992940, 'date': '2026-02-22', 'price': 11248.0, 'merchantId': 21629}, {'prodId': 13992940, 'date': '2026-02-23', 'price': 11248.0, 'merchantId': 21629}, {'prodId': 13992940, 'date': '2026-02-24', 'price': 11248.0, 'merchantId': 21629}, {'prodId': 13992940, 'date': '2026-02-25', 'price': 10999.0, 'merchantId': 9385}, {'prodId': 13992940, 'date': '2026-02-26', 'price': 10999.0, 'merchantId': 9385}, {'prodId': 13992940, 'date': '2026-02-27', 'price': 10999.0, 'merchantId': 9385}, {'prodId': 13992940, 'date': '2026-02-28', 'price': 10124.1, 'merchantId': 22902}, {'prodId': 13992940, 'date': '2026-03-01', 'price': 10124.1, 'merchantId': 22902}, {'prodId': 13992940, 'date': '2026-03-02', 'price': 10124.1, 'merchantId': 22902}, {'prodId': 13992940, 'date': '2026-03-03', 'price': 9899.0, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-03-04', 'price': 9899.0, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-03-05', 'price': 9899.0, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-03-06', 'price': 9899.0, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-03-07', 'price': 10124.1, 'merchantId': 22902}, {'prodId': 13992940, 'date': '2026-03-08', 'price': 10124.1, 'merchantId': 22902}, {'prodId': 13992940, 'date': '2026-03-09', 'price': 9899.0, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-03-10', 'price': 9899.0, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-03-11', 'price': 9899.0, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-03-12', 'price': 10124.1, 'merchantId': 22902}, {'prodId': 13992940, 'date': '2026-03-13', 'price': 10124.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2026-03-14', 'price': 10124.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2026-03-15', 'price': 10124.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2026-03-16', 'price': 10124.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2026-03-17', 'price': 10123.9, 'merchantId': 4}, {'prodId': 13992940, 'date': '2026-03-18', 'price': 10123.9, 'merchantId': 4}, {'prodId': 13992940, 'date': '2026-03-19', 'price': 10123.0, 'merchantId': 4}, {'prodId': 13992940, 'date': '2026-03-20', 'price': 10027.779999999999, 'merchantId': 20904}, {'prodId': 13992940, 'date': '2026-03-21', 'price': 10027.779999999999, 'merchantId': 20904}, {'prodId': 13992940, 'date': '2026-03-22', 'price': 10027.779999999999, 'merchantId': 20904}, {'prodId': 13992940, 'date': '2026-03-23', 'price': 10027.779999999999, 'merchantId': 20904}, {'prodId': 13992940, 'date': '2026-03-24', 'price': 10027.779999999999, 'merchantId': 20904}, {'prodId': 13992940, 'date': '2026-03-25', 'price': 10027.779999999999, 'merchantId': 20904}, {'prodId': 13992940, 'date': '2026-03-26', 'price': 9349.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-03-27', 'price': 9349.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-03-28', 'price': 9349.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-03-29', 'price': 9349.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-03-30', 'price': 9349.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-03-31', 'price': 9349.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-04-01', 'price': 9299.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-04-02', 'price': 9299.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-04-03', 'price': 9299.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-04-04', 'price': 9299.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-04-05', 'price': 9399.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-04-06', 'price': 9399.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-04-07', 'price': 10799.1, 'merchantId': 22902}, {'prodId': 13992940, 'date': '2026-04-08', 'price': 10799.1, 'merchantId': 22902}, {'prodId': 13992940, 'date': '2026-04-09', 'price': 9299.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-04-10', 'price': 9299.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-04-11', 'price': 11099.9, 'merchantId': 20583}, {'prodId': 13992940, 'date': '2026-04-12', 'price': 9711.109999999999, 'merchantId': 20904}, {'prodId': 13992940, 'date': '2026-04-13', 'price': 9711.109999999999, 'merchantId': 20904}, {'prodId': 13992940, 'date': '2026-04-14', 'price': 9711.109999999999, 'merchantId': 20904}, {'prodId': 13992940, 'date': '2026-04-15', 'price': 9711.109999999999, 'merchantId': 20904}, {'prodId': 13992940, 'date': '2026-04-16', 'price': 9299.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-04-17', 'price': 9299.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-04-18', 'price': 9299.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-04-19', 'price': 9299.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-04-20', 'price': 9299.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-04-21', 'price': 9299.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-04-22', 'price': 9149.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-04-23', 'price': 9149.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-04-24', 'price': 10999.1, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-04-25', 'price': 9711.109999999999, 'merchantId': 20904}, {'prodId': 13992940, 'date': '2026-04-26', 'price': 9711.109999999999, 'merchantId': 20904}, {'prodId': 13992940, 'date': '2026-04-27', 'price': 9149.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-04-28', 'price': 9049.0, 'merchantId': 15125}, {'prodId': 13992940, 'date': '2026-04-29', 'price': 9048.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-04-30', 'price': 8999.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-05-01', 'price': 8999.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-05-02', 'price': 8999.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-05-03', 'price': 8999.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-05-04', 'price': 8999.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-05-05', 'price': 8999.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-05-06', 'price': 8999.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-05-07', 'price': 8999.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-05-08', 'price': 9998.1, 'merchantId': 9385}, {'prodId': 13992940, 'date': '2026-05-09', 'price': 9998.1, 'merchantId': 9385}, {'prodId': 13992940, 'date': '2026-05-10', 'price': 9998.1, 'merchantId': 9385}, {'prodId': 13992940, 'date': '2026-05-11', 'price': 9711.109999999999, 'merchantId': 20904}, {'prodId': 13992940, 'date': '2026-05-12', 'price': 9711.109999999999, 'merchantId': 20904}, {'prodId': 13992940, 'date': '2026-05-13', 'price': 9711.109999999999, 'merchantId': 20904}, {'prodId': 13992940, 'date': '2026-05-14', 'price': 9711.109999999999, 'merchantId': 20904}, {'prodId': 13992940, 'date': '2026-05-15', 'price': 9711.109999999999, 'merchantId': 20904}, {'prodId': 13992940, 'date': '2026-05-16', 'price': 9711.109999999999, 'merchantId': 20904}, {'prodId': 13992940, 'date': '2026-05-17', 'price': 9711.109999999999, 'merchantId': 20904}, {'prodId': 13992940, 'date': '2026-05-18', 'price': 9711.109999999999, 'merchantId': 20904}, {'prodId': 13992940, 'date': '2026-05-19', 'price': 9711.109999999999, 'merchantId': 20904}, {'prodId': 13992940, 'date': '2026-05-20', 'price': 9049.0, 'merchantId': 15125}, {'prodId': 13992940, 'date': '2026-05-21', 'price': 9049.0, 'merchantId': 15125}, {'prodId': 13992940, 'date': '2026-05-22', 'price': 9049.0, 'merchantId': 15125}, {'prodId': 13992940, 'date': '2026-05-23', 'price': 9049.0, 'merchantId': 15125}, {'prodId': 13992940, 'date': '2026-05-24', 'price': 9049.0, 'merchantId': 15125}, {'prodId': 13992940, 'date': '2026-05-25', 'price': 8949.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-05-26', 'price': 8949.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-05-27', 'price': 8949.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-05-28', 'price': 8949.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-05-29', 'price': 8849.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-05-30', 'price': 8849.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-05-31', 'price': 8849.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-06-01', 'price': 8649.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-06-02', 'price': 8649.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-06-03', 'price': 8550.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-06-04', 'price': 8550.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-06-05', 'price': 8550.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-06-06', 'price': 8550.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-06-07', 'price': 8550.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-06-08', 'price': 8550.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-06-09', 'price': 8499.0, 'merchantId': 15125}, {'prodId': 13992940, 'date': '2026-06-10', 'price': 8498.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-06-11', 'price': 8449.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-06-12', 'price': 8449.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-06-13', 'price': 8449.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-06-14', 'price': 8449.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-06-15', 'price': 8445.0, 'merchantId': 15125}, {'prodId': 13992940, 'date': '2026-06-16', 'price': 8445.0, 'merchantId': 15125}, {'prodId': 13992940, 'date': '2026-06-17', 'price': 8339.0, 'merchantId': 15125}, {'prodId': 13992940, 'date': '2026-06-18', 'price': 8339.0, 'merchantId': 15125}, {'prodId': 13992940, 'date': '2026-06-19', 'price': 8339.0, 'merchantId': 15125}, {'prodId': 13992940, 'date': '2026-06-20', 'price': 8339.0, 'merchantId': 15125}, {'prodId': 13992940, 'date': '2026-06-21', 'price': 8339.0, 'merchantId': 15125}, {'prodId': 13992940, 'date': '2026-06-22', 'price': 8339.0, 'merchantId': 15125}, {'prodId': 13992940, 'date': '2026-06-23', 'price': 8339.0, 'merchantId': 15125}, {'prodId': 13992940, 'date': '2026-06-24', 'price': 8349.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-06-25', 'price': 8349.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-06-26', 'price': 8349.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-06-27', 'price': 8349.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-06-28', 'price': 8999.99, 'merchantId': 22905}, {'prodId': 13992940, 'date': '2026-06-29', 'price': 8999.99, 'merchantId': 22905}, {'prodId': 13992940, 'date': '2026-06-30', 'price': 9224.1, 'merchantId': 20583}, {'prodId': 13992940, 'date': '2026-07-01', 'price': 8999.99, 'merchantId': 21}, {'prodId': 13992940, 'date': '2026-07-02', 'price': 9224.1, 'merchantId': 20583}, {'prodId': 13992940, 'date': '2026-07-03', 'price': 9224.1, 'merchantId': 20583}, {'prodId': 13992940, 'date': '2026-07-04', 'price': 9224.1, 'merchantId': 20583}, {'prodId': 13992940, 'date': '2026-07-05', 'price': 8349.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-07-06', 'price': 8499.0, 'merchantId': 16623}, {'prodId': 13992940, 'date': '2026-07-07', 'price': 8499.0, 'merchantId': 16623}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13993244, 'date': '2025-10-08', 'price': 709.1, 'merchantId': 21628}, {'prodId': 13993244, 'date': '2025-10-09', 'price': 709.1, 'merchantId': 21628}, {'prodId': 13993244, 'date': '2025-10-10', 'price': 709.1, 'merchantId': 21628}, {'prodId': 13993244, 'date': '2025-10-11', 'price': 709.1, 'merchantId': 21628}, {'prodId': 13993244, 'date': '2025-10-12', 'price': 709.1, 'merchantId': 21628}, {'prodId': 13993244, 'date': '2025-10-13', 'price': 709.1, 'merchantId': 21628}, {'prodId': 13993244, 'date': '2025-10-14', 'price': 709.1, 'merchantId': 21628}, {'prodId': 13993244, 'date': '2025-10-15', 'price': 709.1, 'merchantId': 21628}, {'prodId': 13993244, 'date': '2025-10-16', 'price': 709.1, 'merchantId': 21628}, {'prodId': 13993244, 'date': '2025-10-17', 'price': 709.1, 'merchantId': 21628}, {'prodId': 13993244, 'date': '2025-10-18', 'price': 709.1, 'merchantId': 21628}, {'prodId': 13993244, 'date': '2025-10-19', 'price': 709.1, 'merchantId': 21628}, {'prodId': 13993244, 'date': '2025-10-20', 'price': 709.1, 'merchantId': 21628}, {'prodId': 13993244, 'date': '2025-10-21', 'price': 709.1, 'merchantId': 21628}, {'prodId': 13993244, 'date': '2025-10-22', 'price': 699.9, 'merchantId': 20612}, {'prodId': 13993244, 'date': '2025-10-23', 'price': 699.9, 'merchantId': 20612}, {'prodId': 13993244, 'date': '2025-10-24', 'price': 699.1, 'merchantId': 21628}, {'prodId': 13993244, 'date': '2025-10-25', 'price': 699.1, 'merchantId': 21628}, {'prodId': 13993244, 'date': '2025-10-26', 'price': 699.1, 'merchantId': 21628}, {'prodId': 13993244, 'date': '2025-10-27', 'price': 699.1, 'merchantId': 21628}, {'prodId': 13993244, 'date': '2025-10-28', 'price': 699.1, 'merchantId': 21628}, {'prodId': 13993244, 'date': '2025-10-29', 'price': 699.1, 'merchantId': 21628}, {'prodId': 13993244, 'date': '2025-10-30', 'price': 699.1, 'merchantId': 21628}, {'prodId': 13993244, 'date': '2025-10-31', 'price': 699.1, 'merchantId': 21628}, {'prodId': 13993244, 'date': '2025-11-01', 'price': 699.1, 'merchantId': 21628}, {'prodId': 13993244, 'date': '2025-11-02', 'price': 699.1, 'merchantId': 21628}, {'prodId': 13993244, 'date': '2025-11-03', 'price': 699.1, 'merchantId': 21628}, {'prodId': 13993244, 'date': '2025-11-04', 'price': 699.1, 'merchantId': 21628}, {'prodId': 13993244, 'date': '2025-11-05', 'price': 629.0, 'merchantId': 34}, {'prodId': 13993244, 'date': '2025-11-06', 'price': 619.9, 'merchantId': 6132}, {'prodId': 13993244, 'date': '2025-11-07', 'price': 619.9, 'merchantId': 6132}, {'prodId': 13993244, 'date': '2025-11-08', 'price': 628.0, 'merchantId': 34}, {'prodId': 13993244, 'date': '2025-11-09', 'price': 628.0, 'merchantId': 34}, {'prodId': 13993244, 'date': '2025-11-10', 'price': 628.0, 'merchantId': 34}, {'prodId': 13993244, 'date': '2025-11-11', 'price': 628.0, 'merchantId': 34}, {'prodId': 13993244, 'date': '2025-11-12', 'price': 628.0, 'merchantId': 34}, {'prodId': 13993244, 'date': '2025-11-13', 'price': 619.9, 'merchantId': 6132}, {'prodId': 13993244, 'date': '2025-11-14', 'price': 419.9, 'merchantId': 245}, {'prodId': 13993244, 'date': '2025-11-15', 'price': 570.31, 'merchantId': 245}, {'prodId': 13993244, 'date': '2025-11-16', 'price': 570.31, 'merchantId': 245}, {'prodId': 13993244, 'date': '2025-11-17', 'price': 570.31, 'merchantId': 245}, {'prodId': 13993244, 'date': '2025-11-18', 'price': 570.31, 'merchantId': 245}, {'prodId': 13993244, 'date': '2025-11-19', 'price': 570.31, 'merchantId': 245}, {'prodId': 13993244, 'date': '2025-11-20', 'price': 570.31, 'merchantId': 245}, {'prodId': 13993244, 'date': '2025-11-21', 'price': 570.31, 'merchantId': 245}, {'prodId': 13993244, 'date': '2025-11-22', 'price': 570.31, 'merchantId': 245}, {'prodId': 13993244, 'date': '2025-11-23', 'price': 570.31, 'merchantId': 245}, {'prodId': 13993244, 'date': '2025-11-24', 'price': 570.31, 'merchantId': 245}, {'prodId': 13993244, 'date': '2025-11-25', 'price': 570.31, 'merchantId': 245}, {'prodId': 13993244, 'date': '2025-11-26', 'price': 570.31, 'merchantId': 245}, {'prodId': 13993244, 'date': '2025-11-27', 'price': 599.0, 'merchantId': 34}, {'prodId': 13993244, 'date': '2025-11-28', 'price': 570.31, 'merchantId': 245}, {'prodId': 13993244, 'date': '2025-11-29', 'price': 570.31, 'merchantId': 245}, {'prodId': 13993244, 'date': '2025-11-30', 'price': 567.89, 'merchantId': 1582}, {'prodId': 13993244, 'date': '2025-12-01', 'price': 567.89, 'merchantId': 1582}, {'prodId': 13993244, 'date': '2025-12-02', 'price': 589.9, 'merchantId': 20612}, {'prodId': 13993244, 'date': '2025-12-03', 'price': 569.05, 'merchantId': 23254}, {'prodId': 13993244, 'date': '2025-12-04', 'price': 589.9, 'merchantId': 20612}, {'prodId': 13993244, 'date': '2025-12-05', 'price': 589.9, 'merchantId': 20612}, {'prodId': 13993244, 'date': '2025-12-06', 'price': 589.9, 'merchantId': 20612}, {'prodId': 13993244, 'date': '2025-12-07', 'price': 589.9, 'merchantId': 20612}, {'prodId': 13993244, 'date': '2025-12-08', 'price': 589.9, 'merchantId': 20612}, {'prodId': 13993244, 'date': '2025-12-09', 'price': 589.9, 'merchantId': 20612}, {'prodId': 13993244, 'date': '2025-12-10', 'price': 589.9, 'merchantId': 20612}, {'prodId': 13993244, 'date': '2025-12-11', 'price': 589.9, 'merchantId': 20612}, {'prodId': 13993244, 'date': '2025-12-12', 'price': 589.9, 'merchantId': 20612}, {'prodId': 13993244, 'date': '2025-12-13', 'price': 589.9, 'merchantId': 20612}, {'prodId': 13993244, 'date': '2025-12-14', 'price': 589.9, 'merchantId': 20612}, {'prodId': 13993244, 'date': '2025-12-15', 'price': 589.9, 'merchantId': 20612}, {'prodId': 13993244, 'date': '2025-12-16', 'price': 589.9, 'merchantId': 20612}, {'prodId': 13993244, 'date': '2025-12-17', 'price': 589.9, 'merchantId': 20612}, {'prodId': 13993244, 'date': '2025-12-18', 'price': 589.9, 'merchantId': 20612}, {'prodId': 13993244, 'date': '2025-12-19', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2025-12-20', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2025-12-21', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2025-12-22', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2025-12-23', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2025-12-24', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2025-12-25', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2025-12-26', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2025-12-27', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2025-12-28', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2025-12-29', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2025-12-30', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2025-12-31', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-01-01', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-01-02', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-01-03', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-01-04', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-01-05', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-01-06', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-01-07', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-01-08', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-01-09', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-01-10', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-01-11', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-01-12', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-01-13', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-01-14', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-01-15', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-01-16', 'price': 641.9, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-01-17', 'price': 641.9, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-01-18', 'price': 641.9, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-01-19', 'price': 641.9, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-01-20', 'price': 641.9, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-01-21', 'price': 643.0, 'merchantId': 23326}, {'prodId': 13993244, 'date': '2026-01-22', 'price': 643.9, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-01-23', 'price': 643.9, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-01-24', 'price': 643.9, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-01-25', 'price': 643.9, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-01-26', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-01-27', 'price': 598.99, 'merchantId': 23254}, {'prodId': 13993244, 'date': '2026-01-28', 'price': 568.1, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-01-29', 'price': 568.1, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-01-30', 'price': 568.0, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-01-31', 'price': 568.0, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-02-01', 'price': 568.0, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-02-02', 'price': 568.0, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-02-03', 'price': 596.0, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-02-04', 'price': 566.2, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-02-05', 'price': 595.0, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-02-06', 'price': 594.9, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-02-07', 'price': 594.9, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-02-08', 'price': 594.9, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-02-09', 'price': 594.79, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-02-10', 'price': 594.49, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-02-11', 'price': 594.49, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-02-12', 'price': 594.49, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-02-13', 'price': 594.0, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-02-14', 'price': 594.0, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-02-15', 'price': 594.0, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-02-16', 'price': 594.0, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-02-17', 'price': 597.9, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-02-18', 'price': 597.9, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-02-19', 'price': 597.9, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-02-20', 'price': 597.9, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-02-21', 'price': 597.9, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-02-22', 'price': 597.9, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-02-23', 'price': 597.9, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-02-24', 'price': 597.9, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-02-25', 'price': 597.9, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-02-26', 'price': 597.9, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-02-27', 'price': 597.9, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-02-28', 'price': 597.9, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-03-01', 'price': 597.9, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-03-02', 'price': 597.9, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-03-03', 'price': 597.9, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-03-04', 'price': 598.5, 'merchantId': 23254}, {'prodId': 13993244, 'date': '2026-03-05', 'price': 599.0, 'merchantId': 22902}, {'prodId': 13993244, 'date': '2026-03-06', 'price': 599.0, 'merchantId': 22902}, {'prodId': 13993244, 'date': '2026-03-07', 'price': 599.0, 'merchantId': 22902}, {'prodId': 13993244, 'date': '2026-03-08', 'price': 599.0, 'merchantId': 22902}, {'prodId': 13993244, 'date': '2026-03-09', 'price': 598.0, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-03-10', 'price': 597.9, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-03-11', 'price': 597.0, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-03-12', 'price': 596.0, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-03-13', 'price': 595.9, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-03-14', 'price': 595.8, 'merchantId': 22902}, {'prodId': 13993244, 'date': '2026-03-15', 'price': 595.8, 'merchantId': 22902}, {'prodId': 13993244, 'date': '2026-03-16', 'price': 595.0, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-03-17', 'price': 594.0, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-03-18', 'price': 552.42, 'merchantId': 23326}, {'prodId': 13993244, 'date': '2026-03-19', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-03-20', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-03-21', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-03-22', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-03-23', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-03-24', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-03-25', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-03-26', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-03-27', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-03-28', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-03-29', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-03-30', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-03-31', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-04-01', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-04-02', 'price': 599.0, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-04-03', 'price': 660.99, 'merchantId': 9385}, {'prodId': 13993244, 'date': '2026-04-04', 'price': 628.99, 'merchantId': 9385}, {'prodId': 13993244, 'date': '2026-04-05', 'price': 628.99, 'merchantId': 9385}, {'prodId': 13993244, 'date': '2026-04-06', 'price': 628.99, 'merchantId': 9385}, {'prodId': 13993244, 'date': '2026-04-07', 'price': 659.9, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-04-08', 'price': 659.0, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-04-09', 'price': 649.0, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-04-10', 'price': 660.0, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-04-11', 'price': 646.21, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-04-12', 'price': 646.21, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-04-13', 'price': 646.21, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-04-14', 'price': 585.69, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-04-15', 'price': 585.69, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-04-16', 'price': 585.59, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-04-17', 'price': 585.59, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-04-18', 'price': 598.0, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-04-19', 'price': 598.0, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-04-20', 'price': 597.0, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-04-21', 'price': 597.0, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-04-22', 'price': 596.9, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-04-23', 'price': 596.9, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-04-24', 'price': 596.0, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-04-25', 'price': 596.0, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-04-26', 'price': 596.0, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-04-27', 'price': 595.9, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-04-28', 'price': 595.9, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-04-29', 'price': 598.9, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-04-30', 'price': 597.9, 'merchantId': 34}, {'prodId': 13993244, 'date': '2026-05-01', 'price': 585.69, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-05-02', 'price': 585.69, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-05-03', 'price': 585.69, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-05-04', 'price': 585.69, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-05-05', 'price': 592.35, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-05-06', 'price': 590.85, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-05-07', 'price': 590.85, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-05-08', 'price': 592.35, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-05-09', 'price': 592.35, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-05-10', 'price': 592.35, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-05-11', 'price': 590.36, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-05-12', 'price': 583.73, 'merchantId': 23326}, {'prodId': 13993244, 'date': '2026-05-13', 'price': 590.36, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-05-14', 'price': 590.36, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-05-15', 'price': 590.36, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-05-16', 'price': 590.36, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-05-17', 'price': 590.36, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-05-18', 'price': 583.44, 'merchantId': 23326}, {'prodId': 13993244, 'date': '2026-05-19', 'price': 582.75, 'merchantId': 23326}, {'prodId': 13993244, 'date': '2026-05-20', 'price': 582.75, 'merchantId': 23326}, {'prodId': 13993244, 'date': '2026-05-21', 'price': 539.1, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-05-22', 'price': 539.1, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-05-23', 'price': 539.1, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-05-24', 'price': 586.41, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-05-25', 'price': 539.1, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-05-26', 'price': 539.1, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-05-27', 'price': 539.1, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-05-28', 'price': 539.1, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-05-29', 'price': 539.1, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-05-30', 'price': 539.1, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-05-31', 'price': 584.34, 'merchantId': 23326}, {'prodId': 13993244, 'date': '2026-06-01', 'price': 576.89, 'merchantId': 23326}, {'prodId': 13993244, 'date': '2026-06-02', 'price': 576.89, 'merchantId': 23326}, {'prodId': 13993244, 'date': '2026-06-03', 'price': 557.12, 'merchantId': 22905}, {'prodId': 13993244, 'date': '2026-06-04', 'price': 564.53, 'merchantId': 23326}, {'prodId': 13993244, 'date': '2026-06-05', 'price': 564.53, 'merchantId': 23326}, {'prodId': 13993244, 'date': '2026-06-06', 'price': 563.78, 'merchantId': 23326}, {'prodId': 13993244, 'date': '2026-06-07', 'price': 563.78, 'merchantId': 23326}, {'prodId': 13993244, 'date': '2026-06-08', 'price': 563.78, 'merchantId': 23326}, {'prodId': 13993244, 'date': '2026-06-09', 'price': 576.68, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-06-10', 'price': 576.68, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-06-11', 'price': 575.9, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-06-12', 'price': 543.19, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-06-13', 'price': 543.19, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-06-14', 'price': 552.31, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-06-15', 'price': 552.31, 'merchantId': 245}, {'prodId': 13993244, 'date': '2026-06-16', 'price': 569.28, 'merchantId': 16108}, {'prodId': 13993244, 'date': '2026-06-17', 'price': 581.03, 'merchantId': 9385}, {'prodId': 13993244, 'date': '2026-06-18', 'price': 599.4, 'merchantId': 23254}, {'prodId': 13993244, 'date': '2026-06-19', 'price': 631.0, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-06-20', 'price': 631.0, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-06-21', 'price': 631.0, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-06-22', 'price': 631.0, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-06-23', 'price': 589.9, 'merchantId': 23326}, {'prodId': 13993244, 'date': '2026-06-24', 'price': 589.9, 'merchantId': 23326}, {'prodId': 13993244, 'date': '2026-06-25', 'price': 631.0, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-06-26', 'price': 631.0, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-06-27', 'price': 631.0, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-06-28', 'price': 631.0, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-06-29', 'price': 631.0, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-06-30', 'price': 631.0, 'merchantId': 21627}, {'prodId': 13993244, 'date': '2026-07-01', 'price': 622.64, 'merchantId': 23326}, {'prodId': 13993244, 'date': '2026-07-02', 'price': 622.64, 'merchantId': 23326}, {'prodId': 13993244, 'date': '2026-07-03', 'price': 594.15, 'merchantId': 23276}, {'prodId': 13993244, 'date': '2026-07-04', 'price': 594.15, 'merchantId': 23276}, {'prodId': 13993244, 'date': '2026-07-05', 'price': 594.15, 'merchantId': 23276}, {'prodId': 13993244, 'date': '2026-07-06', 'price': 594.15, 'merchantId': 23276}, {'prodId': 13993244, 'date': '2026-07-07', 'price': 594.15, 'merchantId': 23276}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 12534144, 'date': '2025-07-07', 'price': 4016.62, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-07-08', 'price': 4016.62, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-07-09', 'price': 4299.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-07-10', 'price': 4299.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-07-11', 'price': 4299.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-07-12', 'price': 4299.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-07-13', 'price': 4299.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-07-14', 'price': 4299.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-07-15', 'price': 4162.0, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-07-16', 'price': 4162.0, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-07-17', 'price': 4203.47, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-07-18', 'price': 4203.48, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-07-19', 'price': 4203.52, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-07-20', 'price': 4203.52, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-07-21', 'price': 4203.52, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-07-22', 'price': 4203.52, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-07-23', 'price': 4258.98, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-07-24', 'price': 4258.98, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-07-25', 'price': 4258.98, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-07-26', 'price': 4258.98, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-07-27', 'price': 3974.98, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-07-28', 'price': 3974.98, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-07-29', 'price': 4258.0, 'merchantId': 34}, {'prodId': 12534144, 'date': '2025-07-30', 'price': 3974.98, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-07-31', 'price': 3974.98, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-08-01', 'price': 3974.98, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-08-02', 'price': 4259.0, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-08-03', 'price': 4195.77, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-08-04', 'price': 4195.76, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-08-05', 'price': 4195.83, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-08-06', 'price': 4060.16, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-08-07', 'price': 4258.92, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-08-08', 'price': 4258.92, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-08-09', 'price': 4258.92, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-08-10', 'price': 4195.71, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-08-11', 'price': 4071.31, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-08-12', 'price': 4258.93, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-08-13', 'price': 4258.98, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-08-14', 'price': 4259.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-08-15', 'price': 4259.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-08-16', 'price': 4259.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-08-17', 'price': 4259.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-08-18', 'price': 4259.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-08-19', 'price': 4259.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-08-20', 'price': 4099.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-08-21', 'price': 4049.01, 'merchantId': 4}, {'prodId': 12534144, 'date': '2025-08-22', 'price': 4049.01, 'merchantId': 4}, {'prodId': 12534144, 'date': '2025-08-23', 'price': 4049.01, 'merchantId': 4}, {'prodId': 12534144, 'date': '2025-08-24', 'price': 4049.01, 'merchantId': 4}, {'prodId': 12534144, 'date': '2025-08-25', 'price': 4049.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-08-26', 'price': 4047.3, 'merchantId': 4}, {'prodId': 12534144, 'date': '2025-08-27', 'price': 4047.3, 'merchantId': 4}, {'prodId': 12534144, 'date': '2025-08-28', 'price': 4099.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-08-29', 'price': 4099.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-08-30', 'price': 4099.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-08-31', 'price': 4099.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-09-01', 'price': 4099.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-09-02', 'price': 4099.0, 'merchantId': 22902}, {'prodId': 12534144, 'date': '2025-09-03', 'price': 4199.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-09-04', 'price': 4098.98, 'merchantId': 22902}, {'prodId': 12534144, 'date': '2025-09-05', 'price': 4098.51, 'merchantId': 4}, {'prodId': 12534144, 'date': '2025-09-06', 'price': 4098.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-09-07', 'price': 4098.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-09-08', 'price': 4098.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-09-09', 'price': 3978.0, 'merchantId': 16108}, {'prodId': 12534144, 'date': '2025-09-10', 'price': 3978.0, 'merchantId': 16108}, {'prodId': 12534144, 'date': '2025-09-11', 'price': 3978.0, 'merchantId': 16108}, {'prodId': 12534144, 'date': '2025-09-12', 'price': 4012.63, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-09-13', 'price': 4012.63, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-09-14', 'price': 4012.63, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-09-15', 'price': 4012.63, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-09-16', 'price': 4012.63, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-09-17', 'price': 4012.63, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-09-18', 'price': 3920.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2025-09-19', 'price': 3920.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2025-09-20', 'price': 3920.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2025-09-21', 'price': 3920.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2025-09-22', 'price': 3920.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2025-09-23', 'price': 3998.13, 'merchantId': 34}, {'prodId': 12534144, 'date': '2025-09-24', 'price': 3999.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-09-25', 'price': 3999.0, 'merchantId': 34}, {'prodId': 12534144, 'date': '2025-09-26', 'price': 3999.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-09-27', 'price': 3999.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-09-28', 'price': 3999.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-09-29', 'price': 3999.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-09-30', 'price': 3999.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-10-01', 'price': 3999.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-10-02', 'price': 3999.0, 'merchantId': 34}, {'prodId': 12534144, 'date': '2025-10-03', 'price': 3999.0, 'merchantId': 34}, {'prodId': 12534144, 'date': '2025-10-04', 'price': 3999.0, 'merchantId': 34}, {'prodId': 12534144, 'date': '2025-10-05', 'price': 3999.0, 'merchantId': 34}, {'prodId': 12534144, 'date': '2025-10-06', 'price': 3999.0, 'merchantId': 34}, {'prodId': 12534144, 'date': '2025-10-07', 'price': 3999.0, 'merchantId': 34}, {'prodId': 12534144, 'date': '2025-10-08', 'price': 3999.0, 'merchantId': 34}, {'prodId': 12534144, 'date': '2025-10-09', 'price': 3998.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2025-10-10', 'price': 3998.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2025-10-11', 'price': 3998.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2025-10-12', 'price': 3920.01, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-10-13', 'price': 3998.0, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-10-14', 'price': 3998.0, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-10-15', 'price': 3997.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2025-10-16', 'price': 3996.0, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-10-17', 'price': 3996.0, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-10-18', 'price': 3996.0, 'merchantId': 1582}, {'prodId': 12534144, 'date': '2025-10-19', 'price': 3996.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2025-10-20', 'price': 3996.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2025-10-21', 'price': 3996.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2025-10-22', 'price': 3995.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2025-10-23', 'price': 3995.0, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-10-24', 'price': 3998.0, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2025-10-25', 'price': 3999.0, 'merchantId': 34}, {'prodId': 12534144, 'date': '2025-10-26', 'price': 3999.0, 'merchantId': 34}, {'prodId': 12534144, 'date': '2025-10-27', 'price': 3999.0, 'merchantId': 34}, {'prodId': 12534144, 'date': '2025-10-28', 'price': 3998.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-10-29', 'price': 3652.0, 'merchantId': 2}, {'prodId': 12534144, 'date': '2025-10-30', 'price': 4098.99, 'merchantId': 1582}, {'prodId': 12534144, 'date': '2025-10-31', 'price': 4098.99, 'merchantId': 1582}, {'prodId': 12534144, 'date': '2025-11-01', 'price': 3998.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-11-02', 'price': 4098.99, 'merchantId': 1582}, {'prodId': 12534144, 'date': '2025-11-03', 'price': 4148.0, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2025-11-04', 'price': 4148.0, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2025-11-05', 'price': 4148.0, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2025-11-06', 'price': 4148.0, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2025-11-07', 'price': 3998.0, 'merchantId': 5}, {'prodId': 12534144, 'date': '2025-11-08', 'price': 4148.0, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2025-11-09', 'price': 4148.0, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2025-11-10', 'price': 3848.39, 'merchantId': 16108}, {'prodId': 12534144, 'date': '2025-11-11', 'price': 4058.0, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2025-11-12', 'price': 4058.0, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2025-11-13', 'price': 4139.0, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2025-11-14', 'price': 4139.0, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2025-11-15', 'price': 3871.12, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-11-16', 'price': 3871.12, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-11-17', 'price': 3871.12, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-11-18', 'price': 4203.46, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-11-19', 'price': 4229.0, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-11-20', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-11-21', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-11-22', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-11-23', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-11-24', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-11-25', 'price': 3833.1, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-11-26', 'price': 3833.08, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-11-27', 'price': 3833.08, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-11-28', 'price': 3832.27, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-11-29', 'price': 3869.04, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-11-30', 'price': 3832.27, 'merchantId': 1582}, {'prodId': 12534144, 'date': '2025-12-01', 'price': 3869.04, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-12-02', 'price': 3980.09, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2025-12-03', 'price': 4179.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2025-12-04', 'price': 4179.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2025-12-05', 'price': 4178.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2025-12-06', 'price': 4178.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2025-12-07', 'price': 4178.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2025-12-08', 'price': 4177.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2025-12-09', 'price': 4163.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2025-12-10', 'price': 4162.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2025-12-11', 'price': 4162.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2025-12-12', 'price': 4138.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2025-12-13', 'price': 4138.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2025-12-14', 'price': 4138.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2025-12-15', 'price': 4138.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2025-12-16', 'price': 4082.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2025-12-17', 'price': 3997.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2025-12-18', 'price': 3997.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2025-12-19', 'price': 3997.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2025-12-20', 'price': 3997.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2025-12-21', 'price': 3997.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2025-12-22', 'price': 3997.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2025-12-23', 'price': 3997.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2025-12-24', 'price': 3997.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2025-12-25', 'price': 3997.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2025-12-26', 'price': 3997.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2025-12-27', 'price': 3997.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2025-12-28', 'price': 3997.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2025-12-29', 'price': 3997.0, 'merchantId': 34}, {'prodId': 12534144, 'date': '2025-12-30', 'price': 3997.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2025-12-31', 'price': 3997.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-01-01', 'price': 3997.0, 'merchantId': 34}, {'prodId': 12534144, 'date': '2026-01-02', 'price': 4199.0, 'merchantId': 22902}, {'prodId': 12534144, 'date': '2026-01-03', 'price': 3997.0, 'merchantId': 34}, {'prodId': 12534144, 'date': '2026-01-04', 'price': 3997.0, 'merchantId': 34}, {'prodId': 12534144, 'date': '2026-01-05', 'price': 3997.0, 'merchantId': 34}, {'prodId': 12534144, 'date': '2026-01-06', 'price': 3997.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-01-07', 'price': 3997.0, 'merchantId': 34}, {'prodId': 12534144, 'date': '2026-01-08', 'price': 3997.0, 'merchantId': 34}, {'prodId': 12534144, 'date': '2026-01-09', 'price': 3996.0, 'merchantId': 22902}, {'prodId': 12534144, 'date': '2026-01-10', 'price': 3996.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-01-11', 'price': 3996.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-01-12', 'price': 3996.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-01-13', 'price': 3996.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-01-14', 'price': 3996.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-01-15', 'price': 4138.0, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2026-01-16', 'price': 4138.0, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2026-01-17', 'price': 4138.0, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2026-01-18', 'price': 4138.0, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2026-01-19', 'price': 4084.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-01-20', 'price': 4084.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-01-21', 'price': 4084.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-01-22', 'price': 4119.0, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-01-23', 'price': 4084.0, 'merchantId': 34}, {'prodId': 12534144, 'date': '2026-01-24', 'price': 4084.0, 'merchantId': 34}, {'prodId': 12534144, 'date': '2026-01-25', 'price': 4084.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-01-26', 'price': 3899.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-01-27', 'price': 3898.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-01-28', 'price': 3898.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-01-29', 'price': 3898.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-01-30', 'price': 3898.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-01-31', 'price': 3898.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-02-01', 'price': 3898.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-02-02', 'price': 3898.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-02-03', 'price': 3994.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-02-04', 'price': 3994.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-02-05', 'price': 3413.83, 'merchantId': 16108}, {'prodId': 12534144, 'date': '2026-02-06', 'price': 3413.83, 'merchantId': 16108}, {'prodId': 12534144, 'date': '2026-02-07', 'price': 3413.83, 'merchantId': 16108}, {'prodId': 12534144, 'date': '2026-02-08', 'price': 4098.0, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2026-02-09', 'price': 4097.9, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-02-10', 'price': 4097.79, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-02-11', 'price': 4097.79, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-02-12', 'price': 4097.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-02-13', 'price': 4053.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-02-14', 'price': 4053.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-02-15', 'price': 4053.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-02-16', 'price': 4053.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-02-17', 'price': 4053.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-02-18', 'price': 4049.0, 'merchantId': 22902}, {'prodId': 12534144, 'date': '2026-02-19', 'price': 4048.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-02-20', 'price': 4047.9, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-02-21', 'price': 4047.9, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-02-22', 'price': 4047.9, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-02-23', 'price': 4047.9, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-02-24', 'price': 3994.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-02-25', 'price': 3993.9, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-02-26', 'price': 3993.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-02-27', 'price': 3593.7, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-02-28', 'price': 3593.7, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-03-01', 'price': 3993.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-03-02', 'price': 3993.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-03-03', 'price': 3992.9, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-03-04', 'price': 3992.9, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-03-05', 'price': 3992.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-03-06', 'price': 3991.9, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-03-07', 'price': 3991.9, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-03-08', 'price': 3991.9, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-03-09', 'price': 3849.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-03-10', 'price': 3848.9, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-03-11', 'price': 3849.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-03-12', 'price': 3988.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-03-13', 'price': 3979.9, 'merchantId': 20612}, {'prodId': 12534144, 'date': '2026-03-14', 'price': 3987.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-03-15', 'price': 3987.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-03-16', 'price': 3986.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-03-17', 'price': 3985.9, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-03-18', 'price': 3985.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-03-19', 'price': 3734.1, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-03-20', 'price': 3982.9, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2026-03-21', 'price': 3983.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-03-22', 'price': 3983.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-03-23', 'price': 3982.9, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-03-24', 'price': 3982.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-03-25', 'price': 3981.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-03-26', 'price': 3979.9, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-03-27', 'price': 3957.49, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-03-28', 'price': 3957.49, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-03-29', 'price': 3957.49, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-03-30', 'price': 3957.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-03-31', 'price': 3957.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-04-01', 'price': 3957.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-04-02', 'price': 3979.9, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2026-04-03', 'price': 3979.9, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2026-04-04', 'price': 3979.9, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2026-04-05', 'price': 3979.9, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2026-04-06', 'price': 3979.9, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2026-04-07', 'price': 3979.9, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2026-04-08', 'price': 3979.9, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2026-04-09', 'price': 3979.9, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2026-04-10', 'price': 3979.9, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2026-04-11', 'price': 3979.9, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2026-04-12', 'price': 3979.9, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2026-04-13', 'price': 3979.9, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2026-04-14', 'price': 4433.34, 'merchantId': 20904}, {'prodId': 12534144, 'date': '2026-04-15', 'price': 4433.34, 'merchantId': 20904}, {'prodId': 12534144, 'date': '2026-04-16', 'price': 4433.34, 'merchantId': 20904}, {'prodId': 12534144, 'date': '2026-04-17', 'price': 4433.34, 'merchantId': 20904}, {'prodId': 12534144, 'date': '2026-04-18', 'price': 4433.34, 'merchantId': 20904}, {'prodId': 12534144, 'date': '2026-04-19', 'price': 4433.34, 'merchantId': 20904}, {'prodId': 12534144, 'date': '2026-04-20', 'price': 4433.34, 'merchantId': 20904}, {'prodId': 12534144, 'date': '2026-04-21', 'price': 4433.34, 'merchantId': 20904}, {'prodId': 12534144, 'date': '2026-04-22', 'price': 4199.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-04-23', 'price': 4198.9, 'merchantId': 34}, {'prodId': 12534144, 'date': '2026-04-24', 'price': 4198.89, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-04-25', 'price': 4198.9, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-04-26', 'price': 4198.9, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-04-27', 'price': 4198.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-04-28', 'price': 4197.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-04-29', 'price': 4196.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-04-30', 'price': 4196.0, 'merchantId': 23326}, {'prodId': 12534144, 'date': '2026-05-01', 'price': 4196.0, 'merchantId': 34}, {'prodId': 12534144, 'date': '2026-05-02', 'price': 4196.0, 'merchantId': 4}, {'prodId': 12534144, 'date': '2026-05-03', 'price': 4195.99, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-05-04', 'price': 4195.99, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-05-05', 'price': 4195.99, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-05-06', 'price': 4099.0, 'merchantId': 22902}, {'prodId': 12534144, 'date': '2026-05-07', 'price': 4099.0, 'merchantId': 22902}, {'prodId': 12534144, 'date': '2026-05-08', 'price': 4099.0, 'merchantId': 22902}, {'prodId': 12534144, 'date': '2026-05-09', 'price': 4099.0, 'merchantId': 22902}, {'prodId': 12534144, 'date': '2026-05-10', 'price': 4099.0, 'merchantId': 22902}, {'prodId': 12534144, 'date': '2026-05-11', 'price': 4099.0, 'merchantId': 22902}, {'prodId': 12534144, 'date': '2026-05-12', 'price': 4110.49, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-05-13', 'price': 4110.49, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-05-14', 'price': 4110.49, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-05-15', 'price': 4110.49, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-05-16', 'price': 4110.49, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-05-17', 'price': 4299.0, 'merchantId': 22902}, {'prodId': 12534144, 'date': '2026-05-18', 'price': 4195.0, 'merchantId': 34}, {'prodId': 12534144, 'date': '2026-05-19', 'price': 4194.99, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-05-20', 'price': 4110.49, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-05-21', 'price': 4110.49, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-05-22', 'price': 4110.49, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-05-23', 'price': 4299.0, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-05-24', 'price': 4299.0, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-05-25', 'price': 4299.0, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-05-26', 'price': 4299.0, 'merchantId': 22902}, {'prodId': 12534144, 'date': '2026-05-27', 'price': 4299.0, 'merchantId': 22902}, {'prodId': 12534144, 'date': '2026-05-28', 'price': 4299.0, 'merchantId': 22902}, {'prodId': 12534144, 'date': '2026-05-29', 'price': 4299.0, 'merchantId': 22902}, {'prodId': 12534144, 'date': '2026-05-30', 'price': 4299.0, 'merchantId': 22902}, {'prodId': 12534144, 'date': '2026-05-31', 'price': 4299.0, 'merchantId': 22902}, {'prodId': 12534144, 'date': '2026-06-01', 'price': 4094.1, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-06-02', 'price': 4094.1, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-06-03', 'price': 4094.1, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-06-04', 'price': 4094.1, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-06-05', 'price': 4094.1, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-06-06', 'price': 4094.0, 'merchantId': 22902}, {'prodId': 12534144, 'date': '2026-06-07', 'price': 4094.0, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-06-08', 'price': 4094.0, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-06-09', 'price': 4094.0, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-06-10', 'price': 4094.0, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-06-11', 'price': 4094.0, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-06-12', 'price': 4094.0, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-06-13', 'price': 4196.0, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2026-06-14', 'price': 4196.0, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2026-06-15', 'price': 4196.0, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2026-06-16', 'price': 4196.0, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2026-06-17', 'price': 4196.0, 'merchantId': 21627}, {'prodId': 12534144, 'date': '2026-06-18', 'price': 3999.0, 'merchantId': 1582}, {'prodId': 12534144, 'date': '2026-06-19', 'price': 3998.84, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-06-20', 'price': 3998.84, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-06-21', 'price': 3998.84, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-06-22', 'price': 3998.84, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-06-23', 'price': 3998.86, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-06-24', 'price': 3998.86, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-06-25', 'price': 3998.84, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-06-26', 'price': 3998.84, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-06-27', 'price': 3998.84, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-06-28', 'price': 3998.84, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-06-29', 'price': 3998.84, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-06-30', 'price': 3998.84, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-07-01', 'price': 3788.83, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-07-02', 'price': 3941.01, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-07-03', 'price': 3941.01, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-07-04', 'price': 3851.1, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-07-05', 'price': 3851.1, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-07-06', 'price': 3851.1, 'merchantId': 9385}, {'prodId': 12534144, 'date': '2026-07-07', 'price': 3851.1, 'merchantId': 9385}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 12755140, 'date': '2025-07-07', 'price': 4949.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-07-08', 'price': 4899.0, 'merchantId': 22902}, {'prodId': 12755140, 'date': '2025-07-09', 'price': 4899.0, 'merchantId': 22902}, {'prodId': 12755140, 'date': '2025-07-10', 'price': 4899.0, 'merchantId': 22902}, {'prodId': 12755140, 'date': '2025-07-11', 'price': 4949.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2025-07-12', 'price': 4949.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-07-13', 'price': 4949.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-07-14', 'price': 4949.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-07-15', 'price': 4949.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-07-16', 'price': 4899.0, 'merchantId': 22902}, {'prodId': 12755140, 'date': '2025-07-17', 'price': 4898.99, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2025-07-18', 'price': 4899.0, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2025-07-19', 'price': 4899.07, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-07-20', 'price': 4701.55, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-07-21', 'price': 4701.55, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-07-22', 'price': 4876.05, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-07-23', 'price': 4876.05, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2025-07-24', 'price': 4876.06, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2025-07-25', 'price': 4799.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-07-26', 'price': 4799.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-07-27', 'price': 4799.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-07-28', 'price': 4799.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-07-29', 'price': 4799.0, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-07-30', 'price': 4733.51, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-07-31', 'price': 4698.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2025-08-01', 'price': 4594.58, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-08-02', 'price': 4698.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2025-08-03', 'price': 4698.0, 'merchantId': 2}, {'prodId': 12755140, 'date': '2025-08-04', 'price': 4698.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2025-08-05', 'price': 4698.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2025-08-06', 'price': 4698.0, 'merchantId': 2}, {'prodId': 12755140, 'date': '2025-08-07', 'price': 4698.0, 'merchantId': 2}, {'prodId': 12755140, 'date': '2025-08-08', 'price': 4733.52, 'merchantId': 22902}, {'prodId': 12755140, 'date': '2025-08-09', 'price': 4729.0, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-08-10', 'price': 4729.0, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-08-11', 'price': 4575.12, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-08-12', 'price': 4575.12, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-08-13', 'price': 4575.12, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-08-14', 'price': 4679.09, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2025-08-15', 'price': 4679.09, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2025-08-16', 'price': 4679.09, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2025-08-17', 'price': 4679.09, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2025-08-18', 'price': 4679.09, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2025-08-19', 'price': 4679.09, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2025-08-20', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-08-21', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-08-22', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-08-23', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-08-24', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-08-25', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-08-26', 'price': 4727.7, 'merchantId': 34}, {'prodId': 12755140, 'date': '2025-08-27', 'price': 4727.7, 'merchantId': 34}, {'prodId': 12755140, 'date': '2025-08-28', 'price': 4599.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-08-29', 'price': 4599.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-08-30', 'price': 4599.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-08-31', 'price': 4599.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-09-01', 'price': 4599.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-09-02', 'price': 4499.9, 'merchantId': 22905}, {'prodId': 12755140, 'date': '2025-09-03', 'price': 4499.9, 'merchantId': 22905}, {'prodId': 12755140, 'date': '2025-09-04', 'price': 4599.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-09-05', 'price': 4399.9, 'merchantId': 22905}, {'prodId': 12755140, 'date': '2025-09-06', 'price': 4399.9, 'merchantId': 22905}, {'prodId': 12755140, 'date': '2025-09-07', 'price': 4399.9, 'merchantId': 22905}, {'prodId': 12755140, 'date': '2025-09-08', 'price': 4399.9, 'merchantId': 22905}, {'prodId': 12755140, 'date': '2025-09-09', 'price': 4447.91, 'merchantId': 22905}, {'prodId': 12755140, 'date': '2025-09-10', 'price': 4600.08, 'merchantId': 16108}, {'prodId': 12755140, 'date': '2025-09-11', 'price': 4649.07, 'merchantId': 16108}, {'prodId': 12755140, 'date': '2025-09-12', 'price': 4650.07, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-09-13', 'price': 4650.07, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-09-14', 'price': 4650.07, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-09-15', 'price': 4650.07, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-09-16', 'price': 4650.07, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-09-17', 'price': 4650.07, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-09-18', 'price': 4404.31, 'merchantId': 34}, {'prodId': 12755140, 'date': '2025-09-19', 'price': 4199.26, 'merchantId': 23254}, {'prodId': 12755140, 'date': '2025-09-20', 'price': 4299.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-09-21', 'price': 4299.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-09-22', 'price': 4299.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-09-23', 'price': 4199.26, 'merchantId': 23254}, {'prodId': 12755140, 'date': '2025-09-24', 'price': 4298.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-09-25', 'price': 4398.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-09-26', 'price': 4399.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-09-27', 'price': 4399.0, 'merchantId': 21}, {'prodId': 12755140, 'date': '2025-09-28', 'price': 4599.0, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-09-29', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-09-30', 'price': 4399.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-10-01', 'price': 4399.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-10-02', 'price': 4598.96, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-10-03', 'price': 4598.96, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-10-04', 'price': 4598.96, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-10-05', 'price': 4549.0, 'merchantId': 21}, {'prodId': 12755140, 'date': '2025-10-06', 'price': 4499.0, 'merchantId': 21}, {'prodId': 12755140, 'date': '2025-10-07', 'price': 4598.96, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-10-08', 'price': 4404.34, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2025-10-09', 'price': 4404.34, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2025-10-10', 'price': 4499.99, 'merchantId': 21}, {'prodId': 12755140, 'date': '2025-10-11', 'price': 4499.99, 'merchantId': 21}, {'prodId': 12755140, 'date': '2025-10-12', 'price': 4597.99, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2025-10-13', 'price': 4499.99, 'merchantId': 21}, {'prodId': 12755140, 'date': '2025-10-14', 'price': 4499.99, 'merchantId': 21}, {'prodId': 12755140, 'date': '2025-10-15', 'price': 4598.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2025-10-16', 'price': 4598.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2025-10-17', 'price': 4598.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2025-10-18', 'price': 4598.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2025-10-19', 'price': 4598.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2025-10-20', 'price': 4598.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2025-10-21', 'price': 4598.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2025-10-22', 'price': 4598.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2025-10-23', 'price': 4598.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2025-10-24', 'price': 4598.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2025-10-25', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-10-26', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-10-27', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-10-28', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-10-29', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-10-30', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-10-31', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-11-01', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-11-02', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-11-03', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-11-04', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-11-05', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-11-06', 'price': 4705.04, 'merchantId': 245}, {'prodId': 12755140, 'date': '2025-11-07', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-11-08', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-11-09', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-11-10', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-11-11', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-11-12', 'price': 4364.1, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2025-11-13', 'price': 4364.1, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2025-11-14', 'price': 4359.9, 'merchantId': 21}, {'prodId': 12755140, 'date': '2025-11-15', 'price': 4359.9, 'merchantId': 21}, {'prodId': 12755140, 'date': '2025-11-16', 'price': 4359.9, 'merchantId': 21}, {'prodId': 12755140, 'date': '2025-11-17', 'price': 4359.9, 'merchantId': 21}, {'prodId': 12755140, 'date': '2025-11-18', 'price': 4359.89, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2025-11-19', 'price': 4359.89, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-11-20', 'price': 4359.89, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-11-21', 'price': 4359.89, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-11-22', 'price': 4359.89, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-11-23', 'price': 4359.89, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-11-24', 'price': 4359.89, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-11-25', 'price': 4359.89, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-11-26', 'price': 4359.89, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-11-27', 'price': 4364.1, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2025-11-28', 'price': 4317.3, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2025-11-29', 'price': 4364.1, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2025-11-30', 'price': 4514.33, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2025-12-01', 'price': 4499.1, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2025-12-02', 'price': 4499.1, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2025-12-03', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-12-04', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-12-05', 'price': 4709.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-12-06', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-12-07', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-12-08', 'price': 4709.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-12-09', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-12-10', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-12-11', 'price': 4709.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-12-12', 'price': 4508.61, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-12-13', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-12-14', 'price': 4728.99, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2025-12-15', 'price': 4709.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-12-16', 'price': 4709.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-12-17', 'price': 4709.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-12-18', 'price': 4709.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-12-19', 'price': 4709.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-12-20', 'price': 4709.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-12-21', 'price': 4709.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-12-22', 'price': 4709.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-12-23', 'price': 4709.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-12-24', 'price': 4709.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-12-25', 'price': 4709.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-12-26', 'price': 4709.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-12-27', 'price': 4709.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-12-28', 'price': 4895.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2025-12-29', 'price': 4709.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-12-30', 'price': 4709.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2025-12-31', 'price': 4679.1, 'merchantId': 20612}, {'prodId': 12755140, 'date': '2026-01-01', 'price': 4679.1, 'merchantId': 20612}, {'prodId': 12755140, 'date': '2026-01-02', 'price': 4679.1, 'merchantId': 20612}, {'prodId': 12755140, 'date': '2026-01-03', 'price': 4679.1, 'merchantId': 20612}, {'prodId': 12755140, 'date': '2026-01-04', 'price': 4709.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-01-05', 'price': 4679.1, 'merchantId': 20612}, {'prodId': 12755140, 'date': '2026-01-06', 'price': 4679.1, 'merchantId': 20612}, {'prodId': 12755140, 'date': '2026-01-07', 'price': 4698.0, 'merchantId': 21}, {'prodId': 12755140, 'date': '2026-01-08', 'price': 4698.0, 'merchantId': 21}, {'prodId': 12755140, 'date': '2026-01-09', 'price': 4549.0, 'merchantId': 22902}, {'prodId': 12755140, 'date': '2026-01-10', 'price': 4549.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-01-11', 'price': 4549.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-01-12', 'price': 4548.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-01-13', 'price': 4548.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-01-14', 'price': 4548.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2026-01-15', 'price': 4548.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2026-01-16', 'price': 4548.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2026-01-17', 'price': 4548.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2026-01-18', 'price': 4548.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2026-01-19', 'price': 4544.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-01-20', 'price': 4539.9, 'merchantId': 21}, {'prodId': 12755140, 'date': '2026-01-21', 'price': 4539.9, 'merchantId': 21}, {'prodId': 12755140, 'date': '2026-01-22', 'price': 4539.9, 'merchantId': 21}, {'prodId': 12755140, 'date': '2026-01-23', 'price': 4499.9, 'merchantId': 21}, {'prodId': 12755140, 'date': '2026-01-24', 'price': 4499.9, 'merchantId': 21}, {'prodId': 12755140, 'date': '2026-01-25', 'price': 4499.9, 'merchantId': 21}, {'prodId': 12755140, 'date': '2026-01-26', 'price': 4499.9, 'merchantId': 21}, {'prodId': 12755140, 'date': '2026-01-27', 'price': 4499.9, 'merchantId': 21}, {'prodId': 12755140, 'date': '2026-01-28', 'price': 4499.9, 'merchantId': 21}, {'prodId': 12755140, 'date': '2026-01-29', 'price': 4499.9, 'merchantId': 21}, {'prodId': 12755140, 'date': '2026-01-30', 'price': 4548.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2026-01-31', 'price': 4548.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2026-02-01', 'price': 4498.8, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-02-02', 'price': 4498.8, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-02-03', 'price': 4498.8, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-02-04', 'price': 4498.8, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-02-05', 'price': 4498.8, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-02-06', 'price': 4498.8, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-02-07', 'price': 4498.8, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-02-08', 'price': 4498.8, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-02-09', 'price': 4498.8, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-02-10', 'price': 4498.8, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-02-11', 'price': 4498.8, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-02-12', 'price': 4498.8, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-02-13', 'price': 4499.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-02-14', 'price': 4499.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-02-15', 'price': 4499.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-02-16', 'price': 4499.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-02-17', 'price': 4499.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-02-18', 'price': 4498.9, 'merchantId': 21}, {'prodId': 12755140, 'date': '2026-02-19', 'price': 4498.9, 'merchantId': 21}, {'prodId': 12755140, 'date': '2026-02-20', 'price': 4459.9, 'merchantId': 21}, {'prodId': 12755140, 'date': '2026-02-21', 'price': 4459.9, 'merchantId': 21}, {'prodId': 12755140, 'date': '2026-02-22', 'price': 4459.9, 'merchantId': 21}, {'prodId': 12755140, 'date': '2026-02-23', 'price': 4298.9, 'merchantId': 21}, {'prodId': 12755140, 'date': '2026-02-24', 'price': 4298.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-02-25', 'price': 4297.9, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-02-26', 'price': 4499.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-02-27', 'price': 4499.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-02-28', 'price': 4499.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-03-01', 'price': 4499.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-03-02', 'price': 4549.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-03-03', 'price': 4410.0, 'merchantId': 22902}, {'prodId': 12755140, 'date': '2026-03-04', 'price': 4547.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-03-05', 'price': 4546.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-03-06', 'price': 4506.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2026-03-07', 'price': 4506.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2026-03-08', 'price': 4506.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2026-03-09', 'price': 4410.0, 'merchantId': 22902}, {'prodId': 12755140, 'date': '2026-03-10', 'price': 4499.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-03-11', 'price': 4545.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-03-12', 'price': 4545.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-03-13', 'price': 4545.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-03-14', 'price': 4545.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-03-15', 'price': 4545.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-03-16', 'price': 4544.9, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-03-17', 'price': 4543.9, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-03-18', 'price': 4543.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-03-19', 'price': 4499.1, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-03-20', 'price': 4529.0, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2026-03-21', 'price': 4529.0, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2026-03-22', 'price': 4529.0, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2026-03-23', 'price': 4529.0, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2026-03-24', 'price': 4540.9, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-03-25', 'price': 4540.9, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-03-26', 'price': 4540.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-03-27', 'price': 4499.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-03-28', 'price': 4499.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-03-29', 'price': 4499.0, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-03-30', 'price': 4498.9, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-03-31', 'price': 4498.9, 'merchantId': 34}, {'prodId': 12755140, 'date': '2026-04-01', 'price': 4498.9, 'merchantId': 2}, {'prodId': 12755140, 'date': '2026-04-02', 'price': 4540.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2026-04-03', 'price': 4540.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2026-04-04', 'price': 4540.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2026-04-05', 'price': 4540.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2026-04-06', 'price': 4540.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2026-04-07', 'price': 4540.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2026-04-08', 'price': 4540.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2026-04-09', 'price': 4540.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2026-04-10', 'price': 4540.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2026-04-11', 'price': 4540.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2026-04-12', 'price': 4540.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2026-04-13', 'price': 4540.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2026-04-14', 'price': 4540.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2026-04-15', 'price': 4540.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2026-04-16', 'price': 4540.0, 'merchantId': 21627}, {'prodId': 12755140, 'date': '2026-04-17', 'price': 4983.73, 'merchantId': 245}, {'prodId': 12755140, 'date': '2026-04-18', 'price': 5042.97, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2026-04-19', 'price': 5042.97, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-04-20', 'price': 5042.97, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2026-04-21', 'price': 5042.97, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2026-04-22', 'price': 5042.97, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2026-04-23', 'price': 5042.97, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-04-24', 'price': 5042.97, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-04-25', 'price': 5079.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-04-26', 'price': 5079.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-04-27', 'price': 5066.66, 'merchantId': 20904}, {'prodId': 12755140, 'date': '2026-04-28', 'price': 5066.66, 'merchantId': 20904}, {'prodId': 12755140, 'date': '2026-04-29', 'price': 5066.66, 'merchantId': 20904}, {'prodId': 12755140, 'date': '2026-04-30', 'price': 4599.0, 'merchantId': 20612}, {'prodId': 12755140, 'date': '2026-05-01', 'price': 4599.0, 'merchantId': 20612}, {'prodId': 12755140, 'date': '2026-05-02', 'price': 4599.0, 'merchantId': 20609}, {'prodId': 12755140, 'date': '2026-05-03', 'price': 4599.0, 'merchantId': 20609}, {'prodId': 12755140, 'date': '2026-05-04', 'price': 4599.0, 'merchantId': 20609}, {'prodId': 12755140, 'date': '2026-05-05', 'price': 4599.0, 'merchantId': 20609}, {'prodId': 12755140, 'date': '2026-05-06', 'price': 4599.0, 'merchantId': 20609}, {'prodId': 12755140, 'date': '2026-05-07', 'price': 4599.0, 'merchantId': 20612}, {'prodId': 12755140, 'date': '2026-05-08', 'price': 4898.7, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-05-09', 'price': 4898.7, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2026-05-10', 'price': 4845.15, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-05-11', 'price': 4899.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-05-12', 'price': 4845.15, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2026-05-13', 'price': 4845.15, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2026-05-14', 'price': 4845.15, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2026-05-15', 'price': 4845.15, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2026-05-16', 'price': 4845.15, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2026-05-17', 'price': 4845.15, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2026-05-18', 'price': 4845.15, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2026-05-19', 'price': 4845.15, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2026-05-20', 'price': 4899.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-05-21', 'price': 4845.15, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2026-05-22', 'price': 4845.15, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-05-23', 'price': 4845.15, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2026-05-24', 'price': 4899.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-05-25', 'price': 4899.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-05-26', 'price': 4899.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-05-27', 'price': 4899.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-05-28', 'price': 4899.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-05-29', 'price': 4735.8, 'merchantId': 22905}, {'prodId': 12755140, 'date': '2026-05-30', 'price': 4735.8, 'merchantId': 22905}, {'prodId': 12755140, 'date': '2026-05-31', 'price': 4735.8, 'merchantId': 22905}, {'prodId': 12755140, 'date': '2026-06-01', 'price': 4549.9, 'merchantId': 20609}, {'prodId': 12755140, 'date': '2026-06-02', 'price': 4549.9, 'merchantId': 20609}, {'prodId': 12755140, 'date': '2026-06-03', 'price': 4899.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-06-04', 'price': 4589.1, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-06-05', 'price': 4579.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-06-06', 'price': 4579.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-06-07', 'price': 4579.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-06-08', 'price': 4569.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-06-09', 'price': 4569.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-06-10', 'price': 4399.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-06-11', 'price': 4399.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-06-12', 'price': 4569.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-06-13', 'price': 4399.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-06-14', 'price': 4399.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-06-15', 'price': 4399.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-06-16', 'price': 4399.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-06-17', 'price': 4940.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-06-18', 'price': 4940.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-06-19', 'price': 4737.98, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-06-20', 'price': 4737.98, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-06-21', 'price': 4446.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-06-22', 'price': 4446.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-06-23', 'price': 4637.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-06-24', 'price': 4637.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-06-25', 'price': 4637.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-06-26', 'price': 4637.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-06-27', 'price': 4637.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-06-28', 'price': 4829.0, 'merchantId': 5}, {'prodId': 12755140, 'date': '2026-06-29', 'price': 4737.98, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-06-30', 'price': 4737.98, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-07-01', 'price': 4499.0, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-07-02', 'price': 4499.0, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-07-03', 'price': 4498.19, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-07-04', 'price': 4499.0, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2026-07-05', 'price': 4409.0, 'merchantId': 1582}, {'prodId': 12755140, 'date': '2026-07-06', 'price': 4409.0, 'merchantId': 9385}, {'prodId': 12755140, 'date': '2026-07-07', 'price': 4829.0, 'merchantId': 5}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 12547939, 'date': '2025-07-07', 'price': 5399.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-07-08', 'price': 5399.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-07-09', 'price': 5399.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-07-10', 'price': 5399.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-07-11', 'price': 5399.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-07-12', 'price': 5399.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-07-13', 'price': 5399.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-07-14', 'price': 5399.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-07-15', 'price': 5399.1, 'merchantId': 22905}, {'prodId': 12547939, 'date': '2025-07-16', 'price': 4949.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-07-17', 'price': 4949.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-07-18', 'price': 5357.06, 'merchantId': 22905}, {'prodId': 12547939, 'date': '2025-07-19', 'price': 5399.1, 'merchantId': 20609}, {'prodId': 12547939, 'date': '2025-07-20', 'price': 5399.1, 'merchantId': 20609}, {'prodId': 12547939, 'date': '2025-07-21', 'price': 5317.57, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2025-07-22', 'price': 5299.0, 'merchantId': 22905}, {'prodId': 12547939, 'date': '2025-07-23', 'price': 5298.99, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-07-24', 'price': 5299.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-07-25', 'price': 5129.1, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-07-26', 'price': 5129.1, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2025-07-27', 'price': 5039.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-07-28', 'price': 5039.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-07-29', 'price': 5129.1, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-07-30', 'price': 5129.1, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-07-31', 'price': 4999.0, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-08-01', 'price': 4844.15, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2025-08-02', 'price': 4844.15, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2025-08-03', 'price': 4844.15, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2025-08-04', 'price': 5129.1, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-08-05', 'price': 5120.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-08-06', 'price': 4844.15, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2025-08-07', 'price': 4844.15, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2025-08-08', 'price': 4844.15, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2025-08-09', 'price': 5129.1, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-08-10', 'price': 5129.1, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-08-11', 'price': 5129.1, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-08-12', 'price': 5219.13, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2025-08-13', 'price': 5219.13, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2025-08-14', 'price': 5309.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-08-15', 'price': 5309.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-08-16', 'price': 5309.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-08-17', 'price': 5309.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-08-18', 'price': 5309.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-08-19', 'price': 5129.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-08-20', 'price': 5309.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-08-21', 'price': 5399.1, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-08-22', 'price': 5309.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-08-23', 'price': 5399.1, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-08-24', 'price': 5399.1, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-08-25', 'price': 5399.1, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-08-26', 'price': 5309.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-08-27', 'price': 5309.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-08-28', 'price': 5309.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-08-29', 'price': 5309.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-08-30', 'price': 5309.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-08-31', 'price': 5309.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-09-01', 'price': 5309.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-09-02', 'price': 5309.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-09-03', 'price': 4949.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-09-04', 'price': 4949.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-09-05', 'price': 4949.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-09-06', 'price': 4949.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-09-07', 'price': 4949.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-09-08', 'price': 4949.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-09-09', 'price': 4499.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-09-10', 'price': 4499.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-09-11', 'price': 4499.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-09-12', 'price': 4499.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-09-13', 'price': 4499.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-09-14', 'price': 4499.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-09-15', 'price': 4499.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-09-16', 'price': 4749.05, 'merchantId': 2584}, {'prodId': 12547939, 'date': '2025-09-17', 'price': 4990.0, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2025-09-18', 'price': 4979.9, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-09-19', 'price': 4990.0, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2025-09-20', 'price': 4990.0, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-09-21', 'price': 4990.0, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2025-09-22', 'price': 4990.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-09-23', 'price': 4990.0, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-09-24', 'price': 4990.0, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-09-25', 'price': 4990.0, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-09-26', 'price': 4606.88, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-09-27', 'price': 4606.88, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-09-28', 'price': 4606.88, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2025-09-29', 'price': 4606.88, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2025-09-30', 'price': 4606.88, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-10-01', 'price': 4606.88, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2025-10-02', 'price': 4606.88, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2025-10-03', 'price': 4990.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-10-04', 'price': 4990.0, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2025-10-05', 'price': 4898.7, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2025-10-06', 'price': 4849.9, 'merchantId': 21}, {'prodId': 12547939, 'date': '2025-10-07', 'price': 4798.8, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2025-10-08', 'price': 4798.8, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2025-10-09', 'price': 4798.8, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2025-10-10', 'price': 4699.0, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2025-10-11', 'price': 4798.8, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2025-10-12', 'price': 4699.0, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2025-10-13', 'price': 4649.07, 'merchantId': 20609}, {'prodId': 12547939, 'date': '2025-10-14', 'price': 4649.07, 'merchantId': 20609}, {'prodId': 12547939, 'date': '2025-10-15', 'price': 4649.07, 'merchantId': 20609}, {'prodId': 12547939, 'date': '2025-10-16', 'price': 4649.07, 'merchantId': 20609}, {'prodId': 12547939, 'date': '2025-10-17', 'price': 4649.07, 'merchantId': 20609}, {'prodId': 12547939, 'date': '2025-10-18', 'price': 4649.07, 'merchantId': 20583}, {'prodId': 12547939, 'date': '2025-10-19', 'price': 4649.07, 'merchantId': 20583}, {'prodId': 12547939, 'date': '2025-10-20', 'price': 4649.07, 'merchantId': 20583}, {'prodId': 12547939, 'date': '2025-10-21', 'price': 4649.07, 'merchantId': 20583}, {'prodId': 12547939, 'date': '2025-10-22', 'price': 4649.07, 'merchantId': 20583}, {'prodId': 12547939, 'date': '2025-10-23', 'price': 4649.07, 'merchantId': 20583}, {'prodId': 12547939, 'date': '2025-10-24', 'price': 4649.07, 'merchantId': 20583}, {'prodId': 12547939, 'date': '2025-10-25', 'price': 4649.07, 'merchantId': 20583}, {'prodId': 12547939, 'date': '2025-10-26', 'price': 4649.07, 'merchantId': 20583}, {'prodId': 12547939, 'date': '2025-10-27', 'price': 4649.07, 'merchantId': 20583}, {'prodId': 12547939, 'date': '2025-10-28', 'price': 4649.07, 'merchantId': 20583}, {'prodId': 12547939, 'date': '2025-10-29', 'price': 4649.07, 'merchantId': 20583}, {'prodId': 12547939, 'date': '2025-10-30', 'price': 4499.1, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2025-10-31', 'price': 4499.1, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2025-11-01', 'price': 4649.07, 'merchantId': 20583}, {'prodId': 12547939, 'date': '2025-11-02', 'price': 4649.07, 'merchantId': 20583}, {'prodId': 12547939, 'date': '2025-11-03', 'price': 4499.1, 'merchantId': 22905}, {'prodId': 12547939, 'date': '2025-11-04', 'price': 4649.07, 'merchantId': 20583}, {'prodId': 12547939, 'date': '2025-11-05', 'price': 4649.07, 'merchantId': 20583}, {'prodId': 12547939, 'date': '2025-11-06', 'price': 4649.07, 'merchantId': 20583}, {'prodId': 12547939, 'date': '2025-11-07', 'price': 4649.07, 'merchantId': 20583}, {'prodId': 12547939, 'date': '2025-11-08', 'price': 4649.07, 'merchantId': 20583}, {'prodId': 12547939, 'date': '2025-11-09', 'price': 4649.07, 'merchantId': 20583}, {'prodId': 12547939, 'date': '2025-11-10', 'price': 4649.07, 'merchantId': 20583}, {'prodId': 12547939, 'date': '2025-11-11', 'price': 4649.07, 'merchantId': 20583}, {'prodId': 12547939, 'date': '2025-11-12', 'price': 4649.07, 'merchantId': 20583}, {'prodId': 12547939, 'date': '2025-11-13', 'price': 4649.07, 'merchantId': 20583}, {'prodId': 12547939, 'date': '2025-11-14', 'price': 4789.9, 'merchantId': 21}, {'prodId': 12547939, 'date': '2025-11-15', 'price': 4789.9, 'merchantId': 21}, {'prodId': 12547939, 'date': '2025-11-16', 'price': 4798.76, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-11-17', 'price': 4789.9, 'merchantId': 21}, {'prodId': 12547939, 'date': '2025-11-18', 'price': 4789.9, 'merchantId': 21}, {'prodId': 12547939, 'date': '2025-11-19', 'price': 4749.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-11-20', 'price': 4409.1, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-11-21', 'price': 4749.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-11-22', 'price': 4749.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-11-23', 'price': 4795.0, 'merchantId': 23326}, {'prodId': 12547939, 'date': '2025-11-24', 'price': 4499.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-11-25', 'price': 4499.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-11-26', 'price': 4498.98, 'merchantId': 4}, {'prodId': 12547939, 'date': '2025-11-27', 'price': 4498.98, 'merchantId': 23326}, {'prodId': 12547939, 'date': '2025-11-28', 'price': 4399.01, 'merchantId': 23326}, {'prodId': 12547939, 'date': '2025-11-29', 'price': 4471.03, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2025-11-30', 'price': 4471.03, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-12-01', 'price': 4471.03, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-12-02', 'price': 4498.0, 'merchantId': 23326}, {'prodId': 12547939, 'date': '2025-12-03', 'price': 4498.0, 'merchantId': 23326}, {'prodId': 12547939, 'date': '2025-12-04', 'price': 4498.0, 'merchantId': 4}, {'prodId': 12547939, 'date': '2025-12-05', 'price': 4398.05, 'merchantId': 4}, {'prodId': 12547939, 'date': '2025-12-06', 'price': 4398.05, 'merchantId': 23326}, {'prodId': 12547939, 'date': '2025-12-07', 'price': 4498.0, 'merchantId': 4}, {'prodId': 12547939, 'date': '2025-12-08', 'price': 4498.0, 'merchantId': 4}, {'prodId': 12547939, 'date': '2025-12-09', 'price': 4498.0, 'merchantId': 4}, {'prodId': 12547939, 'date': '2025-12-10', 'price': 4498.0, 'merchantId': 4}, {'prodId': 12547939, 'date': '2025-12-11', 'price': 4498.0, 'merchantId': 4}, {'prodId': 12547939, 'date': '2025-12-12', 'price': 4498.0, 'merchantId': 4}, {'prodId': 12547939, 'date': '2025-12-13', 'price': 4498.0, 'merchantId': 4}, {'prodId': 12547939, 'date': '2025-12-14', 'price': 4498.0, 'merchantId': 4}, {'prodId': 12547939, 'date': '2025-12-15', 'price': 4795.0, 'merchantId': 4}, {'prodId': 12547939, 'date': '2025-12-16', 'price': 4795.0, 'merchantId': 4}, {'prodId': 12547939, 'date': '2025-12-17', 'price': 4795.0, 'merchantId': 4}, {'prodId': 12547939, 'date': '2025-12-18', 'price': 4795.0, 'merchantId': 4}, {'prodId': 12547939, 'date': '2025-12-19', 'price': 4979.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-12-20', 'price': 4979.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-12-21', 'price': 4979.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-12-22', 'price': 4979.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-12-23', 'price': 4979.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-12-24', 'price': 4979.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-12-25', 'price': 5599.9, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-12-26', 'price': 5298.0, 'merchantId': 4}, {'prodId': 12547939, 'date': '2025-12-27', 'price': 4749.0, 'merchantId': 21627}, {'prodId': 12547939, 'date': '2025-12-28', 'price': 5599.9, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-12-29', 'price': 5599.9, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-12-30', 'price': 5869.9, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2025-12-31', 'price': 5298.0, 'merchantId': 4}, {'prodId': 12547939, 'date': '2026-01-01', 'price': 5886.67, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2026-01-02', 'price': 5298.0, 'merchantId': 4}, {'prodId': 12547939, 'date': '2026-01-03', 'price': 5669.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2026-01-04', 'price': 5298.0, 'merchantId': 4}, {'prodId': 12547939, 'date': '2026-01-05', 'price': 4798.8, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2026-01-06', 'price': 4798.8, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2026-01-07', 'price': 5059.08, 'merchantId': 20583}, {'prodId': 12547939, 'date': '2026-01-08', 'price': 4798.0, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2026-01-09', 'price': 4798.0, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2026-01-10', 'price': 4798.0, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2026-01-11', 'price': 4799.0, 'merchantId': 4}, {'prodId': 12547939, 'date': '2026-01-12', 'price': 4979.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-01-13', 'price': 4799.0, 'merchantId': 4}, {'prodId': 12547939, 'date': '2026-01-14', 'price': 4979.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-01-15', 'price': 4799.0, 'merchantId': 4}, {'prodId': 12547939, 'date': '2026-01-16', 'price': 4799.0, 'merchantId': 4}, {'prodId': 12547939, 'date': '2026-01-17', 'price': 4979.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-01-18', 'price': 4979.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-01-19', 'price': 4979.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-01-20', 'price': 4979.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-01-21', 'price': 4979.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-01-22', 'price': 4979.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-01-23', 'price': 4979.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-01-24', 'price': 4979.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-01-25', 'price': 4979.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-01-26', 'price': 4979.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-01-27', 'price': 4979.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-01-28', 'price': 4979.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-01-29', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-01-30', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-01-31', 'price': 5179.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-02-01', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-02-02', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-02-03', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-02-04', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-02-05', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-02-06', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-02-07', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-02-08', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-02-09', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-02-10', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-02-11', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-02-12', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-02-13', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-02-14', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-02-15', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-02-16', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-02-17', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-02-18', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-02-19', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-02-20', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-02-21', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-02-22', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-02-23', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-02-24', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-02-25', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-02-26', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-02-27', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-02-28', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-03-01', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-03-02', 'price': 5039.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2026-03-03', 'price': 5039.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2026-03-04', 'price': 5039.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2026-03-05', 'price': 5039.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2026-03-06', 'price': 5039.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2026-03-07', 'price': 5039.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2026-03-08', 'price': 5039.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2026-03-09', 'price': 5039.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2026-03-10', 'price': 5039.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2026-03-11', 'price': 5039.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2026-03-12', 'price': 4949.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2026-03-13', 'price': 4949.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2026-03-14', 'price': 4949.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2026-03-15', 'price': 5039.1, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-03-16', 'price': 5039.1, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-03-17', 'price': 5039.1, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-03-18', 'price': 5039.1, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-03-19', 'price': 5039.1, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-03-20', 'price': 5039.1, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-03-21', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-03-22', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-03-23', 'price': 5196.56, 'merchantId': 16108}, {'prodId': 12547939, 'date': '2026-03-24', 'price': 5069.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-03-25', 'price': 5069.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-03-26', 'price': 5069.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-03-27', 'price': 5069.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-03-28', 'price': 5069.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-03-29', 'price': 5069.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-03-30', 'price': 5069.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-03-31', 'price': 5069.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-04-01', 'price': 5069.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-04-02', 'price': 4769.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-04-03', 'price': 4769.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-04-04', 'price': 4769.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-04-05', 'price': 4769.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-04-06', 'price': 4769.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-04-07', 'price': 4769.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-04-08', 'price': 4769.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-04-09', 'price': 4769.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-04-10', 'price': 4769.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-04-11', 'price': 4769.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-04-12', 'price': 4769.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-04-13', 'price': 4769.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-04-14', 'price': 4332.0, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2026-04-15', 'price': 5056.27, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-04-16', 'price': 5056.2699999999995, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-04-17', 'price': 4332.0, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2026-04-18', 'price': 5056.27, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-04-19', 'price': 4332.0, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2026-04-20', 'price': 3924.08, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2026-04-21', 'price': 3924.08, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2026-04-22', 'price': 3949.0, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2026-04-23', 'price': 4619.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-04-24', 'price': 4033.22, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2026-04-25', 'price': 4619.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-04-26', 'price': 5056.27, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-04-27', 'price': 4619.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-04-28', 'price': 4619.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-04-29', 'price': 5056.27, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-04-30', 'price': 4619.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-05-01', 'price': 4619.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-05-02', 'price': 4049.91, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2026-05-03', 'price': 4685.47, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-05-04', 'price': 4619.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-05-05', 'price': 4619.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-05-06', 'price': 4025.37, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2026-05-07', 'price': 4619.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-05-08', 'price': 4619.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-05-09', 'price': 4619.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-05-10', 'price': 4619.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-05-11', 'price': 4619.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-05-12', 'price': 4025.37, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2026-05-13', 'price': 4025.37, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2026-05-14', 'price': 4025.37, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2026-05-15', 'price': 4025.37, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2026-05-16', 'price': 4025.37, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2026-05-17', 'price': 4619.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-05-18', 'price': 4569.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-05-19', 'price': 4569.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-05-20', 'price': 4569.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-05-21', 'price': 4569.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-05-22', 'price': 4569.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-05-23', 'price': 4569.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-05-24', 'price': 4075.78, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2026-05-25', 'price': 4075.78, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2026-05-26', 'price': 4619.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-05-27', 'price': 4619.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-05-28', 'price': 4619.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-05-29', 'price': 4335.27, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-05-30', 'price': 4335.27, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-05-31', 'price': 4619.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-06-01', 'price': 4619.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-06-02', 'price': 4332.22, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2026-06-03', 'price': 4332.22, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-06-04', 'price': 4335.27, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-06-05', 'price': 3998.89, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2026-06-06', 'price': 3998.89, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2026-06-07', 'price': 4335.27, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-06-08', 'price': 3998.89, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2026-06-09', 'price': 3998.89, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2026-06-10', 'price': 4479.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-06-11', 'price': 4335.27, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-06-12', 'price': 5129.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2026-06-13', 'price': 5129.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2026-06-14', 'price': 5129.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2026-06-15', 'price': 5129.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2026-06-16', 'price': 5129.1, 'merchantId': 22902}, {'prodId': 12547939, 'date': '2026-06-17', 'price': 4335.27, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-06-18', 'price': 4335.27, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-06-19', 'price': 4249.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-06-20', 'price': 4479.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-06-21', 'price': 4335.27, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-06-22', 'price': 4249.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-06-23', 'price': 4249.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-06-24', 'price': 4249.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-06-25', 'price': 4249.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-06-26', 'price': 2908.66, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2026-06-27', 'price': 4249.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-06-28', 'price': 4249.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-06-29', 'price': 4249.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-06-30', 'price': 4249.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-07-01', 'price': 4249.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-07-02', 'price': 4249.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-07-03', 'price': 4350.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-07-04', 'price': 4350.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-07-05', 'price': 4319.1, 'merchantId': 9385}, {'prodId': 12547939, 'date': '2026-07-06', 'price': 4249.0, 'merchantId': 1582}, {'prodId': 12547939, 'date': '2026-07-07', 'price': 4249.0, 'merchantId': 1582}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13991952, 'date': '2025-07-07', 'price': 3799.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-07-08', 'price': 3799.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-07-09', 'price': 3799.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-07-10', 'price': 3799.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-07-11', 'price': 3749.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-07-12', 'price': 3749.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-07-13', 'price': 3749.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-07-14', 'price': 3749.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-07-15', 'price': 3779.1, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2025-07-16', 'price': 3798.99, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2025-07-17', 'price': 3761.09, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2025-07-18', 'price': 3761.1, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2025-07-19', 'price': 3761.1, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2025-07-20', 'price': 3761.1, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2025-07-21', 'price': 3761.1, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2025-07-22', 'price': 3761.1, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2025-07-23', 'price': 3789.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-07-24', 'price': 3789.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-07-25', 'price': 3789.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-07-26', 'price': 3789.0, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2025-07-27', 'price': 3789.0, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2025-07-28', 'price': 3788.99, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2025-07-29', 'price': 3768.0, 'merchantId': 4}, {'prodId': 13991952, 'date': '2025-07-30', 'price': 3768.0, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2025-07-31', 'price': 3479.13, 'merchantId': 22902}, {'prodId': 13991952, 'date': '2025-08-01', 'price': 3599.1, 'merchantId': 22902}, {'prodId': 13991952, 'date': '2025-08-02', 'price': 3768.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2025-08-03', 'price': 3768.0, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2025-08-04', 'price': 3599.1, 'merchantId': 16108}, {'prodId': 13991952, 'date': '2025-08-05', 'price': 3599.1, 'merchantId': 16108}, {'prodId': 13991952, 'date': '2025-08-06', 'price': 3700.88, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2025-08-07', 'price': 3747.99, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2025-08-08', 'price': 3747.99, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2025-08-09', 'price': 3748.0, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2025-08-10', 'price': 3748.0, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2025-08-11', 'price': 3748.0, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2025-08-12', 'price': 3748.01, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2025-08-13', 'price': 3624.04, 'merchantId': 22902}, {'prodId': 13991952, 'date': '2025-08-14', 'price': 3748.99, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2025-08-15', 'price': 3748.99, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2025-08-16', 'price': 3748.99, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2025-08-17', 'price': 3748.99, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2025-08-18', 'price': 3748.99, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2025-08-19', 'price': 3599.1, 'merchantId': 22902}, {'prodId': 13991952, 'date': '2025-08-20', 'price': 3599.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-08-21', 'price': 3599.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-08-22', 'price': 3748.99, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2025-08-23', 'price': 3748.99, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2025-08-24', 'price': 3748.99, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2025-08-25', 'price': 3599.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-08-26', 'price': 3598.2, 'merchantId': 34}, {'prodId': 13991952, 'date': '2025-08-27', 'price': 3598.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-08-28', 'price': 3499.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-08-29', 'price': 3499.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-08-30', 'price': 3499.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-08-31', 'price': 3499.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-09-01', 'price': 3498.0, 'merchantId': 21}, {'prodId': 13991952, 'date': '2025-09-02', 'price': 3498.0, 'merchantId': 21}, {'prodId': 13991952, 'date': '2025-09-03', 'price': 3499.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-09-04', 'price': 3498.66, 'merchantId': 34}, {'prodId': 13991952, 'date': '2025-09-05', 'price': 3399.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-09-06', 'price': 3399.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-09-07', 'price': 3399.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-09-08', 'price': 3399.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-09-09', 'price': 3399.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-09-10', 'price': 3230.27, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-09-11', 'price': 3230.27, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-09-12', 'price': 3230.27, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-09-13', 'price': 3230.27, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-09-14', 'price': 3230.27, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-09-15', 'price': 3230.27, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-09-16', 'price': 3661.89, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2025-09-17', 'price': 3499.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-09-18', 'price': 3497.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2025-09-19', 'price': 3199.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-09-20', 'price': 3199.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-09-21', 'price': 3199.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-09-22', 'price': 3199.0, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2025-09-23', 'price': 3198.0, 'merchantId': 21}, {'prodId': 13991952, 'date': '2025-09-24', 'price': 3198.0, 'merchantId': 21}, {'prodId': 13991952, 'date': '2025-09-25', 'price': 3198.0, 'merchantId': 21}, {'prodId': 13991952, 'date': '2025-09-26', 'price': 3299.0, 'merchantId': 21}, {'prodId': 13991952, 'date': '2025-09-27', 'price': 3299.0, 'merchantId': 21}, {'prodId': 13991952, 'date': '2025-09-28', 'price': 3399.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-09-29', 'price': 3399.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-09-30', 'price': 3399.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-10-01', 'price': 3399.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2025-10-02', 'price': 3567.0, 'merchantId': 21628}, {'prodId': 13991952, 'date': '2025-10-03', 'price': 3399.0, 'merchantId': 22902}, {'prodId': 13991952, 'date': '2025-10-04', 'price': 3399.0, 'merchantId': 22902}, {'prodId': 13991952, 'date': '2025-10-05', 'price': 3399.0, 'merchantId': 22902}, {'prodId': 13991952, 'date': '2025-10-06', 'price': 3299.0, 'merchantId': 21}, {'prodId': 13991952, 'date': '2025-10-07', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-10-08', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-10-09', 'price': 3299.0, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2025-10-10', 'price': 3398.97, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2025-10-11', 'price': 3299.0, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2025-10-12', 'price': 3299.0, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2025-10-13', 'price': 3239.1, 'merchantId': 22902}, {'prodId': 13991952, 'date': '2025-10-14', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-10-15', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-10-16', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-10-17', 'price': 3398.97, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2025-10-18', 'price': 3398.97, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2025-10-19', 'price': 3398.97, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2025-10-20', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-10-21', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-10-22', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-10-23', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-10-24', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-10-25', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-10-26', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-10-27', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-10-28', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-10-29', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-10-30', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-10-31', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-11-01', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-11-02', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-11-03', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-11-04', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-11-05', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-11-06', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-11-07', 'price': 3399.0, 'merchantId': 21}, {'prodId': 13991952, 'date': '2025-11-08', 'price': 3399.0, 'merchantId': 21}, {'prodId': 13991952, 'date': '2025-11-09', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-11-10', 'price': 3399.0, 'merchantId': 21}, {'prodId': 13991952, 'date': '2025-11-11', 'price': 3399.0, 'merchantId': 21}, {'prodId': 13991952, 'date': '2025-11-12', 'price': 3399.0, 'merchantId': 21}, {'prodId': 13991952, 'date': '2025-11-13', 'price': 3399.0, 'merchantId': 21}, {'prodId': 13991952, 'date': '2025-11-14', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-11-15', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-11-16', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-11-17', 'price': 3399.0, 'merchantId': 21}, {'prodId': 13991952, 'date': '2025-11-18', 'price': 3399.0, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-11-19', 'price': 3430.98, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-11-20', 'price': 3430.98, 'merchantId': 20583}, {'prodId': 13991952, 'date': '2025-11-21', 'price': 3229.0, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2025-11-22', 'price': 3229.0, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2025-11-23', 'price': 3229.0, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2025-11-24', 'price': 3228.98, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2025-11-25', 'price': 3228.98, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2025-11-26', 'price': 3430.98, 'merchantId': 20609}, {'prodId': 13991952, 'date': '2025-11-27', 'price': 3430.98, 'merchantId': 20612}, {'prodId': 13991952, 'date': '2025-11-28', 'price': 3415.28, 'merchantId': 23326}, {'prodId': 13991952, 'date': '2025-11-29', 'price': 3430.98, 'merchantId': 20612}, {'prodId': 13991952, 'date': '2025-11-30', 'price': 3430.98, 'merchantId': 20612}, {'prodId': 13991952, 'date': '2025-12-01', 'price': 3430.98, 'merchantId': 20612}, {'prodId': 13991952, 'date': '2025-12-02', 'price': 3430.98, 'merchantId': 20612}, {'prodId': 13991952, 'date': '2025-12-03', 'price': 3430.98, 'merchantId': 20612}, {'prodId': 13991952, 'date': '2025-12-04', 'price': 3430.98, 'merchantId': 20612}, {'prodId': 13991952, 'date': '2025-12-05', 'price': 3430.98, 'merchantId': 20612}, {'prodId': 13991952, 'date': '2025-12-06', 'price': 3430.98, 'merchantId': 20612}, {'prodId': 13991952, 'date': '2025-12-07', 'price': 3430.98, 'merchantId': 20612}, {'prodId': 13991952, 'date': '2025-12-08', 'price': 3430.98, 'merchantId': 20612}, {'prodId': 13991952, 'date': '2025-12-09', 'price': 3430.98, 'merchantId': 20612}, {'prodId': 13991952, 'date': '2025-12-10', 'price': 3430.98, 'merchantId': 20612}, {'prodId': 13991952, 'date': '2025-12-11', 'price': 3430.98, 'merchantId': 20612}, {'prodId': 13991952, 'date': '2025-12-12', 'price': 3430.98, 'merchantId': 20612}, {'prodId': 13991952, 'date': '2025-12-13', 'price': 3430.98, 'merchantId': 20612}, {'prodId': 13991952, 'date': '2025-12-14', 'price': 3430.98, 'merchantId': 20612}, {'prodId': 13991952, 'date': '2025-12-15', 'price': 3430.98, 'merchantId': 20612}, {'prodId': 13991952, 'date': '2025-12-16', 'price': 3430.98, 'merchantId': 20612}, {'prodId': 13991952, 'date': '2025-12-17', 'price': 3430.98, 'merchantId': 20612}, {'prodId': 13991952, 'date': '2025-12-18', 'price': 3430.98, 'merchantId': 20612}, {'prodId': 13991952, 'date': '2025-12-19', 'price': 3569.99, 'merchantId': 21}, {'prodId': 13991952, 'date': '2025-12-20', 'price': 3569.99, 'merchantId': 21}, {'prodId': 13991952, 'date': '2025-12-21', 'price': 3650.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2025-12-22', 'price': 3650.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2025-12-23', 'price': 3650.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2025-12-24', 'price': 3699.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2025-12-25', 'price': 3699.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2025-12-26', 'price': 3699.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2025-12-27', 'price': 3699.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2025-12-28', 'price': 3699.0, 'merchantId': 245}, {'prodId': 13991952, 'date': '2025-12-29', 'price': 3699.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2025-12-30', 'price': 3699.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2025-12-31', 'price': 3699.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-01-01', 'price': 3799.0, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-01-02', 'price': 3599.0, 'merchantId': 20609}, {'prodId': 13991952, 'date': '2026-01-03', 'price': 3699.0, 'merchantId': 22902}, {'prodId': 13991952, 'date': '2026-01-04', 'price': 3699.0, 'merchantId': 2}, {'prodId': 13991952, 'date': '2026-01-05', 'price': 3599.0, 'merchantId': 20609}, {'prodId': 13991952, 'date': '2026-01-06', 'price': 3699.0, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-01-07', 'price': 3699.0, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-01-08', 'price': 3699.0, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-01-09', 'price': 3699.0, 'merchantId': 23326}, {'prodId': 13991952, 'date': '2026-01-10', 'price': 3699.0, 'merchantId': 245}, {'prodId': 13991952, 'date': '2026-01-11', 'price': 3699.0, 'merchantId': 245}, {'prodId': 13991952, 'date': '2026-01-12', 'price': 3699.0, 'merchantId': 23326}, {'prodId': 13991952, 'date': '2026-01-13', 'price': 3699.0, 'merchantId': 23326}, {'prodId': 13991952, 'date': '2026-01-14', 'price': 3699.0, 'merchantId': 23326}, {'prodId': 13991952, 'date': '2026-01-15', 'price': 3749.0, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-01-16', 'price': 3749.0, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-01-17', 'price': 3749.0, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-01-18', 'price': 3749.0, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-01-19', 'price': 3699.9, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-01-20', 'price': 3589.18, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-01-21', 'price': 3589.18, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-01-22', 'price': 3589.18, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-01-23', 'price': 3549.9, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-01-24', 'price': 3549.9, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-01-25', 'price': 3549.9, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-01-26', 'price': 3549.9, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-01-27', 'price': 3549.9, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-01-28', 'price': 3549.0, 'merchantId': 23326}, {'prodId': 13991952, 'date': '2026-01-29', 'price': 3549.0, 'merchantId': 23326}, {'prodId': 13991952, 'date': '2026-01-30', 'price': 3549.0, 'merchantId': 23326}, {'prodId': 13991952, 'date': '2026-01-31', 'price': 3549.0, 'merchantId': 23326}, {'prodId': 13991952, 'date': '2026-02-01', 'price': 3549.0, 'merchantId': 23326}, {'prodId': 13991952, 'date': '2026-02-02', 'price': 3549.0, 'merchantId': 23326}, {'prodId': 13991952, 'date': '2026-02-03', 'price': 3548.9, 'merchantId': 23326}, {'prodId': 13991952, 'date': '2026-02-04', 'price': 3548.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-02-05', 'price': 3509.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-02-06', 'price': 3509.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-02-07', 'price': 3509.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-02-08', 'price': 3509.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-02-09', 'price': 3508.9, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-02-10', 'price': 3508.79, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-02-11', 'price': 3508.79, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-02-12', 'price': 3508.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-02-13', 'price': 3507.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-02-14', 'price': 3507.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-02-15', 'price': 3507.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-02-16', 'price': 3507.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-02-17', 'price': 3507.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-02-18', 'price': 3499.9, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-02-19', 'price': 3499.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-02-20', 'price': 3449.9, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-02-21', 'price': 3449.9, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-02-22', 'price': 3449.9, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-02-23', 'price': 3449.9, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-02-24', 'price': 3449.9, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-02-25', 'price': 3449.9, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-02-26', 'price': 3498.9, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-02-27', 'price': 3498.9, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-02-28', 'price': 3498.9, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-03-01', 'price': 3498.9, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-03-02', 'price': 3498.9, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-03-03', 'price': 3498.9, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-03-04', 'price': 3498.9, 'merchantId': 2}, {'prodId': 13991952, 'date': '2026-03-05', 'price': 3498.9, 'merchantId': 23326}, {'prodId': 13991952, 'date': '2026-03-06', 'price': 3498.0, 'merchantId': 23326}, {'prodId': 13991952, 'date': '2026-03-07', 'price': 3498.0, 'merchantId': 23326}, {'prodId': 13991952, 'date': '2026-03-08', 'price': 3498.0, 'merchantId': 23326}, {'prodId': 13991952, 'date': '2026-03-09', 'price': 3497.9, 'merchantId': 23326}, {'prodId': 13991952, 'date': '2026-03-10', 'price': 3491.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-03-11', 'price': 3490.9, 'merchantId': 23326}, {'prodId': 13991952, 'date': '2026-03-12', 'price': 3490.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-03-13', 'price': 3489.9, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-03-14', 'price': 3489.9, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-03-15', 'price': 3489.9, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-03-16', 'price': 3489.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-03-17', 'price': 3449.9, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-03-18', 'price': 3449.9, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-03-19', 'price': 3449.9, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-03-20', 'price': 3449.9, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-03-21', 'price': 3449.9, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-03-22', 'price': 3449.9, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-03-23', 'price': 3449.9, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-03-24', 'price': 3449.9, 'merchantId': 21}, {'prodId': 13991952, 'date': '2026-03-25', 'price': 3598.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-03-26', 'price': 3597.49, 'merchantId': 23326}, {'prodId': 13991952, 'date': '2026-03-27', 'price': 3597.49, 'merchantId': 23326}, {'prodId': 13991952, 'date': '2026-03-28', 'price': 3597.49, 'merchantId': 23326}, {'prodId': 13991952, 'date': '2026-03-29', 'price': 3597.49, 'merchantId': 23326}, {'prodId': 13991952, 'date': '2026-03-30', 'price': 3597.0, 'merchantId': 23326}, {'prodId': 13991952, 'date': '2026-03-31', 'price': 3597.0, 'merchantId': 34}, {'prodId': 13991952, 'date': '2026-04-01', 'price': 3499.0, 'merchantId': 16108}, {'prodId': 13991952, 'date': '2026-04-02', 'price': 3329.01, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-04-03', 'price': 3499.0, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-04-04', 'price': 3499.0, 'merchantId': 22902}, {'prodId': 13991952, 'date': '2026-04-05', 'price': 3499.0, 'merchantId': 22902}, {'prodId': 13991952, 'date': '2026-04-06', 'price': 3499.0, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-04-07', 'price': 3499.0, 'merchantId': 16108}, {'prodId': 13991952, 'date': '2026-04-08', 'price': 3499.0, 'merchantId': 16108}, {'prodId': 13991952, 'date': '2026-04-09', 'price': 3499.0, 'merchantId': 16108}, {'prodId': 13991952, 'date': '2026-04-10', 'price': 3693.39, 'merchantId': 2584}, {'prodId': 13991952, 'date': '2026-04-11', 'price': 3697.49, 'merchantId': 21628}, {'prodId': 13991952, 'date': '2026-04-12', 'price': 3697.49, 'merchantId': 21628}, {'prodId': 13991952, 'date': '2026-04-13', 'price': 3697.49, 'merchantId': 21628}, {'prodId': 13991952, 'date': '2026-04-14', 'price': 3697.49, 'merchantId': 21627}, {'prodId': 13991952, 'date': '2026-04-15', 'price': 3697.49, 'merchantId': 21627}, {'prodId': 13991952, 'date': '2026-04-16', 'price': 3697.49, 'merchantId': 21627}, {'prodId': 13991952, 'date': '2026-04-17', 'price': 3697.49, 'merchantId': 21627}, {'prodId': 13991952, 'date': '2026-04-18', 'price': 3699.0, 'merchantId': 16108}, {'prodId': 13991952, 'date': '2026-04-19', 'price': 3697.49, 'merchantId': 21628}, {'prodId': 13991952, 'date': '2026-04-20', 'price': 3697.49, 'merchantId': 21627}, {'prodId': 13991952, 'date': '2026-04-21', 'price': 3699.0, 'merchantId': 16108}, {'prodId': 13991952, 'date': '2026-04-22', 'price': 3697.49, 'merchantId': 21627}, {'prodId': 13991952, 'date': '2026-04-23', 'price': 3697.49, 'merchantId': 21627}, {'prodId': 13991952, 'date': '2026-04-24', 'price': 3697.49, 'merchantId': 21627}, {'prodId': 13991952, 'date': '2026-04-25', 'price': 3699.0, 'merchantId': 16108}, {'prodId': 13991952, 'date': '2026-04-26', 'price': 3697.49, 'merchantId': 21627}, {'prodId': 13991952, 'date': '2026-04-27', 'price': 3697.49, 'merchantId': 21627}, {'prodId': 13991952, 'date': '2026-04-28', 'price': 3697.49, 'merchantId': 21627}, {'prodId': 13991952, 'date': '2026-04-29', 'price': 3697.49, 'merchantId': 21627}, {'prodId': 13991952, 'date': '2026-04-30', 'price': 3499.0, 'merchantId': 16108}, {'prodId': 13991952, 'date': '2026-05-01', 'price': 3499.0, 'merchantId': 16108}, {'prodId': 13991952, 'date': '2026-05-02', 'price': 3499.0, 'merchantId': 16108}, {'prodId': 13991952, 'date': '2026-05-03', 'price': 3499.0, 'merchantId': 16108}, {'prodId': 13991952, 'date': '2026-05-04', 'price': 3499.0, 'merchantId': 16108}, {'prodId': 13991952, 'date': '2026-05-05', 'price': 3499.0, 'merchantId': 16108}, {'prodId': 13991952, 'date': '2026-05-06', 'price': 3499.0, 'merchantId': 16108}, {'prodId': 13991952, 'date': '2026-05-07', 'price': 3499.0, 'merchantId': 16108}, {'prodId': 13991952, 'date': '2026-05-08', 'price': 3499.0, 'merchantId': 16108}, {'prodId': 13991952, 'date': '2026-05-09', 'price': 3499.0, 'merchantId': 16108}, {'prodId': 13991952, 'date': '2026-05-10', 'price': 3499.0, 'merchantId': 16108}, {'prodId': 13991952, 'date': '2026-05-11', 'price': 3460.54, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-05-12', 'price': 3460.54, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2026-05-13', 'price': 3489.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2026-05-14', 'price': 3489.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2026-05-15', 'price': 3489.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2026-05-16', 'price': 3489.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2026-05-17', 'price': 3489.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2026-05-18', 'price': 3460.54, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-05-19', 'price': 3460.54, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-05-20', 'price': 3460.54, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-05-21', 'price': 3460.54, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-05-22', 'price': 3489.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2026-05-23', 'price': 3460.54, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-05-24', 'price': 3499.0, 'merchantId': 16108}, {'prodId': 13991952, 'date': '2026-05-25', 'price': 3499.0, 'merchantId': 16108}, {'prodId': 13991952, 'date': '2026-05-26', 'price': 3693.39, 'merchantId': 2584}, {'prodId': 13991952, 'date': '2026-05-27', 'price': 3693.39, 'merchantId': 2584}, {'prodId': 13991952, 'date': '2026-05-28', 'price': 3693.39, 'merchantId': 2584}, {'prodId': 13991952, 'date': '2026-05-29', 'price': 3693.39, 'merchantId': 2584}, {'prodId': 13991952, 'date': '2026-05-30', 'price': 3693.39, 'merchantId': 2584}, {'prodId': 13991952, 'date': '2026-05-31', 'price': 3693.39, 'merchantId': 2584}, {'prodId': 13991952, 'date': '2026-06-01', 'price': 3460.54, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-06-02', 'price': 3374.1, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-06-03', 'price': 3374.1, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2026-06-04', 'price': 3374.1, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-06-05', 'price': 3374.1, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-06-06', 'price': 3374.0, 'merchantId': 16108}, {'prodId': 13991952, 'date': '2026-06-07', 'price': 3374.0, 'merchantId': 16108}, {'prodId': 13991952, 'date': '2026-06-08', 'price': 3182.77, 'merchantId': 22905}, {'prodId': 13991952, 'date': '2026-06-09', 'price': 3374.1, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-06-10', 'price': 3374.1, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-06-11', 'price': 3374.1, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-06-12', 'price': 3374.1, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-06-13', 'price': 3498.99, 'merchantId': 16108}, {'prodId': 13991952, 'date': '2026-06-14', 'price': 3498.99, 'merchantId': 16108}, {'prodId': 13991952, 'date': '2026-06-15', 'price': 3498.99, 'merchantId': 16108}, {'prodId': 13991952, 'date': '2026-06-16', 'price': 3369.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2026-06-17', 'price': 3498.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2026-06-18', 'price': 3498.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2026-06-19', 'price': 3498.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2026-06-20', 'price': 3498.0, 'merchantId': 5}, {'prodId': 13991952, 'date': '2026-06-21', 'price': 3649.5, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-06-22', 'price': 3148.2, 'merchantId': 5}, {'prodId': 13991952, 'date': '2026-06-23', 'price': 3649.5, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-06-24', 'price': 3649.5, 'merchantId': 1582}, {'prodId': 13991952, 'date': '2026-06-25', 'price': 3649.5, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-06-26', 'price': 3693.39, 'merchantId': 2584}, {'prodId': 13991952, 'date': '2026-06-27', 'price': 3649.5, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-06-28', 'price': 3649.5, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-06-29', 'price': 3693.39, 'merchantId': 2584}, {'prodId': 13991952, 'date': '2026-06-30', 'price': 3693.39, 'merchantId': 2584}, {'prodId': 13991952, 'date': '2026-07-01', 'price': 3237.83, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-07-02', 'price': 3237.83, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-07-03', 'price': 3237.83, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-07-04', 'price': 3149.1, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-07-05', 'price': 3149.1, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-07-06', 'price': 3149.1, 'merchantId': 9385}, {'prodId': 13991952, 'date': '2026-07-07', 'price': 3149.1, 'merchantId': 9385}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13993093, 'date': '2025-10-11', 'price': 6612.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-10-12', 'price': 6612.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-10-13', 'price': 6612.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-10-14', 'price': 6612.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-10-15', 'price': 6612.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-10-16', 'price': 6612.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-10-17', 'price': 6612.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-10-18', 'price': 6612.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-10-19', 'price': 6612.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-10-20', 'price': 6612.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-10-21', 'price': 6612.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-10-22', 'price': 6612.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-10-23', 'price': 6612.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-10-24', 'price': 6612.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-10-25', 'price': 6612.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-10-26', 'price': 6612.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-10-27', 'price': 6612.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-10-28', 'price': 6612.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-10-29', 'price': 6612.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-10-30', 'price': 6612.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-10-31', 'price': 6612.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-11-01', 'price': 6612.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-11-02', 'price': 6612.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-11-03', 'price': 6612.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-11-04', 'price': 6524.09, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-11-05', 'price': 5741.09, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-11-06', 'price': 5741.09, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-11-07', 'price': 5741.09, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-11-08', 'price': 5741.09, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-11-09', 'price': 5741.09, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-11-10', 'price': 5741.09, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-11-11', 'price': 5741.09, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-11-12', 'price': 5741.09, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-11-13', 'price': 4859.99, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-11-14', 'price': 4859.99, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-11-15', 'price': 5741.09, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-11-16', 'price': 5741.09, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-11-17', 'price': 5741.09, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-11-18', 'price': 5741.09, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-11-19', 'price': 5829.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-11-20', 'price': 5829.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-11-21', 'price': 5829.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-11-22', 'price': 7477.8, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-11-23', 'price': 5642.99, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-11-24', 'price': 4083.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-11-25', 'price': 4083.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-11-26', 'price': 4083.29, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2025-11-27', 'price': 3299.0, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2025-11-28', 'price': 3199.0, 'merchantId': 21629}, {'prodId': 13993093, 'date': '2025-11-29', 'price': 3199.0, 'merchantId': 21629}, {'prodId': 13993093, 'date': '2025-11-30', 'price': 3199.0, 'merchantId': 21629}, {'prodId': 13993093, 'date': '2025-12-01', 'price': 2999.0, 'merchantId': 1582}, {'prodId': 13993093, 'date': '2025-12-02', 'price': 2999.0, 'merchantId': 1582}, {'prodId': 13993093, 'date': '2025-12-03', 'price': 3298.0, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2025-12-04', 'price': 3279.0, 'merchantId': 21629}, {'prodId': 13993093, 'date': '2025-12-05', 'price': 3279.0, 'merchantId': 21629}, {'prodId': 13993093, 'date': '2025-12-06', 'price': 3279.0, 'merchantId': 21629}, {'prodId': 13993093, 'date': '2025-12-07', 'price': 3279.0, 'merchantId': 21629}, {'prodId': 13993093, 'date': '2025-12-08', 'price': 3279.0, 'merchantId': 21629}, {'prodId': 13993093, 'date': '2025-12-09', 'price': 3279.0, 'merchantId': 21629}, {'prodId': 13993093, 'date': '2025-12-10', 'price': 3279.0, 'merchantId': 21629}, {'prodId': 13993093, 'date': '2025-12-11', 'price': 3298.0, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2025-12-12', 'price': 2932.45, 'merchantId': 20609}, {'prodId': 13993093, 'date': '2025-12-13', 'price': 2932.45, 'merchantId': 20609}, {'prodId': 13993093, 'date': '2025-12-14', 'price': 2932.45, 'merchantId': 20609}, {'prodId': 13993093, 'date': '2025-12-15', 'price': 2932.45, 'merchantId': 20609}, {'prodId': 13993093, 'date': '2025-12-16', 'price': 2932.45, 'merchantId': 20609}, {'prodId': 13993093, 'date': '2025-12-17', 'price': 2932.45, 'merchantId': 20609}, {'prodId': 13993093, 'date': '2025-12-18', 'price': 2932.45, 'merchantId': 20609}, {'prodId': 13993093, 'date': '2025-12-19', 'price': 2665.78, 'merchantId': 20612}, {'prodId': 13993093, 'date': '2025-12-20', 'price': 3332.22, 'merchantId': 1582}, {'prodId': 13993093, 'date': '2025-12-21', 'price': 3479.0, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2025-12-22', 'price': 3479.0, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2025-12-23', 'price': 3299.0, 'merchantId': 20583}, {'prodId': 13993093, 'date': '2025-12-24', 'price': 3479.0, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2025-12-25', 'price': 3479.0, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2025-12-26', 'price': 3479.0, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2025-12-27', 'price': 3279.0, 'merchantId': 21628}, {'prodId': 13993093, 'date': '2025-12-28', 'price': 3479.0, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2025-12-29', 'price': 3479.0, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2025-12-30', 'price': 3479.0, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2025-12-31', 'price': 3479.0, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-01-01', 'price': 3479.0, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-01-02', 'price': 3299.0, 'merchantId': 20612}, {'prodId': 13993093, 'date': '2026-01-03', 'price': 3479.0, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-01-04', 'price': 3597.0, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-01-05', 'price': 3098.7, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-01-06', 'price': 3098.61, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-01-07', 'price': 3098.61, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-01-08', 'price': 2799.0, 'merchantId': 20612}, {'prodId': 13993093, 'date': '2026-01-09', 'price': 2736.8, 'merchantId': 20583}, {'prodId': 13993093, 'date': '2026-01-10', 'price': 3098.61, 'merchantId': 4}, {'prodId': 13993093, 'date': '2026-01-11', 'price': 3098.7, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-01-12', 'price': 3030.13, 'merchantId': 20609}, {'prodId': 13993093, 'date': '2026-01-13', 'price': 3099.0, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-01-14', 'price': 3099.0, 'merchantId': 4}, {'prodId': 13993093, 'date': '2026-01-15', 'price': 3099.0, 'merchantId': 20612}, {'prodId': 13993093, 'date': '2026-01-16', 'price': 3099.0, 'merchantId': 4}, {'prodId': 13993093, 'date': '2026-01-17', 'price': 3199.0, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-01-18', 'price': 3199.0, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-01-19', 'price': 3199.0, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-01-20', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-01-21', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-01-22', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-01-23', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-01-24', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-01-25', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-01-26', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-01-27', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-01-28', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-01-29', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-01-30', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-01-31', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-02-01', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-02-02', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-02-03', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-02-04', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-02-05', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-02-06', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-02-07', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-02-08', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-02-09', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-02-10', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-02-11', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-02-12', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-02-13', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-02-14', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-02-15', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-02-16', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-02-17', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-02-18', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-02-19', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-02-20', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-02-21', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-02-22', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-02-23', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-02-24', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-02-25', 'price': 3225.69, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-02-26', 'price': 3599.0, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-02-27', 'price': 3599.0, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-02-28', 'price': 3599.0, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-03-01', 'price': 3599.0, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-03-02', 'price': 3419.1, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-03-03', 'price': 3419.1, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-03-04', 'price': 3419.1, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-03-05', 'price': 3419.1, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-03-06', 'price': 3419.1, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-03-07', 'price': 3419.1, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-03-08', 'price': 3419.1, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-03-09', 'price': 3419.1, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-03-10', 'price': 3419.1, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-03-11', 'price': 3419.1, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-03-12', 'price': 3419.1, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-03-13', 'price': 3419.1, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-03-14', 'price': 3419.1, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-03-15', 'price': 3419.1, 'merchantId': 20612}, {'prodId': 13993093, 'date': '2026-03-16', 'price': 3299.0, 'merchantId': 1582}, {'prodId': 13993093, 'date': '2026-03-17', 'price': 3299.0, 'merchantId': 1582}, {'prodId': 13993093, 'date': '2026-03-18', 'price': 3299.0, 'merchantId': 1582}, {'prodId': 13993093, 'date': '2026-03-19', 'price': 3599.0, 'merchantId': 4}, {'prodId': 13993093, 'date': '2026-03-20', 'price': 3251.31, 'merchantId': 1582}, {'prodId': 13993093, 'date': '2026-03-21', 'price': 3299.0, 'merchantId': 1582}, {'prodId': 13993093, 'date': '2026-03-22', 'price': 3299.0, 'merchantId': 1582}, {'prodId': 13993093, 'date': '2026-03-23', 'price': 3599.1, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-03-24', 'price': 3599.1, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-03-25', 'price': 3599.1, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-03-26', 'price': 3599.0, 'merchantId': 4}, {'prodId': 13993093, 'date': '2026-03-27', 'price': 3599.0, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-03-28', 'price': 3599.0, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-03-29', 'price': 3572.6, 'merchantId': 1582}, {'prodId': 13993093, 'date': '2026-03-30', 'price': 3199.0, 'merchantId': 1582}, {'prodId': 13993093, 'date': '2026-03-31', 'price': 3418.9, 'merchantId': 4}, {'prodId': 13993093, 'date': '2026-04-01', 'price': 3418.9, 'merchantId': 4}, {'prodId': 13993093, 'date': '2026-04-02', 'price': 3418.9, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-04-03', 'price': 3418.9, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-04-04', 'price': 3418.9, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-04-05', 'price': 3418.9, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-04-06', 'price': 3418.0, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-04-07', 'price': 3417.9, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-04-08', 'price': 3417.9, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-04-09', 'price': 3417.9, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-04-10', 'price': 3417.3, 'merchantId': 20612}, {'prodId': 13993093, 'date': '2026-04-11', 'price': 3417.3, 'merchantId': 20612}, {'prodId': 13993093, 'date': '2026-04-12', 'price': 3417.3, 'merchantId': 20612}, {'prodId': 13993093, 'date': '2026-04-13', 'price': 3417.3, 'merchantId': 20612}, {'prodId': 13993093, 'date': '2026-04-14', 'price': 3417.3, 'merchantId': 20612}, {'prodId': 13993093, 'date': '2026-04-15', 'price': 3684.6, 'merchantId': 1582}, {'prodId': 13993093, 'date': '2026-04-16', 'price': 3612.75, 'merchantId': 1582}, {'prodId': 13993093, 'date': '2026-04-17', 'price': 3954.56, 'merchantId': 20612}, {'prodId': 13993093, 'date': '2026-04-18', 'price': 3954.56, 'merchantId': 20612}, {'prodId': 13993093, 'date': '2026-04-19', 'price': 3954.56, 'merchantId': 20612}, {'prodId': 13993093, 'date': '2026-04-20', 'price': 3779.0, 'merchantId': 4}, {'prodId': 13993093, 'date': '2026-04-21', 'price': 3737.11, 'merchantId': 20612}, {'prodId': 13993093, 'date': '2026-04-22', 'price': 3737.11, 'merchantId': 20612}, {'prodId': 13993093, 'date': '2026-04-23', 'price': 3737.11, 'merchantId': 20612}, {'prodId': 13993093, 'date': '2026-04-24', 'price': 3779.0, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-04-25', 'price': 3779.0, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-04-26', 'price': 3779.0, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-04-27', 'price': 3779.0, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-04-28', 'price': 3779.0, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-04-29', 'price': 3779.0, 'merchantId': 21628}, {'prodId': 13993093, 'date': '2026-04-30', 'price': 3779.0, 'merchantId': 21628}, {'prodId': 13993093, 'date': '2026-05-01', 'price': 3307.5, 'merchantId': 1582}, {'prodId': 13993093, 'date': '2026-05-02', 'price': 3307.5, 'merchantId': 1582}, {'prodId': 13993093, 'date': '2026-05-03', 'price': 3307.5, 'merchantId': 1582}, {'prodId': 13993093, 'date': '2026-05-04', 'price': 3251.7, 'merchantId': 1582}, {'prodId': 13993093, 'date': '2026-05-05', 'price': 3251.7, 'merchantId': 1582}, {'prodId': 13993093, 'date': '2026-05-06', 'price': 3251.49, 'merchantId': 1582}, {'prodId': 13993093, 'date': '2026-05-07', 'price': 3251.7, 'merchantId': 1582}, {'prodId': 13993093, 'date': '2026-05-08', 'price': 3251.7, 'merchantId': 1582}, {'prodId': 13993093, 'date': '2026-05-09', 'price': 2970.7, 'merchantId': 1582}, {'prodId': 13993093, 'date': '2026-05-10', 'price': 3412.53, 'merchantId': 1582}, {'prodId': 13993093, 'date': '2026-05-11', 'price': 3412.53, 'merchantId': 1582}, {'prodId': 13993093, 'date': '2026-05-12', 'price': 3412.53, 'merchantId': 1582}, {'prodId': 13993093, 'date': '2026-05-13', 'price': 3412.53, 'merchantId': 1582}, {'prodId': 13993093, 'date': '2026-05-14', 'price': 3791.7, 'merchantId': 1582}, {'prodId': 13993093, 'date': '2026-05-15', 'price': 3343.12, 'merchantId': 20609}, {'prodId': 13993093, 'date': '2026-05-16', 'price': 3343.12, 'merchantId': 20612}, {'prodId': 13993093, 'date': '2026-05-17', 'price': 3343.12, 'merchantId': 20612}, {'prodId': 13993093, 'date': '2026-05-18', 'price': 3343.12, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-05-19', 'price': 3343.12, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-05-20', 'price': 2903.12, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-05-21', 'price': 2903.12, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-05-22', 'price': 2903.12, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-05-23', 'price': 2903.12, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-05-24', 'price': 2903.12, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-05-25', 'price': 2903.12, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-05-26', 'price': 2903.12, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-05-27', 'price': 2903.12, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-05-28', 'price': 3263.22, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-05-29', 'price': 3263.22, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-05-30', 'price': 3376.95, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-05-31', 'price': 3376.95, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-06-01', 'price': 3339.01, 'merchantId': 245}, {'prodId': 13993093, 'date': '2026-06-02', 'price': 3339.01, 'merchantId': 245}, {'prodId': 13993093, 'date': '2026-06-03', 'price': 3598.2, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-06-04', 'price': 3598.2, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-06-05', 'price': 3598.2, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-06-06', 'price': 3266.09, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-06-07', 'price': 3266.09, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-06-08', 'price': 3266.09, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-06-09', 'price': 3341.07, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-06-10', 'price': 3341.07, 'merchantId': 245}, {'prodId': 13993093, 'date': '2026-06-11', 'price': 3340.98, 'merchantId': 245}, {'prodId': 13993093, 'date': '2026-06-12', 'price': 3150.32, 'merchantId': 245}, {'prodId': 13993093, 'date': '2026-06-13', 'price': 3150.32, 'merchantId': 245}, {'prodId': 13993093, 'date': '2026-06-14', 'price': 3150.32, 'merchantId': 245}, {'prodId': 13993093, 'date': '2026-06-15', 'price': 3150.32, 'merchantId': 245}, {'prodId': 13993093, 'date': '2026-06-16', 'price': 3340.1, 'merchantId': 245}, {'prodId': 13993093, 'date': '2026-06-17', 'price': 3699.0, 'merchantId': 21628}, {'prodId': 13993093, 'date': '2026-06-18', 'price': 3656.0, 'merchantId': 4}, {'prodId': 13993093, 'date': '2026-06-19', 'price': 3655.9, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-06-20', 'price': 3466.74, 'merchantId': 245}, {'prodId': 13993093, 'date': '2026-06-21', 'price': 3466.74, 'merchantId': 245}, {'prodId': 13993093, 'date': '2026-06-22', 'price': 3466.74, 'merchantId': 245}, {'prodId': 13993093, 'date': '2026-06-23', 'price': 3417.0, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-06-24', 'price': 3417.0, 'merchantId': 23326}, {'prodId': 13993093, 'date': '2026-06-25', 'price': 3149.0, 'merchantId': 20609}, {'prodId': 13993093, 'date': '2026-06-26', 'price': 3149.0, 'merchantId': 20609}, {'prodId': 13993093, 'date': '2026-06-27', 'price': 3149.0, 'merchantId': 20609}, {'prodId': 13993093, 'date': '2026-06-28', 'price': 3185.1, 'merchantId': 22905}, {'prodId': 13993093, 'date': '2026-06-29', 'price': 3199.0, 'merchantId': 22902}, {'prodId': 13993093, 'date': '2026-06-30', 'price': 2899.0, 'merchantId': 16108}, {'prodId': 13993093, 'date': '2026-07-01', 'price': 2699.1, 'merchantId': 16108}, {'prodId': 13993093, 'date': '2026-07-02', 'price': 3125.95, 'merchantId': 245}, {'prodId': 13993093, 'date': '2026-07-03', 'price': 3125.95, 'merchantId': 245}, {'prodId': 13993093, 'date': '2026-07-04', 'price': 3124.98, 'merchantId': 245}, {'prodId': 13993093, 'date': '2026-07-05', 'price': 3124.98, 'merchantId': 245}, {'prodId': 13993093, 'date': '2026-07-06', 'price': 3124.98, 'merchantId': 245}, {'prodId': 13993093, 'date': '2026-07-07', 'price': 3124.0, 'merchantId': 245}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13538152, 'date': '2025-07-07', 'price': 5039.1, 'merchantId': 23199}, {'prodId': 13538152, 'date': '2025-07-08', 'price': 5319.05, 'merchantId': 20583}, {'prodId': 13538152, 'date': '2025-07-09', 'price': 5319.05, 'merchantId': 20583}, {'prodId': 13538152, 'date': '2025-07-10', 'price': 5199.0, 'merchantId': 34}, {'prodId': 13538152, 'date': '2025-07-11', 'price': 5039.1, 'merchantId': 23199}, {'prodId': 13538152, 'date': '2025-07-12', 'price': 5039.1, 'merchantId': 23199}, {'prodId': 13538152, 'date': '2025-07-13', 'price': 4859.1, 'merchantId': 23199}, {'prodId': 13538152, 'date': '2025-07-14', 'price': 4859.1, 'merchantId': 23199}, {'prodId': 13538152, 'date': '2025-07-15', 'price': 5207.07, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2025-07-16', 'price': 5207.07, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2025-07-17', 'price': 5039.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2025-07-18', 'price': 5039.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2025-07-19', 'price': 5207.07, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2025-07-20', 'price': 5207.07, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2025-07-21', 'price': 5039.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2025-07-22', 'price': 5039.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2025-07-23', 'price': 5039.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2025-07-24', 'price': 5039.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2025-07-25', 'price': 5039.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2025-07-26', 'price': 5039.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2025-07-27', 'price': 5039.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2025-07-28', 'price': 4899.0, 'merchantId': 5}, {'prodId': 13538152, 'date': '2025-07-29', 'price': 4899.0, 'merchantId': 5}, {'prodId': 13538152, 'date': '2025-07-30', 'price': 5038.2, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2025-07-31', 'price': 5038.2, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2025-08-01', 'price': 5038.2, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2025-08-02', 'price': 5038.2, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2025-08-03', 'price': 5038.2, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2025-08-04', 'price': 5037.3, 'merchantId': 23199}, {'prodId': 13538152, 'date': '2025-08-05', 'price': 4994.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2025-08-06', 'price': 4994.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2025-08-07', 'price': 4994.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2025-08-08', 'price': 4985.1, 'merchantId': 20583}, {'prodId': 13538152, 'date': '2025-08-09', 'price': 4985.1, 'merchantId': 20583}, {'prodId': 13538152, 'date': '2025-08-10', 'price': 4985.1, 'merchantId': 20583}, {'prodId': 13538152, 'date': '2025-08-11', 'price': 4985.1, 'merchantId': 20583}, {'prodId': 13538152, 'date': '2025-08-12', 'price': 4994.1, 'merchantId': 23199}, {'prodId': 13538152, 'date': '2025-08-13', 'price': 4899.9, 'merchantId': 5}, {'prodId': 13538152, 'date': '2025-08-14', 'price': 4899.9, 'merchantId': 5}, {'prodId': 13538152, 'date': '2025-08-15', 'price': 4899.9, 'merchantId': 5}, {'prodId': 13538152, 'date': '2025-08-16', 'price': 4899.9, 'merchantId': 5}, {'prodId': 13538152, 'date': '2025-08-17', 'price': 4899.9, 'merchantId': 5}, {'prodId': 13538152, 'date': '2025-08-18', 'price': 4899.9, 'merchantId': 5}, {'prodId': 13538152, 'date': '2025-08-19', 'price': 4769.1, 'merchantId': 23199}, {'prodId': 13538152, 'date': '2025-08-20', 'price': 4769.1, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2025-08-21', 'price': 4769.1, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2025-08-22', 'price': 4769.1, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2025-08-23', 'price': 4769.1, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2025-08-24', 'price': 4769.1, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2025-08-25', 'price': 4769.1, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2025-08-26', 'price': 4769.1, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2025-08-27', 'price': 4769.1, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2025-08-28', 'price': 4769.1, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2025-08-29', 'price': 4769.1, 'merchantId': 23199}, {'prodId': 13538152, 'date': '2025-08-30', 'price': 4679.1, 'merchantId': 23199}, {'prodId': 13538152, 'date': '2025-08-31', 'price': 4679.1, 'merchantId': 23199}, {'prodId': 13538152, 'date': '2025-09-01', 'price': 4679.1, 'merchantId': 23199}, {'prodId': 13538152, 'date': '2025-09-02', 'price': 4679.1, 'merchantId': 23199}, {'prodId': 13538152, 'date': '2025-09-03', 'price': 4679.1, 'merchantId': 23199}, {'prodId': 13538152, 'date': '2025-09-04', 'price': 4679.1, 'merchantId': 23199}, {'prodId': 13538152, 'date': '2025-09-05', 'price': 4678.2, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2025-09-06', 'price': 4678.2, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2025-09-07', 'price': 4678.2, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2025-09-08', 'price': 4669.9, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2025-09-09', 'price': 4566.13, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2025-09-10', 'price': 4318.2, 'merchantId': 23199}, {'prodId': 13538152, 'date': '2025-09-11', 'price': 4318.2, 'merchantId': 23199}, {'prodId': 13538152, 'date': '2025-09-12', 'price': 4318.2, 'merchantId': 23199}, {'prodId': 13538152, 'date': '2025-09-13', 'price': 4228.2, 'merchantId': 23199}, {'prodId': 13538152, 'date': '2025-09-14', 'price': 4228.2, 'merchantId': 23199}, {'prodId': 13538152, 'date': '2025-09-15', 'price': 4228.2, 'merchantId': 23199}, {'prodId': 13538152, 'date': '2025-09-16', 'price': 4223.09, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2025-09-17', 'price': 4215.15, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-09-18', 'price': 4199.0, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2025-09-19', 'price': 4199.0, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2025-09-20', 'price': 4199.0, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2025-09-21', 'price': 4199.0, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2025-09-22', 'price': 4199.0, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2025-09-23', 'price': 4199.0, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2025-09-24', 'price': 4199.0, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2025-09-25', 'price': 4198.0, 'merchantId': 23199}, {'prodId': 13538152, 'date': '2025-09-26', 'price': 4198.0, 'merchantId': 23199}, {'prodId': 13538152, 'date': '2025-09-27', 'price': 4099.0, 'merchantId': 5}, {'prodId': 13538152, 'date': '2025-09-28', 'price': 4099.0, 'merchantId': 5}, {'prodId': 13538152, 'date': '2025-09-29', 'price': 4099.0, 'merchantId': 5}, {'prodId': 13538152, 'date': '2025-09-30', 'price': 4198.0, 'merchantId': 23199}, {'prodId': 13538152, 'date': '2025-10-01', 'price': 4198.0, 'merchantId': 23199}, {'prodId': 13538152, 'date': '2025-10-02', 'price': 4198.0, 'merchantId': 23199}, {'prodId': 13538152, 'date': '2025-10-03', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-04', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-05', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-06', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-07', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-08', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-09', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-10', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-11', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-12', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-13', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-14', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-15', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-16', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-17', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-18', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-19', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-20', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-21', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-22', 'price': 3999.6, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-23', 'price': 3999.6, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-24', 'price': 3999.6, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-25', 'price': 3999.6, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-26', 'price': 3999.6, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-27', 'price': 3999.6, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-28', 'price': 3999.6, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-29', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-30', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-10-31', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-11-01', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-11-02', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-11-03', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-11-04', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-11-05', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-11-06', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-11-07', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-11-08', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-11-09', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-11-10', 'price': 4158.99, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-11-11', 'price': 3959.0, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-11-12', 'price': 3959.0, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-11-13', 'price': 3959.0, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-11-14', 'price': 3959.0, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-11-15', 'price': 3959.0, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-11-16', 'price': 3959.0, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-11-17', 'price': 3959.0, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-11-18', 'price': 3959.0, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-11-19', 'price': 3959.0, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-11-20', 'price': 3959.0, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-11-21', 'price': 3959.0, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-11-22', 'price': 3959.0, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-11-23', 'price': 3959.0, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-11-24', 'price': 3959.0, 'merchantId': 20612}, {'prodId': 13538152, 'date': '2025-11-25', 'price': 4298.99, 'merchantId': 22902}, {'prodId': 13538152, 'date': '2025-11-26', 'price': 4298.97, 'merchantId': 23326}, {'prodId': 13538152, 'date': '2025-11-27', 'price': 4298.97, 'merchantId': 23326}, {'prodId': 13538152, 'date': '2025-11-28', 'price': 4203.43, 'merchantId': 23326}, {'prodId': 13538152, 'date': '2025-11-29', 'price': 4298.97, 'merchantId': 2}, {'prodId': 13538152, 'date': '2025-11-30', 'price': 4298.97, 'merchantId': 2}, {'prodId': 13538152, 'date': '2025-12-01', 'price': 4298.97, 'merchantId': 2}, {'prodId': 13538152, 'date': '2025-12-02', 'price': 4298.97, 'merchantId': 2}, {'prodId': 13538152, 'date': '2025-12-03', 'price': 4298.97, 'merchantId': 2}, {'prodId': 13538152, 'date': '2025-12-04', 'price': 4298.97, 'merchantId': 2}, {'prodId': 13538152, 'date': '2025-12-05', 'price': 4298.97, 'merchantId': 2}, {'prodId': 13538152, 'date': '2025-12-06', 'price': 4298.97, 'merchantId': 2}, {'prodId': 13538152, 'date': '2025-12-07', 'price': 4298.97, 'merchantId': 2}, {'prodId': 13538152, 'date': '2025-12-08', 'price': 4298.97, 'merchantId': 2}, {'prodId': 13538152, 'date': '2025-12-09', 'price': 4298.97, 'merchantId': 2}, {'prodId': 13538152, 'date': '2025-12-10', 'price': 4298.97, 'merchantId': 2}, {'prodId': 13538152, 'date': '2025-12-11', 'price': 4298.97, 'merchantId': 2}, {'prodId': 13538152, 'date': '2025-12-12', 'price': 4298.97, 'merchantId': 2}, {'prodId': 13538152, 'date': '2025-12-13', 'price': 4298.97, 'merchantId': 2}, {'prodId': 13538152, 'date': '2025-12-14', 'price': 4298.97, 'merchantId': 2}, {'prodId': 13538152, 'date': '2025-12-15', 'price': 4298.97, 'merchantId': 2}, {'prodId': 13538152, 'date': '2025-12-16', 'price': 4298.97, 'merchantId': 2}, {'prodId': 13538152, 'date': '2025-12-17', 'price': 4298.97, 'merchantId': 2}, {'prodId': 13538152, 'date': '2025-12-18', 'price': 4298.97, 'merchantId': 34}, {'prodId': 13538152, 'date': '2025-12-19', 'price': 4499.0, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2025-12-20', 'price': 4499.0, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2025-12-21', 'price': 4499.0, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2025-12-22', 'price': 4499.0, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2025-12-23', 'price': 4799.0, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2025-12-24', 'price': 4799.0, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2025-12-25', 'price': 4799.0, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2025-12-26', 'price': 4799.0, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2025-12-27', 'price': 4299.0, 'merchantId': 21627}, {'prodId': 13538152, 'date': '2025-12-28', 'price': 5143.3, 'merchantId': 1582}, {'prodId': 13538152, 'date': '2025-12-29', 'price': 5332.22, 'merchantId': 1582}, {'prodId': 13538152, 'date': '2025-12-30', 'price': 5143.3, 'merchantId': 1582}, {'prodId': 13538152, 'date': '2025-12-31', 'price': 4299.0, 'merchantId': 21627}, {'prodId': 13538152, 'date': '2026-01-01', 'price': 6023.0, 'merchantId': 1582}, {'prodId': 13538152, 'date': '2026-01-02', 'price': 6023.0, 'merchantId': 1582}, {'prodId': 13538152, 'date': '2026-01-03', 'price': 4729.0, 'merchantId': 1582}, {'prodId': 13538152, 'date': '2026-01-04', 'price': 6023.0, 'merchantId': 1582}, {'prodId': 13538152, 'date': '2026-01-05', 'price': 4729.0, 'merchantId': 1582}, {'prodId': 13538152, 'date': '2026-01-06', 'price': 3999.0, 'merchantId': 2}, {'prodId': 13538152, 'date': '2026-01-07', 'price': 4745.68, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-01-08', 'price': 4372.41, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-01-09', 'price': 3999.0, 'merchantId': 2}, {'prodId': 13538152, 'date': '2026-01-10', 'price': 4372.41, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-01-11', 'price': 4372.41, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-01-12', 'price': 4221.16, 'merchantId': 2584}, {'prodId': 13538152, 'date': '2026-01-13', 'price': 4221.16, 'merchantId': 2584}, {'prodId': 13538152, 'date': '2026-01-14', 'price': 4372.41, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-01-15', 'price': 4372.41, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-01-16', 'price': 4372.41, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-01-17', 'price': 3999.0, 'merchantId': 2}, {'prodId': 13538152, 'date': '2026-01-18', 'price': 4372.41, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-01-19', 'price': 4372.41, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-01-20', 'price': 4699.0, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-01-21', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-01-22', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-01-23', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-01-24', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-01-25', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-01-26', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-01-27', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-01-28', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-01-29', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-01-30', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-01-31', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-02-01', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-02-02', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-02-03', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-02-04', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-02-05', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-02-06', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-02-07', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-02-08', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-02-09', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-02-10', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-02-11', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-02-12', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-02-13', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-02-14', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-02-15', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-02-16', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-02-17', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-02-18', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-02-19', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-02-20', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-02-21', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-02-22', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-02-23', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-02-24', 'price': 3998.7, 'merchantId': 16108}, {'prodId': 13538152, 'date': '2026-02-25', 'price': 4699.0, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-02-26', 'price': 4699.0, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-02-27', 'price': 4699.0, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-02-28', 'price': 4699.0, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-01', 'price': 4699.0, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-02', 'price': 4599.0, 'merchantId': 9385}, {'prodId': 13538152, 'date': '2026-03-03', 'price': 4599.0, 'merchantId': 1582}, {'prodId': 13538152, 'date': '2026-03-04', 'price': 4454.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-05', 'price': 4454.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-06', 'price': 4454.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-07', 'price': 4454.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-08', 'price': 4454.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-09', 'price': 4454.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-10', 'price': 4454.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-11', 'price': 4454.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-12', 'price': 4454.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-13', 'price': 4454.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-14', 'price': 4454.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-15', 'price': 4454.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-16', 'price': 4454.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-17', 'price': 4454.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-18', 'price': 4699.0, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-19', 'price': 4699.0, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-20', 'price': 4699.0, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-21', 'price': 4699.0, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-22', 'price': 4699.0, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-23', 'price': 4699.0, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-24', 'price': 4646.79, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-25', 'price': 4646.79, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-26', 'price': 4646.79, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-27', 'price': 4646.79, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-28', 'price': 4646.79, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-29', 'price': 4646.79, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-30', 'price': 4646.79, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-03-31', 'price': 4646.79, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-04-01', 'price': 4646.79, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-04-02', 'price': 4360.11, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-04-03', 'price': 4360.11, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-04-04', 'price': 4360.11, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-04-05', 'price': 4360.11, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-04-06', 'price': 4360.11, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-04-07', 'price': 4360.11, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-04-08', 'price': 4360.11, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-04-09', 'price': 4360.11, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-04-10', 'price': 4360.11, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-04-11', 'price': 4409.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-04-12', 'price': 4409.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-04-13', 'price': 4409.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-04-14', 'price': 4409.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-04-15', 'price': 4409.1, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-04-16', 'price': 4409.1, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-04-17', 'price': 4360.11, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-04-18', 'price': 4360.11, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-04-19', 'price': 4360.11, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-04-20', 'price': 4319.1, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-04-21', 'price': 4223.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-04-22', 'price': 4223.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-04-23', 'price': 4223.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-04-24', 'price': 4223.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-04-25', 'price': 4223.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-04-26', 'price': 4311.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-04-27', 'price': 4311.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-04-28', 'price': 4360.11, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-04-29', 'price': 4360.11, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-04-30', 'price': 4271.11, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-05-01', 'price': 4271.11, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-05-02', 'price': 4271.11, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-05-03', 'price': 4271.11, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-05-04', 'price': 4223.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-05-05', 'price': 4223.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-05-06', 'price': 4223.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-05-07', 'price': 4223.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-05-08', 'price': 4223.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-05-09', 'price': 4223.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-05-10', 'price': 4223.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-05-11', 'price': 4223.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-05-12', 'price': 4223.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-05-13', 'price': 4223.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-05-14', 'price': 4223.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-05-15', 'price': 4223.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-05-16', 'price': 4223.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-05-17', 'price': 4223.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-05-18', 'price': 4223.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-05-19', 'price': 4223.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-05-20', 'price': 3869.1, 'merchantId': 9385}, {'prodId': 13538152, 'date': '2026-05-21', 'price': 3869.1, 'merchantId': 9385}, {'prodId': 13538152, 'date': '2026-05-22', 'price': 3869.1, 'merchantId': 9385}, {'prodId': 13538152, 'date': '2026-05-23', 'price': 3869.1, 'merchantId': 9385}, {'prodId': 13538152, 'date': '2026-05-24', 'price': 3869.1, 'merchantId': 9385}, {'prodId': 13538152, 'date': '2026-05-25', 'price': 4127.14, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-05-26', 'price': 4127.14, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-05-27', 'price': 4127.14, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-05-28', 'price': 4041.14, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-05-29', 'price': 4041.14, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-05-30', 'price': 4041.14, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-05-31', 'price': 4041.14, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-06-01', 'price': 4041.14, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-06-02', 'price': 4041.14, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-06-03', 'price': 3697.14, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-06-04', 'price': 3783.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-06-05', 'price': 3783.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-06-06', 'price': 3783.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-06-07', 'price': 3783.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-06-08', 'price': 3783.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-06-09', 'price': 3783.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-06-10', 'price': 3783.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-06-11', 'price': 3783.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-06-12', 'price': 3783.12, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-06-13', 'price': 3783.12, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-06-14', 'price': 3783.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-06-15', 'price': 3783.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-06-16', 'price': 3783.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-06-17', 'price': 3783.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-06-18', 'price': 3783.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-06-19', 'price': 3783.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-06-20', 'price': 3783.12, 'merchantId': 22905}, {'prodId': 13538152, 'date': '2026-06-21', 'price': 3783.12, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-06-22', 'price': 3783.12, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-06-23', 'price': 3783.12, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-06-24', 'price': 3783.12, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-06-25', 'price': 3783.12, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-06-26', 'price': 3783.12, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-06-27', 'price': 3869.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-06-28', 'price': 3869.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-06-29', 'price': 3869.1, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-06-30', 'price': 4067.47, 'merchantId': 9385}, {'prodId': 13538152, 'date': '2026-07-01', 'price': 4049.1, 'merchantId': 9385}, {'prodId': 13538152, 'date': '2026-07-02', 'price': 4047.12, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-07-03', 'price': 4047.12, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-07-04', 'price': 4047.12, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-07-05', 'price': 4047.12, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-07-06', 'price': 4047.12, 'merchantId': 20609}, {'prodId': 13538152, 'date': '2026-07-07', 'price': 4047.12, 'merchantId': 20609}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13570649, 'date': '2025-07-07', 'price': 4633.0, 'merchantId': 5}, {'prodId': 13570649, 'date': '2025-07-08', 'price': 4891.55, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2025-07-09', 'price': 4879.0, 'merchantId': 10763}, {'prodId': 13570649, 'date': '2025-07-10', 'price': 4631.31, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2025-07-11', 'price': 4631.31, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2025-07-12', 'price': 4634.1, 'merchantId': 20583}, {'prodId': 13570649, 'date': '2025-07-13', 'price': 4499.1, 'merchantId': 20583}, {'prodId': 13570649, 'date': '2025-07-14', 'price': 4499.1, 'merchantId': 20583}, {'prodId': 13570649, 'date': '2025-07-15', 'price': 4419.0, 'merchantId': 10763}, {'prodId': 13570649, 'date': '2025-07-16', 'price': 4049.1, 'merchantId': 22902}, {'prodId': 13570649, 'date': '2025-07-17', 'price': 4049.1, 'merchantId': 22902}, {'prodId': 13570649, 'date': '2025-07-18', 'price': 4419.0, 'merchantId': 10763}, {'prodId': 13570649, 'date': '2025-07-19', 'price': 4419.0, 'merchantId': 10763}, {'prodId': 13570649, 'date': '2025-07-20', 'price': 4419.0, 'merchantId': 10763}, {'prodId': 13570649, 'date': '2025-07-21', 'price': 4419.0, 'merchantId': 10763}, {'prodId': 13570649, 'date': '2025-07-22', 'price': 4419.0, 'merchantId': 10763}, {'prodId': 13570649, 'date': '2025-07-23', 'price': 4419.0, 'merchantId': 10763}, {'prodId': 13570649, 'date': '2025-07-24', 'price': 4419.0, 'merchantId': 10763}, {'prodId': 13570649, 'date': '2025-07-25', 'price': 4419.0, 'merchantId': 10763}, {'prodId': 13570649, 'date': '2025-07-26', 'price': 4419.0, 'merchantId': 10763}, {'prodId': 13570649, 'date': '2025-07-27', 'price': 4419.0, 'merchantId': 10763}, {'prodId': 13570649, 'date': '2025-07-28', 'price': 4419.0, 'merchantId': 10763}, {'prodId': 13570649, 'date': '2025-07-29', 'price': 4419.0, 'merchantId': 10763}, {'prodId': 13570649, 'date': '2025-07-30', 'price': 4419.0, 'merchantId': 10763}, {'prodId': 13570649, 'date': '2025-07-31', 'price': 4419.0, 'merchantId': 10763}, {'prodId': 13570649, 'date': '2025-08-01', 'price': 4419.0, 'merchantId': 10763}, {'prodId': 13570649, 'date': '2025-08-02', 'price': 4419.0, 'merchantId': 10763}, {'prodId': 13570649, 'date': '2025-08-03', 'price': 4419.0, 'merchantId': 10763}, {'prodId': 13570649, 'date': '2025-08-04', 'price': 3998.7, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-08-05', 'price': 3865.7, 'merchantId': 20612}, {'prodId': 13570649, 'date': '2025-08-06', 'price': 3865.7, 'merchantId': 20612}, {'prodId': 13570649, 'date': '2025-08-07', 'price': 3865.7, 'merchantId': 20612}, {'prodId': 13570649, 'date': '2025-08-08', 'price': 3865.7, 'merchantId': 20612}, {'prodId': 13570649, 'date': '2025-08-09', 'price': 3865.7, 'merchantId': 20612}, {'prodId': 13570649, 'date': '2025-08-10', 'price': 3865.7, 'merchantId': 20612}, {'prodId': 13570649, 'date': '2025-08-11', 'price': 3865.7, 'merchantId': 20612}, {'prodId': 13570649, 'date': '2025-08-12', 'price': 3998.7, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2025-08-13', 'price': 3998.7, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2025-08-14', 'price': 3998.7, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2025-08-15', 'price': 3998.7, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2025-08-16', 'price': 3998.7, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2025-08-17', 'price': 3998.7, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2025-08-18', 'price': 3998.7, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2025-08-19', 'price': 3998.7, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2025-08-20', 'price': 3998.7, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-08-21', 'price': 3998.7, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-08-22', 'price': 3998.7, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-08-23', 'price': 3998.7, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-08-24', 'price': 3998.7, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-08-25', 'price': 3998.7, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-08-26', 'price': 3998.7, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-08-27', 'price': 3998.7, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-08-28', 'price': 3998.7, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-08-29', 'price': 3995.1, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-08-30', 'price': 3995.1, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-08-31', 'price': 3995.1, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-09-01', 'price': 3995.1, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-09-02', 'price': 3995.1, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-09-03', 'price': 3995.1, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-09-04', 'price': 3995.1, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-09-05', 'price': 3995.1, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-09-06', 'price': 3995.1, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-09-07', 'price': 3995.1, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-09-08', 'price': 3995.1, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-09-09', 'price': 3995.1, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-09-10', 'price': 3995.1, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-09-11', 'price': 3995.1, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-09-12', 'price': 3895.1, 'merchantId': 21628}, {'prodId': 13570649, 'date': '2025-09-13', 'price': 3895.1, 'merchantId': 21628}, {'prodId': 13570649, 'date': '2025-09-14', 'price': 3895.1, 'merchantId': 21628}, {'prodId': 13570649, 'date': '2025-09-15', 'price': 3895.1, 'merchantId': 21628}, {'prodId': 13570649, 'date': '2025-09-16', 'price': 3895.1, 'merchantId': 21628}, {'prodId': 13570649, 'date': '2025-09-17', 'price': 3895.1, 'merchantId': 21628}, {'prodId': 13570649, 'date': '2025-09-18', 'price': 3915.69, 'merchantId': 5}, {'prodId': 13570649, 'date': '2025-09-19', 'price': 3915.69, 'merchantId': 5}, {'prodId': 13570649, 'date': '2025-09-20', 'price': 3915.69, 'merchantId': 5}, {'prodId': 13570649, 'date': '2025-09-21', 'price': 3915.69, 'merchantId': 1582}, {'prodId': 13570649, 'date': '2025-09-22', 'price': 3799.0, 'merchantId': 5}, {'prodId': 13570649, 'date': '2025-09-23', 'price': 3799.0, 'merchantId': 5}, {'prodId': 13570649, 'date': '2025-09-24', 'price': 3995.0, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-09-25', 'price': 3995.0, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-09-26', 'price': 3979.9, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2025-09-27', 'price': 3995.0, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-09-28', 'price': 3995.0, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-09-29', 'price': 3979.9, 'merchantId': 1582}, {'prodId': 13570649, 'date': '2025-09-30', 'price': 3979.9, 'merchantId': 1582}, {'prodId': 13570649, 'date': '2025-10-01', 'price': 3995.0, 'merchantId': 20612}, {'prodId': 13570649, 'date': '2025-10-02', 'price': 3994.99, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2025-10-03', 'price': 3994.99, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2025-10-04', 'price': 3979.9, 'merchantId': 1582}, {'prodId': 13570649, 'date': '2025-10-05', 'price': 3995.0, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-10-06', 'price': 3979.9, 'merchantId': 1582}, {'prodId': 13570649, 'date': '2025-10-07', 'price': 3979.9, 'merchantId': 1582}, {'prodId': 13570649, 'date': '2025-10-08', 'price': 3988.0, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-10-09', 'price': 3987.0, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-10-10', 'price': 3935.0, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-10-11', 'price': 3935.0, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-10-12', 'price': 3935.0, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-10-13', 'price': 3934.0, 'merchantId': 4}, {'prodId': 13570649, 'date': '2025-10-14', 'price': 3934.0, 'merchantId': 4}, {'prodId': 13570649, 'date': '2025-10-15', 'price': 3899.0, 'merchantId': 4}, {'prodId': 13570649, 'date': '2025-10-16', 'price': 3898.0, 'merchantId': 4}, {'prodId': 13570649, 'date': '2025-10-17', 'price': 3898.0, 'merchantId': 4}, {'prodId': 13570649, 'date': '2025-10-18', 'price': 3872.7, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2025-10-19', 'price': 3872.7, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2025-10-20', 'price': 3872.7, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2025-10-21', 'price': 3872.7, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2025-10-22', 'price': 3872.7, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2025-10-23', 'price': 3897.99, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2025-10-24', 'price': 3935.0, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-10-25', 'price': 3935.0, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-10-26', 'price': 3935.0, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-10-27', 'price': 3935.0, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-10-28', 'price': 3935.0, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-10-29', 'price': 3935.0, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-10-30', 'price': 3990.1, 'merchantId': 21628}, {'prodId': 13570649, 'date': '2025-10-31', 'price': 3990.1, 'merchantId': 21628}, {'prodId': 13570649, 'date': '2025-11-01', 'price': 3990.1, 'merchantId': 21628}, {'prodId': 13570649, 'date': '2025-11-02', 'price': 3990.1, 'merchantId': 21628}, {'prodId': 13570649, 'date': '2025-11-03', 'price': 3990.1, 'merchantId': 21628}, {'prodId': 13570649, 'date': '2025-11-04', 'price': 3935.0, 'merchantId': 2}, {'prodId': 13570649, 'date': '2025-11-05', 'price': 3980.7, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2025-11-06', 'price': 3876.68, 'merchantId': 245}, {'prodId': 13570649, 'date': '2025-11-07', 'price': 3792.4, 'merchantId': 245}, {'prodId': 13570649, 'date': '2025-11-08', 'price': 3792.4, 'merchantId': 245}, {'prodId': 13570649, 'date': '2025-11-09', 'price': 3792.4, 'merchantId': 245}, {'prodId': 13570649, 'date': '2025-11-10', 'price': 3792.4, 'merchantId': 245}, {'prodId': 13570649, 'date': '2025-11-11', 'price': 3792.4, 'merchantId': 245}, {'prodId': 13570649, 'date': '2025-11-12', 'price': 3792.4, 'merchantId': 245}, {'prodId': 13570649, 'date': '2025-11-13', 'price': 3792.4, 'merchantId': 245}, {'prodId': 13570649, 'date': '2025-11-14', 'price': 3792.4, 'merchantId': 245}, {'prodId': 13570649, 'date': '2025-11-15', 'price': 3792.4, 'merchantId': 245}, {'prodId': 13570649, 'date': '2025-11-16', 'price': 3792.4, 'merchantId': 245}, {'prodId': 13570649, 'date': '2025-11-17', 'price': 3792.4, 'merchantId': 245}, {'prodId': 13570649, 'date': '2025-11-18', 'price': 3792.4, 'merchantId': 245}, {'prodId': 13570649, 'date': '2025-11-19', 'price': 3890.0, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2025-11-20', 'price': 3792.4, 'merchantId': 245}, {'prodId': 13570649, 'date': '2025-11-21', 'price': 3792.4, 'merchantId': 245}, {'prodId': 13570649, 'date': '2025-11-22', 'price': 3876.68, 'merchantId': 245}, {'prodId': 13570649, 'date': '2025-11-23', 'price': 3876.68, 'merchantId': 245}, {'prodId': 13570649, 'date': '2025-11-24', 'price': 3599.06, 'merchantId': 20612}, {'prodId': 13570649, 'date': '2025-11-25', 'price': 3599.05, 'merchantId': 2584}, {'prodId': 13570649, 'date': '2025-11-26', 'price': 3599.05, 'merchantId': 2584}, {'prodId': 13570649, 'date': '2025-11-27', 'price': 3599.05, 'merchantId': 23326}, {'prodId': 13570649, 'date': '2025-11-28', 'price': 3519.07, 'merchantId': 23326}, {'prodId': 13570649, 'date': '2025-11-29', 'price': 3597.16, 'merchantId': 23326}, {'prodId': 13570649, 'date': '2025-11-30', 'price': 3597.16, 'merchantId': 23326}, {'prodId': 13570649, 'date': '2025-12-01', 'price': 3597.11, 'merchantId': 23326}, {'prodId': 13570649, 'date': '2025-12-02', 'price': 3599.06, 'merchantId': 20612}, {'prodId': 13570649, 'date': '2025-12-03', 'price': 3599.06, 'merchantId': 20612}, {'prodId': 13570649, 'date': '2025-12-04', 'price': 3596.21, 'merchantId': 23326}, {'prodId': 13570649, 'date': '2025-12-05', 'price': 3596.21, 'merchantId': 23326}, {'prodId': 13570649, 'date': '2025-12-06', 'price': 3596.21, 'merchantId': 245}, {'prodId': 13570649, 'date': '2025-12-07', 'price': 3596.21, 'merchantId': 245}, {'prodId': 13570649, 'date': '2025-12-08', 'price': 3596.21, 'merchantId': 245}, {'prodId': 13570649, 'date': '2025-12-09', 'price': 3599.06, 'merchantId': 20612}, {'prodId': 13570649, 'date': '2025-12-10', 'price': 3599.06, 'merchantId': 20612}, {'prodId': 13570649, 'date': '2025-12-11', 'price': 3599.06, 'merchantId': 20612}, {'prodId': 13570649, 'date': '2025-12-12', 'price': 3599.06, 'merchantId': 20612}, {'prodId': 13570649, 'date': '2025-12-13', 'price': 3599.06, 'merchantId': 20612}, {'prodId': 13570649, 'date': '2025-12-14', 'price': 3599.06, 'merchantId': 20612}, {'prodId': 13570649, 'date': '2025-12-15', 'price': 3599.06, 'merchantId': 20612}, {'prodId': 13570649, 'date': '2025-12-16', 'price': 3599.06, 'merchantId': 20612}, {'prodId': 13570649, 'date': '2025-12-17', 'price': 3599.06, 'merchantId': 20612}, {'prodId': 13570649, 'date': '2025-12-18', 'price': 3599.06, 'merchantId': 20612}, {'prodId': 13570649, 'date': '2025-12-19', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2025-12-20', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2025-12-21', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2025-12-22', 'price': 3779.05, 'merchantId': 21628}, {'prodId': 13570649, 'date': '2025-12-23', 'price': 3799.0, 'merchantId': 21628}, {'prodId': 13570649, 'date': '2025-12-24', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2025-12-25', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2025-12-26', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2025-12-27', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2025-12-28', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2025-12-29', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2025-12-30', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2025-12-31', 'price': 3779.05, 'merchantId': 21628}, {'prodId': 13570649, 'date': '2026-01-01', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-01-02', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-01-03', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-01-04', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-01-05', 'price': 3499.0, 'merchantId': 2}, {'prodId': 13570649, 'date': '2026-01-06', 'price': 3499.0, 'merchantId': 23326}, {'prodId': 13570649, 'date': '2026-01-07', 'price': 3499.0, 'merchantId': 23326}, {'prodId': 13570649, 'date': '2026-01-08', 'price': 3499.0, 'merchantId': 2}, {'prodId': 13570649, 'date': '2026-01-09', 'price': 3497.0, 'merchantId': 2}, {'prodId': 13570649, 'date': '2026-01-10', 'price': 3497.0, 'merchantId': 2}, {'prodId': 13570649, 'date': '2026-01-11', 'price': 3497.0, 'merchantId': 2}, {'prodId': 13570649, 'date': '2026-01-12', 'price': 3497.0, 'merchantId': 2}, {'prodId': 13570649, 'date': '2026-01-13', 'price': 3497.0, 'merchantId': 2}, {'prodId': 13570649, 'date': '2026-01-14', 'price': 3496.9, 'merchantId': 2}, {'prodId': 13570649, 'date': '2026-01-15', 'price': 3496.9, 'merchantId': 2}, {'prodId': 13570649, 'date': '2026-01-16', 'price': 3496.9, 'merchantId': 245}, {'prodId': 13570649, 'date': '2026-01-17', 'price': 3599.0, 'merchantId': 23326}, {'prodId': 13570649, 'date': '2026-01-18', 'price': 3599.0, 'merchantId': 23326}, {'prodId': 13570649, 'date': '2026-01-19', 'price': 3599.0, 'merchantId': 23326}, {'prodId': 13570649, 'date': '2026-01-20', 'price': 3599.0, 'merchantId': 245}, {'prodId': 13570649, 'date': '2026-01-21', 'price': 3698.0, 'merchantId': 245}, {'prodId': 13570649, 'date': '2026-01-22', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-01-23', 'price': 3482.91, 'merchantId': 20609}, {'prodId': 13570649, 'date': '2026-01-24', 'price': 3482.91, 'merchantId': 20609}, {'prodId': 13570649, 'date': '2026-01-25', 'price': 3482.91, 'merchantId': 20609}, {'prodId': 13570649, 'date': '2026-01-26', 'price': 3482.91, 'merchantId': 20609}, {'prodId': 13570649, 'date': '2026-01-27', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-01-28', 'price': 3703.01, 'merchantId': 245}, {'prodId': 13570649, 'date': '2026-01-29', 'price': 3703.01, 'merchantId': 245}, {'prodId': 13570649, 'date': '2026-01-30', 'price': 3482.91, 'merchantId': 20583}, {'prodId': 13570649, 'date': '2026-01-31', 'price': 3482.91, 'merchantId': 20583}, {'prodId': 13570649, 'date': '2026-02-01', 'price': 3702.15, 'merchantId': 245}, {'prodId': 13570649, 'date': '2026-02-02', 'price': 3482.91, 'merchantId': 20583}, {'prodId': 13570649, 'date': '2026-02-03', 'price': 3702.15, 'merchantId': 245}, {'prodId': 13570649, 'date': '2026-02-04', 'price': 3482.91, 'merchantId': 20612}, {'prodId': 13570649, 'date': '2026-02-05', 'price': 3758.4700000000003, 'merchantId': 1582}, {'prodId': 13570649, 'date': '2026-02-06', 'price': 3758.4700000000003, 'merchantId': 1582}, {'prodId': 13570649, 'date': '2026-02-07', 'price': 3758.4700000000003, 'merchantId': 1582}, {'prodId': 13570649, 'date': '2026-02-08', 'price': 3758.4700000000003, 'merchantId': 1582}, {'prodId': 13570649, 'date': '2026-02-09', 'price': 3758.4700000000003, 'merchantId': 1582}, {'prodId': 13570649, 'date': '2026-02-10', 'price': 3758.4700000000003, 'merchantId': 1582}, {'prodId': 13570649, 'date': '2026-02-11', 'price': 3758.4700000000003, 'merchantId': 1582}, {'prodId': 13570649, 'date': '2026-02-12', 'price': 3758.47, 'merchantId': 1582}, {'prodId': 13570649, 'date': '2026-02-13', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-02-14', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-02-15', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-02-16', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-02-17', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-02-18', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-02-19', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-02-20', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-02-21', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-02-22', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-02-23', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-02-24', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-02-25', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-02-26', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-02-27', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-02-28', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-03-01', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-03-02', 'price': 3599.1, 'merchantId': 22902}, {'prodId': 13570649, 'date': '2026-03-03', 'price': 3599.1, 'merchantId': 22902}, {'prodId': 13570649, 'date': '2026-03-04', 'price': 3599.1, 'merchantId': 22902}, {'prodId': 13570649, 'date': '2026-03-05', 'price': 3599.1, 'merchantId': 22902}, {'prodId': 13570649, 'date': '2026-03-06', 'price': 3599.1, 'merchantId': 22902}, {'prodId': 13570649, 'date': '2026-03-07', 'price': 3599.1, 'merchantId': 22902}, {'prodId': 13570649, 'date': '2026-03-08', 'price': 3599.1, 'merchantId': 22902}, {'prodId': 13570649, 'date': '2026-03-09', 'price': 3599.1, 'merchantId': 22902}, {'prodId': 13570649, 'date': '2026-03-10', 'price': 3599.1, 'merchantId': 22902}, {'prodId': 13570649, 'date': '2026-03-11', 'price': 3599.1, 'merchantId': 22902}, {'prodId': 13570649, 'date': '2026-03-12', 'price': 3599.1, 'merchantId': 22902}, {'prodId': 13570649, 'date': '2026-03-13', 'price': 3599.1, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-03-14', 'price': 3599.1, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-03-15', 'price': 3599.1, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-03-16', 'price': 3599.1, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-03-17', 'price': 3599.1, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-03-18', 'price': 3724.09, 'merchantId': 20583}, {'prodId': 13570649, 'date': '2026-03-19', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-03-20', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-03-21', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-03-22', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-03-23', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-03-24', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-03-25', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-03-26', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-03-27', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-03-28', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-03-29', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-03-30', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-03-31', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-04-01', 'price': 3799.0, 'merchantId': 22905}, {'prodId': 13570649, 'date': '2026-04-02', 'price': 2998.78, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-04-03', 'price': 3896.9, 'merchantId': 2}, {'prodId': 13570649, 'date': '2026-04-04', 'price': 2998.78, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-04-05', 'price': 3820.5, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-04-06', 'price': 3820.5, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-04-07', 'price': 3896.9, 'merchantId': 2}, {'prodId': 13570649, 'date': '2026-04-08', 'price': 3896.9, 'merchantId': 2}, {'prodId': 13570649, 'date': '2026-04-09', 'price': 3898.8, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-04-10', 'price': 3898.8, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-04-11', 'price': 3898.8, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-04-12', 'price': 3898.8, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-04-13', 'price': 3898.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-04-14', 'price': 3898.79, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-04-15', 'price': 3898.79, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-04-16', 'price': 3779.99, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-04-17', 'price': 3898.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-04-18', 'price': 3898.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-04-19', 'price': 3898.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-04-20', 'price': 3898.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-04-21', 'price': 3898.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-04-22', 'price': 3898.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-04-23', 'price': 3898.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-04-24', 'price': 3898.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-04-25', 'price': 3899.0, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-04-26', 'price': 3899.0, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-04-27', 'price': 3899.0, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-04-28', 'price': 3899.0, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-04-29', 'price': 3899.0, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-04-30', 'price': 3898.99, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-05-01', 'price': 3898.99, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-05-02', 'price': 3898.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-05-03', 'price': 3898.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-05-04', 'price': 3898.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-05-05', 'price': 3898.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-05-06', 'price': 3898.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-05-07', 'price': 3898.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-05-08', 'price': 3898.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-05-09', 'price': 3898.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-05-10', 'price': 3898.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-05-11', 'price': 3898.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-05-12', 'price': 3899.0, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-05-13', 'price': 3899.0, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-05-14', 'price': 3899.0, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-05-15', 'price': 3899.0, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-05-16', 'price': 3898.99, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-05-17', 'price': 3889.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-05-18', 'price': 3898.99, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-05-19', 'price': 3898.99, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-05-20', 'price': 3898.99, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-05-21', 'price': 3599.0, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-05-22', 'price': 3599.0, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-05-23', 'price': 3599.0, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-05-24', 'price': 3599.0, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-05-25', 'price': 3599.0, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-05-26', 'price': 3899.0, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-05-27', 'price': 3899.0, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-05-28', 'price': 3899.0, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-05-29', 'price': 3899.0, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-05-30', 'price': 3899.0, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-05-31', 'price': 3899.0, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-06-01', 'price': 3826.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-06-02', 'price': 3826.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-06-03', 'price': 3898.99, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-06-04', 'price': 3826.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-06-05', 'price': 3826.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-06-06', 'price': 3826.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-06-07', 'price': 3826.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-06-08', 'price': 3826.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-06-09', 'price': 3826.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-06-10', 'price': 3826.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-06-11', 'price': 3826.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-06-12', 'price': 3826.8, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-06-13', 'price': 3899.0, 'merchantId': 22902}, {'prodId': 13570649, 'date': '2026-06-14', 'price': 3899.0, 'merchantId': 22902}, {'prodId': 13570649, 'date': '2026-06-15', 'price': 3898.99, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-06-16', 'price': 3898.99, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-06-17', 'price': 4049.0, 'merchantId': 20583}, {'prodId': 13570649, 'date': '2026-06-18', 'price': 3898.99, 'merchantId': 1582}, {'prodId': 13570649, 'date': '2026-06-19', 'price': 3795.24, 'merchantId': 23326}, {'prodId': 13570649, 'date': '2026-06-20', 'price': 3680.67, 'merchantId': 245}, {'prodId': 13570649, 'date': '2026-06-21', 'price': 3680.67, 'merchantId': 245}, {'prodId': 13570649, 'date': '2026-06-22', 'price': 3680.67, 'merchantId': 245}, {'prodId': 13570649, 'date': '2026-06-23', 'price': 3678.21, 'merchantId': 245}, {'prodId': 13570649, 'date': '2026-06-24', 'price': 3650.81, 'merchantId': 245}, {'prodId': 13570649, 'date': '2026-06-25', 'price': 3650.81, 'merchantId': 245}, {'prodId': 13570649, 'date': '2026-06-26', 'price': 3650.61, 'merchantId': 245}, {'prodId': 13570649, 'date': '2026-06-27', 'price': 3649.77, 'merchantId': 245}, {'prodId': 13570649, 'date': '2026-06-28', 'price': 3649.77, 'merchantId': 245}, {'prodId': 13570649, 'date': '2026-06-29', 'price': 3649.77, 'merchantId': 245}, {'prodId': 13570649, 'date': '2026-06-30', 'price': 3648.91, 'merchantId': 245}, {'prodId': 13570649, 'date': '2026-07-01', 'price': 3648.81, 'merchantId': 245}, {'prodId': 13570649, 'date': '2026-07-02', 'price': 3648.81, 'merchantId': 245}, {'prodId': 13570649, 'date': '2026-07-03', 'price': 3496.5, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-07-04', 'price': 3496.5, 'merchantId': 16108}, {'prodId': 13570649, 'date': '2026-07-05', 'price': 3496.5, 'merchantId': 22902}, {'prodId': 13570649, 'date': '2026-07-06', 'price': 3496.5, 'merchantId': 9385}, {'prodId': 13570649, 'date': '2026-07-07', 'price': 3646.98, 'merchantId': 9385}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13993374, 'date': '2025-07-07', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-07-08', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-07-09', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-07-10', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-07-11', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-07-12', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-07-13', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-07-14', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-07-15', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-07-16', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-07-17', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-07-18', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-07-19', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-07-20', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-07-21', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-07-22', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-07-23', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-07-24', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-07-25', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-07-26', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-07-27', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-07-28', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-07-29', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-07-30', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-07-31', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-01', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-02', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-03', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-04', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-05', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-06', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-07', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-08', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-09', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-10', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-11', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-12', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-13', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-14', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-15', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-16', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-17', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-18', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-19', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-20', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-21', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-22', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-23', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-24', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-25', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-26', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-27', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-28', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-29', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-30', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-08-31', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-01', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-02', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-03', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-04', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-05', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-06', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-07', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-08', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-09', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-10', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-11', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-12', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-13', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-14', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-15', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-16', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-17', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-18', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-19', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-20', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-21', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-22', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-23', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-24', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-25', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-26', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-27', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-28', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-29', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-09-30', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-10-01', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-10-02', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-10-03', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-10-04', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-10-05', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-10-06', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-10-07', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-10-08', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-10-09', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-10-10', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-10-11', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-10-12', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-10-13', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-10-14', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-10-15', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-10-16', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-10-17', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-10-18', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-10-19', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993374, 'date': '2025-10-20', 'price': 1781.1, 'merchantId': 23254}, {'prodId': 13993381, 'date': '2025-10-21', 'price': 1688.0, 'merchantId': 34}, {'prodId': 13993381, 'date': '2025-10-22', 'price': 1678.0, 'merchantId': 34}, {'prodId': 13993381, 'date': '2025-10-23', 'price': 1677.0, 'merchantId': 34}, {'prodId': 13993381, 'date': '2025-10-24', 'price': 1677.0, 'merchantId': 34}, {'prodId': 13993381, 'date': '2025-10-25', 'price': 1677.0, 'merchantId': 34}, {'prodId': 13993381, 'date': '2025-10-26', 'price': 1677.0, 'merchantId': 34}, {'prodId': 13993381, 'date': '2025-10-27', 'price': 1675.0, 'merchantId': 34}, {'prodId': 13993381, 'date': '2025-10-28', 'price': 1673.0, 'merchantId': 34}, {'prodId': 13993381, 'date': '2025-10-29', 'price': 1673.0, 'merchantId': 34}, {'prodId': 13993381, 'date': '2025-10-30', 'price': 1673.0, 'merchantId': 34}, {'prodId': 13993381, 'date': '2025-10-31', 'price': 1673.0, 'merchantId': 34}, {'prodId': 13993381, 'date': '2025-11-01', 'price': 1673.0, 'merchantId': 34}, {'prodId': 13993381, 'date': '2025-11-02', 'price': 1673.0, 'merchantId': 34}, {'prodId': 13993381, 'date': '2025-11-03', 'price': 1618.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2025-11-04', 'price': 1598.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2025-11-05', 'price': 1595.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2025-11-06', 'price': 1595.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2025-11-07', 'price': 1595.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2025-11-08', 'price': 1594.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2025-11-09', 'price': 1594.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2025-11-10', 'price': 1594.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2025-11-11', 'price': 1589.0, 'merchantId': 34}, {'prodId': 13993381, 'date': '2025-11-12', 'price': 1589.0, 'merchantId': 34}, {'prodId': 13993381, 'date': '2025-11-13', 'price': 1588.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2025-11-14', 'price': 1588.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2025-11-15', 'price': 1588.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2025-11-16', 'price': 1588.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2025-11-17', 'price': 1587.92, 'merchantId': 9385}, {'prodId': 13993381, 'date': '2025-11-18', 'price': 1587.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2025-11-19', 'price': 1586.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2025-11-20', 'price': 1585.98, 'merchantId': 9385}, {'prodId': 13993381, 'date': '2025-11-21', 'price': 1529.11, 'merchantId': 9385}, {'prodId': 13993381, 'date': '2025-11-22', 'price': 1529.11, 'merchantId': 9385}, {'prodId': 13993381, 'date': '2025-11-23', 'price': 1529.11, 'merchantId': 9385}, {'prodId': 13993381, 'date': '2025-11-24', 'price': 1542.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2025-11-25', 'price': 1542.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2025-11-26', 'price': 1540.9, 'merchantId': 2}, {'prodId': 13993381, 'date': '2025-11-27', 'price': 1539.0, 'merchantId': 22902}, {'prodId': 13993381, 'date': '2025-11-28', 'price': 1506.66, 'merchantId': 23326}, {'prodId': 13993381, 'date': '2025-11-29', 'price': 1518.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2025-11-30', 'price': 1518.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2025-12-01', 'price': 1518.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2025-12-02', 'price': 1518.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2025-12-03', 'price': 1518.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2025-12-04', 'price': 1518.0, 'merchantId': 23326}, {'prodId': 13993381, 'date': '2025-12-05', 'price': 1612.02, 'merchantId': 22701}, {'prodId': 13993381, 'date': '2025-12-06', 'price': 1612.02, 'merchantId': 22701}, {'prodId': 13993381, 'date': '2025-12-07', 'price': 1698.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2025-12-08', 'price': 1599.0, 'merchantId': 1582}, {'prodId': 13993381, 'date': '2025-12-09', 'price': 1612.02, 'merchantId': 22701}, {'prodId': 13993381, 'date': '2025-12-10', 'price': 719.9, 'merchantId': 1582}, {'prodId': 13993381, 'date': '2025-12-11', 'price': 1645.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2025-12-12', 'price': 1499.0, 'merchantId': 21627}, {'prodId': 13993381, 'date': '2025-12-13', 'price': 1499.0, 'merchantId': 21627}, {'prodId': 13993381, 'date': '2025-12-14', 'price': 1499.0, 'merchantId': 21627}, {'prodId': 13993381, 'date': '2025-12-15', 'price': 719.9, 'merchantId': 1582}, {'prodId': 13993381, 'date': '2025-12-16', 'price': 1499.0, 'merchantId': 21627}, {'prodId': 13993381, 'date': '2025-12-17', 'price': 1499.0, 'merchantId': 21627}, {'prodId': 13993381, 'date': '2025-12-18', 'price': 1499.0, 'merchantId': 21627}, {'prodId': 13993381, 'date': '2025-12-19', 'price': 1499.0, 'merchantId': 21627}, {'prodId': 13993381, 'date': '2025-12-20', 'price': 1499.0, 'merchantId': 21627}, {'prodId': 13993381, 'date': '2025-12-21', 'price': 1499.0, 'merchantId': 21627}, {'prodId': 13993381, 'date': '2025-12-22', 'price': 1499.0, 'merchantId': 21627}, {'prodId': 13993381, 'date': '2025-12-23', 'price': 1499.0, 'merchantId': 21627}, {'prodId': 13993381, 'date': '2025-12-24', 'price': 1499.0, 'merchantId': 21627}, {'prodId': 13993381, 'date': '2025-12-25', 'price': 1499.0, 'merchantId': 21627}, {'prodId': 13993381, 'date': '2025-12-26', 'price': 1499.0, 'merchantId': 21627}, {'prodId': 13993381, 'date': '2025-12-27', 'price': 1499.0, 'merchantId': 21627}, {'prodId': 13993381, 'date': '2025-12-28', 'price': 1499.0, 'merchantId': 21627}, {'prodId': 13993381, 'date': '2025-12-29', 'price': 1499.0, 'merchantId': 21627}, {'prodId': 13993381, 'date': '2025-12-30', 'price': 1499.0, 'merchantId': 21628}, {'prodId': 13993381, 'date': '2025-12-31', 'price': 1499.0, 'merchantId': 21628}, {'prodId': 13993381, 'date': '2026-01-01', 'price': 1519.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2026-01-02', 'price': 1519.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2026-01-03', 'price': 1569.64, 'merchantId': 23326}, {'prodId': 13993381, 'date': '2026-01-04', 'price': 1569.64, 'merchantId': 23326}, {'prodId': 13993381, 'date': '2026-01-05', 'price': 1649.9, 'merchantId': 1582}, {'prodId': 13993381, 'date': '2026-01-06', 'price': 1649.9, 'merchantId': 1582}, {'prodId': 13993381, 'date': '2026-01-07', 'price': 1698.0, 'merchantId': 23326}, {'prodId': 13993381, 'date': '2026-01-08', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-01-09', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-01-10', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-01-11', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-01-12', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-01-13', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-01-14', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-01-15', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-01-16', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-01-17', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-01-18', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-01-19', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-01-20', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-01-21', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-01-22', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-01-23', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-01-24', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-01-25', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-01-26', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-01-27', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-01-28', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-01-29', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-01-30', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-01-31', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-02-01', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-02-02', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-02-03', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-02-04', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-02-05', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-02-06', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-02-07', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-02-08', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-02-09', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-02-10', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-02-11', 'price': 1652.13, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-02-12', 'price': 1652.13, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-02-13', 'price': 1652.13, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-02-14', 'price': 1652.13, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-02-15', 'price': 1652.13, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-02-16', 'price': 1652.13, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-02-17', 'price': 1652.13, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-02-18', 'price': 1652.13, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-02-19', 'price': 1671.12, 'merchantId': 20609}, {'prodId': 13993381, 'date': '2026-02-20', 'price': 1652.13, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-02-21', 'price': 1652.13, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-02-22', 'price': 1652.13, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-02-23', 'price': 1652.13, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-02-24', 'price': 1652.13, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-02-25', 'price': 1652.13, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-02-26', 'price': 1652.13, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-02-27', 'price': 1649.9, 'merchantId': 9385}, {'prodId': 13993381, 'date': '2026-02-28', 'price': 1539.0, 'merchantId': 22902}, {'prodId': 13993381, 'date': '2026-03-01', 'price': 1539.0, 'merchantId': 22902}, {'prodId': 13993381, 'date': '2026-03-02', 'price': 1523.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2026-03-03', 'price': 1522.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2026-03-04', 'price': 1522.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2026-03-05', 'price': 1521.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2026-03-06', 'price': 1520.9, 'merchantId': 2}, {'prodId': 13993381, 'date': '2026-03-07', 'price': 1520.9, 'merchantId': 2}, {'prodId': 13993381, 'date': '2026-03-08', 'price': 1520.9, 'merchantId': 2}, {'prodId': 13993381, 'date': '2026-03-09', 'price': 1519.9, 'merchantId': 2}, {'prodId': 13993381, 'date': '2026-03-10', 'price': 1519.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2026-03-11', 'price': 1510.0, 'merchantId': 9385}, {'prodId': 13993381, 'date': '2026-03-12', 'price': 1518.9, 'merchantId': 2}, {'prodId': 13993381, 'date': '2026-03-13', 'price': 1469.01, 'merchantId': 22902}, {'prodId': 13993381, 'date': '2026-03-14', 'price': 1469.01, 'merchantId': 22902}, {'prodId': 13993381, 'date': '2026-03-15', 'price': 1469.01, 'merchantId': 22902}, {'prodId': 13993381, 'date': '2026-03-16', 'price': 1469.01, 'merchantId': 22902}, {'prodId': 13993381, 'date': '2026-03-17', 'price': 1468.9, 'merchantId': 2}, {'prodId': 13993381, 'date': '2026-03-18', 'price': 1468.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2026-03-19', 'price': 1467.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2026-03-20', 'price': 1466.9, 'merchantId': 2}, {'prodId': 13993381, 'date': '2026-03-21', 'price': 1466.9, 'merchantId': 2}, {'prodId': 13993381, 'date': '2026-03-22', 'price': 1466.9, 'merchantId': 2}, {'prodId': 13993381, 'date': '2026-03-23', 'price': 1466.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2026-03-24', 'price': 1576.17, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-03-25', 'price': 1576.17, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-03-26', 'price': 1576.17, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-03-27', 'price': 1538.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2026-03-28', 'price': 1538.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2026-03-29', 'price': 1538.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2026-03-30', 'price': 1538.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2026-03-31', 'price': 1499.0, 'merchantId': 22902}, {'prodId': 13993381, 'date': '2026-04-01', 'price': 1498.89, 'merchantId': 9385}, {'prodId': 13993381, 'date': '2026-04-02', 'price': 1488.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2026-04-03', 'price': 1487.99, 'merchantId': 9385}, {'prodId': 13993381, 'date': '2026-04-04', 'price': 1439.1, 'merchantId': 9385}, {'prodId': 13993381, 'date': '2026-04-05', 'price': 1439.1, 'merchantId': 9385}, {'prodId': 13993381, 'date': '2026-04-06', 'price': 1499.0, 'merchantId': 22902}, {'prodId': 13993381, 'date': '2026-04-07', 'price': 1499.0, 'merchantId': 22902}, {'prodId': 13993381, 'date': '2026-04-08', 'price': 1582.28, 'merchantId': 2584}, {'prodId': 13993381, 'date': '2026-04-09', 'price': 1661.55, 'merchantId': 23326}, {'prodId': 13993381, 'date': '2026-04-10', 'price': 1652.13, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-04-11', 'price': 1652.13, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-04-12', 'price': 1652.13, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-04-13', 'price': 1652.13, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-04-14', 'price': 1652.13, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-04-15', 'price': 1652.13, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-04-16', 'price': 1652.13, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-04-17', 'price': 1652.13, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-04-18', 'price': 1599.0, 'merchantId': 1582}, {'prodId': 13993381, 'date': '2026-04-19', 'price': 1476.07, 'merchantId': 9385}, {'prodId': 13993381, 'date': '2026-04-20', 'price': 1599.0, 'merchantId': 1582}, {'prodId': 13993381, 'date': '2026-04-21', 'price': 1599.0, 'merchantId': 1582}, {'prodId': 13993381, 'date': '2026-04-22', 'price': 1599.0, 'merchantId': 1582}, {'prodId': 13993381, 'date': '2026-04-23', 'price': 1647.8600000000001, 'merchantId': 9385}, {'prodId': 13993381, 'date': '2026-04-24', 'price': 1599.2, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-04-25', 'price': 1599.2, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-04-26', 'price': 1599.2, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-04-27', 'price': 1599.2, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-04-28', 'price': 1599.2, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-04-29', 'price': 1599.2, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-04-30', 'price': 1599.2, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-05-01', 'price': 1599.2, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-05-02', 'price': 1666.3, 'merchantId': 20612}, {'prodId': 13993381, 'date': '2026-05-03', 'price': 1666.3, 'merchantId': 20612}, {'prodId': 13993381, 'date': '2026-05-04', 'price': 1367.92, 'merchantId': 9385}, {'prodId': 13993381, 'date': '2026-05-05', 'price': 1647.0, 'merchantId': 9385}, {'prodId': 13993381, 'date': '2026-05-06', 'price': 1599.0, 'merchantId': 1582}, {'prodId': 13993381, 'date': '2026-05-07', 'price': 1599.0, 'merchantId': 1582}, {'prodId': 13993381, 'date': '2026-05-08', 'price': 1599.2, 'merchantId': 20609}, {'prodId': 13993381, 'date': '2026-05-09', 'price': 1367.92, 'merchantId': 9385}, {'prodId': 13993381, 'date': '2026-05-10', 'price': 1599.2, 'merchantId': 20609}, {'prodId': 13993381, 'date': '2026-05-11', 'price': 1599.2, 'merchantId': 20609}, {'prodId': 13993381, 'date': '2026-05-12', 'price': 1599.2, 'merchantId': 20609}, {'prodId': 13993381, 'date': '2026-05-13', 'price': 1599.2, 'merchantId': 20609}, {'prodId': 13993381, 'date': '2026-05-14', 'price': 1599.2, 'merchantId': 20609}, {'prodId': 13993381, 'date': '2026-05-15', 'price': 1583.02, 'merchantId': 23326}, {'prodId': 13993381, 'date': '2026-05-16', 'price': 1583.02, 'merchantId': 23326}, {'prodId': 13993381, 'date': '2026-05-17', 'price': 1583.02, 'merchantId': 23326}, {'prodId': 13993381, 'date': '2026-05-18', 'price': 1583.02, 'merchantId': 23326}, {'prodId': 13993381, 'date': '2026-05-19', 'price': 1583.02, 'merchantId': 23326}, {'prodId': 13993381, 'date': '2026-05-20', 'price': 1583.02, 'merchantId': 23326}, {'prodId': 13993381, 'date': '2026-05-21', 'price': 1599.2, 'merchantId': 20612}, {'prodId': 13993381, 'date': '2026-05-22', 'price': 1564.2, 'merchantId': 34}, {'prodId': 13993381, 'date': '2026-05-23', 'price': 1651.09, 'merchantId': 9385}, {'prodId': 13993381, 'date': '2026-05-24', 'price': 1699.38, 'merchantId': 23326}, {'prodId': 13993381, 'date': '2026-05-25', 'price': 1699.38, 'merchantId': 23326}, {'prodId': 13993381, 'date': '2026-05-26', 'price': 1699.38, 'merchantId': 23326}, {'prodId': 13993381, 'date': '2026-05-27', 'price': 1699.38, 'merchantId': 23326}, {'prodId': 13993381, 'date': '2026-05-28', 'price': 1681.78, 'merchantId': 23326}, {'prodId': 13993381, 'date': '2026-05-29', 'price': 1681.78, 'merchantId': 23326}, {'prodId': 13993381, 'date': '2026-05-30', 'price': 1739.13, 'merchantId': 20612}, {'prodId': 13993381, 'date': '2026-05-31', 'price': 1713.3400000000001, 'merchantId': 9385}, {'prodId': 13993381, 'date': '2026-06-01', 'price': 1716.6100000000001, 'merchantId': 9385}, {'prodId': 13993381, 'date': '2026-06-02', 'price': 1679.0, 'merchantId': 9385}, {'prodId': 13993381, 'date': '2026-06-03', 'price': 1599.2, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-06-04', 'price': 1599.2, 'merchantId': 22905}, {'prodId': 13993381, 'date': '2026-06-05', 'price': 1599.2, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-06-06', 'price': 1599.2, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-06-07', 'price': 1599.2, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-06-08', 'price': 1599.2, 'merchantId': 20583}, {'prodId': 13993381, 'date': '2026-06-09', 'price': 1636.3, 'merchantId': 23326}, {'prodId': 13993381, 'date': '2026-06-10', 'price': 1634.75, 'merchantId': 245}, {'prodId': 13993381, 'date': '2026-06-11', 'price': 1634.75, 'merchantId': 245}, {'prodId': 13993381, 'date': '2026-06-12', 'price': 1540.94, 'merchantId': 245}, {'prodId': 13993381, 'date': '2026-06-13', 'price': 1540.94, 'merchantId': 245}, {'prodId': 13993381, 'date': '2026-06-14', 'price': 1540.94, 'merchantId': 245}, {'prodId': 13993381, 'date': '2026-06-15', 'price': 1540.94, 'merchantId': 245}, {'prodId': 13993381, 'date': '2026-06-16', 'price': 1633.78, 'merchantId': 245}, {'prodId': 13993381, 'date': '2026-06-17', 'price': 1587.37, 'merchantId': 245}, {'prodId': 13993381, 'date': '2026-06-18', 'price': 1539.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2026-06-19', 'price': 1462.05, 'merchantId': 245}, {'prodId': 13993381, 'date': '2026-06-20', 'price': 1459.37, 'merchantId': 245}, {'prodId': 13993381, 'date': '2026-06-21', 'price': 1496.35, 'merchantId': 245}, {'prodId': 13993381, 'date': '2026-06-22', 'price': 1496.35, 'merchantId': 245}, {'prodId': 13993381, 'date': '2026-06-23', 'price': 1474.0, 'merchantId': 9385}, {'prodId': 13993381, 'date': '2026-06-24', 'price': 1474.0, 'merchantId': 9385}, {'prodId': 13993381, 'date': '2026-06-25', 'price': 1490.0, 'merchantId': 2}, {'prodId': 13993381, 'date': '2026-06-26', 'price': 1412.92, 'merchantId': 245}, {'prodId': 13993381, 'date': '2026-06-27', 'price': 1412.92, 'merchantId': 245}, {'prodId': 13993381, 'date': '2026-06-28', 'price': 1412.92, 'merchantId': 245}, {'prodId': 13993381, 'date': '2026-06-29', 'price': 1412.92, 'merchantId': 245}, {'prodId': 13993381, 'date': '2026-06-30', 'price': 1459.18, 'merchantId': 245}, {'prodId': 13993381, 'date': '2026-07-01', 'price': 1538.79, 'merchantId': 2}, {'prodId': 13993381, 'date': '2026-07-02', 'price': 1504.6, 'merchantId': 245}, {'prodId': 13993381, 'date': '2026-07-03', 'price': 1536.57, 'merchantId': 245}, {'prodId': 13993381, 'date': '2026-07-04', 'price': 1536.57, 'merchantId': 245}, {'prodId': 13993381, 'date': '2026-07-05', 'price': 1536.57, 'merchantId': 245}, {'prodId': 13993381, 'date': '2026-07-06', 'price': 1529.1, 'merchantId': 16108}, {'prodId': 13993381, 'date': '2026-07-07', 'price': 1501.18, 'merchantId': 23326}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13991985, 'date': '2025-07-07', 'price': 1839.9, 'merchantId': 20583}, {'prodId': 13991985, 'date': '2025-07-08', 'price': 1848.6, 'merchantId': 34}, {'prodId': 13991985, 'date': '2025-07-09', 'price': 1835.91, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2025-07-10', 'price': 1834.0, 'merchantId': 34}, {'prodId': 13991985, 'date': '2025-07-11', 'price': 949.0, 'merchantId': 10763}, {'prodId': 13991985, 'date': '2025-07-12', 'price': 1789.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-07-13', 'price': 1789.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-07-14', 'price': 1789.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-07-15', 'price': 1789.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-07-16', 'price': 1789.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-07-17', 'price': 1789.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-07-18', 'price': 1789.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-07-19', 'price': 1789.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-07-20', 'price': 1789.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-07-21', 'price': 1789.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-07-22', 'price': 1789.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-07-23', 'price': 1789.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-07-24', 'price': 1789.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-07-25', 'price': 1789.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-07-26', 'price': 1789.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-07-27', 'price': 1789.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-07-28', 'price': 1789.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-07-29', 'price': 1828.8, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2025-07-30', 'price': 1827.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-07-31', 'price': 1799.0, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2025-08-01', 'price': 1759.12, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-08-02', 'price': 1759.12, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-08-03', 'price': 1759.12, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-08-04', 'price': 1759.12, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-08-05', 'price': 1759.12, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-08-06', 'price': 1759.12, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-08-07', 'price': 1759.12, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-08-08', 'price': 1759.12, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-08-09', 'price': 1759.12, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-08-10', 'price': 1791.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-08-11', 'price': 1759.12, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-08-12', 'price': 1769.9, 'merchantId': 5}, {'prodId': 13991985, 'date': '2025-08-13', 'price': 1710.04, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2025-08-14', 'price': 1710.04, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2025-08-15', 'price': 1710.04, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2025-08-16', 'price': 1710.04, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2025-08-17', 'price': 1710.04, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2025-08-18', 'price': 1710.04, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2025-08-19', 'price': 1710.05, 'merchantId': 9385}, {'prodId': 13991985, 'date': '2025-08-20', 'price': 1799.1, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-08-21', 'price': 1799.1, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-08-22', 'price': 1759.12, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-08-23', 'price': 1759.12, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-08-24', 'price': 1799.1, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-08-25', 'price': 1799.1, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-08-26', 'price': 1799.1, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-08-27', 'price': 1699.0, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2025-08-28', 'price': 1699.0, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2025-08-29', 'price': 1699.0, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2025-08-30', 'price': 1699.0, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2025-08-31', 'price': 1699.0, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2025-09-01', 'price': 1699.0, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2025-09-02', 'price': 1799.0, 'merchantId': 20583}, {'prodId': 13991985, 'date': '2025-09-03', 'price': 1799.0, 'merchantId': 20583}, {'prodId': 13991985, 'date': '2025-09-04', 'price': 1799.0, 'merchantId': 20583}, {'prodId': 13991985, 'date': '2025-09-05', 'price': 1798.2, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-09-06', 'price': 1798.2, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-09-07', 'price': 1798.2, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-09-08', 'price': 1798.2, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-09-09', 'price': 1698.3, 'merchantId': 34}, {'prodId': 13991985, 'date': '2025-09-10', 'price': 1693.86, 'merchantId': 5}, {'prodId': 13991985, 'date': '2025-09-11', 'price': 1697.45, 'merchantId': 34}, {'prodId': 13991985, 'date': '2025-09-12', 'price': 1697.45, 'merchantId': 34}, {'prodId': 13991985, 'date': '2025-09-13', 'price': 1798.2, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-09-14', 'price': 1754.1, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2025-09-15', 'price': 1754.1, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2025-09-16', 'price': 1799.1, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-09-17', 'price': 1798.9, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-09-18', 'price': 1798.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-09-19', 'price': 1798.9, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-09-20', 'price': 1798.9, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-09-21', 'price': 1798.9, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-09-22', 'price': 1797.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-09-23', 'price': 1797.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-09-24', 'price': 1789.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-09-25', 'price': 1789.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-09-26', 'price': 1789.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-09-27', 'price': 1789.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-09-28', 'price': 1789.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-09-29', 'price': 1789.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-09-30', 'price': 1789.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-10-01', 'price': 1789.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-10-02', 'price': 1789.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-10-03', 'price': 1789.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-10-04', 'price': 1789.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-10-05', 'price': 1789.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-10-06', 'price': 1788.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-10-07', 'price': 1787.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-10-08', 'price': 1787.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-10-09', 'price': 1792.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-10-10', 'price': 1792.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-10-11', 'price': 1792.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-10-12', 'price': 1792.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-10-13', 'price': 1792.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-10-14', 'price': 1792.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-10-15', 'price': 1792.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-10-16', 'price': 1792.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-10-17', 'price': 1699.0, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2025-10-18', 'price': 1649.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-10-19', 'price': 1649.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-10-20', 'price': 1649.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-10-21', 'price': 1673.37, 'merchantId': 1582}, {'prodId': 13991985, 'date': '2025-10-22', 'price': 1699.0, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2025-10-23', 'price': 1788.3, 'merchantId': 9385}, {'prodId': 13991985, 'date': '2025-10-24', 'price': 1792.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-10-25', 'price': 1792.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-10-26', 'price': 1792.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-10-27', 'price': 1792.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-10-28', 'price': 1792.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-10-29', 'price': 1792.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-10-30', 'price': 1792.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-10-31', 'price': 1792.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-11-01', 'price': 1699.0, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2025-11-02', 'price': 1699.0, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2025-11-03', 'price': 1749.0, 'merchantId': 20583}, {'prodId': 13991985, 'date': '2025-11-04', 'price': 1748.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-11-05', 'price': 1746.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-11-06', 'price': 1697.5, 'merchantId': 245}, {'prodId': 13991985, 'date': '2025-11-07', 'price': 1660.6, 'merchantId': 245}, {'prodId': 13991985, 'date': '2025-11-08', 'price': 1660.6, 'merchantId': 245}, {'prodId': 13991985, 'date': '2025-11-09', 'price': 1660.6, 'merchantId': 245}, {'prodId': 13991985, 'date': '2025-11-10', 'price': 1660.6, 'merchantId': 245}, {'prodId': 13991985, 'date': '2025-11-11', 'price': 1660.6, 'merchantId': 245}, {'prodId': 13991985, 'date': '2025-11-12', 'price': 1660.6, 'merchantId': 245}, {'prodId': 13991985, 'date': '2025-11-13', 'price': 1660.6, 'merchantId': 245}, {'prodId': 13991985, 'date': '2025-11-14', 'price': 1660.6, 'merchantId': 245}, {'prodId': 13991985, 'date': '2025-11-15', 'price': 1660.6, 'merchantId': 245}, {'prodId': 13991985, 'date': '2025-11-16', 'price': 1660.6, 'merchantId': 245}, {'prodId': 13991985, 'date': '2025-11-17', 'price': 1660.6, 'merchantId': 245}, {'prodId': 13991985, 'date': '2025-11-18', 'price': 1660.6, 'merchantId': 245}, {'prodId': 13991985, 'date': '2025-11-19', 'price': 1660.6, 'merchantId': 245}, {'prodId': 13991985, 'date': '2025-11-20', 'price': 1660.6, 'merchantId': 245}, {'prodId': 13991985, 'date': '2025-11-21', 'price': 1660.6, 'merchantId': 245}, {'prodId': 13991985, 'date': '2025-11-22', 'price': 1647.05, 'merchantId': 1582}, {'prodId': 13991985, 'date': '2025-11-23', 'price': 1647.05, 'merchantId': 9385}, {'prodId': 13991985, 'date': '2025-11-24', 'price': 1697.5, 'merchantId': 245}, {'prodId': 13991985, 'date': '2025-11-25', 'price': 1698.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2025-11-26', 'price': 1698.0, 'merchantId': 23326}, {'prodId': 13991985, 'date': '2025-11-27', 'price': 1698.0, 'merchantId': 23326}, {'prodId': 13991985, 'date': '2025-11-28', 'price': 1660.27, 'merchantId': 23326}, {'prodId': 13991985, 'date': '2025-11-29', 'price': 1698.0, 'merchantId': 23326}, {'prodId': 13991985, 'date': '2025-11-30', 'price': 1698.0, 'merchantId': 23326}, {'prodId': 13991985, 'date': '2025-12-01', 'price': 1698.0, 'merchantId': 23326}, {'prodId': 13991985, 'date': '2025-12-02', 'price': 1698.0, 'merchantId': 23326}, {'prodId': 13991985, 'date': '2025-12-03', 'price': 1698.0, 'merchantId': 23326}, {'prodId': 13991985, 'date': '2025-12-04', 'price': 1679.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-12-05', 'price': 1679.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-12-06', 'price': 1679.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-12-07', 'price': 1679.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-12-08', 'price': 1679.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-12-09', 'price': 1679.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-12-10', 'price': 1679.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2025-12-11', 'price': 1699.0, 'merchantId': 21629}, {'prodId': 13991985, 'date': '2025-12-12', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-12-13', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-12-14', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-12-15', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-12-16', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-12-17', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-12-18', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-12-19', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-12-20', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-12-21', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-12-22', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-12-23', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-12-24', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-12-25', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-12-26', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-12-27', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-12-28', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-12-29', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-12-30', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2025-12-31', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2026-01-01', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2026-01-02', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2026-01-03', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2026-01-04', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2026-01-05', 'price': 1699.0, 'merchantId': 22905}, {'prodId': 13991985, 'date': '2026-01-06', 'price': 1748.61, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-01-07', 'price': 1748.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-01-08', 'price': 1747.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-01-09', 'price': 1747.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-01-10', 'price': 1709.05, 'merchantId': 2584}, {'prodId': 13991985, 'date': '2026-01-11', 'price': 1709.05, 'merchantId': 2584}, {'prodId': 13991985, 'date': '2026-01-12', 'price': 1709.05, 'merchantId': 2584}, {'prodId': 13991985, 'date': '2026-01-13', 'price': 1746.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-01-14', 'price': 1745.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-01-15', 'price': 1745.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-01-16', 'price': 1744.9, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-01-17', 'price': 1744.9, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-01-18', 'price': 1744.9, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-01-19', 'price': 1744.9, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-01-20', 'price': 1744.9, 'merchantId': 245}, {'prodId': 13991985, 'date': '2026-01-21', 'price': 1796.0, 'merchantId': 21627}, {'prodId': 13991985, 'date': '2026-01-22', 'price': 1796.0, 'merchantId': 21627}, {'prodId': 13991985, 'date': '2026-01-23', 'price': 1796.0, 'merchantId': 21627}, {'prodId': 13991985, 'date': '2026-01-24', 'price': 1796.0, 'merchantId': 21627}, {'prodId': 13991985, 'date': '2026-01-25', 'price': 1796.0, 'merchantId': 21627}, {'prodId': 13991985, 'date': '2026-01-26', 'price': 1796.0, 'merchantId': 21627}, {'prodId': 13991985, 'date': '2026-01-27', 'price': 1796.0, 'merchantId': 21627}, {'prodId': 13991985, 'date': '2026-01-28', 'price': 1796.0, 'merchantId': 21627}, {'prodId': 13991985, 'date': '2026-01-29', 'price': 1796.0, 'merchantId': 21627}, {'prodId': 13991985, 'date': '2026-01-30', 'price': 1796.0, 'merchantId': 21627}, {'prodId': 13991985, 'date': '2026-01-31', 'price': 1796.0, 'merchantId': 21627}, {'prodId': 13991985, 'date': '2026-02-01', 'price': 1796.0, 'merchantId': 21627}, {'prodId': 13991985, 'date': '2026-02-02', 'price': 1796.0, 'merchantId': 21627}, {'prodId': 13991985, 'date': '2026-02-03', 'price': 1796.0, 'merchantId': 21627}, {'prodId': 13991985, 'date': '2026-02-04', 'price': 1796.0, 'merchantId': 21627}, {'prodId': 13991985, 'date': '2026-02-05', 'price': 1796.0, 'merchantId': 21627}, {'prodId': 13991985, 'date': '2026-02-06', 'price': 1796.0, 'merchantId': 21627}, {'prodId': 13991985, 'date': '2026-02-07', 'price': 1796.0, 'merchantId': 21627}, {'prodId': 13991985, 'date': '2026-02-08', 'price': 1796.0, 'merchantId': 21627}, {'prodId': 13991985, 'date': '2026-02-09', 'price': 1796.0, 'merchantId': 21627}, {'prodId': 13991985, 'date': '2026-02-10', 'price': 1796.0, 'merchantId': 21627}, {'prodId': 13991985, 'date': '2026-02-11', 'price': 1846.0, 'merchantId': 21629}, {'prodId': 13991985, 'date': '2026-02-12', 'price': 1846.0, 'merchantId': 21629}, {'prodId': 13991985, 'date': '2026-02-13', 'price': 1846.0, 'merchantId': 21629}, {'prodId': 13991985, 'date': '2026-02-14', 'price': 1846.0, 'merchantId': 21629}, {'prodId': 13991985, 'date': '2026-02-15', 'price': 1846.0, 'merchantId': 21629}, {'prodId': 13991985, 'date': '2026-02-16', 'price': 1846.0, 'merchantId': 21629}, {'prodId': 13991985, 'date': '2026-02-17', 'price': 1846.0, 'merchantId': 21629}, {'prodId': 13991985, 'date': '2026-02-18', 'price': 1846.0, 'merchantId': 21629}, {'prodId': 13991985, 'date': '2026-02-19', 'price': 1846.0, 'merchantId': 21629}, {'prodId': 13991985, 'date': '2026-02-20', 'price': 1846.0, 'merchantId': 21629}, {'prodId': 13991985, 'date': '2026-02-21', 'price': 1846.0, 'merchantId': 21629}, {'prodId': 13991985, 'date': '2026-02-22', 'price': 1846.0, 'merchantId': 21629}, {'prodId': 13991985, 'date': '2026-02-23', 'price': 1846.0, 'merchantId': 21629}, {'prodId': 13991985, 'date': '2026-02-24', 'price': 1799.1, 'merchantId': 16108}, {'prodId': 13991985, 'date': '2026-02-25', 'price': 1799.1, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2026-02-26', 'price': 1799.1, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2026-02-27', 'price': 1799.1, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2026-02-28', 'price': 1799.1, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2026-03-01', 'price': 1799.1, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2026-03-02', 'price': 1799.1, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2026-03-03', 'price': 1846.0, 'merchantId': 21629}, {'prodId': 13991985, 'date': '2026-03-04', 'price': 1869.9, 'merchantId': 9385}, {'prodId': 13991985, 'date': '2026-03-05', 'price': 1889.1, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2026-03-06', 'price': 1929.0, 'merchantId': 21627}, {'prodId': 13991985, 'date': '2026-03-07', 'price': 1929.0, 'merchantId': 21627}, {'prodId': 13991985, 'date': '2026-03-08', 'price': 1929.0, 'merchantId': 21627}, {'prodId': 13991985, 'date': '2026-03-09', 'price': 1929.0, 'merchantId': 21627}, {'prodId': 13991985, 'date': '2026-03-10', 'price': 1929.0, 'merchantId': 21627}, {'prodId': 13991985, 'date': '2026-03-11', 'price': 1929.0, 'merchantId': 21627}, {'prodId': 13991985, 'date': '2026-03-12', 'price': 1798.99, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2026-03-13', 'price': 1798.99, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2026-03-14', 'price': 1798.99, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2026-03-15', 'price': 1798.99, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2026-03-16', 'price': 1975.9, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-03-17', 'price': 1977.9, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2026-03-18', 'price': 1977.9, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2026-03-19', 'price': 1977.9, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2026-03-20', 'price': 1977.9, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2026-03-21', 'price': 1977.9, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2026-03-22', 'price': 1977.9, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2026-03-23', 'price': 1977.9, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2026-03-24', 'price': 1977.9, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2026-03-25', 'price': 1977.9, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2026-03-26', 'price': 1699.9, 'merchantId': 9385}, {'prodId': 13991985, 'date': '2026-03-27', 'price': 1899.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2026-03-28', 'price': 1899.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2026-03-29', 'price': 1899.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2026-03-30', 'price': 1899.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2026-03-31', 'price': 1899.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2026-04-01', 'price': 1899.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2026-04-02', 'price': 1899.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2026-04-03', 'price': 1899.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2026-04-04', 'price': 1899.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2026-04-05', 'price': 1899.0, 'merchantId': 21628}, {'prodId': 13991985, 'date': '2026-04-06', 'price': 1848.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-04-07', 'price': 1847.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-04-08', 'price': 1846.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-04-09', 'price': 1845.9, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-04-10', 'price': 1845.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-04-11', 'price': 1804.0, 'merchantId': 245}, {'prodId': 13991985, 'date': '2026-04-12', 'price': 1804.0, 'merchantId': 245}, {'prodId': 13991985, 'date': '2026-04-13', 'price': 1804.0, 'merchantId': 245}, {'prodId': 13991985, 'date': '2026-04-14', 'price': 1699.9, 'merchantId': 9385}, {'prodId': 13991985, 'date': '2026-04-15', 'price': 1759.02, 'merchantId': 245}, {'prodId': 13991985, 'date': '2026-04-16', 'price': 1758.93, 'merchantId': 245}, {'prodId': 13991985, 'date': '2026-04-17', 'price': 1758.93, 'merchantId': 245}, {'prodId': 13991985, 'date': '2026-04-18', 'price': 1798.9, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-04-19', 'price': 1798.9, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-04-20', 'price': 1798.9, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-04-21', 'price': 1798.9, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-04-22', 'price': 1798.9, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-04-23', 'price': 1798.9, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-04-24', 'price': 1698.9, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-04-25', 'price': 1698.9, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-04-26', 'price': 1698.9, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-04-27', 'price': 1698.9, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-04-28', 'price': 1698.9, 'merchantId': 23326}, {'prodId': 13991985, 'date': '2026-04-29', 'price': 1798.9, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-04-30', 'price': 1798.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-05-01', 'price': 1759.02, 'merchantId': 245}, {'prodId': 13991985, 'date': '2026-05-02', 'price': 1759.02, 'merchantId': 245}, {'prodId': 13991985, 'date': '2026-05-03', 'price': 1759.02, 'merchantId': 245}, {'prodId': 13991985, 'date': '2026-05-04', 'price': 1599.0, 'merchantId': 16108}, {'prodId': 13991985, 'date': '2026-05-05', 'price': 1599.0, 'merchantId': 16108}, {'prodId': 13991985, 'date': '2026-05-06', 'price': 1599.0, 'merchantId': 16108}, {'prodId': 13991985, 'date': '2026-05-07', 'price': 1778.03, 'merchantId': 245}, {'prodId': 13991985, 'date': '2026-05-08', 'price': 1565.96, 'merchantId': 9385}, {'prodId': 13991985, 'date': '2026-05-09', 'price': 1779.01, 'merchantId': 245}, {'prodId': 13991985, 'date': '2026-05-10', 'price': 1779.01, 'merchantId': 245}, {'prodId': 13991985, 'date': '2026-05-11', 'price': 1790.1, 'merchantId': 9385}, {'prodId': 13991985, 'date': '2026-05-12', 'price': 1790.1, 'merchantId': 9385}, {'prodId': 13991985, 'date': '2026-05-13', 'price': 1799.1, 'merchantId': 23254}, {'prodId': 13991985, 'date': '2026-05-14', 'price': 1799.1, 'merchantId': 23254}, {'prodId': 13991985, 'date': '2026-05-15', 'price': 1799.1, 'merchantId': 23254}, {'prodId': 13991985, 'date': '2026-05-16', 'price': 1665.71, 'merchantId': 9385}, {'prodId': 13991985, 'date': '2026-05-17', 'price': 1799.1, 'merchantId': 23254}, {'prodId': 13991985, 'date': '2026-05-18', 'price': 1575.31, 'merchantId': 9385}, {'prodId': 13991985, 'date': '2026-05-19', 'price': 1798.0, 'merchantId': 34}, {'prodId': 13991985, 'date': '2026-05-20', 'price': 1798.0, 'merchantId': 34}, {'prodId': 13991985, 'date': '2026-05-21', 'price': 1798.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-05-22', 'price': 1798.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-05-23', 'price': 1798.0, 'merchantId': 34}, {'prodId': 13991985, 'date': '2026-05-24', 'price': 1799.1, 'merchantId': 23254}, {'prodId': 13991985, 'date': '2026-05-25', 'price': 1779.01, 'merchantId': 245}, {'prodId': 13991985, 'date': '2026-05-26', 'price': 1779.01, 'merchantId': 245}, {'prodId': 13991985, 'date': '2026-05-27', 'price': 1798.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-05-28', 'price': 1799.1, 'merchantId': 23254}, {'prodId': 13991985, 'date': '2026-05-29', 'price': 1798.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-05-30', 'price': 1798.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-05-31', 'price': 1799.1, 'merchantId': 23254}, {'prodId': 13991985, 'date': '2026-06-01', 'price': 1798.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-06-02', 'price': 1798.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-06-03', 'price': 1798.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-06-04', 'price': 1798.0, 'merchantId': 2}, {'prodId': 13991985, 'date': '2026-06-05', 'price': 1798.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-06-06', 'price': 1798.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-06-07', 'price': 1798.0, 'merchantId': 2}, {'prodId': 13991985, 'date': '2026-06-08', 'price': 1798.0, 'merchantId': 4}, {'prodId': 13991985, 'date': '2026-06-09', 'price': 1799.1, 'merchantId': 23254}, {'prodId': 13991985, 'date': '2026-06-10', 'price': 1799.1, 'merchantId': 23254}, {'prodId': 13991985, 'date': '2026-06-11', 'price': 1799.1, 'merchantId': 23254}, {'prodId': 13991985, 'date': '2026-06-12', 'price': 1889.1, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2026-06-13', 'price': 1889.1, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2026-06-14', 'price': 1898.95, 'merchantId': 2584}, {'prodId': 13991985, 'date': '2026-06-15', 'price': 1897.0, 'merchantId': 34}, {'prodId': 13991985, 'date': '2026-06-16', 'price': 1889.1, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2026-06-17', 'price': 1889.1, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2026-06-18', 'price': 1889.1, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2026-06-19', 'price': 1889.1, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2026-06-20', 'price': 1889.1, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2026-06-21', 'price': 1889.1, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2026-06-22', 'price': 1889.1, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2026-06-23', 'price': 1889.1, 'merchantId': 22902}, {'prodId': 13991985, 'date': '2026-06-24', 'price': 1898.95, 'merchantId': 2584}, {'prodId': 13991985, 'date': '2026-06-25', 'price': 1898.95, 'merchantId': 2584}, {'prodId': 13991985, 'date': '2026-06-26', 'price': 1898.95, 'merchantId': 2584}, {'prodId': 13991985, 'date': '2026-06-27', 'price': 1898.95, 'merchantId': 2584}, {'prodId': 13991985, 'date': '2026-06-28', 'price': 1898.95, 'merchantId': 2584}, {'prodId': 13991985, 'date': '2026-06-29', 'price': 1898.95, 'merchantId': 2584}, {'prodId': 13991985, 'date': '2026-06-30', 'price': 1898.95, 'merchantId': 2584}, {'prodId': 13991985, 'date': '2026-07-01', 'price': 1619.0, 'merchantId': 1582}, {'prodId': 13991985, 'date': '2026-07-02', 'price': 1898.95, 'merchantId': 2584}, {'prodId': 13991985, 'date': '2026-07-03', 'price': 1898.95, 'merchantId': 2584}, {'prodId': 13991985, 'date': '2026-07-04', 'price': 1898.95, 'merchantId': 2584}, {'prodId': 13991985, 'date': '2026-07-05', 'price': 1688.0, 'merchantId': 1582}, {'prodId': 13991985, 'date': '2026-07-06', 'price': 1688.0, 'merchantId': 9385}, {'prodId': 13991985, 'date': '2026-07-07', 'price': 1898.95, 'merchantId': 2584}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13993243, 'date': '2025-10-08', 'price': 1044.05, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2025-10-09', 'price': 989.1, 'merchantId': 4}, {'prodId': 13993243, 'date': '2025-10-10', 'price': 989.1, 'merchantId': 4}, {'prodId': 13993243, 'date': '2025-10-11', 'price': 969.9, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2025-10-12', 'price': 969.9, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2025-10-13', 'price': 969.9, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2025-10-14', 'price': 969.9, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2025-10-15', 'price': 969.9, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2025-10-16', 'price': 989.0, 'merchantId': 4}, {'prodId': 13993243, 'date': '2025-10-17', 'price': 989.0, 'merchantId': 4}, {'prodId': 13993243, 'date': '2025-10-18', 'price': 989.0, 'merchantId': 4}, {'prodId': 13993243, 'date': '2025-10-19', 'price': 989.0, 'merchantId': 4}, {'prodId': 13993243, 'date': '2025-10-20', 'price': 989.0, 'merchantId': 4}, {'prodId': 13993243, 'date': '2025-10-21', 'price': 989.0, 'merchantId': 4}, {'prodId': 13993243, 'date': '2025-10-22', 'price': 989.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-10-23', 'price': 989.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-10-24', 'price': 989.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-10-25', 'price': 989.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-10-26', 'price': 989.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-10-27', 'price': 989.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-10-28', 'price': 899.1, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-10-29', 'price': 899.1, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-10-30', 'price': 899.1, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-10-31', 'price': 898.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-11-01', 'price': 898.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-11-02', 'price': 898.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-11-03', 'price': 898.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-11-04', 'price': 890.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-11-05', 'price': 890.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-11-06', 'price': 890.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-11-07', 'price': 809.1, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-11-08', 'price': 809.1, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-11-09', 'price': 809.1, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-11-10', 'price': 809.1, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-11-11', 'price': 809.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-11-12', 'price': 809.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-11-13', 'price': 714.6, 'merchantId': 9385}, {'prodId': 13993243, 'date': '2025-11-14', 'price': 785.7, 'merchantId': 9385}, {'prodId': 13993243, 'date': '2025-11-15', 'price': 785.7, 'merchantId': 9385}, {'prodId': 13993243, 'date': '2025-11-16', 'price': 785.7, 'merchantId': 9385}, {'prodId': 13993243, 'date': '2025-11-17', 'price': 809.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-11-18', 'price': 809.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-11-19', 'price': 809.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-11-20', 'price': 809.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-11-21', 'price': 809.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-11-22', 'price': 809.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-11-23', 'price': 809.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-11-24', 'price': 748.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-11-25', 'price': 748.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-11-26', 'price': 748.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-11-27', 'price': 699.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-11-28', 'price': 698.39, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-11-29', 'price': 698.39, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-11-30', 'price': 698.39, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-12-01', 'price': 698.39, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-12-02', 'price': 698.39, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-12-03', 'price': 698.39, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-12-04', 'price': 698.39, 'merchantId': 34}, {'prodId': 13993243, 'date': '2025-12-05', 'price': 698.0, 'merchantId': 23326}, {'prodId': 13993243, 'date': '2025-12-06', 'price': 698.0, 'merchantId': 23326}, {'prodId': 13993243, 'date': '2025-12-07', 'price': 698.0, 'merchantId': 23326}, {'prodId': 13993243, 'date': '2025-12-08', 'price': 698.0, 'merchantId': 23326}, {'prodId': 13993243, 'date': '2025-12-09', 'price': 698.0, 'merchantId': 23326}, {'prodId': 13993243, 'date': '2025-12-10', 'price': 698.0, 'merchantId': 23326}, {'prodId': 13993243, 'date': '2025-12-11', 'price': 736.78, 'merchantId': 21629}, {'prodId': 13993243, 'date': '2025-12-12', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2025-12-13', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2025-12-14', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2025-12-15', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2025-12-16', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2025-12-17', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2025-12-18', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2025-12-19', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2025-12-20', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2025-12-21', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2025-12-22', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2025-12-23', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2025-12-24', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2025-12-25', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2025-12-26', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2025-12-27', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2025-12-28', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2025-12-29', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2025-12-30', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2025-12-31', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-01', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-02', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-03', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-04', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-05', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-06', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-07', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-08', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-09', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-10', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-11', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-12', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-13', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-14', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-15', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-16', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-17', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-18', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-19', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-20', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-21', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-22', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-23', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-24', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-25', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-26', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-27', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-28', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-29', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-30', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-01-31', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-01', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-02', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-03', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-04', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-05', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-06', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-07', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-08', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-09', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-10', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-11', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-12', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-13', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-14', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-15', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-16', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-17', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-18', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-19', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-20', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-21', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-22', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-23', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-24', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-25', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-26', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-27', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-02-28', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-01', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-02', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-03', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-04', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-05', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-06', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-07', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-08', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-09', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-10', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-11', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-12', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-13', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-14', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-15', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-16', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-17', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-18', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-19', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-20', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-21', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-22', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-23', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-24', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-25', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-26', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-27', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-28', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-29', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-30', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-03-31', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-04-01', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-04-02', 'price': 732.35, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-04-03', 'price': 782.88, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-04-04', 'price': 782.88, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-04-05', 'price': 782.88, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-04-06', 'price': 898.9, 'merchantId': 23326}, {'prodId': 13993243, 'date': '2026-04-07', 'price': 898.0, 'merchantId': 23326}, {'prodId': 13993243, 'date': '2026-04-08', 'price': 897.0, 'merchantId': 23326}, {'prodId': 13993243, 'date': '2026-04-09', 'price': 896.9, 'merchantId': 23326}, {'prodId': 13993243, 'date': '2026-04-10', 'price': 896.0, 'merchantId': 23326}, {'prodId': 13993243, 'date': '2026-04-11', 'price': 896.0, 'merchantId': 23326}, {'prodId': 13993243, 'date': '2026-04-12', 'price': 876.09, 'merchantId': 245}, {'prodId': 13993243, 'date': '2026-04-13', 'price': 876.09, 'merchantId': 245}, {'prodId': 13993243, 'date': '2026-04-14', 'price': 851.1, 'merchantId': 21627}, {'prodId': 13993243, 'date': '2026-04-15', 'price': 871.2, 'merchantId': 245}, {'prodId': 13993243, 'date': '2026-04-16', 'price': 864.35, 'merchantId': 245}, {'prodId': 13993243, 'date': '2026-04-17', 'price': 864.35, 'merchantId': 245}, {'prodId': 13993243, 'date': '2026-04-18', 'price': 883.9, 'merchantId': 34}, {'prodId': 13993243, 'date': '2026-04-19', 'price': 883.9, 'merchantId': 34}, {'prodId': 13993243, 'date': '2026-04-20', 'price': 848.97, 'merchantId': 22902}, {'prodId': 13993243, 'date': '2026-04-21', 'price': 848.97, 'merchantId': 22902}, {'prodId': 13993243, 'date': '2026-04-22', 'price': 848.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2026-04-23', 'price': 789.64, 'merchantId': 9385}, {'prodId': 13993243, 'date': '2026-04-24', 'price': 793.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2026-04-25', 'price': 793.0, 'merchantId': 245}, {'prodId': 13993243, 'date': '2026-04-26', 'price': 793.9, 'merchantId': 23326}, {'prodId': 13993243, 'date': '2026-04-27', 'price': 793.9, 'merchantId': 23326}, {'prodId': 13993243, 'date': '2026-04-28', 'price': 848.79, 'merchantId': 23326}, {'prodId': 13993243, 'date': '2026-04-29', 'price': 880.0, 'merchantId': 21627}, {'prodId': 13993243, 'date': '2026-04-30', 'price': 880.0, 'merchantId': 21627}, {'prodId': 13993243, 'date': '2026-05-01', 'price': 896.13, 'merchantId': 2584}, {'prodId': 13993243, 'date': '2026-05-02', 'price': 880.0, 'merchantId': 21627}, {'prodId': 13993243, 'date': '2026-05-03', 'price': 800.1, 'merchantId': 9385}, {'prodId': 13993243, 'date': '2026-05-04', 'price': 800.1, 'merchantId': 9385}, {'prodId': 13993243, 'date': '2026-05-05', 'price': 799.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2026-05-06', 'price': 750.49, 'merchantId': 4}, {'prodId': 13993243, 'date': '2026-05-07', 'price': 897.3, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-05-08', 'price': 749.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2026-05-09', 'price': 897.3, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-05-10', 'price': 897.3, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-05-11', 'price': 809.0, 'merchantId': 4}, {'prodId': 13993243, 'date': '2026-05-12', 'price': 809.0, 'merchantId': 9385}, {'prodId': 13993243, 'date': '2026-05-13', 'price': 879.0, 'merchantId': 9385}, {'prodId': 13993243, 'date': '2026-05-14', 'price': 879.0, 'merchantId': 9385}, {'prodId': 13993243, 'date': '2026-05-15', 'price': 879.0, 'merchantId': 9385}, {'prodId': 13993243, 'date': '2026-05-16', 'price': 808.2, 'merchantId': 1582}, {'prodId': 13993243, 'date': '2026-05-17', 'price': 836.1, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-05-18', 'price': 768.6, 'merchantId': 22902}, {'prodId': 13993243, 'date': '2026-05-19', 'price': 768.6, 'merchantId': 22902}, {'prodId': 13993243, 'date': '2026-05-20', 'price': 799.0, 'merchantId': 22902}, {'prodId': 13993243, 'date': '2026-05-21', 'price': 753.22, 'merchantId': 1582}, {'prodId': 13993243, 'date': '2026-05-22', 'price': 799.0, 'merchantId': 22902}, {'prodId': 13993243, 'date': '2026-05-23', 'price': 799.0, 'merchantId': 1582}, {'prodId': 13993243, 'date': '2026-05-24', 'price': 799.0, 'merchantId': 22902}, {'prodId': 13993243, 'date': '2026-05-25', 'price': 768.6, 'merchantId': 9385}, {'prodId': 13993243, 'date': '2026-05-26', 'price': 799.0, 'merchantId': 22902}, {'prodId': 13993243, 'date': '2026-05-27', 'price': 790.0, 'merchantId': 22902}, {'prodId': 13993243, 'date': '2026-05-28', 'price': 790.0, 'merchantId': 22902}, {'prodId': 13993243, 'date': '2026-05-29', 'price': 773.1, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-05-30', 'price': 773.1, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-05-31', 'price': 773.1, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-06-01', 'price': 773.1, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-06-02', 'price': 799.0, 'merchantId': 22902}, {'prodId': 13993243, 'date': '2026-06-03', 'price': 799.0, 'merchantId': 22902}, {'prodId': 13993243, 'date': '2026-06-04', 'price': 799.0, 'merchantId': 22902}, {'prodId': 13993243, 'date': '2026-06-05', 'price': 799.0, 'merchantId': 22902}, {'prodId': 13993243, 'date': '2026-06-06', 'price': 768.6, 'merchantId': 9385}, {'prodId': 13993243, 'date': '2026-06-07', 'price': 799.02, 'merchantId': 22902}, {'prodId': 13993243, 'date': '2026-06-08', 'price': 789.57, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-06-09', 'price': 799.0, 'merchantId': 22902}, {'prodId': 13993243, 'date': '2026-06-10', 'price': 787.55, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-06-11', 'price': 787.55, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-06-12', 'price': 787.55, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-06-13', 'price': 745.15, 'merchantId': 245}, {'prodId': 13993243, 'date': '2026-06-14', 'price': 787.55, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-06-15', 'price': 787.55, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-06-16', 'price': 787.55, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-06-17', 'price': 763.9, 'merchantId': 9385}, {'prodId': 13993243, 'date': '2026-06-18', 'price': 787.55, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-06-19', 'price': 779.0, 'merchantId': 4}, {'prodId': 13993243, 'date': '2026-06-20', 'price': 779.0, 'merchantId': 2}, {'prodId': 13993243, 'date': '2026-06-21', 'price': 787.55, 'merchantId': 22905}, {'prodId': 13993243, 'date': '2026-06-22', 'price': 779.0, 'merchantId': 2}, {'prodId': 13993243, 'date': '2026-06-23', 'price': 779.0, 'merchantId': 34}, {'prodId': 13993243, 'date': '2026-06-24', 'price': 759.05, 'merchantId': 20583}, {'prodId': 13993243, 'date': '2026-06-25', 'price': 759.05, 'merchantId': 20583}, {'prodId': 13993243, 'date': '2026-06-26', 'price': 759.05, 'merchantId': 20583}, {'prodId': 13993243, 'date': '2026-06-27', 'price': 759.05, 'merchantId': 20583}, {'prodId': 13993243, 'date': '2026-06-28', 'price': 759.05, 'merchantId': 20583}, {'prodId': 13993243, 'date': '2026-06-29', 'price': 759.05, 'merchantId': 20583}, {'prodId': 13993243, 'date': '2026-06-30', 'price': 759.05, 'merchantId': 20583}, {'prodId': 13993243, 'date': '2026-07-01', 'price': 759.05, 'merchantId': 20583}, {'prodId': 13993243, 'date': '2026-07-02', 'price': 799.0, 'merchantId': 16108}, {'prodId': 13993243, 'date': '2026-07-03', 'price': 799.0, 'merchantId': 16108}, {'prodId': 13993243, 'date': '2026-07-04', 'price': 799.0, 'merchantId': 16108}, {'prodId': 13993243, 'date': '2026-07-05', 'price': 799.0, 'merchantId': 16108}, {'prodId': 13993243, 'date': '2026-07-06', 'price': 797.4, 'merchantId': 1582}, {'prodId': 13993243, 'date': '2026-07-07', 'price': 799.0, 'merchantId': 22902}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13994392, 'date': '2026-04-23', 'price': 3599.1, 'merchantId': 20583}, {'prodId': 13994392, 'date': '2026-04-24', 'price': 3098.0, 'merchantId': 2}, {'prodId': 13994392, 'date': '2026-04-25', 'price': 2999.0, 'merchantId': 2}, {'prodId': 13994392, 'date': '2026-04-26', 'price': 2999.0, 'merchantId': 2}, {'prodId': 13994392, 'date': '2026-04-27', 'price': 2999.0, 'merchantId': 2}, {'prodId': 13994392, 'date': '2026-04-28', 'price': 2999.0, 'merchantId': 2}, {'prodId': 13994392, 'date': '2026-04-29', 'price': 2849.05, 'merchantId': 34}, {'prodId': 13994392, 'date': '2026-04-30', 'price': 2699.1, 'merchantId': 20583}, {'prodId': 13994392, 'date': '2026-05-01', 'price': 2699.1, 'merchantId': 20583}, {'prodId': 13994392, 'date': '2026-05-02', 'price': 2699.1, 'merchantId': 22905}, {'prodId': 13994392, 'date': '2026-05-03', 'price': 2699.1, 'merchantId': 22905}, {'prodId': 13994392, 'date': '2026-05-04', 'price': 2699.1, 'merchantId': 22905}, {'prodId': 13994392, 'date': '2026-05-05', 'price': 2699.1, 'merchantId': 22905}, {'prodId': 13994392, 'date': '2026-05-06', 'price': 2699.1, 'merchantId': 22905}, {'prodId': 13994392, 'date': '2026-05-07', 'price': 2639.12, 'merchantId': 22905}, {'prodId': 13994392, 'date': '2026-05-08', 'price': 2639.12, 'merchantId': 22905}, {'prodId': 13994392, 'date': '2026-05-09', 'price': 2639.12, 'merchantId': 22905}, {'prodId': 13994392, 'date': '2026-05-10', 'price': 2639.12, 'merchantId': 22905}, {'prodId': 13994392, 'date': '2026-05-11', 'price': 2639.12, 'merchantId': 22905}, {'prodId': 13994392, 'date': '2026-05-12', 'price': 2639.12, 'merchantId': 22905}, {'prodId': 13994392, 'date': '2026-05-13', 'price': 2639.12, 'merchantId': 22905}, {'prodId': 13994392, 'date': '2026-05-14', 'price': 2639.12, 'merchantId': 22905}, {'prodId': 13994392, 'date': '2026-05-15', 'price': 2639.12, 'merchantId': 22905}, {'prodId': 13994392, 'date': '2026-05-16', 'price': 2639.12, 'merchantId': 22905}, {'prodId': 13994392, 'date': '2026-05-17', 'price': 2639.12, 'merchantId': 22905}, {'prodId': 13994392, 'date': '2026-05-18', 'price': 2639.12, 'merchantId': 22905}, {'prodId': 13994392, 'date': '2026-05-19', 'price': 2639.12, 'merchantId': 22905}, {'prodId': 13994392, 'date': '2026-05-20', 'price': 2498.79, 'merchantId': 34}, {'prodId': 13994392, 'date': '2026-05-21', 'price': 2498.49, 'merchantId': 34}, {'prodId': 13994392, 'date': '2026-05-22', 'price': 2498.49, 'merchantId': 34}, {'prodId': 13994392, 'date': '2026-05-23', 'price': 2442.97, 'merchantId': 23326}, {'prodId': 13994392, 'date': '2026-05-24', 'price': 2442.97, 'merchantId': 23326}, {'prodId': 13994392, 'date': '2026-05-25', 'price': 2442.97, 'merchantId': 23326}, {'prodId': 13994392, 'date': '2026-05-26', 'price': 2442.97, 'merchantId': 23326}, {'prodId': 13994392, 'date': '2026-05-27', 'price': 2442.97, 'merchantId': 23326}, {'prodId': 13994392, 'date': '2026-05-28', 'price': 2442.97, 'merchantId': 23326}, {'prodId': 13994392, 'date': '2026-05-29', 'price': 2597.0, 'merchantId': 2}, {'prodId': 13994392, 'date': '2026-05-30', 'price': 2597.0, 'merchantId': 34}, {'prodId': 13994392, 'date': '2026-05-31', 'price': 2597.0, 'merchantId': 2}, {'prodId': 13994392, 'date': '2026-06-01', 'price': 2541.25, 'merchantId': 23326}, {'prodId': 13994392, 'date': '2026-06-02', 'price': 2541.24, 'merchantId': 23326}, {'prodId': 13994392, 'date': '2026-06-03', 'price': 2483.48, 'merchantId': 23326}, {'prodId': 13994392, 'date': '2026-06-04', 'price': 2483.4, 'merchantId': 23326}, {'prodId': 13994392, 'date': '2026-06-05', 'price': 2483.4, 'merchantId': 23326}, {'prodId': 13994392, 'date': '2026-06-06', 'price': 2483.4, 'merchantId': 23326}, {'prodId': 13994392, 'date': '2026-06-07', 'price': 2483.4, 'merchantId': 23326}, {'prodId': 13994392, 'date': '2026-06-08', 'price': 2541.44, 'merchantId': 20583}, {'prodId': 13994392, 'date': '2026-06-09', 'price': 2541.44, 'merchantId': 20583}, {'prodId': 13994392, 'date': '2026-06-10', 'price': 2541.44, 'merchantId': 20583}, {'prodId': 13994392, 'date': '2026-06-11', 'price': 2541.44, 'merchantId': 20583}, {'prodId': 13994392, 'date': '2026-06-12', 'price': 2541.44, 'merchantId': 20583}, {'prodId': 13994392, 'date': '2026-06-13', 'price': 2541.44, 'merchantId': 20583}, {'prodId': 13994392, 'date': '2026-06-14', 'price': 2541.44, 'merchantId': 20583}, {'prodId': 13994392, 'date': '2026-06-15', 'price': 2541.04, 'merchantId': 23326}, {'prodId': 13994392, 'date': '2026-06-16', 'price': 2541.44, 'merchantId': 20583}, {'prodId': 13994392, 'date': '2026-06-17', 'price': 2610.0, 'merchantId': 21627}, {'prodId': 13994392, 'date': '2026-06-18', 'price': 2610.0, 'merchantId': 21627}, {'prodId': 13994392, 'date': '2026-06-19', 'price': 2610.0, 'merchantId': 21627}, {'prodId': 13994392, 'date': '2026-06-20', 'price': 2610.0, 'merchantId': 21627}, {'prodId': 13994392, 'date': '2026-06-21', 'price': 2610.0, 'merchantId': 21627}, {'prodId': 13994392, 'date': '2026-06-22', 'price': 2610.0, 'merchantId': 21627}, {'prodId': 13994392, 'date': '2026-06-23', 'price': 2610.0, 'merchantId': 21627}, {'prodId': 13994392, 'date': '2026-06-24', 'price': 2610.0, 'merchantId': 21627}, {'prodId': 13994392, 'date': '2026-06-25', 'price': 2610.0, 'merchantId': 21627}, {'prodId': 13994392, 'date': '2026-06-26', 'price': 2610.0, 'merchantId': 21627}, {'prodId': 13994392, 'date': '2026-06-27', 'price': 2610.0, 'merchantId': 21627}, {'prodId': 13994392, 'date': '2026-06-28', 'price': 2610.0, 'merchantId': 21627}, {'prodId': 13994392, 'date': '2026-06-29', 'price': 2610.0, 'merchantId': 21627}, {'prodId': 13994392, 'date': '2026-06-30', 'price': 2610.0, 'merchantId': 21627}, {'prodId': 13994392, 'date': '2026-07-01', 'price': 2610.0, 'merchantId': 21629}, {'prodId': 13994392, 'date': '2026-07-02', 'price': 2598.9, 'merchantId': 2}, {'prodId': 13994392, 'date': '2026-07-03', 'price': 2498.9, 'merchantId': 2}, {'prodId': 13994392, 'date': '2026-07-04', 'price': 2498.9, 'merchantId': 2}, {'prodId': 13994392, 'date': '2026-07-05', 'price': 2498.9, 'merchantId': 2}, {'prodId': 13994392, 'date': '2026-07-06', 'price': 2498.0, 'merchantId': 2}, {'prodId': 13994392, 'date': '2026-07-07', 'price': 2442.49, 'merchantId': 23326}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13561997, 'date': '2025-07-07', 'price': 5939.1, 'merchantId': 23199}, {'prodId': 13561997, 'date': '2025-07-08', 'price': 6090.0, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2025-07-09', 'price': 5657.0, 'merchantId': 10763}, {'prodId': 13561997, 'date': '2025-07-10', 'price': 5657.0, 'merchantId': 10763}, {'prodId': 13561997, 'date': '2025-07-11', 'price': 5657.0, 'merchantId': 10763}, {'prodId': 13561997, 'date': '2025-07-12', 'price': 5657.0, 'merchantId': 10763}, {'prodId': 13561997, 'date': '2025-07-13', 'price': 5849.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-07-14', 'price': 5849.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-07-15', 'price': 5610.0, 'merchantId': 10763}, {'prodId': 13561997, 'date': '2025-07-16', 'price': 5610.0, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2025-07-17', 'price': 5610.0, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2025-07-18', 'price': 5657.0, 'merchantId': 10763}, {'prodId': 13561997, 'date': '2025-07-19', 'price': 5939.1, 'merchantId': 20609}, {'prodId': 13561997, 'date': '2025-07-20', 'price': 5939.1, 'merchantId': 20609}, {'prodId': 13561997, 'date': '2025-07-21', 'price': 5939.1, 'merchantId': 20609}, {'prodId': 13561997, 'date': '2025-07-22', 'price': 6137.07, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2025-07-23', 'price': 6209.1, 'merchantId': 20612}, {'prodId': 13561997, 'date': '2025-07-24', 'price': 6209.1, 'merchantId': 20609}, {'prodId': 13561997, 'date': '2025-07-25', 'price': 6209.1, 'merchantId': 20612}, {'prodId': 13561997, 'date': '2025-07-26', 'price': 6209.1, 'merchantId': 20612}, {'prodId': 13561997, 'date': '2025-07-27', 'price': 6209.1, 'merchantId': 20612}, {'prodId': 13561997, 'date': '2025-07-28', 'price': 5799.0, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2025-07-29', 'price': 6199.0, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2025-07-30', 'price': 5999.0, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2025-07-31', 'price': 6209.1, 'merchantId': 20612}, {'prodId': 13561997, 'date': '2025-08-01', 'price': 6209.1, 'merchantId': 20612}, {'prodId': 13561997, 'date': '2025-08-02', 'price': 6209.1, 'merchantId': 20612}, {'prodId': 13561997, 'date': '2025-08-03', 'price': 6209.09, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2025-08-04', 'price': 6209.09, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2025-08-05', 'price': 6209.09, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2025-08-06', 'price': 6209.09, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2025-08-07', 'price': 4443.0, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2025-08-08', 'price': 4443.0, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2025-08-09', 'price': 6209.1, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-08-10', 'price': 6209.1, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-08-11', 'price': 6209.1, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-08-12', 'price': 6209.1, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-08-13', 'price': 6209.1, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-08-14', 'price': 6209.1, 'merchantId': 23199}, {'prodId': 13561997, 'date': '2025-08-15', 'price': 6209.1, 'merchantId': 23199}, {'prodId': 13561997, 'date': '2025-08-16', 'price': 6209.1, 'merchantId': 23199}, {'prodId': 13561997, 'date': '2025-08-17', 'price': 6209.1, 'merchantId': 23199}, {'prodId': 13561997, 'date': '2025-08-18', 'price': 6209.1, 'merchantId': 23199}, {'prodId': 13561997, 'date': '2025-08-19', 'price': 6029.1, 'merchantId': 23199}, {'prodId': 13561997, 'date': '2025-08-20', 'price': 6279.12, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2025-08-21', 'price': 6279.12, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2025-08-22', 'price': 6279.12, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2025-08-23', 'price': 6279.12, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2025-08-24', 'price': 6279.12, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2025-08-25', 'price': 6279.12, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2025-08-26', 'price': 6279.12, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2025-08-27', 'price': 6029.1, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-08-28', 'price': 6029.1, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-08-29', 'price': 6029.1, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-08-30', 'price': 6029.1, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-08-31', 'price': 6029.1, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-09-01', 'price': 6029.1, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-09-02', 'price': 6029.1, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-09-03', 'price': 6029.1, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-09-04', 'price': 6029.1, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-09-05', 'price': 6028.2, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-09-06', 'price': 6028.2, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-09-07', 'price': 6028.2, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-09-08', 'price': 5908.99, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-09-09', 'price': 5908.99, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-09-10', 'price': 5908.99, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-09-11', 'price': 6028.2, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-09-12', 'price': 6028.2, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-09-13', 'price': 5938.2, 'merchantId': 23199}, {'prodId': 13561997, 'date': '2025-09-14', 'price': 5938.2, 'merchantId': 23199}, {'prodId': 13561997, 'date': '2025-09-15', 'price': 5938.2, 'merchantId': 23199}, {'prodId': 13561997, 'date': '2025-09-16', 'price': 5938.2, 'merchantId': 23199}, {'prodId': 13561997, 'date': '2025-09-17', 'price': 5938.2, 'merchantId': 23199}, {'prodId': 13561997, 'date': '2025-09-18', 'price': 5938.2, 'merchantId': 23199}, {'prodId': 13561997, 'date': '2025-09-19', 'price': 5938.2, 'merchantId': 23199}, {'prodId': 13561997, 'date': '2025-09-20', 'price': 5938.2, 'merchantId': 23199}, {'prodId': 13561997, 'date': '2025-09-21', 'price': 5938.2, 'merchantId': 23199}, {'prodId': 13561997, 'date': '2025-09-22', 'price': 5938.2, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-09-23', 'price': 5938.2, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-09-24', 'price': 5938.2, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-09-25', 'price': 5938.2, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-09-26', 'price': 5938.2, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-09-27', 'price': 5938.2, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-09-28', 'price': 5938.2, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-09-29', 'price': 5938.2, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-09-30', 'price': 5938.2, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-10-01', 'price': 5938.2, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-10-02', 'price': 4654.9, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2025-10-03', 'price': 4654.9, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2025-10-04', 'price': 4654.9, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2025-10-05', 'price': 4654.9, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2025-10-06', 'price': 4654.9, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2025-10-07', 'price': 6099.0, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2025-10-08', 'price': 6099.0, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2025-10-09', 'price': 6099.0, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2025-10-10', 'price': 5849.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-10-11', 'price': 5849.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-10-12', 'price': 5849.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-10-13', 'price': 5114.07, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-10-14', 'price': 4949.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-10-15', 'price': 4949.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-10-16', 'price': 4803.3, 'merchantId': 20609}, {'prodId': 13561997, 'date': '2025-10-17', 'price': 4803.3, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-10-18', 'price': 4803.3, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-10-19', 'price': 4803.3, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-10-20', 'price': 4803.3, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-10-21', 'price': 4803.3, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-10-22', 'price': 4803.3, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-10-23', 'price': 4803.3, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-10-24', 'price': 4803.3, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-10-25', 'price': 4803.3, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-10-26', 'price': 4803.3, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-10-27', 'price': 4803.3, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-10-28', 'price': 4803.3, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-10-29', 'price': 4803.3, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-10-30', 'price': 4803.3, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-10-31', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2025-11-01', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2025-11-02', 'price': 4589.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-11-03', 'price': 4589.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-11-04', 'price': 4589.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-11-05', 'price': 4589.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-11-06', 'price': 4589.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-11-07', 'price': 4487.12, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-11-08', 'price': 4589.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-11-09', 'price': 4589.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-11-10', 'price': 4589.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-11-11', 'price': 4499.1, 'merchantId': 20612}, {'prodId': 13561997, 'date': '2025-11-12', 'price': 4499.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-11-13', 'price': 4499.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-11-14', 'price': 4349.13, 'merchantId': 20612}, {'prodId': 13561997, 'date': '2025-11-15', 'price': 4349.13, 'merchantId': 20612}, {'prodId': 13561997, 'date': '2025-11-16', 'price': 4349.13, 'merchantId': 20612}, {'prodId': 13561997, 'date': '2025-11-17', 'price': 4349.13, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-11-18', 'price': 4349.13, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-11-19', 'price': 4349.13, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2025-11-20', 'price': 4349.13, 'merchantId': 20612}, {'prodId': 13561997, 'date': '2025-11-21', 'price': 3299.0, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2025-11-22', 'price': 4349.13, 'merchantId': 20612}, {'prodId': 13561997, 'date': '2025-11-23', 'price': 4349.13, 'merchantId': 20612}, {'prodId': 13561997, 'date': '2025-11-24', 'price': 4349.13, 'merchantId': 20612}, {'prodId': 13561997, 'date': '2025-11-25', 'price': 4349.13, 'merchantId': 20612}, {'prodId': 13561997, 'date': '2025-11-26', 'price': 4349.13, 'merchantId': 20612}, {'prodId': 13561997, 'date': '2025-11-27', 'price': 4349.13, 'merchantId': 20612}, {'prodId': 13561997, 'date': '2025-11-28', 'price': 4349.13, 'merchantId': 20612}, {'prodId': 13561997, 'date': '2025-11-29', 'price': 3665.56, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2025-11-30', 'price': 4349.13, 'merchantId': 20612}, {'prodId': 13561997, 'date': '2025-12-01', 'price': 4349.13, 'merchantId': 20612}, {'prodId': 13561997, 'date': '2025-12-02', 'price': 4599.0, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-12-03', 'price': 4599.0, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-12-04', 'price': 4599.0, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-12-05', 'price': 4599.0, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-12-06', 'price': 4599.0, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-12-07', 'price': 4599.0, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-12-08', 'price': 4599.0, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-12-09', 'price': 4599.0, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-12-10', 'price': 4799.0, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-12-11', 'price': 4799.0, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-12-12', 'price': 4799.0, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-12-13', 'price': 4799.0, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-12-14', 'price': 4799.0, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-12-15', 'price': 4799.0, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-12-16', 'price': 4999.0, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-12-17', 'price': 4999.0, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-12-18', 'price': 4799.0, 'merchantId': 20609}, {'prodId': 13561997, 'date': '2025-12-19', 'price': 4799.0, 'merchantId': 20609}, {'prodId': 13561997, 'date': '2025-12-20', 'price': 4799.0, 'merchantId': 20609}, {'prodId': 13561997, 'date': '2025-12-21', 'price': 4999.0, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-12-22', 'price': 4999.0, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2025-12-23', 'price': 5499.0, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2025-12-24', 'price': 5554.44, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2025-12-25', 'price': 5599.99, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2025-12-26', 'price': 5599.99, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2025-12-27', 'price': 5599.99, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2025-12-28', 'price': 5599.99, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2025-12-29', 'price': 5599.99, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2025-12-30', 'price': 5599.99, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2025-12-31', 'price': 5999.0, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2026-01-01', 'price': 5890.0, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2026-01-02', 'price': 5890.0, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2026-01-03', 'price': 5890.0, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2026-01-04', 'price': 5890.0, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2026-01-05', 'price': 5890.0, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2026-01-06', 'price': 5890.0, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2026-01-07', 'price': 4399.0, 'merchantId': 2}, {'prodId': 13561997, 'date': '2026-01-08', 'price': 4399.0, 'merchantId': 2}, {'prodId': 13561997, 'date': '2026-01-09', 'price': 4399.0, 'merchantId': 2}, {'prodId': 13561997, 'date': '2026-01-10', 'price': 4399.0, 'merchantId': 2}, {'prodId': 13561997, 'date': '2026-01-11', 'price': 4399.0, 'merchantId': 2}, {'prodId': 13561997, 'date': '2026-01-12', 'price': 4399.0, 'merchantId': 4}, {'prodId': 13561997, 'date': '2026-01-13', 'price': 4399.0, 'merchantId': 4}, {'prodId': 13561997, 'date': '2026-01-14', 'price': 4420.55, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-01-15', 'price': 4420.55, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-01-16', 'price': 4420.55, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-01-17', 'price': 4420.55, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-01-18', 'price': 4420.55, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-01-19', 'price': 4420.55, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-01-20', 'price': 4911.72, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2026-01-21', 'price': 5072.11, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-01-22', 'price': 5072.11, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-01-23', 'price': 5072.11, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-01-24', 'price': 5072.11, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-01-25', 'price': 5072.11, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-01-26', 'price': 5072.11, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-01-27', 'price': 5072.11, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-01-28', 'price': 5129.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-01-29', 'price': 5039.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-01-30', 'price': 5039.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-01-31', 'price': 5039.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-02-01', 'price': 5039.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-02-02', 'price': 5039.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-02-03', 'price': 4803.3, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-02-04', 'price': 4783.08, 'merchantId': 16108}, {'prodId': 13561997, 'date': '2026-02-05', 'price': 5149.0, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2026-02-06', 'price': 5149.0, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2026-02-07', 'price': 5149.0, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2026-02-08', 'price': 5149.0, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2026-02-09', 'price': 5149.0, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2026-02-10', 'price': 5039.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-02-11', 'price': 5039.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-02-12', 'price': 5039.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-02-13', 'price': 4769.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-02-14', 'price': 4769.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-02-15', 'price': 4769.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-02-16', 'price': 4769.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-02-17', 'price': 4769.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-02-18', 'price': 4769.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-02-19', 'price': 4769.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-02-20', 'price': 4769.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-02-21', 'price': 4769.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-02-22', 'price': 4769.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-02-23', 'price': 4769.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-02-24', 'price': 4769.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-02-25', 'price': 4769.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-02-26', 'price': 4769.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-02-27', 'price': 4769.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-02-28', 'price': 4769.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-03-01', 'price': 4769.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-03-02', 'price': 4769.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-03-03', 'price': 4769.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-03-04', 'price': 4769.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-03-05', 'price': 4769.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-03-06', 'price': 4769.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-03-07', 'price': 4769.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-03-08', 'price': 4769.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-03-09', 'price': 4769.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-03-10', 'price': 4679.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-03-11', 'price': 4679.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-03-12', 'price': 4679.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-03-13', 'price': 4679.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-03-14', 'price': 4679.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-03-15', 'price': 4679.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-03-16', 'price': 4679.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-03-17', 'price': 4769.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-03-18', 'price': 5099.0, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2026-03-19', 'price': 5099.0, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2026-03-20', 'price': 5099.0, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2026-03-21', 'price': 5299.0, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-03-22', 'price': 5299.0, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-03-23', 'price': 5299.0, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-03-24', 'price': 5099.0, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2026-03-25', 'price': 5099.0, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2026-03-26', 'price': 5240.12, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-03-27', 'price': 5240.12, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-03-28', 'price': 5240.12, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-03-29', 'price': 5240.12, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-03-30', 'price': 5099.0, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2026-03-31', 'price': 5240.12, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-04-01', 'price': 5099.0, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2026-04-02', 'price': 4627.11, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-04-03', 'price': 4627.11, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-04-04', 'price': 4627.11, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-04-05', 'price': 4627.11, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-04-06', 'price': 4627.11, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-04-07', 'price': 4627.11, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-04-08', 'price': 4627.11, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-04-09', 'price': 4627.11, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-04-10', 'price': 4627.11, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-04-11', 'price': 4679.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-04-12', 'price': 4679.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-04-13', 'price': 4679.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-04-14', 'price': 4679.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-04-15', 'price': 4679.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-04-16', 'price': 4679.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-04-17', 'price': 4679.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-04-18', 'price': 4679.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-04-19', 'price': 4679.1, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-04-20', 'price': 4499.1, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-04-21', 'price': 4399.12, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-04-22', 'price': 4399.12, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-04-23', 'price': 4399.12, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-04-24', 'price': 4399.12, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-04-25', 'price': 4399.12, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-04-26', 'price': 4487.12, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-04-27', 'price': 4487.12, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-04-28', 'price': 4538.11, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-04-29', 'price': 4538.11, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-04-30', 'price': 4449.0, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-05-01', 'price': 4449.0, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-05-02', 'price': 4449.0, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-05-03', 'price': 4449.0, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-05-04', 'price': 4399.01, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-05-05', 'price': 4399.01, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-05-06', 'price': 4399.01, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-05-07', 'price': 4399.01, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-05-08', 'price': 4399.01, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-05-09', 'price': 4399.01, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-05-10', 'price': 4399.01, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-05-11', 'price': 4399.01, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-05-12', 'price': 4399.01, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-05-13', 'price': 4399.01, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-05-14', 'price': 4399.01, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-05-15', 'price': 4399.01, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-05-16', 'price': 4332.0, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2026-05-17', 'price': 4399.01, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-05-18', 'price': 4335.27, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2026-05-19', 'price': 4274.05, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2026-05-20', 'price': 4399.01, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-05-21', 'price': 4049.1, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2026-05-22', 'price': 4299.05, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-05-23', 'price': 4049.1, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2026-05-24', 'price': 4299.05, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-05-25', 'price': 4299.05, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-05-26', 'price': 4299.05, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-05-27', 'price': 4299.04, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-05-28', 'price': 4127.14, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-05-29', 'price': 4127.14, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-05-30', 'price': 4127.14, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-05-31', 'price': 4127.14, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-06-01', 'price': 4127.14, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-06-02', 'price': 4127.14, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-06-03', 'price': 3869.14, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-06-04', 'price': 3959.12, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-06-05', 'price': 3959.12, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-06-06', 'price': 3959.12, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-06-07', 'price': 3959.12, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-06-08', 'price': 3959.12, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-06-09', 'price': 2995.56, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2026-06-10', 'price': 2995.56, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2026-06-11', 'price': 3959.12, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-06-12', 'price': 3959.12, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-06-13', 'price': 3959.12, 'merchantId': 20609}, {'prodId': 13561997, 'date': '2026-06-14', 'price': 3959.12, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-06-15', 'price': 3959.12, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-06-16', 'price': 3959.12, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-06-17', 'price': 3959.12, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-06-18', 'price': 3959.12, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-06-19', 'price': 3959.12, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-06-20', 'price': 3959.12, 'merchantId': 20583}, {'prodId': 13561997, 'date': '2026-06-21', 'price': 4299.0, 'merchantId': 1582}, {'prodId': 13561997, 'date': '2026-06-22', 'price': 3959.12, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-06-23', 'price': 3959.12, 'merchantId': 22905}, {'prodId': 13561997, 'date': '2026-06-24', 'price': 4049.1, 'merchantId': 20609}, {'prodId': 13561997, 'date': '2026-06-25', 'price': 4049.1, 'merchantId': 20609}, {'prodId': 13561997, 'date': '2026-06-26', 'price': 4049.1, 'merchantId': 20609}, {'prodId': 13561997, 'date': '2026-06-27', 'price': 4499.0, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2026-06-28', 'price': 4499.0, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2026-06-29', 'price': 4899.0, 'merchantId': 9385}, {'prodId': 13561997, 'date': '2026-07-02', 'price': 4311.12, 'merchantId': 20609}, {'prodId': 13561997, 'date': '2026-07-03', 'price': 4311.12, 'merchantId': 20609}, {'prodId': 13561997, 'date': '2026-07-04', 'price': 4311.12, 'merchantId': 20609}, {'prodId': 13561997, 'date': '2026-07-05', 'price': 4311.12, 'merchantId': 20609}, {'prodId': 13561997, 'date': '2026-07-06', 'price': 4311.12, 'merchantId': 20609}, {'prodId': 13561997, 'date': '2026-07-07', 'price': 4311.12, 'merchantId': 20609}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13564531, 'date': '2025-07-07', 'price': 6479.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-07-08', 'price': 6839.05, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-07-09', 'price': 6695.07, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-07-10', 'price': 6695.07, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-07-11', 'price': 6479.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-07-12', 'price': 6479.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-07-13', 'price': 6299.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-07-14', 'price': 6299.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-07-15', 'price': 6299.1, 'merchantId': 20583}, {'prodId': 13564531, 'date': '2025-07-16', 'price': 6299.1, 'merchantId': 20583}, {'prodId': 13564531, 'date': '2025-07-17', 'price': 6299.1, 'merchantId': 20583}, {'prodId': 13564531, 'date': '2025-07-18', 'price': 6479.0, 'merchantId': 22902}, {'prodId': 13564531, 'date': '2025-07-19', 'price': 6479.0, 'merchantId': 22902}, {'prodId': 13564531, 'date': '2025-07-20', 'price': 6479.0, 'merchantId': 22902}, {'prodId': 13564531, 'date': '2025-07-21', 'price': 5831.1, 'merchantId': 22902}, {'prodId': 13564531, 'date': '2025-07-22', 'price': 6479.0, 'merchantId': 22902}, {'prodId': 13564531, 'date': '2025-07-23', 'price': 6479.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-07-24', 'price': 6479.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-07-25', 'price': 6479.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-07-26', 'price': 6479.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-07-27', 'price': 6479.1, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-07-28', 'price': 6599.0, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2025-07-29', 'price': 6479.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-07-30', 'price': 6479.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-07-31', 'price': 6479.1, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-08-01', 'price': 6479.1, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-08-02', 'price': 6479.1, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-08-03', 'price': 6479.1, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-08-04', 'price': 6479.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-08-05', 'price': 6479.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-08-06', 'price': 6479.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-08-07', 'price': 6479.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-08-08', 'price': 5999.0, 'merchantId': 22902}, {'prodId': 13564531, 'date': '2025-08-09', 'price': 5999.0, 'merchantId': 22902}, {'prodId': 13564531, 'date': '2025-08-10', 'price': 5999.0, 'merchantId': 22902}, {'prodId': 13564531, 'date': '2025-08-11', 'price': 5999.0, 'merchantId': 22902}, {'prodId': 13564531, 'date': '2025-08-12', 'price': 6479.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-08-13', 'price': 6479.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-08-14', 'price': 6479.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-08-15', 'price': 6479.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-08-16', 'price': 6479.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-08-17', 'price': 6479.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-08-18', 'price': 6479.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-08-19', 'price': 6209.1, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-08-20', 'price': 6209.1, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-08-21', 'price': 6209.1, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-08-22', 'price': 6209.1, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-08-23', 'price': 6209.1, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-08-24', 'price': 6209.1, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-08-25', 'price': 6209.1, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-08-26', 'price': 6209.1, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-08-27', 'price': 6209.1, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-08-28', 'price': 6209.1, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-08-29', 'price': 6209.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-08-30', 'price': 6209.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-08-31', 'price': 6209.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-09-01', 'price': 6209.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-09-02', 'price': 6209.1, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-09-03', 'price': 6209.1, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-09-04', 'price': 6209.1, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-09-05', 'price': 6209.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-09-06', 'price': 6209.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-09-07', 'price': 6109.65, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-09-08', 'price': 6109.65, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-09-09', 'price': 6109.65, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-09-10', 'price': 6168.66, 'merchantId': 5}, {'prodId': 13564531, 'date': '2025-09-11', 'price': 6168.66, 'merchantId': 5}, {'prodId': 13564531, 'date': '2025-09-12', 'price': 5747.61, 'merchantId': 5}, {'prodId': 13564531, 'date': '2025-09-13', 'price': 5747.61, 'merchantId': 5}, {'prodId': 13564531, 'date': '2025-09-14', 'price': 5747.61, 'merchantId': 5}, {'prodId': 13564531, 'date': '2025-09-15', 'price': 5747.61, 'merchantId': 5}, {'prodId': 13564531, 'date': '2025-09-16', 'price': 5874.02, 'merchantId': 5}, {'prodId': 13564531, 'date': '2025-09-17', 'price': 5874.02, 'merchantId': 5}, {'prodId': 13564531, 'date': '2025-09-18', 'price': 5874.02, 'merchantId': 5}, {'prodId': 13564531, 'date': '2025-09-19', 'price': 5874.02, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2025-09-20', 'price': 5874.02, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2025-09-21', 'price': 5938.2, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-09-22', 'price': 5938.2, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-09-23', 'price': 5938.2, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-09-24', 'price': 5930.1, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-09-25', 'price': 5930.1, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-09-26', 'price': 5930.1, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-09-27', 'price': 5930.1, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-09-28', 'price': 5930.1, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-09-29', 'price': 5930.1, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-09-30', 'price': 5930.1, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-10-01', 'price': 5930.1, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-10-02', 'price': 5819.0, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-10-03', 'price': 5819.0, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-10-04', 'price': 6241.4, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-10-05', 'price': 6241.4, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-10-06', 'price': 6241.4, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-10-07', 'price': 6241.4, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-10-08', 'price': 6298.2, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-10-09', 'price': 6298.2, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-10-10', 'price': 6298.2, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-10-11', 'price': 6298.2, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-10-12', 'price': 6298.2, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-10-13', 'price': 6298.2, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-10-14', 'price': 6298.2, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2025-10-15', 'price': 6498.45, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-10-16', 'price': 6438.16, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-10-17', 'price': 6298.2, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-10-18', 'price': 6298.2, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-10-19', 'price': 6298.2, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-10-20', 'price': 6298.2, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-10-21', 'price': 6438.16, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-10-22', 'price': 6438.16, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-10-23', 'price': 6438.16, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-10-24', 'price': 6298.2, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-10-25', 'price': 6298.2, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-10-26', 'price': 6298.2, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-10-27', 'price': 5823.05, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2025-10-28', 'price': 5823.05, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2025-10-29', 'price': 6438.16, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-10-30', 'price': 6438.16, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-10-31', 'price': 6438.16, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-11-01', 'price': 6438.16, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-11-02', 'price': 6438.16, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-11-03', 'price': 6438.16, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-11-04', 'price': 6438.16, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-11-05', 'price': 6438.16, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-11-06', 'price': 6438.16, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-11-07', 'price': 6438.16, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-11-08', 'price': 6438.16, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-11-09', 'price': 6438.16, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-11-10', 'price': 6438.16, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-11-11', 'price': 6438.16, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-11-12', 'price': 6498.45, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-11-13', 'price': 6498.45, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-11-14', 'price': 6340.5, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-11-15', 'price': 6340.5, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-11-16', 'price': 6340.5, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-11-17', 'price': 6340.5, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-11-18', 'price': 6362.86, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2025-11-19', 'price': 6340.5, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-11-20', 'price': 6340.5, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-11-21', 'price': 6340.5, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-11-22', 'price': 5848.2, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-11-23', 'price': 5848.2, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-11-24', 'price': 5848.2, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-11-25', 'price': 6498.45, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-11-26', 'price': 6498.45, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-11-27', 'price': 5998.9, 'merchantId': 2}, {'prodId': 13564531, 'date': '2025-11-28', 'price': 5865.59, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2025-11-29', 'price': 5998.85, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2025-11-30', 'price': 5998.85, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2025-12-01', 'price': 5998.84, 'merchantId': 1582}, {'prodId': 13564531, 'date': '2025-12-02', 'price': 5998.0, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2025-12-03', 'price': 5997.0, 'merchantId': 2}, {'prodId': 13564531, 'date': '2025-12-04', 'price': 5997.0, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2025-12-05', 'price': 5399.1, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-12-06', 'price': 5399.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-12-07', 'price': 5399.1, 'merchantId': 23199}, {'prodId': 13564531, 'date': '2025-12-08', 'price': 5758.2, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-12-09', 'price': 5758.2, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-12-10', 'price': 5758.2, 'merchantId': 20609}, {'prodId': 13564531, 'date': '2025-12-11', 'price': 5758.2, 'merchantId': 20609}, {'prodId': 13564531, 'date': '2025-12-12', 'price': 5665.73, 'merchantId': 20609}, {'prodId': 13564531, 'date': '2025-12-13', 'price': 5665.73, 'merchantId': 20609}, {'prodId': 13564531, 'date': '2025-12-14', 'price': 5665.73, 'merchantId': 20609}, {'prodId': 13564531, 'date': '2025-12-15', 'price': 5665.73, 'merchantId': 20609}, {'prodId': 13564531, 'date': '2025-12-16', 'price': 5665.73, 'merchantId': 20609}, {'prodId': 13564531, 'date': '2025-12-17', 'price': 5665.73, 'merchantId': 20609}, {'prodId': 13564531, 'date': '2025-12-18', 'price': 5996.0, 'merchantId': 2}, {'prodId': 13564531, 'date': '2025-12-19', 'price': 5665.72, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-12-20', 'price': 5665.72, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-12-21', 'price': 5665.72, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-12-22', 'price': 5665.72, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-12-23', 'price': 5665.72, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-12-24', 'price': 5665.72, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-12-25', 'price': 5665.72, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-12-26', 'price': 5665.72, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-12-27', 'price': 5665.72, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-12-28', 'price': 5665.72, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2025-12-29', 'price': 5994.0, 'merchantId': 2}, {'prodId': 13564531, 'date': '2025-12-30', 'price': 5994.0, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2025-12-31', 'price': 5994.0, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-01-01', 'price': 5994.0, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-01-02', 'price': 5993.0, 'merchantId': 2}, {'prodId': 13564531, 'date': '2026-01-03', 'price': 5993.0, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-01-04', 'price': 5993.0, 'merchantId': 245}, {'prodId': 13564531, 'date': '2026-01-05', 'price': 5999.0, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2026-01-06', 'price': 5999.0, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-01-07', 'price': 5999.0, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-01-08', 'price': 5999.0, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-01-09', 'price': 5999.0, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-01-10', 'price': 5999.0, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2026-01-11', 'price': 5999.0, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2026-01-12', 'price': 5999.0, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-01-13', 'price': 5999.0, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-01-14', 'price': 5998.0, 'merchantId': 34}, {'prodId': 13564531, 'date': '2026-01-15', 'price': 5997.0, 'merchantId': 34}, {'prodId': 13564531, 'date': '2026-01-16', 'price': 5996.9, 'merchantId': 34}, {'prodId': 13564531, 'date': '2026-01-17', 'price': 5996.9, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-01-18', 'price': 5996.9, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-01-19', 'price': 5996.9, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-01-20', 'price': 5996.9, 'merchantId': 245}, {'prodId': 13564531, 'date': '2026-01-21', 'price': 5999.0, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2026-01-22', 'price': 5999.0, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2026-01-23', 'price': 5999.0, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2026-01-24', 'price': 5999.0, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2026-01-25', 'price': 5999.0, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2026-01-26', 'price': 5999.0, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2026-01-27', 'price': 5999.0, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2026-01-28', 'price': 6117.17, 'merchantId': 1582}, {'prodId': 13564531, 'date': '2026-01-29', 'price': 6117.17, 'merchantId': 1582}, {'prodId': 13564531, 'date': '2026-01-30', 'price': 6117.17, 'merchantId': 1582}, {'prodId': 13564531, 'date': '2026-01-31', 'price': 6456.0, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-02-01', 'price': 6456.0, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-02-02', 'price': 6455.9, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-02-03', 'price': 6389.1, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2026-02-04', 'price': 6389.1, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2026-02-05', 'price': 6597.9, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-02-06', 'price': 6597.9, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-02-07', 'price': 6597.9, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-02-08', 'price': 6597.9, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-02-09', 'price': 6597.9, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-02-10', 'price': 6597.9, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-02-11', 'price': 6597.9, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-02-12', 'price': 6597.9, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-02-13', 'price': 6597.9, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-02-14', 'price': 6597.9, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-02-15', 'price': 6597.9, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-02-16', 'price': 6597.9, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-02-17', 'price': 6597.9, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-02-18', 'price': 6597.9, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-02-19', 'price': 6597.9, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-02-20', 'price': 6597.9, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-02-21', 'price': 6597.9, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-02-22', 'price': 6597.9, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-02-23', 'price': 6597.9, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-02-24', 'price': 6597.9, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-02-25', 'price': 6597.9, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-02-26', 'price': 6597.9, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-02-27', 'price': 6597.9, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-02-28', 'price': 6597.9, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-03-01', 'price': 6597.9, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-03-02', 'price': 6597.9, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-03-03', 'price': 6597.9, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-03-04', 'price': 6749.1, 'merchantId': 16108}, {'prodId': 13564531, 'date': '2026-03-05', 'price': 6749.1, 'merchantId': 16108}, {'prodId': 13564531, 'date': '2026-03-06', 'price': 6749.1, 'merchantId': 16108}, {'prodId': 13564531, 'date': '2026-03-07', 'price': 6749.1, 'merchantId': 16108}, {'prodId': 13564531, 'date': '2026-03-08', 'price': 6749.1, 'merchantId': 16108}, {'prodId': 13564531, 'date': '2026-03-09', 'price': 6599.0, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-03-10', 'price': 6599.0, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-03-11', 'price': 6597.0, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-03-12', 'price': 6597.0, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-03-13', 'price': 6597.0, 'merchantId': 16108}, {'prodId': 13564531, 'date': '2026-03-14', 'price': 6597.0, 'merchantId': 16108}, {'prodId': 13564531, 'date': '2026-03-15', 'price': 6597.0, 'merchantId': 16108}, {'prodId': 13564531, 'date': '2026-03-16', 'price': 6597.0, 'merchantId': 16108}, {'prodId': 13564531, 'date': '2026-03-17', 'price': 6598.0, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-03-18', 'price': 6598.0, 'merchantId': 21628}, {'prodId': 13564531, 'date': '2026-03-19', 'price': 6594.9, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-03-20', 'price': 6594.9, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-03-21', 'price': 6594.9, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-03-22', 'price': 6594.9, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-03-23', 'price': 6594.0, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-03-24', 'price': 6593.9, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-03-25', 'price': 6249.9, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2026-03-26', 'price': 6592.9, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-03-27', 'price': 6592.0, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-03-28', 'price': 6592.0, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-03-29', 'price': 6592.0, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-03-30', 'price': 5999.0, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-03-31', 'price': 5998.9, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-04-01', 'price': 5822.32, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2026-04-02', 'price': 5998.0, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-04-03', 'price': 5998.0, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-04-04', 'price': 5998.0, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-04-05', 'price': 5872.37, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2026-04-06', 'price': 5872.37, 'merchantId': 1582}, {'prodId': 13564531, 'date': '2026-04-07', 'price': 5999.4, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2026-04-08', 'price': 5999.0, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-04-09', 'price': 5999.4, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2026-04-10', 'price': 5999.4, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2026-04-11', 'price': 5999.4, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2026-04-12', 'price': 5999.4, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2026-04-13', 'price': 5999.4, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2026-04-14', 'price': 5999.4, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2026-04-15', 'price': 5999.4, 'merchantId': 1582}, {'prodId': 13564531, 'date': '2026-04-16', 'price': 6439.9, 'merchantId': 1582}, {'prodId': 13564531, 'date': '2026-04-17', 'price': 6439.9, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2026-04-18', 'price': 6999.9, 'merchantId': 1582}, {'prodId': 13564531, 'date': '2026-04-19', 'price': 6999.0, 'merchantId': 1582}, {'prodId': 13564531, 'date': '2026-04-20', 'price': 6999.0, 'merchantId': 1582}, {'prodId': 13564531, 'date': '2026-04-21', 'price': 6998.99, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2026-04-22', 'price': 6998.99, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2026-04-23', 'price': 6998.99, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2026-04-24', 'price': 6998.99, 'merchantId': 22905}, {'prodId': 13564531, 'date': '2026-04-25', 'price': 6708.9, 'merchantId': 245}, {'prodId': 13564531, 'date': '2026-04-26', 'price': 6708.9, 'merchantId': 245}, {'prodId': 13564531, 'date': '2026-04-27', 'price': 5999.0, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2026-04-28', 'price': 5999.0, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2026-04-29', 'price': 5999.0, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2026-04-30', 'price': 5999.0, 'merchantId': 20612}, {'prodId': 13564531, 'date': '2026-05-01', 'price': 5998.89, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2026-05-02', 'price': 5997.99, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2026-05-03', 'price': 5865.69, 'merchantId': 245}, {'prodId': 13564531, 'date': '2026-05-04', 'price': 5997.99, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2026-05-05', 'price': 5997.89, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2026-05-06', 'price': 5997.89, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2026-05-07', 'price': 5937.3, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2026-05-08', 'price': 5936.0, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2026-05-09', 'price': 5932.35, 'merchantId': 245}, {'prodId': 13564531, 'date': '2026-05-10', 'price': 5865.69, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-05-11', 'price': 5932.35, 'merchantId': 245}, {'prodId': 13564531, 'date': '2026-05-12', 'price': 5935.89, 'merchantId': 1582}, {'prodId': 13564531, 'date': '2026-05-13', 'price': 5999.0, 'merchantId': 16108}, {'prodId': 13564531, 'date': '2026-05-14', 'price': 5999.0, 'merchantId': 16108}, {'prodId': 13564531, 'date': '2026-05-15', 'price': 5935.89, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2026-05-16', 'price': 5934.99, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2026-05-17', 'price': 5999.0, 'merchantId': 16108}, {'prodId': 13564531, 'date': '2026-05-18', 'price': 5999.0, 'merchantId': 16108}, {'prodId': 13564531, 'date': '2026-05-19', 'price': 5750.91, 'merchantId': 1582}, {'prodId': 13564531, 'date': '2026-05-20', 'price': 5750.91, 'merchantId': 1582}, {'prodId': 13564531, 'date': '2026-05-21', 'price': 5199.0, 'merchantId': 1582}, {'prodId': 13564531, 'date': '2026-05-22', 'price': 5199.0, 'merchantId': 16108}, {'prodId': 13564531, 'date': '2026-05-23', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2026-05-24', 'price': 5199.0, 'merchantId': 16108}, {'prodId': 13564531, 'date': '2026-05-25', 'price': 5199.0, 'merchantId': 16108}, {'prodId': 13564531, 'date': '2026-05-26', 'price': 5199.0, 'merchantId': 16108}, {'prodId': 13564531, 'date': '2026-05-27', 'price': 5199.0, 'merchantId': 16108}, {'prodId': 13564531, 'date': '2026-05-28', 'price': 5199.0, 'merchantId': 16108}, {'prodId': 13564531, 'date': '2026-05-29', 'price': 5199.0, 'merchantId': 16108}, {'prodId': 13564531, 'date': '2026-05-30', 'price': 5141.14, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-05-31', 'price': 5141.14, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-06-01', 'price': 5083.37, 'merchantId': 23326}, {'prodId': 13564531, 'date': '2026-06-02', 'price': 5083.38, 'merchantId': 245}, {'prodId': 13564531, 'date': '2026-06-03', 'price': 5199.0, 'merchantId': 16108}, {'prodId': 13564531, 'date': '2026-06-04', 'price': 5199.0, 'merchantId': 16108}, {'prodId': 13564531, 'date': '2026-06-05', 'price': 5199.0, 'merchantId': 16108}, {'prodId': 13564531, 'date': '2026-06-06', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2026-06-07', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2026-06-08', 'price': 5199.0, 'merchantId': 16108}, {'prodId': 13564531, 'date': '2026-06-09', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2026-06-10', 'price': 5199.0, 'merchantId': 1582}, {'prodId': 13564531, 'date': '2026-06-11', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2026-06-12', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2026-06-13', 'price': 5199.0, 'merchantId': 16108}, {'prodId': 13564531, 'date': '2026-06-14', 'price': 5199.0, 'merchantId': 16108}, {'prodId': 13564531, 'date': '2026-06-15', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2026-06-16', 'price': 5865.68, 'merchantId': 245}, {'prodId': 13564531, 'date': '2026-06-17', 'price': 5699.06, 'merchantId': 245}, {'prodId': 13564531, 'date': '2026-06-18', 'price': 5698.1, 'merchantId': 245}, {'prodId': 13564531, 'date': '2026-06-19', 'price': 5636.35, 'merchantId': 245}, {'prodId': 13564531, 'date': '2026-06-20', 'price': 5625.94, 'merchantId': 245}, {'prodId': 13564531, 'date': '2026-06-21', 'price': 5625.94, 'merchantId': 245}, {'prodId': 13564531, 'date': '2026-06-22', 'price': 5625.94, 'merchantId': 245}, {'prodId': 13564531, 'date': '2026-06-23', 'price': 5624.99, 'merchantId': 245}, {'prodId': 13564531, 'date': '2026-06-24', 'price': 5624.14, 'merchantId': 245}, {'prodId': 13564531, 'date': '2026-06-25', 'price': 5624.14, 'merchantId': 245}, {'prodId': 13564531, 'date': '2026-06-26', 'price': 5449.9, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2026-06-27', 'price': 5623.09, 'merchantId': 245}, {'prodId': 13564531, 'date': '2026-06-28', 'price': 5623.09, 'merchantId': 245}, {'prodId': 13564531, 'date': '2026-06-29', 'price': 5622.24, 'merchantId': 245}, {'prodId': 13564531, 'date': '2026-06-30', 'price': 5622.24, 'merchantId': 245}, {'prodId': 13564531, 'date': '2026-07-01', 'price': 5549.0, 'merchantId': 1582}, {'prodId': 13564531, 'date': '2026-07-02', 'price': 4994.1, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2026-07-03', 'price': 4994.1, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2026-07-04', 'price': 4994.1, 'merchantId': 1582}, {'prodId': 13564531, 'date': '2026-07-05', 'price': 4998.6, 'merchantId': 9385}, {'prodId': 13564531, 'date': '2026-07-06', 'price': 4994.1, 'merchantId': 1582}, {'prodId': 13564531, 'date': '2026-07-07', 'price': 4994.1, 'merchantId': 9385}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13993303, 'date': '2025-10-10', 'price': 1186.54, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2025-10-11', 'price': 1122.26, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2025-10-12', 'price': 1101.05, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2025-10-13', 'price': 1101.05, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2025-10-14', 'price': 1044.05, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2025-10-15', 'price': 1044.05, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2025-10-16', 'price': 1049.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-10-17', 'price': 1049.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-10-18', 'price': 1049.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-10-19', 'price': 1049.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-10-20', 'price': 1049.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-10-21', 'price': 1049.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-10-22', 'price': 1049.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-10-23', 'price': 1049.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-10-24', 'price': 1049.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-10-25', 'price': 1049.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-10-26', 'price': 1049.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-10-27', 'price': 1049.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-10-28', 'price': 1049.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-10-29', 'price': 1049.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-10-30', 'price': 1049.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-10-31', 'price': 1049.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-11-01', 'price': 1049.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-11-02', 'price': 1049.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-11-03', 'price': 1049.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-11-04', 'price': 1022.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2025-11-05', 'price': 1022.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2025-11-06', 'price': 1022.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2025-11-07', 'price': 1022.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2025-11-08', 'price': 1022.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2025-11-09', 'price': 1022.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2025-11-10', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-11-11', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-11-12', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-11-13', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-11-14', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-11-15', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-11-16', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-11-17', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-11-18', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-11-19', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-11-20', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-11-21', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-11-22', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-11-23', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-11-24', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-11-25', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-11-26', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-11-27', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-11-28', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-11-29', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-11-30', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-12-01', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-12-02', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-12-03', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-12-04', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-12-05', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-12-06', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-12-07', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-12-08', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-12-09', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-12-10', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-12-11', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-12-12', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-12-13', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-12-14', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2025-12-15', 'price': 1050.9, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2025-12-16', 'price': 1050.9, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2025-12-17', 'price': 1050.9, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2025-12-18', 'price': 1050.9, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2025-12-19', 'price': 1104.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2025-12-20', 'price': 1104.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2025-12-21', 'price': 1104.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2025-12-22', 'price': 1104.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2025-12-23', 'price': 1104.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2025-12-24', 'price': 1104.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2025-12-25', 'price': 1104.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2025-12-26', 'price': 1104.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2025-12-27', 'price': 1104.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2025-12-28', 'price': 1104.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2025-12-29', 'price': 1104.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2025-12-30', 'price': 1104.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2025-12-31', 'price': 1104.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-01-01', 'price': 1104.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-01-02', 'price': 1104.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-01-03', 'price': 1104.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-01-04', 'price': 1104.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-01-05', 'price': 1104.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-01-06', 'price': 1104.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-01-07', 'price': 1104.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-01-08', 'price': 1104.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-01-09', 'price': 1104.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-01-10', 'price': 1104.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-01-11', 'price': 1104.07, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-01-12', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-01-13', 'price': 1078.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-01-14', 'price': 1078.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-01-15', 'price': 1078.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-01-16', 'price': 1078.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-01-17', 'price': 1078.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-01-18', 'price': 1078.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-01-19', 'price': 1078.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-01-20', 'price': 1078.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-01-21', 'price': 1078.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-01-22', 'price': 1078.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-01-23', 'price': 1078.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-01-24', 'price': 1078.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-01-25', 'price': 1078.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-01-26', 'price': 1078.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-01-27', 'price': 1078.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-01-28', 'price': 1078.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-01-29', 'price': 1078.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-01-30', 'price': 1078.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-01-31', 'price': 1078.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-01', 'price': 1078.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-02', 'price': 1078.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-03', 'price': 1078.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-04', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-05', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-06', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-07', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-08', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-09', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-10', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-11', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-12', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-13', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-14', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-15', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-16', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-17', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-18', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-19', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-20', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-21', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-22', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-23', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-24', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-25', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-26', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-27', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-02-28', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-03-01', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-03-02', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-03-03', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-03-04', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-03-05', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-03-06', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-03-07', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-03-08', 'price': 1044.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-03-09', 'price': 1008.9999999999999, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-03-10', 'price': 1008.9999999999999, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-03-11', 'price': 1008.9999999999999, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-03-12', 'price': 1008.9999999999999, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-03-13', 'price': 1008.9999999999999, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-03-14', 'price': 1008.9999999999999, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-03-15', 'price': 1045.1599999999999, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-03-16', 'price': 1045.1599999999999, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-03-17', 'price': 1045.1599999999999, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-03-18', 'price': 1045.1599999999999, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-03-19', 'price': 1045.1599999999999, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-03-20', 'price': 1045.1599999999999, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-03-21', 'price': 1045.1599999999999, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-03-22', 'price': 1045.1599999999999, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-03-23', 'price': 1045.1599999999999, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-03-24', 'price': 1098.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-03-25', 'price': 1098.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-03-26', 'price': 1098.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-03-27', 'price': 1098.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-03-28', 'price': 1098.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-03-29', 'price': 1098.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-03-30', 'price': 1098.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-03-31', 'price': 1098.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-04-01', 'price': 1098.0, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-04-02', 'price': 1098.0, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-04-03', 'price': 1098.0, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-04-04', 'price': 1098.0, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-04-05', 'price': 1098.0, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-04-06', 'price': 1098.0, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-04-07', 'price': 1098.0, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-04-08', 'price': 1098.0, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-04-09', 'price': 1098.0, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-04-10', 'price': 1098.0, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-04-11', 'price': 1098.0, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-04-12', 'price': 1098.0, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-04-13', 'price': 1098.0, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-04-14', 'price': 1098.0, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-04-15', 'price': 1098.0, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-04-16', 'price': 1098.0, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-04-17', 'price': 1098.0, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-04-18', 'price': 1098.0, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-04-19', 'price': 1098.0, 'merchantId': 15125}, {'prodId': 13993303, 'date': '2026-04-20', 'price': 1093.5, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-04-21', 'price': 1093.5, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-04-22', 'price': 1093.5, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-04-23', 'price': 1093.5, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-04-24', 'price': 1034.55, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-04-25', 'price': 1034.55, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-04-26', 'price': 1034.55, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-04-27', 'price': 1034.55, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-04-28', 'price': 1117.99, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-04-29', 'price': 1117.99, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-04-30', 'price': 1117.99, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-05-01', 'price': 1117.99, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-05-02', 'price': 1117.99, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-05-03', 'price': 1117.99, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-05-04', 'price': 1117.99, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-05-05', 'price': 1117.99, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-05-06', 'price': 1160.99, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-05-07', 'price': 1160.99, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-05-08', 'price': 1160.99, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-05-09', 'price': 1160.99, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-05-10', 'price': 1160.99, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-05-11', 'price': 1129.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-05-12', 'price': 1129.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-05-13', 'price': 1129.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-05-14', 'price': 1129.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-05-15', 'price': 1129.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-05-16', 'price': 1129.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-05-17', 'price': 1129.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-05-18', 'price': 1129.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-05-19', 'price': 1129.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-05-20', 'price': 1129.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-05-21', 'price': 1129.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-05-22', 'price': 1129.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-05-23', 'price': 1129.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-05-24', 'price': 1129.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-05-25', 'price': 1129.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-05-26', 'price': 1129.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-05-27', 'price': 1129.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-05-28', 'price': 1129.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-05-29', 'price': 1129.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-05-30', 'price': 1129.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-05-31', 'price': 1129.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-06-01', 'price': 1129.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-06-02', 'price': 1124.97, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-06-03', 'price': 1124.97, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-06-04', 'price': 1124.97, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-06-05', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-06-06', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-06-07', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-06-08', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-06-09', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-06-10', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-06-11', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-06-12', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-06-13', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-06-14', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-06-15', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-06-16', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-06-17', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-06-18', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-06-19', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-06-20', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-06-21', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-06-22', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-06-23', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-06-24', 'price': 1119.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-06-25', 'price': 1119.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-06-26', 'price': 1119.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-06-27', 'price': 1119.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-06-28', 'price': 1119.0, 'merchantId': 16623}, {'prodId': 13993303, 'date': '2026-06-29', 'price': 939.24, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-06-30', 'price': 939.24, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-07-01', 'price': 939.24, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-07-02', 'price': 994.49, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-07-03', 'price': 994.49, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-07-04', 'price': 994.49, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-07-05', 'price': 994.49, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-07-06', 'price': 915.44, 'merchantId': 22905}, {'prodId': 13993303, 'date': '2026-07-07', 'price': 915.44, 'merchantId': 22905}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13992308, 'date': '2025-07-07', 'price': 3399.15, 'merchantId': 20583}, {'prodId': 13992308, 'date': '2025-07-08', 'price': 3499.1, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-07-09', 'price': 3499.1, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-07-10', 'price': 3499.1, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-07-11', 'price': 3311.89, 'merchantId': 9385}, {'prodId': 13992308, 'date': '2025-07-12', 'price': 3311.89, 'merchantId': 9385}, {'prodId': 13992308, 'date': '2025-07-13', 'price': 3499.1, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-07-14', 'price': 3499.1, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-07-15', 'price': 3499.1, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-07-16', 'price': 3499.1, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-07-17', 'price': 3499.1, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-07-18', 'price': 3499.1, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-07-19', 'price': 3499.1, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-07-20', 'price': 3499.1, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-07-21', 'price': 3499.1, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-07-22', 'price': 3499.1, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-07-23', 'price': 3499.1, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-07-24', 'price': 3450.0, 'merchantId': 9385}, {'prodId': 13992308, 'date': '2025-07-25', 'price': 3105.01, 'merchantId': 9385}, {'prodId': 13992308, 'date': '2025-07-26', 'price': 3105.0, 'merchantId': 9385}, {'prodId': 13992308, 'date': '2025-07-27', 'price': 3105.0, 'merchantId': 1582}, {'prodId': 13992308, 'date': '2025-07-28', 'price': 3104.99, 'merchantId': 9385}, {'prodId': 13992308, 'date': '2025-07-29', 'price': 3104.99, 'merchantId': 9385}, {'prodId': 13992308, 'date': '2025-07-30', 'price': 3105.0, 'merchantId': 1582}, {'prodId': 13992308, 'date': '2025-07-31', 'price': 3105.0, 'merchantId': 1582}, {'prodId': 13992308, 'date': '2025-08-01', 'price': 3148.2, 'merchantId': 23199}, {'prodId': 13992308, 'date': '2025-08-02', 'price': 3148.2, 'merchantId': 23199}, {'prodId': 13992308, 'date': '2025-08-03', 'price': 3148.2, 'merchantId': 23199}, {'prodId': 13992308, 'date': '2025-08-04', 'price': 3148.2, 'merchantId': 23199}, {'prodId': 13992308, 'date': '2025-08-05', 'price': 3105.0, 'merchantId': 1582}, {'prodId': 13992308, 'date': '2025-08-06', 'price': 3105.0, 'merchantId': 1582}, {'prodId': 13992308, 'date': '2025-08-07', 'price': 3148.2, 'merchantId': 23199}, {'prodId': 13992308, 'date': '2025-08-08', 'price': 3098.0, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2025-08-09', 'price': 3098.0, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2025-08-10', 'price': 3098.0, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2025-08-11', 'price': 3098.0, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2025-08-12', 'price': 3098.0, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2025-08-13', 'price': 3098.0, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2025-08-14', 'price': 3098.0, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2025-08-15', 'price': 3098.0, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2025-08-16', 'price': 3098.0, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2025-08-17', 'price': 3098.0, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2025-08-18', 'price': 3098.0, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2025-08-19', 'price': 3098.0, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2025-08-20', 'price': 3098.0, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2025-08-21', 'price': 3098.0, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2025-08-22', 'price': 3098.0, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2025-08-23', 'price': 3098.0, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2025-08-24', 'price': 3098.0, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2025-08-25', 'price': 3098.0, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2025-08-26', 'price': 3099.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2025-08-27', 'price': 3099.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2025-08-28', 'price': 3099.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2025-08-29', 'price': 3099.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2025-08-30', 'price': 3099.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2025-08-31', 'price': 3099.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2025-09-01', 'price': 3099.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2025-09-02', 'price': 3099.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2025-09-03', 'price': 3099.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2025-09-04', 'price': 3099.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2025-09-05', 'price': 3099.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2025-09-06', 'price': 3099.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2025-09-07', 'price': 3099.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2025-09-08', 'price': 3099.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2025-09-09', 'price': 2999.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-09-10', 'price': 2999.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-09-11', 'price': 2999.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-09-12', 'price': 2989.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-09-13', 'price': 2989.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-09-14', 'price': 2989.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-09-15', 'price': 2989.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-09-16', 'price': 2959.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-09-17', 'price': 2959.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-09-18', 'price': 2989.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-09-19', 'price': 2989.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-09-20', 'price': 2989.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-09-21', 'price': 2989.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-09-22', 'price': 2775.07, 'merchantId': 9385}, {'prodId': 13992308, 'date': '2025-09-23', 'price': 2775.07, 'merchantId': 9385}, {'prodId': 13992308, 'date': '2025-09-24', 'price': 2749.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2025-09-25', 'price': 2748.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2025-09-26', 'price': 2748.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2025-09-27', 'price': 2748.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2025-09-28', 'price': 2748.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2025-09-29', 'price': 2746.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-09-30', 'price': 2746.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-10-01', 'price': 2746.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-10-02', 'price': 2746.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-10-03', 'price': 2746.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-10-04', 'price': 2746.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-10-05', 'price': 2744.1, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2025-10-06', 'price': 2743.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2025-10-07', 'price': 2699.1, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2025-10-08', 'price': 2699.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2025-10-09', 'price': 2699.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2025-10-10', 'price': 2699.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2025-10-11', 'price': 2699.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2025-10-12', 'price': 2699.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2025-10-13', 'price': 2699.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2025-10-14', 'price': 2746.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-10-15', 'price': 2691.0, 'merchantId': 34}, {'prodId': 13992308, 'date': '2025-10-16', 'price': 2533.92, 'merchantId': 9385}, {'prodId': 13992308, 'date': '2025-10-17', 'price': 2533.92, 'merchantId': 9385}, {'prodId': 13992308, 'date': '2025-10-18', 'price': 2746.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-10-19', 'price': 2746.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-10-20', 'price': 2746.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-10-21', 'price': 2646.09, 'merchantId': 9385}, {'prodId': 13992308, 'date': '2025-10-22', 'price': 2637.0, 'merchantId': 34}, {'prodId': 13992308, 'date': '2025-10-23', 'price': 2636.0, 'merchantId': 34}, {'prodId': 13992308, 'date': '2025-10-24', 'price': 2635.0, 'merchantId': 34}, {'prodId': 13992308, 'date': '2025-10-25', 'price': 2634.98, 'merchantId': 1582}, {'prodId': 13992308, 'date': '2025-10-26', 'price': 2634.98, 'merchantId': 1582}, {'prodId': 13992308, 'date': '2025-10-27', 'price': 2633.0, 'merchantId': 34}, {'prodId': 13992308, 'date': '2025-10-28', 'price': 2631.99, 'merchantId': 9385}, {'prodId': 13992308, 'date': '2025-10-29', 'price': 2599.0, 'merchantId': 34}, {'prodId': 13992308, 'date': '2025-10-30', 'price': 2599.0, 'merchantId': 34}, {'prodId': 13992308, 'date': '2025-10-31', 'price': 2598.0, 'merchantId': 34}, {'prodId': 13992308, 'date': '2025-11-01', 'price': 2598.0, 'merchantId': 34}, {'prodId': 13992308, 'date': '2025-11-02', 'price': 2598.0, 'merchantId': 34}, {'prodId': 13992308, 'date': '2025-11-03', 'price': 2549.0, 'merchantId': 16108}, {'prodId': 13992308, 'date': '2025-11-04', 'price': 2549.0, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2025-11-05', 'price': 2547.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2025-11-06', 'price': 2539.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2025-11-07', 'price': 2538.99, 'merchantId': 1582}, {'prodId': 13992308, 'date': '2025-11-08', 'price': 2538.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2025-11-09', 'price': 2538.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2025-11-10', 'price': 2499.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2025-11-11', 'price': 2499.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2025-11-12', 'price': 2498.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2025-11-13', 'price': 2497.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2025-11-14', 'price': 2496.99, 'merchantId': 1582}, {'prodId': 13992308, 'date': '2025-11-15', 'price': 2497.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2025-11-16', 'price': 2497.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2025-11-17', 'price': 2495.99, 'merchantId': 9385}, {'prodId': 13992308, 'date': '2025-11-18', 'price': 2495.99, 'merchantId': 1582}, {'prodId': 13992308, 'date': '2025-11-19', 'price': 2459.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-11-20', 'price': 2459.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-11-21', 'price': 2459.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-11-22', 'price': 2459.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-11-23', 'price': 2459.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-11-24', 'price': 2459.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-11-25', 'price': 2459.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-11-26', 'price': 2429.02, 'merchantId': 9385}, {'prodId': 13992308, 'date': '2025-11-27', 'price': 2428.2, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2025-11-28', 'price': 2398.98, 'merchantId': 2}, {'prodId': 13992308, 'date': '2025-11-29', 'price': 2397.92, 'merchantId': 1582}, {'prodId': 13992308, 'date': '2025-11-30', 'price': 2397.92, 'merchantId': 1582}, {'prodId': 13992308, 'date': '2025-12-01', 'price': 2397.87, 'merchantId': 1582}, {'prodId': 13992308, 'date': '2025-12-02', 'price': 2397.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2025-12-03', 'price': 2397.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2025-12-04', 'price': 2428.2, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2025-12-05', 'price': 2549.0, 'merchantId': 20612}, {'prodId': 13992308, 'date': '2025-12-06', 'price': 2549.0, 'merchantId': 20612}, {'prodId': 13992308, 'date': '2025-12-07', 'price': 2549.0, 'merchantId': 20612}, {'prodId': 13992308, 'date': '2025-12-08', 'price': 2519.1, 'merchantId': 2}, {'prodId': 13992308, 'date': '2025-12-09', 'price': 2518.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2025-12-10', 'price': 2518.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2025-12-11', 'price': 2499.9, 'merchantId': 1582}, {'prodId': 13992308, 'date': '2025-12-12', 'price': 2378.11, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-12-13', 'price': 2378.11, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-12-14', 'price': 2378.11, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-12-15', 'price': 2378.11, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-12-16', 'price': 2378.11, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-12-17', 'price': 2378.11, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-12-18', 'price': 2378.11, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-12-19', 'price': 2378.11, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-12-20', 'price': 2378.11, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-12-21', 'price': 2378.11, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-12-22', 'price': 2378.11, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-12-23', 'price': 2378.11, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-12-24', 'price': 2378.11, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-12-25', 'price': 2378.11, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-12-26', 'price': 2378.11, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-12-27', 'price': 2378.11, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-12-28', 'price': 2378.11, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-12-29', 'price': 2378.11, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-12-30', 'price': 2378.11, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2025-12-31', 'price': 2378.11, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2026-01-01', 'price': 2378.11, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2026-01-02', 'price': 2378.11, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2026-01-03', 'price': 2378.11, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2026-01-04', 'price': 2638.24, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2026-01-05', 'price': 2499.9, 'merchantId': 1582}, {'prodId': 13992308, 'date': '2026-01-06', 'price': 2638.24, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2026-01-07', 'price': 2638.24, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2026-01-08', 'price': 2638.24, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2026-01-09', 'price': 2638.24, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2026-01-10', 'price': 2638.24, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2026-01-11', 'price': 2638.24, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2026-01-12', 'price': 2609.1, 'merchantId': 23254}, {'prodId': 13992308, 'date': '2026-01-13', 'price': 2609.1, 'merchantId': 23254}, {'prodId': 13992308, 'date': '2026-01-14', 'price': 2638.24, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2026-01-15', 'price': 3499.0, 'merchantId': 20612}, {'prodId': 13992308, 'date': '2026-01-16', 'price': 3099.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-01-17', 'price': 3099.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-01-18', 'price': 3099.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-01-19', 'price': 3099.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-01-20', 'price': 3099.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-01-21', 'price': 2679.9, 'merchantId': 1582}, {'prodId': 13992308, 'date': '2026-01-22', 'price': 2679.9, 'merchantId': 1582}, {'prodId': 13992308, 'date': '2026-01-23', 'price': 2679.9, 'merchantId': 1582}, {'prodId': 13992308, 'date': '2026-01-24', 'price': 2679.9, 'merchantId': 1582}, {'prodId': 13992308, 'date': '2026-01-25', 'price': 2679.9, 'merchantId': 1582}, {'prodId': 13992308, 'date': '2026-01-26', 'price': 2679.9, 'merchantId': 1582}, {'prodId': 13992308, 'date': '2026-01-27', 'price': 2679.9, 'merchantId': 1582}, {'prodId': 13992308, 'date': '2026-01-28', 'price': 2679.9, 'merchantId': 1582}, {'prodId': 13992308, 'date': '2026-01-29', 'price': 2799.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-01-30', 'price': 2799.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-01-31', 'price': 2799.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-02-01', 'price': 2799.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-02-02', 'price': 2799.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-02-03', 'price': 2798.9, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-02-04', 'price': 2798.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-02-05', 'price': 2799.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-02-06', 'price': 2799.0, 'merchantId': 16108}, {'prodId': 13992308, 'date': '2026-02-07', 'price': 3066.93, 'merchantId': 16108}, {'prodId': 13992308, 'date': '2026-02-08', 'price': 3066.93, 'merchantId': 16108}, {'prodId': 13992308, 'date': '2026-02-09', 'price': 3066.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-02-10', 'price': 3066.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-02-11', 'price': 2859.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-02-12', 'price': 2859.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-02-13', 'price': 2859.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-02-14', 'price': 2859.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-02-15', 'price': 2859.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-02-16', 'price': 2774.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-02-17', 'price': 2774.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-02-18', 'price': 2774.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-02-19', 'price': 2859.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-02-20', 'price': 2859.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-02-21', 'price': 2858.9, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-02-22', 'price': 2858.9, 'merchantId': 34}, {'prodId': 13992308, 'date': '2026-02-23', 'price': 2858.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-02-24', 'price': 2949.0, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-02-25', 'price': 2857.9, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-02-26', 'price': 2742.57, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-02-27', 'price': 2742.57, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-02-28', 'price': 2744.1, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-03-01', 'price': 2744.1, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-03-02', 'price': 2744.1, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-03-03', 'price': 2744.1, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-03-04', 'price': 2725.06, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-03-05', 'price': 2725.06, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-03-06', 'price': 2725.06, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-03-07', 'price': 2725.06, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-03-08', 'price': 2725.06, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-03-09', 'price': 2725.06, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-03-10', 'price': 2725.06, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-03-11', 'price': 2725.06, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-03-12', 'price': 2725.06, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-03-13', 'price': 2725.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-03-14', 'price': 2725.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-03-15', 'price': 2725.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-03-16', 'price': 2725.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-03-17', 'price': 2725.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-03-18', 'price': 2609.06, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-03-19', 'price': 2609.06, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-03-20', 'price': 2725.06, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-03-21', 'price': 2725.06, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-03-22', 'price': 2725.06, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-03-23', 'price': 2725.06, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-03-24', 'price': 2725.06, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-03-25', 'price': 2725.06, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-03-26', 'price': 2725.06, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-03-27', 'price': 2725.06, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-03-28', 'price': 2725.06, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-03-29', 'price': 2725.06, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-03-30', 'price': 2725.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-03-31', 'price': 2699.1, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-04-01', 'price': 2698.9, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-04-02', 'price': 2699.1, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-04-03', 'price': 2699.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-04-04', 'price': 2699.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-04-05', 'price': 2699.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-04-06', 'price': 2698.9, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-04-07', 'price': 2697.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-04-08', 'price': 2696.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-04-09', 'price': 2696.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-04-10', 'price': 2695.9, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-04-11', 'price': 2695.9, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-04-12', 'price': 2695.9, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-04-13', 'price': 2695.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-04-14', 'price': 2694.9, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-04-15', 'price': 2694.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-04-16', 'price': 2694.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-04-17', 'price': 2693.9, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-04-18', 'price': 2693.9, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-04-19', 'price': 2693.9, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-04-20', 'price': 2599.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-04-21', 'price': 2599.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-04-22', 'price': 2599.0, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-04-23', 'price': 2598.9, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-04-24', 'price': 2520.92, 'merchantId': 9385}, {'prodId': 13992308, 'date': '2026-04-25', 'price': 2598.9, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-04-26', 'price': 2598.9, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-04-27', 'price': 2598.9, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-04-28', 'price': 2598.9, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-04-29', 'price': 2598.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-04-30', 'price': 2597.9, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-05-01', 'price': 2597.9, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-05-02', 'price': 2597.9, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-05-03', 'price': 2597.9, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-05-04', 'price': 2597.49, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-05-05', 'price': 2597.49, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-05-06', 'price': 2597.49, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-05-07', 'price': 2597.0, 'merchantId': 2}, {'prodId': 13992308, 'date': '2026-05-08', 'price': 2595.99, 'merchantId': 9385}, {'prodId': 13992308, 'date': '2026-05-09', 'price': 2595.99, 'merchantId': 9385}, {'prodId': 13992308, 'date': '2026-05-10', 'price': 2595.99, 'merchantId': 9385}, {'prodId': 13992308, 'date': '2026-05-11', 'price': 2595.99, 'merchantId': 9385}, {'prodId': 13992308, 'date': '2026-05-12', 'price': 2595.99, 'merchantId': 9385}, {'prodId': 13992308, 'date': '2026-05-13', 'price': 2595.99, 'merchantId': 9385}, {'prodId': 13992308, 'date': '2026-05-14', 'price': 2596.0, 'merchantId': 34}, {'prodId': 13992308, 'date': '2026-05-15', 'price': 2596.0, 'merchantId': 34}, {'prodId': 13992308, 'date': '2026-05-16', 'price': 2596.0, 'merchantId': 34}, {'prodId': 13992308, 'date': '2026-05-17', 'price': 2595.99, 'merchantId': 9385}, {'prodId': 13992308, 'date': '2026-05-18', 'price': 2596.0, 'merchantId': 34}, {'prodId': 13992308, 'date': '2026-05-19', 'price': 2596.0, 'merchantId': 34}, {'prodId': 13992308, 'date': '2026-05-20', 'price': 2596.0, 'merchantId': 4}, {'prodId': 13992308, 'date': '2026-05-21', 'price': 2596.0, 'merchantId': 4}, {'prodId': 13992308, 'date': '2026-05-22', 'price': 2561.1, 'merchantId': 9385}, {'prodId': 13992308, 'date': '2026-05-23', 'price': 2693.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2026-05-24', 'price': 2693.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2026-05-25', 'price': 2693.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2026-05-26', 'price': 2679.8999999999996, 'merchantId': 1582}, {'prodId': 13992308, 'date': '2026-05-27', 'price': 2679.8999999999996, 'merchantId': 9385}, {'prodId': 13992308, 'date': '2026-05-28', 'price': 2693.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2026-05-29', 'price': 2299.0, 'merchantId': 1582}, {'prodId': 13992308, 'date': '2026-05-30', 'price': 2693.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2026-05-31', 'price': 2693.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2026-06-01', 'price': 2693.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2026-06-02', 'price': 2693.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2026-06-03', 'price': 2693.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2026-06-04', 'price': 2693.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2026-06-05', 'price': 1953.0, 'merchantId': 23254}, {'prodId': 13992308, 'date': '2026-06-06', 'price': 1953.0, 'merchantId': 23254}, {'prodId': 13992308, 'date': '2026-06-07', 'price': 1953.0, 'merchantId': 23254}, {'prodId': 13992308, 'date': '2026-06-08', 'price': 1953.0, 'merchantId': 23254}, {'prodId': 13992308, 'date': '2026-06-09', 'price': 2585.09, 'merchantId': 9385}, {'prodId': 13992308, 'date': '2026-06-10', 'price': 2693.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2026-06-11', 'price': 2799.99, 'merchantId': 9385}, {'prodId': 13992308, 'date': '2026-06-12', 'price': 2693.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2026-06-13', 'price': 2693.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2026-06-14', 'price': 2971.23, 'merchantId': 22905}, {'prodId': 13992308, 'date': '2026-06-15', 'price': 2693.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2026-06-16', 'price': 2693.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2026-06-17', 'price': 2693.0, 'merchantId': 21627}, {'prodId': 13992308, 'date': '2026-06-18', 'price': 2913.06, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-06-19', 'price': 2249.9, 'merchantId': 20612}, {'prodId': 13992308, 'date': '2026-06-20', 'price': 2249.9, 'merchantId': 20612}, {'prodId': 13992308, 'date': '2026-06-21', 'price': 2249.9, 'merchantId': 20612}, {'prodId': 13992308, 'date': '2026-06-22', 'price': 2249.9, 'merchantId': 20612}, {'prodId': 13992308, 'date': '2026-06-23', 'price': 2249.9, 'merchantId': 20612}, {'prodId': 13992308, 'date': '2026-06-24', 'price': 2837.14, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-06-25', 'price': 2913.06, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-06-26', 'price': 2913.06, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-06-27', 'price': 2913.06, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-06-28', 'price': 2913.06, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-06-29', 'price': 2913.06, 'merchantId': 23326}, {'prodId': 13992308, 'date': '2026-06-30', 'price': 2937.0, 'merchantId': 1582}, {'prodId': 13992308, 'date': '2026-07-01', 'price': 2969.1, 'merchantId': 22902}, {'prodId': 13992308, 'date': '2026-07-02', 'price': 2591.1, 'merchantId': 20612}, {'prodId': 13992308, 'date': '2026-07-03', 'price': 2591.1, 'merchantId': 20612}, {'prodId': 13992308, 'date': '2026-07-04', 'price': 2591.1, 'merchantId': 20612}, {'prodId': 13992308, 'date': '2026-07-05', 'price': 2591.1, 'merchantId': 20612}, {'prodId': 13992308, 'date': '2026-07-06', 'price': 2591.1, 'merchantId': 20612}, {'prodId': 13992308, 'date': '2026-07-07', 'price': 2591.1, 'merchantId': 20612}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 12534152, 'date': '2025-07-07', 'price': 8639.1, 'merchantId': 34}, {'prodId': 12534152, 'date': '2025-07-08', 'price': 8639.1, 'merchantId': 34}, {'prodId': 12534152, 'date': '2025-07-09', 'price': 8639.1, 'merchantId': 34}, {'prodId': 12534152, 'date': '2025-07-10', 'price': 8639.1, 'merchantId': 34}, {'prodId': 12534152, 'date': '2025-07-11', 'price': 8639.1, 'merchantId': 34}, {'prodId': 12534152, 'date': '2025-07-12', 'price': 8639.1, 'merchantId': 34}, {'prodId': 12534152, 'date': '2025-07-13', 'price': 8639.1, 'merchantId': 34}, {'prodId': 12534152, 'date': '2025-07-14', 'price': 8639.1, 'merchantId': 34}, {'prodId': 12534152, 'date': '2025-07-15', 'price': 8639.1, 'merchantId': 34}, {'prodId': 12534152, 'date': '2025-07-16', 'price': 8639.1, 'merchantId': 34}, {'prodId': 12534152, 'date': '2025-07-17', 'price': 8639.1, 'merchantId': 34}, {'prodId': 12534152, 'date': '2025-07-18', 'price': 8639.1, 'merchantId': 34}, {'prodId': 12534152, 'date': '2025-07-19', 'price': 8639.1, 'merchantId': 34}, {'prodId': 12534152, 'date': '2025-07-20', 'price': 8639.1, 'merchantId': 34}, {'prodId': 12534152, 'date': '2025-07-21', 'price': 8639.1, 'merchantId': 34}, {'prodId': 12534152, 'date': '2025-07-22', 'price': 8639.1, 'merchantId': 34}, {'prodId': 12534152, 'date': '2025-07-23', 'price': 8639.1, 'merchantId': 34}, {'prodId': 12534152, 'date': '2025-07-24', 'price': 8639.1, 'merchantId': 34}, {'prodId': 12534152, 'date': '2025-07-25', 'price': 8639.1, 'merchantId': 34}, {'prodId': 12534152, 'date': '2025-07-26', 'price': 8639.1, 'merchantId': 34}, {'prodId': 12534152, 'date': '2025-07-27', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-07-28', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-07-29', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-07-30', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-07-31', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-01', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-02', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-03', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-04', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-05', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-06', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-07', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-08', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-09', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-10', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-11', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-12', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-13', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-14', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-15', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-16', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-17', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-18', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-19', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-20', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-21', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-22', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-23', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-24', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-25', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-26', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-27', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-28', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-29', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-30', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-08-31', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-09-01', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-09-02', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-09-03', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-09-04', 'price': 6933.99, 'merchantId': 16108}, {'prodId': 12534152, 'date': '2025-09-05', 'price': 6933.99, 'merchantId': 16108}, {'prodId': 12534152, 'date': '2025-09-06', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-09-07', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-09-08', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-09-09', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-09-10', 'price': 6933.99, 'merchantId': 16108}, {'prodId': 12534152, 'date': '2025-09-11', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-09-12', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-09-13', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-09-14', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-09-15', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-09-16', 'price': 6933.99, 'merchantId': 16108}, {'prodId': 12534152, 'date': '2025-09-17', 'price': 6933.99, 'merchantId': 16108}, {'prodId': 12534152, 'date': '2025-09-18', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-09-19', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-09-20', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-09-21', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-09-22', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-09-23', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-09-24', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-09-25', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-09-26', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-09-27', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-09-28', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-09-29', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-09-30', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-01', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-02', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-03', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-04', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-05', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-06', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-07', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-08', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-09', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-10', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-11', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-12', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-13', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-14', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-15', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-16', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-17', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-18', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-19', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-20', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-21', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-22', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-23', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-24', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-25', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-26', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-27', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-28', 'price': 8639.1, 'merchantId': 2}, {'prodId': 12534152, 'date': '2025-10-29', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-10-30', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-10-31', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-01', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-02', 'price': 4774.44, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-03', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-04', 'price': 4774.44, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-05', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-06', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-07', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-08', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-09', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-10', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-11', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-12', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-13', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-14', 'price': 4719.78, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-15', 'price': 4708.89, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-16', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-17', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-18', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-19', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-20', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-21', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-22', 'price': 4699.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-23', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-24', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-25', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-26', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-27', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-28', 'price': 6259.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-11-29', 'price': 6259.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-12-01', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-12-06', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-12-07', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-12-08', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-12-09', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-12-10', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-12-11', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-12-12', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-12-14', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-12-15', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-12-16', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-12-17', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-12-18', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-12-19', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-12-20', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-12-21', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-12-22', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-12-23', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-12-24', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-12-25', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-12-26', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-12-27', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-12-28', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-12-29', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-12-30', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2025-12-31', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-01', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-02', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-03', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-04', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-05', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-06', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-07', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-08', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-09', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-10', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-11', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-12', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-13', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-14', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-15', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-16', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-17', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-18', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-19', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-20', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-21', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-22', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-23', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-24', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-25', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-26', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-27', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-28', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-29', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-30', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-01-31', 'price': 6449.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-02-01', 'price': 6639.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-02-02', 'price': 6639.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-02-03', 'price': 6639.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-02-04', 'price': 6639.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-03-09', 'price': 5999.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-03-10', 'price': 5999.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-03-11', 'price': 5999.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-03-12', 'price': 5643.37, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-03-13', 'price': 5643.37, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-03-14', 'price': 5643.37, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-03-18', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-03-19', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-03-20', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-03-21', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-03-22', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-03-23', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-03-24', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-03-25', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-03-26', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-03-27', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-03-28', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-03-29', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-03-30', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-03-31', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-04-01', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-04-02', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-04-03', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-04-04', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-04-05', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-04-06', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-04-07', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-04-08', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-04-09', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-04-10', 'price': 6251.07, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-04-11', 'price': 6251.07, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-04-12', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-04-13', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-04-14', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-04-15', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-04-16', 'price': 9999.0, 'merchantId': 34}, {'prodId': 12534152, 'date': '2026-04-17', 'price': 9999.0, 'merchantId': 34}, {'prodId': 12534152, 'date': '2026-04-19', 'price': 5659.99, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-04-20', 'price': 5659.99, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-04-21', 'price': 5659.99, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-04-22', 'price': 5659.99, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-04-23', 'price': 5659.99, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-04-24', 'price': 6109.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-04-25', 'price': 6109.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-04-26', 'price': 6109.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-04-27', 'price': 6109.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-04-28', 'price': 6109.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-04-29', 'price': 6109.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-05-17', 'price': 6109.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-05-18', 'price': 6109.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-05-19', 'price': 6109.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-05-20', 'price': 5659.99, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-05-21', 'price': 5659.99, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-05-22', 'price': 5659.99, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-05-23', 'price': 5880.27, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-05-24', 'price': 5880.27, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-05-25', 'price': 5880.27, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-05-26', 'price': 5880.27, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-05-27', 'price': 5427.07, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-05-28', 'price': 5427.07, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-05-29', 'price': 5427.07, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-06-03', 'price': 6109.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-06-04', 'price': 6109.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-06-05', 'price': 5427.07, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-06-06', 'price': 5427.07, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-06-11', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-06-12', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-06-13', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-06-14', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-06-15', 'price': 6289.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-06-16', 'price': 5427.07, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-06-17', 'price': 5427.07, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-06-18', 'price': 5427.07, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-06-19', 'price': 5427.07, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-06-20', 'price': 5427.07, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-06-21', 'price': 5427.07, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-06-22', 'price': 6109.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-06-23', 'price': 6109.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-06-24', 'price': 6109.0, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-06-25', 'price': 5427.07, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-06-26', 'price': 5427.07, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-06-27', 'price': 5427.07, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-06-28', 'price': 5427.07, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-06-29', 'price': 5427.07, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-06-30', 'price': 5427.07, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-07-01', 'price': 5797.99, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-07-02', 'price': 5642.99, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-07-03', 'price': 5642.99, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-07-04', 'price': 5642.99, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-07-05', 'price': 5642.99, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-07-06', 'price': 5642.99, 'merchantId': 1582}, {'prodId': 12534152, 'date': '2026-07-07', 'price': 5642.99, 'merchantId': 1582}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13991987, 'date': '2025-07-07', 'price': 1646.0, 'merchantId': 34}, {'prodId': 13991987, 'date': '2025-07-08', 'price': 1646.1, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2025-07-09', 'price': 1646.1, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2025-07-10', 'price': 1609.9, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2025-07-11', 'price': 1609.0, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2025-07-12', 'price': 1597.06, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2025-07-13', 'price': 1597.06, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2025-07-14', 'price': 1597.06, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2025-07-15', 'price': 1597.06, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2025-07-16', 'price': 1597.06, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2025-07-17', 'price': 1597.06, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2025-07-18', 'price': 1605.0, 'merchantId': 2}, {'prodId': 13991987, 'date': '2025-07-19', 'price': 1605.0, 'merchantId': 2}, {'prodId': 13991987, 'date': '2025-07-20', 'price': 1605.0, 'merchantId': 2}, {'prodId': 13991987, 'date': '2025-07-21', 'price': 1605.0, 'merchantId': 2}, {'prodId': 13991987, 'date': '2025-07-22', 'price': 1605.0, 'merchantId': 2}, {'prodId': 13991987, 'date': '2025-07-23', 'price': 1565.1, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2025-07-24', 'price': 1565.1, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2025-07-25', 'price': 1565.1, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2025-07-26', 'price': 1565.1, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2025-07-27', 'price': 1529.1, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2025-07-28', 'price': 1528.0, 'merchantId': 2}, {'prodId': 13991987, 'date': '2025-07-29', 'price': 1528.0, 'merchantId': 2}, {'prodId': 13991987, 'date': '2025-07-30', 'price': 1499.0, 'merchantId': 5}, {'prodId': 13991987, 'date': '2025-07-31', 'price': 1489.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2025-08-01', 'price': 1489.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2025-08-02', 'price': 1499.0, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2025-08-03', 'price': 1549.0, 'merchantId': 5}, {'prodId': 13991987, 'date': '2025-08-04', 'price': 1499.4, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2025-08-05', 'price': 1498.5, 'merchantId': 2}, {'prodId': 13991987, 'date': '2025-08-06', 'price': 1498.5, 'merchantId': 2}, {'prodId': 13991987, 'date': '2025-08-07', 'price': 1498.5, 'merchantId': 2}, {'prodId': 13991987, 'date': '2025-08-08', 'price': 1487.52, 'merchantId': 20583}, {'prodId': 13991987, 'date': '2025-08-09', 'price': 1423.05, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2025-08-10', 'price': 1423.05, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2025-08-11', 'price': 1423.05, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2025-08-12', 'price': 1423.01, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2025-08-13', 'price': 1423.01, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2025-08-14', 'price': 1423.01, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2025-08-15', 'price': 1423.01, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2025-08-16', 'price': 1423.01, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2025-08-17', 'price': 1423.01, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2025-08-18', 'price': 1423.01, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2025-08-19', 'price': 1423.01, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2025-08-20', 'price': 1429.9, 'merchantId': 5}, {'prodId': 13991987, 'date': '2025-08-21', 'price': 1499.4, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2025-08-22', 'price': 1499.4, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2025-08-23', 'price': 1499.4, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2025-08-24', 'price': 1499.4, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2025-08-25', 'price': 1499.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2025-08-26', 'price': 1499.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2025-08-27', 'price': 1497.6, 'merchantId': 2}, {'prodId': 13991987, 'date': '2025-08-28', 'price': 1497.6, 'merchantId': 2}, {'prodId': 13991987, 'date': '2025-08-29', 'price': 1497.6, 'merchantId': 2}, {'prodId': 13991987, 'date': '2025-08-30', 'price': 1497.6, 'merchantId': 2}, {'prodId': 13991987, 'date': '2025-08-31', 'price': 1497.6, 'merchantId': 2}, {'prodId': 13991987, 'date': '2025-09-01', 'price': 1497.6, 'merchantId': 2}, {'prodId': 13991987, 'date': '2025-09-02', 'price': 1484.1, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2025-09-03', 'price': 1484.1, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2025-09-04', 'price': 1414.6, 'merchantId': 16108}, {'prodId': 13991987, 'date': '2025-09-05', 'price': 1414.6, 'merchantId': 16108}, {'prodId': 13991987, 'date': '2025-09-06', 'price': 1414.6, 'merchantId': 23254}, {'prodId': 13991987, 'date': '2025-09-07', 'price': 1414.6, 'merchantId': 23254}, {'prodId': 13991987, 'date': '2025-09-08', 'price': 1414.6, 'merchantId': 23254}, {'prodId': 13991987, 'date': '2025-09-09', 'price': 1414.6, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2025-09-10', 'price': 1400.11, 'merchantId': 5}, {'prodId': 13991987, 'date': '2025-09-11', 'price': 1400.11, 'merchantId': 5}, {'prodId': 13991987, 'date': '2025-09-12', 'price': 1400.11, 'merchantId': 5}, {'prodId': 13991987, 'date': '2025-09-13', 'price': 1400.11, 'merchantId': 5}, {'prodId': 13991987, 'date': '2025-09-14', 'price': 1400.11, 'merchantId': 5}, {'prodId': 13991987, 'date': '2025-09-15', 'price': 1400.11, 'merchantId': 5}, {'prodId': 13991987, 'date': '2025-09-16', 'price': 1400.11, 'merchantId': 5}, {'prodId': 13991987, 'date': '2025-09-17', 'price': 1499.4, 'merchantId': 16108}, {'prodId': 13991987, 'date': '2025-09-18', 'price': 1499.4, 'merchantId': 16108}, {'prodId': 13991987, 'date': '2025-09-19', 'price': 1420.0, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2025-09-20', 'price': 1419.99, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2025-09-21', 'price': 1419.99, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2025-09-22', 'price': 1361.65, 'merchantId': 5}, {'prodId': 13991987, 'date': '2025-09-23', 'price': 1361.65, 'merchantId': 5}, {'prodId': 13991987, 'date': '2025-09-24', 'price': 1529.0, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2025-09-25', 'price': 1529.0, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2025-09-26', 'price': 1511.43, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2025-09-27', 'price': 1528.0, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2025-09-28', 'price': 1528.0, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2025-09-29', 'price': 1527.0, 'merchantId': 2}, {'prodId': 13991987, 'date': '2025-09-30', 'price': 1478.0, 'merchantId': 23254}, {'prodId': 13991987, 'date': '2025-10-01', 'price': 1478.0, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2025-10-02', 'price': 1478.0, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2025-10-03', 'price': 1478.0, 'merchantId': 20583}, {'prodId': 13991987, 'date': '2025-10-04', 'price': 1478.0, 'merchantId': 20583}, {'prodId': 13991987, 'date': '2025-10-05', 'price': 1478.0, 'merchantId': 20583}, {'prodId': 13991987, 'date': '2025-10-06', 'price': 1478.0, 'merchantId': 20583}, {'prodId': 13991987, 'date': '2025-10-07', 'price': 1478.0, 'merchantId': 20583}, {'prodId': 13991987, 'date': '2025-10-08', 'price': 1444.59, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-10-09', 'price': 1444.59, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-10-10', 'price': 1478.0, 'merchantId': 20583}, {'prodId': 13991987, 'date': '2025-10-11', 'price': 1478.0, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2025-10-12', 'price': 1478.0, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2025-10-13', 'price': 1478.0, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2025-10-14', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2025-10-15', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2025-10-16', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2025-10-17', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2025-10-18', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2025-10-19', 'price': 1475.25, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2025-10-20', 'price': 1475.25, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2025-10-21', 'price': 1365.76, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2025-10-22', 'price': 1365.76, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2025-10-23', 'price': 1397.61, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2025-10-24', 'price': 1476.72, 'merchantId': 2584}, {'prodId': 13991987, 'date': '2025-10-25', 'price': 1476.72, 'merchantId': 2584}, {'prodId': 13991987, 'date': '2025-10-26', 'price': 1476.72, 'merchantId': 2584}, {'prodId': 13991987, 'date': '2025-10-27', 'price': 1476.72, 'merchantId': 2584}, {'prodId': 13991987, 'date': '2025-10-28', 'price': 1476.72, 'merchantId': 2584}, {'prodId': 13991987, 'date': '2025-10-29', 'price': 1469.9, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2025-10-30', 'price': 1478.0, 'merchantId': 23254}, {'prodId': 13991987, 'date': '2025-10-31', 'price': 1469.9, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2025-11-01', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-11-02', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-11-03', 'price': 1469.0, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2025-11-04', 'price': 1469.0, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2025-11-05', 'price': 1469.0, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2025-11-06', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-11-07', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-11-08', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-11-09', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-11-10', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-11-11', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-11-12', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-11-13', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-11-14', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-11-15', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-11-16', 'price': 1499.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2025-11-17', 'price': 1424.05, 'merchantId': 2584}, {'prodId': 13991987, 'date': '2025-11-18', 'price': 1379.08, 'merchantId': 23326}, {'prodId': 13991987, 'date': '2025-11-19', 'price': 1379.08, 'merchantId': 23326}, {'prodId': 13991987, 'date': '2025-11-20', 'price': 1379.08, 'merchantId': 23326}, {'prodId': 13991987, 'date': '2025-11-21', 'price': 1379.08, 'merchantId': 23326}, {'prodId': 13991987, 'date': '2025-11-22', 'price': 1286.11, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2025-11-23', 'price': 1286.11, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2025-11-24', 'price': 1286.11, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2025-11-25', 'price': 1439.04, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2025-11-26', 'price': 1379.08, 'merchantId': 23326}, {'prodId': 13991987, 'date': '2025-11-27', 'price': 1259.1, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2025-11-28', 'price': 1259.1, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2025-11-29', 'price': 1379.08, 'merchantId': 23326}, {'prodId': 13991987, 'date': '2025-11-30', 'price': 1379.08, 'merchantId': 23326}, {'prodId': 13991987, 'date': '2025-12-01', 'price': 1379.08, 'merchantId': 23326}, {'prodId': 13991987, 'date': '2025-12-02', 'price': 1379.08, 'merchantId': 23326}, {'prodId': 13991987, 'date': '2025-12-03', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-12-04', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-12-05', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-12-06', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-12-07', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-12-08', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-12-09', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-12-10', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-12-11', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-12-12', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-12-13', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-12-14', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-12-15', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-12-16', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-12-17', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-12-18', 'price': 1499.0, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-12-19', 'price': 1499.9, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2025-12-20', 'price': 1529.0, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2025-12-21', 'price': 1529.0, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2025-12-22', 'price': 1499.9, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2025-12-23', 'price': 1499.9, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2025-12-24', 'price': 1529.15, 'merchantId': 20583}, {'prodId': 13991987, 'date': '2025-12-25', 'price': 1529.15, 'merchantId': 20583}, {'prodId': 13991987, 'date': '2025-12-26', 'price': 1499.9, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2025-12-27', 'price': 1529.15, 'merchantId': 20612}, {'prodId': 13991987, 'date': '2025-12-28', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2025-12-29', 'price': 1499.9, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2025-12-30', 'price': 1469.9, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2025-12-31', 'price': 1469.9, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2026-01-01', 'price': 1469.9, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2026-01-02', 'price': 1469.9, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2026-01-03', 'price': 1469.9, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2026-01-04', 'price': 1469.9, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2026-01-05', 'price': 1469.9, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2026-01-06', 'price': 1469.9, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2026-01-07', 'price': 1469.9, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2026-01-08', 'price': 1498.0, 'merchantId': 23326}, {'prodId': 13991987, 'date': '2026-01-09', 'price': 1498.0, 'merchantId': 23326}, {'prodId': 13991987, 'date': '2026-01-10', 'price': 1498.0, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-01-11', 'price': 1498.0, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-01-12', 'price': 1497.9, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-01-13', 'price': 1497.9, 'merchantId': 23326}, {'prodId': 13991987, 'date': '2026-01-14', 'price': 1497.0, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-01-15', 'price': 1496.0, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-01-16', 'price': 1495.9, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-01-17', 'price': 1495.9, 'merchantId': 23326}, {'prodId': 13991987, 'date': '2026-01-18', 'price': 1495.9, 'merchantId': 23326}, {'prodId': 13991987, 'date': '2026-01-19', 'price': 1495.9, 'merchantId': 23326}, {'prodId': 13991987, 'date': '2026-01-20', 'price': 1495.9, 'merchantId': 245}, {'prodId': 13991987, 'date': '2026-01-21', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-01-22', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-01-23', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-01-24', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-01-25', 'price': 1499.9, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2026-01-26', 'price': 1499.9, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2026-01-27', 'price': 1499.9, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2026-01-28', 'price': 1499.9, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2026-01-29', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-01-30', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-01-31', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-02-01', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-02-02', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-02-03', 'price': 1499.0, 'merchantId': 20583}, {'prodId': 13991987, 'date': '2026-02-04', 'price': 1523.8, 'merchantId': 245}, {'prodId': 13991987, 'date': '2026-02-05', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-02-06', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-02-07', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-02-08', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-02-09', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-02-10', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-02-11', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-02-12', 'price': 1583.02, 'merchantId': 23254}, {'prodId': 13991987, 'date': '2026-02-13', 'price': 1499.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-02-14', 'price': 1499.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-02-15', 'price': 1499.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-02-16', 'price': 1498.0, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-02-17', 'price': 1498.0, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-02-18', 'price': 1497.0, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-02-19', 'price': 1497.0, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-02-20', 'price': 1499.0, 'merchantId': 16108}, {'prodId': 13991987, 'date': '2026-02-21', 'price': 1582.28, 'merchantId': 2584}, {'prodId': 13991987, 'date': '2026-02-22', 'price': 1582.28, 'merchantId': 2584}, {'prodId': 13991987, 'date': '2026-02-23', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-02-24', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-02-25', 'price': 1469.9, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2026-02-26', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-02-27', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-02-28', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-03-01', 'price': 1529.9, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2026-03-02', 'price': 1511.1, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-03-03', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-03-04', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-03-05', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-03-06', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-03-07', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-03-08', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-03-09', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-03-10', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-03-11', 'price': 1449.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-03-12', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-03-13', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-03-14', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-03-15', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-03-16', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-03-17', 'price': 1556.72, 'merchantId': 23326}, {'prodId': 13991987, 'date': '2026-03-18', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-03-19', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-03-20', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-03-21', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-03-22', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-03-23', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-03-24', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-03-25', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-03-26', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-03-27', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-03-28', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-03-29', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-03-30', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-03-31', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-04-01', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-04-02', 'price': 1469.0, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-04-03', 'price': 1468.99, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2026-04-04', 'price': 1469.0, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-04-05', 'price': 1468.99, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2026-04-06', 'price': 1448.0, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-04-07', 'price': 1448.0, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-04-08', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-04-09', 'price': 1448.0, 'merchantId': 23326}, {'prodId': 13991987, 'date': '2026-04-10', 'price': 1448.0, 'merchantId': 23326}, {'prodId': 13991987, 'date': '2026-04-11', 'price': 1448.0, 'merchantId': 23326}, {'prodId': 13991987, 'date': '2026-04-12', 'price': 1587.95, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-04-13', 'price': 1566.0, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2026-04-14', 'price': 1407.02, 'merchantId': 245}, {'prodId': 13991987, 'date': '2026-04-15', 'price': 1406.05, 'merchantId': 245}, {'prodId': 13991987, 'date': '2026-04-16', 'price': 1406.05, 'merchantId': 245}, {'prodId': 13991987, 'date': '2026-04-17', 'price': 1405.95, 'merchantId': 245}, {'prodId': 13991987, 'date': '2026-04-18', 'price': 1437.9, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-04-19', 'price': 1430.1, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2026-04-20', 'price': 1437.0, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-04-21', 'price': 1437.0, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-04-22', 'price': 1436.0, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-04-23', 'price': 1429.9, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-04-24', 'price': 1430.1, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2026-04-25', 'price': 1439.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-04-26', 'price': 1439.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-04-27', 'price': 1438.9, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-04-28', 'price': 1439.0, 'merchantId': 245}, {'prodId': 13991987, 'date': '2026-04-29', 'price': 1438.9, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-04-30', 'price': 1438.9, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-05-01', 'price': 1438.9, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-05-02', 'price': 1420.2, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2026-05-03', 'price': 1420.2, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2026-05-04', 'price': 1420.0, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-05-05', 'price': 1280.71, 'merchantId': 245}, {'prodId': 13991987, 'date': '2026-05-06', 'price': 1404.23, 'merchantId': 245}, {'prodId': 13991987, 'date': '2026-05-07', 'price': 1404.23, 'merchantId': 245}, {'prodId': 13991987, 'date': '2026-05-08', 'price': 1420.0, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-05-09', 'price': 1348.99, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2026-05-10', 'price': 1404.23, 'merchantId': 245}, {'prodId': 13991987, 'date': '2026-05-11', 'price': 1348.99, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2026-05-12', 'price': 1420.0, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-05-13', 'price': 1176.0, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2026-05-14', 'price': 1439.1, 'merchantId': 23254}, {'prodId': 13991987, 'date': '2026-05-15', 'price': 1439.1, 'merchantId': 23254}, {'prodId': 13991987, 'date': '2026-05-16', 'price': 1340.58, 'merchantId': 9385}, {'prodId': 13991987, 'date': '2026-05-17', 'price': 1439.1, 'merchantId': 23254}, {'prodId': 13991987, 'date': '2026-05-18', 'price': 1420.0, 'merchantId': 34}, {'prodId': 13991987, 'date': '2026-05-19', 'price': 1439.1, 'merchantId': 23254}, {'prodId': 13991987, 'date': '2026-05-20', 'price': 1420.0, 'merchantId': 4}, {'prodId': 13991987, 'date': '2026-05-21', 'price': 1420.0, 'merchantId': 4}, {'prodId': 13991987, 'date': '2026-05-22', 'price': 1349.1, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-05-23', 'price': 1349.1, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-05-24', 'price': 1349.1, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-05-25', 'price': 1349.1, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-05-26', 'price': 1349.1, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-05-27', 'price': 1420.0, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-05-28', 'price': 1349.1, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-05-29', 'price': 1349.1, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-05-30', 'price': 1349.1, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-05-31', 'price': 1349.1, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-06-01', 'price': 1349.1, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-06-02', 'price': 1407.01, 'merchantId': 23326}, {'prodId': 13991987, 'date': '2026-06-03', 'price': 1375.04, 'merchantId': 23326}, {'prodId': 13991987, 'date': '2026-06-04', 'price': 1407.01, 'merchantId': 23326}, {'prodId': 13991987, 'date': '2026-06-05', 'price': 1438.99, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-06-06', 'price': 1439.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-06-07', 'price': 1439.0, 'merchantId': 22902}, {'prodId': 13991987, 'date': '2026-06-08', 'price': 1438.99, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-06-09', 'price': 1438.99, 'merchantId': 2}, {'prodId': 13991987, 'date': '2026-06-10', 'price': 1321.99, 'merchantId': 16108}, {'prodId': 13991987, 'date': '2026-06-11', 'price': 1321.99, 'merchantId': 16108}, {'prodId': 13991987, 'date': '2026-06-12', 'price': 1407.02, 'merchantId': 245}, {'prodId': 13991987, 'date': '2026-06-13', 'price': 1421.97, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-06-14', 'price': 1421.97, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-06-15', 'price': 1421.97, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-06-16', 'price': 1321.99, 'merchantId': 16108}, {'prodId': 13991987, 'date': '2026-06-17', 'price': 1399.9, 'merchantId': 16108}, {'prodId': 13991987, 'date': '2026-06-18', 'price': 1399.9, 'merchantId': 16108}, {'prodId': 13991987, 'date': '2026-06-19', 'price': 1399.9, 'merchantId': 16108}, {'prodId': 13991987, 'date': '2026-06-20', 'price': 1399.9, 'merchantId': 16108}, {'prodId': 13991987, 'date': '2026-06-21', 'price': 1399.9, 'merchantId': 16108}, {'prodId': 13991987, 'date': '2026-06-22', 'price': 1399.9, 'merchantId': 16108}, {'prodId': 13991987, 'date': '2026-06-23', 'price': 1399.9, 'merchantId': 16108}, {'prodId': 13991987, 'date': '2026-06-24', 'price': 1364.55, 'merchantId': 245}, {'prodId': 13991987, 'date': '2026-06-25', 'price': 1364.55, 'merchantId': 245}, {'prodId': 13991987, 'date': '2026-06-26', 'price': 1363.61, 'merchantId': 245}, {'prodId': 13991987, 'date': '2026-06-27', 'price': 1363.61, 'merchantId': 245}, {'prodId': 13991987, 'date': '2026-06-28', 'price': 1363.61, 'merchantId': 245}, {'prodId': 13991987, 'date': '2026-06-29', 'price': 1363.61, 'merchantId': 245}, {'prodId': 13991987, 'date': '2026-06-30', 'price': 1363.61, 'merchantId': 245}, {'prodId': 13991987, 'date': '2026-07-01', 'price': 1394.07, 'merchantId': 22905}, {'prodId': 13991987, 'date': '2026-07-02', 'price': 1376.55, 'merchantId': 1582}, {'prodId': 13991987, 'date': '2026-07-03', 'price': 1399.9, 'merchantId': 16108}, {'prodId': 13991987, 'date': '2026-07-04', 'price': 1399.9, 'merchantId': 16108}, {'prodId': 13991987, 'date': '2026-07-05', 'price': 1399.9, 'merchantId': 16108}, {'prodId': 13991987, 'date': '2026-07-06', 'price': 1399.9, 'merchantId': 16108}, {'prodId': 13991987, 'date': '2026-07-07', 'price': 1399.9, 'merchantId': 16108}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13340189, 'date': '2025-07-07', 'price': 413.22, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-07-08', 'price': 413.22, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-07-09', 'price': 413.22, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-07-10', 'price': 413.22, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-07-11', 'price': 413.22, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-07-12', 'price': 413.22, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-07-13', 'price': 420.7, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-07-14', 'price': 420.7, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-07-15', 'price': 421.97, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-07-16', 'price': 421.97, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-07-17', 'price': 688.77, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-07-18', 'price': 688.48, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-07-19', 'price': 688.48, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-07-20', 'price': 688.48, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-07-21', 'price': 688.48, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-07-22', 'price': 688.48, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-07-23', 'price': 691.16, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-07-24', 'price': 691.49, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-07-25', 'price': 691.49, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-07-26', 'price': 423.5, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-07-27', 'price': 423.5, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-07-28', 'price': 423.5, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-07-29', 'price': 423.5, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-07-30', 'price': 423.5, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-07-31', 'price': 423.5, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-08-01', 'price': 423.5, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-08-02', 'price': 354.74, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-08-03', 'price': 354.74, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-08-04', 'price': 354.74, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-08-05', 'price': 1279.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-08-06', 'price': 1259.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-08-07', 'price': 1304.1, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-08-08', 'price': 1397.83, 'merchantId': 22325}, {'prodId': 13340189, 'date': '2025-08-09', 'price': 1397.83, 'merchantId': 22325}, {'prodId': 13340189, 'date': '2025-08-10', 'price': 1397.83, 'merchantId': 22325}, {'prodId': 13340189, 'date': '2025-08-11', 'price': 1397.83, 'merchantId': 22325}, {'prodId': 13340189, 'date': '2025-08-12', 'price': 1397.83, 'merchantId': 22325}, {'prodId': 13340189, 'date': '2025-08-13', 'price': 1397.83, 'merchantId': 22325}, {'prodId': 13340189, 'date': '2025-08-14', 'price': 1439.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-08-15', 'price': 1439.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-08-16', 'price': 1439.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-08-17', 'price': 1439.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-08-18', 'price': 1439.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-08-19', 'price': 1439.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-08-20', 'price': 1449.9, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-08-21', 'price': 1449.9, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-08-22', 'price': 1449.9, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-08-23', 'price': 1449.9, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-08-24', 'price': 1449.9, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-08-25', 'price': 1449.9, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-08-26', 'price': 1449.9, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-08-27', 'price': 1340.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-08-28', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-08-29', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-08-30', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-08-31', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-09-01', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-09-02', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-09-03', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-09-04', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-09-05', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-09-06', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-09-07', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-09-08', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-09-09', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-09-10', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-09-11', 'price': 1338.3, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-09-12', 'price': 1338.3, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-09-13', 'price': 1338.3, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-09-14', 'price': 1338.3, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-09-15', 'price': 1338.3, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-09-16', 'price': 1338.3, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-09-17', 'price': 1304.1, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-09-18', 'price': 1304.1, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-09-19', 'price': 331.58, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-09-20', 'price': 331.58, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-09-21', 'price': 517.19, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-09-22', 'price': 517.19, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-09-23', 'price': 343.69, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-09-24', 'price': 343.69, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-09-25', 'price': 343.69, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-09-26', 'price': 1449.99, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-09-27', 'price': 1469.99, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-09-28', 'price': 1469.99, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-09-29', 'price': 1469.99, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-09-30', 'price': 1469.99, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-10-01', 'price': 1338.3, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-02', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-03', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-04', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-05', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-06', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-07', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-08', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-09', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-10', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-11', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-12', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-13', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-14', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-15', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-16', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-17', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-18', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-19', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-20', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-21', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-22', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-23', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-24', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-25', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-26', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-27', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-28', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-29', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-30', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-10-31', 'price': 1199.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-11-01', 'price': 1199.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-11-02', 'price': 1199.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-11-03', 'price': 1199.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-11-04', 'price': 1199.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-11-05', 'price': 1199.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-11-06', 'price': 1229.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-11-07', 'price': 1229.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-11-08', 'price': 1399.99, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-11-09', 'price': 1399.99, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-11-10', 'price': 993.95, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-11-11', 'price': 993.95, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-11-12', 'price': 993.95, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-11-13', 'price': 993.95, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-11-14', 'price': 993.95, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-11-15', 'price': 1109.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-11-16', 'price': 1405.99, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-11-17', 'price': 1109.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-11-18', 'price': 1405.99, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-11-19', 'price': 1405.99, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-11-20', 'price': 1405.99, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-11-21', 'price': 1405.99, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-11-22', 'price': 1405.99, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-11-23', 'price': 1405.99, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-11-24', 'price': 1405.99, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-11-25', 'price': 1405.99, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2025-11-26', 'price': 1109.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-11-27', 'price': 1102.17, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-11-28', 'price': 993.95, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-11-29', 'price': 1102.17, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-11-30', 'price': 1102.17, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-12-01', 'price': 1102.17, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-12-02', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-12-03', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-12-04', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-12-05', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-12-06', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-12-07', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-12-08', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-12-09', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-12-10', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-12-11', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-12-12', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-12-13', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-12-14', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-12-15', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-12-16', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-12-17', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-12-18', 'price': 1109.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-12-19', 'price': 1109.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-12-20', 'price': 1109.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-12-21', 'price': 1109.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-12-22', 'price': 1109.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-12-23', 'price': 1109.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-12-24', 'price': 1109.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2025-12-25', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-12-26', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-12-27', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-12-28', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-12-29', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-12-30', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2025-12-31', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-01-01', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-01-02', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-01-03', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-01-04', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-01-05', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-01-06', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-01-07', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-01-08', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-01-09', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-01-10', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-01-11', 'price': 1109.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-01-12', 'price': 1109.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-01-13', 'price': 1109.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-01-14', 'price': 1109.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-01-15', 'price': 1109.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-01-16', 'price': 1109.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-01-17', 'price': 1109.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-01-18', 'price': 1109.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-01-19', 'price': 1109.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-01-20', 'price': 1109.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-01-21', 'price': 1109.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-01-22', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-01-23', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-01-24', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-01-25', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-01-26', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-01-27', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-01-28', 'price': 204.52, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-01-29', 'price': 204.52, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-01-30', 'price': 204.52, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-01-31', 'price': 204.52, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-02-01', 'price': 204.52, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-02-02', 'price': 204.52, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-02-03', 'price': 204.52, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-02-04', 'price': 204.52, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-02-05', 'price': 204.52, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-02-06', 'price': 204.52, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-02-07', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-02-08', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-02-09', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-02-10', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-02-11', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-02-12', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-02-13', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-02-14', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-02-15', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-02-16', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-02-17', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-02-18', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-02-19', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-02-20', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-02-21', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-02-22', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-02-23', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-02-24', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-02-25', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-02-26', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-02-27', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-02-28', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-01', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-02', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-03', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-04', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-05', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-06', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-07', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-08', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-09', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-10', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-11', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-12', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-13', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-14', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-15', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-16', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-17', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-18', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-19', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-20', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-21', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-22', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-23', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-24', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-25', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-26', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-27', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-28', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-29', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-30', 'price': 1199.0, 'merchantId': 16108}, {'prodId': 13340189, 'date': '2026-03-31', 'price': 1101.0700000000002, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-04-01', 'price': 1101.07, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-04-02', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2026-04-03', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2026-04-04', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2026-04-05', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2026-04-06', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2026-04-07', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2026-04-08', 'price': 1219.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-04-09', 'price': 1219.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-04-10', 'price': 1101.07, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-04-11', 'price': 1101.07, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-04-12', 'price': 1219.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-04-13', 'price': 1219.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-04-14', 'price': 1101.0700000000002, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-04-15', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2026-04-16', 'price': 1219.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-04-17', 'price': 1069.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-04-18', 'price': 1069.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-04-19', 'price': 1069.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-04-20', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2026-04-21', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2026-04-22', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2026-04-23', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2026-04-24', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2026-04-25', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2026-04-26', 'price': 1219.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-04-27', 'price': 1219.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-04-28', 'price': 1069.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-04-29', 'price': 1069.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-04-30', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2026-05-01', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2026-05-02', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2026-05-03', 'price': 1304.1, 'merchantId': 23254}, {'prodId': 13340189, 'date': '2026-05-04', 'price': 1173.17, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-05-05', 'price': 1173.17, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-05-06', 'price': 1173.17, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-05-07', 'price': 1173.17, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-05-08', 'price': 1173.17, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-05-09', 'price': 1173.17, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-05-10', 'price': 1173.17, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-05-11', 'price': 1173.17, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-05-12', 'price': 1173.17, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-05-13', 'price': 1219.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-05-14', 'price': 1219.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-05-15', 'price': 1219.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-05-16', 'price': 1173.17, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-05-17', 'price': 1173.17, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-05-18', 'price': 1173.17, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-05-19', 'price': 1173.17, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-05-20', 'price': 1173.17, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-05-21', 'price': 1173.17, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-05-22', 'price': 1173.17, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-05-23', 'price': 1173.17, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-05-24', 'price': 1173.17, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-05-25', 'price': 1173.17, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-05-26', 'price': 1173.17, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-05-27', 'price': 1173.17, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-05-28', 'price': 1219.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-05-29', 'price': 1219.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-05-30', 'price': 1219.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-05-31', 'price': 1219.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-06-01', 'price': 1219.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-06-02', 'price': 1219.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-06-03', 'price': 1219.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-06-04', 'price': 1219.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-06-05', 'price': 1219.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-06-06', 'price': 1219.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-06-07', 'price': 1219.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-06-08', 'price': 1219.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-06-09', 'price': 1199.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-06-10', 'price': 1199.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-06-11', 'price': 1199.0, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-06-12', 'price': 1110.65, 'merchantId': 22905}, {'prodId': 13340189, 'date': '2026-06-13', 'price': 1110.65, 'merchantId': 22905}, {'prodId': 13340189, 'date': '2026-06-14', 'price': 1183.47, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-06-15', 'price': 1110.65, 'merchantId': 22905}, {'prodId': 13340189, 'date': '2026-06-16', 'price': 1183.47, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-06-17', 'price': 1183.47, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-06-18', 'price': 1183.47, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-06-19', 'price': 1183.47, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-06-20', 'price': 1183.47, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-06-21', 'price': 1183.47, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-06-22', 'price': 1133.47, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-06-23', 'price': 1133.47, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-06-24', 'price': 1133.47, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-06-25', 'price': 1133.47, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-06-26', 'price': 1133.47, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-06-27', 'price': 1133.47, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-06-28', 'price': 1133.47, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-06-29', 'price': 1124.29, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-06-30', 'price': 1124.29, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-07-01', 'price': 1124.29, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-07-02', 'price': 1124.29, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-07-03', 'price': 1124.29, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-07-04', 'price': 1124.29, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-07-05', 'price': 1124.29, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-07-06', 'price': 1124.29, 'merchantId': 1582}, {'prodId': 13340189, 'date': '2026-07-07', 'price': 1131.97, 'merchantId': 1582}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13994199, 'date': '2026-02-26', 'price': 6749.1, 'merchantId': 4}, {'prodId': 13994199, 'date': '2026-02-27', 'price': 6748.0, 'merchantId': 21627}, {'prodId': 13994199, 'date': '2026-02-28', 'price': 6748.0, 'merchantId': 21627}, {'prodId': 13994199, 'date': '2026-03-01', 'price': 6748.0, 'merchantId': 21627}, {'prodId': 13994199, 'date': '2026-03-02', 'price': 6748.0, 'merchantId': 21627}, {'prodId': 13994199, 'date': '2026-03-03', 'price': 6748.0, 'merchantId': 21627}, {'prodId': 13994199, 'date': '2026-03-04', 'price': 6748.0, 'merchantId': 21627}, {'prodId': 13994199, 'date': '2026-03-05', 'price': 6748.0, 'merchantId': 21627}, {'prodId': 13994199, 'date': '2026-03-06', 'price': 6748.0, 'merchantId': 21627}, {'prodId': 13994199, 'date': '2026-03-07', 'price': 6748.0, 'merchantId': 21627}, {'prodId': 13994199, 'date': '2026-03-08', 'price': 6748.0, 'merchantId': 21627}, {'prodId': 13994199, 'date': '2026-03-09', 'price': 6748.0, 'merchantId': 21627}, {'prodId': 13994199, 'date': '2026-03-10', 'price': 6748.0, 'merchantId': 21627}, {'prodId': 13994199, 'date': '2026-03-11', 'price': 6748.0, 'merchantId': 21627}, {'prodId': 13994199, 'date': '2026-03-12', 'price': 6749.1, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-03-13', 'price': 6749.1, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-03-14', 'price': 6749.1, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-03-15', 'price': 6749.1, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-03-16', 'price': 6749.1, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-03-17', 'price': 6749.1, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-03-18', 'price': 6749.1, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-03-19', 'price': 6749.1, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-03-20', 'price': 6749.1, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-03-21', 'price': 6749.1, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-03-22', 'price': 6749.1, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-03-23', 'price': 6749.1, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-03-24', 'price': 6749.1, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-03-25', 'price': 6749.1, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-03-26', 'price': 6749.1, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-03-27', 'price': 6749.1, 'merchantId': 34}, {'prodId': 13994199, 'date': '2026-03-28', 'price': 6749.1, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-03-29', 'price': 6749.1, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-03-30', 'price': 6749.1, 'merchantId': 20583}, {'prodId': 13994199, 'date': '2026-03-31', 'price': 6749.1, 'merchantId': 20583}, {'prodId': 13994199, 'date': '2026-04-01', 'price': 6749.1, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-04-02', 'price': 6749.1, 'merchantId': 4}, {'prodId': 13994199, 'date': '2026-04-03', 'price': 6749.1, 'merchantId': 4}, {'prodId': 13994199, 'date': '2026-04-04', 'price': 6749.1, 'merchantId': 4}, {'prodId': 13994199, 'date': '2026-04-05', 'price': 6749.1, 'merchantId': 4}, {'prodId': 13994199, 'date': '2026-04-06', 'price': 6548.1, 'merchantId': 4}, {'prodId': 13994199, 'date': '2026-04-07', 'price': 6299.0, 'merchantId': 4}, {'prodId': 13994199, 'date': '2026-04-08', 'price': 6299.0, 'merchantId': 4}, {'prodId': 13994199, 'date': '2026-04-09', 'price': 6298.9, 'merchantId': 4}, {'prodId': 13994199, 'date': '2026-04-10', 'price': 6298.9, 'merchantId': 4}, {'prodId': 13994199, 'date': '2026-04-11', 'price': 6749.1, 'merchantId': 4}, {'prodId': 13994199, 'date': '2026-04-12', 'price': 6749.1, 'merchantId': 4}, {'prodId': 13994199, 'date': '2026-04-13', 'price': 6749.1, 'merchantId': 4}, {'prodId': 13994199, 'date': '2026-04-14', 'price': 6749.1, 'merchantId': 4}, {'prodId': 13994199, 'date': '2026-04-15', 'price': 6749.1, 'merchantId': 4}, {'prodId': 13994199, 'date': '2026-04-16', 'price': 6749.1, 'merchantId': 4}, {'prodId': 13994199, 'date': '2026-04-17', 'price': 6749.0, 'merchantId': 4}, {'prodId': 13994199, 'date': '2026-04-18', 'price': 6749.0, 'merchantId': 4}, {'prodId': 13994199, 'date': '2026-04-19', 'price': 6749.0, 'merchantId': 4}, {'prodId': 13994199, 'date': '2026-04-20', 'price': 6749.0, 'merchantId': 4}, {'prodId': 13994199, 'date': '2026-04-21', 'price': 6749.0, 'merchantId': 4}, {'prodId': 13994199, 'date': '2026-04-22', 'price': 6749.0, 'merchantId': 4}, {'prodId': 13994199, 'date': '2026-04-23', 'price': 5623.88, 'merchantId': 4}, {'prodId': 13994199, 'date': '2026-04-24', 'price': 5623.88, 'merchantId': 4}, {'prodId': 13994199, 'date': '2026-04-25', 'price': 5623.88, 'merchantId': 4}, {'prodId': 13994199, 'date': '2026-04-26', 'price': 5623.88, 'merchantId': 4}, {'prodId': 13994199, 'date': '2026-04-27', 'price': 5623.88, 'merchantId': 4}, {'prodId': 13994199, 'date': '2026-04-28', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-04-29', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-04-30', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-05-01', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-05-02', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-05-03', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-05-04', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-05-05', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-05-06', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-05-07', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-05-08', 'price': 5999.0, 'merchantId': 21627}, {'prodId': 13994199, 'date': '2026-05-09', 'price': 5999.0, 'merchantId': 21627}, {'prodId': 13994199, 'date': '2026-05-10', 'price': 5999.0, 'merchantId': 21627}, {'prodId': 13994199, 'date': '2026-05-11', 'price': 5999.0, 'merchantId': 21627}, {'prodId': 13994199, 'date': '2026-05-12', 'price': 6749.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-05-13', 'price': 6749.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-05-14', 'price': 6749.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-05-15', 'price': 6749.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-05-16', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-05-17', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-05-18', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-05-19', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-05-20', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-05-21', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-05-22', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-05-23', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-05-24', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-05-25', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-05-26', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-05-27', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-05-28', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-05-29', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-05-30', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-05-31', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-06-01', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-06-02', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-06-03', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-06-04', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-06-05', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-06-06', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-06-07', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-06-08', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-06-09', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-06-10', 'price': 5999.0, 'merchantId': 21629}, {'prodId': 13994199, 'date': '2026-06-11', 'price': 6499.9, 'merchantId': 16623}, {'prodId': 13994199, 'date': '2026-06-12', 'price': 6224.08, 'merchantId': 245}, {'prodId': 13994199, 'date': '2026-06-13', 'price': 6224.08, 'merchantId': 245}, {'prodId': 13994199, 'date': '2026-06-14', 'price': 6499.9, 'merchantId': 16623}, {'prodId': 13994199, 'date': '2026-06-15', 'price': 6499.9, 'merchantId': 16623}, {'prodId': 13994199, 'date': '2026-06-16', 'price': 6499.9, 'merchantId': 16623}, {'prodId': 13994199, 'date': '2026-06-17', 'price': 6499.9, 'merchantId': 16623}, {'prodId': 13994199, 'date': '2026-06-18', 'price': 6411.46, 'merchantId': 245}, {'prodId': 13994199, 'date': '2026-06-19', 'price': 6411.46, 'merchantId': 245}, {'prodId': 13994199, 'date': '2026-06-20', 'price': 6399.72, 'merchantId': 245}, {'prodId': 13994199, 'date': '2026-06-21', 'price': 6399.72, 'merchantId': 245}, {'prodId': 13994199, 'date': '2026-06-22', 'price': 4730.0, 'merchantId': 20609}, {'prodId': 13994199, 'date': '2026-06-23', 'price': 4645.49, 'merchantId': 22905}, {'prodId': 13994199, 'date': '2026-06-24', 'price': 4749.05, 'merchantId': 20609}, {'prodId': 13994199, 'date': '2026-06-25', 'price': 4749.05, 'merchantId': 20609}, {'prodId': 13994199, 'date': '2026-06-26', 'price': 4749.05, 'merchantId': 20609}, {'prodId': 13994199, 'date': '2026-06-27', 'price': 4749.05, 'merchantId': 20609}, {'prodId': 13994199, 'date': '2026-06-28', 'price': 4749.05, 'merchantId': 20609}, {'prodId': 13994199, 'date': '2026-06-29', 'price': 4749.05, 'merchantId': 20609}, {'prodId': 13994199, 'date': '2026-06-30', 'price': 4749.05, 'merchantId': 20609}, {'prodId': 13994199, 'date': '2026-07-01', 'price': 4749.05, 'merchantId': 20609}, {'prodId': 13994199, 'date': '2026-07-02', 'price': 4199.0, 'merchantId': 34}, {'prodId': 13994199, 'date': '2026-07-03', 'price': 4198.9, 'merchantId': 34}, {'prodId': 13994199, 'date': '2026-07-04', 'price': 4198.9, 'merchantId': 34}, {'prodId': 13994199, 'date': '2026-07-05', 'price': 4198.9, 'merchantId': 34}, {'prodId': 13994199, 'date': '2026-07-06', 'price': 4197.49, 'merchantId': 34}, {'prodId': 13994199, 'date': '2026-07-07', 'price': 4197.49, 'merchantId': 34}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13340176, 'date': '2025-07-07', 'price': 846.68, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2025-07-08', 'price': 846.68, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2025-07-09', 'price': 899.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-07-10', 'price': 871.99, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2025-07-11', 'price': 871.99, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2025-07-12', 'price': 899.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-07-13', 'price': 899.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-07-14', 'price': 899.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-07-15', 'price': 899.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-07-16', 'price': 899.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-07-17', 'price': 899.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-07-18', 'price': 889.2, 'merchantId': 34}, {'prodId': 13340176, 'date': '2025-07-19', 'price': 844.74, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-07-20', 'price': 844.74, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-07-21', 'price': 886.0, 'merchantId': 4}, {'prodId': 13340176, 'date': '2025-07-22', 'price': 886.0, 'merchantId': 4}, {'prodId': 13340176, 'date': '2025-07-23', 'price': 885.98, 'merchantId': 20583}, {'prodId': 13340176, 'date': '2025-07-24', 'price': 880.0, 'merchantId': 4}, {'prodId': 13340176, 'date': '2025-07-25', 'price': 880.0, 'merchantId': 4}, {'prodId': 13340176, 'date': '2025-07-26', 'price': 880.0, 'merchantId': 4}, {'prodId': 13340176, 'date': '2025-07-27', 'price': 880.0, 'merchantId': 4}, {'prodId': 13340176, 'date': '2025-07-28', 'price': 880.0, 'merchantId': 4}, {'prodId': 13340176, 'date': '2025-07-29', 'price': 799.0, 'merchantId': 22902}, {'prodId': 13340176, 'date': '2025-07-30', 'price': 797.99, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-07-31', 'price': 797.99, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-08-01', 'price': 798.0, 'merchantId': 4}, {'prodId': 13340176, 'date': '2025-08-02', 'price': 719.1, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-08-03', 'price': 719.1, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-08-04', 'price': 719.1, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-08-05', 'price': 779.0, 'merchantId': 16108}, {'prodId': 13340176, 'date': '2025-08-06', 'price': 779.0, 'merchantId': 16108}, {'prodId': 13340176, 'date': '2025-08-07', 'price': 766.92, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2025-08-08', 'price': 766.92, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2025-08-09', 'price': 766.92, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2025-08-10', 'price': 766.92, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2025-08-11', 'price': 766.92, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2025-08-12', 'price': 766.92, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2025-08-13', 'price': 768.99, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-08-14', 'price': 768.99, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-08-15', 'price': 768.99, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-08-16', 'price': 768.99, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-08-17', 'price': 768.99, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-08-18', 'price': 768.99, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-08-19', 'price': 799.0, 'merchantId': 22902}, {'prodId': 13340176, 'date': '2025-08-20', 'price': 798.15, 'merchantId': 20583}, {'prodId': 13340176, 'date': '2025-08-21', 'price': 789.0, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-08-22', 'price': 798.15, 'merchantId': 20583}, {'prodId': 13340176, 'date': '2025-08-23', 'price': 763.02, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2025-08-24', 'price': 798.15, 'merchantId': 20583}, {'prodId': 13340176, 'date': '2025-08-25', 'price': 789.0, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-08-26', 'price': 783.68, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-08-27', 'price': 749.0, 'merchantId': 22902}, {'prodId': 13340176, 'date': '2025-08-28', 'price': 749.0, 'merchantId': 22902}, {'prodId': 13340176, 'date': '2025-08-29', 'price': 749.0, 'merchantId': 16108}, {'prodId': 13340176, 'date': '2025-08-30', 'price': 749.0, 'merchantId': 16108}, {'prodId': 13340176, 'date': '2025-08-31', 'price': 749.0, 'merchantId': 22902}, {'prodId': 13340176, 'date': '2025-09-01', 'price': 749.0, 'merchantId': 22902}, {'prodId': 13340176, 'date': '2025-09-02', 'price': 749.0, 'merchantId': 22902}, {'prodId': 13340176, 'date': '2025-09-03', 'price': 749.0, 'merchantId': 22902}, {'prodId': 13340176, 'date': '2025-09-04', 'price': 820.62, 'merchantId': 20609}, {'prodId': 13340176, 'date': '2025-09-05', 'price': 820.62, 'merchantId': 20609}, {'prodId': 13340176, 'date': '2025-09-06', 'price': 820.62, 'merchantId': 20609}, {'prodId': 13340176, 'date': '2025-09-07', 'price': 820.62, 'merchantId': 20609}, {'prodId': 13340176, 'date': '2025-09-08', 'price': 820.62, 'merchantId': 20609}, {'prodId': 13340176, 'date': '2025-09-09', 'price': 820.62, 'merchantId': 20609}, {'prodId': 13340176, 'date': '2025-09-10', 'price': 820.62, 'merchantId': 20609}, {'prodId': 13340176, 'date': '2025-09-11', 'price': 820.62, 'merchantId': 20609}, {'prodId': 13340176, 'date': '2025-09-12', 'price': 820.62, 'merchantId': 20609}, {'prodId': 13340176, 'date': '2025-09-13', 'price': 820.62, 'merchantId': 20609}, {'prodId': 13340176, 'date': '2025-09-14', 'price': 820.62, 'merchantId': 20609}, {'prodId': 13340176, 'date': '2025-09-15', 'price': 820.62, 'merchantId': 20609}, {'prodId': 13340176, 'date': '2025-09-16', 'price': 820.62, 'merchantId': 20609}, {'prodId': 13340176, 'date': '2025-09-17', 'price': 820.62, 'merchantId': 20609}, {'prodId': 13340176, 'date': '2025-09-18', 'price': 809.19, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-09-19', 'price': 809.19, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-09-20', 'price': 809.19, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-09-21', 'price': 820.62, 'merchantId': 20609}, {'prodId': 13340176, 'date': '2025-09-22', 'price': 820.62, 'merchantId': 20609}, {'prodId': 13340176, 'date': '2025-09-23', 'price': 820.62, 'merchantId': 20609}, {'prodId': 13340176, 'date': '2025-09-24', 'price': 820.62, 'merchantId': 20609}, {'prodId': 13340176, 'date': '2025-09-25', 'price': 820.62, 'merchantId': 20609}, {'prodId': 13340176, 'date': '2025-09-26', 'price': 820.62, 'merchantId': 20583}, {'prodId': 13340176, 'date': '2025-09-27', 'price': 820.62, 'merchantId': 20583}, {'prodId': 13340176, 'date': '2025-09-28', 'price': 820.62, 'merchantId': 20583}, {'prodId': 13340176, 'date': '2025-09-29', 'price': 829.9, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2025-09-30', 'price': 829.9, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2025-10-01', 'price': 848.0, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-10-02', 'price': 848.0, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-10-03', 'price': 849.0, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-10-04', 'price': 834.9, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-10-05', 'price': 834.9, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-10-06', 'price': 814.19, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-10-07', 'price': 789.9, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2025-10-08', 'price': 789.9, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2025-10-09', 'price': 737.1, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-10-10', 'price': 713.7, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-10-11', 'price': 713.7, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-10-12', 'price': 793.15, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-10-13', 'price': 793.15, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-10-14', 'price': 775.3, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-10-15', 'price': 682.88, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-10-16', 'price': 682.88, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-10-17', 'price': 740.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-10-18', 'price': 740.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-10-19', 'price': 740.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-10-20', 'price': 739.1, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-10-21', 'price': 692.1, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-10-22', 'price': 692.1, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-10-23', 'price': 692.1, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-10-24', 'price': 692.1, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-10-25', 'price': 719.1, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-10-26', 'price': 719.1, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-10-27', 'price': 719.1, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-10-28', 'price': 719.1, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-10-29', 'price': 718.2, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-10-30', 'price': 718.2, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-10-31', 'price': 710.04, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-11-01', 'price': 710.04, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-11-02', 'price': 710.04, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-11-03', 'price': 710.04, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-11-04', 'price': 710.1, 'merchantId': 16108}, {'prodId': 13340176, 'date': '2025-11-05', 'price': 710.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2025-11-06', 'price': 710.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2025-11-07', 'price': 710.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2025-11-08', 'price': 710.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2025-11-09', 'price': 710.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2025-11-10', 'price': 710.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2025-11-11', 'price': 694.32, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-11-12', 'price': 710.1, 'merchantId': 16108}, {'prodId': 13340176, 'date': '2025-11-13', 'price': 710.1, 'merchantId': 16108}, {'prodId': 13340176, 'date': '2025-11-14', 'price': 801.83, 'merchantId': 34}, {'prodId': 13340176, 'date': '2025-11-15', 'price': 710.1, 'merchantId': 22902}, {'prodId': 13340176, 'date': '2025-11-16', 'price': 749.55, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-11-17', 'price': 569.0, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-11-18', 'price': 749.55, 'merchantId': 2584}, {'prodId': 13340176, 'date': '2025-11-19', 'price': 710.1, 'merchantId': 22902}, {'prodId': 13340176, 'date': '2025-11-20', 'price': 710.1, 'merchantId': 22902}, {'prodId': 13340176, 'date': '2025-11-21', 'price': 791.12, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2025-11-22', 'price': 759.05, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-11-23', 'price': 759.05, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-11-24', 'price': 756.2, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-11-25', 'price': 719.1, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-11-26', 'price': 719.1, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-11-27', 'price': 719.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-11-28', 'price': 710.1, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-11-29', 'price': 710.1, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2025-11-30', 'price': 719.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-12-01', 'price': 719.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-12-02', 'price': 719.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-12-03', 'price': 719.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-12-04', 'price': 719.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-12-05', 'price': 719.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-12-06', 'price': 719.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-12-07', 'price': 719.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-12-08', 'price': 719.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-12-09', 'price': 719.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-12-10', 'price': 719.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-12-11', 'price': 719.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-12-12', 'price': 719.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-12-13', 'price': 719.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-12-14', 'price': 719.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-12-15', 'price': 719.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-12-16', 'price': 719.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-12-17', 'price': 719.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-12-18', 'price': 719.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-12-19', 'price': 719.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2025-12-20', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-12-21', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-12-22', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-12-23', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-12-24', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-12-25', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-12-26', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-12-27', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-12-28', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-12-29', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-12-30', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2025-12-31', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-01', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-02', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-03', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-04', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-05', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-06', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-07', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-08', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-09', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-10', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-11', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-12', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-13', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-14', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-15', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-16', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-17', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-18', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-19', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-20', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-21', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-22', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-23', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-24', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-25', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-26', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-27', 'price': 759.05, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-01-28', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-01-29', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-01-30', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-01-31', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-01', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-02', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-03', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-04', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-05', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-06', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-07', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-08', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-09', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-10', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-11', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-12', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-13', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-14', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-15', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-16', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-17', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-18', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-19', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-20', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-21', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-22', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-23', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-24', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-25', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-26', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-27', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-02-28', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-03-01', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-03-02', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-03-03', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-03-04', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-03-05', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-03-06', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-03-07', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-03-08', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-03-09', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-03-10', 'price': 779.9, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-03-11', 'price': 863.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2026-03-12', 'price': 863.1, 'merchantId': 20612}, {'prodId': 13340176, 'date': '2026-03-13', 'price': 789.0, 'merchantId': 16108}, {'prodId': 13340176, 'date': '2026-03-14', 'price': 789.0, 'merchantId': 16108}, {'prodId': 13340176, 'date': '2026-03-15', 'price': 789.0, 'merchantId': 16108}, {'prodId': 13340176, 'date': '2026-03-16', 'price': 789.0, 'merchantId': 16108}, {'prodId': 13340176, 'date': '2026-03-17', 'price': 788.9, 'merchantId': 4}, {'prodId': 13340176, 'date': '2026-03-18', 'price': 788.9, 'merchantId': 4}, {'prodId': 13340176, 'date': '2026-03-19', 'price': 788.9, 'merchantId': 4}, {'prodId': 13340176, 'date': '2026-03-20', 'price': 789.0, 'merchantId': 16108}, {'prodId': 13340176, 'date': '2026-03-21', 'price': 788.9, 'merchantId': 4}, {'prodId': 13340176, 'date': '2026-03-22', 'price': 789.0, 'merchantId': 22902}, {'prodId': 13340176, 'date': '2026-03-23', 'price': 789.0, 'merchantId': 22902}, {'prodId': 13340176, 'date': '2026-03-24', 'price': 788.9, 'merchantId': 4}, {'prodId': 13340176, 'date': '2026-03-25', 'price': 788.9, 'merchantId': 4}, {'prodId': 13340176, 'date': '2026-03-26', 'price': 789.0, 'merchantId': 16108}, {'prodId': 13340176, 'date': '2026-03-27', 'price': 854.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-03-28', 'price': 854.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-03-29', 'price': 854.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-03-30', 'price': 854.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-03-31', 'price': 789.0, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-04-01', 'price': 854.1, 'merchantId': 16108}, {'prodId': 13340176, 'date': '2026-04-02', 'price': 854.1, 'merchantId': 16108}, {'prodId': 13340176, 'date': '2026-04-03', 'price': 788.9, 'merchantId': 4}, {'prodId': 13340176, 'date': '2026-04-04', 'price': 854.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-04-05', 'price': 789.0, 'merchantId': 16108}, {'prodId': 13340176, 'date': '2026-04-06', 'price': 854.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-04-07', 'price': 854.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-04-08', 'price': 854.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-04-09', 'price': 854.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-04-10', 'price': 788.9, 'merchantId': 4}, {'prodId': 13340176, 'date': '2026-04-11', 'price': 854.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-04-12', 'price': 854.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-04-13', 'price': 854.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-04-14', 'price': 779.9, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2026-04-15', 'price': 854.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-04-16', 'price': 854.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-04-17', 'price': 788.9, 'merchantId': 4}, {'prodId': 13340176, 'date': '2026-04-18', 'price': 854.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-04-19', 'price': 854.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-04-20', 'price': 854.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-04-21', 'price': 854.1, 'merchantId': 16108}, {'prodId': 13340176, 'date': '2026-04-22', 'price': 881.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-04-23', 'price': 832.84, 'merchantId': 2584}, {'prodId': 13340176, 'date': '2026-04-24', 'price': 832.84, 'merchantId': 2584}, {'prodId': 13340176, 'date': '2026-04-25', 'price': 789.0, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-04-26', 'price': 881.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-04-27', 'price': 788.9, 'merchantId': 4}, {'prodId': 13340176, 'date': '2026-04-28', 'price': 788.9, 'merchantId': 4}, {'prodId': 13340176, 'date': '2026-04-29', 'price': 881.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-04-30', 'price': 789.0, 'merchantId': 16108}, {'prodId': 13340176, 'date': '2026-05-01', 'price': 881.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-05-02', 'price': 881.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-05-03', 'price': 881.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-05-04', 'price': 789.0, 'merchantId': 16108}, {'prodId': 13340176, 'date': '2026-05-05', 'price': 788.9, 'merchantId': 4}, {'prodId': 13340176, 'date': '2026-05-06', 'price': 788.9, 'merchantId': 4}, {'prodId': 13340176, 'date': '2026-05-07', 'price': 854.1, 'merchantId': 22902}, {'prodId': 13340176, 'date': '2026-05-08', 'price': 854.1, 'merchantId': 22902}, {'prodId': 13340176, 'date': '2026-05-09', 'price': 859.91, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-05-10', 'price': 859.91, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-05-11', 'price': 789.0, 'merchantId': 16108}, {'prodId': 13340176, 'date': '2026-05-12', 'price': 789.0, 'merchantId': 16108}, {'prodId': 13340176, 'date': '2026-05-13', 'price': 789.0, 'merchantId': 16108}, {'prodId': 13340176, 'date': '2026-05-14', 'price': 881.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-05-15', 'price': 881.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-05-16', 'price': 844.89, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2026-05-17', 'price': 881.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-05-18', 'price': 788.9, 'merchantId': 4}, {'prodId': 13340176, 'date': '2026-05-19', 'price': 844.89, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-05-20', 'price': 789.0, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-05-21', 'price': 881.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-05-22', 'price': 830.74, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2026-05-23', 'price': 789.0, 'merchantId': 22902}, {'prodId': 13340176, 'date': '2026-05-24', 'price': 789.0, 'merchantId': 22902}, {'prodId': 13340176, 'date': '2026-05-25', 'price': 837.25, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-05-26', 'price': 837.25, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-05-27', 'price': 854.1, 'merchantId': 22902}, {'prodId': 13340176, 'date': '2026-05-28', 'price': 881.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-05-29', 'price': 881.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-05-30', 'price': 881.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-05-31', 'price': 881.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-06-01', 'price': 881.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-06-02', 'price': 788.9, 'merchantId': 4}, {'prodId': 13340176, 'date': '2026-06-03', 'price': 788.9, 'merchantId': 4}, {'prodId': 13340176, 'date': '2026-06-04', 'price': 881.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-06-05', 'price': 789.0, 'merchantId': 22902}, {'prodId': 13340176, 'date': '2026-06-06', 'price': 881.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-06-07', 'price': 881.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-06-08', 'price': 881.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-06-09', 'price': 828.75, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2026-06-10', 'price': 881.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-06-11', 'price': 828.75, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-06-12', 'price': 789.0, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-06-13', 'price': 881.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-06-14', 'price': 881.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-06-15', 'price': 881.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-06-16', 'price': 881.1, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-06-17', 'price': 732.87, 'merchantId': 22905}, {'prodId': 13340176, 'date': '2026-06-18', 'price': 789.0, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2026-06-19', 'price': 766.0, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-06-20', 'price': 789.0, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2026-06-21', 'price': 789.0, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2026-06-22', 'price': 789.0, 'merchantId': 16108}, {'prodId': 13340176, 'date': '2026-06-23', 'price': 789.0, 'merchantId': 16108}, {'prodId': 13340176, 'date': '2026-06-24', 'price': 789.0, 'merchantId': 16108}, {'prodId': 13340176, 'date': '2026-06-25', 'price': 849.15, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-06-26', 'price': 849.15, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-06-27', 'price': 849.15, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-06-28', 'price': 849.15, 'merchantId': 9385}, {'prodId': 13340176, 'date': '2026-06-29', 'price': 866.7, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-06-30', 'price': 789.0, 'merchantId': 16108}, {'prodId': 13340176, 'date': '2026-07-01', 'price': 866.7, 'merchantId': 23254}, {'prodId': 13340176, 'date': '2026-07-02', 'price': 789.0, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2026-07-03', 'price': 789.0, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2026-07-04', 'price': 789.0, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2026-07-05', 'price': 789.0, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2026-07-06', 'price': 789.0, 'merchantId': 1582}, {'prodId': 13340176, 'date': '2026-07-07', 'price': 789.0, 'merchantId': 1582}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13994348, 'date': '2026-04-15', 'price': 2849.93, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-04-16', 'price': 2476.8, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-04-17', 'price': 2429.99, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-04-18', 'price': 2429.99, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-04-19', 'price': 2429.99, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-04-20', 'price': 2429.99, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-04-21', 'price': 2429.99, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-04-22', 'price': 2278.84, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-04-23', 'price': 2278.84, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-04-24', 'price': 2278.84, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-04-25', 'price': 2338.34, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-04-26', 'price': 2338.34, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-04-27', 'price': 2338.34, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-04-28', 'price': 2338.34, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-04-29', 'price': 2338.34, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-04-30', 'price': 2338.34, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-01', 'price': 2294.15, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-02', 'price': 2338.34, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-03', 'price': 2338.34, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-04', 'price': 2294.99, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-05', 'price': 2274.59, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-06', 'price': 2263.19, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-07', 'price': 2200.79, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-08', 'price': 2200.79, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-09', 'price': 2200.79, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-10', 'price': 2200.79, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-11', 'price': 2200.79, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-12', 'price': 2274.59, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-13', 'price': 2271.19, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-14', 'price': 2271.19, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-15', 'price': 2271.19, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-16', 'price': 2271.19, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-17', 'price': 2271.19, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-18', 'price': 2271.19, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-19', 'price': 2289.59, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-20', 'price': 2289.59, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-21', 'price': 2289.59, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-22', 'price': 2289.59, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-23', 'price': 2374.05, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-24', 'price': 2374.05, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-25', 'price': 2374.05, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-26', 'price': 2374.05, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-27', 'price': 2374.05, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-28', 'price': 2374.05, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-29', 'price': 2374.05, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-30', 'price': 2374.05, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-05-31', 'price': 2374.05, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-06-01', 'price': 2124.15, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-06-02', 'price': 2235.99, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-06-03', 'price': 2179.0, 'merchantId': 16623}, {'prodId': 13994348, 'date': '2026-06-04', 'price': 2209.15, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-06-05', 'price': 2209.15, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-06-06', 'price': 2209.15, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-06-07', 'price': 2209.15, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-06-08', 'price': 2209.15, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-06-09', 'price': 2209.15, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-06-10', 'price': 2209.15, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-06-11', 'price': 2209.15, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-06-12', 'price': 2209.15, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-06-13', 'price': 2209.15, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-06-14', 'price': 2209.15, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-06-15', 'price': 2209.15, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-06-16', 'price': 2209.15, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-06-17', 'price': 2209.15, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-06-18', 'price': 2179.0, 'merchantId': 16623}, {'prodId': 13994348, 'date': '2026-06-19', 'price': 2179.0, 'merchantId': 16623}, {'prodId': 13994348, 'date': '2026-06-20', 'price': 2179.0, 'merchantId': 16623}, {'prodId': 13994348, 'date': '2026-06-21', 'price': 2179.0, 'merchantId': 16623}, {'prodId': 13994348, 'date': '2026-06-22', 'price': 2179.0, 'merchantId': 16623}, {'prodId': 13994348, 'date': '2026-06-23', 'price': 2179.0, 'merchantId': 16623}, {'prodId': 13994348, 'date': '2026-06-24', 'price': 2185.0, 'merchantId': 16623}, {'prodId': 13994348, 'date': '2026-06-25', 'price': 2185.0, 'merchantId': 16623}, {'prodId': 13994348, 'date': '2026-06-26', 'price': 2185.0, 'merchantId': 16623}, {'prodId': 13994348, 'date': '2026-06-27', 'price': 2185.0, 'merchantId': 16623}, {'prodId': 13994348, 'date': '2026-06-28', 'price': 2185.0, 'merchantId': 16623}, {'prodId': 13994348, 'date': '2026-06-29', 'price': 2185.0, 'merchantId': 16623}, {'prodId': 13994348, 'date': '2026-06-30', 'price': 2185.0, 'merchantId': 16623}, {'prodId': 13994348, 'date': '2026-07-01', 'price': 2185.0, 'merchantId': 16623}, {'prodId': 13994348, 'date': '2026-07-02', 'price': 2300.0, 'merchantId': 16623}, {'prodId': 13994348, 'date': '2026-07-03', 'price': 2300.0, 'merchantId': 16623}, {'prodId': 13994348, 'date': '2026-07-04', 'price': 2300.0, 'merchantId': 16623}, {'prodId': 13994348, 'date': '2026-07-05', 'price': 2300.0, 'merchantId': 16623}, {'prodId': 13994348, 'date': '2026-07-06', 'price': 2294.15, 'merchantId': 22905}, {'prodId': 13994348, 'date': '2026-07-07', 'price': 2294.15, 'merchantId': 22905}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13994245, 'date': '2026-03-09', 'price': 5219.1, 'merchantId': 34}, {'prodId': 13994245, 'date': '2026-03-10', 'price': 5219.1, 'merchantId': 34}, {'prodId': 13994245, 'date': '2026-03-11', 'price': 5219.1, 'merchantId': 34}, {'prodId': 13994245, 'date': '2026-03-12', 'price': 5219.1, 'merchantId': 34}, {'prodId': 13994245, 'date': '2026-03-13', 'price': 5219.0, 'merchantId': 21}, {'prodId': 13994245, 'date': '2026-03-14', 'price': 5219.0, 'merchantId': 21}, {'prodId': 13994245, 'date': '2026-03-15', 'price': 5219.0, 'merchantId': 21}, {'prodId': 13994245, 'date': '2026-03-16', 'price': 5219.0, 'merchantId': 20612}, {'prodId': 13994245, 'date': '2026-03-17', 'price': 5219.0, 'merchantId': 20612}, {'prodId': 13994245, 'date': '2026-03-18', 'price': 5219.0, 'merchantId': 20612}, {'prodId': 13994245, 'date': '2026-03-19', 'price': 5219.0, 'merchantId': 20612}, {'prodId': 13994245, 'date': '2026-03-20', 'price': 5219.0, 'merchantId': 20612}, {'prodId': 13994245, 'date': '2026-03-21', 'price': 5219.0, 'merchantId': 20612}, {'prodId': 13994245, 'date': '2026-03-22', 'price': 5219.0, 'merchantId': 20612}, {'prodId': 13994245, 'date': '2026-03-23', 'price': 5219.0, 'merchantId': 20612}, {'prodId': 13994245, 'date': '2026-03-24', 'price': 5219.0, 'merchantId': 20612}, {'prodId': 13994245, 'date': '2026-03-25', 'price': 5219.0, 'merchantId': 20612}, {'prodId': 13994245, 'date': '2026-03-26', 'price': 5219.0, 'merchantId': 20612}, {'prodId': 13994245, 'date': '2026-03-27', 'price': 5219.0, 'merchantId': 20612}, {'prodId': 13994245, 'date': '2026-03-28', 'price': 5219.0, 'merchantId': 20612}, {'prodId': 13994245, 'date': '2026-03-29', 'price': 5219.0, 'merchantId': 20612}, {'prodId': 13994245, 'date': '2026-03-30', 'price': 5219.0, 'merchantId': 20612}, {'prodId': 13994245, 'date': '2026-03-31', 'price': 5219.0, 'merchantId': 20612}, {'prodId': 13994245, 'date': '2026-04-01', 'price': 5219.0, 'merchantId': 20612}, {'prodId': 13994245, 'date': '2026-04-02', 'price': 5219.0, 'merchantId': 20612}, {'prodId': 13994245, 'date': '2026-04-03', 'price': 5219.0, 'merchantId': 23326}, {'prodId': 13994245, 'date': '2026-04-04', 'price': 5219.0, 'merchantId': 23326}, {'prodId': 13994245, 'date': '2026-04-05', 'price': 5219.0, 'merchantId': 23326}, {'prodId': 13994245, 'date': '2026-04-06', 'price': 5219.0, 'merchantId': 23326}, {'prodId': 13994245, 'date': '2026-04-07', 'price': 5199.9, 'merchantId': 21}, {'prodId': 13994245, 'date': '2026-04-08', 'price': 5199.9, 'merchantId': 21}, {'prodId': 13994245, 'date': '2026-04-09', 'price': 5199.9, 'merchantId': 21}, {'prodId': 13994245, 'date': '2026-04-10', 'price': 5199.9, 'merchantId': 21}, {'prodId': 13994245, 'date': '2026-04-11', 'price': 5199.9, 'merchantId': 21}, {'prodId': 13994245, 'date': '2026-04-12', 'price': 5199.9, 'merchantId': 21}, {'prodId': 13994245, 'date': '2026-04-13', 'price': 5199.9, 'merchantId': 21}, {'prodId': 13994245, 'date': '2026-04-14', 'price': 5199.9, 'merchantId': 21}, {'prodId': 13994245, 'date': '2026-04-15', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-04-16', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-04-17', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-04-18', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-04-19', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-04-20', 'price': 4499.9, 'merchantId': 21}, {'prodId': 13994245, 'date': '2026-04-21', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-04-22', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-04-23', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-04-24', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-04-25', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-04-26', 'price': 4498.9, 'merchantId': 4}, {'prodId': 13994245, 'date': '2026-04-27', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-04-28', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-04-29', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-04-30', 'price': 4497.9, 'merchantId': 4}, {'prodId': 13994245, 'date': '2026-05-01', 'price': 4497.9, 'merchantId': 4}, {'prodId': 13994245, 'date': '2026-05-02', 'price': 4497.9, 'merchantId': 34}, {'prodId': 13994245, 'date': '2026-05-03', 'price': 4497.9, 'merchantId': 4}, {'prodId': 13994245, 'date': '2026-05-04', 'price': 4497.9, 'merchantId': 4}, {'prodId': 13994245, 'date': '2026-05-05', 'price': 4496.99, 'merchantId': 21}, {'prodId': 13994245, 'date': '2026-05-06', 'price': 4496.99, 'merchantId': 21}, {'prodId': 13994245, 'date': '2026-05-07', 'price': 4496.99, 'merchantId': 21}, {'prodId': 13994245, 'date': '2026-05-08', 'price': 4496.99, 'merchantId': 21}, {'prodId': 13994245, 'date': '2026-05-09', 'price': 4496.99, 'merchantId': 21}, {'prodId': 13994245, 'date': '2026-05-10', 'price': 4497.9, 'merchantId': 4}, {'prodId': 13994245, 'date': '2026-05-11', 'price': 4497.9, 'merchantId': 4}, {'prodId': 13994245, 'date': '2026-05-12', 'price': 4497.9, 'merchantId': 4}, {'prodId': 13994245, 'date': '2026-05-13', 'price': 4499.1, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-05-14', 'price': 4499.1, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-05-15', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-05-16', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-05-17', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-05-18', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-05-19', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-05-20', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-05-21', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-05-22', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-05-23', 'price': 4499.1, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-05-24', 'price': 4497.9, 'merchantId': 4}, {'prodId': 13994245, 'date': '2026-05-25', 'price': 4497.9, 'merchantId': 4}, {'prodId': 13994245, 'date': '2026-05-26', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-05-27', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-05-28', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-05-29', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-05-30', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-05-31', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-01', 'price': 4499.1, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-02', 'price': 4497.9, 'merchantId': 34}, {'prodId': 13994245, 'date': '2026-06-03', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-04', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-05', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-06', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-07', 'price': 4499.1, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-08', 'price': 4499.1, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-09', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-10', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-11', 'price': 4499.1, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-12', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-13', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-14', 'price': 4499.1, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-15', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-16', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-17', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-18', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-19', 'price': 4497.9, 'merchantId': 34}, {'prodId': 13994245, 'date': '2026-06-20', 'price': 4499.1, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-21', 'price': 4499.1, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-22', 'price': 4499.1, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-23', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-24', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-25', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-26', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-27', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-28', 'price': 4499.1, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-29', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-06-30', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-07-01', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-07-02', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-07-03', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-07-04', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-07-05', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-07-06', 'price': 4051.18, 'merchantId': 22902}, {'prodId': 13994245, 'date': '2026-07-07', 'price': 4699.0, 'merchantId': 22902}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13567220, 'date': '2025-07-07', 'price': 7649.1, 'merchantId': 23199}, {'prodId': 13567220, 'date': '2025-07-08', 'price': 7590.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-07-09', 'price': 7590.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-07-10', 'price': 7399.0, 'merchantId': 10763}, {'prodId': 13567220, 'date': '2025-07-11', 'price': 7399.0, 'merchantId': 10763}, {'prodId': 13567220, 'date': '2025-07-12', 'price': 7399.0, 'merchantId': 10763}, {'prodId': 13567220, 'date': '2025-07-13', 'price': 7109.1, 'merchantId': 20583}, {'prodId': 13567220, 'date': '2025-07-14', 'price': 7109.1, 'merchantId': 20583}, {'prodId': 13567220, 'date': '2025-07-15', 'price': 7469.0, 'merchantId': 10763}, {'prodId': 13567220, 'date': '2025-07-16', 'price': 7399.0, 'merchantId': 10763}, {'prodId': 13567220, 'date': '2025-07-17', 'price': 7399.0, 'merchantId': 10763}, {'prodId': 13567220, 'date': '2025-07-18', 'price': 7399.0, 'merchantId': 10763}, {'prodId': 13567220, 'date': '2025-07-19', 'price': 7399.0, 'merchantId': 10763}, {'prodId': 13567220, 'date': '2025-07-20', 'price': 7399.0, 'merchantId': 10763}, {'prodId': 13567220, 'date': '2025-07-21', 'price': 7399.0, 'merchantId': 10763}, {'prodId': 13567220, 'date': '2025-07-22', 'price': 6299.1, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2025-07-23', 'price': 6299.1, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2025-07-24', 'price': 6299.1, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2025-07-25', 'price': 6299.1, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2025-07-26', 'price': 7399.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2025-07-27', 'price': 7399.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2025-07-28', 'price': 7399.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2025-07-29', 'price': 7399.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2025-07-30', 'price': 7399.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2025-07-31', 'price': 7399.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2025-08-01', 'price': 7399.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2025-08-02', 'price': 7890.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2025-08-03', 'price': 7890.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2025-08-04', 'price': 7890.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2025-08-05', 'price': 7890.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2025-08-06', 'price': 7890.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-08-07', 'price': 7884.05, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2025-08-08', 'price': 7884.05, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2025-08-09', 'price': 7884.05, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2025-08-10', 'price': 7790.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-08-11', 'price': 7789.0, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2025-08-12', 'price': 7789.0, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2025-08-13', 'price': 7790.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-08-14', 'price': 7919.1, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-08-15', 'price': 7919.1, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-08-16', 'price': 7919.1, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-08-17', 'price': 7919.1, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-08-18', 'price': 7919.1, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-08-19', 'price': 7919.1, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-08-20', 'price': 7919.1, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-08-21', 'price': 7919.1, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-08-22', 'price': 7919.1, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-08-23', 'price': 7919.1, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-08-24', 'price': 7919.1, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-08-25', 'price': 7379.1, 'merchantId': 23199}, {'prodId': 13567220, 'date': '2025-08-26', 'price': 7379.1, 'merchantId': 23199}, {'prodId': 13567220, 'date': '2025-08-27', 'price': 7379.1, 'merchantId': 23199}, {'prodId': 13567220, 'date': '2025-08-28', 'price': 7379.1, 'merchantId': 23199}, {'prodId': 13567220, 'date': '2025-08-29', 'price': 7379.1, 'merchantId': 23199}, {'prodId': 13567220, 'date': '2025-08-30', 'price': 7379.1, 'merchantId': 23199}, {'prodId': 13567220, 'date': '2025-08-31', 'price': 7379.1, 'merchantId': 23199}, {'prodId': 13567220, 'date': '2025-09-01', 'price': 7379.1, 'merchantId': 23199}, {'prodId': 13567220, 'date': '2025-09-02', 'price': 7700.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-09-03', 'price': 7700.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-09-04', 'price': 7789.05, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-09-05', 'price': 7789.05, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-09-06', 'price': 7789.05, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-09-07', 'price': 7789.05, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-09-08', 'price': 7700.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-09-09', 'price': 7789.05, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-09-10', 'price': 7748.06, 'merchantId': 16108}, {'prodId': 13567220, 'date': '2025-09-11', 'price': 7748.06, 'merchantId': 16108}, {'prodId': 13567220, 'date': '2025-09-12', 'price': 7748.06, 'merchantId': 16108}, {'prodId': 13567220, 'date': '2025-09-13', 'price': 7598.1, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-09-14', 'price': 7598.1, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-09-15', 'price': 7598.1, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-09-16', 'price': 7558.11, 'merchantId': 16108}, {'prodId': 13567220, 'date': '2025-09-17', 'price': 7558.11, 'merchantId': 16108}, {'prodId': 13567220, 'date': '2025-09-18', 'price': 7558.11, 'merchantId': 16108}, {'prodId': 13567220, 'date': '2025-09-19', 'price': 6999.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-09-20', 'price': 6700.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-09-21', 'price': 6999.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-09-22', 'price': 6999.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-09-23', 'price': 6999.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-09-24', 'price': 6999.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-09-25', 'price': 6999.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-09-26', 'price': 6999.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-09-27', 'price': 6999.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-09-28', 'price': 7190.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-09-29', 'price': 7198.2, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-09-30', 'price': 7198.2, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-10-01', 'price': 7198.2, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-10-02', 'price': 7198.2, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-10-03', 'price': 7099.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-10-04', 'price': 7275.7, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-10-05', 'price': 7275.7, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-10-06', 'price': 7274.53, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-10-07', 'price': 6700.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-10-08', 'price': 6958.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-10-09', 'price': 7156.53, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-10-10', 'price': 7156.53, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-10-11', 'price': 6999.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2025-10-12', 'price': 6999.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2025-10-13', 'price': 6700.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-10-14', 'price': 6999.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-10-15', 'price': 7156.53, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-10-16', 'price': 7156.53, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-10-17', 'price': 7156.53, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-10-18', 'price': 7156.53, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-10-19', 'price': 7156.53, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-10-20', 'price': 6856.84, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2025-10-21', 'price': 6856.84, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2025-10-22', 'price': 7156.53, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-10-23', 'price': 7156.53, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-10-24', 'price': 6856.84, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2025-10-25', 'price': 7156.53, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-10-26', 'price': 7156.53, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-10-27', 'price': 7156.53, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-10-28', 'price': 7156.53, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-10-29', 'price': 7156.53, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-10-30', 'price': 7156.53, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-10-31', 'price': 7156.53, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-11-01', 'price': 7156.53, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-11-02', 'price': 7156.53, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-11-03', 'price': 7156.53, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-11-04', 'price': 7156.53, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-11-05', 'price': 7598.1, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-11-06', 'price': 6832.63, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-11-07', 'price': 6832.63, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-11-08', 'price': 6832.63, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2025-11-09', 'price': 7109.99, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-11-10', 'price': 6832.63, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2025-11-11', 'price': 7818.16, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-11-12', 'price': 7400.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-11-13', 'price': 7400.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-11-14', 'price': 7799.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-11-15', 'price': 7799.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-11-16', 'price': 7400.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-11-17', 'price': 7400.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-11-18', 'price': 7799.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-11-19', 'price': 7799.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-11-20', 'price': 7400.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-11-21', 'price': 7690.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-11-22', 'price': 7690.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-11-23', 'price': 7400.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2025-11-24', 'price': 6399.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-11-25', 'price': 6399.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-11-26', 'price': 6399.0, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2025-11-27', 'price': 6399.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-11-28', 'price': 6327.9, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-11-29', 'price': 6327.9, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-11-30', 'price': 6327.9, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-12-01', 'price': 5998.86, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-12-02', 'price': 5998.86, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-12-03', 'price': 6327.9, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-12-04', 'price': 6327.9, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-12-05', 'price': 6327.9, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-12-06', 'price': 6327.9, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-12-07', 'price': 6327.9, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-12-08', 'price': 6327.9, 'merchantId': 20609}, {'prodId': 13567220, 'date': '2025-12-09', 'price': 6327.9, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2025-12-10', 'price': 6327.9, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2025-12-11', 'price': 6399.0, 'merchantId': 20583}, {'prodId': 13567220, 'date': '2025-12-12', 'price': 6399.0, 'merchantId': 4}, {'prodId': 13567220, 'date': '2025-12-13', 'price': 6399.0, 'merchantId': 4}, {'prodId': 13567220, 'date': '2025-12-14', 'price': 6399.0, 'merchantId': 4}, {'prodId': 13567220, 'date': '2025-12-15', 'price': 6399.0, 'merchantId': 4}, {'prodId': 13567220, 'date': '2025-12-16', 'price': 6399.0, 'merchantId': 4}, {'prodId': 13567220, 'date': '2025-12-17', 'price': 6399.0, 'merchantId': 4}, {'prodId': 13567220, 'date': '2025-12-18', 'price': 6399.0, 'merchantId': 4}, {'prodId': 13567220, 'date': '2025-12-19', 'price': 6610.17, 'merchantId': 20583}, {'prodId': 13567220, 'date': '2025-12-20', 'price': 7410.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2025-12-21', 'price': 7410.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2025-12-22', 'price': 7410.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2025-12-23', 'price': 6399.0, 'merchantId': 4}, {'prodId': 13567220, 'date': '2025-12-24', 'price': 6999.0, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2025-12-25', 'price': 7639.99, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-12-26', 'price': 7490.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-12-27', 'price': 6399.0, 'merchantId': 4}, {'prodId': 13567220, 'date': '2025-12-28', 'price': 7490.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-12-29', 'price': 7490.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-12-30', 'price': 7490.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2025-12-31', 'price': 7490.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2026-01-01', 'price': 7649.08, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2026-01-02', 'price': 6999.0, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-01-03', 'price': 7649.08, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2026-01-04', 'price': 7649.08, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2026-01-05', 'price': 6999.0, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-01-06', 'price': 7221.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2026-01-07', 'price': 7221.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2026-01-08', 'price': 7221.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2026-01-09', 'price': 7221.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2026-01-10', 'price': 7221.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2026-01-11', 'price': 6168.67, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2026-01-12', 'price': 6168.67, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2026-01-13', 'price': 6168.67, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2026-01-14', 'price': 6168.67, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2026-01-15', 'price': 6168.67, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2026-01-16', 'price': 6168.67, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2026-01-17', 'price': 6168.67, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2026-01-18', 'price': 6168.67, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2026-01-19', 'price': 6168.67, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2026-01-20', 'price': 6168.67, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2026-01-21', 'price': 6168.67, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2026-01-22', 'price': 6335.91, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-01-23', 'price': 6335.91, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-01-24', 'price': 6335.91, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-01-25', 'price': 6335.91, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-01-26', 'price': 6335.91, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-01-27', 'price': 6335.91, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-01-28', 'price': 6407.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-01-29', 'price': 6407.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-01-30', 'price': 6407.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-01-31', 'price': 6407.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-01', 'price': 6407.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-02', 'price': 6407.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-03', 'price': 6479.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-04', 'price': 7198.99, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-05', 'price': 7198.99, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-06', 'price': 7198.99, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-07', 'price': 7198.99, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-08', 'price': 7198.99, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-09', 'price': 7198.99, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-10', 'price': 6479.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-11', 'price': 6479.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-12', 'price': 6479.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-13', 'price': 6479.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-14', 'price': 6479.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-15', 'price': 6479.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-16', 'price': 6479.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-17', 'price': 6479.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-18', 'price': 6479.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-19', 'price': 6479.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-20', 'price': 6479.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-21', 'price': 6479.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-22', 'price': 6479.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-23', 'price': 6479.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-24', 'price': 6479.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-25', 'price': 6479.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-26', 'price': 6479.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-27', 'price': 6659.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-02-28', 'price': 6659.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-03-01', 'price': 6659.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-03-02', 'price': 6659.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-03-03', 'price': 6659.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-03-04', 'price': 6569.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-03-05', 'price': 6569.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-03-06', 'price': 6569.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-03-07', 'price': 6569.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-03-08', 'price': 6569.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-03-09', 'price': 6569.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-03-10', 'price': 6569.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-03-11', 'price': 6569.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-03-12', 'price': 6569.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-03-13', 'price': 6569.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-03-14', 'price': 6569.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-03-15', 'price': 6569.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-03-16', 'price': 6569.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-03-17', 'price': 6569.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-03-18', 'price': 6999.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2026-03-19', 'price': 6999.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2026-03-20', 'price': 6999.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2026-03-21', 'price': 6999.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2026-03-22', 'price': 7199.0, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-03-23', 'price': 6998.99, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2026-03-24', 'price': 6998.99, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2026-03-25', 'price': 6999.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2026-03-26', 'price': 6999.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2026-03-27', 'price': 6999.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2026-03-28', 'price': 6999.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2026-03-29', 'price': 6999.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2026-03-30', 'price': 6999.0, 'merchantId': 1582}, {'prodId': 13567220, 'date': '2026-03-31', 'price': 6999.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2026-04-01', 'price': 6999.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2026-04-02', 'price': 6407.11, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-04-03', 'price': 6407.11, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-04-04', 'price': 6407.11, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-04-05', 'price': 6407.11, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-04-06', 'price': 6407.11, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-04-07', 'price': 6229.11, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-04-08', 'price': 6229.11, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-04-09', 'price': 6229.11, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-04-10', 'price': 6229.11, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-04-11', 'price': 6299.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-04-12', 'price': 6299.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-04-13', 'price': 6299.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-04-14', 'price': 6299.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-04-15', 'price': 6299.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-04-16', 'price': 6389.1, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-04-17', 'price': 6318.11, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-04-18', 'price': 6318.11, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-04-19', 'price': 6318.11, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-04-20', 'price': 6299.1, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-04-21', 'price': 6159.12, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-04-22', 'price': 6071.12, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-04-23', 'price': 6071.12, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-04-24', 'price': 6071.12, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-04-25', 'price': 6071.12, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-04-26', 'price': 6247.12, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-04-27', 'price': 6247.12, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-04-28', 'price': 6318.11, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-04-29', 'price': 6318.11, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-04-30', 'price': 6229.11, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-05-01', 'price': 6229.11, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-05-02', 'price': 6229.11, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-05-03', 'price': 6229.11, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-05-04', 'price': 6159.12, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-05-05', 'price': 6159.12, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-05-06', 'price': 6159.12, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-05-07', 'price': 6159.12, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-05-08', 'price': 6159.12, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-05-09', 'price': 6159.12, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-05-10', 'price': 6159.12, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-05-11', 'price': 6159.12, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-05-12', 'price': 6159.12, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-05-13', 'price': 6139.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2026-05-14', 'price': 6159.12, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-05-15', 'price': 6159.12, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-05-16', 'price': 6159.12, 'merchantId': 20583}, {'prodId': 13567220, 'date': '2026-05-17', 'price': 6159.12, 'merchantId': 20583}, {'prodId': 13567220, 'date': '2026-05-18', 'price': 6159.12, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-05-19', 'price': 6159.12, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-05-20', 'price': 5799.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2026-05-21', 'price': 6019.14, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-05-22', 'price': 6019.14, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-05-23', 'price': 6019.14, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-05-24', 'price': 6019.14, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-05-25', 'price': 6019.14, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-05-26', 'price': 6019.14, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-05-27', 'price': 6019.14, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-05-28', 'price': 5933.14, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-05-29', 'price': 5933.14, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-05-30', 'price': 5933.14, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-05-31', 'price': 5933.14, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-06-01', 'price': 5933.14, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-06-02', 'price': 5933.14, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-06-03', 'price': 5331.14, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-06-04', 'price': 5455.12, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-06-05', 'price': 5455.12, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-06-06', 'price': 5455.12, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-06-07', 'price': 5455.12, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-06-08', 'price': 5455.12, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-06-09', 'price': 5455.12, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-06-10', 'price': 5455.12, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-06-11', 'price': 5455.12, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-06-12', 'price': 5455.12, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-06-13', 'price': 5455.12, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-06-14', 'price': 5455.12, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-06-15', 'price': 5455.12, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-06-16', 'price': 5455.12, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-06-17', 'price': 5455.12, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-06-18', 'price': 5455.12, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-06-19', 'price': 6159.12, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-06-20', 'price': 6159.12, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-06-21', 'price': 6159.12, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-06-22', 'price': 6159.12, 'merchantId': 22905}, {'prodId': 13567220, 'date': '2026-06-23', 'price': 6335.12, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-06-24', 'price': 6335.12, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-06-25', 'price': 6478.99, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-06-26', 'price': 6478.99, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-06-27', 'price': 6478.99, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-06-28', 'price': 6478.99, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-06-29', 'price': 6478.99, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-06-30', 'price': 6478.99, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-07-01', 'price': 6478.99, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-07-02', 'price': 5999.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2026-07-03', 'price': 5999.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2026-07-04', 'price': 6335.01, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-07-05', 'price': 5999.0, 'merchantId': 9385}, {'prodId': 13567220, 'date': '2026-07-06', 'price': 6335.01, 'merchantId': 20612}, {'prodId': 13567220, 'date': '2026-07-07', 'price': 5865.69, 'merchantId': 20612}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 12474762, 'date': '2025-07-07', 'price': 4499.1, 'merchantId': 22902}, {'prodId': 12474762, 'date': '2025-07-08', 'price': 4499.1, 'merchantId': 22902}, {'prodId': 12474762, 'date': '2025-07-09', 'price': 4499.1, 'merchantId': 22902}, {'prodId': 12474762, 'date': '2025-07-10', 'price': 4499.1, 'merchantId': 22902}, {'prodId': 12474762, 'date': '2025-07-11', 'price': 4499.1, 'merchantId': 22902}, {'prodId': 12474762, 'date': '2025-07-12', 'price': 4499.1, 'merchantId': 22902}, {'prodId': 12474762, 'date': '2025-07-13', 'price': 4499.1, 'merchantId': 22902}, {'prodId': 12474762, 'date': '2025-07-14', 'price': 4499.1, 'merchantId': 22902}, {'prodId': 12474762, 'date': '2025-07-15', 'price': 3699.0, 'merchantId': 10763}, {'prodId': 12474762, 'date': '2025-07-16', 'price': 3699.0, 'merchantId': 10763}, {'prodId': 12474762, 'date': '2025-07-17', 'price': 3509.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-07-18', 'price': 3554.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-07-19', 'price': 3554.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-07-20', 'price': 3554.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-07-21', 'price': 3554.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-07-22', 'price': 3554.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-07-23', 'price': 3554.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-07-24', 'price': 3554.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-07-25', 'price': 3554.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-07-26', 'price': 3554.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-07-27', 'price': 3554.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-07-28', 'price': 3554.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-07-29', 'price': 3554.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-07-30', 'price': 3554.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-07-31', 'price': 3554.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-01', 'price': 3554.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-02', 'price': 3554.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-03', 'price': 3554.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-04', 'price': 3329.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-05', 'price': 3329.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-06', 'price': 3329.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-07', 'price': 3440.07, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-08', 'price': 3440.07, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-09', 'price': 3440.07, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-10', 'price': 3329.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-11', 'price': 3329.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-12', 'price': 3329.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-13', 'price': 3329.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-14', 'price': 3329.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-15', 'price': 3329.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-16', 'price': 3329.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-17', 'price': 3329.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-18', 'price': 3329.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-19', 'price': 3329.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-20', 'price': 3699.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-21', 'price': 3699.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-22', 'price': 3699.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-23', 'price': 3699.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-24', 'price': 3699.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-25', 'price': 3699.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-26', 'price': 3949.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-27', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-28', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-08-29', 'price': 4020.21, 'merchantId': 16108}, {'prodId': 12474762, 'date': '2025-08-30', 'price': 4020.21, 'merchantId': 16108}, {'prodId': 12474762, 'date': '2025-08-31', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-09-01', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-09-02', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-09-03', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-09-04', 'price': 4020.21, 'merchantId': 16108}, {'prodId': 12474762, 'date': '2025-09-05', 'price': 4020.21, 'merchantId': 16108}, {'prodId': 12474762, 'date': '2025-09-06', 'price': 4020.21, 'merchantId': 16108}, {'prodId': 12474762, 'date': '2025-09-07', 'price': 4020.21, 'merchantId': 16108}, {'prodId': 12474762, 'date': '2025-09-08', 'price': 4020.21, 'merchantId': 16108}, {'prodId': 12474762, 'date': '2025-09-09', 'price': 4020.21, 'merchantId': 16108}, {'prodId': 12474762, 'date': '2025-09-10', 'price': 4020.21, 'merchantId': 16108}, {'prodId': 12474762, 'date': '2025-09-11', 'price': 4020.21, 'merchantId': 16108}, {'prodId': 12474762, 'date': '2025-09-12', 'price': 4020.21, 'merchantId': 16108}, {'prodId': 12474762, 'date': '2025-09-13', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-09-14', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-09-15', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-09-16', 'price': 4020.21, 'merchantId': 16108}, {'prodId': 12474762, 'date': '2025-09-17', 'price': 4020.21, 'merchantId': 16108}, {'prodId': 12474762, 'date': '2025-09-18', 'price': 4020.21, 'merchantId': 16108}, {'prodId': 12474762, 'date': '2025-09-19', 'price': 4020.21, 'merchantId': 16108}, {'prodId': 12474762, 'date': '2025-09-20', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-09-21', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-09-22', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-09-23', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-09-24', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-09-25', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-09-26', 'price': 3779.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-09-27', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-09-28', 'price': 3866.31, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-09-29', 'price': 3779.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-09-30', 'price': 3779.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-01', 'price': 3779.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-02', 'price': 3779.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-03', 'price': 3779.1, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-04', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-05', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-06', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-07', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-08', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-09', 'price': 4199.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-10', 'price': 3699.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-11', 'price': 3699.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-12', 'price': 3699.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-13', 'price': 3699.0, 'merchantId': 21}, {'prodId': 12474762, 'date': '2025-10-14', 'price': 3699.0, 'merchantId': 21}, {'prodId': 12474762, 'date': '2025-10-15', 'price': 3616.8, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-16', 'price': 3616.8, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-17', 'price': 3695.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-18', 'price': 3695.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-19', 'price': 3695.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-20', 'price': 3695.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-21', 'price': 3695.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-22', 'price': 3695.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-23', 'price': 3695.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-24', 'price': 3607.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-25', 'price': 3607.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-26', 'price': 3607.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-27', 'price': 3607.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-28', 'price': 3607.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-29', 'price': 3607.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-30', 'price': 3607.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-10-31', 'price': 3607.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-11-01', 'price': 3607.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-11-02', 'price': 3622.95, 'merchantId': 23326}, {'prodId': 12474762, 'date': '2025-11-03', 'price': 3167.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-11-04', 'price': 3167.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-11-05', 'price': 3167.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-11-06', 'price': 3167.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-11-07', 'price': 3149.0, 'merchantId': 21}, {'prodId': 12474762, 'date': '2025-11-08', 'price': 3149.0, 'merchantId': 21}, {'prodId': 12474762, 'date': '2025-11-09', 'price': 3167.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-11-10', 'price': 3149.0, 'merchantId': 21}, {'prodId': 12474762, 'date': '2025-11-11', 'price': 3149.0, 'merchantId': 21}, {'prodId': 12474762, 'date': '2025-11-12', 'price': 3149.0, 'merchantId': 21}, {'prodId': 12474762, 'date': '2025-11-13', 'price': 3167.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-11-14', 'price': 3167.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-11-15', 'price': 3167.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-11-16', 'price': 3167.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-11-17', 'price': 3167.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-11-18', 'price': 2815.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-11-19', 'price': 3167.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-11-20', 'price': 3167.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-11-21', 'price': 3167.12, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-11-22', 'price': 3167.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-11-23', 'price': 3167.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-11-24', 'price': 3167.12, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-11-25', 'price': 3349.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-11-26', 'price': 3349.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-11-27', 'price': 3999.0, 'merchantId': 2}, {'prodId': 12474762, 'date': '2025-11-28', 'price': 3149.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-11-29', 'price': 3255.8, 'merchantId': 21627}, {'prodId': 12474762, 'date': '2025-11-30', 'price': 3255.8, 'merchantId': 21627}, {'prodId': 12474762, 'date': '2025-12-01', 'price': 2737.21, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2025-12-02', 'price': 3149.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-12-03', 'price': 3149.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-12-04', 'price': 3255.8, 'merchantId': 21627}, {'prodId': 12474762, 'date': '2025-12-05', 'price': 3999.0, 'merchantId': 2}, {'prodId': 12474762, 'date': '2025-12-06', 'price': 3255.8, 'merchantId': 21627}, {'prodId': 12474762, 'date': '2025-12-07', 'price': 3409.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-12-08', 'price': 3409.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-12-09', 'price': 3409.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-12-10', 'price': 3409.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-12-11', 'price': 3409.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-12-12', 'price': 3409.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-12-13', 'price': 3255.8, 'merchantId': 21627}, {'prodId': 12474762, 'date': '2025-12-14', 'price': 3255.8, 'merchantId': 21629}, {'prodId': 12474762, 'date': '2025-12-15', 'price': 3409.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-12-16', 'price': 3409.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-12-17', 'price': 3409.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-12-18', 'price': 3409.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-12-19', 'price': 3169.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-12-20', 'price': 3169.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-12-21', 'price': 3169.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-12-22', 'price': 3169.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-12-23', 'price': 3169.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-12-24', 'price': 3169.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-12-25', 'price': 3169.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-12-26', 'price': 3169.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-12-27', 'price': 3169.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-12-28', 'price': 3169.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-12-29', 'price': 3169.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-12-30', 'price': 3169.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2025-12-31', 'price': 3169.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-01-01', 'price': 3169.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-01-02', 'price': 3169.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-01-03', 'price': 3169.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-01-04', 'price': 3169.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-01-05', 'price': 3169.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-01-06', 'price': 3169.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-01-07', 'price': 3169.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-01-08', 'price': 3169.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-01-09', 'price': 3169.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-01-10', 'price': 3169.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-01-11', 'price': 3169.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-01-12', 'price': 3169.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-01-13', 'price': 3169.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-01-14', 'price': 3169.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-01-15', 'price': 4699.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-01-16', 'price': 4699.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-01-17', 'price': 4699.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-01-18', 'price': 4699.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-01-19', 'price': 4699.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-01-20', 'price': 4099.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2026-01-21', 'price': 4699.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-01-22', 'price': 4699.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-01-23', 'price': 4699.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-01-24', 'price': 4699.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-01-25', 'price': 4699.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-01-26', 'price': 4699.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-01-27', 'price': 4699.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-01-28', 'price': 4699.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-01-29', 'price': 4099.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2026-01-30', 'price': 4099.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2026-01-31', 'price': 3119.87, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-02-01', 'price': 3119.87, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-02-02', 'price': 3119.87, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-02-03', 'price': 4099.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2026-02-04', 'price': 4099.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2026-02-05', 'price': 4052.0, 'merchantId': 23326}, {'prodId': 12474762, 'date': '2026-02-06', 'price': 4052.0, 'merchantId': 23326}, {'prodId': 12474762, 'date': '2026-02-07', 'price': 4699.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-02-08', 'price': 4699.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-02-09', 'price': 4699.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-02-10', 'price': 4699.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-02-11', 'price': 4699.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-02-12', 'price': 4319.1, 'merchantId': 20609}, {'prodId': 12474762, 'date': '2026-02-13', 'price': 4319.1, 'merchantId': 20609}, {'prodId': 12474762, 'date': '2026-02-14', 'price': 4699.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-02-15', 'price': 4699.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-02-16', 'price': 4699.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-02-17', 'price': 4699.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-02-18', 'price': 4558.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-02-19', 'price': 4558.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-02-20', 'price': 4558.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-02-21', 'price': 4558.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-02-22', 'price': 4558.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-02-23', 'price': 4099.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2026-02-24', 'price': 4099.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2026-02-25', 'price': 4099.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2026-02-26', 'price': 4099.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2026-02-27', 'price': 4558.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-02-28', 'price': 4099.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2026-03-01', 'price': 4099.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2026-03-02', 'price': 4099.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2026-03-03', 'price': 4099.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2026-03-04', 'price': 4099.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2026-03-05', 'price': 4099.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2026-03-06', 'price': 4099.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2026-03-07', 'price': 4099.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2026-03-08', 'price': 4099.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2026-03-09', 'price': 3159.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-03-10', 'price': 3159.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-03-11', 'price': 2903.57, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-03-12', 'price': 2903.57, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-03-13', 'price': 2903.57, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-03-14', 'price': 2903.57, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-03-15', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-03-16', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-03-17', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-03-18', 'price': 2903.57, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-03-19', 'price': 2903.57, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-03-20', 'price': 2903.57, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-03-21', 'price': 2903.57, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-03-22', 'price': 4289.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-03-23', 'price': 4289.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-03-24', 'price': 2903.57, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-03-25', 'price': 4289.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-03-26', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-03-27', 'price': 2903.57, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-03-28', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-03-29', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-03-30', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-03-31', 'price': 4289.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-04-01', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-04-02', 'price': 4289.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-04-03', 'price': 4289.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-04-04', 'price': 4289.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-04-05', 'price': 4099.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2026-04-06', 'price': 2759.37, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-04-07', 'price': 2759.37, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-04-08', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-04-09', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-04-10', 'price': 2759.37, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-04-11', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-04-12', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-04-13', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-04-14', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-04-15', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-04-16', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-04-17', 'price': 2679.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-04-18', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-04-19', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-04-20', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-04-21', 'price': 4196.0, 'merchantId': 2}, {'prodId': 12474762, 'date': '2026-04-22', 'price': 4289.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-04-23', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-04-24', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-04-25', 'price': 4099.0, 'merchantId': 9385}, {'prodId': 12474762, 'date': '2026-04-26', 'price': 4099.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-04-27', 'price': 4196.0, 'merchantId': 2}, {'prodId': 12474762, 'date': '2026-04-28', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-04-29', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-04-30', 'price': 5919.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-05-01', 'price': 4196.0, 'merchantId': 2}, {'prodId': 12474762, 'date': '2026-05-02', 'price': 5919.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-05-03', 'price': 5919.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-05-04', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-05-05', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-05-06', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-05-07', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-05-08', 'price': 3069.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-05-09', 'price': 3159.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-05-10', 'price': 3159.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-05-11', 'price': 3159.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-05-12', 'price': 5919.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-05-13', 'price': 5919.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-05-14', 'price': 5919.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-05-15', 'price': 5919.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-05-16', 'price': 5919.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-05-17', 'price': 5919.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-05-18', 'price': 3999.0, 'merchantId': 20609}, {'prodId': 12474762, 'date': '2026-05-19', 'price': 5659.9, 'merchantId': 21}, {'prodId': 12474762, 'date': '2026-05-20', 'price': 3999.0, 'merchantId': 20609}, {'prodId': 12474762, 'date': '2026-05-21', 'price': 3159.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-05-22', 'price': 2944.77, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-05-23', 'price': 2944.77, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-05-24', 'price': 2944.77, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-05-25', 'price': 2944.77, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-05-26', 'price': 3159.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-05-27', 'price': 3159.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-05-28', 'price': 3159.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-05-29', 'price': 3159.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-05-30', 'price': 3159.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-05-31', 'price': 3159.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-01', 'price': 3159.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-02', 'price': 3159.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-03', 'price': 3159.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-04', 'price': 3159.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-05', 'price': 3161.07, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-06', 'price': 3161.07, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-07', 'price': 3159.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-08', 'price': 3159.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-09', 'price': 3159.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-10', 'price': 3159.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-11', 'price': 3159.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-12', 'price': 2934.47, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-13', 'price': 2934.47, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-14', 'price': 2934.47, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-15', 'price': 2934.47, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-16', 'price': 3009.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-17', 'price': 3009.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-18', 'price': 3009.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-19', 'price': 2934.47, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-20', 'price': 2934.47, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-21', 'price': 2934.47, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-22', 'price': 2884.47, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-23', 'price': 2884.47, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-24', 'price': 2884.47, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-25', 'price': 2884.47, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-26', 'price': 2884.47, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-27', 'price': 2884.47, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-28', 'price': 2884.47, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-29', 'price': 2854.47, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-06-30', 'price': 2854.47, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-07-01', 'price': 2512.1699999999996, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-07-02', 'price': 2512.1699999999996, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-07-03', 'price': 2512.1699999999996, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-07-04', 'price': 3009.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-07-05', 'price': 3009.0, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-07-06', 'price': 2512.1699999999996, 'merchantId': 1582}, {'prodId': 12474762, 'date': '2026-07-07', 'price': 2512.1699999999996, 'merchantId': 1582}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13991991, 'date': '2025-07-07', 'price': 1445.9, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-07-08', 'price': 1439.0, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-07-09', 'price': 1439.0, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-07-10', 'price': 1439.0, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-07-11', 'price': 1439.0, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-07-12', 'price': 1439.0, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-07-13', 'price': 1439.0, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-07-14', 'price': 1439.0, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-07-15', 'price': 1392.3, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-07-16', 'price': 1392.3, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-07-17', 'price': 1392.3, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-07-18', 'price': 1392.3, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-07-19', 'price': 1392.3, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-07-20', 'price': 1392.3, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-07-21', 'price': 1392.3, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-07-22', 'price': 1392.3, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-07-23', 'price': 1388.9, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-07-24', 'price': 1388.9, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-07-25', 'price': 1388.9, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-07-26', 'price': 1388.9, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-07-27', 'price': 1388.9, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-07-28', 'price': 1388.9, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-07-29', 'price': 1339.9, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-07-30', 'price': 1339.9, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-07-31', 'price': 1339.9, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-08-01', 'price': 1339.9, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-08-02', 'price': 1392.3, 'merchantId': 20612}, {'prodId': 13991991, 'date': '2025-08-03', 'price': 1399.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-08-04', 'price': 1399.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-08-05', 'price': 1391.13, 'merchantId': 20583}, {'prodId': 13991991, 'date': '2025-08-06', 'price': 1391.13, 'merchantId': 20583}, {'prodId': 13991991, 'date': '2025-08-07', 'price': 1391.13, 'merchantId': 20583}, {'prodId': 13991991, 'date': '2025-08-08', 'price': 1391.13, 'merchantId': 20609}, {'prodId': 13991991, 'date': '2025-08-09', 'price': 1405.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-08-10', 'price': 1406.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-08-11', 'price': 1406.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-08-12', 'price': 1415.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-08-13', 'price': 1439.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-08-14', 'price': 1439.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-08-15', 'price': 1439.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-08-16', 'price': 1439.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-08-17', 'price': 1439.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-08-18', 'price': 1439.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-08-19', 'price': 1439.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-08-20', 'price': 1439.99, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2025-08-21', 'price': 1439.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-08-22', 'price': 1439.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-08-23', 'price': 1439.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-08-24', 'price': 1439.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-08-25', 'price': 1438.39, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-08-26', 'price': 1439.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-08-27', 'price': 1438.39, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-08-28', 'price': 1438.39, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-08-29', 'price': 1438.39, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-08-30', 'price': 1439.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-08-31', 'price': 1439.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-09-01', 'price': 1423.11, 'merchantId': 20609}, {'prodId': 13991991, 'date': '2025-09-02', 'price': 1372.8, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-09-03', 'price': 1349.1, 'merchantId': 20583}, {'prodId': 13991991, 'date': '2025-09-04', 'price': 1349.1, 'merchantId': 20583}, {'prodId': 13991991, 'date': '2025-09-05', 'price': 1349.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-09-06', 'price': 1349.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-09-07', 'price': 1349.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-09-08', 'price': 1349.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-09-09', 'price': 1349.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-09-10', 'price': 1298.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-09-11', 'price': 1298.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-09-12', 'price': 1325.7, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-09-13', 'price': 1298.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-09-14', 'price': 1349.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-09-15', 'price': 1298.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-09-16', 'price': 1298.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-09-17', 'price': 1334.11, 'merchantId': 20609}, {'prodId': 13991991, 'date': '2025-09-18', 'price': 1298.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-09-19', 'price': 1298.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-09-20', 'price': 1298.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-09-21', 'price': 1299.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-09-22', 'price': 1299.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-09-23', 'price': 1298.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-09-24', 'price': 1298.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-09-25', 'price': 1299.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-09-26', 'price': 1299.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-09-27', 'price': 1299.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-09-28', 'price': 1298.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-09-29', 'price': 1298.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-09-30', 'price': 1349.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-10-01', 'price': 1349.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-10-02', 'price': 1278.7, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-10-03', 'price': 1278.7, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-10-04', 'price': 1295.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-10-05', 'price': 1295.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-10-06', 'price': 1349.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-10-07', 'price': 1298.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-10-08', 'price': 1230.25, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-10-09', 'price': 1229.3, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-10-10', 'price': 1249.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-10-11', 'price': 1249.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-10-12', 'price': 1259.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-10-13', 'price': 1259.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-10-14', 'price': 1259.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2025-10-15', 'price': 1212.55, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-10-16', 'price': 1299.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-10-17', 'price': 1284.92, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-10-18', 'price': 1349.99, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2025-10-19', 'price': 1349.99, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2025-10-20', 'price': 1349.99, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2025-10-21', 'price': 1349.99, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2025-10-22', 'price': 1319.67, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-10-23', 'price': 1328.97, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-10-24', 'price': 1349.99, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2025-10-25', 'price': 1329.05, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-10-26', 'price': 1349.99, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2025-10-27', 'price': 1284.92, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-10-28', 'price': 1349.99, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2025-10-29', 'price': 1366.17, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-10-30', 'price': 1366.17, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-10-31', 'price': 1298.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-11-01', 'price': 1356.87, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-11-02', 'price': 1439.1, 'merchantId': 34}, {'prodId': 13991991, 'date': '2025-11-03', 'price': 1342.28, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-11-04', 'price': 1283.92, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-11-05', 'price': 1287.08, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-11-06', 'price': 1287.08, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-11-07', 'price': 1287.08, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-11-08', 'price': 1287.08, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-11-09', 'price': 1287.08, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-11-10', 'price': 1255.7, 'merchantId': 20583}, {'prodId': 13991991, 'date': '2025-11-11', 'price': 1255.7, 'merchantId': 20583}, {'prodId': 13991991, 'date': '2025-11-12', 'price': 1255.7, 'merchantId': 20583}, {'prodId': 13991991, 'date': '2025-11-13', 'price': 1255.7, 'merchantId': 20583}, {'prodId': 13991991, 'date': '2025-11-14', 'price': 1215.05, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-11-15', 'price': 1215.05, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-11-16', 'price': 1215.05, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-11-17', 'price': 1279.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-11-18', 'price': 1279.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-11-19', 'price': 1287.08, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-11-20', 'price': 1287.08, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-11-21', 'price': 1287.08, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-11-22', 'price': 1287.08, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-11-23', 'price': 1298.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-11-24', 'price': 1287.08, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-11-25', 'price': 1287.08, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-11-26', 'price': 1287.08, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-11-27', 'price': 1287.08, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-11-28', 'price': 1284.56, 'merchantId': 20583}, {'prodId': 13991991, 'date': '2025-11-29', 'price': 1284.56, 'merchantId': 20583}, {'prodId': 13991991, 'date': '2025-11-30', 'price': 1284.56, 'merchantId': 20583}, {'prodId': 13991991, 'date': '2025-12-01', 'price': 1284.56, 'merchantId': 20583}, {'prodId': 13991991, 'date': '2025-12-02', 'price': 1287.08, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-12-03', 'price': 1287.08, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-12-04', 'price': 1287.08, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-12-05', 'price': 1287.08, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-12-06', 'price': 1299.0, 'merchantId': 20583}, {'prodId': 13991991, 'date': '2025-12-07', 'price': 1299.0, 'merchantId': 20583}, {'prodId': 13991991, 'date': '2025-12-08', 'price': 1299.0, 'merchantId': 20583}, {'prodId': 13991991, 'date': '2025-12-09', 'price': 1299.0, 'merchantId': 20583}, {'prodId': 13991991, 'date': '2025-12-10', 'price': 1333.86, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-12-11', 'price': 1305.48, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-12-12', 'price': 1305.48, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-12-13', 'price': 1305.48, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-12-14', 'price': 1305.48, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-12-15', 'price': 1305.48, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-12-16', 'price': 1305.48, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-12-17', 'price': 1305.48, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2025-12-18', 'price': 1299.0, 'merchantId': 20609}, {'prodId': 13991991, 'date': '2025-12-19', 'price': 1299.0, 'merchantId': 20609}, {'prodId': 13991991, 'date': '2025-12-20', 'price': 1329.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-12-21', 'price': 1329.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-12-22', 'price': 1329.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-12-23', 'price': 1329.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-12-24', 'price': 1299.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-12-25', 'price': 1299.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-12-26', 'price': 1299.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-12-27', 'price': 1299.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-12-28', 'price': 1389.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-12-29', 'price': 1299.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-12-30', 'price': 1389.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2025-12-31', 'price': 1389.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-01-01', 'price': 1389.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-01-02', 'price': 1399.0, 'merchantId': 21627}, {'prodId': 13991991, 'date': '2026-01-03', 'price': 1299.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-01-04', 'price': 1389.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-01-05', 'price': 1299.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-01-06', 'price': 1299.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-01-07', 'price': 1389.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-01-08', 'price': 1348.2, 'merchantId': 22902}, {'prodId': 13991991, 'date': '2026-01-09', 'price': 1348.2, 'merchantId': 22902}, {'prodId': 13991991, 'date': '2026-01-10', 'price': 1439.91, 'merchantId': 20612}, {'prodId': 13991991, 'date': '2026-01-11', 'price': 1389.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-01-12', 'price': 1389.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-01-13', 'price': 1389.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-01-14', 'price': 1439.91, 'merchantId': 20612}, {'prodId': 13991991, 'date': '2026-01-15', 'price': 1439.91, 'merchantId': 20612}, {'prodId': 13991991, 'date': '2026-01-16', 'price': 1439.91, 'merchantId': 20612}, {'prodId': 13991991, 'date': '2026-01-17', 'price': 1439.91, 'merchantId': 20612}, {'prodId': 13991991, 'date': '2026-01-18', 'price': 1439.91, 'merchantId': 20612}, {'prodId': 13991991, 'date': '2026-01-19', 'price': 1439.91, 'merchantId': 20612}, {'prodId': 13991991, 'date': '2026-01-20', 'price': 1439.91, 'merchantId': 20612}, {'prodId': 13991991, 'date': '2026-01-21', 'price': 1439.91, 'merchantId': 20612}, {'prodId': 13991991, 'date': '2026-01-22', 'price': 1439.91, 'merchantId': 20612}, {'prodId': 13991991, 'date': '2026-01-23', 'price': 1439.91, 'merchantId': 20612}, {'prodId': 13991991, 'date': '2026-01-24', 'price': 1419.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-01-25', 'price': 1419.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-01-26', 'price': 1419.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-01-27', 'price': 1399.9, 'merchantId': 20583}, {'prodId': 13991991, 'date': '2026-01-28', 'price': 1399.9, 'merchantId': 20583}, {'prodId': 13991991, 'date': '2026-01-29', 'price': 1399.9, 'merchantId': 20583}, {'prodId': 13991991, 'date': '2026-01-30', 'price': 1399.9, 'merchantId': 20583}, {'prodId': 13991991, 'date': '2026-01-31', 'price': 1399.9, 'merchantId': 20583}, {'prodId': 13991991, 'date': '2026-02-01', 'price': 1399.9, 'merchantId': 20583}, {'prodId': 13991991, 'date': '2026-02-02', 'price': 1415.8, 'merchantId': 22902}, {'prodId': 13991991, 'date': '2026-02-03', 'price': 1349.1, 'merchantId': 20583}, {'prodId': 13991991, 'date': '2026-02-04', 'price': 1349.1, 'merchantId': 20583}, {'prodId': 13991991, 'date': '2026-02-05', 'price': 1440.57, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2026-02-06', 'price': 1440.57, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2026-02-07', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-02-08', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-02-09', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-02-10', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-02-11', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-02-12', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-02-13', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-02-14', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-02-15', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-02-16', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-02-17', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-02-18', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-02-19', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-02-20', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-02-21', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-02-22', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-02-23', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-02-24', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-02-25', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-02-26', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-02-27', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-02-28', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-03-01', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-03-02', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-03-03', 'price': 1237.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-03-04', 'price': 1299.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-03-05', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-03-06', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-03-07', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-03-08', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-03-09', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-03-10', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-03-11', 'price': 1403.91, 'merchantId': 20609}, {'prodId': 13991991, 'date': '2026-03-12', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-03-13', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-03-14', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-03-15', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-03-16', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-03-17', 'price': 1388.64, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2026-03-18', 'price': 1388.64, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2026-03-19', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-03-20', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-03-21', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-03-22', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-03-23', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-03-24', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-03-25', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-03-26', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-03-27', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-03-28', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-03-29', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-03-30', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-03-31', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-04-01', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-04-02', 'price': 1495.76, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-04-03', 'price': 1529.0, 'merchantId': 16108}, {'prodId': 13991991, 'date': '2026-04-04', 'price': 1529.0, 'merchantId': 16108}, {'prodId': 13991991, 'date': '2026-04-05', 'price': 1529.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-04-06', 'price': 1448.0, 'merchantId': 34}, {'prodId': 13991991, 'date': '2026-04-07', 'price': 1513.1, 'merchantId': 2}, {'prodId': 13991991, 'date': '2026-04-08', 'price': 1513.1, 'merchantId': 2}, {'prodId': 13991991, 'date': '2026-04-09', 'price': 1513.1, 'merchantId': 2}, {'prodId': 13991991, 'date': '2026-04-10', 'price': 1513.1, 'merchantId': 2}, {'prodId': 13991991, 'date': '2026-04-11', 'price': 1513.1, 'merchantId': 2}, {'prodId': 13991991, 'date': '2026-04-12', 'price': 1479.47, 'merchantId': 245}, {'prodId': 13991991, 'date': '2026-04-13', 'price': 1479.47, 'merchantId': 245}, {'prodId': 13991991, 'date': '2026-04-14', 'price': 1479.47, 'merchantId': 245}, {'prodId': 13991991, 'date': '2026-04-15', 'price': 1479.47, 'merchantId': 245}, {'prodId': 13991991, 'date': '2026-04-16', 'price': 1411.68, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-04-17', 'price': 1514.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-04-18', 'price': 1513.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-04-19', 'price': 1519.91, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-04-20', 'price': 1510.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-04-21', 'price': 1510.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-04-22', 'price': 1510.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-04-23', 'price': 1499.91, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-04-24', 'price': 1499.91, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-04-25', 'price': 1510.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-04-26', 'price': 1510.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-04-27', 'price': 1529.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-04-28', 'price': 1499.0, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2026-04-29', 'price': 1499.0, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2026-04-30', 'price': 1499.0, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2026-05-01', 'price': 1499.0, 'merchantId': 23326}, {'prodId': 13991991, 'date': '2026-05-02', 'price': 1529.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-05-03', 'price': 1489.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-05-04', 'price': 1529.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-05-05', 'price': 1489.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-05-06', 'price': 1529.0, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-05-07', 'price': 1529.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-05-08', 'price': 1439.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-05-09', 'price': 1439.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-05-10', 'price': 1439.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-05-11', 'price': 1439.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-05-12', 'price': 1499.9, 'merchantId': 16108}, {'prodId': 13991991, 'date': '2026-05-13', 'price': 1511.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-05-14', 'price': 1511.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-05-15', 'price': 1511.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-05-16', 'price': 1439.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-05-17', 'price': 1439.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-05-18', 'price': 1439.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-05-19', 'price': 1439.1, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-05-20', 'price': 1392.0, 'merchantId': 16108}, {'prodId': 13991991, 'date': '2026-05-21', 'price': 1392.0, 'merchantId': 16108}, {'prodId': 13991991, 'date': '2026-05-22', 'price': 1484.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-05-23', 'price': 1484.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-05-24', 'price': 1484.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-05-25', 'price': 1484.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-05-26', 'price': 1484.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-05-27', 'price': 1475.9, 'merchantId': 16108}, {'prodId': 13991991, 'date': '2026-05-28', 'price': 1471.08, 'merchantId': 20583}, {'prodId': 13991991, 'date': '2026-05-29', 'price': 1471.08, 'merchantId': 20583}, {'prodId': 13991991, 'date': '2026-05-30', 'price': 1484.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-05-31', 'price': 1484.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-06-01', 'price': 1421.32, 'merchantId': 1582}, {'prodId': 13991991, 'date': '2026-06-02', 'price': 1484.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-06-03', 'price': 1484.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-06-04', 'price': 1484.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-06-05', 'price': 1484.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-06-06', 'price': 1484.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-06-07', 'price': 1484.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-06-08', 'price': 1484.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-06-09', 'price': 1484.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-06-10', 'price': 1484.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-06-11', 'price': 1484.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-06-12', 'price': 1484.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-06-13', 'price': 1484.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-06-14', 'price': 1484.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-06-15', 'price': 932.9, 'merchantId': 22905}, {'prodId': 13991991, 'date': '2026-06-16', 'price': 1484.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-06-17', 'price': 1484.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-06-18', 'price': 1484.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-06-19', 'price': 1484.1, 'merchantId': 23254}, {'prodId': 13991991, 'date': '2026-06-20', 'price': 1421.34, 'merchantId': 245}, {'prodId': 13991991, 'date': '2026-06-21', 'price': 1421.34, 'merchantId': 245}, {'prodId': 13991991, 'date': '2026-06-22', 'price': 1421.34, 'merchantId': 245}, {'prodId': 13991991, 'date': '2026-06-23', 'price': 1421.34, 'merchantId': 245}, {'prodId': 13991991, 'date': '2026-06-24', 'price': 1421.34, 'merchantId': 245}, {'prodId': 13991991, 'date': '2026-06-25', 'price': 1421.34, 'merchantId': 245}, {'prodId': 13991991, 'date': '2026-06-26', 'price': 1421.34, 'merchantId': 245}, {'prodId': 13991991, 'date': '2026-06-27', 'price': 1421.34, 'merchantId': 245}, {'prodId': 13991991, 'date': '2026-06-28', 'price': 1421.34, 'merchantId': 245}, {'prodId': 13991991, 'date': '2026-06-29', 'price': 1421.34, 'merchantId': 245}, {'prodId': 13991991, 'date': '2026-06-30', 'price': 1421.34, 'merchantId': 245}, {'prodId': 13991991, 'date': '2026-07-01', 'price': 1421.34, 'merchantId': 245}, {'prodId': 13991991, 'date': '2026-07-02', 'price': 1421.34, 'merchantId': 245}, {'prodId': 13991991, 'date': '2026-07-03', 'price': 1421.34, 'merchantId': 245}, {'prodId': 13991991, 'date': '2026-07-04', 'price': 1421.34, 'merchantId': 245}, {'prodId': 13991991, 'date': '2026-07-05', 'price': 1421.34, 'merchantId': 245}, {'prodId': 13991991, 'date': '2026-07-06', 'price': 1421.34, 'merchantId': 245}, {'prodId': 13991991, 'date': '2026-07-07', 'price': 1421.34, 'merchantId': 245}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13993126, 'date': '2025-09-25', 'price': 1070.15, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2025-09-26', 'price': 1070.15, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2025-09-27', 'price': 1070.15, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2025-09-28', 'price': 1070.15, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2025-09-29', 'price': 1070.15, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2025-09-30', 'price': 965.08, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2025-10-01', 'price': 965.08, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2025-10-02', 'price': 965.08, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2025-10-03', 'price': 965.08, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2025-10-04', 'price': 965.08, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2025-10-05', 'price': 965.08, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2025-10-06', 'price': 965.08, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2025-10-07', 'price': 975.57, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2025-10-08', 'price': 975.57, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2025-10-09', 'price': 975.57, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2025-10-10', 'price': 996.55, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2025-10-11', 'price': 996.55, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2025-10-12', 'price': 996.55, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2025-10-13', 'price': 996.55, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2025-10-14', 'price': 996.55, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2025-10-15', 'price': 996.55, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2025-10-16', 'price': 1240.5, 'merchantId': 22906}, {'prodId': 13993126, 'date': '2025-10-17', 'price': 1240.5, 'merchantId': 22906}, {'prodId': 13993126, 'date': '2025-10-18', 'price': 1240.5, 'merchantId': 22906}, {'prodId': 13993126, 'date': '2025-10-19', 'price': 1240.5, 'merchantId': 22906}, {'prodId': 13993126, 'date': '2025-10-20', 'price': 1240.5, 'merchantId': 22906}, {'prodId': 13993126, 'date': '2025-10-21', 'price': 1240.5, 'merchantId': 22906}, {'prodId': 13993126, 'date': '2025-10-22', 'price': 1240.5, 'merchantId': 22906}, {'prodId': 13993126, 'date': '2025-10-23', 'price': 1240.5, 'merchantId': 22906}, {'prodId': 13993126, 'date': '2025-10-24', 'price': 1240.5, 'merchantId': 22906}, {'prodId': 13993126, 'date': '2025-10-25', 'price': 1240.5, 'merchantId': 22906}, {'prodId': 13993126, 'date': '2025-10-26', 'price': 1240.5, 'merchantId': 22906}, {'prodId': 13993126, 'date': '2025-10-27', 'price': 1240.5, 'merchantId': 22906}, {'prodId': 13993126, 'date': '2025-10-28', 'price': 1240.5, 'merchantId': 22906}, {'prodId': 13993126, 'date': '2025-10-29', 'price': 899.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-10-30', 'price': 899.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-10-31', 'price': 899.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-11-01', 'price': 899.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2025-11-02', 'price': 899.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2025-11-03', 'price': 899.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2025-11-04', 'price': 899.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2025-11-05', 'price': 899.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2025-11-06', 'price': 882.99, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-11-07', 'price': 882.99, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-11-08', 'price': 899.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2025-11-09', 'price': 849.99, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-11-10', 'price': 860.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-11-11', 'price': 849.99, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-11-12', 'price': 840.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-11-13', 'price': 829.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-11-14', 'price': 829.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-11-15', 'price': 840.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-11-16', 'price': 852.89, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-11-17', 'price': 855.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-11-18', 'price': 849.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-11-19', 'price': 810.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-11-20', 'price': 810.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-11-21', 'price': 839.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-11-22', 'price': 845.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-11-23', 'price': 815.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-11-24', 'price': 810.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-11-25', 'price': 809.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2025-11-26', 'price': 809.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2025-11-27', 'price': 809.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2025-11-28', 'price': 809.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2025-11-29', 'price': 809.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2025-11-30', 'price': 809.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2025-12-01', 'price': 809.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2025-12-02', 'price': 839.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2025-12-03', 'price': 839.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2025-12-04', 'price': 839.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2025-12-05', 'price': 839.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2025-12-06', 'price': 880.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-12-07', 'price': 873.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-12-08', 'price': 860.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-12-09', 'price': 839.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2025-12-10', 'price': 839.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2025-12-11', 'price': 839.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2025-12-12', 'price': 839.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2025-12-13', 'price': 839.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2025-12-14', 'price': 839.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2025-12-15', 'price': 839.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2025-12-16', 'price': 837.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2025-12-17', 'price': 837.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2025-12-18', 'price': 837.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2025-12-19', 'price': 837.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2025-12-20', 'price': 837.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2025-12-21', 'price': 837.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2025-12-22', 'price': 837.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2025-12-23', 'price': 889.99, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-12-24', 'price': 888.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-12-25', 'price': 885.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-12-26', 'price': 874.2, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-12-27', 'price': 879.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-12-28', 'price': 890.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-12-29', 'price': 874.2, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-12-30', 'price': 879.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2025-12-31', 'price': 890.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-01-01', 'price': 885.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-01-02', 'price': 885.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-01-03', 'price': 885.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-01-04', 'price': 890.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-01-05', 'price': 885.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-01-06', 'price': 885.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-01-07', 'price': 885.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-01-08', 'price': 902.69, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-01-09', 'price': 885.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-01-10', 'price': 902.69, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-01-11', 'price': 885.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-01-12', 'price': 879.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-01-13', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-01-14', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-01-15', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-01-16', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-01-17', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-01-18', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-01-19', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-01-20', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-01-21', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-01-22', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-01-23', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-01-24', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-01-25', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-01-26', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-01-27', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-01-28', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-01-29', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-01-30', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-01-31', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-02-01', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-02-02', 'price': 846.77, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-02-03', 'price': 846.77, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-02-04', 'price': 846.77, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-02-05', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-02-06', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-02-07', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-02-08', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-02-09', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-02-10', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-02-11', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-02-12', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-02-13', 'price': 879.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-02-14', 'price': 879.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-02-15', 'price': 902.69, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-02-16', 'price': 902.69, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-02-17', 'price': 902.69, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-02-18', 'price': 902.69, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-02-19', 'price': 902.69, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-02-20', 'price': 902.69, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-02-21', 'price': 902.69, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-02-22', 'price': 902.69, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-02-23', 'price': 890.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-02-24', 'price': 890.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-02-25', 'price': 902.69, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-02-26', 'price': 902.69, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-02-27', 'price': 899.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-02-28', 'price': 894.99, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-03-01', 'price': 894.99, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-03-02', 'price': 889.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-03-03', 'price': 889.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-03-04', 'price': 850.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-03-05', 'price': 879.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-03-06', 'price': 879.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-03-07', 'price': 879.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-03-08', 'price': 875.0, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-03-09', 'price': 845.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-03-10', 'price': 845.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-03-11', 'price': 845.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-03-12', 'price': 845.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-03-13', 'price': 829.8, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-03-14', 'price': 829.8, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-03-15', 'price': 829.8, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-03-16', 'price': 829.8, 'merchantId': 15125}, {'prodId': 13993126, 'date': '2026-03-17', 'price': 845.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-03-18', 'price': 875.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-03-19', 'price': 875.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-03-20', 'price': 850.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-03-21', 'price': 875.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-03-22', 'price': 875.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-03-23', 'price': 875.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-03-24', 'price': 895.5, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-03-25', 'price': 895.5, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-03-26', 'price': 895.5, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-03-27', 'price': 890.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-03-28', 'price': 895.5, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-03-29', 'price': 895.5, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-03-30', 'price': 895.5, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-03-31', 'price': 894.9, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-04-01', 'price': 894.9, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-04-02', 'price': 894.9, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-04-03', 'price': 894.9, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-04-04', 'price': 894.9, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-04-05', 'price': 894.9, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-04-06', 'price': 894.9, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-04-07', 'price': 894.9, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-04-08', 'price': 894.9, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-04-09', 'price': 894.9, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-04-10', 'price': 902.69, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-04-11', 'price': 902.69, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-04-12', 'price': 902.69, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-04-13', 'price': 902.69, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-04-14', 'price': 902.69, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-04-15', 'price': 880.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-04-16', 'price': 880.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-04-17', 'price': 880.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-04-18', 'price': 880.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-04-19', 'price': 880.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-04-20', 'price': 880.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-04-21', 'price': 899.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-04-22', 'price': 928.79, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-04-23', 'price': 920.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-04-24', 'price': 928.79, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-04-25', 'price': 944.99, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-04-26', 'price': 944.99, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-04-27', 'price': 940.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-04-28', 'price': 940.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-04-29', 'price': 945.0, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-04-30', 'price': 919.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-05-01', 'price': 919.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-05-02', 'price': 919.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-05-03', 'price': 919.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-05-04', 'price': 919.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-05-05', 'price': 919.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-05-06', 'price': 919.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-05-07', 'price': 915.03, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-05-08', 'price': 915.03, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-05-09', 'price': 894.16, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-05-10', 'price': 894.16, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-05-11', 'price': 894.16, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-05-12', 'price': 915.03, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-05-13', 'price': 915.03, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-05-14', 'price': 915.03, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-05-15', 'price': 915.03, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-05-16', 'price': 915.03, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-05-17', 'price': 915.03, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-05-18', 'price': 915.03, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-05-19', 'price': 705.19, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-05-20', 'price': 705.19, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-05-21', 'price': 869.46, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-05-22', 'price': 979.99, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-05-23', 'price': 979.99, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-05-24', 'price': 845.59, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-05-25', 'price': 845.59, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-05-26', 'price': 845.59, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-05-27', 'price': 968.15, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-05-28', 'price': 968.15, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-05-29', 'price': 928.19, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-05-30', 'price': 928.19, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-05-31', 'price': 909.99, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-06-01', 'price': 928.19, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-06-02', 'price': 928.19, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-06-03', 'price': 928.19, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-06-04', 'price': 928.19, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-06-05', 'price': 925.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-06-06', 'price': 925.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-06-07', 'price': 925.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-06-08', 'price': 925.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-06-09', 'price': 925.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-06-10', 'price': 925.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-06-11', 'price': 925.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-06-12', 'price': 941.59, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-06-13', 'price': 969.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-06-14', 'price': 969.0, 'merchantId': 16623}, {'prodId': 13993126, 'date': '2026-06-15', 'price': 959.99, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-06-16', 'price': 959.99, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-06-17', 'price': 959.99, 'merchantId': 1582}, {'prodId': 13993126, 'date': '2026-06-18', 'price': 892.04, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-06-19', 'price': 898.69, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-06-20', 'price': 898.69, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-06-21', 'price': 928.19, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-06-22', 'price': 892.04, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-06-23', 'price': 892.04, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-06-24', 'price': 928.19, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-06-25', 'price': 928.19, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-06-26', 'price': 928.19, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-06-27', 'price': 928.19, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-06-28', 'price': 928.19, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-06-29', 'price': 928.19, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-06-30', 'price': 928.19, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-07-01', 'price': 928.19, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-07-02', 'price': 939.11, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-07-03', 'price': 939.11, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-07-04', 'price': 939.11, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-07-05', 'price': 939.11, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-07-06', 'price': 939.11, 'merchantId': 22905}, {'prodId': 13993126, 'date': '2026-07-07', 'price': 939.11, 'merchantId': 22905}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 12755141, 'date': '2025-07-07', 'price': 5699.0, 'merchantId': 5}, {'prodId': 12755141, 'date': '2025-07-08', 'price': 5799.0, 'merchantId': 5}, {'prodId': 12755141, 'date': '2025-07-09', 'price': 5699.0, 'merchantId': 22902}, {'prodId': 12755141, 'date': '2025-07-10', 'price': 5699.0, 'merchantId': 22902}, {'prodId': 12755141, 'date': '2025-07-11', 'price': 5699.0, 'merchantId': 22902}, {'prodId': 12755141, 'date': '2025-07-12', 'price': 5699.0, 'merchantId': 22902}, {'prodId': 12755141, 'date': '2025-07-13', 'price': 5699.0, 'merchantId': 22902}, {'prodId': 12755141, 'date': '2025-07-14', 'price': 5699.0, 'merchantId': 22902}, {'prodId': 12755141, 'date': '2025-07-15', 'price': 5698.99, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-07-16', 'price': 5698.99, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-07-17', 'price': 5699.0, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-07-18', 'price': 5798.99, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-07-19', 'price': 5799.01, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-07-20', 'price': 5799.01, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-07-21', 'price': 5799.01, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-07-22', 'price': 5799.01, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-07-23', 'price': 5799.0, 'merchantId': 5}, {'prodId': 12755141, 'date': '2025-07-24', 'price': 5799.01, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-07-25', 'price': 5799.01, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-07-26', 'price': 5799.0, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-07-27', 'price': 5799.0, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-07-28', 'price': 5799.0, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-07-29', 'price': 5799.0, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-07-30', 'price': 5116.43, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-07-31', 'price': 5799.0, 'merchantId': 5}, {'prodId': 12755141, 'date': '2025-08-01', 'price': 5799.01, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-08-02', 'price': 5116.43, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-08-03', 'price': 5799.0, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-08-04', 'price': 5699.0, 'merchantId': 16108}, {'prodId': 12755141, 'date': '2025-08-05', 'price': 5699.0, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-08-06', 'price': 5699.0, 'merchantId': 16108}, {'prodId': 12755141, 'date': '2025-08-07', 'price': 5699.0, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-08-08', 'price': 5698.99, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-08-09', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-08-10', 'price': 5698.93, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-08-11', 'price': 5698.92, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-08-12', 'price': 5698.92, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-08-13', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-08-14', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-08-15', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-08-16', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-08-17', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-08-18', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-08-19', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-08-20', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-08-21', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-08-22', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-08-23', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-08-24', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-08-25', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-08-26', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-08-27', 'price': 5349.0, 'merchantId': 5}, {'prodId': 12755141, 'date': '2025-08-28', 'price': 5249.0, 'merchantId': 5}, {'prodId': 12755141, 'date': '2025-08-29', 'price': 5249.0, 'merchantId': 5}, {'prodId': 12755141, 'date': '2025-08-30', 'price': 5399.1, 'merchantId': 16108}, {'prodId': 12755141, 'date': '2025-08-31', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-09-01', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-09-02', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-09-03', 'price': 5249.0, 'merchantId': 5}, {'prodId': 12755141, 'date': '2025-09-04', 'price': 5249.0, 'merchantId': 5}, {'prodId': 12755141, 'date': '2025-09-05', 'price': 5399.1, 'merchantId': 16108}, {'prodId': 12755141, 'date': '2025-09-06', 'price': 5249.0, 'merchantId': 5}, {'prodId': 12755141, 'date': '2025-09-07', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-09-08', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-09-09', 'price': 5399.1, 'merchantId': 16108}, {'prodId': 12755141, 'date': '2025-09-10', 'price': 5399.1, 'merchantId': 16108}, {'prodId': 12755141, 'date': '2025-09-11', 'price': 5399.1, 'merchantId': 16108}, {'prodId': 12755141, 'date': '2025-09-12', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-09-13', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-09-14', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-09-15', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-09-16', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-09-17', 'price': 5399.1, 'merchantId': 16108}, {'prodId': 12755141, 'date': '2025-09-18', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-09-19', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-09-20', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-09-21', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-09-22', 'price': 5399.14, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-09-23', 'price': 5399.14, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-09-24', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-09-25', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-09-26', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-09-27', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-09-28', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-09-29', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-09-30', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-10-01', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-10-02', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-10-03', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-10-04', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-10-05', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-10-06', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-10-07', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-10-08', 'price': 5698.93, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-10-09', 'price': 5599.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2025-10-10', 'price': 5399.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2025-10-11', 'price': 5399.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2025-10-12', 'price': 5399.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2025-10-13', 'price': 5399.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2025-10-14', 'price': 5299.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-10-15', 'price': 5299.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-10-16', 'price': 5299.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-10-17', 'price': 5299.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-10-18', 'price': 5299.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-10-19', 'price': 5112.94, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-10-20', 'price': 5112.94, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-10-21', 'price': 5112.94, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-10-22', 'price': 5112.94, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-10-23', 'price': 5112.94, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-10-24', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-10-25', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-10-26', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-10-27', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-10-28', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-10-29', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-10-30', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-10-31', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-11-01', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-11-02', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-11-03', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-11-04', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-11-05', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-11-06', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-11-07', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-11-08', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-11-09', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-11-10', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-11-11', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-11-12', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-11-13', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-11-14', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-11-15', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-11-16', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-11-17', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-11-18', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-11-19', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-11-20', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-11-21', 'price': 5297.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-11-22', 'price': 5390.06, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-11-23', 'price': 5390.06, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-11-24', 'price': 5297.0, 'merchantId': 21629}, {'prodId': 12755141, 'date': '2025-11-25', 'price': 5299.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-11-26', 'price': 5393.95, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-11-27', 'price': 4798.92, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-11-28', 'price': 5393.95, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2025-11-29', 'price': 4648.91, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-11-30', 'price': 5394.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2025-12-01', 'price': 5299.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2025-12-02', 'price': 5394.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2025-12-03', 'price': 5394.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2025-12-04', 'price': 5394.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2025-12-05', 'price': 5394.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2025-12-06', 'price': 5394.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2025-12-07', 'price': 5394.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2025-12-08', 'price': 5394.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2025-12-09', 'price': 5394.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2025-12-10', 'price': 5394.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2025-12-11', 'price': 5394.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2025-12-12', 'price': 5394.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2025-12-13', 'price': 5394.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2025-12-14', 'price': 5394.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2025-12-15', 'price': 5394.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2025-12-16', 'price': 5394.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2025-12-17', 'price': 5394.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2025-12-18', 'price': 5394.0, 'merchantId': 4}, {'prodId': 12755141, 'date': '2025-12-19', 'price': 5394.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2025-12-20', 'price': 5993.19, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-12-21', 'price': 5993.19, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-12-22', 'price': 5993.19, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-12-23', 'price': 5993.19, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-12-24', 'price': 6099.0, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-12-25', 'price': 6099.0, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-12-26', 'price': 6099.0, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-12-27', 'price': 5489.1, 'merchantId': 2}, {'prodId': 12755141, 'date': '2025-12-28', 'price': 6099.0, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-12-29', 'price': 5489.1, 'merchantId': 2}, {'prodId': 12755141, 'date': '2025-12-30', 'price': 6099.0, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2025-12-31', 'price': 5489.1, 'merchantId': 2}, {'prodId': 12755141, 'date': '2026-01-01', 'price': 6099.0, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-01-02', 'price': 6099.0, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-01-03', 'price': 5699.05, 'merchantId': 2584}, {'prodId': 12755141, 'date': '2026-01-04', 'price': 5699.05, 'merchantId': 2584}, {'prodId': 12755141, 'date': '2026-01-05', 'price': 5489.0, 'merchantId': 21}, {'prodId': 12755141, 'date': '2026-01-06', 'price': 5489.0, 'merchantId': 21}, {'prodId': 12755141, 'date': '2026-01-07', 'price': 5489.0, 'merchantId': 21}, {'prodId': 12755141, 'date': '2026-01-08', 'price': 5489.0, 'merchantId': 21}, {'prodId': 12755141, 'date': '2026-01-09', 'price': 5489.0, 'merchantId': 21}, {'prodId': 12755141, 'date': '2026-01-10', 'price': 5999.0, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-01-11', 'price': 5999.0, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-01-12', 'price': 5489.1, 'merchantId': 2}, {'prodId': 12755141, 'date': '2026-01-13', 'price': 5489.1, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-01-14', 'price': 5489.1, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-01-15', 'price': 5149.9, 'merchantId': 21}, {'prodId': 12755141, 'date': '2026-01-16', 'price': 5149.9, 'merchantId': 21}, {'prodId': 12755141, 'date': '2026-01-17', 'price': 5439.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2026-01-18', 'price': 5439.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2026-01-19', 'price': 5439.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2026-01-20', 'price': 5439.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2026-01-21', 'price': 5439.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2026-01-22', 'price': 5399.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-01-23', 'price': 5399.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-01-24', 'price': 5399.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-01-25', 'price': 5399.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-01-26', 'price': 5399.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-01-27', 'price': 5399.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-01-28', 'price': 5399.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-01-29', 'price': 5399.0, 'merchantId': 23326}, {'prodId': 12755141, 'date': '2026-01-30', 'price': 5414.0, 'merchantId': 245}, {'prodId': 12755141, 'date': '2026-01-31', 'price': 5414.0, 'merchantId': 245}, {'prodId': 12755141, 'date': '2026-02-01', 'price': 5414.0, 'merchantId': 245}, {'prodId': 12755141, 'date': '2026-02-02', 'price': 5414.0, 'merchantId': 245}, {'prodId': 12755141, 'date': '2026-02-03', 'price': 5414.0, 'merchantId': 245}, {'prodId': 12755141, 'date': '2026-02-04', 'price': 5398.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-02-05', 'price': 5398.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-02-06', 'price': 5398.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2026-02-07', 'price': 5398.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-02-08', 'price': 5414.0, 'merchantId': 245}, {'prodId': 12755141, 'date': '2026-02-09', 'price': 5414.0, 'merchantId': 245}, {'prodId': 12755141, 'date': '2026-02-10', 'price': 5398.0, 'merchantId': 4}, {'prodId': 12755141, 'date': '2026-02-11', 'price': 5398.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-02-12', 'price': 5398.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-02-13', 'price': 5398.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-02-14', 'price': 5398.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-02-15', 'price': 5398.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-02-16', 'price': 5398.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-02-17', 'price': 5398.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-02-18', 'price': 5397.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-02-19', 'price': 5339.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-02-20', 'price': 5337.9, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-02-21', 'price': 5337.9, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-02-22', 'price': 5337.9, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-02-23', 'price': 5337.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2026-02-24', 'price': 5337.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2026-02-25', 'price': 5336.9, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-02-26', 'price': 5336.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-02-27', 'price': 5308.9, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-02-28', 'price': 5308.9, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-03-01', 'price': 5308.9, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-03-02', 'price': 5308.9, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-03-03', 'price': 5308.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-03-04', 'price': 4999.0, 'merchantId': 16108}, {'prodId': 12755141, 'date': '2026-03-05', 'price': 4949.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-03-06', 'price': 4949.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2026-03-07', 'price': 4949.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-03-08', 'price': 4949.0, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-03-09', 'price': 4948.9, 'merchantId': 2}, {'prodId': 12755141, 'date': '2026-03-10', 'price': 4948.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2026-03-11', 'price': 4948.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2026-03-12', 'price': 4947.9, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-03-13', 'price': 4949.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-03-14', 'price': 4949.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-03-15', 'price': 4949.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-03-16', 'price': 4949.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-03-17', 'price': 4949.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-03-18', 'price': 4949.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-03-19', 'price': 4949.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-03-20', 'price': 4949.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-03-21', 'price': 4949.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-03-22', 'price': 4949.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-03-23', 'price': 4949.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-03-24', 'price': 4949.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-03-25', 'price': 4949.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-03-26', 'price': 4949.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-03-27', 'price': 4949.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-03-28', 'price': 4999.0, 'merchantId': 22902}, {'prodId': 12755141, 'date': '2026-03-29', 'price': 4949.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-03-30', 'price': 4949.0, 'merchantId': 21629}, {'prodId': 12755141, 'date': '2026-03-31', 'price': 4949.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-04-01', 'price': 4949.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-04-02', 'price': 4949.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-04-03', 'price': 5297.9, 'merchantId': 2}, {'prodId': 12755141, 'date': '2026-04-04', 'price': 5849.1, 'merchantId': 22902}, {'prodId': 12755141, 'date': '2026-04-05', 'price': 5297.9, 'merchantId': 4}, {'prodId': 12755141, 'date': '2026-04-06', 'price': 5297.9, 'merchantId': 2}, {'prodId': 12755141, 'date': '2026-04-07', 'price': 5297.9, 'merchantId': 4}, {'prodId': 12755141, 'date': '2026-04-08', 'price': 4423.18, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2026-04-09', 'price': 4949.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-04-10', 'price': 5297.9, 'merchantId': 2}, {'prodId': 12755141, 'date': '2026-04-11', 'price': 5776.67, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-04-12', 'price': 5700.0, 'merchantId': 20904}, {'prodId': 12755141, 'date': '2026-04-13', 'price': 5700.0, 'merchantId': 20904}, {'prodId': 12755141, 'date': '2026-04-14', 'price': 4949.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-04-15', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-04-16', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-04-17', 'price': 4949.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-04-18', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-04-19', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-04-20', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-04-21', 'price': 5205.19, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-04-22', 'price': 5297.0, 'merchantId': 2}, {'prodId': 12755141, 'date': '2026-04-23', 'price': 5297.9, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-04-24', 'price': 5297.9, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-04-25', 'price': 5775.0, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-04-26', 'price': 5775.0, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-04-27', 'price': 4949.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-04-28', 'price': 4949.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-04-29', 'price': 4949.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-04-30', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-05-01', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-05-02', 'price': 5199.3, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-05-03', 'price': 5199.3, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-05-04', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-05-05', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-05-06', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-05-07', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-05-08', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-05-09', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-05-10', 'price': 5199.3, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-05-11', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-05-12', 'price': 4949.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-05-13', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-05-14', 'price': 5297.0, 'merchantId': 245}, {'prodId': 12755141, 'date': '2026-05-15', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-05-16', 'price': 5297.0, 'merchantId': 245}, {'prodId': 12755141, 'date': '2026-05-17', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-05-18', 'price': 4949.0, 'merchantId': 21629}, {'prodId': 12755141, 'date': '2026-05-19', 'price': 4949.0, 'merchantId': 21627}, {'prodId': 12755141, 'date': '2026-05-20', 'price': 5179.19, 'merchantId': 23326}, {'prodId': 12755141, 'date': '2026-05-21', 'price': 5197.5, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2026-05-22', 'price': 5296.9, 'merchantId': 4}, {'prodId': 12755141, 'date': '2026-05-23', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-05-24', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-05-25', 'price': 5296.9, 'merchantId': 4}, {'prodId': 12755141, 'date': '2026-05-26', 'price': 5296.9, 'merchantId': 2}, {'prodId': 12755141, 'date': '2026-05-27', 'price': 5296.9, 'merchantId': 2}, {'prodId': 12755141, 'date': '2026-05-28', 'price': 5296.9, 'merchantId': 34}, {'prodId': 12755141, 'date': '2026-05-29', 'price': 5296.9, 'merchantId': 2}, {'prodId': 12755141, 'date': '2026-05-30', 'price': 5297.0, 'merchantId': 245}, {'prodId': 12755141, 'date': '2026-05-31', 'price': 5296.9, 'merchantId': 2}, {'prodId': 12755141, 'date': '2026-06-01', 'price': 5297.0, 'merchantId': 245}, {'prodId': 12755141, 'date': '2026-06-02', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-06-03', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-06-04', 'price': 5197.5, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2026-06-05', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-06-06', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-06-07', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-06-08', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-06-09', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-06-10', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-06-11', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-06-12', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-06-13', 'price': 5297.0, 'merchantId': 245}, {'prodId': 12755141, 'date': '2026-06-14', 'price': 5297.0, 'merchantId': 245}, {'prodId': 12755141, 'date': '2026-06-15', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-06-16', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-06-17', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-06-18', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-06-19', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-06-20', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-06-21', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-06-22', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-06-23', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-06-24', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-06-25', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-06-26', 'price': 5296.9, 'merchantId': 2}, {'prodId': 12755141, 'date': '2026-06-27', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-06-28', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-06-29', 'price': 5197.5, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-06-30', 'price': 5486.23, 'merchantId': 1582}, {'prodId': 12755141, 'date': '2026-07-01', 'price': 4859.1, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-07-02', 'price': 4859.1, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-07-03', 'price': 4859.1, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-07-04', 'price': 4769.1, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-07-05', 'price': 4769.1, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-07-06', 'price': 4769.1, 'merchantId': 9385}, {'prodId': 12755141, 'date': '2026-07-07', 'price': 5299.0, 'merchantId': 1582}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13994393, 'date': '2026-04-23', 'price': 2699.0, 'merchantId': 2}, {'prodId': 13994393, 'date': '2026-04-24', 'price': 2699.0, 'merchantId': 2}, {'prodId': 13994393, 'date': '2026-04-25', 'price': 2699.0, 'merchantId': 2}, {'prodId': 13994393, 'date': '2026-04-26', 'price': 2699.0, 'merchantId': 2}, {'prodId': 13994393, 'date': '2026-04-27', 'price': 2699.0, 'merchantId': 2}, {'prodId': 13994393, 'date': '2026-04-28', 'price': 2699.0, 'merchantId': 2}, {'prodId': 13994393, 'date': '2026-04-29', 'price': 2564.06, 'merchantId': 34}, {'prodId': 13994393, 'date': '2026-04-30', 'price': 2429.1, 'merchantId': 22905}, {'prodId': 13994393, 'date': '2026-05-01', 'price': 2429.1, 'merchantId': 22905}, {'prodId': 13994393, 'date': '2026-05-02', 'price': 2429.1, 'merchantId': 22905}, {'prodId': 13994393, 'date': '2026-05-03', 'price': 2429.1, 'merchantId': 22905}, {'prodId': 13994393, 'date': '2026-05-04', 'price': 2429.1, 'merchantId': 22905}, {'prodId': 13994393, 'date': '2026-05-05', 'price': 2429.1, 'merchantId': 22905}, {'prodId': 13994393, 'date': '2026-05-06', 'price': 2429.1, 'merchantId': 22905}, {'prodId': 13994393, 'date': '2026-05-07', 'price': 2375.12, 'merchantId': 22905}, {'prodId': 13994393, 'date': '2026-05-08', 'price': 2375.12, 'merchantId': 22905}, {'prodId': 13994393, 'date': '2026-05-09', 'price': 2375.12, 'merchantId': 22905}, {'prodId': 13994393, 'date': '2026-05-10', 'price': 2375.12, 'merchantId': 22905}, {'prodId': 13994393, 'date': '2026-05-11', 'price': 2375.12, 'merchantId': 22905}, {'prodId': 13994393, 'date': '2026-05-12', 'price': 2375.12, 'merchantId': 22905}, {'prodId': 13994393, 'date': '2026-05-13', 'price': 2375.12, 'merchantId': 22905}, {'prodId': 13994393, 'date': '2026-05-14', 'price': 2375.12, 'merchantId': 22905}, {'prodId': 13994393, 'date': '2026-05-15', 'price': 2375.12, 'merchantId': 22905}, {'prodId': 13994393, 'date': '2026-05-16', 'price': 2375.12, 'merchantId': 22905}, {'prodId': 13994393, 'date': '2026-05-17', 'price': 2375.12, 'merchantId': 22905}, {'prodId': 13994393, 'date': '2026-05-18', 'price': 2375.12, 'merchantId': 22905}, {'prodId': 13994393, 'date': '2026-05-19', 'price': 2375.12, 'merchantId': 22905}, {'prodId': 13994393, 'date': '2026-05-20', 'price': 2375.12, 'merchantId': 22905}, {'prodId': 13994393, 'date': '2026-05-21', 'price': 2373.89, 'merchantId': 4}, {'prodId': 13994393, 'date': '2026-05-22', 'price': 2136.49, 'merchantId': 4}, {'prodId': 13994393, 'date': '2026-05-23', 'price': 2136.49, 'merchantId': 4}, {'prodId': 13994393, 'date': '2026-05-24', 'price': 2136.49, 'merchantId': 4}, {'prodId': 13994393, 'date': '2026-05-25', 'price': 2136.49, 'merchantId': 4}, {'prodId': 13994393, 'date': '2026-05-26', 'price': 2136.49, 'merchantId': 2}, {'prodId': 13994393, 'date': '2026-05-27', 'price': 2136.0, 'merchantId': 2}, {'prodId': 13994393, 'date': '2026-05-28', 'price': 2136.0, 'merchantId': 2}, {'prodId': 13994393, 'date': '2026-05-29', 'price': 2136.0, 'merchantId': 22902}, {'prodId': 13994393, 'date': '2026-05-30', 'price': 2233.8, 'merchantId': 23326}, {'prodId': 13994393, 'date': '2026-05-31', 'price': 2233.8, 'merchantId': 23326}, {'prodId': 13994393, 'date': '2026-06-01', 'price': 2208.7, 'merchantId': 23326}, {'prodId': 13994393, 'date': '2026-06-02', 'price': 2201.46, 'merchantId': 23326}, {'prodId': 13994393, 'date': '2026-06-03', 'price': 2151.43, 'merchantId': 23326}, {'prodId': 13994393, 'date': '2026-06-04', 'price': 2196.82, 'merchantId': 23326}, {'prodId': 13994393, 'date': '2026-06-05', 'price': 2196.82, 'merchantId': 23326}, {'prodId': 13994393, 'date': '2026-06-06', 'price': 2187.26, 'merchantId': 23326}, {'prodId': 13994393, 'date': '2026-06-07', 'price': 2187.26, 'merchantId': 23326}, {'prodId': 13994393, 'date': '2026-06-08', 'price': 2187.26, 'merchantId': 23326}, {'prodId': 13994393, 'date': '2026-06-09', 'price': 2200.48, 'merchantId': 23326}, {'prodId': 13994393, 'date': '2026-06-10', 'price': 2200.48, 'merchantId': 23326}, {'prodId': 13994393, 'date': '2026-06-11', 'price': 2240.79, 'merchantId': 23326}, {'prodId': 13994393, 'date': '2026-06-12', 'price': 2240.59, 'merchantId': 23326}, {'prodId': 13994393, 'date': '2026-06-13', 'price': 2240.59, 'merchantId': 23326}, {'prodId': 13994393, 'date': '2026-06-14', 'price': 2240.59, 'merchantId': 23326}, {'prodId': 13994393, 'date': '2026-06-15', 'price': 2240.59, 'merchantId': 23326}, {'prodId': 13994393, 'date': '2026-06-16', 'price': 2247.52, 'merchantId': 20583}, {'prodId': 13994393, 'date': '2026-06-17', 'price': 2247.52, 'merchantId': 20583}, {'prodId': 13994393, 'date': '2026-06-18', 'price': 2247.52, 'merchantId': 20583}, {'prodId': 13994393, 'date': '2026-06-19', 'price': 2247.52, 'merchantId': 20583}, {'prodId': 13994393, 'date': '2026-06-20', 'price': 2247.32, 'merchantId': 23326}, {'prodId': 13994393, 'date': '2026-06-21', 'price': 2247.52, 'merchantId': 22905}, {'prodId': 13994393, 'date': '2026-06-22', 'price': 2247.52, 'merchantId': 22905}, {'prodId': 13994393, 'date': '2026-06-23', 'price': 2200.48, 'merchantId': 23326}, {'prodId': 13994393, 'date': '2026-06-24', 'price': 2240.0, 'merchantId': 23326}, {'prodId': 13994393, 'date': '2026-06-25', 'price': 2239.9, 'merchantId': 23326}, {'prodId': 13994393, 'date': '2026-06-26', 'price': 2190.13, 'merchantId': 23326}, {'prodId': 13994393, 'date': '2026-06-27', 'price': 2239.0, 'merchantId': 23326}, {'prodId': 13994393, 'date': '2026-06-28', 'price': 2239.0, 'merchantId': 2}, {'prodId': 13994393, 'date': '2026-06-29', 'price': 2239.0, 'merchantId': 2}, {'prodId': 13994393, 'date': '2026-06-30', 'price': 2189.25, 'merchantId': 23326}, {'prodId': 13994393, 'date': '2026-07-01', 'price': 2096.0, 'merchantId': 2}, {'prodId': 13994393, 'date': '2026-07-02', 'price': 2022.99, 'merchantId': 2}, {'prodId': 13994393, 'date': '2026-07-03', 'price': 2022.9, 'merchantId': 2}, {'prodId': 13994393, 'date': '2026-07-04', 'price': 2022.9, 'merchantId': 2}, {'prodId': 13994393, 'date': '2026-07-05', 'price': 2022.9, 'merchantId': 2}, {'prodId': 13994393, 'date': '2026-07-06', 'price': 2022.79, 'merchantId': 2}, {'prodId': 13994393, 'date': '2026-07-07', 'price': 2022.79, 'merchantId': 2}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13992942, 'date': '2025-09-16', 'price': 10349.1, 'merchantId': 22902}, {'prodId': 13992942, 'date': '2025-09-17', 'price': 10349.1, 'merchantId': 22902}, {'prodId': 13992942, 'date': '2025-09-18', 'price': 10349.1, 'merchantId': 22902}, {'prodId': 13992942, 'date': '2025-09-19', 'price': 10349.1, 'merchantId': 22902}, {'prodId': 13992942, 'date': '2025-09-20', 'price': 10349.1, 'merchantId': 22902}, {'prodId': 13992942, 'date': '2025-09-21', 'price': 10349.1, 'merchantId': 22902}, {'prodId': 13992942, 'date': '2025-09-22', 'price': 10349.1, 'merchantId': 22902}, {'prodId': 13992942, 'date': '2025-09-23', 'price': 10348.99, 'merchantId': 9385}, {'prodId': 13992942, 'date': '2025-09-24', 'price': 10348.99, 'merchantId': 9385}, {'prodId': 13992942, 'date': '2025-09-25', 'price': 10348.99, 'merchantId': 9385}, {'prodId': 13992942, 'date': '2025-09-26', 'price': 10348.99, 'merchantId': 9385}, {'prodId': 13992942, 'date': '2025-09-27', 'price': 10348.99, 'merchantId': 9385}, {'prodId': 13992942, 'date': '2025-09-28', 'price': 10348.99, 'merchantId': 9385}, {'prodId': 13992942, 'date': '2025-09-29', 'price': 10349.0, 'merchantId': 9385}, {'prodId': 13992942, 'date': '2025-09-30', 'price': 10349.0, 'merchantId': 9385}, {'prodId': 13992942, 'date': '2025-10-01', 'price': 10349.0, 'merchantId': 9385}, {'prodId': 13992942, 'date': '2025-10-02', 'price': 10119.12, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-10-03', 'price': 10119.12, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-10-04', 'price': 10119.12, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-10-05', 'price': 10119.12, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-10-06', 'price': 10119.12, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-10-07', 'price': 10119.12, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-10-08', 'price': 10119.12, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-10-09', 'price': 10119.12, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-10-10', 'price': 10119.12, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-10-11', 'price': 10119.12, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-10-12', 'price': 10348.99, 'merchantId': 9385}, {'prodId': 13992942, 'date': '2025-10-13', 'price': 10348.99, 'merchantId': 9385}, {'prodId': 13992942, 'date': '2025-10-14', 'price': 10348.99, 'merchantId': 9385}, {'prodId': 13992942, 'date': '2025-10-15', 'price': 10348.99, 'merchantId': 9385}, {'prodId': 13992942, 'date': '2025-10-16', 'price': 10348.99, 'merchantId': 9385}, {'prodId': 13992942, 'date': '2025-10-17', 'price': 10348.99, 'merchantId': 9385}, {'prodId': 13992942, 'date': '2025-10-18', 'price': 10119.12, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-10-19', 'price': 10119.12, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-10-20', 'price': 10119.12, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-10-21', 'price': 10349.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2025-10-22', 'price': 10349.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2025-10-23', 'price': 10119.12, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-10-24', 'price': 10349.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2025-10-25', 'price': 9774.15, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-10-26', 'price': 9774.15, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-10-27', 'price': 10348.99, 'merchantId': 9385}, {'prodId': 13992942, 'date': '2025-10-28', 'price': 10348.99, 'merchantId': 9385}, {'prodId': 13992942, 'date': '2025-10-29', 'price': 10348.99, 'merchantId': 9385}, {'prodId': 13992942, 'date': '2025-10-30', 'price': 9774.15, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-10-31', 'price': 9774.15, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-11-01', 'price': 9774.15, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-11-02', 'price': 9774.15, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-11-03', 'price': 9774.15, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-11-04', 'price': 9774.15, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-11-05', 'price': 6799.0, 'merchantId': 20612}, {'prodId': 13992942, 'date': '2025-11-06', 'price': 9699.0, 'merchantId': 20612}, {'prodId': 13992942, 'date': '2025-11-07', 'price': 9699.0, 'merchantId': 20612}, {'prodId': 13992942, 'date': '2025-11-08', 'price': 9699.0, 'merchantId': 20612}, {'prodId': 13992942, 'date': '2025-11-09', 'price': 9699.0, 'merchantId': 20612}, {'prodId': 13992942, 'date': '2025-11-10', 'price': 9699.0, 'merchantId': 20612}, {'prodId': 13992942, 'date': '2025-11-11', 'price': 9699.0, 'merchantId': 20612}, {'prodId': 13992942, 'date': '2025-11-12', 'price': 9699.0, 'merchantId': 20612}, {'prodId': 13992942, 'date': '2025-11-13', 'price': 9699.0, 'merchantId': 20612}, {'prodId': 13992942, 'date': '2025-11-14', 'price': 9699.0, 'merchantId': 20612}, {'prodId': 13992942, 'date': '2025-11-15', 'price': 9699.0, 'merchantId': 20612}, {'prodId': 13992942, 'date': '2025-11-16', 'price': 9699.0, 'merchantId': 20612}, {'prodId': 13992942, 'date': '2025-11-17', 'price': 9699.0, 'merchantId': 20612}, {'prodId': 13992942, 'date': '2025-11-18', 'price': 9349.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2025-11-19', 'price': 9349.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2025-11-20', 'price': 9349.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2025-11-21', 'price': 9349.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2025-11-22', 'price': 9349.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2025-11-23', 'price': 10348.0, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-11-24', 'price': 9349.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2025-11-25', 'price': 9899.1, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-11-26', 'price': 8610.9, 'merchantId': 21627}, {'prodId': 13992942, 'date': '2025-11-27', 'price': 9719.1, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-11-28', 'price': 10348.0, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-11-29', 'price': 9373.14, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-11-30', 'price': 9591.12, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-12-01', 'price': 9591.12, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-12-02', 'price': 10119.12, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-12-03', 'price': 10119.12, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-12-04', 'price': 10119.12, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-12-05', 'price': 10348.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2025-12-06', 'price': 10021.5, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-12-07', 'price': 10021.5, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-12-08', 'price': 10021.5, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-12-09', 'price': 10348.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2025-12-10', 'price': 10348.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2025-12-11', 'price': 10348.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2025-12-12', 'price': 10348.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2025-12-13', 'price': 10021.5, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-12-14', 'price': 10021.5, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-12-15', 'price': 10021.5, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-12-16', 'price': 10021.5, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-12-17', 'price': 10021.5, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-12-18', 'price': 10259.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2025-12-19', 'price': 10259.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2025-12-20', 'price': 9714.32, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-12-21', 'price': 9714.32, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-12-22', 'price': 9935.1, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-12-23', 'price': 9935.1, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-12-24', 'price': 9935.1, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-12-25', 'price': 9935.1, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-12-26', 'price': 9935.1, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2025-12-27', 'price': 10259.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2025-12-28', 'price': 10349.1, 'merchantId': 20583}, {'prodId': 13992942, 'date': '2025-12-29', 'price': 10259.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2025-12-30', 'price': 10259.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2025-12-31', 'price': 10259.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-01-01', 'price': 10259.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-01-02', 'price': 10259.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-01-03', 'price': 10259.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-01-04', 'price': 10259.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-01-05', 'price': 9259.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-01-06', 'price': 9259.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-01-07', 'price': 9259.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-01-08', 'price': 10259.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-01-09', 'price': 10348.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2026-01-10', 'price': 10348.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2026-01-11', 'price': 10348.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2026-01-12', 'price': 9259.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-01-13', 'price': 9259.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-01-14', 'price': 9259.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-01-15', 'price': 9259.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-01-16', 'price': 9259.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-01-17', 'price': 9259.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-01-18', 'price': 9259.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-01-19', 'price': 9259.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-01-20', 'price': 9259.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-01-21', 'price': 9359.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-01-22', 'price': 9359.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-01-23', 'price': 9359.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-01-24', 'price': 9359.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-01-25', 'price': 10259.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-01-26', 'price': 9314.1, 'merchantId': 22902}, {'prodId': 13992942, 'date': '2026-01-27', 'price': 9259.1, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-01-28', 'price': 9309.9, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-01-29', 'price': 9199.9, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-01-30', 'price': 9199.9, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-01-31', 'price': 9309.9, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-02-01', 'price': 9309.9, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-02-02', 'price': 9236.109999999999, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-02-03', 'price': 9236.109999999999, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-02-04', 'price': 9236.109999999999, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-02-05', 'price': 9236.109999999999, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-02-06', 'price': 9236.109999999999, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-02-07', 'price': 9236.109999999999, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-02-08', 'price': 9236.109999999999, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-02-09', 'price': 9236.109999999999, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-02-10', 'price': 9236.109999999999, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-02-11', 'price': 9314.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2026-02-12', 'price': 9314.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2026-02-13', 'price': 9314.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2026-02-14', 'price': 9314.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2026-02-15', 'price': 9314.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2026-02-16', 'price': 9314.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2026-02-17', 'price': 9314.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2026-02-18', 'price': 9314.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2026-02-19', 'price': 9314.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2026-02-20', 'price': 9314.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2026-02-21', 'price': 9314.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2026-02-22', 'price': 9314.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2026-02-23', 'price': 9314.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2026-02-24', 'price': 9314.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2026-02-25', 'price': 9314.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2026-02-26', 'price': 8500.0, 'merchantId': 9385}, {'prodId': 13992942, 'date': '2026-02-27', 'price': 8967.01, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2026-02-28', 'price': 8967.01, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2026-03-01', 'price': 8967.01, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2026-03-02', 'price': 8967.01, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2026-03-03', 'price': 8967.01, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2026-03-04', 'price': 8967.01, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2026-03-05', 'price': 8967.01, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2026-03-06', 'price': 8967.01, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2026-03-07', 'price': 8967.01, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2026-03-08', 'price': 8967.01, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2026-03-09', 'price': 8967.01, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2026-03-10', 'price': 8967.01, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2026-03-11', 'price': 8967.01, 'merchantId': 23326}, {'prodId': 13992942, 'date': '2026-03-12', 'price': 8999.1, 'merchantId': 22902}, {'prodId': 13992942, 'date': '2026-03-13', 'price': 8999.1, 'merchantId': 22902}, {'prodId': 13992942, 'date': '2026-03-14', 'price': 8972.220000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-03-15', 'price': 8972.220000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-03-16', 'price': 8972.220000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-03-17', 'price': 8972.220000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-03-18', 'price': 8972.220000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-03-19', 'price': 8972.220000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-03-20', 'price': 8972.220000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-03-21', 'price': 8972.220000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-03-22', 'price': 8972.220000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-03-23', 'price': 9314.0, 'merchantId': 2}, {'prodId': 13992942, 'date': '2026-03-24', 'price': 9314.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2026-03-25', 'price': 9314.0, 'merchantId': 2}, {'prodId': 13992942, 'date': '2026-03-26', 'price': 9314.0, 'merchantId': 2}, {'prodId': 13992942, 'date': '2026-03-27', 'price': 8999.1, 'merchantId': 22902}, {'prodId': 13992942, 'date': '2026-03-28', 'price': 9314.0, 'merchantId': 2}, {'prodId': 13992942, 'date': '2026-03-29', 'price': 8999.1, 'merchantId': 22902}, {'prodId': 13992942, 'date': '2026-03-30', 'price': 9314.0, 'merchantId': 2}, {'prodId': 13992942, 'date': '2026-03-31', 'price': 9314.0, 'merchantId': 2}, {'prodId': 13992942, 'date': '2026-04-01', 'price': 9314.0, 'merchantId': 2}, {'prodId': 13992942, 'date': '2026-04-02', 'price': 9314.0, 'merchantId': 2}, {'prodId': 13992942, 'date': '2026-04-03', 'price': 9314.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2026-04-04', 'price': 9314.0, 'merchantId': 2}, {'prodId': 13992942, 'date': '2026-04-05', 'price': 9314.0, 'merchantId': 2}, {'prodId': 13992942, 'date': '2026-04-06', 'price': 9314.0, 'merchantId': 2}, {'prodId': 13992942, 'date': '2026-04-07', 'price': 10169.1, 'merchantId': 22902}, {'prodId': 13992942, 'date': '2026-04-08', 'price': 9314.0, 'merchantId': 2}, {'prodId': 13992942, 'date': '2026-04-09', 'price': 9314.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2026-04-10', 'price': 10349.1, 'merchantId': 22902}, {'prodId': 13992942, 'date': '2026-04-11', 'price': 9314.0, 'merchantId': 4}, {'prodId': 13992942, 'date': '2026-04-12', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-04-13', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-04-14', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-04-15', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-04-16', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-04-17', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-04-18', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-04-19', 'price': 9499.9, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-04-20', 'price': 9314.0, 'merchantId': 2}, {'prodId': 13992942, 'date': '2026-04-21', 'price': 9499.9, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-04-22', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-04-23', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-04-24', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-04-25', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-04-26', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-04-27', 'price': 10235.369999999999, 'merchantId': 9385}, {'prodId': 13992942, 'date': '2026-04-28', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-04-29', 'price': 7885.19, 'merchantId': 9385}, {'prodId': 13992942, 'date': '2026-04-30', 'price': 9314.0, 'merchantId': 2}, {'prodId': 13992942, 'date': '2026-05-01', 'price': 9107.02, 'merchantId': 245}, {'prodId': 13992942, 'date': '2026-05-02', 'price': 9107.02, 'merchantId': 245}, {'prodId': 13992942, 'date': '2026-05-03', 'price': 9107.02, 'merchantId': 245}, {'prodId': 13992942, 'date': '2026-05-04', 'price': 9107.02, 'merchantId': 245}, {'prodId': 13992942, 'date': '2026-05-05', 'price': 9107.02, 'merchantId': 245}, {'prodId': 13992942, 'date': '2026-05-06', 'price': 8639.1, 'merchantId': 20583}, {'prodId': 13992942, 'date': '2026-05-07', 'price': 8639.1, 'merchantId': 20583}, {'prodId': 13992942, 'date': '2026-05-08', 'price': 9107.02, 'merchantId': 245}, {'prodId': 13992942, 'date': '2026-05-09', 'price': 9107.02, 'merchantId': 245}, {'prodId': 13992942, 'date': '2026-05-10', 'price': 9107.02, 'merchantId': 245}, {'prodId': 13992942, 'date': '2026-05-11', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-05-12', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-05-13', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-05-14', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-05-15', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-05-16', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-05-17', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-05-18', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-05-19', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-05-20', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-05-21', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-05-22', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-05-23', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-05-24', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-05-25', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-05-26', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-05-27', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-05-28', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-05-29', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-05-30', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-05-31', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-06-01', 'price': 8655.550000000001, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-06-02', 'price': 8798.99, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-06-03', 'price': 8798.99, 'merchantId': 21}, {'prodId': 13992942, 'date': '2026-06-04', 'price': 9099.99, 'merchantId': 22905}, {'prodId': 13992942, 'date': '2026-06-05', 'price': 8823.89, 'merchantId': 22902}, {'prodId': 13992942, 'date': '2026-06-06', 'price': 9034.0, 'merchantId': 5}, {'prodId': 13992942, 'date': '2026-06-07', 'price': 9034.0, 'merchantId': 5}, {'prodId': 13992942, 'date': '2026-06-08', 'price': 9034.0, 'merchantId': 5}, {'prodId': 13992942, 'date': '2026-06-09', 'price': 9107.02, 'merchantId': 245}, {'prodId': 13992942, 'date': '2026-06-10', 'price': 9107.02, 'merchantId': 245}, {'prodId': 13992942, 'date': '2026-06-11', 'price': 9107.02, 'merchantId': 245}, {'prodId': 13992942, 'date': '2026-06-12', 'price': 8823.89, 'merchantId': 22902}, {'prodId': 13992942, 'date': '2026-06-13', 'price': 8823.89, 'merchantId': 22902}, {'prodId': 13992942, 'date': '2026-06-14', 'price': 9107.02, 'merchantId': 245}, {'prodId': 13992942, 'date': '2026-06-15', 'price': 8823.89, 'merchantId': 22902}, {'prodId': 13992942, 'date': '2026-06-16', 'price': 8823.88, 'merchantId': 9385}, {'prodId': 13992942, 'date': '2026-06-17', 'price': 8823.88, 'merchantId': 9385}, {'prodId': 13992942, 'date': '2026-06-18', 'price': 8337.84, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-06-19', 'price': 8337.84, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-06-20', 'price': 8337.84, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-06-21', 'price': 8220.69, 'merchantId': 5}, {'prodId': 13992942, 'date': '2026-06-22', 'price': 8220.69, 'merchantId': 5}, {'prodId': 13992942, 'date': '2026-06-23', 'price': 8337.84, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-06-24', 'price': 8337.84, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-06-25', 'price': 8337.84, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-06-26', 'price': 8337.84, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-06-27', 'price': 8337.84, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-06-28', 'price': 8337.84, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-06-29', 'price': 8337.84, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-06-30', 'price': 8337.84, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-07-01', 'price': 8337.84, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-07-02', 'price': 8776.67, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-07-03', 'price': 8776.67, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-07-04', 'price': 8776.67, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-07-05', 'price': 8776.67, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-07-06', 'price': 8776.67, 'merchantId': 20904}, {'prodId': 13992942, 'date': '2026-07-07', 'price': 8776.67, 'merchantId': 20904}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13994236, 'date': '2026-02-27', 'price': 1158.9, 'merchantId': 21628}, {'prodId': 13994236, 'date': '2026-02-28', 'price': 1034.1, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-03-01', 'price': 1034.1, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-03-02', 'price': 1034.1, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-03-03', 'price': 1034.1, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-03-04', 'price': 1034.1, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-03-05', 'price': 1034.1, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-03-06', 'price': 1034.1, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-03-07', 'price': 1234.05, 'merchantId': 2584}, {'prodId': 13994236, 'date': '2026-03-08', 'price': 1234.05, 'merchantId': 2584}, {'prodId': 13994236, 'date': '2026-03-09', 'price': 1169.0, 'merchantId': 23326}, {'prodId': 13994236, 'date': '2026-03-10', 'price': 1168.9, 'merchantId': 23326}, {'prodId': 13994236, 'date': '2026-03-11', 'price': 1168.9, 'merchantId': 21628}, {'prodId': 13994236, 'date': '2026-03-12', 'price': 1168.9, 'merchantId': 21628}, {'prodId': 13994236, 'date': '2026-03-13', 'price': 1229.0, 'merchantId': 21628}, {'prodId': 13994236, 'date': '2026-03-14', 'price': 1168.9, 'merchantId': 21628}, {'prodId': 13994236, 'date': '2026-03-15', 'price': 1229.0, 'merchantId': 21628}, {'prodId': 13994236, 'date': '2026-03-16', 'price': 1168.9, 'merchantId': 21628}, {'prodId': 13994236, 'date': '2026-03-17', 'price': 1229.0, 'merchantId': 21628}, {'prodId': 13994236, 'date': '2026-03-18', 'price': 1168.9, 'merchantId': 21629}, {'prodId': 13994236, 'date': '2026-03-19', 'price': 1229.0, 'merchantId': 21628}, {'prodId': 13994236, 'date': '2026-03-20', 'price': 1168.9, 'merchantId': 21628}, {'prodId': 13994236, 'date': '2026-03-21', 'price': 1168.9, 'merchantId': 21628}, {'prodId': 13994236, 'date': '2026-03-22', 'price': 1229.0, 'merchantId': 21628}, {'prodId': 13994236, 'date': '2026-03-23', 'price': 1168.9, 'merchantId': 21628}, {'prodId': 13994236, 'date': '2026-03-24', 'price': 1229.0, 'merchantId': 21628}, {'prodId': 13994236, 'date': '2026-03-25', 'price': 1229.0, 'merchantId': 21628}, {'prodId': 13994236, 'date': '2026-03-26', 'price': 1229.0, 'merchantId': 21628}, {'prodId': 13994236, 'date': '2026-03-27', 'price': 1168.9, 'merchantId': 21628}, {'prodId': 13994236, 'date': '2026-03-28', 'price': 1219.0, 'merchantId': 21628}, {'prodId': 13994236, 'date': '2026-03-29', 'price': 1219.0, 'merchantId': 21628}, {'prodId': 13994236, 'date': '2026-03-30', 'price': 1079.0, 'merchantId': 34}, {'prodId': 13994236, 'date': '2026-03-31', 'price': 1079.0, 'merchantId': 34}, {'prodId': 13994236, 'date': '2026-04-01', 'price': 1078.9, 'merchantId': 4}, {'prodId': 13994236, 'date': '2026-04-02', 'price': 1078.9, 'merchantId': 4}, {'prodId': 13994236, 'date': '2026-04-03', 'price': 1078.9, 'merchantId': 4}, {'prodId': 13994236, 'date': '2026-04-04', 'price': 1078.9, 'merchantId': 4}, {'prodId': 13994236, 'date': '2026-04-05', 'price': 1078.9, 'merchantId': 4}, {'prodId': 13994236, 'date': '2026-04-06', 'price': 1078.0, 'merchantId': 4}, {'prodId': 13994236, 'date': '2026-04-07', 'price': 1077.9, 'merchantId': 4}, {'prodId': 13994236, 'date': '2026-04-08', 'price': 1077.9, 'merchantId': 4}, {'prodId': 13994236, 'date': '2026-04-09', 'price': 938.57, 'merchantId': 20609}, {'prodId': 13994236, 'date': '2026-04-10', 'price': 938.57, 'merchantId': 20609}, {'prodId': 13994236, 'date': '2026-04-11', 'price': 938.57, 'merchantId': 20609}, {'prodId': 13994236, 'date': '2026-04-12', 'price': 959.0, 'merchantId': 20609}, {'prodId': 13994236, 'date': '2026-04-13', 'price': 959.0, 'merchantId': 20609}, {'prodId': 13994236, 'date': '2026-04-14', 'price': 959.0, 'merchantId': 20609}, {'prodId': 13994236, 'date': '2026-04-15', 'price': 984.72, 'merchantId': 22905}, {'prodId': 13994236, 'date': '2026-04-16', 'price': 1119.0, 'merchantId': 20583}, {'prodId': 13994236, 'date': '2026-04-17', 'price': 1176.9, 'merchantId': 4}, {'prodId': 13994236, 'date': '2026-04-18', 'price': 1231.88, 'merchantId': 20583}, {'prodId': 13994236, 'date': '2026-04-19', 'price': 1231.88, 'merchantId': 20583}, {'prodId': 13994236, 'date': '2026-04-20', 'price': 1231.88, 'merchantId': 20583}, {'prodId': 13994236, 'date': '2026-04-21', 'price': 1231.88, 'merchantId': 20583}, {'prodId': 13994236, 'date': '2026-04-22', 'price': 1169.0, 'merchantId': 22905}, {'prodId': 13994236, 'date': '2026-04-23', 'price': 1169.0, 'merchantId': 22905}, {'prodId': 13994236, 'date': '2026-04-24', 'price': 1169.0, 'merchantId': 22905}, {'prodId': 13994236, 'date': '2026-04-25', 'price': 1169.0, 'merchantId': 22905}, {'prodId': 13994236, 'date': '2026-04-26', 'price': 1169.0, 'merchantId': 22905}, {'prodId': 13994236, 'date': '2026-04-27', 'price': 1169.0, 'merchantId': 4}, {'prodId': 13994236, 'date': '2026-04-28', 'price': 1169.0, 'merchantId': 245}, {'prodId': 13994236, 'date': '2026-04-29', 'price': 1110.56, 'merchantId': 34}, {'prodId': 13994236, 'date': '2026-04-30', 'price': 1110.56, 'merchantId': 34}, {'prodId': 13994236, 'date': '2026-05-01', 'price': 1110.56, 'merchantId': 34}, {'prodId': 13994236, 'date': '2026-05-02', 'price': 1110.56, 'merchantId': 34}, {'prodId': 13994236, 'date': '2026-05-03', 'price': 1110.56, 'merchantId': 34}, {'prodId': 13994236, 'date': '2026-05-04', 'price': 1110.0, 'merchantId': 4}, {'prodId': 13994236, 'date': '2026-05-05', 'price': 1110.0, 'merchantId': 4}, {'prodId': 13994236, 'date': '2026-05-06', 'price': 1095.0, 'merchantId': 4}, {'prodId': 13994236, 'date': '2026-05-07', 'price': 1099.0, 'merchantId': 22905}, {'prodId': 13994236, 'date': '2026-05-08', 'price': 1059.99, 'merchantId': 22905}, {'prodId': 13994236, 'date': '2026-05-09', 'price': 1059.99, 'merchantId': 22905}, {'prodId': 13994236, 'date': '2026-05-10', 'price': 1059.99, 'merchantId': 22905}, {'prodId': 13994236, 'date': '2026-05-11', 'price': 1059.99, 'merchantId': 22905}, {'prodId': 13994236, 'date': '2026-05-12', 'price': 1059.99, 'merchantId': 22905}, {'prodId': 13994236, 'date': '2026-05-13', 'price': 1059.99, 'merchantId': 22905}, {'prodId': 13994236, 'date': '2026-05-14', 'price': 1059.99, 'merchantId': 22905}, {'prodId': 13994236, 'date': '2026-05-15', 'price': 1055.02, 'merchantId': 23326}, {'prodId': 13994236, 'date': '2026-05-16', 'price': 1055.02, 'merchantId': 23326}, {'prodId': 13994236, 'date': '2026-05-17', 'price': 1055.02, 'merchantId': 23326}, {'prodId': 13994236, 'date': '2026-05-18', 'price': 1055.02, 'merchantId': 23326}, {'prodId': 13994236, 'date': '2026-05-19', 'price': 1055.02, 'merchantId': 23326}, {'prodId': 13994236, 'date': '2026-05-20', 'price': 1011.49, 'merchantId': 4}, {'prodId': 13994236, 'date': '2026-05-21', 'price': 1011.49, 'merchantId': 4}, {'prodId': 13994236, 'date': '2026-05-22', 'price': 989.01, 'merchantId': 23326}, {'prodId': 13994236, 'date': '2026-05-23', 'price': 989.01, 'merchantId': 23326}, {'prodId': 13994236, 'date': '2026-05-24', 'price': 989.01, 'merchantId': 23326}, {'prodId': 13994236, 'date': '2026-05-25', 'price': 960.0, 'merchantId': 4}, {'prodId': 13994236, 'date': '2026-05-26', 'price': 949.34, 'merchantId': 245}, {'prodId': 13994236, 'date': '2026-05-27', 'price': 949.34, 'merchantId': 245}, {'prodId': 13994236, 'date': '2026-05-28', 'price': 949.24, 'merchantId': 245}, {'prodId': 13994236, 'date': '2026-05-29', 'price': 967.12, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-05-30', 'price': 967.12, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-05-31', 'price': 967.12, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-06-01', 'price': 967.12, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-06-02', 'price': 1055.01, 'merchantId': 23326}, {'prodId': 13994236, 'date': '2026-06-03', 'price': 1031.04, 'merchantId': 23326}, {'prodId': 13994236, 'date': '2026-06-04', 'price': 1030.0, 'merchantId': 23326}, {'prodId': 13994236, 'date': '2026-06-05', 'price': 1030.0, 'merchantId': 23326}, {'prodId': 13994236, 'date': '2026-06-06', 'price': 1067.01, 'merchantId': 245}, {'prodId': 13994236, 'date': '2026-06-07', 'price': 1067.01, 'merchantId': 245}, {'prodId': 13994236, 'date': '2026-06-08', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-06-09', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-06-10', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-06-11', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-06-12', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-06-13', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-06-14', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-06-15', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-06-16', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-06-17', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-06-18', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-06-19', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-06-20', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-06-21', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-06-22', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-06-23', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-06-24', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-06-25', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-06-26', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-06-27', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-06-28', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-06-29', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-06-30', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-07-01', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-07-02', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-07-03', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-07-04', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-07-05', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-07-06', 'price': 934.15, 'merchantId': 23276}, {'prodId': 13994236, 'date': '2026-07-07', 'price': 1164.6, 'merchantId': 22905}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13382394, 'date': '2025-07-07', 'price': 1629.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-07-08', 'price': 1574.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-07-09', 'price': 1559.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-07-10', 'price': 1559.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-07-11', 'price': 1578.9, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-07-12', 'price': 1551.1, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-07-13', 'price': 1551.1, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-07-14', 'price': 1559.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-07-15', 'price': 1551.1, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-07-16', 'price': 1559.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-07-17', 'price': 1559.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-07-18', 'price': 1581.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-07-19', 'price': 1589.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-07-20', 'price': 1589.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-07-21', 'price': 1589.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-07-22', 'price': 1580.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-07-23', 'price': 1580.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-07-24', 'price': 1579.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-07-25', 'price': 1579.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-07-26', 'price': 1571.5, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-07-27', 'price': 1565.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-07-28', 'price': 1551.1, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-07-29', 'price': 1565.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-07-30', 'price': 1567.5, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-07-31', 'price': 1567.5, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-08-01', 'price': 1567.5, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-08-02', 'price': 1550.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-08-03', 'price': 1554.5, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-08-04', 'price': 1567.5, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-08-05', 'price': 1567.5, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-08-06', 'price': 1567.5, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-08-07', 'price': 1560.1, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-08-08', 'price': 1560.1, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-08-09', 'price': 1558.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-08-10', 'price': 1550.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-08-11', 'price': 1550.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-08-12', 'price': 1567.5, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-08-13', 'price': 1560.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-08-14', 'price': 1564.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-08-15', 'price': 1564.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-08-16', 'price': 1564.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-08-17', 'price': 1564.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-08-18', 'price': 1540.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-08-19', 'price': 1524.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-08-20', 'price': 1508.03, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-08-21', 'price': 1508.03, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-08-22', 'price': 1508.03, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-08-23', 'price': 1505.04, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-08-24', 'price': 1505.04, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-08-25', 'price': 1508.03, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-08-26', 'price': 1505.04, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-08-27', 'price': 1505.04, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-08-28', 'price': 1505.04, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-08-29', 'price': 1539.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-08-30', 'price': 1539.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-08-31', 'price': 1532.09, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-09-01', 'price': 1505.04, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-09-02', 'price': 1539.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-09-03', 'price': 1539.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-09-04', 'price': 1539.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-09-05', 'price': 1555.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-09-06', 'price': 1554.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-09-07', 'price': 1517.04, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-09-08', 'price': 1517.04, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-09-09', 'price': 1554.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-09-10', 'price': 1517.04, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-09-11', 'price': 1520.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-09-12', 'price': 1520.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-09-13', 'price': 1470.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-09-14', 'price': 1510.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-09-15', 'price': 1470.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-09-16', 'price': 1510.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-09-17', 'price': 1452.74, 'merchantId': 16108}, {'prodId': 13382394, 'date': '2025-09-18', 'price': 1452.74, 'merchantId': 16108}, {'prodId': 13382394, 'date': '2025-09-19', 'price': 1452.74, 'merchantId': 16108}, {'prodId': 13382394, 'date': '2025-09-20', 'price': 1452.74, 'merchantId': 16108}, {'prodId': 13382394, 'date': '2025-09-21', 'price': 1452.74, 'merchantId': 16108}, {'prodId': 13382394, 'date': '2025-09-22', 'price': 1452.74, 'merchantId': 16108}, {'prodId': 13382394, 'date': '2025-09-23', 'price': 1452.74, 'merchantId': 16108}, {'prodId': 13382394, 'date': '2025-09-24', 'price': 1452.74, 'merchantId': 16108}, {'prodId': 13382394, 'date': '2025-09-25', 'price': 1452.74, 'merchantId': 16108}, {'prodId': 13382394, 'date': '2025-09-26', 'price': 1452.74, 'merchantId': 16108}, {'prodId': 13382394, 'date': '2025-09-27', 'price': 1452.74, 'merchantId': 16108}, {'prodId': 13382394, 'date': '2025-09-28', 'price': 1452.74, 'merchantId': 16108}, {'prodId': 13382394, 'date': '2025-09-29', 'price': 1452.74, 'merchantId': 16108}, {'prodId': 13382394, 'date': '2025-09-30', 'price': 1452.74, 'merchantId': 16108}, {'prodId': 13382394, 'date': '2025-10-01', 'price': 1488.99, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-10-02', 'price': 1488.99, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-10-03', 'price': 1488.99, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-10-04', 'price': 1488.99, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-10-05', 'price': 1488.99, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-10-06', 'price': 1488.99, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-10-07', 'price': 1488.99, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-10-08', 'price': 1488.99, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-10-09', 'price': 1488.99, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-10-10', 'price': 1471.35, 'merchantId': 22905}, {'prodId': 13382394, 'date': '2025-10-11', 'price': 1471.35, 'merchantId': 22905}, {'prodId': 13382394, 'date': '2025-10-12', 'price': 1488.99, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-10-13', 'price': 1488.99, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-10-14', 'price': 1488.99, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-10-15', 'price': 1488.99, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-10-16', 'price': 1488.99, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-10-17', 'price': 1488.99, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-10-18', 'price': 1488.99, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-10-19', 'price': 1488.99, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-10-20', 'price': 1488.99, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-10-21', 'price': 1488.99, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-10-22', 'price': 1488.99, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-10-23', 'price': 1488.99, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-10-24', 'price': 1502.09, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-10-25', 'price': 1538.0, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2025-10-26', 'price': 1551.09, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-10-27', 'price': 1530.82, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-10-28', 'price': 1562.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-10-29', 'price': 1409.16, 'merchantId': 16108}, {'prodId': 13382394, 'date': '2025-10-30', 'price': 1409.16, 'merchantId': 16108}, {'prodId': 13382394, 'date': '2025-10-31', 'price': 1550.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-11-01', 'price': 1528.99, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-11-02', 'price': 1528.99, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-11-03', 'price': 1528.99, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-11-04', 'price': 1492.27, 'merchantId': 22905}, {'prodId': 13382394, 'date': '2025-11-05', 'price': 1549.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-11-06', 'price': 1530.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-11-07', 'price': 1551.09, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-11-08', 'price': 1530.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-11-09', 'price': 1614.15, 'merchantId': 22905}, {'prodId': 13382394, 'date': '2025-11-10', 'price': 1530.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-11-11', 'price': 1530.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-11-12', 'price': 1642.45, 'merchantId': 22905}, {'prodId': 13382394, 'date': '2025-11-13', 'price': 1559.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-11-14', 'price': 1559.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-11-15', 'price': 1643.52, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-11-16', 'price': 1662.5, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-11-17', 'price': 1662.5, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-11-18', 'price': 1564.0, 'merchantId': 22905}, {'prodId': 13382394, 'date': '2025-11-19', 'price': 1650.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-11-20', 'price': 1650.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-11-21', 'price': 1650.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-11-22', 'price': 1649.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-11-23', 'price': 1647.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-11-24', 'price': 1647.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-11-25', 'price': 1647.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-11-26', 'price': 1647.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-11-27', 'price': 1647.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-11-28', 'price': 1647.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-11-29', 'price': 1637.11, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-11-30', 'price': 1579.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-12-01', 'price': 1579.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-12-02', 'price': 1637.11, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-12-03', 'price': 1647.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-12-04', 'price': 1662.75, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-12-05', 'price': 1647.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-12-06', 'price': 1650.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-12-07', 'price': 1647.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-12-08', 'price': 1647.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-12-09', 'price': 1650.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-12-10', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-12-11', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-12-12', 'price': 1670.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-12-13', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-12-14', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-12-15', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-12-16', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-12-17', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-12-18', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-12-19', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-12-20', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-12-21', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-12-22', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-12-23', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-12-24', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-12-25', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-12-26', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2025-12-27', 'price': 1689.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-12-28', 'price': 1699.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-12-29', 'price': 1647.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-12-30', 'price': 1699.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2025-12-31', 'price': 1699.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-01-01', 'price': 1738.71, 'merchantId': 22905}, {'prodId': 13382394, 'date': '2026-01-02', 'price': 1738.71, 'merchantId': 22905}, {'prodId': 13382394, 'date': '2026-01-03', 'price': 1738.71, 'merchantId': 22905}, {'prodId': 13382394, 'date': '2026-01-04', 'price': 1699.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-01-05', 'price': 1699.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-01-06', 'price': 1738.71, 'merchantId': 22905}, {'prodId': 13382394, 'date': '2026-01-07', 'price': 1679.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-01-08', 'price': 1679.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-01-09', 'price': 1700.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-01-10', 'price': 1699.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-01-11', 'price': 1700.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-01-12', 'price': 1679.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-01-13', 'price': 1679.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-01-14', 'price': 1679.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-01-15', 'price': 1689.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-01-16', 'price': 1689.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-01-17', 'price': 1689.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-01-18', 'price': 1679.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-01-19', 'price': 1679.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-01-20', 'price': 1689.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-01-21', 'price': 1669.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-01-22', 'price': 1689.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-01-23', 'price': 1689.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-01-24', 'price': 1689.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-01-25', 'price': 1689.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-01-26', 'price': 1669.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-01-27', 'price': 1674.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-01-28', 'price': 1665.0, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-01-29', 'price': 1665.0, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-01-30', 'price': 1665.0, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-01-31', 'price': 1665.0, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-02-01', 'price': 1665.0, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-02-02', 'price': 1611.29, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-02-03', 'price': 1611.29, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-02-04', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-02-05', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-02-06', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-02-07', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-02-08', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-02-09', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-02-10', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-02-11', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-02-12', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-02-13', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-02-14', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-02-15', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-02-16', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-02-17', 'price': 1599.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-02-18', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-02-19', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-02-20', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-02-21', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-02-22', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-02-23', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-02-24', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-02-25', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-02-26', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-02-27', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-02-28', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-03-01', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-03-02', 'price': 1599.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-03-03', 'price': 1547.4099999999999, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-03-04', 'price': 1547.4099999999999, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-03-05', 'price': 1549.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-03-06', 'price': 1549.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-03-07', 'price': 1549.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-03-08', 'price': 1549.0, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-03-09', 'price': 1499.03, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-03-10', 'price': 1499.03, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-03-11', 'price': 1499.03, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-03-12', 'price': 1499.03, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-03-13', 'price': 1625.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-03-14', 'price': 1655.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-03-15', 'price': 1655.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-03-16', 'price': 1656.0, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-03-17', 'price': 1665.0, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-03-18', 'price': 1665.0, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-03-19', 'price': 1665.0, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-03-20', 'price': 1611.29, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-03-21', 'price': 1611.29, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-03-22', 'price': 1611.29, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-03-23', 'price': 1611.29, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-03-24', 'price': 1674.9, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-03-25', 'price': 1674.9, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-03-26', 'price': 1674.9, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-03-27', 'price': 1674.9, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-03-28', 'price': 1674.9, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-03-29', 'price': 1674.9, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-03-30', 'price': 1674.9, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-03-31', 'price': 1674.8999999999999, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-04-01', 'price': 1674.8999999999999, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-04-02', 'price': 1674.8999999999999, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-04-03', 'price': 1674.8999999999999, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-04-04', 'price': 1674.8999999999999, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-04-05', 'price': 1674.8999999999999, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-04-06', 'price': 1674.8999999999999, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-04-07', 'price': 1674.8999999999999, 'merchantId': 16623}, {'prodId': 13382394, 'date': '2026-04-08', 'price': 1673.9, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-04-09', 'price': 1673.9, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-04-10', 'price': 1673.9, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-04-11', 'price': 1673.9, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-04-12', 'price': 1673.9, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-04-13', 'price': 1673.9, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-04-14', 'price': 1673.9, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-04-15', 'price': 1673.9, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-04-16', 'price': 1673.9, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-04-17', 'price': 1673.9, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-04-18', 'price': 1673.9, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-04-19', 'price': 1673.9, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-04-20', 'price': 1673.9, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-04-21', 'price': 1673.9, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-04-22', 'price': 1673.9, 'merchantId': 15125}, {'prodId': 13382394, 'date': '2026-04-23', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-04-24', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-04-25', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-04-26', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-04-27', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-04-28', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-04-29', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-04-30', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-05-01', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-05-02', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-05-03', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-05-04', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-05-05', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-05-06', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-05-07', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-05-08', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-05-09', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-05-10', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-05-11', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-05-12', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-05-13', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-05-14', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-05-15', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-05-16', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-05-17', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-05-18', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-05-19', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-05-20', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-05-21', 'price': 1698.5, 'merchantId': 22905}, {'prodId': 13382394, 'date': '2026-05-22', 'price': 1698.5, 'merchantId': 22905}, {'prodId': 13382394, 'date': '2026-05-23', 'price': 1698.5, 'merchantId': 22905}, {'prodId': 13382394, 'date': '2026-05-24', 'price': 1698.5, 'merchantId': 22905}, {'prodId': 13382394, 'date': '2026-05-25', 'price': 1698.5, 'merchantId': 22905}, {'prodId': 13382394, 'date': '2026-05-26', 'price': 1698.5, 'merchantId': 22905}, {'prodId': 13382394, 'date': '2026-05-27', 'price': 1698.5, 'merchantId': 22905}, {'prodId': 13382394, 'date': '2026-05-28', 'price': 1699.55, 'merchantId': 22905}, {'prodId': 13382394, 'date': '2026-05-29', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-05-30', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-05-31', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-06-01', 'price': 1598.9, 'merchantId': 21}, {'prodId': 13382394, 'date': '2026-06-02', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-06-03', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-06-04', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-06-05', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-06-06', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-06-07', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-06-08', 'price': 1544.44, 'merchantId': 22905}, {'prodId': 13382394, 'date': '2026-06-09', 'price': 1592.89, 'merchantId': 22905}, {'prodId': 13382394, 'date': '2026-06-10', 'price': 1592.89, 'merchantId': 22905}, {'prodId': 13382394, 'date': '2026-06-11', 'price': 1592.89, 'merchantId': 22905}, {'prodId': 13382394, 'date': '2026-06-12', 'price': 1599.99, 'merchantId': 21}, {'prodId': 13382394, 'date': '2026-06-13', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-06-14', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-06-15', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-06-16', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-06-17', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-06-18', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-06-19', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-06-20', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-06-21', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-06-22', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-06-23', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-06-24', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-06-25', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-06-26', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-06-27', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-06-28', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-06-29', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-06-30', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-07-01', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-07-02', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-07-03', 'price': 1685.59, 'merchantId': 22905}, {'prodId': 13382394, 'date': '2026-07-04', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-07-05', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-07-06', 'price': 1699.9, 'merchantId': 1582}, {'prodId': 13382394, 'date': '2026-07-07', 'price': 1699.9, 'merchantId': 1582}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13186208, 'date': '2025-07-07', 'price': 2974.15, 'merchantId': 22905}, {'prodId': 13186208, 'date': '2025-07-08', 'price': 2969.1, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-07-09', 'price': 2899.0, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-07-10', 'price': 2899.0, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-07-11', 'price': 2899.0, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-07-12', 'price': 2899.0, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-07-13', 'price': 2899.0, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-07-14', 'price': 2899.0, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-07-15', 'price': 2998.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-07-16', 'price': 2997.99, 'merchantId': 9385}, {'prodId': 13186208, 'date': '2025-07-17', 'price': 2998.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-07-18', 'price': 2998.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-07-19', 'price': 3066.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-07-20', 'price': 3066.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-07-21', 'price': 2999.0, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-07-22', 'price': 2299.99, 'merchantId': 22905}, {'prodId': 13186208, 'date': '2025-07-23', 'price': 2299.99, 'merchantId': 22905}, {'prodId': 13186208, 'date': '2025-07-24', 'price': 2999.0, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-07-25', 'price': 1632.99, 'merchantId': 22905}, {'prodId': 13186208, 'date': '2025-07-26', 'price': 2999.0, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-07-27', 'price': 2999.0, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-07-28', 'price': 2999.0, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-07-29', 'price': 3046.0, 'merchantId': 9385}, {'prodId': 13186208, 'date': '2025-07-30', 'price': 3030.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-07-31', 'price': 3030.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-08-01', 'price': 3030.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-08-02', 'price': 3030.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-08-03', 'price': 3030.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-08-04', 'price': 2928.42, 'merchantId': 20609}, {'prodId': 13186208, 'date': '2025-08-05', 'price': 2928.42, 'merchantId': 20609}, {'prodId': 13186208, 'date': '2025-08-06', 'price': 2928.42, 'merchantId': 20609}, {'prodId': 13186208, 'date': '2025-08-07', 'price': 2928.42, 'merchantId': 20609}, {'prodId': 13186208, 'date': '2025-08-08', 'price': 2998.98, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-08-09', 'price': 2998.97, 'merchantId': 9385}, {'prodId': 13186208, 'date': '2025-08-10', 'price': 2998.98, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-08-11', 'price': 2998.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-08-12', 'price': 2998.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-08-13', 'price': 2799.0, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-08-14', 'price': 2799.0, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-08-15', 'price': 2799.0, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-08-16', 'price': 2799.0, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-08-17', 'price': 2799.0, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-08-18', 'price': 2799.0, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-08-19', 'price': 2997.9, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-08-20', 'price': 2997.9, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-08-21', 'price': 2128.51, 'merchantId': 22905}, {'prodId': 13186208, 'date': '2025-08-22', 'price': 2997.9, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-08-23', 'price': 2997.9, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-08-24', 'price': 2997.9, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-08-25', 'price': 2997.9, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-08-26', 'price': 2989.9, 'merchantId': 23254}, {'prodId': 13186208, 'date': '2025-08-27', 'price': 2799.0, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-08-28', 'price': 2898.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-08-29', 'price': 2898.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-08-30', 'price': 2898.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-08-31', 'price': 2898.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-09-01', 'price': 2898.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-09-02', 'price': 2898.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-09-03', 'price': 2897.91, 'merchantId': 20609}, {'prodId': 13186208, 'date': '2025-09-04', 'price': 2848.3, 'merchantId': 23254}, {'prodId': 13186208, 'date': '2025-09-05', 'price': 2799.0, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-09-06', 'price': 2799.0, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-09-07', 'price': 2799.0, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-09-08', 'price': 2789.07, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-09-09', 'price': 2699.1, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-09-10', 'price': 2642.77, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-09-11', 'price': 2642.77, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-09-12', 'price': 2642.77, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-09-13', 'price': 2642.77, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-09-14', 'price': 2642.77, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-09-15', 'price': 2642.77, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-09-16', 'price': 2642.77, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-09-17', 'price': 2699.1, 'merchantId': 20609}, {'prodId': 13186208, 'date': '2025-09-18', 'price': 2699.1, 'merchantId': 20609}, {'prodId': 13186208, 'date': '2025-09-19', 'price': 2679.98, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-09-20', 'price': 2699.0, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-09-21', 'price': 2699.0, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-09-22', 'price': 2679.98, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-09-23', 'price': 2699.0, 'merchantId': 9385}, {'prodId': 13186208, 'date': '2025-09-24', 'price': 2649.0, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-09-25', 'price': 2649.0, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-09-26', 'price': 2649.0, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-09-27', 'price': 2649.0, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-09-28', 'price': 2649.0, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-09-29', 'price': 2699.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-09-30', 'price': 2699.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-10-01', 'price': 2699.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-10-02', 'price': 2699.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-10-03', 'price': 2699.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-10-04', 'price': 2699.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-10-05', 'price': 2699.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-10-06', 'price': 2698.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-10-07', 'price': 2649.0, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-10-08', 'price': 2649.0, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-10-09', 'price': 2698.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-10-10', 'price': 2698.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-10-11', 'price': 2698.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-10-12', 'price': 2698.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-10-13', 'price': 2698.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-10-14', 'price': 2698.0, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-10-15', 'price': 2775.24, 'merchantId': 20609}, {'prodId': 13186208, 'date': '2025-10-16', 'price': 2775.24, 'merchantId': 20609}, {'prodId': 13186208, 'date': '2025-10-17', 'price': 2699.0, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-10-18', 'price': 2699.0, 'merchantId': 5}, {'prodId': 13186208, 'date': '2025-10-19', 'price': 2599.0, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-10-20', 'price': 2599.0, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-10-21', 'price': 2599.0, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-10-22', 'price': 2599.0, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-10-23', 'price': 2775.24, 'merchantId': 20609}, {'prodId': 13186208, 'date': '2025-10-24', 'price': 2775.24, 'merchantId': 20583}, {'prodId': 13186208, 'date': '2025-10-25', 'price': 2775.24, 'merchantId': 20583}, {'prodId': 13186208, 'date': '2025-10-26', 'price': 2775.24, 'merchantId': 20583}, {'prodId': 13186208, 'date': '2025-10-27', 'price': 2775.24, 'merchantId': 20583}, {'prodId': 13186208, 'date': '2025-10-28', 'price': 2775.24, 'merchantId': 20583}, {'prodId': 13186208, 'date': '2025-10-29', 'price': 2775.24, 'merchantId': 20583}, {'prodId': 13186208, 'date': '2025-10-30', 'price': 2775.24, 'merchantId': 20583}, {'prodId': 13186208, 'date': '2025-10-31', 'price': 2775.24, 'merchantId': 20583}, {'prodId': 13186208, 'date': '2025-11-01', 'price': 2775.24, 'merchantId': 20583}, {'prodId': 13186208, 'date': '2025-11-02', 'price': 2775.24, 'merchantId': 20583}, {'prodId': 13186208, 'date': '2025-11-03', 'price': 2775.24, 'merchantId': 20583}, {'prodId': 13186208, 'date': '2025-11-04', 'price': 2775.24, 'merchantId': 20583}, {'prodId': 13186208, 'date': '2025-11-05', 'price': 2775.24, 'merchantId': 20583}, {'prodId': 13186208, 'date': '2025-11-06', 'price': 2669.0, 'merchantId': 1582}, {'prodId': 13186208, 'date': '2025-11-07', 'price': 2667.99, 'merchantId': 9385}, {'prodId': 13186208, 'date': '2025-11-08', 'price': 2667.99, 'merchantId': 9385}, {'prodId': 13186208, 'date': '2025-11-09', 'price': 2667.99, 'merchantId': 9385}, {'prodId': 13186208, 'date': '2025-11-10', 'price': 2667.99, 'merchantId': 9385}, {'prodId': 13186208, 'date': '2025-11-11', 'price': 2666.99, 'merchantId': 9385}, {'prodId': 13186208, 'date': '2025-11-12', 'price': 2666.99, 'merchantId': 9385}, {'prodId': 13186208, 'date': '2025-11-13', 'price': 2666.99, 'merchantId': 9385}, {'prodId': 13186208, 'date': '2025-11-14', 'price': 2664.0, 'merchantId': 9385}, {'prodId': 13186208, 'date': '2025-11-15', 'price': 2664.0, 'merchantId': 9385}, {'prodId': 13186208, 'date': '2025-11-16', 'price': 2775.24, 'merchantId': 20583}, {'prodId': 13186208, 'date': '2025-11-17', 'price': 2775.24, 'merchantId': 20583}, {'prodId': 13186208, 'date': '2025-11-18', 'price': 2775.24, 'merchantId': 20583}, {'prodId': 13186208, 'date': '2025-11-19', 'price': 2775.24, 'merchantId': 20583}, {'prodId': 13186208, 'date': '2025-11-20', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2025-11-21', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2025-11-22', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2025-11-23', 'price': 2647.99, 'merchantId': 9385}, {'prodId': 13186208, 'date': '2025-11-24', 'price': 2698.92, 'merchantId': 9385}, {'prodId': 13186208, 'date': '2025-11-25', 'price': 2698.92, 'merchantId': 9385}, {'prodId': 13186208, 'date': '2025-11-26', 'price': 2698.92, 'merchantId': 9385}, {'prodId': 13186208, 'date': '2025-11-27', 'price': 2698.9, 'merchantId': 9385}, {'prodId': 13186208, 'date': '2025-11-28', 'price': 2698.9, 'merchantId': 9385}, {'prodId': 13186208, 'date': '2025-11-29', 'price': 2698.9, 'merchantId': 1582}, {'prodId': 13186208, 'date': '2025-11-30', 'price': 2699.0, 'merchantId': 9385}, {'prodId': 13186208, 'date': '2025-12-01', 'price': 2697.95, 'merchantId': 1582}, {'prodId': 13186208, 'date': '2025-12-02', 'price': 2697.9, 'merchantId': 1582}, {'prodId': 13186208, 'date': '2025-12-03', 'price': 2697.9, 'merchantId': 1582}, {'prodId': 13186208, 'date': '2025-12-04', 'price': 2697.9, 'merchantId': 1582}, {'prodId': 13186208, 'date': '2025-12-05', 'price': 2697.9, 'merchantId': 1582}, {'prodId': 13186208, 'date': '2025-12-06', 'price': 2699.0, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-12-07', 'price': 2699.0, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-12-08', 'price': 2699.1, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2025-12-09', 'price': 2698.9, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-12-10', 'price': 2698.9, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-12-11', 'price': 2698.9, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-12-12', 'price': 2698.9, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-12-13', 'price': 2698.9, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-12-14', 'price': 2698.9, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-12-15', 'price': 2698.9, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-12-16', 'price': 2698.9, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-12-17', 'price': 2698.9, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-12-18', 'price': 2698.9, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-12-19', 'price': 2698.9, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-12-20', 'price': 2698.9, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-12-21', 'price': 2698.9, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-12-22', 'price': 2698.9, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-12-23', 'price': 2698.9, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-12-24', 'price': 2698.9, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-12-25', 'price': 2698.9, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-12-26', 'price': 2698.9, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-12-27', 'price': 2698.9, 'merchantId': 34}, {'prodId': 13186208, 'date': '2025-12-28', 'price': 2744.54, 'merchantId': 23254}, {'prodId': 13186208, 'date': '2025-12-29', 'price': 2744.54, 'merchantId': 23254}, {'prodId': 13186208, 'date': '2025-12-30', 'price': 2744.54, 'merchantId': 23254}, {'prodId': 13186208, 'date': '2025-12-31', 'price': 2744.54, 'merchantId': 23254}, {'prodId': 13186208, 'date': '2026-01-01', 'price': 2744.54, 'merchantId': 23254}, {'prodId': 13186208, 'date': '2026-01-02', 'price': 2744.54, 'merchantId': 23254}, {'prodId': 13186208, 'date': '2026-01-03', 'price': 2744.54, 'merchantId': 23254}, {'prodId': 13186208, 'date': '2026-01-04', 'price': 2744.54, 'merchantId': 23254}, {'prodId': 13186208, 'date': '2026-01-05', 'price': 2744.54, 'merchantId': 23254}, {'prodId': 13186208, 'date': '2026-01-06', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-01-07', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-01-08', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-01-09', 'price': 2743.39, 'merchantId': 2584}, {'prodId': 13186208, 'date': '2026-01-10', 'price': 2743.39, 'merchantId': 2584}, {'prodId': 13186208, 'date': '2026-01-11', 'price': 2743.39, 'merchantId': 2584}, {'prodId': 13186208, 'date': '2026-01-12', 'price': 2743.39, 'merchantId': 2584}, {'prodId': 13186208, 'date': '2026-01-13', 'price': 2743.39, 'merchantId': 2584}, {'prodId': 13186208, 'date': '2026-01-14', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-01-15', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-01-16', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-01-17', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-01-18', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-01-19', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-01-20', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-01-21', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-01-22', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-01-23', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-01-24', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-01-25', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-01-26', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-01-27', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-01-28', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-01-29', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-01-30', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-01-31', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-02-01', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-02-02', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-02-03', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-02-04', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-02-05', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-02-06', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-02-07', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-02-08', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-02-09', 'price': 2190.0, 'merchantId': 23326}, {'prodId': 13186208, 'date': '2026-02-10', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-02-11', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-02-12', 'price': 2736.8, 'merchantId': 23254}, {'prodId': 13186208, 'date': '2026-02-13', 'price': 2736.8, 'merchantId': 23254}, {'prodId': 13186208, 'date': '2026-02-14', 'price': 2736.8, 'merchantId': 23254}, {'prodId': 13186208, 'date': '2026-02-15', 'price': 2736.8, 'merchantId': 23254}, {'prodId': 13186208, 'date': '2026-02-16', 'price': 2736.8, 'merchantId': 23254}, {'prodId': 13186208, 'date': '2026-02-17', 'price': 2736.8, 'merchantId': 23254}, {'prodId': 13186208, 'date': '2026-02-18', 'price': 2736.8, 'merchantId': 23254}, {'prodId': 13186208, 'date': '2026-02-19', 'price': 2736.8, 'merchantId': 23254}, {'prodId': 13186208, 'date': '2026-02-20', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-02-21', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-02-22', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-02-23', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-02-24', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-02-25', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-02-26', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-02-27', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-02-28', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-01', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-02', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-03', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-04', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-05', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-06', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-07', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-08', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-09', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-10', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-11', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-12', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-13', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-14', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-15', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-16', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-17', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-18', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-19', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-20', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-21', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-22', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-23', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-24', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-25', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-26', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-27', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-28', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-29', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-30', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-03-31', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-01', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-02', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-03', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-04', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-05', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-06', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-07', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-08', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-09', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-10', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-11', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-12', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-13', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-14', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-15', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-16', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-17', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-18', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-19', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-20', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-21', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-22', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-23', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-24', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-25', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-26', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-27', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-28', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-29', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-04-30', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-05-01', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-05-02', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-05-03', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-05-04', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-05-05', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-05-06', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-05-07', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-05-08', 'price': 2699.1, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2026-05-09', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-05-10', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-05-11', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-05-12', 'price': 2699.1, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2026-05-13', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-05-14', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-05-15', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-05-16', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-05-17', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-05-18', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-05-19', 'price': 2699.1, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2026-05-20', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-05-21', 'price': 2699.1, 'merchantId': 22902}, {'prodId': 13186208, 'date': '2026-05-22', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-05-23', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-05-24', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-05-25', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-05-26', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-05-27', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-05-28', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-05-29', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-05-30', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-05-31', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-01', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-02', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-03', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-04', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-05', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-06', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-07', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-08', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-09', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-10', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-11', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-12', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-13', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-14', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-15', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-16', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-17', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-18', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-19', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-20', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-21', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-22', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-23', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-24', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-25', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-26', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-27', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-28', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-29', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-06-30', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-07-01', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-07-02', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-07-03', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-07-04', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-07-05', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-07-06', 'price': 2775.24, 'merchantId': 20612}, {'prodId': 13186208, 'date': '2026-07-07', 'price': 2775.24, 'merchantId': 20612}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 12481774, 'date': '2025-07-07', 'price': 5856.84, 'merchantId': 5}, {'prodId': 12481774, 'date': '2025-07-08', 'price': 5856.84, 'merchantId': 5}, {'prodId': 12481774, 'date': '2025-07-09', 'price': 5856.84, 'merchantId': 5}, {'prodId': 12481774, 'date': '2025-07-10', 'price': 5856.84, 'merchantId': 5}, {'prodId': 12481774, 'date': '2025-07-11', 'price': 5856.84, 'merchantId': 5}, {'prodId': 12481774, 'date': '2025-07-12', 'price': 5856.84, 'merchantId': 5}, {'prodId': 12481774, 'date': '2025-07-13', 'price': 5856.84, 'merchantId': 5}, {'prodId': 12481774, 'date': '2025-07-14', 'price': 5856.84, 'merchantId': 5}, {'prodId': 12481774, 'date': '2025-07-15', 'price': 6199.0, 'merchantId': 20612}, {'prodId': 12481774, 'date': '2025-07-16', 'price': 4649.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-07-17', 'price': 4649.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-07-18', 'price': 4649.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-07-19', 'price': 4649.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-07-20', 'price': 4649.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-07-21', 'price': 4649.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-07-22', 'price': 4649.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-07-23', 'price': 4649.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-07-24', 'price': 4699.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-07-25', 'price': 4699.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-07-26', 'price': 4699.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-07-27', 'price': 4699.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-07-28', 'price': 4699.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-07-29', 'price': 4699.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-07-30', 'price': 4722.9, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-07-31', 'price': 4722.9, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-01', 'price': 3999.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-02', 'price': 3999.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-03', 'price': 3999.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-04', 'price': 3999.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-05', 'price': 4499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-06', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-07', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-08', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-09', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-10', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-11', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-12', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-13', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-14', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-15', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-16', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-17', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-18', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-19', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-20', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-21', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-22', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-23', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-24', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-25', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-26', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-27', 'price': 5199.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-28', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-29', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-30', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-08-31', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-01', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-02', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-03', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-04', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-05', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-06', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-07', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-08', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-09', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-10', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-11', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-12', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-13', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-14', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-15', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-16', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-17', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-18', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-19', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-20', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-21', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-22', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-23', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-24', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-25', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-26', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-27', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-28', 'price': 4499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-29', 'price': 4499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-09-30', 'price': 4499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-01', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-02', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-03', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-04', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-05', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-06', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-07', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-08', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-09', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-10', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-11', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-12', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-13', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-14', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-15', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-16', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-17', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-18', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-19', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-20', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-21', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-22', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-23', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-24', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-25', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-26', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-27', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-28', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-10-29', 'price': 4579.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-10-30', 'price': 4579.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-10-31', 'price': 4579.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-11-01', 'price': 4579.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-11-02', 'price': 4579.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-11-03', 'price': 4499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-11-04', 'price': 4499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-11-05', 'price': 4499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-11-06', 'price': 4499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2025-11-07', 'price': 4719.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-11-08', 'price': 4479.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-11-09', 'price': 4479.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-11-10', 'price': 4479.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-11-11', 'price': 4479.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-11-12', 'price': 4719.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-11-13', 'price': 4479.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-11-14', 'price': 4479.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-11-15', 'price': 4479.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-11-16', 'price': 4479.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-11-17', 'price': 4479.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-11-18', 'price': 4479.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-11-19', 'price': 4249.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-11-20', 'price': 4249.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-11-21', 'price': 4249.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-11-22', 'price': 4249.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-11-23', 'price': 3579.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-11-24', 'price': 3579.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-11-25', 'price': 3579.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-11-26', 'price': 3579.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-11-27', 'price': 3579.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-11-28', 'price': 3479.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-11-29', 'price': 3309.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-11-30', 'price': 3309.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-01', 'price': 4079.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-02', 'price': 4249.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-03', 'price': 4249.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-04', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-05', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-06', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-07', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-08', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-09', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-10', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-11', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-12', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-13', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-14', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-15', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-16', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-17', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-18', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-19', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-20', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-21', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-22', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-23', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-24', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-25', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-26', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-27', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-28', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-29', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-30', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2025-12-31', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-01-01', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-01-02', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-01-03', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-01-04', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-01-05', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-01-06', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-01-07', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-01-08', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-01-09', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-01-10', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-01-11', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-01-12', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-01-13', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-01-14', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-01-15', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-01-16', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-01-17', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-01-18', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-01-19', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-01-20', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-01-21', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-01-22', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-01-23', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-01-24', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-01-25', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-01-26', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-01-27', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-01-28', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-01-29', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-01-30', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-01-31', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-02-01', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-02-02', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-02-03', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-02-04', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-02-05', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-02-06', 'price': 4449.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-02-07', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-02-08', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-02-09', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-02-10', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-02-11', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-02-12', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-02-13', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-02-14', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-02-15', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-02-16', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-02-17', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-02-18', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-02-19', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-02-20', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-02-21', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-02-23', 'price': 7299.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-02-24', 'price': 7299.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-02-25', 'price': 7299.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-02-26', 'price': 7299.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-02-27', 'price': 7299.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-02-28', 'price': 7299.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-03-01', 'price': 7299.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-03-02', 'price': 7299.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-03-03', 'price': 7299.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-03-04', 'price': 7299.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-03-05', 'price': 7299.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-03-06', 'price': 7299.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-03-07', 'price': 7299.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-03-08', 'price': 7299.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-03-09', 'price': 3974.77, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-03-10', 'price': 3974.77, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-03-11', 'price': 3974.77, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-03-12', 'price': 3974.77, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-03-13', 'price': 3974.77, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-03-14', 'price': 3974.77, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-03-15', 'price': 3974.77, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-03-16', 'price': 3974.77, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-03-17', 'price': 3974.77, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-03-18', 'price': 3974.77, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-03-19', 'price': 3974.77, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-03-20', 'price': 3974.77, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-03-21', 'price': 3974.77, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-03-22', 'price': 3974.77, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-03-23', 'price': 3974.77, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-03-24', 'price': 3974.77, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-03-25', 'price': 3974.77, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-03-26', 'price': 3974.77, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-03-27', 'price': 3974.77, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-03-28', 'price': 3974.77, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-03-29', 'price': 3974.77, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-03-30', 'price': 3859.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-03-31', 'price': 3418.57, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-04-01', 'price': 3418.57, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-04-02', 'price': 3418.57, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-04-03', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-04-04', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-04-05', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-04-06', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-04-07', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-04-08', 'price': 4009.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-04-09', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-04-10', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-04-11', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-04-12', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-04-16', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-04-17', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-04-18', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-04-19', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-04-20', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-04-21', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-04-22', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-04-23', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-04-24', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-04-25', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-04-26', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-04-27', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-04-28', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-04-29', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-04-30', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-05-01', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-05-02', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-05-03', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-05-04', 'price': 4009.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-05-05', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-05-06', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-05-07', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-05-08', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-05-09', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-05-10', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-05-11', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-05-12', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-05-13', 'price': 6499.0, 'merchantId': 9385}, {'prodId': 12481774, 'date': '2026-05-21', 'price': 3912.97, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-05-22', 'price': 3912.97, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-05-23', 'price': 3912.97, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-05-24', 'price': 3912.97, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-05-25', 'price': 3912.97, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-05-26', 'price': 3912.97, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-05-27', 'price': 3645.17, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-05-28', 'price': 3645.17, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-05-29', 'price': 3645.17, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-05-30', 'price': 3645.17, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-05-31', 'price': 3645.17, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-01', 'price': 3645.17, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-02', 'price': 4009.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-03', 'price': 4009.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-04', 'price': 4009.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-05', 'price': 3645.17, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-06', 'price': 3645.17, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-07', 'price': 3645.17, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-08', 'price': 3645.17, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-09', 'price': 4009.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-10', 'price': 4009.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-11', 'price': 4009.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-12', 'price': 4009.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-13', 'price': 4009.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-14', 'price': 4009.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-15', 'price': 4009.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-16', 'price': 4009.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-17', 'price': 3645.17, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-18', 'price': 3645.17, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-19', 'price': 3645.17, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-20', 'price': 3645.17, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-21', 'price': 3459.77, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-22', 'price': 3459.77, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-23', 'price': 3459.77, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-24', 'price': 3459.77, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-25', 'price': 3459.77, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-26', 'price': 3645.17, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-27', 'price': 3645.17, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-28', 'price': 3645.17, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-29', 'price': 3645.17, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-06-30', 'price': 3645.17, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-07-01', 'price': 3499.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-07-02', 'price': 3499.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-07-03', 'price': 3499.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-07-04', 'price': 3499.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-07-05', 'price': 3499.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-07-06', 'price': 3499.0, 'merchantId': 1582}, {'prodId': 12481774, 'date': '2026-07-07', 'price': 3499.0, 'merchantId': 1582}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13992135, 'date': '2025-07-07', 'price': 2289.0, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-07-08', 'price': 2289.0, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-07-09', 'price': 2289.9, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-07-10', 'price': 2289.9, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-07-11', 'price': 2289.9, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-07-12', 'price': 2289.9, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-07-13', 'price': 2289.9, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-07-14', 'price': 2289.9, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-07-15', 'price': 2289.9, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-07-16', 'price': 2114.1, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2025-07-17', 'price': 2110.0, 'merchantId': 2}, {'prodId': 13992135, 'date': '2025-07-18', 'price': 2110.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-07-19', 'price': 2110.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-07-20', 'price': 2110.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-07-21', 'price': 2060.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-07-22', 'price': 2060.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-07-23', 'price': 2060.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-07-24', 'price': 2059.2, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-07-25', 'price': 2059.2, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-07-26', 'price': 2059.2, 'merchantId': 1582}, {'prodId': 13992135, 'date': '2025-07-27', 'price': 2113.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-07-28', 'price': 2113.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-07-29', 'price': 2113.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-07-30', 'price': 2113.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-07-31', 'price': 1999.0, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2025-08-01', 'price': 1876.35, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-08-02', 'price': 1876.35, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-08-03', 'price': 1876.35, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-08-04', 'price': 1876.35, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-08-05', 'price': 1876.35, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-08-06', 'price': 1919.0, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-08-07', 'price': 1919.0, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-08-08', 'price': 1880.1, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2025-08-09', 'price': 1880.1, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2025-08-10', 'price': 1880.1, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2025-08-11', 'price': 1880.1, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2025-08-12', 'price': 1880.1, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2025-08-13', 'price': 1880.06, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-08-14', 'price': 1880.06, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-08-15', 'price': 1880.06, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-08-16', 'price': 1880.06, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-08-17', 'price': 1880.06, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-08-18', 'price': 1880.06, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-08-19', 'price': 1880.06, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-08-20', 'price': 1880.06, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-08-21', 'price': 1880.06, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-08-22', 'price': 2069.1, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-08-23', 'price': 2069.1, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-08-24', 'price': 2069.1, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-08-25', 'price': 2069.1, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-08-26', 'price': 1999.0, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2025-08-27', 'price': 1930.41, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2025-08-28', 'price': 1930.41, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2025-08-29', 'price': 1930.41, 'merchantId': 16108}, {'prodId': 13992135, 'date': '2025-08-30', 'price': 1939.0, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2025-08-31', 'price': 1939.0, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2025-09-01', 'price': 1939.0, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2025-09-02', 'price': 1889.1, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2025-09-03', 'price': 1926.32, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-09-04', 'price': 1849.0, 'merchantId': 16108}, {'prodId': 13992135, 'date': '2025-09-05', 'price': 1847.12, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-09-06', 'price': 1880.1, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2025-09-07', 'price': 1880.1, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2025-09-08', 'price': 1835.1, 'merchantId': 20612}, {'prodId': 13992135, 'date': '2025-09-09', 'price': 1835.1, 'merchantId': 20612}, {'prodId': 13992135, 'date': '2025-09-10', 'price': 1835.1, 'merchantId': 20612}, {'prodId': 13992135, 'date': '2025-09-11', 'price': 1835.1, 'merchantId': 20612}, {'prodId': 13992135, 'date': '2025-09-12', 'price': 1835.1, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2025-09-13', 'price': 1835.1, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2025-09-14', 'price': 1835.1, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2025-09-15', 'price': 1835.1, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2025-09-16', 'price': 1846.8, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-09-17', 'price': 1846.8, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2025-09-18', 'price': 1846.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-09-19', 'price': 1845.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-09-20', 'price': 1845.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-09-21', 'price': 1845.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-09-22', 'price': 1845.0, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-09-23', 'price': 1844.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-09-24', 'price': 1793.7, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-09-25', 'price': 1843.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-09-26', 'price': 1843.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-09-27', 'price': 1843.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-09-28', 'price': 1843.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-09-29', 'price': 1741.52, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2025-09-30', 'price': 1899.0, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2025-10-01', 'price': 1909.99, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-10-02', 'price': 1928.4, 'merchantId': 20609}, {'prodId': 13992135, 'date': '2025-10-03', 'price': 1928.4, 'merchantId': 20609}, {'prodId': 13992135, 'date': '2025-10-04', 'price': 1928.4, 'merchantId': 20612}, {'prodId': 13992135, 'date': '2025-10-05', 'price': 1978.2, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2025-10-06', 'price': 1969.0, 'merchantId': 21628}, {'prodId': 13992135, 'date': '2025-10-07', 'price': 1969.0, 'merchantId': 21628}, {'prodId': 13992135, 'date': '2025-10-08', 'price': 1969.0, 'merchantId': 21628}, {'prodId': 13992135, 'date': '2025-10-09', 'price': 1779.24, 'merchantId': 1582}, {'prodId': 13992135, 'date': '2025-10-10', 'price': 1839.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-10-11', 'price': 1838.99, 'merchantId': 1582}, {'prodId': 13992135, 'date': '2025-10-12', 'price': 1838.99, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-10-13', 'price': 1838.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-10-14', 'price': 1815.3, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2025-10-15', 'price': 1815.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-10-16', 'price': 1815.0, 'merchantId': 23254}, {'prodId': 13992135, 'date': '2025-10-17', 'price': 1738.0, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2025-10-18', 'price': 1737.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-10-19', 'price': 1737.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-10-20', 'price': 1737.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-10-21', 'price': 1737.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-10-22', 'price': 1727.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-10-23', 'price': 1726.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-10-24', 'price': 1726.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-10-25', 'price': 1738.99, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-10-26', 'price': 1738.99, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-10-27', 'price': 1727.08, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-10-28', 'price': 1727.08, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-10-29', 'price': 1699.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-10-30', 'price': 1698.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-10-31', 'price': 1697.0, 'merchantId': 4}, {'prodId': 13992135, 'date': '2025-11-01', 'price': 1697.0, 'merchantId': 4}, {'prodId': 13992135, 'date': '2025-11-02', 'price': 1697.0, 'merchantId': 4}, {'prodId': 13992135, 'date': '2025-11-03', 'price': 1696.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-11-04', 'price': 1697.0, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-11-05', 'price': 1749.0, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2025-11-06', 'price': 1739.0, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2025-11-07', 'price': 1738.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-11-08', 'price': 1738.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-11-09', 'price': 1738.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-11-10', 'price': 1664.1, 'merchantId': 23326}, {'prodId': 13992135, 'date': '2025-11-11', 'price': 1709.9, 'merchantId': 16108}, {'prodId': 13992135, 'date': '2025-11-12', 'price': 1709.9, 'merchantId': 16108}, {'prodId': 13992135, 'date': '2025-11-13', 'price': 1667.3, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-11-14', 'price': 1667.3, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-11-15', 'price': 1667.3, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-11-16', 'price': 1667.3, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-11-17', 'price': 1667.3, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-11-18', 'price': 1667.3, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-11-19', 'price': 1667.3, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-11-20', 'price': 1667.3, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-11-21', 'price': 1667.3, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-11-22', 'price': 1727.1, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-11-23', 'price': 1727.1, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-11-24', 'price': 1709.1, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-11-25', 'price': 1688.2, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-11-26', 'price': 1688.2, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-11-27', 'price': 1687.5, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2025-11-28', 'price': 1594.41, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-11-29', 'price': 1686.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-11-30', 'price': 1685.93, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-12-01', 'price': 1670.25, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-12-02', 'price': 1670.25, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2025-12-03', 'price': 1685.9, 'merchantId': 23326}, {'prodId': 13992135, 'date': '2025-12-04', 'price': 1687.0, 'merchantId': 23326}, {'prodId': 13992135, 'date': '2025-12-05', 'price': 1799.9, 'merchantId': 20609}, {'prodId': 13992135, 'date': '2025-12-06', 'price': 1799.9, 'merchantId': 20609}, {'prodId': 13992135, 'date': '2025-12-07', 'price': 1799.9, 'merchantId': 20609}, {'prodId': 13992135, 'date': '2025-12-08', 'price': 1799.9, 'merchantId': 20609}, {'prodId': 13992135, 'date': '2025-12-09', 'price': 1799.9, 'merchantId': 20609}, {'prodId': 13992135, 'date': '2025-12-10', 'price': 1799.9, 'merchantId': 20609}, {'prodId': 13992135, 'date': '2025-12-11', 'price': 1799.9, 'merchantId': 20609}, {'prodId': 13992135, 'date': '2025-12-12', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-12-13', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-12-14', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-12-15', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-12-16', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-12-17', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-12-18', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-12-19', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-12-20', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-12-21', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-12-22', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-12-23', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-12-24', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-12-25', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-12-26', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-12-27', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-12-28', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2025-12-29', 'price': 1799.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-12-30', 'price': 1799.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2025-12-31', 'price': 1799.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2026-01-01', 'price': 1799.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2026-01-02', 'price': 1799.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2026-01-03', 'price': 1799.0, 'merchantId': 23326}, {'prodId': 13992135, 'date': '2026-01-04', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-01-05', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-01-06', 'price': 1756.55, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2026-01-07', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-01-08', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-01-09', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-01-10', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-01-11', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-01-12', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-01-13', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-01-14', 'price': 1756.55, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2026-01-15', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-01-16', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-01-17', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-01-18', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-01-19', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-01-20', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-01-21', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-01-22', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-01-23', 'price': 1799.1, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-01-24', 'price': 1799.1, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-01-25', 'price': 1799.1, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-01-26', 'price': 1799.1, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-01-27', 'price': 1799.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2026-01-28', 'price': 1709.05, 'merchantId': 245}, {'prodId': 13992135, 'date': '2026-01-29', 'price': 1709.05, 'merchantId': 245}, {'prodId': 13992135, 'date': '2026-01-30', 'price': 1709.05, 'merchantId': 245}, {'prodId': 13992135, 'date': '2026-01-31', 'price': 1709.05, 'merchantId': 245}, {'prodId': 13992135, 'date': '2026-02-01', 'price': 1709.05, 'merchantId': 245}, {'prodId': 13992135, 'date': '2026-02-02', 'price': 1709.05, 'merchantId': 245}, {'prodId': 13992135, 'date': '2026-02-03', 'price': 1799.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2026-02-04', 'price': 1709.05, 'merchantId': 245}, {'prodId': 13992135, 'date': '2026-02-05', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-02-06', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-02-07', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-02-08', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-02-09', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-02-10', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-02-11', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-02-12', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-02-13', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-02-14', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-02-15', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-02-16', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-02-17', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-02-18', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-02-19', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-02-20', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-02-21', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-02-22', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-02-23', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-02-24', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-02-25', 'price': 1399.0, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2026-02-26', 'price': 1399.0, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2026-02-27', 'price': 1399.0, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2026-02-28', 'price': 1399.0, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2026-03-01', 'price': 1399.0, 'merchantId': 1582}, {'prodId': 13992135, 'date': '2026-03-02', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-03-03', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-03-04', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-03-05', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-03-06', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-03-07', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-03-08', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-03-09', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-03-10', 'price': 1399.0, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2026-03-11', 'price': 1399.0, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2026-03-12', 'price': 1399.0, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2026-03-13', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-03-14', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-03-15', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-03-16', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-03-17', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-03-18', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-03-19', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-03-20', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-03-21', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-03-22', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-03-23', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-03-24', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-03-25', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-03-26', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-03-27', 'price': 1767.0, 'merchantId': 23326}, {'prodId': 13992135, 'date': '2026-03-28', 'price': 1767.0, 'merchantId': 23326}, {'prodId': 13992135, 'date': '2026-03-29', 'price': 1767.0, 'merchantId': 23326}, {'prodId': 13992135, 'date': '2026-03-30', 'price': 1767.0, 'merchantId': 23326}, {'prodId': 13992135, 'date': '2026-03-31', 'price': 1699.0, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-04-01', 'price': 1698.9, 'merchantId': 23326}, {'prodId': 13992135, 'date': '2026-04-02', 'price': 1698.9, 'merchantId': 23326}, {'prodId': 13992135, 'date': '2026-04-03', 'price': 1698.9, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2026-04-04', 'price': 1698.9, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2026-04-05', 'price': 1699.0, 'merchantId': 16108}, {'prodId': 13992135, 'date': '2026-04-06', 'price': 1699.0, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-04-07', 'price': 1699.0, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-04-08', 'price': 1793.39, 'merchantId': 2584}, {'prodId': 13992135, 'date': '2026-04-09', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-04-10', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-04-11', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-04-12', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-04-13', 'price': 1799.1, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-04-14', 'price': 1803.12, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-04-15', 'price': 1781.19, 'merchantId': 16108}, {'prodId': 13992135, 'date': '2026-04-16', 'price': 1781.19, 'merchantId': 16108}, {'prodId': 13992135, 'date': '2026-04-17', 'price': 1781.19, 'merchantId': 16108}, {'prodId': 13992135, 'date': '2026-04-18', 'price': 1938.6, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2026-04-19', 'price': 1699.2, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-04-20', 'price': 1699.0, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-04-21', 'price': 1699.0, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-04-22', 'price': 1699.0, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-04-23', 'price': 1699.0, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-04-24', 'price': 1914.4600000000003, 'merchantId': 22701}, {'prodId': 13992135, 'date': '2026-04-25', 'price': 1914.4600000000003, 'merchantId': 22701}, {'prodId': 13992135, 'date': '2026-04-26', 'price': 1914.4600000000003, 'merchantId': 22701}, {'prodId': 13992135, 'date': '2026-04-27', 'price': 1914.4600000000003, 'merchantId': 22701}, {'prodId': 13992135, 'date': '2026-04-28', 'price': 1937.79, 'merchantId': 23326}, {'prodId': 13992135, 'date': '2026-04-29', 'price': 1937.79, 'merchantId': 23326}, {'prodId': 13992135, 'date': '2026-04-30', 'price': 1937.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2026-05-01', 'price': 1937.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2026-05-02', 'price': 1936.99, 'merchantId': 1582}, {'prodId': 13992135, 'date': '2026-05-03', 'price': 1936.99, 'merchantId': 1582}, {'prodId': 13992135, 'date': '2026-05-04', 'price': 1936.9, 'merchantId': 34}, {'prodId': 13992135, 'date': '2026-05-05', 'price': 1936.89, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2026-05-06', 'price': 1914.4600000000003, 'merchantId': 22701}, {'prodId': 13992135, 'date': '2026-05-07', 'price': 1899.0, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-05-08', 'price': 1898.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2026-05-09', 'price': 1898.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2026-05-10', 'price': 1898.0, 'merchantId': 1582}, {'prodId': 13992135, 'date': '2026-05-11', 'price': 1898.0, 'merchantId': 1582}, {'prodId': 13992135, 'date': '2026-05-12', 'price': 1876.91, 'merchantId': 245}, {'prodId': 13992135, 'date': '2026-05-13', 'price': 1856.8, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2026-05-14', 'price': 1856.8, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2026-05-15', 'price': 1799.1, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-05-16', 'price': 1799.1, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-05-17', 'price': 1799.1, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-05-18', 'price': 1799.1, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-05-19', 'price': 1799.1, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-05-20', 'price': 1799.1, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-05-21', 'price': 1799.1, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-05-22', 'price': 1799.1, 'merchantId': 16108}, {'prodId': 13992135, 'date': '2026-05-23', 'price': 1799.1, 'merchantId': 16108}, {'prodId': 13992135, 'date': '2026-05-24', 'price': 1799.1, 'merchantId': 16108}, {'prodId': 13992135, 'date': '2026-05-25', 'price': 1799.1, 'merchantId': 16108}, {'prodId': 13992135, 'date': '2026-05-26', 'price': 1799.1, 'merchantId': 16108}, {'prodId': 13992135, 'date': '2026-05-27', 'price': 1799.1, 'merchantId': 16108}, {'prodId': 13992135, 'date': '2026-05-28', 'price': 1799.1, 'merchantId': 16108}, {'prodId': 13992135, 'date': '2026-05-29', 'price': 1799.1, 'merchantId': 16108}, {'prodId': 13992135, 'date': '2026-05-30', 'price': 1799.1, 'merchantId': 16108}, {'prodId': 13992135, 'date': '2026-05-31', 'price': 1799.1, 'merchantId': 16108}, {'prodId': 13992135, 'date': '2026-06-01', 'price': 1799.1, 'merchantId': 16108}, {'prodId': 13992135, 'date': '2026-06-02', 'price': 1799.1, 'merchantId': 16108}, {'prodId': 13992135, 'date': '2026-06-03', 'price': 1799.1, 'merchantId': 16108}, {'prodId': 13992135, 'date': '2026-06-04', 'price': 1889.9, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-06-05', 'price': 1889.9, 'merchantId': 22905}, {'prodId': 13992135, 'date': '2026-06-06', 'price': 1699.15, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2026-06-07', 'price': 1699.15, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2026-06-08', 'price': 1699.15, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2026-06-09', 'price': 1934.05, 'merchantId': 245}, {'prodId': 13992135, 'date': '2026-06-10', 'price': 1799.1, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2026-06-11', 'price': 1954.15, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2026-06-12', 'price': 1799.1, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2026-06-13', 'price': 1899.0, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2026-06-14', 'price': 1954.15, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2026-06-15', 'price': 1862.1, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-06-16', 'price': 1862.1, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-06-17', 'price': 1862.1, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-06-18', 'price': 1862.1, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-06-19', 'price': 1820.72, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2026-06-20', 'price': 1820.72, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2026-06-21', 'price': 1820.72, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2026-06-22', 'price': 1799.1, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2026-06-23', 'price': 1619.0, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2026-06-24', 'price': 1799.1, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2026-06-25', 'price': 1799.1, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2026-06-26', 'price': 1799.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2026-06-27', 'price': 1619.0, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2026-06-28', 'price': 1799.1, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2026-06-29', 'price': 1799.1, 'merchantId': 20583}, {'prodId': 13992135, 'date': '2026-06-30', 'price': 1759.02, 'merchantId': 23326}, {'prodId': 13992135, 'date': '2026-07-01', 'price': 1799.0, 'merchantId': 34}, {'prodId': 13992135, 'date': '2026-07-02', 'price': 1619.0, 'merchantId': 9385}, {'prodId': 13992135, 'date': '2026-07-03', 'price': 1754.1, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-07-04', 'price': 1754.1, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-07-05', 'price': 1754.1, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-07-06', 'price': 1754.1, 'merchantId': 22902}, {'prodId': 13992135, 'date': '2026-07-07', 'price': 1754.1, 'merchantId': 22902}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13994350, 'date': '2026-04-17', 'price': 2565.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-04-18', 'price': 2565.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-04-19', 'price': 2565.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-04-20', 'price': 2565.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-04-26', 'price': 3349.0, 'merchantId': 22905}, {'prodId': 13994350, 'date': '2026-04-27', 'price': 3349.0, 'merchantId': 22905}, {'prodId': 13994350, 'date': '2026-04-28', 'price': 3349.0, 'merchantId': 22905}, {'prodId': 13994350, 'date': '2026-04-29', 'price': 2999.0, 'merchantId': 22905}, {'prodId': 13994350, 'date': '2026-04-30', 'price': 2565.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-01', 'price': 2565.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-02', 'price': 2565.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-03', 'price': 2999.0, 'merchantId': 22905}, {'prodId': 13994350, 'date': '2026-05-04', 'price': 2999.0, 'merchantId': 22905}, {'prodId': 13994350, 'date': '2026-05-05', 'price': 2565.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-06', 'price': 2565.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-07', 'price': 2565.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-08', 'price': 2565.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-09', 'price': 2565.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-10', 'price': 2565.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-11', 'price': 2517.5, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-12', 'price': 2517.5, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-13', 'price': 2517.5, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-14', 'price': 2517.5, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-15', 'price': 2517.5, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-16', 'price': 2517.5, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-17', 'price': 2517.5, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-18', 'price': 2517.5, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-19', 'price': 2517.5, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-20', 'price': 2517.5, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-21', 'price': 2517.5, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-22', 'price': 2517.5, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-23', 'price': 2517.5, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-24', 'price': 2517.5, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-25', 'price': 2517.5, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-26', 'price': 2517.5, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-27', 'price': 2517.5, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-28', 'price': 2517.5, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-29', 'price': 2517.5, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-30', 'price': 2549.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-05-31', 'price': 2549.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-06-01', 'price': 2549.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-06-02', 'price': 2549.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-06-03', 'price': 2549.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-06-04', 'price': 2549.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-06-05', 'price': 2549.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-06-06', 'price': 2699.1, 'merchantId': 22905}, {'prodId': 13994350, 'date': '2026-06-07', 'price': 2751.05, 'merchantId': 22905}, {'prodId': 13994350, 'date': '2026-06-08', 'price': 2706.39, 'merchantId': 22905}, {'prodId': 13994350, 'date': '2026-06-09', 'price': 2706.39, 'merchantId': 22905}, {'prodId': 13994350, 'date': '2026-06-10', 'price': 2751.05, 'merchantId': 22905}, {'prodId': 13994350, 'date': '2026-06-11', 'price': 2549.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-06-12', 'price': 2549.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-06-13', 'price': 2699.1, 'merchantId': 22905}, {'prodId': 13994350, 'date': '2026-06-14', 'price': 2699.1, 'merchantId': 22905}, {'prodId': 13994350, 'date': '2026-06-15', 'price': 2699.1, 'merchantId': 22905}, {'prodId': 13994350, 'date': '2026-06-16', 'price': 2676.64, 'merchantId': 22905}, {'prodId': 13994350, 'date': '2026-06-17', 'price': 2676.64, 'merchantId': 22905}, {'prodId': 13994350, 'date': '2026-06-18', 'price': 2549.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-06-19', 'price': 2549.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-06-20', 'price': 2549.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-06-21', 'price': 2549.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-06-22', 'price': 2549.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-06-23', 'price': 2549.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-06-24', 'price': 2599.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-06-25', 'price': 2599.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-06-26', 'price': 2599.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-06-27', 'price': 2599.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-06-28', 'price': 2599.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-06-29', 'price': 2599.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-06-30', 'price': 2599.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-07-01', 'price': 2599.0, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-07-02', 'price': 2735.79, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-07-03', 'price': 2735.79, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-07-04', 'price': 2735.79, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-07-05', 'price': 2735.79, 'merchantId': 16623}, {'prodId': 13994350, 'date': '2026-07-06', 'price': 2719.15, 'merchantId': 22905}, {'prodId': 13994350, 'date': '2026-07-07', 'price': 2719.15, 'merchantId': 22905}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13994352, 'date': '2026-04-15', 'price': 4512.49, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-04-16', 'price': 4512.49, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-04-17', 'price': 4512.49, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-04-18', 'price': 4512.49, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-04-19', 'price': 4512.49, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-04-20', 'price': 4512.49, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-04-21', 'price': 4512.49, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-04-22', 'price': 4274.99, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-04-23', 'price': 4274.99, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-04-24', 'price': 4274.99, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-04-25', 'price': 4274.99, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-04-26', 'price': 4274.99, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-04-27', 'price': 4274.99, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-04-28', 'price': 4274.99, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-04-29', 'price': 4274.99, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-04-30', 'price': 4274.99, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-01', 'price': 4274.99, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-02', 'price': 4274.99, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-03', 'price': 4274.99, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-04', 'price': 4274.99, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-05', 'price': 4274.99, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-06', 'price': 3518.14, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-07', 'price': 3518.14, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-08', 'price': 3518.14, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-09', 'price': 3518.14, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-10', 'price': 3518.14, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-11', 'price': 3518.14, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-12', 'price': 3518.14, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-13', 'price': 4117.49, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-14', 'price': 4117.49, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-15', 'price': 4117.49, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-16', 'price': 3779.69, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-17', 'price': 3779.69, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-18', 'price': 3698.0, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-19', 'price': 3779.69, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-20', 'price': 3698.0, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-21', 'price': 3698.0, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-22', 'price': 3698.0, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-23', 'price': 3698.0, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-24', 'price': 3698.0, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-25', 'price': 3698.0, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-26', 'price': 3698.0, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-27', 'price': 3779.69, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-28', 'price': 3779.69, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-29', 'price': 3779.69, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-30', 'price': 3455.19, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-05-31', 'price': 3455.19, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-01', 'price': 3455.19, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-02', 'price': 3455.19, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-03', 'price': 3406.39, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-04', 'price': 3406.39, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-05', 'price': 3406.39, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-06', 'price': 3406.39, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-07', 'price': 3406.39, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-08', 'price': 3159.97, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-09', 'price': 3105.04, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-10', 'price': 3499.0, 'merchantId': 16623}, {'prodId': 13994352, 'date': '2026-06-11', 'price': 3499.0, 'merchantId': 16623}, {'prodId': 13994352, 'date': '2026-06-12', 'price': 3617.59, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-13', 'price': 3617.59, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-14', 'price': 3698.0, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-15', 'price': 3698.0, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-16', 'price': 3698.0, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-17', 'price': 3611.14, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-18', 'price': 3611.14, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-19', 'price': 3611.14, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-20', 'price': 3611.14, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-21', 'price': 3611.14, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-22', 'price': 3611.14, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-23', 'price': 3611.14, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-24', 'price': 3611.14, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-25', 'price': 3611.14, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-26', 'price': 3611.14, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-27', 'price': 3611.14, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-28', 'price': 3611.14, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-29', 'price': 3611.14, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-06-30', 'price': 3611.14, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-07-01', 'price': 2500.69, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-07-02', 'price': 3611.14, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-07-03', 'price': 3599.1, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-07-04', 'price': 3599.1, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-07-05', 'price': 3499.0, 'merchantId': 16623}, {'prodId': 13994352, 'date': '2026-07-06', 'price': 3399.15, 'merchantId': 22905}, {'prodId': 13994352, 'date': '2026-07-07', 'price': 3399.15, 'merchantId': 22905}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13992383, 'date': '2025-07-07', 'price': 1619.1, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-07-08', 'price': 1619.1, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-07-09', 'price': 1619.1, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-07-10', 'price': 1619.1, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-07-11', 'price': 1619.1, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-07-12', 'price': 1619.1, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-07-13', 'price': 1619.1, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-07-14', 'price': 1619.1, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-07-15', 'price': 1619.1, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-07-16', 'price': 1619.1, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-07-17', 'price': 1619.1, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-07-18', 'price': 1619.1, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-07-19', 'price': 1619.1, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-07-20', 'price': 1619.1, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-07-21', 'price': 1599.0, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2025-07-22', 'price': 1599.0, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2025-07-23', 'price': 1619.1, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-07-24', 'price': 1619.1, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-07-25', 'price': 1619.1, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-07-26', 'price': 1599.0, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2025-07-27', 'price': 1599.0, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2025-07-28', 'price': 1599.0, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2025-07-29', 'price': 1599.0, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2025-07-30', 'price': 1529.1, 'merchantId': 22902}, {'prodId': 13992383, 'date': '2025-07-31', 'price': 1444.15, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2025-08-01', 'price': 1519.0, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-08-02', 'price': 1519.0, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-08-03', 'price': 1519.0, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-08-04', 'price': 1519.0, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-08-05', 'price': 1519.0, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-08-06', 'price': 1519.0, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-08-07', 'price': 1519.0, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-08-08', 'price': 1493.1, 'merchantId': 22902}, {'prodId': 13992383, 'date': '2025-08-09', 'price': 1484.1, 'merchantId': 20609}, {'prodId': 13992383, 'date': '2025-08-10', 'price': 1484.1, 'merchantId': 20609}, {'prodId': 13992383, 'date': '2025-08-11', 'price': 1484.1, 'merchantId': 20609}, {'prodId': 13992383, 'date': '2025-08-12', 'price': 1469.1, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-08-13', 'price': 1469.1, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-08-14', 'price': 1469.1, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-08-15', 'price': 1469.1, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-08-16', 'price': 1469.1, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-08-17', 'price': 1469.1, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-08-18', 'price': 1459.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-08-19', 'price': 1369.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-08-20', 'price': 1369.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-08-21', 'price': 1369.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-08-22', 'price': 1369.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-08-23', 'price': 1369.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-08-24', 'price': 1369.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-08-25', 'price': 1369.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-08-26', 'price': 1369.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-08-27', 'price': 1369.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-08-28', 'price': 1369.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-08-29', 'price': 1369.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-08-30', 'price': 1369.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-08-31', 'price': 1369.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-09-01', 'price': 1369.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-09-02', 'price': 1369.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-09-03', 'price': 1369.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-09-04', 'price': 1369.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-09-05', 'price': 1369.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-09-06', 'price': 1369.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-09-07', 'price': 1369.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-09-08', 'price': 1369.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-09-09', 'price': 1349.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2025-09-10', 'price': 1349.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2025-09-11', 'price': 1349.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2025-09-12', 'price': 1309.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2025-09-13', 'price': 1309.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2025-09-14', 'price': 1309.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2025-09-15', 'price': 1309.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2025-09-16', 'price': 1309.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2025-09-17', 'price': 1295.19, 'merchantId': 22902}, {'prodId': 13992383, 'date': '2025-09-18', 'price': 1294.0, 'merchantId': 34}, {'prodId': 13992383, 'date': '2025-09-19', 'price': 1294.0, 'merchantId': 34}, {'prodId': 13992383, 'date': '2025-09-20', 'price': 1294.02, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2025-09-21', 'price': 1299.0, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-09-22', 'price': 1285.0, 'merchantId': 34}, {'prodId': 13992383, 'date': '2025-09-23', 'price': 1235.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2025-09-24', 'price': 1235.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2025-09-25', 'price': 1249.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-09-26', 'price': 1249.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-09-27', 'price': 1249.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-09-28', 'price': 1249.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-09-29', 'price': 1249.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-09-30', 'price': 1238.67, 'merchantId': 20583}, {'prodId': 13992383, 'date': '2025-10-01', 'price': 1239.0, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-10-02', 'price': 1239.0, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-10-03', 'price': 1239.0, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-10-04', 'price': 1239.0, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-10-05', 'price': 1239.0, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-10-06', 'price': 1239.0, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-10-07', 'price': 1239.0, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-10-08', 'price': 1239.0, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-10-09', 'price': 1239.0, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2025-10-10', 'price': 1232.1, 'merchantId': 34}, {'prodId': 13992383, 'date': '2025-10-11', 'price': 1232.1, 'merchantId': 34}, {'prodId': 13992383, 'date': '2025-10-12', 'price': 1232.1, 'merchantId': 34}, {'prodId': 13992383, 'date': '2025-10-13', 'price': 1232.1, 'merchantId': 34}, {'prodId': 13992383, 'date': '2025-10-14', 'price': 1201.73, 'merchantId': 23254}, {'prodId': 13992383, 'date': '2025-10-15', 'price': 1201.73, 'merchantId': 23254}, {'prodId': 13992383, 'date': '2025-10-16', 'price': 1201.73, 'merchantId': 23254}, {'prodId': 13992383, 'date': '2025-10-17', 'price': 1177.7, 'merchantId': 23254}, {'prodId': 13992383, 'date': '2025-10-18', 'price': 1177.7, 'merchantId': 23254}, {'prodId': 13992383, 'date': '2025-10-19', 'price': 1177.7, 'merchantId': 23254}, {'prodId': 13992383, 'date': '2025-10-20', 'price': 1177.7, 'merchantId': 23254}, {'prodId': 13992383, 'date': '2025-10-21', 'price': 1177.7, 'merchantId': 23254}, {'prodId': 13992383, 'date': '2025-10-22', 'price': 1177.7, 'merchantId': 23254}, {'prodId': 13992383, 'date': '2025-10-23', 'price': 1177.7, 'merchantId': 23254}, {'prodId': 13992383, 'date': '2025-10-24', 'price': 1177.7, 'merchantId': 23254}, {'prodId': 13992383, 'date': '2025-10-25', 'price': 1187.99, 'merchantId': 1582}, {'prodId': 13992383, 'date': '2025-10-26', 'price': 1213.0, 'merchantId': 34}, {'prodId': 13992383, 'date': '2025-10-27', 'price': 1199.0, 'merchantId': 22902}, {'prodId': 13992383, 'date': '2025-10-28', 'price': 1198.0, 'merchantId': 34}, {'prodId': 13992383, 'date': '2025-10-29', 'price': 1198.0, 'merchantId': 34}, {'prodId': 13992383, 'date': '2025-10-30', 'price': 1128.6, 'merchantId': 34}, {'prodId': 13992383, 'date': '2025-10-31', 'price': 1128.6, 'merchantId': 34}, {'prodId': 13992383, 'date': '2025-11-01', 'price': 1155.42, 'merchantId': 23254}, {'prodId': 13992383, 'date': '2025-11-02', 'price': 1155.42, 'merchantId': 23254}, {'prodId': 13992383, 'date': '2025-11-03', 'price': 1155.42, 'merchantId': 23254}, {'prodId': 13992383, 'date': '2025-11-04', 'price': 1155.42, 'merchantId': 23254}, {'prodId': 13992383, 'date': '2025-11-05', 'price': 1179.0, 'merchantId': 20609}, {'prodId': 13992383, 'date': '2025-11-06', 'price': 1149.0, 'merchantId': 22902}, {'prodId': 13992383, 'date': '2025-11-07', 'price': 1148.0, 'merchantId': 2}, {'prodId': 13992383, 'date': '2025-11-08', 'price': 1148.0, 'merchantId': 2}, {'prodId': 13992383, 'date': '2025-11-09', 'price': 1148.0, 'merchantId': 2}, {'prodId': 13992383, 'date': '2025-11-10', 'price': 1148.0, 'merchantId': 2}, {'prodId': 13992383, 'date': '2025-11-11', 'price': 1148.0, 'merchantId': 2}, {'prodId': 13992383, 'date': '2025-11-12', 'price': 1122.42, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2025-11-13', 'price': 1122.42, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2025-11-14', 'price': 1122.42, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2025-11-15', 'price': 1122.42, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2025-11-16', 'price': 1122.42, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2025-11-17', 'price': 1121.0, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2025-11-18', 'price': 1121.0, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2025-11-19', 'price': 1121.0, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2025-11-20', 'price': 1122.42, 'merchantId': 1582}, {'prodId': 13992383, 'date': '2025-11-21', 'price': 1122.42, 'merchantId': 1582}, {'prodId': 13992383, 'date': '2025-11-22', 'price': 1129.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-11-23', 'price': 1129.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-11-24', 'price': 1129.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-11-25', 'price': 1129.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-11-26', 'price': 1129.0, 'merchantId': 21629}, {'prodId': 13992383, 'date': '2025-11-27', 'price': 1099.0, 'merchantId': 6149}, {'prodId': 13992383, 'date': '2025-11-28', 'price': 1099.0, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2025-11-29', 'price': 1099.0, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2025-11-30', 'price': 1099.05, 'merchantId': 20612}, {'prodId': 13992383, 'date': '2025-12-01', 'price': 1099.05, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2025-12-02', 'price': 1099.05, 'merchantId': 20612}, {'prodId': 13992383, 'date': '2025-12-03', 'price': 1099.05, 'merchantId': 20612}, {'prodId': 13992383, 'date': '2025-12-04', 'price': 1099.05, 'merchantId': 20612}, {'prodId': 13992383, 'date': '2025-12-05', 'price': 1142.0, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2025-12-06', 'price': 1142.0, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2025-12-07', 'price': 1149.0, 'merchantId': 2584}, {'prodId': 13992383, 'date': '2025-12-08', 'price': 1149.0, 'merchantId': 2584}, {'prodId': 13992383, 'date': '2025-12-09', 'price': 1199.9, 'merchantId': 20609}, {'prodId': 13992383, 'date': '2025-12-10', 'price': 1199.9, 'merchantId': 20609}, {'prodId': 13992383, 'date': '2025-12-11', 'price': 1199.9, 'merchantId': 20609}, {'prodId': 13992383, 'date': '2025-12-12', 'price': 1219.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2025-12-13', 'price': 1219.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2025-12-14', 'price': 1219.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2025-12-15', 'price': 1219.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2025-12-16', 'price': 1219.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2025-12-17', 'price': 1219.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2025-12-18', 'price': 1219.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2025-12-19', 'price': 1219.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2025-12-20', 'price': 1219.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2025-12-21', 'price': 1219.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2025-12-22', 'price': 1172.0, 'merchantId': 34}, {'prodId': 13992383, 'date': '2025-12-23', 'price': 1172.0, 'merchantId': 2}, {'prodId': 13992383, 'date': '2025-12-24', 'price': 1172.0, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2025-12-25', 'price': 1172.0, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2025-12-26', 'price': 1172.0, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2025-12-27', 'price': 1172.0, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2025-12-28', 'price': 1172.0, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2025-12-29', 'price': 1172.0, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2025-12-30', 'price': 1172.0, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2025-12-31', 'price': 1172.0, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-01-01', 'price': 1172.0, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-01-02', 'price': 1172.0, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-01-03', 'price': 1172.0, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-01-04', 'price': 1172.0, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-01-05', 'price': 1172.0, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-01-06', 'price': 1172.0, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-01-07', 'price': 1172.0, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-01-08', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-01-09', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-01-10', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-01-11', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-01-12', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-01-13', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-01-14', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-01-15', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-01-16', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-01-17', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-01-18', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-01-19', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-01-20', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-01-21', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-01-22', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-01-23', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-01-24', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-01-25', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-01-26', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-01-27', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-01-28', 'price': 1143.12, 'merchantId': 23254}, {'prodId': 13992383, 'date': '2026-01-29', 'price': 1230.25, 'merchantId': 245}, {'prodId': 13992383, 'date': '2026-01-30', 'price': 1228.26, 'merchantId': 245}, {'prodId': 13992383, 'date': '2026-01-31', 'price': 1228.26, 'merchantId': 245}, {'prodId': 13992383, 'date': '2026-02-01', 'price': 1228.26, 'merchantId': 245}, {'prodId': 13992383, 'date': '2026-02-02', 'price': 1228.26, 'merchantId': 245}, {'prodId': 13992383, 'date': '2026-02-03', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-02-04', 'price': 1233.1, 'merchantId': 245}, {'prodId': 13992383, 'date': '2026-02-05', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-02-06', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-02-07', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-02-08', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-02-09', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-02-10', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-02-11', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-02-12', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-02-13', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-02-14', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-02-15', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-02-16', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-02-17', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-02-18', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-02-19', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-02-20', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-02-21', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-02-22', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-02-23', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-02-24', 'price': 1241.32, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-02-25', 'price': 1274.24, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-02-26', 'price': 1224.9, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2026-02-27', 'price': 1274.24, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-02-28', 'price': 1274.24, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-03-01', 'price': 1274.24, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-03-02', 'price': 1274.24, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-03-03', 'price': 1259.1, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-03-04', 'price': 1224.9, 'merchantId': 1582}, {'prodId': 13992383, 'date': '2026-03-05', 'price': 1258.9, 'merchantId': 34}, {'prodId': 13992383, 'date': '2026-03-06', 'price': 1258.0, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-03-07', 'price': 1258.0, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-03-08', 'price': 1258.0, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-03-09', 'price': 1240.79, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-03-10', 'price': 1240.0, 'merchantId': 2}, {'prodId': 13992383, 'date': '2026-03-11', 'price': 1200.0, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2026-03-12', 'price': 1200.0, 'merchantId': 1582}, {'prodId': 13992383, 'date': '2026-03-13', 'price': 1235.0, 'merchantId': 34}, {'prodId': 13992383, 'date': '2026-03-14', 'price': 1274.24, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-03-15', 'price': 1274.24, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-03-16', 'price': 1274.24, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-03-17', 'price': 1274.24, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-03-18', 'price': 1274.24, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-03-19', 'price': 1274.24, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-03-20', 'price': 1274.24, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-03-21', 'price': 1274.24, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-03-22', 'price': 1274.24, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-03-23', 'price': 1200.75, 'merchantId': 23254}, {'prodId': 13992383, 'date': '2026-03-24', 'price': 1274.24, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-03-25', 'price': 1274.24, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-03-26', 'price': 1274.24, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-03-27', 'price': 1274.24, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-03-28', 'price': 1274.24, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-03-29', 'price': 1274.24, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-03-30', 'price': 1274.24, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-03-31', 'price': 1195.92, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-04-01', 'price': 1195.92, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-04-02', 'price': 1163.65, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2026-04-03', 'price': 1275.12, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-04-04', 'price': 1275.12, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-04-05', 'price': 1299.0, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-04-06', 'price': 1195.92, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-04-07', 'price': 1266.32, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-04-08', 'price': 1291.05, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-04-09', 'price': 1291.05, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-04-10', 'price': 1291.05, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-04-11', 'price': 1291.05, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-04-12', 'price': 1291.05, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-04-13', 'price': 1291.05, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-04-14', 'price': 1291.05, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-04-15', 'price': 1291.05, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-04-16', 'price': 1291.05, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-04-17', 'price': 1259.1, 'merchantId': 245}, {'prodId': 13992383, 'date': '2026-04-18', 'price': 1291.05, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-04-19', 'price': 1291.05, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-04-20', 'price': 1291.05, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-04-21', 'price': 1291.05, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-04-22', 'price': 1241.1, 'merchantId': 1582}, {'prodId': 13992383, 'date': '2026-04-23', 'price': 1241.1, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2026-04-24', 'price': 1348.05, 'merchantId': 20612}, {'prodId': 13992383, 'date': '2026-04-25', 'price': 1406.0, 'merchantId': 245}, {'prodId': 13992383, 'date': '2026-04-26', 'price': 1406.0, 'merchantId': 245}, {'prodId': 13992383, 'date': '2026-04-27', 'price': 1389.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2026-04-28', 'price': 1404.0, 'merchantId': 34}, {'prodId': 13992383, 'date': '2026-04-29', 'price': 1403.9, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-04-30', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13992383, 'date': '2026-05-01', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13992383, 'date': '2026-05-02', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13992383, 'date': '2026-05-03', 'price': 1405.0, 'merchantId': 245}, {'prodId': 13992383, 'date': '2026-05-04', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13992383, 'date': '2026-05-05', 'price': 1389.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2026-05-06', 'price': 1389.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2026-05-07', 'price': 1389.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2026-05-08', 'price': 1389.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2026-05-09', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13992383, 'date': '2026-05-10', 'price': 1398.98, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2026-05-11', 'price': 1389.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2026-05-12', 'price': 1398.98, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2026-05-13', 'price': 1398.98, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2026-05-14', 'price': 1399.0, 'merchantId': 16108}, {'prodId': 13992383, 'date': '2026-05-15', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13992383, 'date': '2026-05-16', 'price': 1398.98, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2026-05-17', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13992383, 'date': '2026-05-18', 'price': 1398.98, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2026-05-19', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13992383, 'date': '2026-05-20', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13992383, 'date': '2026-05-21', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13992383, 'date': '2026-05-22', 'price': 1443.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2026-05-23', 'price': 1349.9, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2026-05-24', 'price': 1427.55, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-05-25', 'price': 1427.55, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-05-26', 'price': 1427.55, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-05-27', 'price': 1427.55, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-05-28', 'price': 1427.55, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-05-29', 'price': 1443.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2026-05-30', 'price': 1443.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2026-05-31', 'price': 1443.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2026-06-01', 'price': 1443.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2026-06-02', 'price': 1418.14, 'merchantId': 23326}, {'prodId': 13992383, 'date': '2026-06-03', 'price': 1227.56, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-06-04', 'price': 1372.93, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-06-05', 'price': 1372.93, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-06-06', 'price': 1443.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2026-06-07', 'price': 1443.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2026-06-08', 'price': 1349.9, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2026-06-09', 'price': 1349.9, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2026-06-10', 'price': 1392.27, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-06-11', 'price': 1392.27, 'merchantId': 22905}, {'prodId': 13992383, 'date': '2026-06-12', 'price': 1476.72, 'merchantId': 2584}, {'prodId': 13992383, 'date': '2026-06-13', 'price': 1476.72, 'merchantId': 2584}, {'prodId': 13992383, 'date': '2026-06-14', 'price': 1476.72, 'merchantId': 2584}, {'prodId': 13992383, 'date': '2026-06-15', 'price': 1389.0, 'merchantId': 21628}, {'prodId': 13992383, 'date': '2026-06-16', 'price': 1359.0, 'merchantId': 34}, {'prodId': 13992383, 'date': '2026-06-17', 'price': 1259.9, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2026-06-18', 'price': 1349.9, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2026-06-19', 'price': 1349.9, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2026-06-20', 'price': 1349.9, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2026-06-21', 'price': 1349.9, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2026-06-22', 'price': 1349.9, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2026-06-23', 'price': 1349.9, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2026-06-24', 'price': 1349.1, 'merchantId': 22902}, {'prodId': 13992383, 'date': '2026-06-25', 'price': 1349.1, 'merchantId': 22902}, {'prodId': 13992383, 'date': '2026-06-26', 'price': 1349.9, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2026-06-27', 'price': 1349.9, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2026-06-28', 'price': 1349.9, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2026-06-29', 'price': 1349.9, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2026-06-30', 'price': 1359.0, 'merchantId': 22902}, {'prodId': 13992383, 'date': '2026-07-01', 'price': 1358.9, 'merchantId': 245}, {'prodId': 13992383, 'date': '2026-07-02', 'price': 1349.9, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2026-07-03', 'price': 1349.9, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2026-07-04', 'price': 1349.9, 'merchantId': 9385}, {'prodId': 13992383, 'date': '2026-07-05', 'price': 1359.0, 'merchantId': 22902}, {'prodId': 13992383, 'date': '2026-07-06', 'price': 1359.0, 'merchantId': 22902}, {'prodId': 13992383, 'date': '2026-07-07', 'price': 1349.9, 'merchantId': 9385}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13340177, 'date': '2025-07-07', 'price': 1547.1, 'merchantId': 23199}, {'prodId': 13340177, 'date': '2025-07-08', 'price': 1256.65, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-07-09', 'price': 959.99, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-07-10', 'price': 899.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-07-11', 'price': 899.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-07-12', 'price': 999.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-07-13', 'price': 969.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-07-14', 'price': 899.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-07-15', 'price': 999.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-07-16', 'price': 1519.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-07-17', 'price': 1519.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-07-18', 'price': 1457.1, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2025-07-19', 'price': 1457.1, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2025-07-20', 'price': 1457.1, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2025-07-21', 'price': 1457.1, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2025-07-22', 'price': 1457.1, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2025-07-23', 'price': 1457.1, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2025-07-24', 'price': 1483.2, 'merchantId': 22905}, {'prodId': 13340177, 'date': '2025-07-25', 'price': 1483.2, 'merchantId': 22905}, {'prodId': 13340177, 'date': '2025-07-26', 'price': 999.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-07-27', 'price': 999.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-07-28', 'price': 1471.83, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-07-29', 'price': 999.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-07-30', 'price': 1438.0, 'merchantId': 34}, {'prodId': 13340177, 'date': '2025-07-31', 'price': 959.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-08-01', 'price': 1398.99, 'merchantId': 9385}, {'prodId': 13340177, 'date': '2025-08-02', 'price': 1199.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-08-03', 'price': 1438.0, 'merchantId': 34}, {'prodId': 13340177, 'date': '2025-08-04', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13340177, 'date': '2025-08-05', 'price': 899.9, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-08-06', 'price': 1368.4, 'merchantId': 22905}, {'prodId': 13340177, 'date': '2025-08-07', 'price': 1368.4, 'merchantId': 22905}, {'prodId': 13340177, 'date': '2025-08-08', 'price': 1199.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-08-09', 'price': 1300.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-08-10', 'price': 1149.99, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-08-11', 'price': 1399.0, 'merchantId': 22902}, {'prodId': 13340177, 'date': '2025-08-12', 'price': 1398.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-08-13', 'price': 1299.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-08-14', 'price': 1299.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-08-15', 'price': 1299.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-08-16', 'price': 1299.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-08-17', 'price': 1299.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-08-18', 'price': 1299.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-08-19', 'price': 1397.99, 'merchantId': 9385}, {'prodId': 13340177, 'date': '2025-08-20', 'price': 999.99, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-08-21', 'price': 999.99, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-08-22', 'price': 1299.85, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-08-23', 'price': 1500.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-08-24', 'price': 1219.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-08-25', 'price': 999.99, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-08-26', 'price': 1500.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-08-27', 'price': 999.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-08-28', 'price': 999.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-08-29', 'price': 999.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-08-30', 'price': 959.59, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-08-31', 'price': 999.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-09-01', 'price': 999.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-09-02', 'price': 959.59, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-09-03', 'price': 1000.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-09-04', 'price': 990.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-09-05', 'price': 1484.09, 'merchantId': 22905}, {'prodId': 13340177, 'date': '2025-09-06', 'price': 1499.0, 'merchantId': 22902}, {'prodId': 13340177, 'date': '2025-09-07', 'price': 1499.0, 'merchantId': 22902}, {'prodId': 13340177, 'date': '2025-09-08', 'price': 1499.0, 'merchantId': 22902}, {'prodId': 13340177, 'date': '2025-09-09', 'price': 1499.0, 'merchantId': 22902}, {'prodId': 13340177, 'date': '2025-09-10', 'price': 1129.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-09-11', 'price': 1129.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-09-12', 'price': 1000.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-09-13', 'price': 1000.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-09-14', 'price': 999.98, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-09-15', 'price': 1000.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-09-16', 'price': 999.98, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-09-17', 'price': 899.99, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-09-18', 'price': 829.9, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-09-19', 'price': 899.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-09-20', 'price': 989.99, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-09-21', 'price': 1434.46, 'merchantId': 9385}, {'prodId': 13340177, 'date': '2025-09-22', 'price': 899.99, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-09-23', 'price': 1511.9, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-09-24', 'price': 1511.9, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-09-25', 'price': 1519.0, 'merchantId': 10763}, {'prodId': 13340177, 'date': '2025-09-26', 'price': 1519.0, 'merchantId': 10763}, {'prodId': 13340177, 'date': '2025-09-27', 'price': 1519.0, 'merchantId': 10763}, {'prodId': 13340177, 'date': '2025-09-28', 'price': 1519.0, 'merchantId': 10763}, {'prodId': 13340177, 'date': '2025-09-29', 'price': 999.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-09-30', 'price': 749.98, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-10-01', 'price': 997.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-10-02', 'price': 799.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-10-03', 'price': 799.98, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-10-04', 'price': 800.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-10-05', 'price': 898.98, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-10-06', 'price': 997.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-10-07', 'price': 1199.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-10-08', 'price': 1389.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-10-09', 'price': 1389.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-10-10', 'price': 1389.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-10-11', 'price': 1389.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-10-12', 'price': 1417.5, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2025-10-13', 'price': 999.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-10-14', 'price': 699.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-10-15', 'price': 800.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-10-16', 'price': 870.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-10-17', 'price': 1347.6, 'merchantId': 9385}, {'prodId': 13340177, 'date': '2025-10-18', 'price': 829.9, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-10-19', 'price': 829.9, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-10-20', 'price': 1350.78, 'merchantId': 9385}, {'prodId': 13340177, 'date': '2025-10-21', 'price': 1350.78, 'merchantId': 9385}, {'prodId': 13340177, 'date': '2025-10-22', 'price': 1345.52, 'merchantId': 9385}, {'prodId': 13340177, 'date': '2025-10-23', 'price': 1298.08, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-10-24', 'price': 1298.08, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-10-25', 'price': 1298.0, 'merchantId': 9385}, {'prodId': 13340177, 'date': '2025-10-26', 'price': 1298.0, 'merchantId': 9385}, {'prodId': 13340177, 'date': '2025-10-27', 'price': 1310.32, 'merchantId': 9385}, {'prodId': 13340177, 'date': '2025-10-28', 'price': 1399.0, 'merchantId': 20609}, {'prodId': 13340177, 'date': '2025-10-29', 'price': 519.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-10-30', 'price': 1399.0, 'merchantId': 34}, {'prodId': 13340177, 'date': '2025-10-31', 'price': 900.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-11-01', 'price': 998.77, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-11-02', 'price': 899.77, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-11-03', 'price': 855.88, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-11-04', 'price': 1279.88, 'merchantId': 9385}, {'prodId': 13340177, 'date': '2025-11-05', 'price': 1260.18, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2025-11-06', 'price': 1260.18, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2025-11-07', 'price': 1252.4, 'merchantId': 9385}, {'prodId': 13340177, 'date': '2025-11-08', 'price': 1249.6, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-11-09', 'price': 1249.6, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-11-10', 'price': 1200.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-11-11', 'price': 1221.24, 'merchantId': 9385}, {'prodId': 13340177, 'date': '2025-11-12', 'price': 1221.24, 'merchantId': 9385}, {'prodId': 13340177, 'date': '2025-11-13', 'price': 1221.24, 'merchantId': 9385}, {'prodId': 13340177, 'date': '2025-11-14', 'price': 1221.24, 'merchantId': 9385}, {'prodId': 13340177, 'date': '2025-11-15', 'price': 1221.24, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-11-16', 'price': 1288.82, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2025-11-17', 'price': 1288.82, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2025-11-18', 'price': 1288.82, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2025-11-19', 'price': 1100.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-11-20', 'price': 1308.99, 'merchantId': 9385}, {'prodId': 13340177, 'date': '2025-11-21', 'price': 1278.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-11-22', 'price': 1284.84, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-11-23', 'price': 1250.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-11-24', 'price': 1100.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-11-25', 'price': 1250.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-11-26', 'price': 1390.5, 'merchantId': 9385}, {'prodId': 13340177, 'date': '2025-11-27', 'price': 1390.5, 'merchantId': 9385}, {'prodId': 13340177, 'date': '2025-11-28', 'price': 1309.0, 'merchantId': 2584}, {'prodId': 13340177, 'date': '2025-11-29', 'price': 1309.0, 'merchantId': 2584}, {'prodId': 13340177, 'date': '2025-11-30', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2025-12-01', 'price': 929.99, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-12-02', 'price': 1309.0, 'merchantId': 2584}, {'prodId': 13340177, 'date': '2025-12-03', 'price': 1299.9, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-12-04', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2025-12-05', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2025-12-06', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2025-12-07', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2025-12-08', 'price': 1299.9, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-12-09', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2025-12-10', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2025-12-11', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2025-12-12', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2025-12-13', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2025-12-14', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2025-12-15', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2025-12-16', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2025-12-17', 'price': 1199.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-12-18', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2025-12-19', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2025-12-20', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2025-12-21', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2025-12-22', 'price': 1199.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2025-12-23', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2025-12-24', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2025-12-25', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2025-12-26', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2025-12-27', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2025-12-28', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2025-12-29', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2025-12-30', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2025-12-31', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-01-01', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-01-02', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-01-03', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-01-04', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-01-05', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-01-06', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-01-07', 'price': 1309.0, 'merchantId': 22902}, {'prodId': 13340177, 'date': '2026-01-08', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-01-09', 'price': 1199.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2026-01-10', 'price': 1199.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2026-01-11', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-01-12', 'price': 1199.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2026-01-13', 'price': 1199.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2026-01-14', 'price': 1199.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2026-01-15', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-01-16', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-01-17', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-01-18', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-01-19', 'price': 1199.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2026-01-20', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-01-21', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-01-22', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-01-23', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-01-24', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-01-25', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-01-26', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-01-27', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-01-28', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-01-29', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-01-30', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-01-31', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-01', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-02', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-03', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-04', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-05', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-06', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-07', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-08', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-09', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-10', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-11', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-12', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-13', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-14', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-15', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-16', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-17', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-18', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-19', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-20', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-21', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-22', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-23', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-24', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-25', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-26', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-27', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-02-28', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-01', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-02', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-03', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-04', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-05', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-06', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-07', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-08', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-09', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-10', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-11', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-12', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-13', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-14', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-15', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-16', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-17', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-18', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-19', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-20', 'price': 1268.21, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2026-03-21', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-22', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-23', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-24', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-25', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-26', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-27', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-28', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-29', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-30', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-03-31', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-04-01', 'price': 1309.0, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-04-02', 'price': 1539.9, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2026-04-03', 'price': 1559.0, 'merchantId': 21629}, {'prodId': 13340177, 'date': '2026-04-04', 'price': 1559.0, 'merchantId': 21629}, {'prodId': 13340177, 'date': '2026-04-05', 'price': 1785.06, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2026-04-06', 'price': 1785.06, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2026-04-07', 'price': 1785.06, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2026-04-08', 'price': 1785.06, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2026-04-09', 'price': 1785.06, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2026-04-10', 'price': 1785.06, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2026-04-11', 'price': 1699.0, 'merchantId': 9385}, {'prodId': 13340177, 'date': '2026-04-12', 'price': 1519.0, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2026-04-13', 'price': 1785.06, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2026-04-14', 'price': 1539.9, 'merchantId': 9385}, {'prodId': 13340177, 'date': '2026-04-15', 'price': 1724.9, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2026-04-16', 'price': 1699.0, 'merchantId': 9385}, {'prodId': 13340177, 'date': '2026-04-17', 'price': 1559.0, 'merchantId': 21629}, {'prodId': 13340177, 'date': '2026-04-18', 'price': 1775.56, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2026-04-19', 'price': 1785.06, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2026-04-20', 'price': 1785.06, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2026-04-21', 'price': 1785.06, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2026-04-22', 'price': 1724.9, 'merchantId': 9385}, {'prodId': 13340177, 'date': '2026-04-23', 'price': 1779.9, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-04-24', 'price': 1779.9, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-04-25', 'price': 1785.06, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2026-04-26', 'price': 1785.06, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2026-04-27', 'price': 1785.06, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2026-04-28', 'price': 1785.06, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2026-04-29', 'price': 1264.83, 'merchantId': 9385}, {'prodId': 13340177, 'date': '2026-04-30', 'price': 1785.06, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2026-05-01', 'price': 1785.06, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2026-05-02', 'price': 1785.06, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2026-05-03', 'price': 1785.06, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2026-05-04', 'price': 1785.06, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2026-05-05', 'price': 1559.0, 'merchantId': 21629}, {'prodId': 13340177, 'date': '2026-05-06', 'price': 1559.0, 'merchantId': 21629}, {'prodId': 13340177, 'date': '2026-05-07', 'price': 1785.06, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2026-05-08', 'price': 1559.0, 'merchantId': 21629}, {'prodId': 13340177, 'date': '2026-05-09', 'price': 1785.06, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2026-05-10', 'price': 1198.21, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2026-05-11', 'price': 1539.9, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2026-05-12', 'price': 1785.06, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2026-05-13', 'price': 1785.06, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2026-05-14', 'price': 1785.06, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2026-05-15', 'price': 1785.06, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2026-05-16', 'price': 1559.0, 'merchantId': 21629}, {'prodId': 13340177, 'date': '2026-05-17', 'price': 1775.56, 'merchantId': 23326}, {'prodId': 13340177, 'date': '2026-05-18', 'price': 1559.0, 'merchantId': 21628}, {'prodId': 13340177, 'date': '2026-05-19', 'price': 1775.56, 'merchantId': 23326}, {'prodId': 13340177, 'date': '2026-05-20', 'price': 1539.9, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2026-05-21', 'price': 1699.0, 'merchantId': 9385}, {'prodId': 13340177, 'date': '2026-05-22', 'price': 1775.56, 'merchantId': 23326}, {'prodId': 13340177, 'date': '2026-05-23', 'price': 1539.9, 'merchantId': 1582}, {'prodId': 13340177, 'date': '2026-05-24', 'price': 1775.56, 'merchantId': 23326}, {'prodId': 13340177, 'date': '2026-05-25', 'price': 1309.0, 'merchantId': 22902}, {'prodId': 13340177, 'date': '2026-05-26', 'price': 1309.0, 'merchantId': 22902}, {'prodId': 13340177, 'date': '2026-05-27', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-05-28', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-05-29', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-05-30', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-05-31', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-01', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-02', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-03', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-04', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-05', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-06', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-07', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-08', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-09', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-10', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-11', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-12', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-13', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-14', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-15', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-16', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-17', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-18', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-19', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-20', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-21', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-22', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-23', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-24', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-25', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-26', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-27', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-28', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-29', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-06-30', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-07-01', 'price': 1349.1, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-07-02', 'price': 1529.1, 'merchantId': 22902}, {'prodId': 13340177, 'date': '2026-07-03', 'price': 1608.9, 'merchantId': 23254}, {'prodId': 13340177, 'date': '2026-07-04', 'price': 1779.9, 'merchantId': 16108}, {'prodId': 13340177, 'date': '2026-07-05', 'price': 1785.06, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2026-07-06', 'price': 1785.06, 'merchantId': 20612}, {'prodId': 13340177, 'date': '2026-07-07', 'price': 1785.06, 'merchantId': 20612}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13341614, 'date': '2025-07-07', 'price': 2369.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-07-08', 'price': 2369.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-07-09', 'price': 2369.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-07-10', 'price': 2337.87, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-07-11', 'price': 2334.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-07-12', 'price': 2337.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-07-13', 'price': 2337.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-07-14', 'price': 2305.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-07-15', 'price': 2337.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-07-16', 'price': 2305.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-07-17', 'price': 2305.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-07-18', 'price': 2319.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-07-19', 'price': 2378.55, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-07-20', 'price': 2378.55, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-07-21', 'price': 2331.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-07-22', 'price': 2263.61, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2025-07-23', 'price': 2263.61, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2025-07-24', 'price': 2322.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-07-25', 'price': 2274.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-07-26', 'price': 2249.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-07-27', 'price': 2239.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-07-28', 'price': 2249.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-07-29', 'price': 2240.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-07-30', 'price': 2240.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-07-31', 'price': 2240.67, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-08-01', 'price': 2259.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-08-02', 'price': 2259.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-08-03', 'price': 2259.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-08-04', 'price': 2259.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-08-05', 'price': 2217.28, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2025-08-06', 'price': 2260.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-08-07', 'price': 2259.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-08-08', 'price': 2259.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-08-09', 'price': 2281.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-08-10', 'price': 2239.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-08-11', 'price': 2289.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-08-12', 'price': 2249.49, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-08-13', 'price': 2239.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-08-14', 'price': 2275.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-08-15', 'price': 2275.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-08-16', 'price': 2275.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-08-17', 'price': 2275.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-08-18', 'price': 2270.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-08-19', 'price': 2207.05, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-08-20', 'price': 2141.29, 'merchantId': 245}, {'prodId': 13341614, 'date': '2025-08-21', 'price': 2141.29, 'merchantId': 245}, {'prodId': 13341614, 'date': '2025-08-22', 'price': 2141.29, 'merchantId': 245}, {'prodId': 13341614, 'date': '2025-08-23', 'price': 2141.29, 'merchantId': 245}, {'prodId': 13341614, 'date': '2025-08-24', 'price': 2141.29, 'merchantId': 245}, {'prodId': 13341614, 'date': '2025-08-25', 'price': 2141.29, 'merchantId': 245}, {'prodId': 13341614, 'date': '2025-08-26', 'price': 2141.29, 'merchantId': 245}, {'prodId': 13341614, 'date': '2025-08-27', 'price': 2141.29, 'merchantId': 245}, {'prodId': 13341614, 'date': '2025-08-28', 'price': 2141.29, 'merchantId': 245}, {'prodId': 13341614, 'date': '2025-08-29', 'price': 2141.29, 'merchantId': 245}, {'prodId': 13341614, 'date': '2025-08-30', 'price': 2141.29, 'merchantId': 245}, {'prodId': 13341614, 'date': '2025-08-31', 'price': 2141.29, 'merchantId': 245}, {'prodId': 13341614, 'date': '2025-09-01', 'price': 2141.29, 'merchantId': 245}, {'prodId': 13341614, 'date': '2025-09-02', 'price': 2141.29, 'merchantId': 245}, {'prodId': 13341614, 'date': '2025-09-03', 'price': 2199.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-09-04', 'price': 2199.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-09-05', 'price': 2185.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-09-06', 'price': 2179.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-09-07', 'price': 2179.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-09-08', 'price': 2185.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-09-09', 'price': 2175.5, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-09-10', 'price': 2175.5, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-09-11', 'price': 2175.5, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-09-12', 'price': 2213.5, 'merchantId': 15125}, {'prodId': 13341614, 'date': '2025-09-13', 'price': 2150.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-09-14', 'price': 2150.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-09-15', 'price': 2184.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-09-16', 'price': 2150.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-09-17', 'price': 2169.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-09-18', 'price': 2160.71, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-09-19', 'price': 2165.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-09-20', 'price': 2153.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-09-21', 'price': 2149.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-09-22', 'price': 2149.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-09-23', 'price': 2149.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-09-24', 'price': 2149.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-09-25', 'price': 2149.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-09-26', 'price': 2149.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-09-27', 'price': 2103.75, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-09-28', 'price': 2103.75, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-09-29', 'price': 2099.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-09-30', 'price': 2099.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-10-01', 'price': 2099.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-10-02', 'price': 2098.0, 'merchantId': 15125}, {'prodId': 13341614, 'date': '2025-10-03', 'price': 2098.0, 'merchantId': 15125}, {'prodId': 13341614, 'date': '2025-10-04', 'price': 2139.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-10-05', 'price': 2139.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-10-06', 'price': 2129.89, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-10-07', 'price': 2139.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-10-08', 'price': 2016.68, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2025-10-09', 'price': 2016.68, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2025-10-10', 'price': 2099.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-10-11', 'price': 2099.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-10-12', 'price': 2099.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-10-13', 'price': 2099.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-10-14', 'price': 2099.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-10-15', 'price': 2099.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-10-16', 'price': 2099.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-10-17', 'price': 2149.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-10-18', 'price': 2099.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-10-19', 'price': 2099.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-10-20', 'price': 2159.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-10-21', 'price': 2159.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-10-22', 'price': 2149.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-10-23', 'price': 2139.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-10-24', 'price': 2099.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-10-25', 'price': 2139.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-10-26', 'price': 2099.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-10-27', 'price': 2137.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-10-28', 'price': 2119.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-10-29', 'price': 2119.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-10-30', 'price': 2119.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-10-31', 'price': 2114.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-11-01', 'price': 2125.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-11-02', 'price': 2110.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-11-03', 'price': 2135.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-11-04', 'price': 2110.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-11-05', 'price': 2109.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-11-06', 'price': 2109.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-11-07', 'price': 2116.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-11-08', 'price': 2115.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-11-09', 'price': 2110.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-11-10', 'price': 2110.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-11-11', 'price': 2110.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-11-12', 'price': 2119.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-11-13', 'price': 2120.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-11-14', 'price': 2120.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-11-15', 'price': 2129.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-11-16', 'price': 2125.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-11-17', 'price': 2139.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-11-18', 'price': 2039.99, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2025-11-19', 'price': 2139.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-11-20', 'price': 2139.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-11-21', 'price': 2139.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-11-22', 'price': 2139.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-11-23', 'price': 2139.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-11-24', 'price': 2139.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-11-25', 'price': 2139.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-11-26', 'price': 2139.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-11-27', 'price': 2139.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-11-28', 'price': 2139.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-11-29', 'price': 2149.0, 'merchantId': 16108}, {'prodId': 13341614, 'date': '2025-11-30', 'price': 2349.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-12-01', 'price': 2249.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-12-02', 'price': 2360.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-12-03', 'price': 2328.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-12-04', 'price': 2289.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-12-05', 'price': 2189.29, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-12-06', 'price': 2199.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-12-07', 'price': 2199.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-12-08', 'price': 2189.29, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-12-09', 'price': 2199.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-12-10', 'price': 2199.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-12-11', 'price': 2289.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-12-12', 'price': 2289.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2025-12-13', 'price': 2239.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-12-14', 'price': 2239.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-12-15', 'price': 2239.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-12-16', 'price': 2239.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-12-17', 'price': 2239.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-12-18', 'price': 2239.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-12-19', 'price': 2239.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-12-20', 'price': 2239.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-12-21', 'price': 2239.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-12-22', 'price': 2239.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-12-23', 'price': 2239.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-12-24', 'price': 2239.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-12-25', 'price': 2239.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-12-26', 'price': 2239.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-12-27', 'price': 2239.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-12-28', 'price': 2239.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-12-29', 'price': 2239.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-12-30', 'price': 2239.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2025-12-31', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-01-01', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-01-02', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-01-03', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-01-04', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-01-05', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-01-06', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-01-07', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-01-08', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-01-09', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-01-10', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-01-11', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-01-12', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-01-13', 'price': 2299.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-01-14', 'price': 2299.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-01-15', 'price': 2299.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-01-16', 'price': 2299.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-01-17', 'price': 2299.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-01-18', 'price': 2299.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-01-19', 'price': 2299.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-01-20', 'price': 2299.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-01-21', 'price': 2299.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-01-22', 'price': 2299.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-01-23', 'price': 2299.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-01-24', 'price': 2299.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-01-25', 'price': 2299.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-01-26', 'price': 2299.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-01-27', 'price': 2299.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-01-28', 'price': 2299.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-01-29', 'price': 2299.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-01-30', 'price': 2299.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-01-31', 'price': 2299.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-02-01', 'price': 2309.0, 'merchantId': 15125}, {'prodId': 13341614, 'date': '2026-02-02', 'price': 2224.84, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-02-03', 'price': 2224.84, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-02-04', 'price': 2224.84, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-02-05', 'price': 2299.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-02-06', 'price': 2299.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-02-07', 'price': 2309.0, 'merchantId': 15125}, {'prodId': 13341614, 'date': '2026-02-08', 'price': 2309.0, 'merchantId': 15125}, {'prodId': 13341614, 'date': '2026-02-09', 'price': 2309.0, 'merchantId': 15125}, {'prodId': 13341614, 'date': '2026-02-10', 'price': 2309.0, 'merchantId': 15125}, {'prodId': 13341614, 'date': '2026-02-11', 'price': 1949.0, 'merchantId': 16108}, {'prodId': 13341614, 'date': '2026-02-12', 'price': 1949.0, 'merchantId': 16108}, {'prodId': 13341614, 'date': '2026-02-13', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-02-14', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-02-15', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-02-16', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-02-17', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-02-18', 'price': 1949.0, 'merchantId': 16108}, {'prodId': 13341614, 'date': '2026-02-19', 'price': 1949.0, 'merchantId': 16108}, {'prodId': 13341614, 'date': '2026-02-20', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-02-21', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-02-22', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-02-23', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-02-24', 'price': 2299.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-02-25', 'price': 2299.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-02-26', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-02-27', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-02-28', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-03-01', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-03-02', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-03-03', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-03-04', 'price': 2325.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-03-05', 'price': 2325.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-03-06', 'price': 2325.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-03-07', 'price': 2325.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-03-08', 'price': 2325.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-03-09', 'price': 2325.0, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-03-10', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-03-11', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-03-12', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-03-13', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-03-14', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-03-15', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-03-16', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-03-17', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-03-18', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-03-19', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-03-20', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-03-21', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-03-22', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-03-23', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-03-24', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-03-25', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-03-26', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-03-27', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-03-28', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-03-29', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-03-30', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-03-31', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-04-01', 'price': 2331.88, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-04-02', 'price': 2336.65, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-04-03', 'price': 2379.15, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-04-04', 'price': 2385.0, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-04-05', 'price': 2409.74, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-04-06', 'price': 2409.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-04-07', 'price': 2421.65, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-04-08', 'price': 2421.65, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-04-09', 'price': 2421.65, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-04-10', 'price': 2421.65, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-04-11', 'price': 2421.65, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-04-12', 'price': 2409.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-04-13', 'price': 2404.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-04-14', 'price': 2348.44, 'merchantId': 16623}, {'prodId': 13341614, 'date': '2026-04-15', 'price': 2419.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-04-16', 'price': 2459.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-04-17', 'price': 2460.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-04-18', 'price': 2340.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-04-19', 'price': 2340.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-04-20', 'price': 2375.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-04-21', 'price': 2393.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-04-22', 'price': 2421.65, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-04-23', 'price': 2420.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-04-24', 'price': 2340.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-04-25', 'price': 2430.7, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-04-26', 'price': 2409.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-04-27', 'price': 2404.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-04-28', 'price': 2415.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-04-29', 'price': 2389.16, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-04-30', 'price': 2389.16, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-05-01', 'price': 2357.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-05-02', 'price': 2339.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-05-03', 'price': 2339.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-05-04', 'price': 2339.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-05-05', 'price': 2185.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-05-06', 'price': 2360.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-05-07', 'price': 2365.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-05-08', 'price': 2369.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-05-09', 'price': 2369.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-05-10', 'price': 2364.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-05-11', 'price': 2364.99, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-05-12', 'price': 2199.0, 'merchantId': 16108}, {'prodId': 13341614, 'date': '2026-05-13', 'price': 2199.0, 'merchantId': 16108}, {'prodId': 13341614, 'date': '2026-05-14', 'price': 2199.0, 'merchantId': 16108}, {'prodId': 13341614, 'date': '2026-05-15', 'price': 2199.0, 'merchantId': 16108}, {'prodId': 13341614, 'date': '2026-05-16', 'price': 2199.0, 'merchantId': 16108}, {'prodId': 13341614, 'date': '2026-05-17', 'price': 2199.0, 'merchantId': 16108}, {'prodId': 13341614, 'date': '2026-05-18', 'price': 2199.0, 'merchantId': 16108}, {'prodId': 13341614, 'date': '2026-05-19', 'price': 2199.0, 'merchantId': 16108}, {'prodId': 13341614, 'date': '2026-05-20', 'price': 2199.0, 'merchantId': 16108}, {'prodId': 13341614, 'date': '2026-05-21', 'price': 2199.0, 'merchantId': 16108}, {'prodId': 13341614, 'date': '2026-05-22', 'price': 2199.0, 'merchantId': 16108}, {'prodId': 13341614, 'date': '2026-05-23', 'price': 2199.0, 'merchantId': 16108}, {'prodId': 13341614, 'date': '2026-05-24', 'price': 2199.0, 'merchantId': 16108}, {'prodId': 13341614, 'date': '2026-05-25', 'price': 2199.0, 'merchantId': 16108}, {'prodId': 13341614, 'date': '2026-05-26', 'price': 2307.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-05-27', 'price': 2307.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-05-28', 'price': 2309.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-05-29', 'price': 2309.16, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-05-30', 'price': 2236.04, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-05-31', 'price': 2300.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-06-01', 'price': 2300.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-06-02', 'price': 2300.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-06-03', 'price': 2294.15, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-06-04', 'price': 2294.15, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-06-05', 'price': 2294.15, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-06-06', 'price': 2209.15, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-06-07', 'price': 2251.65, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-06-08', 'price': 2251.65, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-06-09', 'price': 2251.65, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-06-10', 'price': 2320.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-06-11', 'price': 2319.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-06-12', 'price': 2300.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-06-13', 'price': 2300.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-06-14', 'price': 2300.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-06-15', 'price': 2290.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-06-16', 'price': 2280.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-06-17', 'price': 2280.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-06-18', 'price': 2259.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-06-19', 'price': 2259.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-06-20', 'price': 2279.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-06-21', 'price': 2280.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-06-22', 'price': 2280.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-06-23', 'price': 2165.0, 'merchantId': 16108}, {'prodId': 13341614, 'date': '2026-06-24', 'price': 2165.0, 'merchantId': 16108}, {'prodId': 13341614, 'date': '2026-06-25', 'price': 2165.0, 'merchantId': 16108}, {'prodId': 13341614, 'date': '2026-06-26', 'price': 2165.0, 'merchantId': 16108}, {'prodId': 13341614, 'date': '2026-06-27', 'price': 2165.0, 'merchantId': 16108}, {'prodId': 13341614, 'date': '2026-06-28', 'price': 2165.0, 'merchantId': 16108}, {'prodId': 13341614, 'date': '2026-06-29', 'price': 2165.0, 'merchantId': 16108}, {'prodId': 13341614, 'date': '2026-06-30', 'price': 2332.39, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-07-01', 'price': 2332.39, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-07-02', 'price': 2407.14, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-07-03', 'price': 2320.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-07-04', 'price': 2362.16, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-07-05', 'price': 2390.0, 'merchantId': 1582}, {'prodId': 13341614, 'date': '2026-07-06', 'price': 2336.65, 'merchantId': 22905}, {'prodId': 13341614, 'date': '2026-07-07', 'price': 2336.65, 'merchantId': 22905}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13992139, 'date': '2025-07-07', 'price': 2719.15, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2025-07-08', 'price': 2783.13, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2025-07-09', 'price': 2783.13, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2025-07-10', 'price': 2783.13, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2025-07-11', 'price': 2783.13, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2025-07-12', 'price': 2783.13, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2025-07-13', 'price': 2783.13, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2025-07-14', 'price': 2783.13, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2025-07-15', 'price': 2783.13, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2025-07-16', 'price': 2783.13, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2025-07-17', 'price': 2783.13, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2025-07-18', 'price': 2783.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-07-19', 'price': 2783.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-07-20', 'price': 2783.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-07-21', 'price': 2783.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-07-22', 'price': 2485.08, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-07-23', 'price': 2485.08, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-07-24', 'price': 2727.12, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-07-25', 'price': 2727.12, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-07-26', 'price': 2727.12, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-07-27', 'price': 2727.12, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-07-28', 'price': 2727.12, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-07-29', 'price': 2727.12, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2025-07-30', 'price': 2727.12, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2025-07-31', 'price': 2727.12, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2025-08-01', 'price': 2727.12, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2025-08-02', 'price': 2783.13, 'merchantId': 20612}, {'prodId': 13992139, 'date': '2025-08-03', 'price': 2815.12, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2025-08-04', 'price': 2751.14, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-08-05', 'price': 2751.14, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-08-06', 'price': 2815.12, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2025-08-07', 'price': 2815.12, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2025-08-08', 'price': 2665.14, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-08-09', 'price': 2665.14, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-08-10', 'price': 2665.14, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-08-11', 'price': 2665.14, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-08-12', 'price': 2665.14, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-08-13', 'price': 2789.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-08-14', 'price': 2837.14, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-08-15', 'price': 2837.14, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-08-16', 'price': 2837.14, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-08-17', 'price': 2837.14, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-08-18', 'price': 2789.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-08-19', 'price': 2727.12, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-08-20', 'price': 2789.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-08-21', 'price': 2727.12, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2025-08-22', 'price': 2727.12, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2025-08-23', 'price': 2727.12, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2025-08-24', 'price': 2727.12, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2025-08-25', 'price': 2727.12, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2025-08-26', 'price': 2727.12, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2025-08-27', 'price': 2696.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-08-28', 'price': 2696.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-08-29', 'price': 2696.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-08-30', 'price': 2727.12, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2025-08-31', 'price': 2727.12, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2025-09-01', 'price': 2727.12, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2025-09-02', 'price': 2789.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-09-03', 'price': 2727.12, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2025-09-04', 'price': 2727.12, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2025-09-05', 'price': 2727.12, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2025-09-06', 'price': 2727.12, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2025-09-07', 'price': 2727.12, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2025-09-08', 'price': 2696.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-09-09', 'price': 2696.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-09-10', 'price': 2696.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-09-11', 'price': 2696.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-09-12', 'price': 2696.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-09-13', 'price': 2696.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-09-14', 'price': 2696.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-09-15', 'price': 2696.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-09-16', 'price': 2696.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-09-17', 'price': 2696.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-09-18', 'price': 2609.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-09-19', 'price': 2609.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-09-20', 'price': 2609.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-09-21', 'price': 2609.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-09-22', 'price': 2609.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-09-23', 'price': 2609.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-09-24', 'price': 2609.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-09-25', 'price': 2609.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-09-26', 'price': 2609.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-09-27', 'price': 2609.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-09-28', 'price': 2609.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-09-29', 'price': 2609.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-09-30', 'price': 2609.13, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2025-10-01', 'price': 2609.13, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2025-10-02', 'price': 2698.2, 'merchantId': 23199}, {'prodId': 13992139, 'date': '2025-10-03', 'price': 2698.2, 'merchantId': 23199}, {'prodId': 13992139, 'date': '2025-10-04', 'price': 2698.2, 'merchantId': 23199}, {'prodId': 13992139, 'date': '2025-10-05', 'price': 2698.2, 'merchantId': 23199}, {'prodId': 13992139, 'date': '2025-10-06', 'price': 2698.2, 'merchantId': 23199}, {'prodId': 13992139, 'date': '2025-10-07', 'price': 2698.2, 'merchantId': 23199}, {'prodId': 13992139, 'date': '2025-10-08', 'price': 2698.2, 'merchantId': 23199}, {'prodId': 13992139, 'date': '2025-10-09', 'price': 2698.2, 'merchantId': 23199}, {'prodId': 13992139, 'date': '2025-10-10', 'price': 2549.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-10-11', 'price': 2549.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-10-12', 'price': 2549.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-10-13', 'price': 2549.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-10-14', 'price': 2698.2, 'merchantId': 23199}, {'prodId': 13992139, 'date': '2025-10-15', 'price': 2698.2, 'merchantId': 23199}, {'prodId': 13992139, 'date': '2025-10-16', 'price': 2698.2, 'merchantId': 23199}, {'prodId': 13992139, 'date': '2025-10-17', 'price': 2698.2, 'merchantId': 23199}, {'prodId': 13992139, 'date': '2025-10-18', 'price': 2698.2, 'merchantId': 23199}, {'prodId': 13992139, 'date': '2025-10-19', 'price': 2698.2, 'merchantId': 23199}, {'prodId': 13992139, 'date': '2025-10-20', 'price': 2698.2, 'merchantId': 23199}, {'prodId': 13992139, 'date': '2025-10-21', 'price': 2698.2, 'merchantId': 23199}, {'prodId': 13992139, 'date': '2025-10-22', 'price': 2698.2, 'merchantId': 23199}, {'prodId': 13992139, 'date': '2025-10-23', 'price': 2518.2, 'merchantId': 23199}, {'prodId': 13992139, 'date': '2025-10-24', 'price': 2360.45, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-10-25', 'price': 2360.45, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-10-26', 'price': 2360.45, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-10-27', 'price': 2360.45, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-10-28', 'price': 2360.45, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-10-29', 'price': 2360.45, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-10-30', 'price': 2360.45, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-10-31', 'price': 2360.45, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-11-01', 'price': 2360.45, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-11-02', 'price': 2360.45, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-11-03', 'price': 2360.45, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-11-04', 'price': 2360.45, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-11-05', 'price': 2518.2, 'merchantId': 23199}, {'prodId': 13992139, 'date': '2025-11-06', 'price': 2518.2, 'merchantId': 23199}, {'prodId': 13992139, 'date': '2025-11-07', 'price': 2360.45, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-11-08', 'price': 2360.45, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-11-09', 'price': 2360.45, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-11-10', 'price': 2360.45, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-11-11', 'price': 2360.45, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-11-12', 'price': 2372.35, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-11-13', 'price': 2499.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-11-14', 'price': 2399.0, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-11-15', 'price': 2399.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-11-16', 'price': 2399.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-11-17', 'price': 2399.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-11-18', 'price': 2399.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-11-19', 'price': 2249.1, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-11-20', 'price': 2249.1, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-11-21', 'price': 2249.1, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-11-22', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-11-23', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-11-24', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-11-25', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-11-26', 'price': 2199.12, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-11-27', 'price': 1999.01, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-11-28', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-11-29', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-11-30', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-01', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-02', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-03', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-04', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-05', 'price': 2099.16, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-12-06', 'price': 2099.16, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-12-07', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-08', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-09', 'price': 2099.16, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2025-12-10', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-11', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-12', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-13', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-14', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-15', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-16', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-17', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-18', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-19', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-20', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-21', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-22', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-23', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-24', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-25', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-26', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-27', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-28', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-29', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-30', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2025-12-31', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-01-01', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-01-02', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-01-03', 'price': 2249.1, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-01-04', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-01-05', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-01-06', 'price': 2249.1, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-01-07', 'price': 2249.1, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-01-08', 'price': 2249.1, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-01-09', 'price': 2124.15, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2026-01-10', 'price': 2124.15, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2026-01-11', 'price': 2124.15, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2026-01-12', 'price': 2124.15, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2026-01-13', 'price': 2124.15, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2026-01-14', 'price': 2124.15, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2026-01-15', 'price': 2124.15, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2026-01-16', 'price': 2124.15, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2026-01-17', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-01-18', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-01-19', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-01-20', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-01-21', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-01-22', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-01-23', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-01-24', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-01-25', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-01-26', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-01-27', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-01-28', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-01-29', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-01-30', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-01-31', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-02-01', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-02-02', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-02-03', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-02-04', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-02-05', 'price': 2074.17, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-02-06', 'price': 2074.17, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-02-07', 'price': 2074.17, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-02-08', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-02-09', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-02-10', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-02-11', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-02-12', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-02-13', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-02-14', 'price': 2249.1, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-02-15', 'price': 2249.1, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-02-16', 'price': 2249.1, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-02-17', 'price': 2249.1, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-02-18', 'price': 2249.1, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-02-19', 'price': 2249.1, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-02-20', 'price': 2124.15, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2026-02-21', 'price': 2124.15, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2026-02-22', 'price': 2124.15, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2026-02-23', 'price': 2124.15, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2026-02-24', 'price': 2124.15, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2026-02-25', 'price': 2124.15, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2026-02-26', 'price': 2124.15, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2026-02-27', 'price': 2124.15, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2026-02-28', 'price': 2124.15, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2026-03-01', 'price': 2174.13, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2026-03-02', 'price': 2249.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-03-03', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-03-04', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-03-05', 'price': 2249.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-03-06', 'price': 2174.13, 'merchantId': 20612}, {'prodId': 13992139, 'date': '2026-03-07', 'price': 2174.13, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2026-03-08', 'price': 2174.13, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2026-03-09', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-03-10', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-03-11', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-03-12', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-03-13', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-03-14', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-03-15', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-03-16', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-03-17', 'price': 1999.47, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-03-18', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-03-19', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-03-20', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-03-21', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-03-22', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-03-23', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-03-24', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-03-25', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-03-26', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-03-27', 'price': 1991.17, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-03-28', 'price': 1991.17, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-03-29', 'price': 1991.17, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-03-30', 'price': 1991.17, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-03-31', 'price': 1991.17, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-04-01', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-04-02', 'price': 2249.1, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-04-03', 'price': 2249.1, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-04-04', 'price': 2375.12, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-04-05', 'price': 2375.12, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-04-06', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-04-07', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-04-08', 'price': 2348.13, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-04-09', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-04-10', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-04-11', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-04-12', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-04-13', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-04-14', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-04-15', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-04-16', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-04-17', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-04-18', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-04-19', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-04-20', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-04-21', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-04-22', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-04-23', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-04-24', 'price': 1985.57, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-04-25', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-04-26', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-04-27', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-04-28', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-04-29', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-04-30', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-05-01', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-05-02', 'price': 1999.2, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-05-03', 'price': 1999.2, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-05-04', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-05-05', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-05-06', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-05-07', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-05-08', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-05-09', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-05-10', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-05-11', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-05-12', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-05-13', 'price': 2015.16, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-05-14', 'price': 2015.16, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-05-15', 'price': 2015.16, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-05-16', 'price': 2015.16, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-05-17', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-05-18', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-05-19', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-05-20', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-05-21', 'price': 1999.2, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-05-22', 'price': 1999.2, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-05-23', 'price': 1999.2, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-05-24', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-05-25', 'price': 2099.16, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-05-26', 'price': 2049.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-05-27', 'price': 2049.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-05-28', 'price': 2124.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-05-29', 'price': 2124.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-05-30', 'price': 2124.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-05-31', 'price': 2124.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-06-01', 'price': 2124.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-06-02', 'price': 2029.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-06-03', 'price': 3023.06, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-06-04', 'price': 2124.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-06-05', 'price': 1991.17, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2026-06-06', 'price': 1762.92, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-06-07', 'price': 1762.92, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-06-08', 'price': 2124.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-06-09', 'price': 2124.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-06-10', 'price': 2099.16, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-06-11', 'price': 2124.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-06-12', 'price': 2124.15, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2026-06-13', 'price': 2124.15, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2026-06-14', 'price': 2124.15, 'merchantId': 20583}, {'prodId': 13992139, 'date': '2026-06-15', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-06-16', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-06-17', 'price': 2124.15, 'merchantId': 20609}, {'prodId': 13992139, 'date': '2026-06-18', 'price': 2124.15, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-06-19', 'price': 2124.15, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-06-20', 'price': 2124.15, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-06-21', 'price': 2124.15, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-06-22', 'price': 2124.15, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-06-23', 'price': 2124.15, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-06-24', 'price': 2124.15, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-06-25', 'price': 2124.15, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-06-26', 'price': 2124.15, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-06-27', 'price': 2124.15, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-06-28', 'price': 2124.15, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-06-29', 'price': 2124.15, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-06-30', 'price': 2124.15, 'merchantId': 22905}, {'prodId': 13992139, 'date': '2026-07-01', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-07-02', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-07-03', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-07-04', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-07-05', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-07-06', 'price': 1999.0, 'merchantId': 1582}, {'prodId': 13992139, 'date': '2026-07-07', 'price': 1999.0, 'merchantId': 1582}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13994264, 'date': '2026-03-18', 'price': 2699.1, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-03-19', 'price': 2699.1, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-03-20', 'price': 2699.1, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-03-21', 'price': 2699.1, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-03-22', 'price': 2699.1, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-03-23', 'price': 2699.1, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-03-24', 'price': 2699.1, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-03-25', 'price': 2699.1, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-03-26', 'price': 2699.1, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-03-27', 'price': 2939.02, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-03-28', 'price': 2939.02, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-03-29', 'price': 2939.02, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-03-30', 'price': 2939.02, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-03-31', 'price': 2939.02, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-04-01', 'price': 2699.1, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-04-02', 'price': 2699.1, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-04-03', 'price': 2699.1, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-04-04', 'price': 2999.0, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-04-05', 'price': 2999.0, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-04-06', 'price': 2789.0, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-04-07', 'price': 2789.0, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-04-08', 'price': 2649.55, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-04-09', 'price': 2649.55, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-04-10', 'price': 2649.55, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-04-11', 'price': 2649.55, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-04-12', 'price': 2649.55, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-04-13', 'price': 2649.55, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-04-14', 'price': 2649.55, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-04-15', 'price': 2649.55, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-04-16', 'price': 2649.55, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-04-17', 'price': 2649.55, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-04-18', 'price': 2649.55, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-04-19', 'price': 2649.55, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-04-20', 'price': 2649.55, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-04-21', 'price': 2649.55, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-04-22', 'price': 2649.55, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-04-23', 'price': 2632.45, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-04-24', 'price': 2632.45, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-04-25', 'price': 2632.45, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-04-26', 'price': 2632.45, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-04-27', 'price': 2632.45, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-04-28', 'price': 2699.1, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-04-29', 'price': 2699.1, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-04-30', 'price': 2699.1, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-05-01', 'price': 2699.1, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-05-02', 'price': 2699.1, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-05-03', 'price': 2699.1, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-05-04', 'price': 2699.1, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-05-05', 'price': 2699.1, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-05-06', 'price': 2699.1, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-05-07', 'price': 2699.1, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-05-08', 'price': 2699.1, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-05-09', 'price': 2699.1, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-05-10', 'price': 2699.1, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-05-11', 'price': 2699.1, 'merchantId': 22905}, {'prodId': 13994264, 'date': '2026-05-12', 'price': 2639.12, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-05-13', 'price': 2639.12, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-05-14', 'price': 2639.12, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-05-15', 'price': 2639.12, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-05-16', 'price': 2639.12, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-05-17', 'price': 2639.12, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-05-18', 'price': 2599.0, 'merchantId': 5}, {'prodId': 13994264, 'date': '2026-05-19', 'price': 2339.99, 'merchantId': 23254}, {'prodId': 13994264, 'date': '2026-05-20', 'price': 2339.99, 'merchantId': 23254}, {'prodId': 13994264, 'date': '2026-05-21', 'price': 2463.12, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-05-22', 'price': 2463.12, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-05-23', 'price': 2463.12, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-05-24', 'price': 2463.12, 'merchantId': 20583}, {'prodId': 13994264, 'date': '2026-05-25', 'price': 2463.12, 'merchantId': 20612}, {'prodId': 13994264, 'date': '2026-05-26', 'price': 2313.11, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-05-27', 'price': 2313.11, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-05-28', 'price': 2313.11, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-05-29', 'price': 2313.11, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-05-30', 'price': 2313.11, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-05-31', 'price': 2415.6, 'merchantId': 22905}, {'prodId': 13994264, 'date': '2026-06-01', 'price': 2339.22, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-06-02', 'price': 2339.22, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-06-03', 'price': 2338.85, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-06-04', 'price': 2338.85, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-06-05', 'price': 2349.0, 'merchantId': 5}, {'prodId': 13994264, 'date': '2026-06-06', 'price': 2349.0, 'merchantId': 5}, {'prodId': 13994264, 'date': '2026-06-07', 'price': 2349.0, 'merchantId': 5}, {'prodId': 13994264, 'date': '2026-06-08', 'price': 2349.0, 'merchantId': 5}, {'prodId': 13994264, 'date': '2026-06-09', 'price': 2463.12, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-06-10', 'price': 2164.6, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-06-11', 'price': 2164.5, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-06-12', 'price': 2041.32, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-06-13', 'price': 2041.32, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-06-14', 'price': 2041.32, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-06-15', 'price': 2041.32, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-06-16', 'price': 2164.2, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-06-17', 'price': 2073.18, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-06-18', 'price': 2073.18, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-06-19', 'price': 2070.05, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-06-20', 'price': 2066.17, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-06-21', 'price': 1961.82, 'merchantId': 5}, {'prodId': 13994264, 'date': '2026-06-22', 'price': 1944.0, 'merchantId': 5}, {'prodId': 13994264, 'date': '2026-06-23', 'price': 1944.0, 'merchantId': 5}, {'prodId': 13994264, 'date': '2026-06-24', 'price': 2028.6, 'merchantId': 5}, {'prodId': 13994264, 'date': '2026-06-25', 'price': 1927.17, 'merchantId': 5}, {'prodId': 13994264, 'date': '2026-06-26', 'price': 1927.17, 'merchantId': 5}, {'prodId': 13994264, 'date': '2026-06-27', 'price': 2066.07, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-06-28', 'price': 2113.19, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-06-29', 'price': 2113.19, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-06-30', 'price': 2113.19, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-07-01', 'price': 2018.29, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-07-02', 'price': 1973.44, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-07-03', 'price': 1973.15, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-07-04', 'price': 1874.76, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-07-05', 'price': 1874.76, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-07-06', 'price': 1847.12, 'merchantId': 245}, {'prodId': 13994264, 'date': '2026-07-07', 'price': 1847.12, 'merchantId': 245}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13994235, 'date': '2026-02-27', 'price': 998.0, 'merchantId': 21628}, {'prodId': 13994235, 'date': '2026-02-28', 'price': 998.0, 'merchantId': 21628}, {'prodId': 13994235, 'date': '2026-03-01', 'price': 998.0, 'merchantId': 21628}, {'prodId': 13994235, 'date': '2026-03-02', 'price': 998.0, 'merchantId': 21628}, {'prodId': 13994235, 'date': '2026-03-03', 'price': 899.1, 'merchantId': 22902}, {'prodId': 13994235, 'date': '2026-03-04', 'price': 899.1, 'merchantId': 22902}, {'prodId': 13994235, 'date': '2026-03-05', 'price': 899.1, 'merchantId': 22902}, {'prodId': 13994235, 'date': '2026-03-06', 'price': 899.1, 'merchantId': 22902}, {'prodId': 13994235, 'date': '2026-03-07', 'price': 899.1, 'merchantId': 22902}, {'prodId': 13994235, 'date': '2026-03-08', 'price': 899.1, 'merchantId': 22902}, {'prodId': 13994235, 'date': '2026-03-09', 'price': 899.0, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-03-10', 'price': 899.0, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-03-11', 'price': 898.9, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-03-12', 'price': 898.0, 'merchantId': 21628}, {'prodId': 13994235, 'date': '2026-03-13', 'price': 898.0, 'merchantId': 21628}, {'prodId': 13994235, 'date': '2026-03-14', 'price': 898.9, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-03-15', 'price': 898.9, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-03-16', 'price': 898.0, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-03-17', 'price': 897.9, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-03-18', 'price': 897.9, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-03-19', 'price': 897.9, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-03-20', 'price': 897.9, 'merchantId': 4}, {'prodId': 13994235, 'date': '2026-03-21', 'price': 897.9, 'merchantId': 2}, {'prodId': 13994235, 'date': '2026-03-22', 'price': 897.9, 'merchantId': 2}, {'prodId': 13994235, 'date': '2026-03-23', 'price': 897.9, 'merchantId': 2}, {'prodId': 13994235, 'date': '2026-03-24', 'price': 897.9, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-03-25', 'price': 897.9, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-03-26', 'price': 897.9, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-03-27', 'price': 897.9, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-03-28', 'price': 897.9, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-03-29', 'price': 897.9, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-03-30', 'price': 848.7, 'merchantId': 22902}, {'prodId': 13994235, 'date': '2026-03-31', 'price': 848.7, 'merchantId': 22902}, {'prodId': 13994235, 'date': '2026-04-01', 'price': 848.9, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-04-02', 'price': 848.9, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-04-03', 'price': 848.89, 'merchantId': 9385}, {'prodId': 13994235, 'date': '2026-04-04', 'price': 848.89, 'merchantId': 9385}, {'prodId': 13994235, 'date': '2026-04-05', 'price': 848.9, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-04-06', 'price': 848.0, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-04-07', 'price': 847.9, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-04-08', 'price': 798.99, 'merchantId': 22902}, {'prodId': 13994235, 'date': '2026-04-09', 'price': 798.0, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-04-10', 'price': 797.9, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-04-11', 'price': 780.17, 'merchantId': 245}, {'prodId': 13994235, 'date': '2026-04-12', 'price': 780.17, 'merchantId': 245}, {'prodId': 13994235, 'date': '2026-04-13', 'price': 780.17, 'merchantId': 245}, {'prodId': 13994235, 'date': '2026-04-14', 'price': 779.29, 'merchantId': 245}, {'prodId': 13994235, 'date': '2026-04-15', 'price': 779.29, 'merchantId': 245}, {'prodId': 13994235, 'date': '2026-04-16', 'price': 797.0, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-04-17', 'price': 797.0, 'merchantId': 23326}, {'prodId': 13994235, 'date': '2026-04-18', 'price': 797.0, 'merchantId': 23326}, {'prodId': 13994235, 'date': '2026-04-19', 'price': 797.0, 'merchantId': 23326}, {'prodId': 13994235, 'date': '2026-04-20', 'price': 797.0, 'merchantId': 23326}, {'prodId': 13994235, 'date': '2026-04-21', 'price': 797.0, 'merchantId': 23326}, {'prodId': 13994235, 'date': '2026-04-22', 'price': 797.0, 'merchantId': 23326}, {'prodId': 13994235, 'date': '2026-04-23', 'price': 797.0, 'merchantId': 23326}, {'prodId': 13994235, 'date': '2026-04-24', 'price': 799.2, 'merchantId': 23254}, {'prodId': 13994235, 'date': '2026-04-25', 'price': 799.2, 'merchantId': 23254}, {'prodId': 13994235, 'date': '2026-04-26', 'price': 799.2, 'merchantId': 23254}, {'prodId': 13994235, 'date': '2026-04-27', 'price': 799.2, 'merchantId': 23254}, {'prodId': 13994235, 'date': '2026-04-28', 'price': 799.2, 'merchantId': 23254}, {'prodId': 13994235, 'date': '2026-04-29', 'price': 799.2, 'merchantId': 23254}, {'prodId': 13994235, 'date': '2026-04-30', 'price': 799.2, 'merchantId': 23254}, {'prodId': 13994235, 'date': '2026-05-01', 'price': 799.2, 'merchantId': 23254}, {'prodId': 13994235, 'date': '2026-05-02', 'price': 799.2, 'merchantId': 23254}, {'prodId': 13994235, 'date': '2026-05-03', 'price': 799.2, 'merchantId': 23254}, {'prodId': 13994235, 'date': '2026-05-04', 'price': 799.2, 'merchantId': 23254}, {'prodId': 13994235, 'date': '2026-05-05', 'price': 799.2, 'merchantId': 23254}, {'prodId': 13994235, 'date': '2026-05-06', 'price': 817.27, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-05-07', 'price': 817.27, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-05-08', 'price': 817.27, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-05-09', 'price': 883.15, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-05-10', 'price': 883.15, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-05-11', 'price': 878.93, 'merchantId': 23326}, {'prodId': 13994235, 'date': '2026-05-12', 'price': 809.0, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-05-13', 'price': 808.9, 'merchantId': 4}, {'prodId': 13994235, 'date': '2026-05-14', 'price': 809.0, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-05-15', 'price': 809.0, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-05-16', 'price': 809.0, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-05-17', 'price': 809.0, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-05-18', 'price': 809.0, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-05-19', 'price': 809.0, 'merchantId': 34}, {'prodId': 13994235, 'date': '2026-05-20', 'price': 845.18, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-05-21', 'price': 845.18, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-05-22', 'price': 798.04, 'merchantId': 245}, {'prodId': 13994235, 'date': '2026-05-23', 'price': 789.07, 'merchantId': 23326}, {'prodId': 13994235, 'date': '2026-05-24', 'price': 788.09, 'merchantId': 23326}, {'prodId': 13994235, 'date': '2026-05-25', 'price': 788.09, 'merchantId': 23326}, {'prodId': 13994235, 'date': '2026-05-26', 'price': 788.09, 'merchantId': 23326}, {'prodId': 13994235, 'date': '2026-05-27', 'price': 788.09, 'merchantId': 23326}, {'prodId': 13994235, 'date': '2026-05-28', 'price': 769.22, 'merchantId': 23326}, {'prodId': 13994235, 'date': '2026-05-29', 'price': 769.22, 'merchantId': 23326}, {'prodId': 13994235, 'date': '2026-05-30', 'price': 771.32, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-05-31', 'price': 771.32, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-06-01', 'price': 771.32, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-06-02', 'price': 787.01, 'merchantId': 245}, {'prodId': 13994235, 'date': '2026-06-03', 'price': 771.6, 'merchantId': 23326}, {'prodId': 13994235, 'date': '2026-06-04', 'price': 789.54, 'merchantId': 245}, {'prodId': 13994235, 'date': '2026-06-05', 'price': 730.14, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-06-06', 'price': 730.14, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-06-07', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-06-08', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-06-09', 'price': 764.15, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-06-10', 'price': 809.1, 'merchantId': 23254}, {'prodId': 13994235, 'date': '2026-06-11', 'price': 829.9, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-06-12', 'price': 778.52, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-06-13', 'price': 778.52, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-06-14', 'price': 820.78, 'merchantId': 245}, {'prodId': 13994235, 'date': '2026-06-15', 'price': 820.78, 'merchantId': 245}, {'prodId': 13994235, 'date': '2026-06-16', 'price': 778.52, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-06-17', 'price': 835.83, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-06-18', 'price': 835.83, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-06-19', 'price': 835.19, 'merchantId': 9385}, {'prodId': 13994235, 'date': '2026-06-20', 'price': 835.83, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-06-21', 'price': 835.83, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-06-22', 'price': 835.83, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-06-23', 'price': 778.52, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-06-24', 'price': 778.52, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-06-25', 'price': 792.95, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-06-26', 'price': 792.95, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-06-27', 'price': 792.95, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-06-28', 'price': 835.42, 'merchantId': 245}, {'prodId': 13994235, 'date': '2026-06-29', 'price': 835.33, 'merchantId': 245}, {'prodId': 13994235, 'date': '2026-06-30', 'price': 835.33, 'merchantId': 245}, {'prodId': 13994235, 'date': '2026-07-01', 'price': 799.0, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-07-02', 'price': 799.0, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-07-03', 'price': 749.0, 'merchantId': 16108}, {'prodId': 13994235, 'date': '2026-07-04', 'price': 792.95, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-07-05', 'price': 792.95, 'merchantId': 22905}, {'prodId': 13994235, 'date': '2026-07-06', 'price': 748.0, 'merchantId': 16108}, {'prodId': 13994235, 'date': '2026-07-07', 'price': 748.0, 'merchantId': 22902}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13341612, 'date': '2025-07-07', 'price': 2049.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-07-08', 'price': 2049.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-07-09', 'price': 2049.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-07-10', 'price': 2200.0, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-07-11', 'price': 2204.99, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-07-12', 'price': 2199.99, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-07-13', 'price': 2189.99, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-07-14', 'price': 2200.0, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-07-15', 'price': 2194.99, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-07-16', 'price': 2187.94, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-07-17', 'price': 2170.0, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-07-18', 'price': 2170.0, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-07-19', 'price': 2187.94, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-07-20', 'price': 2187.94, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-07-21', 'price': 2187.94, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-07-22', 'price': 2140.0, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-07-23', 'price': 2151.0, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-07-24', 'price': 2147.0, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-07-25', 'price': 2140.0, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-07-26', 'price': 2138.9, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-07-27', 'price': 2132.0, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-07-28', 'price': 2132.0, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-07-29', 'price': 2159.1, 'merchantId': 16108}, {'prodId': 13341612, 'date': '2025-07-30', 'price': 2159.1, 'merchantId': 16108}, {'prodId': 13341612, 'date': '2025-07-31', 'price': 2138.9, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-08-01', 'price': 2159.1, 'merchantId': 16108}, {'prodId': 13341612, 'date': '2025-08-02', 'price': 2159.1, 'merchantId': 16108}, {'prodId': 13341612, 'date': '2025-08-03', 'price': 2159.1, 'merchantId': 16108}, {'prodId': 13341612, 'date': '2025-08-04', 'price': 2159.1, 'merchantId': 16108}, {'prodId': 13341612, 'date': '2025-08-05', 'price': 2159.1, 'merchantId': 16108}, {'prodId': 13341612, 'date': '2025-08-06', 'price': 2159.1, 'merchantId': 16108}, {'prodId': 13341612, 'date': '2025-08-07', 'price': 2159.1, 'merchantId': 16108}, {'prodId': 13341612, 'date': '2025-08-08', 'price': 2159.1, 'merchantId': 16108}, {'prodId': 13341612, 'date': '2025-08-09', 'price': 2159.1, 'merchantId': 16108}, {'prodId': 13341612, 'date': '2025-08-10', 'price': 2159.1, 'merchantId': 16108}, {'prodId': 13341612, 'date': '2025-08-11', 'price': 2159.1, 'merchantId': 16108}, {'prodId': 13341612, 'date': '2025-08-12', 'price': 2149.0, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-08-13', 'price': 2149.0, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-08-14', 'price': 2159.1, 'merchantId': 16108}, {'prodId': 13341612, 'date': '2025-08-15', 'price': 2159.1, 'merchantId': 16108}, {'prodId': 13341612, 'date': '2025-08-16', 'price': 2159.1, 'merchantId': 16108}, {'prodId': 13341612, 'date': '2025-08-17', 'price': 2159.1, 'merchantId': 16108}, {'prodId': 13341612, 'date': '2025-08-18', 'price': 2149.0, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-08-19', 'price': 2159.1, 'merchantId': 16108}, {'prodId': 13341612, 'date': '2025-08-20', 'price': 2159.1, 'merchantId': 16108}, {'prodId': 13341612, 'date': '2025-08-21', 'price': 2144.98, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2025-08-22', 'price': 2144.98, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2025-08-23', 'price': 2144.98, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2025-08-24', 'price': 2144.98, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2025-08-25', 'price': 2144.98, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2025-08-26', 'price': 2133.55, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2025-08-27', 'price': 1929.0, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-08-28', 'price': 2133.55, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2025-08-29', 'price': 1898.1, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2025-08-30', 'price': 2101.2, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2025-08-31', 'price': 2101.2, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2025-09-01', 'price': 1929.0, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-09-02', 'price': 2070.05, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2025-09-03', 'price': 2031.5, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2025-09-04', 'price': 2031.5, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2025-09-05', 'price': 2031.5, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2025-09-06', 'price': 1899.05, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2025-09-07', 'price': 1899.05, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2025-09-08', 'price': 2038.61, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2025-09-09', 'price': 2038.61, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2025-09-10', 'price': 1975.01, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2025-09-11', 'price': 1949.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-09-12', 'price': 1949.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-09-13', 'price': 1949.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-09-14', 'price': 1949.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-09-15', 'price': 1949.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-09-16', 'price': 1949.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-09-17', 'price': 1835.24, 'merchantId': 16108}, {'prodId': 13341612, 'date': '2025-09-18', 'price': 1835.24, 'merchantId': 16108}, {'prodId': 13341612, 'date': '2025-09-19', 'price': 1835.24, 'merchantId': 16108}, {'prodId': 13341612, 'date': '2025-09-20', 'price': 1949.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-09-21', 'price': 1949.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-09-22', 'price': 1949.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-09-23', 'price': 1949.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-09-24', 'price': 1949.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-09-25', 'price': 1949.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-09-26', 'price': 1949.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-09-27', 'price': 1949.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-09-28', 'price': 1949.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-09-29', 'price': 1899.99, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-09-30', 'price': 1899.99, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-01', 'price': 1899.99, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-02', 'price': 1899.99, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-03', 'price': 1899.99, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-04', 'price': 1899.99, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-05', 'price': 1899.99, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-06', 'price': 1899.99, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-07', 'price': 1849.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-08', 'price': 1847.29, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2025-10-09', 'price': 1847.29, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2025-10-10', 'price': 1849.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-11', 'price': 1849.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-12', 'price': 1849.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-13', 'price': 1849.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-14', 'price': 1849.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-15', 'price': 1849.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-16', 'price': 1849.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-17', 'price': 1849.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-18', 'price': 1849.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-19', 'price': 1849.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-20', 'price': 1849.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-21', 'price': 1849.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-22', 'price': 1849.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-23', 'price': 1849.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-24', 'price': 1849.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-25', 'price': 1849.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-26', 'price': 1849.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-27', 'price': 1849.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-28', 'price': 1849.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-29', 'price': 1849.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-30', 'price': 1849.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-10-31', 'price': 1849.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-01', 'price': 1849.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-02', 'price': 1849.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-03', 'price': 1849.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-04', 'price': 1849.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-05', 'price': 1839.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-06', 'price': 1839.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-07', 'price': 1839.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-08', 'price': 1839.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-09', 'price': 1839.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-10', 'price': 1839.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-11', 'price': 1839.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-12', 'price': 1839.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-13', 'price': 1839.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-14', 'price': 1839.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-15', 'price': 1839.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-16', 'price': 1839.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-17', 'price': 1839.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-18', 'price': 1839.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-19', 'price': 1839.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-20', 'price': 1839.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-21', 'price': 1839.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-22', 'price': 1839.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-23', 'price': 1839.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-24', 'price': 1839.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-25', 'price': 1839.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-26', 'price': 1839.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-27', 'price': 1839.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-28', 'price': 1879.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-29', 'price': 1879.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-11-30', 'price': 2154.4, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-12-01', 'price': 1879.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-12-02', 'price': 1879.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-12-03', 'price': 1879.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-12-04', 'price': 1879.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-12-05', 'price': 1948.9999999999998, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-12-06', 'price': 1948.9999999999998, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-12-07', 'price': 1948.9999999999998, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-12-08', 'price': 1912.0, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-12-09', 'price': 1948.9999999999998, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-12-10', 'price': 1948.9999999999998, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-12-11', 'price': 1948.9999999999998, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-12-12', 'price': 1948.9999999999998, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-12-13', 'price': 1948.9999999999998, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-12-14', 'price': 2015.1, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2025-12-15', 'price': 1948.9999999999998, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-12-16', 'price': 1948.9999999999998, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-12-17', 'price': 2090.0, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-12-18', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2025-12-19', 'price': 1948.9999999999998, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-12-20', 'price': 1948.9999999999998, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-12-21', 'price': 1948.9999999999998, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-12-22', 'price': 1948.9999999999998, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-12-23', 'price': 1948.9999999999998, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-12-24', 'price': 1948.9999999999998, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-12-25', 'price': 1948.9999999999998, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-12-26', 'price': 1948.9999999999998, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-12-27', 'price': 1948.9999999999998, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-12-28', 'price': 1948.9999999999998, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-12-29', 'price': 1948.9999999999998, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-12-30', 'price': 1948.9999999999998, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2025-12-31', 'price': 1948.9999999999998, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-01-01', 'price': 2287.99, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2026-01-02', 'price': 2287.99, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2026-01-03', 'price': 2287.99, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2026-01-04', 'price': 2239.0, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2026-01-05', 'price': 2239.0, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2026-01-06', 'price': 2250.46, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2026-01-07', 'price': 2287.99, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2026-01-08', 'price': 2287.99, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2026-01-09', 'price': 2287.99, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2026-01-10', 'price': 2287.99, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2026-01-11', 'price': 2287.99, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2026-01-12', 'price': 2287.99, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2026-01-13', 'price': 1879.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-01-14', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-01-15', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-01-16', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-01-17', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-01-18', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-01-19', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-01-20', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-01-21', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-01-22', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-01-23', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-01-24', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-01-25', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-01-26', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-01-27', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-01-28', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-01-29', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-01-30', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-01-31', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-01', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-02', 'price': 2011.93, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-03', 'price': 2011.93, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-04', 'price': 2011.93, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-05', 'price': 2019.9, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-06', 'price': 2019.9, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-07', 'price': 2019.9, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-08', 'price': 2019.9, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-09', 'price': 2019.9, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-10', 'price': 2019.9, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-11', 'price': 2019.9, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-12', 'price': 2019.9, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-13', 'price': 2019.9, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-14', 'price': 2019.9, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-15', 'price': 2019.9, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-16', 'price': 2019.9, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-17', 'price': 2019.9, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-18', 'price': 2019.9, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-19', 'price': 2019.9, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-20', 'price': 2019.9, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-21', 'price': 2019.9, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-22', 'price': 2019.9, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-23', 'price': 2019.9, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-24', 'price': 2019.9, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-25', 'price': 1948.9999999999998, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-26', 'price': 2049.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-27', 'price': 2049.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-02-28', 'price': 2049.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-01', 'price': 2049.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-02', 'price': 2049.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-03', 'price': 2049.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-04', 'price': 2049.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-05', 'price': 2049.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-06', 'price': 2049.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-07', 'price': 2049.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-08', 'price': 2049.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-09', 'price': 1982.91, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-10', 'price': 1982.91, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-11', 'price': 1982.91, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-12', 'price': 2099.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-13', 'price': 2099.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-14', 'price': 2099.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-15', 'price': 2099.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-16', 'price': 2099.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-17', 'price': 2099.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-18', 'price': 2099.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-19', 'price': 2160.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-20', 'price': 2160.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-21', 'price': 2160.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-22', 'price': 2160.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-23', 'price': 2160.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-24', 'price': 2160.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-25', 'price': 2160.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-26', 'price': 2160.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-27', 'price': 2160.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-28', 'price': 2160.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-29', 'price': 2160.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-03-30', 'price': 2159.0, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2026-03-31', 'price': 2142.19, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2026-04-01', 'price': 2146.3, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2026-04-02', 'price': 2143.79, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2026-04-03', 'price': 2157.0, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2026-04-04', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-04-05', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-04-06', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-04-07', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-04-08', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-04-09', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-04-10', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-04-11', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-04-12', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-04-13', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-04-14', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-04-15', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-04-16', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-04-17', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-04-18', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-04-19', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-04-20', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-04-21', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-04-22', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-04-23', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-04-24', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-04-25', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-04-26', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-04-27', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-04-28', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-04-29', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-04-30', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-05-01', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2026-05-02', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2026-05-03', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2026-05-04', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2026-05-05', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-05-06', 'price': 2099.0, 'merchantId': 1582}, {'prodId': 13341612, 'date': '2026-05-07', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-05-08', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-05-09', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-05-10', 'price': 2159.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-05-11', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-05-12', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-05-13', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-05-14', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-05-15', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-05-16', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-05-17', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-05-18', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-05-19', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-05-20', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-05-21', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-05-22', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-05-23', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-05-24', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-05-25', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-05-26', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-05-27', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-05-28', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-05-29', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-05-30', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-05-31', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-01', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-02', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-03', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-04', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-05', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-06', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-07', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-08', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-09', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-10', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-11', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-12', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-13', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-14', 'price': 2090.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-15', 'price': 2200.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-16', 'price': 1995.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-17', 'price': 1995.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-18', 'price': 1995.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-19', 'price': 1995.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-20', 'price': 1995.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-21', 'price': 1995.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-22', 'price': 1995.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-23', 'price': 1995.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-24', 'price': 1995.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-25', 'price': 1995.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-26', 'price': 1995.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-27', 'price': 1995.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-28', 'price': 1995.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-29', 'price': 1995.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-06-30', 'price': 1995.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-07-01', 'price': 1995.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-07-02', 'price': 2100.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-07-03', 'price': 2100.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-07-04', 'price': 2100.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-07-05', 'price': 2100.0, 'merchantId': 16623}, {'prodId': 13341612, 'date': '2026-07-06', 'price': 1592.89, 'merchantId': 22905}, {'prodId': 13341612, 'date': '2026-07-07', 'price': 2100.0, 'merchantId': 16623}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13994360, 'date': '2026-03-31', 'price': 2099.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-01', 'price': 2099.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-02', 'price': 2099.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-03', 'price': 2099.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-04', 'price': 2099.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-05', 'price': 2099.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-06', 'price': 2099.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-07', 'price': 2099.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-08', 'price': 2099.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-09', 'price': 2099.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-10', 'price': 2099.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-11', 'price': 2099.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-12', 'price': 2099.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-13', 'price': 2099.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-14', 'price': 1995.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-15', 'price': 1995.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-16', 'price': 1995.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-17', 'price': 1995.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-18', 'price': 1995.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-19', 'price': 1995.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-20', 'price': 1995.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-21', 'price': 1995.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-22', 'price': 1984.9999999999998, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-23', 'price': 1984.9999999999998, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-24', 'price': 1984.9999999999998, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-25', 'price': 1984.9999999999998, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-26', 'price': 1984.9999999999998, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-27', 'price': 1984.9999999999998, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-28', 'price': 1984.9999999999998, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-29', 'price': 1984.9999999999998, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-04-30', 'price': 1984.9999999999998, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-01', 'price': 1984.9999999999998, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-02', 'price': 1984.9999999999998, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-03', 'price': 1984.9999999999998, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-04', 'price': 1984.9999999999998, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-05', 'price': 1984.9999999999998, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-06', 'price': 1984.9999999999998, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-07', 'price': 1984.9999999999998, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-08', 'price': 1984.9999999999998, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-09', 'price': 1984.9999999999998, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-10', 'price': 1984.9999999999998, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-11', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-12', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-13', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-14', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-15', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-16', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-17', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-18', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-19', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-20', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-21', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-22', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-23', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-24', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-25', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-26', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-27', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-28', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-29', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-30', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-05-31', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-06-01', 'price': 1826.65, 'merchantId': 22905}, {'prodId': 13994360, 'date': '2026-06-02', 'price': 1984.9999999999998, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-06-03', 'price': 1954.15, 'merchantId': 22905}, {'prodId': 13994360, 'date': '2026-06-04', 'price': 1954.15, 'merchantId': 22905}, {'prodId': 13994360, 'date': '2026-06-05', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-06-06', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-06-07', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-06-08', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-06-09', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-06-10', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-06-11', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-06-12', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-06-13', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-06-14', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-06-15', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-06-16', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-06-17', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-06-18', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-06-19', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-06-20', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-06-21', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-06-22', 'price': 1899.0, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-06-23', 'price': 1878.99, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-06-24', 'price': 1878.99, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-06-25', 'price': 1878.99, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-06-26', 'price': 1878.99, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-06-27', 'price': 1878.99, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-06-28', 'price': 1878.99, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-06-29', 'price': 1878.99, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-06-30', 'price': 1878.99, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-07-01', 'price': 1878.99, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-07-02', 'price': 1977.89, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-07-03', 'price': 1977.89, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-07-04', 'price': 1977.89, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-07-05', 'price': 1977.89, 'merchantId': 16623}, {'prodId': 13994360, 'date': '2026-07-06', 'price': 1954.15, 'merchantId': 22905}, {'prodId': 13994360, 'date': '2026-07-07', 'price': 1954.15, 'merchantId': 22905}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13645640, 'date': '2025-07-07', 'price': 1118.0, 'merchantId': 15125}, {'prodId': 13645640, 'date': '2025-07-08', 'price': 1110.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-07-09', 'price': 1089.09, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-07-10', 'price': 1077.09, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-07-11', 'price': 1077.09, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-07-12', 'price': 1073.09, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-07-13', 'price': 1093.01, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-07-14', 'price': 1077.09, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-07-15', 'price': 1073.09, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-07-16', 'price': 1080.4, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-07-17', 'price': 1094.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-07-18', 'price': 1094.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-07-19', 'price': 1128.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-07-20', 'price': 1128.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-07-21', 'price': 1120.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-07-22', 'price': 1105.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-07-23', 'price': 1105.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-07-24', 'price': 1090.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-07-25', 'price': 1090.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-07-26', 'price': 1090.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-07-27', 'price': 1090.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-07-28', 'price': 1090.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-07-29', 'price': 1090.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-07-30', 'price': 1068.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-07-31', 'price': 1063.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-08-01', 'price': 1063.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-08-02', 'price': 1063.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-08-03', 'price': 1065.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-08-04', 'price': 1068.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-08-05', 'price': 1060.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-08-06', 'price': 1060.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-08-07', 'price': 1072.55, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-08-08', 'price': 1072.55, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-08-09', 'price': 1072.55, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-08-10', 'price': 1072.55, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-08-11', 'price': 1072.55, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-08-12', 'price': 1070.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-08-13', 'price': 1092.5, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-08-14', 'price': 1092.5, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-08-15', 'price': 1092.5, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-08-16', 'price': 1092.5, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-08-17', 'price': 1092.5, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-08-18', 'price': 1090.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-08-19', 'price': 1067.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-08-20', 'price': 1051.69, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-08-21', 'price': 988.49, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-08-22', 'price': 988.49, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-08-23', 'price': 1073.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-08-24', 'price': 1065.69, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-08-25', 'price': 988.49, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-08-26', 'price': 1058.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-08-27', 'price': 1050.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-08-28', 'price': 1049.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-08-29', 'price': 1045.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-08-30', 'price': 1045.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-08-31', 'price': 1045.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-09-01', 'price': 1045.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-09-02', 'price': 1046.01, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-09-03', 'price': 1036.69, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-09-04', 'price': 1059.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-09-05', 'price': 1035.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-09-06', 'price': 1035.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-09-07', 'price': 1039.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-09-08', 'price': 1035.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-09-09', 'price': 1035.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-09-10', 'price': 1021.69, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-09-11', 'price': 1035.5, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-09-12', 'price': 1021.69, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-09-13', 'price': 1035.5, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-09-14', 'price': 1034.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-09-15', 'price': 1021.69, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-09-16', 'price': 1020.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-09-17', 'price': 1020.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-09-18', 'price': 1013.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-09-19', 'price': 1015.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-09-20', 'price': 1005.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-09-21', 'price': 1005.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-09-22', 'price': 1015.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-09-23', 'price': 1018.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-09-24', 'price': 1000.64, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-09-25', 'price': 1000.64, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-09-26', 'price': 1000.64, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-09-27', 'price': 1000.64, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-09-28', 'price': 1000.64, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-09-29', 'price': 995.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-09-30', 'price': 995.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-10-01', 'price': 1007.9999999999999, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-10-02', 'price': 1002.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-10-03', 'price': 1007.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-10-04', 'price': 1007.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-10-05', 'price': 1007.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-10-06', 'price': 1007.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-10-07', 'price': 1002.9, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-10-08', 'price': 1003.96, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-10-09', 'price': 1007.19, 'merchantId': 15125}, {'prodId': 13645640, 'date': '2025-10-10', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-10-11', 'price': 1005.44, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-10-12', 'price': 1005.44, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-10-13', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-10-14', 'price': 1019.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-10-15', 'price': 1016.95, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-10-16', 'price': 1011.96, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-10-17', 'price': 1007.9999999999999, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-10-18', 'price': 1007.9999999999999, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-10-19', 'price': 1007.9999999999999, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-10-20', 'price': 1007.9999999999999, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-10-21', 'price': 1007.9999999999999, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-10-22', 'price': 1007.9999999999999, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-10-23', 'price': 1009.0, 'merchantId': 15125}, {'prodId': 13645640, 'date': '2025-10-24', 'price': 1025.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-10-25', 'price': 1025.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-10-26', 'price': 1025.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-10-27', 'price': 1025.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-10-28', 'price': 1025.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-10-29', 'price': 1023.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-10-30', 'price': 1015.0000000000001, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-10-31', 'price': 1015.0000000000001, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-11-01', 'price': 1015.0000000000001, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-11-02', 'price': 1015.0000000000001, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-11-03', 'price': 1015.0000000000001, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-11-04', 'price': 1020.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-11-05', 'price': 1017.91, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-11-06', 'price': 1022.95, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-11-07', 'price': 1014.48, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2025-11-08', 'price': 1025.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-11-09', 'price': 1025.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-11-10', 'price': 1020.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-11-11', 'price': 1020.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-11-12', 'price': 1025.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-11-13', 'price': 1025.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-11-14', 'price': 1017.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-11-15', 'price': 1025.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-11-16', 'price': 1025.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-11-17', 'price': 1017.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-11-18', 'price': 1025.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-11-19', 'price': 1021.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-11-20', 'price': 1021.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-11-21', 'price': 1025.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-11-22', 'price': 1025.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-11-23', 'price': 1025.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-11-24', 'price': 1025.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-11-25', 'price': 1025.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-11-26', 'price': 1025.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-11-27', 'price': 1025.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-11-28', 'price': 1025.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-11-29', 'price': 1025.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-11-30', 'price': 1025.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-12-01', 'price': 1025.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-12-02', 'price': 1025.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-12-03', 'price': 1049.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-12-04', 'price': 1049.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-12-05', 'price': 1088.1, 'merchantId': 15125}, {'prodId': 13645640, 'date': '2025-12-06', 'price': 1088.1, 'merchantId': 15125}, {'prodId': 13645640, 'date': '2025-12-07', 'price': 1088.1, 'merchantId': 15125}, {'prodId': 13645640, 'date': '2025-12-08', 'price': 1068.9, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-12-09', 'price': 1093.64, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-12-10', 'price': 1080.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-12-11', 'price': 1080.64, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2025-12-12', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2025-12-13', 'price': 1059.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-12-14', 'price': 1059.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-12-15', 'price': 1059.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-12-16', 'price': 1059.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2025-12-17', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2025-12-18', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2025-12-19', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2025-12-20', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2025-12-21', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2025-12-22', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2025-12-23', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2025-12-24', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2025-12-25', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2025-12-26', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2025-12-27', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2025-12-28', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2025-12-29', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2025-12-30', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2025-12-31', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-01-01', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-01-02', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-01-03', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-01-04', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-01-05', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-01-06', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-01-07', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-01-08', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-01-09', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-01-10', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-01-11', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-01-12', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-01-13', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-01-14', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-01-15', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-01-16', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-01-17', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-01-18', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-01-19', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-01-20', 'price': 1070.31, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-01-21', 'price': 1166.55, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-01-22', 'price': 2117.22, 'merchantId': 20609}, {'prodId': 13645640, 'date': '2026-01-23', 'price': 2117.22, 'merchantId': 20609}, {'prodId': 13645640, 'date': '2026-01-24', 'price': 2117.22, 'merchantId': 20612}, {'prodId': 13645640, 'date': '2026-01-25', 'price': 2117.22, 'merchantId': 20612}, {'prodId': 13645640, 'date': '2026-01-26', 'price': 2117.22, 'merchantId': 20612}, {'prodId': 13645640, 'date': '2026-01-27', 'price': 2117.22, 'merchantId': 20612}, {'prodId': 13645640, 'date': '2026-01-28', 'price': 1239.99, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-01-29', 'price': 1220.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-01-30', 'price': 1220.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-01-31', 'price': 1227.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-02-01', 'price': 1227.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-02-02', 'price': 1227.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-02-03', 'price': 1227.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-02-04', 'price': 1227.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-02-05', 'price': 1227.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-02-06', 'price': 1227.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-02-07', 'price': 1227.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-02-08', 'price': 1227.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-02-09', 'price': 1227.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-02-10', 'price': 1227.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-02-11', 'price': 1199.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-02-12', 'price': 1199.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-02-13', 'price': 1199.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-02-14', 'price': 1167.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-02-15', 'price': 1167.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-02-16', 'price': 1167.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-02-17', 'price': 1119.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-02-18', 'price': 1199.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-02-19', 'price': 1199.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-02-20', 'price': 1190.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-02-21', 'price': 1180.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-02-22', 'price': 1150.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-02-23', 'price': 1175.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-02-24', 'price': 1169.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-02-25', 'price': 1162.5, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-02-26', 'price': 1162.5, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-02-27', 'price': 1159.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-02-28', 'price': 1151.54, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-03-01', 'price': 1151.54, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-03-02', 'price': 1159.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-03-03', 'price': 1159.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-03-04', 'price': 1150.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-03-05', 'price': 1135.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-03-06', 'price': 1135.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-03-07', 'price': 1135.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-03-08', 'price': 1135.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-03-09', 'price': 1098.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-03-10', 'price': 1098.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-03-11', 'price': 1098.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-03-12', 'price': 1098.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-03-13', 'price': 1089.0, 'merchantId': 15125}, {'prodId': 13645640, 'date': '2026-03-14', 'price': 1089.0, 'merchantId': 15125}, {'prodId': 13645640, 'date': '2026-03-15', 'price': 1089.0, 'merchantId': 15125}, {'prodId': 13645640, 'date': '2026-03-16', 'price': 1089.0, 'merchantId': 15125}, {'prodId': 13645640, 'date': '2026-03-17', 'price': 1089.0, 'merchantId': 15125}, {'prodId': 13645640, 'date': '2026-03-18', 'price': 1089.0, 'merchantId': 15125}, {'prodId': 13645640, 'date': '2026-03-19', 'price': 1089.0, 'merchantId': 15125}, {'prodId': 13645640, 'date': '2026-03-20', 'price': 1089.0, 'merchantId': 15125}, {'prodId': 13645640, 'date': '2026-03-21', 'price': 1089.0, 'merchantId': 15125}, {'prodId': 13645640, 'date': '2026-03-22', 'price': 1089.0, 'merchantId': 15125}, {'prodId': 13645640, 'date': '2026-03-23', 'price': 1098.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-03-24', 'price': 1098.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-03-25', 'price': 1145.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-03-26', 'price': 1145.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-03-27', 'price': 1145.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-03-28', 'price': 1143.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-03-29', 'price': 1143.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-03-30', 'price': 1142.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-03-31', 'price': 1142.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-04-01', 'price': 1142.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-04-02', 'price': 1142.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-04-03', 'price': 1149.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-04-04', 'price': 1149.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-04-05', 'price': 1149.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-04-06', 'price': 1145.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-04-07', 'price': 1145.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-04-08', 'price': 1148.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-04-09', 'price': 1135.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-04-10', 'price': 1135.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-04-11', 'price': 1129.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-04-12', 'price': 1129.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-04-13', 'price': 1130.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-04-14', 'price': 1135.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-04-15', 'price': 1135.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-04-16', 'price': 1131.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-04-17', 'price': 1133.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-04-18', 'price': 1129.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-04-19', 'price': 1119.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-04-20', 'price': 1131.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-04-21', 'price': 1131.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-04-22', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-04-23', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-04-24', 'price': 1087.91, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-04-25', 'price': 1087.91, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-04-26', 'price': 1087.91, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-04-27', 'price': 1087.91, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-04-28', 'price': 1087.91, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-04-29', 'price': 1060.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-04-30', 'price': 1060.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-05-01', 'price': 1087.91, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-05-02', 'price': 1087.91, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-05-03', 'price': 1087.91, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-05-04', 'price': 1087.91, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-05-05', 'price': 1069.55, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-05-06', 'price': 1069.55, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-05-07', 'price': 1069.55, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-05-08', 'price': 1069.55, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-05-09', 'price': 1104.15, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-05-10', 'price': 1104.15, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-05-11', 'price': 1104.15, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-05-12', 'price': 1104.15, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-05-13', 'price': 1104.15, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-05-14', 'price': 1104.15, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-05-15', 'price': 1104.15, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-05-16', 'price': 1104.15, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-05-17', 'price': 1104.15, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-05-18', 'price': 1096.47, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-05-19', 'price': 1096.47, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-05-20', 'price': 1096.47, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-05-21', 'price': 1096.47, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-05-22', 'price': 1096.47, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-05-23', 'price': 1099.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-05-24', 'price': 1099.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-05-25', 'price': 1099.0, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-05-26', 'price': 1099.99, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-05-27', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-05-28', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-05-29', 'price': 1118.55, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-05-30', 'price': 1118.55, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-05-31', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-06-01', 'price': 1104.15, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-06-02', 'price': 1118.55, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-06-03', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-06-04', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-06-05', 'price': 959.98, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-06-06', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-06-07', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-06-08', 'price': 1063.51, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-06-09', 'price': 1063.51, 'merchantId': 22905}, {'prodId': 13645640, 'date': '2026-06-10', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-06-11', 'price': 1029.0, 'merchantId': 1582}, {'prodId': 13645640, 'date': '2026-06-12', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-06-13', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-06-14', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-06-15', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-06-16', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-06-17', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-06-18', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-06-19', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-06-20', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-06-21', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-06-22', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-06-23', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-06-24', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-06-25', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-06-26', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-06-27', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-06-28', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-06-29', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-06-30', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-07-01', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-07-02', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-07-03', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-07-04', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-07-05', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-07-06', 'price': 1118.99, 'merchantId': 16623}, {'prodId': 13645640, 'date': '2026-07-07', 'price': 1118.99, 'merchantId': 16623}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13340173, 'date': '2025-07-07', 'price': 1028.0, 'merchantId': 34}, {'prodId': 13340173, 'date': '2025-07-08', 'price': 1029.0, 'merchantId': 20583}, {'prodId': 13340173, 'date': '2025-07-09', 'price': 1070.0, 'merchantId': 34}, {'prodId': 13340173, 'date': '2025-07-10', 'price': 1029.0, 'merchantId': 34}, {'prodId': 13340173, 'date': '2025-07-11', 'price': 1029.0, 'merchantId': 34}, {'prodId': 13340173, 'date': '2025-07-12', 'price': 1014.26, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2025-07-13', 'price': 1029.0, 'merchantId': 34}, {'prodId': 13340173, 'date': '2025-07-14', 'price': 1029.0, 'merchantId': 34}, {'prodId': 13340173, 'date': '2025-07-15', 'price': 800.0, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2025-07-16', 'price': 1029.0, 'merchantId': 34}, {'prodId': 13340173, 'date': '2025-07-17', 'price': 970.89, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-07-18', 'price': 970.89, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-07-19', 'price': 1015.0, 'merchantId': 34}, {'prodId': 13340173, 'date': '2025-07-20', 'price': 1015.0, 'merchantId': 34}, {'prodId': 13340173, 'date': '2025-07-21', 'price': 961.51, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-07-22', 'price': 999.0, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2025-07-23', 'price': 999.0, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2025-07-24', 'price': 999.0, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2025-07-25', 'price': 999.0, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2025-07-26', 'price': 917.24, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-07-27', 'price': 1017.82, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2025-07-28', 'price': 989.0, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2025-07-29', 'price': 989.0, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2025-07-30', 'price': 989.0, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2025-07-31', 'price': 989.0, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2025-08-01', 'price': 863.2, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2025-08-02', 'price': 998.0, 'merchantId': 34}, {'prodId': 13340173, 'date': '2025-08-03', 'price': 998.0, 'merchantId': 34}, {'prodId': 13340173, 'date': '2025-08-04', 'price': 998.0, 'merchantId': 34}, {'prodId': 13340173, 'date': '2025-08-05', 'price': 999.0, 'merchantId': 34}, {'prodId': 13340173, 'date': '2025-08-06', 'price': 999.0, 'merchantId': 34}, {'prodId': 13340173, 'date': '2025-08-07', 'price': 999.0, 'merchantId': 34}, {'prodId': 13340173, 'date': '2025-08-08', 'price': 800.11, 'merchantId': 20583}, {'prodId': 13340173, 'date': '2025-08-09', 'price': 987.01, 'merchantId': 20612}, {'prodId': 13340173, 'date': '2025-08-10', 'price': 987.01, 'merchantId': 20612}, {'prodId': 13340173, 'date': '2025-08-11', 'price': 987.01, 'merchantId': 20612}, {'prodId': 13340173, 'date': '2025-08-12', 'price': 987.01, 'merchantId': 20612}, {'prodId': 13340173, 'date': '2025-08-13', 'price': 987.01, 'merchantId': 20612}, {'prodId': 13340173, 'date': '2025-08-14', 'price': 987.01, 'merchantId': 20612}, {'prodId': 13340173, 'date': '2025-08-15', 'price': 987.01, 'merchantId': 20612}, {'prodId': 13340173, 'date': '2025-08-16', 'price': 987.01, 'merchantId': 20612}, {'prodId': 13340173, 'date': '2025-08-17', 'price': 987.01, 'merchantId': 20612}, {'prodId': 13340173, 'date': '2025-08-18', 'price': 987.01, 'merchantId': 20612}, {'prodId': 13340173, 'date': '2025-08-19', 'price': 987.01, 'merchantId': 20612}, {'prodId': 13340173, 'date': '2025-08-20', 'price': 989.0, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2025-08-21', 'price': 979.9, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2025-08-22', 'price': 989.0, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2025-08-23', 'price': 989.1, 'merchantId': 34}, {'prodId': 13340173, 'date': '2025-08-24', 'price': 989.1, 'merchantId': 34}, {'prodId': 13340173, 'date': '2025-08-25', 'price': 989.0, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2025-08-26', 'price': 1014.48, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2025-08-27', 'price': 929.0, 'merchantId': 22902}, {'prodId': 13340173, 'date': '2025-08-28', 'price': 929.0, 'merchantId': 22902}, {'prodId': 13340173, 'date': '2025-08-29', 'price': 999.99, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2025-08-30', 'price': 989.1, 'merchantId': 23254}, {'prodId': 13340173, 'date': '2025-08-31', 'price': 999.99, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2025-09-01', 'price': 929.9, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2025-09-02', 'price': 929.9, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2025-09-03', 'price': 929.9, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2025-09-04', 'price': 929.9, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2025-09-05', 'price': 929.9, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2025-09-06', 'price': 929.9, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2025-09-07', 'price': 890.1, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-09-08', 'price': 890.1, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-09-09', 'price': 890.1, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-09-10', 'price': 928.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2025-09-11', 'price': 928.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2025-09-12', 'price': 928.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2025-09-13', 'price': 988.2, 'merchantId': 34}, {'prodId': 13340173, 'date': '2025-09-14', 'price': 988.2, 'merchantId': 34}, {'prodId': 13340173, 'date': '2025-09-15', 'price': 934.92, 'merchantId': 20609}, {'prodId': 13340173, 'date': '2025-09-16', 'price': 928.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2025-09-17', 'price': 805.01, 'merchantId': 22902}, {'prodId': 13340173, 'date': '2025-09-18', 'price': 805.01, 'merchantId': 22902}, {'prodId': 13340173, 'date': '2025-09-19', 'price': 805.01, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2025-09-20', 'price': 805.01, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2025-09-21', 'price': 805.01, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2025-09-22', 'price': 805.01, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2025-09-23', 'price': 805.01, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2025-09-24', 'price': 805.01, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2025-09-25', 'price': 805.01, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2025-09-26', 'price': 805.01, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2025-09-27', 'price': 805.01, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2025-09-28', 'price': 805.01, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2025-09-29', 'price': 805.01, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2025-09-30', 'price': 805.01, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2025-10-01', 'price': 902.61, 'merchantId': 22902}, {'prodId': 13340173, 'date': '2025-10-02', 'price': 902.61, 'merchantId': 22902}, {'prodId': 13340173, 'date': '2025-10-03', 'price': 902.61, 'merchantId': 22902}, {'prodId': 13340173, 'date': '2025-10-04', 'price': 902.61, 'merchantId': 22902}, {'prodId': 13340173, 'date': '2025-10-05', 'price': 899.1, 'merchantId': 22902}, {'prodId': 13340173, 'date': '2025-10-06', 'price': 899.1, 'merchantId': 22902}, {'prodId': 13340173, 'date': '2025-10-07', 'price': 899.1, 'merchantId': 22902}, {'prodId': 13340173, 'date': '2025-10-08', 'price': 899.1, 'merchantId': 22902}, {'prodId': 13340173, 'date': '2025-10-09', 'price': 899.1, 'merchantId': 22902}, {'prodId': 13340173, 'date': '2025-10-10', 'price': 872.1, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2025-10-11', 'price': 872.1, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2025-10-12', 'price': 872.1, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2025-10-13', 'price': 872.09, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-10-14', 'price': 798.48, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-10-15', 'price': 798.48, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-10-16', 'price': 829.19, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-10-17', 'price': 829.19, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-10-18', 'price': 829.19, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-10-19', 'price': 829.19, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-10-20', 'price': 829.19, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-10-21', 'price': 829.19, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-10-22', 'price': 852.72, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-10-23', 'price': 846.73, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2025-10-24', 'price': 846.73, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2025-10-25', 'price': 898.9, 'merchantId': 20583}, {'prodId': 13340173, 'date': '2025-10-26', 'price': 898.9, 'merchantId': 20583}, {'prodId': 13340173, 'date': '2025-10-27', 'price': 890.1, 'merchantId': 23254}, {'prodId': 13340173, 'date': '2025-10-28', 'price': 890.1, 'merchantId': 23254}, {'prodId': 13340173, 'date': '2025-10-29', 'price': 849.0, 'merchantId': 34}, {'prodId': 13340173, 'date': '2025-10-30', 'price': 849.0, 'merchantId': 34}, {'prodId': 13340173, 'date': '2025-10-31', 'price': 871.2, 'merchantId': 23254}, {'prodId': 13340173, 'date': '2025-11-01', 'price': 859.0, 'merchantId': 22902}, {'prodId': 13340173, 'date': '2025-11-02', 'price': 859.0, 'merchantId': 22902}, {'prodId': 13340173, 'date': '2025-11-03', 'price': 854.1, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2025-11-04', 'price': 839.9, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-11-05', 'price': 839.9, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-11-06', 'price': 839.9, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-11-07', 'price': 839.87, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-11-08', 'price': 839.87, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-11-09', 'price': 839.87, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2025-11-10', 'price': 839.87, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2025-11-11', 'price': 835.12, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2025-11-12', 'price': 835.12, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2025-11-13', 'price': 835.12, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2025-11-14', 'price': 839.83, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2025-11-15', 'price': 791.12, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2025-11-16', 'price': 791.12, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2025-11-17', 'price': 791.12, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2025-11-18', 'price': 791.12, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2025-11-19', 'price': 835.08, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-11-20', 'price': 858.99, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2025-11-21', 'price': 854.06, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-11-22', 'price': 854.06, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-11-23', 'price': 854.06, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-11-24', 'price': 854.06, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-11-25', 'price': 809.1, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-11-26', 'price': 809.02, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2025-11-27', 'price': 809.02, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-11-28', 'price': 798.33, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-11-29', 'price': 798.33, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-11-30', 'price': 811.29, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-12-01', 'price': 811.29, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-12-02', 'price': 798.34, 'merchantId': 23254}, {'prodId': 13340173, 'date': '2025-12-03', 'price': 811.3, 'merchantId': 22902}, {'prodId': 13340173, 'date': '2025-12-04', 'price': 854.1, 'merchantId': 22902}, {'prodId': 13340173, 'date': '2025-12-05', 'price': 899.1, 'merchantId': 20583}, {'prodId': 13340173, 'date': '2025-12-06', 'price': 899.1, 'merchantId': 20583}, {'prodId': 13340173, 'date': '2025-12-07', 'price': 899.1, 'merchantId': 20583}, {'prodId': 13340173, 'date': '2025-12-08', 'price': 899.1, 'merchantId': 20583}, {'prodId': 13340173, 'date': '2025-12-09', 'price': 899.1, 'merchantId': 20583}, {'prodId': 13340173, 'date': '2025-12-10', 'price': 899.1, 'merchantId': 20583}, {'prodId': 13340173, 'date': '2025-12-11', 'price': 899.0, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-12-12', 'price': 899.0, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-12-13', 'price': 899.1, 'merchantId': 20583}, {'prodId': 13340173, 'date': '2025-12-14', 'price': 899.1, 'merchantId': 22902}, {'prodId': 13340173, 'date': '2025-12-15', 'price': 899.1, 'merchantId': 22902}, {'prodId': 13340173, 'date': '2025-12-16', 'price': 899.1, 'merchantId': 22902}, {'prodId': 13340173, 'date': '2025-12-17', 'price': 899.1, 'merchantId': 22902}, {'prodId': 13340173, 'date': '2025-12-18', 'price': 869.13, 'merchantId': 20583}, {'prodId': 13340173, 'date': '2025-12-19', 'price': 869.13, 'merchantId': 20583}, {'prodId': 13340173, 'date': '2025-12-20', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2025-12-21', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2025-12-22', 'price': 892.8, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2025-12-23', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2025-12-24', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2025-12-25', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2025-12-26', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2025-12-27', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2025-12-28', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2025-12-29', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2025-12-30', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2025-12-31', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-01-01', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-01-02', 'price': 879.9, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2026-01-03', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-01-04', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-01-05', 'price': 879.9, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2026-01-06', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-01-07', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-01-08', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-01-09', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-01-10', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-01-11', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-01-12', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-01-13', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-01-14', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-01-15', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-01-16', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-01-17', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-01-18', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-01-19', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-01-20', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-01-21', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-01-22', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-01-23', 'price': 879.9, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2026-01-24', 'price': 879.9, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2026-01-25', 'price': 879.9, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2026-01-26', 'price': 879.9, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2026-01-27', 'price': 879.9, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2026-01-28', 'price': 879.9, 'merchantId': 1582}, {'prodId': 13340173, 'date': '2026-01-29', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-01-30', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-01-31', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-02-01', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-02-02', 'price': 879.12, 'merchantId': 23326}, {'prodId': 13340173, 'date': '2026-02-03', 'price': 879.12, 'merchantId': 23326}, {'prodId': 13340173, 'date': '2026-02-04', 'price': 879.12, 'merchantId': 23326}, {'prodId': 13340173, 'date': '2026-02-05', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-02-06', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-02-07', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-02-08', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-02-09', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-02-10', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-02-11', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-02-12', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-02-13', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-02-14', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-02-15', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-02-16', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-02-17', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-02-18', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-02-19', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-02-20', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-02-21', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-02-22', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-02-23', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-02-24', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-02-25', 'price': 879.9, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2026-02-26', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-02-27', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-02-28', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-03-01', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-03-02', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-03-03', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-03-04', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-03-05', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-03-06', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-03-07', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-03-08', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-03-09', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-03-10', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-03-11', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-03-12', 'price': 879.9, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2026-03-13', 'price': 879.9, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2026-03-14', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-03-15', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-03-16', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-03-17', 'price': 870.32, 'merchantId': 23326}, {'prodId': 13340173, 'date': '2026-03-18', 'price': 870.32, 'merchantId': 23326}, {'prodId': 13340173, 'date': '2026-03-19', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-03-20', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-03-21', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-03-22', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-03-23', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-03-24', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-03-25', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-03-26', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-03-27', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-03-28', 'price': 899.0, 'merchantId': 20612}, {'prodId': 13340173, 'date': '2026-03-29', 'price': 899.0, 'merchantId': 20612}, {'prodId': 13340173, 'date': '2026-03-30', 'price': 899.0, 'merchantId': 20583}, {'prodId': 13340173, 'date': '2026-03-31', 'price': 899.0, 'merchantId': 20583}, {'prodId': 13340173, 'date': '2026-04-01', 'price': 849.0, 'merchantId': 22902}, {'prodId': 13340173, 'date': '2026-04-02', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-04-03', 'price': 899.1, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-04-04', 'price': 989.1, 'merchantId': 34}, {'prodId': 13340173, 'date': '2026-04-05', 'price': 989.1, 'merchantId': 34}, {'prodId': 13340173, 'date': '2026-04-06', 'price': 979.0, 'merchantId': 34}, {'prodId': 13340173, 'date': '2026-04-07', 'price': 978.0, 'merchantId': 34}, {'prodId': 13340173, 'date': '2026-04-08', 'price': 976.0, 'merchantId': 34}, {'prodId': 13340173, 'date': '2026-04-09', 'price': 975.89, 'merchantId': 34}, {'prodId': 13340173, 'date': '2026-04-10', 'price': 975.0, 'merchantId': 34}, {'prodId': 13340173, 'date': '2026-04-11', 'price': 953.33, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-04-12', 'price': 953.33, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-04-13', 'price': 953.33, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-04-14', 'price': 879.02, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-04-15', 'price': 879.02, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-04-16', 'price': 879.02, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-04-17', 'price': 879.02, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-04-18', 'price': 899.0, 'merchantId': 20609}, {'prodId': 13340173, 'date': '2026-04-19', 'price': 899.0, 'merchantId': 20609}, {'prodId': 13340173, 'date': '2026-04-20', 'price': 899.0, 'merchantId': 20609}, {'prodId': 13340173, 'date': '2026-04-21', 'price': 899.0, 'merchantId': 20609}, {'prodId': 13340173, 'date': '2026-04-22', 'price': 850.93, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2026-04-23', 'price': 856.93, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2026-04-24', 'price': 949.0, 'merchantId': 20609}, {'prodId': 13340173, 'date': '2026-04-25', 'price': 959.0, 'merchantId': 20609}, {'prodId': 13340173, 'date': '2026-04-26', 'price': 959.0, 'merchantId': 20609}, {'prodId': 13340173, 'date': '2026-04-27', 'price': 959.0, 'merchantId': 20609}, {'prodId': 13340173, 'date': '2026-04-28', 'price': 942.3, 'merchantId': 23326}, {'prodId': 13340173, 'date': '2026-04-29', 'price': 1075.0, 'merchantId': 34}, {'prodId': 13340173, 'date': '2026-04-30', 'price': 899.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-05-01', 'price': 899.0, 'merchantId': 22902}, {'prodId': 13340173, 'date': '2026-05-02', 'price': 899.0, 'merchantId': 22902}, {'prodId': 13340173, 'date': '2026-05-03', 'price': 948.95, 'merchantId': 2584}, {'prodId': 13340173, 'date': '2026-05-04', 'price': 849.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-05-05', 'price': 849.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-05-06', 'price': 849.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-05-07', 'price': 888.99, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-05-08', 'price': 809.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-05-09', 'price': 809.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-05-10', 'price': 809.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-05-11', 'price': 809.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-05-12', 'price': 809.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-05-13', 'price': 809.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-05-14', 'price': 809.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-05-15', 'price': 809.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-05-16', 'price': 809.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-05-17', 'price': 809.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-05-18', 'price': 809.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-05-19', 'price': 899.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-05-20', 'price': 899.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-05-21', 'price': 899.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-05-22', 'price': 899.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-05-23', 'price': 899.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-05-24', 'price': 899.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-05-25', 'price': 899.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-05-26', 'price': 899.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-05-27', 'price': 899.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-05-28', 'price': 899.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-05-29', 'price': 899.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-05-30', 'price': 899.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-05-31', 'price': 899.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-06-01', 'price': 899.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-06-02', 'price': 899.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-06-03', 'price': 899.0, 'merchantId': 16108}, {'prodId': 13340173, 'date': '2026-06-04', 'price': 943.5, 'merchantId': 22905}, {'prodId': 13340173, 'date': '2026-06-05', 'price': 929.9, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2026-06-06', 'price': 1050.15, 'merchantId': 23326}, {'prodId': 13340173, 'date': '2026-06-07', 'price': 1050.15, 'merchantId': 23326}, {'prodId': 13340173, 'date': '2026-06-08', 'price': 979.9, 'merchantId': 9385}, {'prodId': 13340173, 'date': '2026-06-09', 'price': 976.8, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-06-10', 'price': 1060.9, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-06-11', 'price': 1060.9, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-06-12', 'price': 975.25, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-06-13', 'price': 975.25, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-06-14', 'price': 975.25, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-06-15', 'price': 975.25, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-06-16', 'price': 1033.3, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-06-17', 'price': 1003.2, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-06-18', 'price': 1003.2, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-06-19', 'price': 1002.15, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-06-20', 'price': 999.47, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-06-21', 'price': 999.47, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-06-22', 'price': 999.47, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-06-23', 'price': 998.52, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-06-24', 'price': 997.57, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-06-25', 'price': 997.57, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-06-26', 'price': 1033.06, 'merchantId': 23326}, {'prodId': 13340173, 'date': '2026-06-27', 'price': 997.48, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-06-28', 'price': 997.48, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-06-29', 'price': 997.48, 'merchantId': 245}, {'prodId': 13340173, 'date': '2026-06-30', 'price': 1033.06, 'merchantId': 23326}, {'prodId': 13340173, 'date': '2026-07-01', 'price': 1019.15, 'merchantId': 23276}, {'prodId': 13340173, 'date': '2026-07-02', 'price': 1019.15, 'merchantId': 23276}, {'prodId': 13340173, 'date': '2026-07-03', 'price': 1019.15, 'merchantId': 23276}, {'prodId': 13340173, 'date': '2026-07-04', 'price': 1019.15, 'merchantId': 23276}, {'prodId': 13340173, 'date': '2026-07-05', 'price': 1019.15, 'merchantId': 23276}, {'prodId': 13340173, 'date': '2026-07-06', 'price': 1019.15, 'merchantId': 23276}, {'prodId': 13340173, 'date': '2026-07-07', 'price': 1019.15, 'merchantId': 23276}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 12481790, 'date': '2025-07-15', 'price': 7998.99, 'merchantId': 22902}, {'prodId': 12481790, 'date': '2025-07-16', 'price': 7998.99, 'merchantId': 22902}, {'prodId': 12481790, 'date': '2025-07-17', 'price': 7998.99, 'merchantId': 22902}, {'prodId': 12481790, 'date': '2025-07-18', 'price': 7998.99, 'merchantId': 22902}, {'prodId': 12481790, 'date': '2025-07-19', 'price': 7998.99, 'merchantId': 22902}, {'prodId': 12481790, 'date': '2025-07-20', 'price': 7998.99, 'merchantId': 22902}, {'prodId': 12481790, 'date': '2025-07-21', 'price': 7998.99, 'merchantId': 22902}, {'prodId': 12481790, 'date': '2025-07-22', 'price': 7998.99, 'merchantId': 22902}, {'prodId': 12481790, 'date': '2025-07-23', 'price': 7998.99, 'merchantId': 22902}, {'prodId': 12481790, 'date': '2025-07-24', 'price': 7998.99, 'merchantId': 22902}, {'prodId': 12481790, 'date': '2025-07-25', 'price': 7998.99, 'merchantId': 22902}, {'prodId': 12481790, 'date': '2025-07-26', 'price': 7998.99, 'merchantId': 22902}, {'prodId': 12481790, 'date': '2025-07-27', 'price': 7998.99, 'merchantId': 22902}, {'prodId': 12481790, 'date': '2025-07-28', 'price': 7998.99, 'merchantId': 22902}, {'prodId': 12481790, 'date': '2025-07-29', 'price': 7998.99, 'merchantId': 22902}, {'prodId': 12481790, 'date': '2025-07-30', 'price': 7998.99, 'merchantId': 22902}, {'prodId': 12481790, 'date': '2025-11-13', 'price': 5139.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-11-14', 'price': 5139.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-11-15', 'price': 5139.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-11-16', 'price': 5139.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-11-17', 'price': 5139.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-11-18', 'price': 5139.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-11-19', 'price': 4879.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-11-20', 'price': 4879.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-11-21', 'price': 4879.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-11-22', 'price': 4879.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-11-23', 'price': 4879.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-11-24', 'price': 4879.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-11-25', 'price': 4879.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-11-26', 'price': 4750.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-11-27', 'price': 4750.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-11-28', 'price': 4499.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-11-29', 'price': 4269.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-11-30', 'price': 4269.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-01', 'price': 4269.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-02', 'price': 4269.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-03', 'price': 4269.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-04', 'price': 4650.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-05', 'price': 4650.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-06', 'price': 4650.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-07', 'price': 4269.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-08', 'price': 4269.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-09', 'price': 4650.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-10', 'price': 4650.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-11', 'price': 4650.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-12', 'price': 4650.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-13', 'price': 4650.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-14', 'price': 4650.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-15', 'price': 4650.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-16', 'price': 4650.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-17', 'price': 4650.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-18', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-19', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-20', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-21', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-22', 'price': 4650.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-23', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-24', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-25', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-26', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-27', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-28', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-29', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-30', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2025-12-31', 'price': 4650.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-01', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-02', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-03', 'price': 4650.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-04', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-05', 'price': 4650.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-06', 'price': 4650.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-07', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-10', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-11', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-12', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-13', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-14', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-15', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-16', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-17', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-18', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-19', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-20', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-21', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-22', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-23', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-24', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-25', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-26', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-27', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-28', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-29', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-30', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-01-31', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-02-01', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-02-02', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-02-03', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-02-04', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-02-05', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-02-06', 'price': 5059.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-03-09', 'price': 4633.97, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-03-10', 'price': 4633.97, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-03-11', 'price': 4633.97, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-03-12', 'price': 4633.97, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-03-13', 'price': 4633.97, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-03-14', 'price': 4633.97, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-03-15', 'price': 4633.97, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-03-16', 'price': 4633.97, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-03-17', 'price': 4633.97, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-03-18', 'price': 4633.97, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-03-19', 'price': 4899.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-03-20', 'price': 4633.97, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-03-21', 'price': 4633.97, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-03-22', 'price': 4633.97, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-03-23', 'price': 4633.97, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-03-24', 'price': 4633.97, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-03-25', 'price': 4633.97, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-03-26', 'price': 4633.97, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-03-27', 'price': 4633.97, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-03-28', 'price': 4633.97, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-03-29', 'price': 4633.97, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-03-30', 'price': 4191.070000000001, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-03-31', 'price': 4191.070000000001, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-04-01', 'price': 4899.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-04-02', 'price': 4191.070000000001, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-04-03', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-04-04', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-04-05', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-04-06', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-04-10', 'price': 4191.07, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-04-11', 'price': 4191.07, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-04-12', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-04-13', 'price': 4191.07, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-04-14', 'price': 4191.07, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-04-15', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-04-16', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-04-17', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-04-18', 'price': 4507.99, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-04-19', 'price': 4507.99, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-04-20', 'price': 4507.99, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-04-21', 'price': 4507.99, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-04-22', 'price': 4069.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-04-23', 'price': 4069.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-04-24', 'price': 4191.07, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-04-25', 'price': 4191.07, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-04-26', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-04-27', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-04-28', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-04-29', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-04-30', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-01', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-02', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-03', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-04', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-05', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-06', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-07', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-08', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-09', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-10', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-11', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-12', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-13', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-14', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-15', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-16', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-17', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-18', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-19', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-20', 'price': 4507.99, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-21', 'price': 4507.99, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-22', 'price': 4507.99, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-23', 'price': 4551.57, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-24', 'price': 4551.57, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-25', 'price': 4551.57, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-26', 'price': 4551.57, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-27', 'price': 4639.0, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-28', 'price': 4583.99, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-29', 'price': 4627.62, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-30', 'price': 4627.62, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-05-31', 'price': 4627.62, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-01', 'price': 4501.57, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-02', 'price': 4501.57, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-03', 'price': 4501.57, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-04', 'price': 4503.69, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-05', 'price': 4218.99, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-06', 'price': 4218.99, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-07', 'price': 4218.99, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-08', 'price': 4218.99, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-09', 'price': 4218.99, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-10', 'price': 4218.99, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-11', 'price': 4218.99, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-12', 'price': 4218.99, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-13', 'price': 4218.99, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-14', 'price': 4218.99, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-15', 'price': 4157.61, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-16', 'price': 4157.61, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-17', 'price': 4157.61, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-18', 'price': 4157.61, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-19', 'price': 4157.61, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-20', 'price': 4157.61, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-21', 'price': 4157.61, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-22', 'price': 4157.61, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-23', 'price': 4157.61, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-24', 'price': 4109.99, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-25', 'price': 4109.99, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-26', 'price': 4109.99, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-27', 'price': 4109.99, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-28', 'price': 4109.99, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-29', 'price': 4008.04, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-06-30', 'price': 4008.04, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-07-01', 'price': 4008.04, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-07-02', 'price': 4008.04, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-07-03', 'price': 4008.04, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-07-04', 'price': 4008.04, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-07-05', 'price': 4008.04, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-07-06', 'price': 4008.04, 'merchantId': 1582}, {'prodId': 12481790, 'date': '2026-07-07', 'price': 4008.04, 'merchantId': 1582}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 12547997, 'date': '2025-07-07', 'price': 809.1, 'merchantId': 22902}, {'prodId': 12547997, 'date': '2025-07-08', 'price': 792.0, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-07-09', 'price': 792.0, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-07-10', 'price': 792.0, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-07-11', 'price': 792.0, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-07-12', 'price': 792.0, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-07-13', 'price': 792.0, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-07-14', 'price': 792.0, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-07-15', 'price': 792.0, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-07-16', 'price': 766.22, 'merchantId': 22905}, {'prodId': 12547997, 'date': '2025-07-17', 'price': 766.22, 'merchantId': 22905}, {'prodId': 12547997, 'date': '2025-07-18', 'price': 767.92, 'merchantId': 6911}, {'prodId': 12547997, 'date': '2025-07-19', 'price': 767.92, 'merchantId': 6911}, {'prodId': 12547997, 'date': '2025-07-20', 'price': 767.92, 'merchantId': 6911}, {'prodId': 12547997, 'date': '2025-07-21', 'price': 767.92, 'merchantId': 6911}, {'prodId': 12547997, 'date': '2025-07-22', 'price': 767.92, 'merchantId': 6911}, {'prodId': 12547997, 'date': '2025-07-23', 'price': 721.9, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-07-24', 'price': 721.9, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-07-25', 'price': 721.9, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-07-26', 'price': 721.9, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-07-27', 'price': 721.9, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-07-28', 'price': 721.9, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-07-29', 'price': 702.0, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-07-30', 'price': 764.1, 'merchantId': 16108}, {'prodId': 12547997, 'date': '2025-07-31', 'price': 764.1, 'merchantId': 16108}, {'prodId': 12547997, 'date': '2025-08-01', 'price': 730.0, 'merchantId': 34}, {'prodId': 12547997, 'date': '2025-08-02', 'price': 730.0, 'merchantId': 34}, {'prodId': 12547997, 'date': '2025-08-03', 'price': 730.0, 'merchantId': 34}, {'prodId': 12547997, 'date': '2025-08-04', 'price': 730.0, 'merchantId': 34}, {'prodId': 12547997, 'date': '2025-08-05', 'price': 730.0, 'merchantId': 34}, {'prodId': 12547997, 'date': '2025-08-06', 'price': 730.0, 'merchantId': 34}, {'prodId': 12547997, 'date': '2025-08-07', 'price': 730.0, 'merchantId': 34}, {'prodId': 12547997, 'date': '2025-08-08', 'price': 730.0, 'merchantId': 34}, {'prodId': 12547997, 'date': '2025-08-09', 'price': 730.0, 'merchantId': 34}, {'prodId': 12547997, 'date': '2025-08-10', 'price': 730.0, 'merchantId': 34}, {'prodId': 12547997, 'date': '2025-08-11', 'price': 730.0, 'merchantId': 34}, {'prodId': 12547997, 'date': '2025-08-12', 'price': 730.0, 'merchantId': 34}, {'prodId': 12547997, 'date': '2025-08-13', 'price': 730.0, 'merchantId': 34}, {'prodId': 12547997, 'date': '2025-08-14', 'price': 730.0, 'merchantId': 34}, {'prodId': 12547997, 'date': '2025-08-15', 'price': 730.0, 'merchantId': 34}, {'prodId': 12547997, 'date': '2025-08-16', 'price': 730.0, 'merchantId': 34}, {'prodId': 12547997, 'date': '2025-08-17', 'price': 730.0, 'merchantId': 34}, {'prodId': 12547997, 'date': '2025-08-18', 'price': 730.0, 'merchantId': 34}, {'prodId': 12547997, 'date': '2025-08-19', 'price': 730.0, 'merchantId': 34}, {'prodId': 12547997, 'date': '2025-08-20', 'price': 730.0, 'merchantId': 34}, {'prodId': 12547997, 'date': '2025-08-21', 'price': 691.54, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-08-22', 'price': 691.54, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-08-23', 'price': 730.0, 'merchantId': 34}, {'prodId': 12547997, 'date': '2025-08-24', 'price': 730.0, 'merchantId': 34}, {'prodId': 12547997, 'date': '2025-08-25', 'price': 691.54, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-08-26', 'price': 691.54, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-08-27', 'price': 699.9, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-08-28', 'price': 699.9, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-08-29', 'price': 710.91, 'merchantId': 16108}, {'prodId': 12547997, 'date': '2025-08-30', 'price': 710.91, 'merchantId': 16108}, {'prodId': 12547997, 'date': '2025-08-31', 'price': 730.0, 'merchantId': 34}, {'prodId': 12547997, 'date': '2025-09-01', 'price': 699.9, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-09-02', 'price': 706.39, 'merchantId': 23326}, {'prodId': 12547997, 'date': '2025-09-03', 'price': 706.39, 'merchantId': 23326}, {'prodId': 12547997, 'date': '2025-09-04', 'price': 706.39, 'merchantId': 23326}, {'prodId': 12547997, 'date': '2025-09-05', 'price': 706.39, 'merchantId': 23326}, {'prodId': 12547997, 'date': '2025-09-06', 'price': 726.0, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-09-07', 'price': 726.0, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-09-08', 'price': 699.0, 'merchantId': 22905}, {'prodId': 12547997, 'date': '2025-09-09', 'price': 699.0, 'merchantId': 22905}, {'prodId': 12547997, 'date': '2025-09-10', 'price': 689.0, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-09-11', 'price': 688.0, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-09-12', 'price': 688.0, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-09-13', 'price': 688.0, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-09-14', 'price': 688.0, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-09-15', 'price': 688.0, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-09-16', 'price': 688.0, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-09-17', 'price': 697.0, 'merchantId': 22905}, {'prodId': 12547997, 'date': '2025-09-18', 'price': 697.0, 'merchantId': 22905}, {'prodId': 12547997, 'date': '2025-09-19', 'price': 667.85, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-09-20', 'price': 667.85, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-09-21', 'price': 667.85, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-09-22', 'price': 667.85, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-09-23', 'price': 667.85, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-09-24', 'price': 676.4, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-09-25', 'price': 676.4, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-09-26', 'price': 666.9, 'merchantId': 9385}, {'prodId': 12547997, 'date': '2025-09-27', 'price': 666.9, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-09-28', 'price': 664.05, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-09-29', 'price': 664.05, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-09-30', 'price': 664.05, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-10-01', 'price': 673.12, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-10-02', 'price': 673.12, 'merchantId': 9385}, {'prodId': 12547997, 'date': '2025-10-03', 'price': 689.9, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-10-04', 'price': 699.0, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-10-05', 'price': 659.9, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-10-06', 'price': 659.9, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-10-07', 'price': 626.9, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-10-08', 'price': 626.9, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-10-09', 'price': 599.0, 'merchantId': 9385}, {'prodId': 12547997, 'date': '2025-10-10', 'price': 599.0, 'merchantId': 9385}, {'prodId': 12547997, 'date': '2025-10-11', 'price': 649.0, 'merchantId': 9385}, {'prodId': 12547997, 'date': '2025-10-12', 'price': 649.0, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-10-13', 'price': 649.0, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-10-14', 'price': 649.0, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-10-15', 'price': 649.0, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-10-16', 'price': 664.9, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-10-17', 'price': 664.9, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-10-18', 'price': 661.9, 'merchantId': 9385}, {'prodId': 12547997, 'date': '2025-10-19', 'price': 661.9, 'merchantId': 9385}, {'prodId': 12547997, 'date': '2025-10-20', 'price': 636.4, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-10-21', 'price': 636.4, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-10-22', 'price': 636.4, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-10-23', 'price': 636.4, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-10-24', 'price': 636.4, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-10-25', 'price': 636.4, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-10-26', 'price': 636.4, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-10-27', 'price': 655.0, 'merchantId': 9385}, {'prodId': 12547997, 'date': '2025-10-28', 'price': 655.0, 'merchantId': 9385}, {'prodId': 12547997, 'date': '2025-10-29', 'price': 649.0, 'merchantId': 9385}, {'prodId': 12547997, 'date': '2025-10-30', 'price': 649.0, 'merchantId': 9385}, {'prodId': 12547997, 'date': '2025-10-31', 'price': 649.0, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-11-01', 'price': 649.0, 'merchantId': 9385}, {'prodId': 12547997, 'date': '2025-11-02', 'price': 654.9, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-11-03', 'price': 610.13, 'merchantId': 23326}, {'prodId': 12547997, 'date': '2025-11-04', 'price': 610.13, 'merchantId': 23326}, {'prodId': 12547997, 'date': '2025-11-05', 'price': 620.25, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-11-06', 'price': 620.25, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-11-07', 'price': 597.55, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-11-08', 'price': 597.55, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-11-09', 'price': 597.55, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-11-10', 'price': 629.0, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-11-11', 'price': 620.25, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-11-12', 'price': 620.25, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-11-13', 'price': 629.0, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-11-14', 'price': 639.9, 'merchantId': 23254}, {'prodId': 12547997, 'date': '2025-11-15', 'price': 639.9, 'merchantId': 23254}, {'prodId': 12547997, 'date': '2025-11-16', 'price': 639.9, 'merchantId': 23254}, {'prodId': 12547997, 'date': '2025-11-17', 'price': 629.0, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-11-18', 'price': 639.9, 'merchantId': 23254}, {'prodId': 12547997, 'date': '2025-11-19', 'price': 639.9, 'merchantId': 23254}, {'prodId': 12547997, 'date': '2025-11-20', 'price': 679.98, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-11-21', 'price': 679.98, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-11-22', 'price': 679.98, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-11-23', 'price': 692.55, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-11-24', 'price': 645.98, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-11-25', 'price': 629.14, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-11-26', 'price': 629.14, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-11-27', 'price': 629.91, 'merchantId': 20609}, {'prodId': 12547997, 'date': '2025-11-28', 'price': 626.4, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-11-29', 'price': 626.4, 'merchantId': 1582}, {'prodId': 12547997, 'date': '2025-11-30', 'price': 629.91, 'merchantId': 20609}, {'prodId': 12547997, 'date': '2025-12-01', 'price': 629.91, 'merchantId': 20609}, {'prodId': 12547997, 'date': '2025-12-02', 'price': 629.9, 'merchantId': 20609}, {'prodId': 12547997, 'date': '2025-12-03', 'price': 629.9, 'merchantId': 20609}, {'prodId': 12547997, 'date': '2025-12-04', 'price': 629.9, 'merchantId': 20609}, {'prodId': 12547997, 'date': '2025-12-05', 'price': 629.9, 'merchantId': 20609}, {'prodId': 12547997, 'date': '2025-12-06', 'price': 629.9, 'merchantId': 20609}, {'prodId': 12547997, 'date': '2025-12-07', 'price': 629.9, 'merchantId': 20609}, {'prodId': 12547997, 'date': '2025-12-08', 'price': 629.9, 'merchantId': 20609}, {'prodId': 12547997, 'date': '2025-12-09', 'price': 629.9, 'merchantId': 20609}, {'prodId': 12547997, 'date': '2025-12-10', 'price': 629.9, 'merchantId': 20609}, {'prodId': 12547997, 'date': '2025-12-11', 'price': 629.9, 'merchantId': 20609}, {'prodId': 12547997, 'date': '2025-12-12', 'price': 629.9, 'merchantId': 20609}, {'prodId': 12547997, 'date': '2025-12-13', 'price': 629.9, 'merchantId': 20609}, {'prodId': 12547997, 'date': '2025-12-14', 'price': 629.9, 'merchantId': 20609}, {'prodId': 12547997, 'date': '2025-12-15', 'price': 629.9, 'merchantId': 20609}, {'prodId': 12547997, 'date': '2025-12-16', 'price': 629.9, 'merchantId': 20609}, {'prodId': 12547997, 'date': '2025-12-17', 'price': 629.9, 'merchantId': 20609}, {'prodId': 12547997, 'date': '2025-12-18', 'price': 629.9, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2025-12-19', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2025-12-20', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2025-12-21', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2025-12-22', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2025-12-23', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2025-12-24', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2025-12-25', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2025-12-26', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2025-12-27', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2025-12-28', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2025-12-29', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2025-12-30', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2025-12-31', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-01', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-02', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-03', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-04', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-05', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-06', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-07', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-08', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-09', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-10', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-11', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-12', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-13', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-14', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-15', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-16', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-17', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-18', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-19', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-20', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-21', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-22', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-23', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-24', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-25', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-26', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-27', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-28', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-29', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-30', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-01-31', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-01', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-02', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-03', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-04', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-05', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-06', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-07', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-08', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-09', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-10', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-11', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-12', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-13', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-14', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-15', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-16', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-17', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-18', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-19', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-20', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-21', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-22', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-23', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-24', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-25', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-26', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-27', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-02-28', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-01', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-02', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-03', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-04', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-05', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-06', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-07', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-08', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-09', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-10', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-11', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-12', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-13', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-14', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-15', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-16', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-17', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-18', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-19', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-20', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-21', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-22', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-23', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-24', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-25', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-26', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-27', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-28', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-29', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-30', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-03-31', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-01', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-02', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-03', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-04', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-05', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-06', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-07', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-08', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-09', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-10', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-11', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-12', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-13', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-14', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-15', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-16', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-17', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-18', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-19', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-20', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-21', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-22', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-23', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-24', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-25', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-26', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-27', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-28', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-29', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-04-30', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-01', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-02', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-03', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-04', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-05', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-06', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-07', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-08', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-09', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-10', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-11', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-12', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-13', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-14', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-15', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-16', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-17', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-18', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-19', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-20', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-21', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-22', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-23', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-24', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-25', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-26', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-27', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-28', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-29', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-30', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-05-31', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-01', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-02', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-03', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-04', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-05', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-06', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-07', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-08', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-09', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-10', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-11', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-12', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-13', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-14', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-15', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-16', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-17', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-18', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-19', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-20', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-21', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-22', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-23', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-24', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-25', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-26', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-27', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-28', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-29', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-06-30', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-07-01', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-07-02', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-07-03', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-07-04', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-07-05', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-07-06', 'price': 635.0, 'merchantId': 20612}, {'prodId': 12547997, 'date': '2026-07-07', 'price': 635.0, 'merchantId': 20612}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13994349, 'date': '2026-04-15', 'price': 3137.21, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-04-16', 'price': 2491.34, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-04-17', 'price': 2491.34, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-04-18', 'price': 2491.34, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-04-19', 'price': 2491.34, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-04-20', 'price': 2491.34, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-04-21', 'price': 2491.34, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-04-22', 'price': 2491.34, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-04-23', 'price': 2491.34, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-04-24', 'price': 2455.64, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-04-25', 'price': 2455.64, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-04-26', 'price': 2455.64, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-04-27', 'price': 2455.64, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-04-28', 'price': 2455.64, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-04-29', 'price': 2455.64, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-04-30', 'price': 2455.64, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-01', 'price': 2455.64, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-02', 'price': 2455.64, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-03', 'price': 2455.64, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-04', 'price': 2455.64, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-05', 'price': 2389.34, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-06', 'price': 2389.34, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-07', 'price': 2389.34, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-08', 'price': 2389.34, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-09', 'price': 2389.34, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-10', 'price': 2389.34, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-11', 'price': 2389.34, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-12', 'price': 2389.34, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-13', 'price': 2389.34, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-14', 'price': 2389.34, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-15', 'price': 2389.34, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-16', 'price': 2389.34, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-17', 'price': 2389.34, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-18', 'price': 2389.34, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-19', 'price': 2455.64, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-20', 'price': 2455.64, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-21', 'price': 2455.64, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-22', 'price': 2455.64, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-23', 'price': 2537.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-24', 'price': 2537.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-25', 'price': 2537.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-26', 'price': 2537.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-27', 'price': 928.19, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-28', 'price': 928.19, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-29', 'price': 928.19, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-30', 'price': 928.19, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-05-31', 'price': 928.19, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-06-01', 'price': 928.19, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-06-02', 'price': 928.19, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-06-03', 'price': 928.19, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-06-04', 'price': 928.19, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-06-05', 'price': 928.19, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-06-06', 'price': 2375.0, 'merchantId': 16623}, {'prodId': 13994349, 'date': '2026-06-07', 'price': 2375.0, 'merchantId': 16623}, {'prodId': 13994349, 'date': '2026-06-08', 'price': 2375.0, 'merchantId': 16623}, {'prodId': 13994349, 'date': '2026-06-09', 'price': 2375.0, 'merchantId': 16623}, {'prodId': 13994349, 'date': '2026-06-10', 'price': 2375.0, 'merchantId': 16623}, {'prodId': 13994349, 'date': '2026-06-11', 'price': 2375.0, 'merchantId': 16623}, {'prodId': 13994349, 'date': '2026-06-12', 'price': 2375.0, 'merchantId': 16623}, {'prodId': 13994349, 'date': '2026-06-13', 'price': 2537.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-06-14', 'price': 2537.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-06-15', 'price': 2537.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-06-16', 'price': 2537.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-06-17', 'price': 2537.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-06-18', 'price': 2537.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-06-19', 'price': 2537.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-06-20', 'price': 2537.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-06-21', 'price': 2579.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-06-22', 'price': 2579.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-06-23', 'price': 2579.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-06-24', 'price': 2579.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-06-25', 'price': 2579.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-06-26', 'price': 2579.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-06-27', 'price': 2579.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-06-28', 'price': 2579.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-06-29', 'price': 2579.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-06-30', 'price': 2579.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-07-01', 'price': 2579.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-07-02', 'price': 2579.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-07-03', 'price': 2579.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-07-04', 'price': 2579.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-07-05', 'price': 2579.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-07-06', 'price': 2537.99, 'merchantId': 22905}, {'prodId': 13994349, 'date': '2026-07-07', 'price': 2537.99, 'merchantId': 22905}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 12534149, 'date': '2025-07-07', 'price': 7869.0, 'merchantId': 23254}, {'prodId': 12534149, 'date': '2025-07-08', 'price': 7869.0, 'merchantId': 23254}, {'prodId': 12534149, 'date': '2025-07-09', 'price': 7869.0, 'merchantId': 23254}, {'prodId': 12534149, 'date': '2025-07-10', 'price': 7869.0, 'merchantId': 23254}, {'prodId': 12534149, 'date': '2025-07-11', 'price': 5399.0, 'merchantId': 10763}, {'prodId': 12534149, 'date': '2025-07-12', 'price': 5399.0, 'merchantId': 10763}, {'prodId': 12534149, 'date': '2025-07-13', 'price': 5399.0, 'merchantId': 10763}, {'prodId': 12534149, 'date': '2025-07-14', 'price': 5399.0, 'merchantId': 10763}, {'prodId': 12534149, 'date': '2025-07-15', 'price': 5399.0, 'merchantId': 10763}, {'prodId': 12534149, 'date': '2025-07-16', 'price': 5399.0, 'merchantId': 10763}, {'prodId': 12534149, 'date': '2025-07-17', 'price': 5399.0, 'merchantId': 10763}, {'prodId': 12534149, 'date': '2025-07-18', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-07-19', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-07-20', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-07-21', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-07-22', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-07-23', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-07-24', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-07-25', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-07-26', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-07-27', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-07-28', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-07-29', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-07-30', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-07-31', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-01', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-02', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-03', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-04', 'price': 4679.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-05', 'price': 4679.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-06', 'price': 4679.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-07', 'price': 4859.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-08', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-09', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-10', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-11', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-12', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-13', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-14', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-15', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-16', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-17', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-18', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-19', 'price': 5084.1, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-20', 'price': 6749.07, 'merchantId': 5}, {'prodId': 12534149, 'date': '2025-08-21', 'price': 5649.0, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-22', 'price': 5649.0, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-23', 'price': 5649.0, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-24', 'price': 5649.0, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-25', 'price': 5649.0, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-26', 'price': 5649.0, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-27', 'price': 5649.0, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-28', 'price': 5649.0, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-29', 'price': 5649.0, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-30', 'price': 5649.0, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-08-31', 'price': 5649.0, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-09-01', 'price': 5649.0, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-09-02', 'price': 5649.0, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-09-03', 'price': 5649.0, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-09-04', 'price': 5649.0, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-09-05', 'price': 5649.0, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-09-06', 'price': 5649.0, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-09-07', 'price': 5649.0, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-09-08', 'price': 5649.0, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-09-09', 'price': 5649.0, 'merchantId': 9385}, {'prodId': 12534149, 'date': '2025-09-10', 'price': 6608.46, 'merchantId': 5}, {'prodId': 12534149, 'date': '2025-09-11', 'price': 6608.46, 'merchantId': 5}, {'prodId': 12534149, 'date': '2025-09-12', 'price': 6608.46, 'merchantId': 5}, {'prodId': 12534149, 'date': '2025-09-13', 'price': 6608.46, 'merchantId': 5}, {'prodId': 12534149, 'date': '2025-09-14', 'price': 6608.46, 'merchantId': 5}, {'prodId': 12534149, 'date': '2025-09-15', 'price': 6608.46, 'merchantId': 5}, {'prodId': 12534149, 'date': '2025-09-16', 'price': 6608.46, 'merchantId': 5}, {'prodId': 12534149, 'date': '2025-09-17', 'price': 6608.46, 'merchantId': 5}, {'prodId': 12534149, 'date': '2025-09-18', 'price': 6608.46, 'merchantId': 5}, {'prodId': 12534149, 'date': '2025-09-19', 'price': 6608.46, 'merchantId': 5}, {'prodId': 12534149, 'date': '2025-09-20', 'price': 6608.46, 'merchantId': 5}, {'prodId': 12534149, 'date': '2025-09-21', 'price': 6608.46, 'merchantId': 5}, {'prodId': 12534149, 'date': '2025-09-22', 'price': 6608.46, 'merchantId': 5}, {'prodId': 12534149, 'date': '2025-09-23', 'price': 6608.46, 'merchantId': 5}, {'prodId': 12534149, 'date': '2025-09-24', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-09-25', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-09-26', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-09-27', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-09-28', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-09-29', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-09-30', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-01', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-02', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-03', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-04', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-05', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-06', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-07', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-08', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-09', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-10', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-11', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-12', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-13', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-14', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-15', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-16', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-17', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-18', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-19', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-20', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-21', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-22', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-23', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-24', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-25', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-26', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-27', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-28', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-29', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-30', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-10-31', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-11-01', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-11-02', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-11-03', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-11-04', 'price': 6790.0, 'merchantId': 34}, {'prodId': 12534149, 'date': '2025-11-05', 'price': 6790.0, 'merchantId': 34}, {'prodId': 12534149, 'date': '2025-11-06', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-11-07', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-11-08', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-11-09', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-11-10', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-11-11', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-11-12', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-11-13', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-11-14', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-11-15', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-11-16', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-11-17', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-11-18', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-11-19', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-11-20', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-11-21', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-11-22', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-11-23', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-11-24', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-11-25', 'price': 7852.9, 'merchantId': 20583}, {'prodId': 12534149, 'date': '2025-11-26', 'price': 7199.0, 'merchantId': 23326}, {'prodId': 12534149, 'date': '2025-11-27', 'price': 6849.0, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-11-28', 'price': 6696.8, 'merchantId': 23326}, {'prodId': 12534149, 'date': '2025-11-29', 'price': 6848.0, 'merchantId': 21628}, {'prodId': 12534149, 'date': '2025-11-30', 'price': 6848.0, 'merchantId': 21628}, {'prodId': 12534149, 'date': '2025-12-01', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-02', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-03', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-04', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-05', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-06', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-07', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-08', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-09', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-10', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-11', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-12', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-13', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-14', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-15', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-16', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-17', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-18', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-19', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-20', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-21', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-22', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-23', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-24', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-25', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-26', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-27', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-28', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-29', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-30', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2025-12-31', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-01', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-02', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-03', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-04', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-05', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-06', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-07', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-08', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-09', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-10', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-11', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-12', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-13', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-14', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-15', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-16', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-17', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-18', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-19', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-20', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-21', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-22', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-23', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-24', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-25', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-26', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-27', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-28', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-29', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-30', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-01-31', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-01', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-02', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-03', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-04', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-05', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-06', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-07', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-08', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-09', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-10', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-11', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-12', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-13', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-14', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-15', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-16', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-17', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-18', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-19', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-20', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-21', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-22', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-23', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-24', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-25', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-26', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-27', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-02-28', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-01', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-02', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-03', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-04', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-05', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-06', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-07', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-08', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-09', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-10', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-11', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-12', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-13', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-14', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-15', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-16', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-17', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-18', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-19', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-20', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-21', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-22', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-23', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-24', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-25', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-26', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-27', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-28', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-29', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-30', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-03-31', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-01', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-02', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-03', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-04', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-05', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-06', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-07', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-08', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-09', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-10', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-11', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-12', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-13', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-14', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-15', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-16', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-17', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-18', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-19', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-20', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-21', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-22', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-23', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-24', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-25', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-26', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-27', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-28', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-29', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-04-30', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-01', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-02', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-03', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-04', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-05', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-06', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-07', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-08', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-09', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-10', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-11', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-12', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-13', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-14', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-15', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-16', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-17', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-18', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-19', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-20', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-21', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-22', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-23', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-24', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-25', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-26', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-27', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-28', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-29', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-30', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-05-31', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-01', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-02', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-03', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-04', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-05', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-06', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-07', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-08', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-09', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-10', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-11', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-12', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-13', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-14', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-15', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-16', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-17', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-18', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-19', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-20', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-21', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-22', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-23', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-24', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-25', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-26', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-27', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-28', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-29', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-06-30', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-07-01', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-07-02', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-07-03', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-07-04', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-07-05', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-07-06', 'price': 4949.1, 'merchantId': 4}, {'prodId': 12534149, 'date': '2026-07-07', 'price': 4949.1, 'merchantId': 4}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13994064, 'date': '2026-03-31', 'price': 2744.45, 'merchantId': 20904}, {'prodId': 13994064, 'date': '2026-04-01', 'price': 2744.45, 'merchantId': 20904}, {'prodId': 13994064, 'date': '2026-04-02', 'price': 2744.45, 'merchantId': 20904}, {'prodId': 13994064, 'date': '2026-04-03', 'price': 2744.45, 'merchantId': 20904}, {'prodId': 13994064, 'date': '2026-04-04', 'price': 2744.45, 'merchantId': 20904}, {'prodId': 13994064, 'date': '2026-04-05', 'price': 2744.45, 'merchantId': 20904}, {'prodId': 13994064, 'date': '2026-04-06', 'price': 2744.45, 'merchantId': 20904}, {'prodId': 13994064, 'date': '2026-04-07', 'price': 2744.45, 'merchantId': 20904}, {'prodId': 13994064, 'date': '2026-04-08', 'price': 2744.45, 'merchantId': 20904}, {'prodId': 13994064, 'date': '2026-04-09', 'price': 2744.45, 'merchantId': 20904}, {'prodId': 13994064, 'date': '2026-04-10', 'price': 2744.45, 'merchantId': 20904}, {'prodId': 13994064, 'date': '2026-04-11', 'price': 2744.45, 'merchantId': 20904}, {'prodId': 13994064, 'date': '2026-04-12', 'price': 2512.2200000000003, 'merchantId': 20904}, {'prodId': 13994064, 'date': '2026-04-13', 'price': 2512.2200000000003, 'merchantId': 20904}, {'prodId': 13994064, 'date': '2026-04-14', 'price': 2512.2200000000003, 'merchantId': 20904}, {'prodId': 13994064, 'date': '2026-04-15', 'price': 2512.2200000000003, 'merchantId': 20904}, {'prodId': 13994064, 'date': '2026-04-16', 'price': 2398.54, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-04-17', 'price': 2235.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-04-18', 'price': 2235.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-04-19', 'price': 2235.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-04-20', 'price': 2235.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-04-21', 'price': 2235.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-04-22', 'price': 2235.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-04-23', 'price': 2235.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-04-24', 'price': 2235.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-04-25', 'price': 2235.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-04-26', 'price': 2235.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-04-27', 'price': 2235.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-04-28', 'price': 2235.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-04-29', 'price': 2235.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-04-30', 'price': 2235.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-01', 'price': 2158.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-02', 'price': 2158.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-03', 'price': 2158.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-04', 'price': 2158.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-05', 'price': 2158.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-06', 'price': 2158.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-07', 'price': 2158.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-08', 'price': 2158.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-09', 'price': 2235.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-10', 'price': 2235.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-11', 'price': 2235.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-12', 'price': 2231.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-13', 'price': 2231.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-14', 'price': 2231.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-15', 'price': 2231.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-16', 'price': 2231.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-17', 'price': 2231.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-18', 'price': 1922.39, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-19', 'price': 2084.79, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-20', 'price': 2084.79, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-21', 'price': 2114.39, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-22', 'price': 2084.79, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-23', 'price': 2084.79, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-24', 'price': 2084.79, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-25', 'price': 2084.79, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-26', 'price': 2084.79, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-27', 'price': 2084.79, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-28', 'price': 2114.39, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-29', 'price': 2114.39, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-30', 'price': 2114.39, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-05-31', 'price': 2114.39, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-06-01', 'price': 2114.39, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-06-02', 'price': 2124.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-06-03', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13994064, 'date': '2026-06-04', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13994064, 'date': '2026-06-05', 'price': 2020.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-06-06', 'price': 2020.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-06-07', 'price': 2020.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-06-08', 'price': 2020.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-06-09', 'price': 2020.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-06-10', 'price': 2020.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-06-11', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13994064, 'date': '2026-06-12', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13994064, 'date': '2026-06-13', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13994064, 'date': '2026-06-14', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13994064, 'date': '2026-06-15', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13994064, 'date': '2026-06-16', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13994064, 'date': '2026-06-17', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13994064, 'date': '2026-06-18', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13994064, 'date': '2026-06-19', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13994064, 'date': '2026-06-20', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13994064, 'date': '2026-06-21', 'price': 2079.0, 'merchantId': 16623}, {'prodId': 13994064, 'date': '2026-06-22', 'price': 1922.96, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-06-23', 'price': 1922.96, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-06-24', 'price': 2020.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-06-25', 'price': 2020.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-06-26', 'price': 2020.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-06-27', 'price': 2020.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-06-28', 'price': 2020.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-06-29', 'price': 2020.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-06-30', 'price': 2020.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-07-01', 'price': 2020.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-07-02', 'price': 2149.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-07-03', 'price': 2020.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-07-04', 'price': 2149.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-07-05', 'price': 2149.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-07-06', 'price': 2149.99, 'merchantId': 22905}, {'prodId': 13994064, 'date': '2026-07-07', 'price': 2188.42, 'merchantId': 16623}]}}</t>
-  </si>
-  <si>
-    <t>{'product_price_history': {'details': {'status': 200, 'success': True, 'metadata': {'ignore-errors': 'ignore'}}, 'result': [{'prodId': 13992144, 'date': '2025-07-07', 'price': 4249.15, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2025-07-08', 'price': 4249.15, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2025-07-09', 'price': 4399.91, 'merchantId': 21627}, {'prodId': 13992144, 'date': '2025-07-10', 'price': 4399.91, 'merchantId': 21627}, {'prodId': 13992144, 'date': '2025-07-11', 'price': 4399.91, 'merchantId': 21627}, {'prodId': 13992144, 'date': '2025-07-12', 'price': 4399.91, 'merchantId': 21627}, {'prodId': 13992144, 'date': '2025-07-13', 'price': 4399.91, 'merchantId': 21627}, {'prodId': 13992144, 'date': '2025-07-14', 'price': 4399.91, 'merchantId': 21627}, {'prodId': 13992144, 'date': '2025-07-15', 'price': 4399.91, 'merchantId': 21627}, {'prodId': 13992144, 'date': '2025-07-16', 'price': 4498.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-07-17', 'price': 4498.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-07-18', 'price': 4498.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-07-19', 'price': 4498.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-07-20', 'price': 4498.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-07-21', 'price': 4498.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-07-22', 'price': 4498.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-07-23', 'price': 4498.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-07-24', 'price': 4498.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-07-25', 'price': 4498.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-07-26', 'price': 4498.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-07-27', 'price': 4498.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-07-28', 'price': 4498.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-07-29', 'price': 4498.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-07-30', 'price': 4498.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-07-31', 'price': 4498.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-08-01', 'price': 3598.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-08-02', 'price': 3598.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-08-03', 'price': 3598.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-08-04', 'price': 3598.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-08-05', 'price': 3598.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-08-06', 'price': 3598.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-08-07', 'price': 3598.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-08-08', 'price': 3598.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-08-09', 'price': 3598.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-08-10', 'price': 3598.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-08-11', 'price': 3598.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-08-12', 'price': 3598.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-08-13', 'price': 3598.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-08-14', 'price': 3598.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-08-15', 'price': 3598.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-08-16', 'price': 3598.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-08-17', 'price': 3598.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-08-18', 'price': 3598.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-08-19', 'price': 3598.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-08-20', 'price': 3598.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-08-21', 'price': 3598.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-08-22', 'price': 3598.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-08-23', 'price': 3598.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-08-24', 'price': 3598.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-08-25', 'price': 3598.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-08-26', 'price': 3419.14, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-08-27', 'price': 3419.14, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-08-28', 'price': 3419.14, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-08-29', 'price': 3419.14, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-08-30', 'price': 3419.14, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-08-31', 'price': 3419.14, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-09-01', 'price': 3419.14, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-09-02', 'price': 3419.14, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-09-03', 'price': 3419.14, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-09-04', 'price': 3419.14, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-09-05', 'price': 3419.14, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-09-06', 'price': 3419.14, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-09-07', 'price': 3419.14, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-09-08', 'price': 3419.14, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-09-09', 'price': 3319.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-09-10', 'price': 3240.0, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2025-09-11', 'price': 3240.0, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2025-09-12', 'price': 3168.0, 'merchantId': 20609}, {'prodId': 13992144, 'date': '2025-09-13', 'price': 3168.0, 'merchantId': 20609}, {'prodId': 13992144, 'date': '2025-09-14', 'price': 3168.0, 'merchantId': 20609}, {'prodId': 13992144, 'date': '2025-09-15', 'price': 3168.0, 'merchantId': 20609}, {'prodId': 13992144, 'date': '2025-09-16', 'price': 3239.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-09-17', 'price': 3239.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-09-18', 'price': 3238.1, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-09-19', 'price': 3239.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-09-20', 'price': 3239.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-09-21', 'price': 3239.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-09-22', 'price': 3239.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-09-23', 'price': 3239.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-09-24', 'price': 3139.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-09-25', 'price': 3139.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-09-26', 'price': 3139.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-09-27', 'price': 3139.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-09-28', 'price': 3139.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-09-29', 'price': 3139.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-09-30', 'price': 3139.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-01', 'price': 3139.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-02', 'price': 3139.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-03', 'price': 3139.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-04', 'price': 3139.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-05', 'price': 3139.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-06', 'price': 3139.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-07', 'price': 3139.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-08', 'price': 3129.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-09', 'price': 3129.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-10', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-11', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-12', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-13', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-14', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-15', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-16', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-17', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-18', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-19', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-20', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-21', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-22', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-23', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-24', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-25', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-26', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-27', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-28', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-29', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-30', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-10-31', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-11-01', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-11-02', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-11-03', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-11-04', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-11-05', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-11-06', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-11-07', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-11-08', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-11-09', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-11-10', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-11-11', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-11-12', 'price': 2879.8, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2025-11-13', 'price': 2879.8, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2025-11-14', 'price': 2879.8, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2025-11-15', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-11-16', 'price': 3079.15, 'merchantId': 21628}, {'prodId': 13992144, 'date': '2025-11-17', 'price': 3048.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-11-18', 'price': 3048.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-11-19', 'price': 2968.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-11-20', 'price': 2968.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-11-21', 'price': 2968.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-11-22', 'price': 2968.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-11-23', 'price': 2968.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-11-24', 'price': 2968.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-11-25', 'price': 2788.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-11-26', 'price': 2788.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-11-27', 'price': 2788.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-11-28', 'price': 2788.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-11-29', 'price': 2788.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-11-30', 'price': 2788.2, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-12-01', 'price': 2748.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-12-02', 'price': 2748.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-12-03', 'price': 2748.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-12-04', 'price': 2748.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-12-05', 'price': 2748.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-12-06', 'price': 2748.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-12-07', 'price': 2748.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-12-08', 'price': 2748.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-12-09', 'price': 2748.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-12-10', 'price': 2748.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-12-11', 'price': 2748.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-12-12', 'price': 2748.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-12-13', 'price': 2748.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-12-14', 'price': 2748.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-12-15', 'price': 2748.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-12-16', 'price': 2748.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-12-17', 'price': 2748.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2025-12-18', 'price': 2748.0, 'merchantId': 4}, {'prodId': 13992144, 'date': '2025-12-19', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2025-12-20', 'price': 3014.1, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-12-21', 'price': 3014.1, 'merchantId': 23199}, {'prodId': 13992144, 'date': '2025-12-22', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2025-12-23', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2025-12-24', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2025-12-25', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2025-12-26', 'price': 3081.08, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2025-12-27', 'price': 3081.08, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2025-12-28', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2025-12-29', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2025-12-30', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2025-12-31', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-01', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-02', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-03', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-04', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-05', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-06', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-07', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-08', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-09', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-10', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-11', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-12', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-13', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-14', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-15', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-16', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-17', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-18', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-19', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-20', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-21', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-22', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-23', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-24', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-25', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-26', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-27', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-28', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-29', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-30', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-01-31', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-02-01', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-02-02', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-02-03', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-02-04', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-02-05', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-02-06', 'price': 3099.0, 'merchantId': 22905}, {'prodId': 13992144, 'date': '2026-02-07', 'price': 3998.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-02-08', 'price': 3998.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-02-09', 'price': 3997.9, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-02-10', 'price': 3997.79, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-02-11', 'price': 3689.1, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-02-12', 'price': 3689.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-02-13', 'price': 3607.12, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-02-14', 'price': 3607.12, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-02-15', 'price': 3607.12, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-02-16', 'price': 3607.12, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-02-17', 'price': 3607.12, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-02-18', 'price': 3607.12, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-02-19', 'price': 3607.12, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-02-20', 'price': 3607.12, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-02-21', 'price': 3688.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-02-22', 'price': 3688.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-02-23', 'price': 3687.9, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-02-24', 'price': 3687.9, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-02-25', 'price': 3687.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-02-26', 'price': 3687.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-02-27', 'price': 3686.9, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-02-28', 'price': 3566.13, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-03-01', 'price': 3566.13, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-03-02', 'price': 3566.13, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-03-03', 'price': 3685.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-03-04', 'price': 3502.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-03-05', 'price': 3501.9, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-03-06', 'price': 3501.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-03-07', 'price': 3501.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-03-08', 'price': 3501.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-03-09', 'price': 3501.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-03-10', 'price': 3500.9, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-03-11', 'price': 3499.0, 'merchantId': 21627}, {'prodId': 13992144, 'date': '2026-03-12', 'price': 3499.0, 'merchantId': 21627}, {'prodId': 13992144, 'date': '2026-03-13', 'price': 3499.0, 'merchantId': 21627}, {'prodId': 13992144, 'date': '2026-03-14', 'price': 3499.0, 'merchantId': 21627}, {'prodId': 13992144, 'date': '2026-03-15', 'price': 3499.0, 'merchantId': 21627}, {'prodId': 13992144, 'date': '2026-03-16', 'price': 3499.0, 'merchantId': 21627}, {'prodId': 13992144, 'date': '2026-03-17', 'price': 3499.0, 'merchantId': 21627}, {'prodId': 13992144, 'date': '2026-03-18', 'price': 3499.0, 'merchantId': 21627}, {'prodId': 13992144, 'date': '2026-03-19', 'price': 3499.0, 'merchantId': 21627}, {'prodId': 13992144, 'date': '2026-03-20', 'price': 3499.0, 'merchantId': 21627}, {'prodId': 13992144, 'date': '2026-03-21', 'price': 3499.0, 'merchantId': 21627}, {'prodId': 13992144, 'date': '2026-03-22', 'price': 3499.0, 'merchantId': 21627}, {'prodId': 13992144, 'date': '2026-03-23', 'price': 3499.0, 'merchantId': 21627}, {'prodId': 13992144, 'date': '2026-03-24', 'price': 3305.13, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-03-25', 'price': 3305.13, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-03-26', 'price': 3305.13, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-03-27', 'price': 3305.13, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-03-28', 'price': 3499.0, 'merchantId': 21627}, {'prodId': 13992144, 'date': '2026-03-29', 'price': 3499.0, 'merchantId': 21627}, {'prodId': 13992144, 'date': '2026-03-30', 'price': 3419.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-03-31', 'price': 3418.9, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-04-01', 'price': 3148.9, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-04-02', 'price': 3419.1, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-04-03', 'price': 3187.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-04-04', 'price': 3187.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-04-05', 'price': 3187.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-04-06', 'price': 3187.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-04-07', 'price': 3178.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-04-08', 'price': 3178.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-04-09', 'price': 3059.1, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-04-10', 'price': 3059.1, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-04-11', 'price': 3059.1, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-04-12', 'price': 3059.1, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-04-13', 'price': 3059.1, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-04-14', 'price': 3059.1, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-04-15', 'price': 3059.1, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-04-16', 'price': 3059.1, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-04-17', 'price': 3059.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-04-18', 'price': 3059.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-04-19', 'price': 3059.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-04-20', 'price': 3059.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-04-21', 'price': 3059.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-04-22', 'price': 3058.9, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-04-23', 'price': 3058.9, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-04-24', 'price': 3058.49, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-04-25', 'price': 3058.49, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-04-26', 'price': 3058.49, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-04-27', 'price': 3058.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-04-28', 'price': 3058.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-04-29', 'price': 3057.9, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-04-30', 'price': 3057.9, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-05-01', 'price': 3057.9, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-05-02', 'price': 3057.9, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-05-03', 'price': 3057.9, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-05-04', 'price': 3057.49, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-05-05', 'price': 3057.49, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-05-06', 'price': 3057.49, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-05-07', 'price': 3057.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-05-08', 'price': 3057.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-05-09', 'price': 3057.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-05-10', 'price': 3057.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-05-11', 'price': 3056.9, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-05-12', 'price': 3056.9, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-05-13', 'price': 3056.9, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-05-14', 'price': 3056.9, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-05-15', 'price': 3056.9, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-05-16', 'price': 3056.9, 'merchantId': 4}, {'prodId': 13992144, 'date': '2026-05-17', 'price': 3056.9, 'merchantId': 4}, {'prodId': 13992144, 'date': '2026-05-18', 'price': 3056.9, 'merchantId': 4}, {'prodId': 13992144, 'date': '2026-05-19', 'price': 3689.0, 'merchantId': 4}, {'prodId': 13992144, 'date': '2026-05-20', 'price': 3689.0, 'merchantId': 4}, {'prodId': 13992144, 'date': '2026-05-21', 'price': 3688.9, 'merchantId': 4}, {'prodId': 13992144, 'date': '2026-05-22', 'price': 3320.0, 'merchantId': 4}, {'prodId': 13992144, 'date': '2026-05-23', 'price': 3320.0, 'merchantId': 4}, {'prodId': 13992144, 'date': '2026-05-24', 'price': 3320.0, 'merchantId': 4}, {'prodId': 13992144, 'date': '2026-05-25', 'price': 3320.0, 'merchantId': 4}, {'prodId': 13992144, 'date': '2026-05-26', 'price': 3319.9, 'merchantId': 4}, {'prodId': 13992144, 'date': '2026-05-27', 'price': 3319.9, 'merchantId': 4}, {'prodId': 13992144, 'date': '2026-05-28', 'price': 3319.9, 'merchantId': 4}, {'prodId': 13992144, 'date': '2026-05-29', 'price': 3319.79, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-05-30', 'price': 3319.79, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-05-31', 'price': 3319.79, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-06-01', 'price': 3319.79, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-06-02', 'price': 3319.49, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-06-03', 'price': 3319.49, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-06-04', 'price': 3629.0, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-06-05', 'price': 3629.0, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-06-06', 'price': 3629.0, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-06-07', 'price': 3629.0, 'merchantId': 20583}, {'prodId': 13992144, 'date': '2026-06-08', 'price': 3519.49, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-06-09', 'price': 3519.49, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-06-10', 'price': 3323.9, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-06-11', 'price': 3323.79, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-06-12', 'price': 3323.79, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-06-13', 'price': 3323.79, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-06-14', 'price': 3323.79, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-06-15', 'price': 3323.79, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-06-16', 'price': 3320.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-06-17', 'price': 3320.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-06-18', 'price': 3320.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-06-19', 'price': 3319.9, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-06-20', 'price': 3319.9, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-06-21', 'price': 3319.9, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-06-22', 'price': 3319.9, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-06-23', 'price': 3319.79, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-06-24', 'price': 3319.79, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-06-25', 'price': 3135.29, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-06-26', 'price': 3135.29, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-06-27', 'price': 3135.29, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-06-28', 'price': 3135.29, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-06-29', 'price': 3135.29, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-06-30', 'price': 3135.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-07-01', 'price': 3135.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-07-02', 'price': 3135.0, 'merchantId': 2}, {'prodId': 13992144, 'date': '2026-07-03', 'price': 2999.0, 'merchantId': 21627}, {'prodId': 13992144, 'date': '2026-07-04', 'price': 2999.0, 'merchantId': 21627}, {'prodId': 13992144, 'date': '2026-07-05', 'price': 2999.0, 'merchantId': 21627}, {'prodId': 13992144, 'date': '2026-07-06', 'price': 2999.0, 'merchantId': 21627}, {'prodId': 13992144, 'date': '2026-07-07', 'price': 2999.0, 'merchantId': 21627}]}}</t>
   </si>
 </sst>
 </file>
@@ -1479,10 +1299,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1498,979 +1318,832 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="F2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="F3" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="F4" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="F5" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="F6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="F7" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="F8" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="F9" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="F10" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="F11" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="F12" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="F13" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="F14" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D15" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="F15" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F16" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="F17" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D18" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="F18" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D19" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="F19" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D20" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F20" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D21" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="F21" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D22" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="F22" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="F23" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D24" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="F24" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D25" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="F25" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="F26" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D27" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="F27" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D28" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="F28" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D29" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="F29" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D30" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="F30" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D31" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="F31" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D32" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="F32" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D33" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="F33" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B34" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D34" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="F34" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C35" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D35" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="F35" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D36" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="F36" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D37" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="F37" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C38" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D38" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="F38" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C39" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D39" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="F39" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D40" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="F40" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B41" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C41" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D41" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F41" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C42" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D42" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="F42" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C43" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D43" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="F43" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C44" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D44" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="F44" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B45" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C45" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D45" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="F45" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C46" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D46" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="F46" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B47" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C47" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D47" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="F47" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B48" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C48" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D48" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="F48" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B49" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C49" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D49" t="s">
-        <v>202</v>
+        <v>232</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="F49" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
+    </row>
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C50" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D50" t="s">
         <v>233</v>
@@ -2478,19 +2151,16 @@
       <c r="E50" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="F50" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
+    </row>
+    <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B51" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C51" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D51" t="s">
         <v>234</v>
@@ -2498,19 +2168,16 @@
       <c r="E51" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="F51" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
+    </row>
+    <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B52" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C52" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D52" t="s">
         <v>235</v>
@@ -2518,19 +2185,16 @@
       <c r="E52" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="F52" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
+    </row>
+    <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B53" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C53" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D53" t="s">
         <v>236</v>
@@ -2538,19 +2202,16 @@
       <c r="E53" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="F53" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
+    </row>
+    <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B54" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C54" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D54" t="s">
         <v>237</v>
@@ -2558,19 +2219,16 @@
       <c r="E54" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="F54" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
+    </row>
+    <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B55" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C55" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D55" t="s">
         <v>238</v>
@@ -2578,19 +2236,16 @@
       <c r="E55" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="F55" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
+    </row>
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B56" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C56" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D56" t="s">
         <v>239</v>
@@ -2598,19 +2253,16 @@
       <c r="E56" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="F56" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
+    </row>
+    <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B57" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C57" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D57" t="s">
         <v>240</v>
@@ -2618,19 +2270,16 @@
       <c r="E57" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="F57" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
+    </row>
+    <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B58" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C58" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D58" t="s">
         <v>241</v>
@@ -2638,19 +2287,16 @@
       <c r="E58" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="F58" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
+    </row>
+    <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B59" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C59" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D59" t="s">
         <v>242</v>
@@ -2658,19 +2304,16 @@
       <c r="E59" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="F59" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
+    </row>
+    <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B60" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C60" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D60" t="s">
         <v>243</v>
@@ -2678,28 +2321,22 @@
       <c r="E60" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="F60" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
+    </row>
+    <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B61" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C61" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D61" t="s">
         <v>244</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>304</v>
-      </c>
-      <c r="F61" t="s">
-        <v>364</v>
       </c>
     </row>
   </sheetData>

--- a/spreadsheet.xlsx
+++ b/spreadsheet.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="304">
   <si>
     <t>product_id</t>
   </si>
@@ -46,45 +46,45 @@
     <t>13993095</t>
   </si>
   <si>
+    <t>13993244</t>
+  </si>
+  <si>
     <t>13992951</t>
   </si>
   <si>
-    <t>13993244</t>
-  </si>
-  <si>
     <t>13993093</t>
   </si>
   <si>
     <t>12547939</t>
   </si>
   <si>
+    <t>13991952</t>
+  </si>
+  <si>
     <t>12755140</t>
   </si>
   <si>
-    <t>13991952</t>
-  </si>
-  <si>
     <t>12534144</t>
   </si>
   <si>
     <t>12547936</t>
   </si>
   <si>
+    <t>13993381</t>
+  </si>
+  <si>
     <t>13538152</t>
   </si>
   <si>
-    <t>13993381</t>
-  </si>
-  <si>
     <t>13993243</t>
   </si>
   <si>
+    <t>13564531</t>
+  </si>
+  <si>
     <t>13570649</t>
   </si>
   <si>
-    <t>13564531</t>
-  </si>
-  <si>
     <t>13994392</t>
   </si>
   <si>
@@ -100,24 +100,24 @@
     <t>13991987</t>
   </si>
   <si>
+    <t>13567220</t>
+  </si>
+  <si>
+    <t>13994348</t>
+  </si>
+  <si>
+    <t>13992308</t>
+  </si>
+  <si>
     <t>13993303</t>
   </si>
   <si>
-    <t>13992308</t>
-  </si>
-  <si>
-    <t>13994348</t>
+    <t>13992942</t>
   </si>
   <si>
     <t>12534152</t>
   </si>
   <si>
-    <t>13567220</t>
-  </si>
-  <si>
-    <t>13992942</t>
-  </si>
-  <si>
     <t>13994192</t>
   </si>
   <si>
@@ -127,16 +127,34 @@
     <t>12755141</t>
   </si>
   <si>
+    <t>13991991</t>
+  </si>
+  <si>
+    <t>13186208</t>
+  </si>
+  <si>
     <t>13340189</t>
   </si>
   <si>
-    <t>13991991</t>
+    <t>13994264</t>
+  </si>
+  <si>
+    <t>13994393</t>
+  </si>
+  <si>
+    <t>13994235</t>
   </si>
   <si>
     <t>13992135</t>
   </si>
   <si>
-    <t>13186208</t>
+    <t>12481774</t>
+  </si>
+  <si>
+    <t>13993126</t>
+  </si>
+  <si>
+    <t>13994236</t>
   </si>
   <si>
     <t>12474762</t>
@@ -145,39 +163,21 @@
     <t>13340176</t>
   </si>
   <si>
-    <t>13994393</t>
-  </si>
-  <si>
-    <t>13994264</t>
-  </si>
-  <si>
-    <t>13994235</t>
-  </si>
-  <si>
-    <t>12481774</t>
-  </si>
-  <si>
-    <t>13993126</t>
-  </si>
-  <si>
-    <t>13994236</t>
+    <t>13992383</t>
+  </si>
+  <si>
+    <t>13994350</t>
   </si>
   <si>
     <t>13994245</t>
   </si>
   <si>
-    <t>13992383</t>
-  </si>
-  <si>
-    <t>13994350</t>
+    <t>13993089</t>
   </si>
   <si>
     <t>13994352</t>
   </si>
   <si>
-    <t>13993089</t>
-  </si>
-  <si>
     <t>13994360</t>
   </si>
   <si>
@@ -190,22 +190,22 @@
     <t>12481790</t>
   </si>
   <si>
+    <t>13992139</t>
+  </si>
+  <si>
     <t>13340173</t>
   </si>
   <si>
-    <t>13992139</t>
-  </si>
-  <si>
     <t>12547997</t>
   </si>
   <si>
+    <t>13992941</t>
+  </si>
+  <si>
     <t>13340177</t>
   </si>
   <si>
-    <t>13992941</t>
-  </si>
-  <si>
-    <t>13992144</t>
+    <t>13918863</t>
   </si>
   <si>
     <t>13341612</t>
@@ -226,45 +226,45 @@
     <t>Celular Samsung Galaxy S25 FE 5G 128GB 8 GB</t>
   </si>
   <si>
+    <t>Celular Samsung Galaxy A07 4G 128GB 4 GB</t>
+  </si>
+  <si>
     <t>Celular Samsung Galaxy A17 5G 256GB 8 GB</t>
   </si>
   <si>
-    <t>Celular Samsung Galaxy A07 4G 128GB 4 GB</t>
-  </si>
-  <si>
     <t>Celular Samsung Galaxy S25 FE 5G 256GB 8 GB</t>
   </si>
   <si>
     <t>Celular Samsung Galaxy S24 Ultra 5G 256GB 12 GB</t>
   </si>
   <si>
+    <t>iPhone 16e 128GB 8 GB</t>
+  </si>
+  <si>
     <t>iPhone 16 128GB</t>
   </si>
   <si>
-    <t>iPhone 16e 128GB 8 GB</t>
-  </si>
-  <si>
     <t>iPhone 15 128GB 6GB</t>
   </si>
   <si>
     <t>Celular Samsung Galaxy S24 5G 256GB 8 GB</t>
   </si>
   <si>
+    <t>Celular Motorola Moto G G86 5G 256GB 8 GB</t>
+  </si>
+  <si>
     <t>Celular Samsung Galaxy S25 Plus 5G 256GB 12 GB</t>
   </si>
   <si>
-    <t>Celular Motorola Moto G G86 5G 256GB 8 GB</t>
-  </si>
-  <si>
     <t>Celular Samsung Galaxy A07 4G 256GB 8 GB</t>
   </si>
   <si>
+    <t>Celular Samsung Galaxy S25 Ultra 5G 256GB 12 GB</t>
+  </si>
+  <si>
     <t>Celular Samsung Galaxy S25 5G 256GB 12 GB</t>
   </si>
   <si>
-    <t>Celular Samsung Galaxy S25 Ultra 5G 256GB 12 GB</t>
-  </si>
-  <si>
     <t>Celular Samsung A57 256GB 8 GB</t>
   </si>
   <si>
@@ -280,24 +280,24 @@
     <t>Celular Samsung Galaxy A36 5G SM-A366E 128GB 6 GB</t>
   </si>
   <si>
+    <t>Celular Samsung Galaxy S25 Ultra 5G SM-S938B 512GB 12 GB</t>
+  </si>
+  <si>
+    <t>Celular Xiaomi Pocophone Poco X8 Pro 256GB 8 GB</t>
+  </si>
+  <si>
+    <t>Celular Motorola Moto Edge 60 Pro 5G 256GB 12 GB</t>
+  </si>
+  <si>
     <t>Celular Xiaomi Redmi 15 256GB 8 GB</t>
   </si>
   <si>
-    <t>Celular Motorola Moto Edge 60 Pro 5G 256GB 12 GB</t>
-  </si>
-  <si>
-    <t>Celular Xiaomi Pocophone Poco X8 Pro 256GB 8 GB</t>
+    <t>iPhone 17 Pro 256GB</t>
   </si>
   <si>
     <t>iPhone 15 Pro Max 8 GB 256GB</t>
   </si>
   <si>
-    <t>Celular Samsung Galaxy S25 Ultra 5G SM-S938B 512GB 12 GB</t>
-  </si>
-  <si>
-    <t>iPhone 17 Pro 256GB</t>
-  </si>
-  <si>
     <t>Celular Samsung Galaxy S26 Ultra 5G 256GB 12 GB</t>
   </si>
   <si>
@@ -307,16 +307,34 @@
     <t>iPhone 16 256GB</t>
   </si>
   <si>
+    <t>Celular Samsung Galaxy A26 5G SM-A266M 256GB 8 GB</t>
+  </si>
+  <si>
+    <t>Celular Samsung Galaxy S24 FE 5G 256GB 8 GB</t>
+  </si>
+  <si>
     <t>Celular Samsung Galaxy A25 5G 256GB 8 GB</t>
   </si>
   <si>
-    <t>Celular Samsung Galaxy A26 5G SM-A266M 256GB 8 GB</t>
+    <t>Celular Motorola Edge 70 Fusion 5G 256GB 8 GB</t>
+  </si>
+  <si>
+    <t>Celular Samsung A57 128GB 8 GB</t>
+  </si>
+  <si>
+    <t>Celular Samsung Galaxy A17 4G 128GB 4 GB</t>
   </si>
   <si>
     <t>Celular Motorola Moto Edge 60 Fusion 5G 256GB 8 GB</t>
   </si>
   <si>
-    <t>Celular Samsung Galaxy S24 FE 5G 256GB 8 GB</t>
+    <t>iPhone 14 Plus 256GB 6GB</t>
+  </si>
+  <si>
+    <t>Celular Xiaomi Poco C85 256GB 8 GB</t>
+  </si>
+  <si>
+    <t>Celular Samsung Galaxy A17 4G 256GB 8 GB</t>
   </si>
   <si>
     <t>iPhone 13 4 GB 256GB</t>
@@ -325,39 +343,21 @@
     <t>Celular Motorola Moto G35 5G 128GB 12 GB</t>
   </si>
   <si>
-    <t>Celular Samsung A57 128GB 8 GB</t>
-  </si>
-  <si>
-    <t>Celular Motorola Edge 70 Fusion 5G 256GB 8 GB</t>
-  </si>
-  <si>
-    <t>Celular Samsung Galaxy A17 4G 128GB 4 GB</t>
-  </si>
-  <si>
-    <t>iPhone 14 Plus 256GB 6GB</t>
-  </si>
-  <si>
-    <t>Celular Xiaomi Poco C85 256GB 8 GB</t>
-  </si>
-  <si>
-    <t>Celular Samsung Galaxy A17 4G 256GB 8 GB</t>
+    <t>Celular Motorola Moto G G56 5G 256GB 8 GB</t>
+  </si>
+  <si>
+    <t>Celular Xiaomi Pocophone Poco X8 Pro 512GB 12 GB</t>
   </si>
   <si>
     <t>Celular Apple iPhone 17e 5G 256GB</t>
   </si>
   <si>
-    <t>Celular Motorola Moto G G56 5G 256GB 8 GB</t>
-  </si>
-  <si>
-    <t>Celular Xiaomi Pocophone Poco X8 Pro 512GB 12 GB</t>
+    <t>Celular Motorola Moto G G06 128GB 4 GB</t>
   </si>
   <si>
     <t>Celular Xiaomi Pocophone Poco X8 Pro Max 512GB 12 GB</t>
   </si>
   <si>
-    <t>Celular Motorola Moto G G06 128GB 4 GB</t>
-  </si>
-  <si>
     <t>Celular Xiaomi Redmi Note 15 Pro 5G 256GB 8 GB</t>
   </si>
   <si>
@@ -370,22 +370,22 @@
     <t>Celular Apple iPhone 14 Pro 256GB 6 GB</t>
   </si>
   <si>
+    <t>Celular Motorola Edge 60 5G XT2505-4 512GB 12 GB</t>
+  </si>
+  <si>
     <t>Celular Motorola Moto G35 5G 256GB 12 GB</t>
   </si>
   <si>
-    <t>Celular Motorola Edge 60 5G XT2505-4 512GB 12 GB</t>
-  </si>
-  <si>
     <t>Celular Samsung Galaxy A05s 128GB 6 GB</t>
   </si>
   <si>
+    <t>iPhone 17 Pro Max 512GB</t>
+  </si>
+  <si>
     <t>Celular Motorola Moto G75 5G XT2437-2 256GB 16 GB</t>
   </si>
   <si>
-    <t>iPhone 17 Pro Max 512GB</t>
-  </si>
-  <si>
-    <t>Celular Motorola Moto Edge 60 Pro 5G 512GB 12 GB</t>
+    <t>Celular Xiaomi Redmi Note 14 Pro 5G 256GB 8 GB</t>
   </si>
   <si>
     <t>Celular Xiaomi Poco X7 Pro 5G 256GB 8 GB</t>
@@ -406,45 +406,45 @@
     <t>/celular/celular-samsung-galaxy-s25-fe-5g-128gb-8-gb?_lc=11</t>
   </si>
   <si>
+    <t>/celular/celular-samsung-galaxy-a07-4g-128gb-4-gb?_lc=11</t>
+  </si>
+  <si>
     <t>/celular/celular-samsung-galaxy-a17-256gb-8-gb?_lc=11</t>
   </si>
   <si>
-    <t>/celular/celular-samsung-galaxy-a07-4g-128gb-4-gb?_lc=11</t>
-  </si>
-  <si>
     <t>/celular/celular-samsung-galaxy-s25-fe-5g-256gb-8-gb?_lc=11</t>
   </si>
   <si>
     <t>/celular/smartphone-samsung-galaxy-s24-ultra-5g-256gb-camera-quadrupla?_lc=11</t>
   </si>
   <si>
+    <t>/celular/celular-apple-iphone-16e-128gb-8-gb?_lc=11</t>
+  </si>
+  <si>
     <t>/celular/smartphone-apple-iphone-16-128gb-camera-dupla?_lc=11</t>
   </si>
   <si>
-    <t>/celular/celular-apple-iphone-16e-128gb-8-gb?_lc=11</t>
-  </si>
-  <si>
     <t>/celular/smartphone-apple-iphone-15-128gb-camera-dupla?_lc=11</t>
   </si>
   <si>
     <t>/celular/smartphone-samsung-galaxy-s24-5g-256gb?_lc=11</t>
   </si>
   <si>
+    <t>/celular/celular-motorola-moto-g86-5g-256gb-8-gb?_lc=11</t>
+  </si>
+  <si>
     <t>/celular/celular-samsung-galaxy-s25-plus-5g-256gb-12-gb?_lc=11</t>
   </si>
   <si>
-    <t>/celular/celular-motorola-moto-g86-5g-256gb-8-gb?_lc=11</t>
-  </si>
-  <si>
     <t>/celular/celular-samsung-galaxy-a07-4g-256gb-8-gb?_lc=11</t>
   </si>
   <si>
+    <t>/celular/celular-samsung-galaxy-s25-ultra-5g-256gb-12-gb?_lc=11</t>
+  </si>
+  <si>
     <t>/celular/celular-samsung-galaxy-s25-5g-256gb-12-gb?_lc=11</t>
   </si>
   <si>
-    <t>/celular/celular-samsung-galaxy-s25-ultra-5g-256gb-12-gb?_lc=11</t>
-  </si>
-  <si>
     <t>/celular/celular-samsung-a57-256gb-8-gb?_lc=11</t>
   </si>
   <si>
@@ -460,24 +460,24 @@
     <t>/celular/celular-samsung-galaxy-a36-5g-128gb-6-gb?_lc=11</t>
   </si>
   <si>
+    <t>/celular/celular-samsung-galaxy-s25-ultra-5g-512gb-12-gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-xiaomi-x8-poco-pro-256gb-8-gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-motorola-moto-edge-60-pro-5g-256gb-12-gb?_lc=11</t>
+  </si>
+  <si>
     <t>/celular/celular-xiaomi-redmi-15-256gb-8-gb?_lc=11</t>
   </si>
   <si>
-    <t>/celular/celular-motorola-moto-edge-60-pro-5g-256gb-12-gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-xiaomi-x8-poco-pro-256gb-8-gb?_lc=11</t>
+    <t>/celular/celular-apple-iphone-17-pro-256gb?_lc=11</t>
   </si>
   <si>
     <t>/celular/smartphone-apple-iphone-15-pro-max-256gb-camera-tripla?_lc=11</t>
   </si>
   <si>
-    <t>/celular/celular-samsung-galaxy-s25-ultra-5g-512gb-12-gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-apple-iphone-17-pro-256gb?_lc=11</t>
-  </si>
-  <si>
     <t>/celular/celular-samsung-galaxy-s26-ultra-5g-256gb?_lc=11</t>
   </si>
   <si>
@@ -487,16 +487,34 @@
     <t>/celular/smartphone-apple-iphone-16-256gb-camera-dupla?_lc=11</t>
   </si>
   <si>
+    <t>/celular/celular-samsung-galaxy-a26-256gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-samsung-galaxy-s24-fe-5g-256gb-8-gb?_lc=11</t>
+  </si>
+  <si>
     <t>/celular/celular-samsung-galaxy-a25-5g-256gb-8-gb?_lc=11</t>
   </si>
   <si>
-    <t>/celular/celular-samsung-galaxy-a26-256gb?_lc=11</t>
+    <t>/celular/celular-motorola-edge-70-fusion-5g-256gb-8-gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-samsung-a57-128gb-8-gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-samsung-galaxy-a17-4g-128gb-4-gb?_lc=11</t>
   </si>
   <si>
     <t>/celular/celular-motorola-edge-60-fusion-5g-256gb-8-gb?_lc=11</t>
   </si>
   <si>
-    <t>/celular/celular-samsung-galaxy-s24-fe-5g-256gb-8-gb?_lc=11</t>
+    <t>/celular/smartphone-apple-iphone-14-plus-256gb-camera-dupla?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-xiaomi-poco-c85-256gb-8-gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-samsung-galaxy-a17-4g-256gb-8-gb?_lc=11</t>
   </si>
   <si>
     <t>/celular/smartphone-apple-iphone-13-256gb-ios?_lc=11</t>
@@ -505,39 +523,21 @@
     <t>/celular/celular-motorola-moto-g35-5g-128gb-12-gb?_lc=11</t>
   </si>
   <si>
-    <t>/celular/celular-samsung-a57-128gb-8-gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-motorola-edge-70-fusion-5g-256gb-8-gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-samsung-galaxy-a17-4g-128gb-4-gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/smartphone-apple-iphone-14-plus-256gb-camera-dupla?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-xiaomi-poco-c85-256gb-8-gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-samsung-galaxy-a17-4g-256gb-8-gb?_lc=11</t>
+    <t>/celular/celular-motorola-moto-g56-256gb-8-gb?_lc=11</t>
+  </si>
+  <si>
+    <t>/celular/celular-xiaomi-x8-poco-pro-512gb-12-gb?_lc=11</t>
   </si>
   <si>
     <t>/celular/celular-apple-iphone-17e-5g-256gb?_lc=11</t>
   </si>
   <si>
-    <t>/celular/celular-motorola-moto-g56-256gb-8-gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-xiaomi-x8-poco-pro-512gb-12-gb?_lc=11</t>
+    <t>/celular/celular-motorola-moto-g-g06-128gb-4-gb?_lc=11</t>
   </si>
   <si>
     <t>/celular/celular-xiaomi-x8-poco-pro-max-512gb-12-gb?_lc=11</t>
   </si>
   <si>
-    <t>/celular/celular-motorola-moto-g-g06-128gb-4-gb?_lc=11</t>
-  </si>
-  <si>
     <t>/celular/celular-xiaomi-redmi-note-15-pro-5g-256gb-8-gb?_lc=11</t>
   </si>
   <si>
@@ -550,28 +550,28 @@
     <t>/celular/smartphone-apple-iphone-14-pro-256gb-camera-tripla?_lc=11</t>
   </si>
   <si>
+    <t>/celular/celular-motorola-edge-60-5g-512gb-12-gb?_lc=11</t>
+  </si>
+  <si>
     <t>/celular/celular-motorola-moto-g35-5g-256gb-12-gb?_lc=11</t>
   </si>
   <si>
-    <t>/celular/celular-motorola-edge-60-5g-512gb-12-gb?_lc=11</t>
-  </si>
-  <si>
     <t>/celular/smartphone-samsung-galaxy-a05s-128gb-camera-tripla?_lc=11</t>
   </si>
   <si>
+    <t>/celular/celular-apple-iphone-17-pro-max-512gb?_lc=11</t>
+  </si>
+  <si>
     <t>/celular/celular-motorola-moto-g75-5g-256gb-16-gb?_lc=11</t>
   </si>
   <si>
-    <t>/celular/celular-apple-iphone-17-pro-max-512gb?_lc=11</t>
-  </si>
-  <si>
-    <t>/celular/celular-motorola-edge-60-pro-512gb-12-gb?_lc=11</t>
+    <t>/celular/celular-xiaomi-redmi-note-14-pro-5g-256gb-8-gb?_lc=11</t>
   </si>
   <si>
     <t>/celular/celular-xiaomi-pocophone-poco-x7-pro-5g-256gb-8-gb?_lc=11</t>
   </si>
   <si>
-    <t>5578</t>
+    <t>5399</t>
   </si>
   <si>
     <t>2287</t>
@@ -586,45 +586,45 @@
     <t>2638</t>
   </si>
   <si>
-    <t>1374</t>
-  </si>
-  <si>
     <t>594</t>
   </si>
   <si>
+    <t>1405</t>
+  </si>
+  <si>
     <t>3123</t>
   </si>
   <si>
     <t>4249</t>
   </si>
   <si>
+    <t>3498</t>
+  </si>
+  <si>
     <t>4599</t>
   </si>
   <si>
-    <t>3498</t>
-  </si>
-  <si>
     <t>4099</t>
   </si>
   <si>
-    <t>2347</t>
+    <t>5579</t>
+  </si>
+  <si>
+    <t>1494</t>
   </si>
   <si>
     <t>4047</t>
   </si>
   <si>
-    <t>1494</t>
-  </si>
-  <si>
     <t>789</t>
   </si>
   <si>
+    <t>5199</t>
+  </si>
+  <si>
     <t>3758</t>
   </si>
   <si>
-    <t>5199</t>
-  </si>
-  <si>
     <t>2443</t>
   </si>
   <si>
@@ -640,43 +640,61 @@
     <t>1399</t>
   </si>
   <si>
+    <t>5865</t>
+  </si>
+  <si>
+    <t>2199</t>
+  </si>
+  <si>
+    <t>2591</t>
+  </si>
+  <si>
     <t>1175</t>
   </si>
   <si>
-    <t>2591</t>
-  </si>
-  <si>
-    <t>2199</t>
+    <t>7892</t>
   </si>
   <si>
     <t>5642</t>
   </si>
   <si>
-    <t>5865</t>
-  </si>
-  <si>
-    <t>7892</t>
-  </si>
-  <si>
     <t>6652</t>
   </si>
   <si>
     <t>1699</t>
   </si>
   <si>
-    <t>5399</t>
+    <t>4859</t>
+  </si>
+  <si>
+    <t>1359</t>
+  </si>
+  <si>
+    <t>2775</t>
   </si>
   <si>
     <t>1131</t>
   </si>
   <si>
-    <t>1421</t>
-  </si>
-  <si>
-    <t>1715</t>
-  </si>
-  <si>
-    <t>2775</t>
+    <t>2198</t>
+  </si>
+  <si>
+    <t>1954</t>
+  </si>
+  <si>
+    <t>729</t>
+  </si>
+  <si>
+    <t>1753</t>
+  </si>
+  <si>
+    <t>3500</t>
+  </si>
+  <si>
+    <t>939</t>
+  </si>
+  <si>
+    <t>1164</t>
   </si>
   <si>
     <t>3009</t>
@@ -685,39 +703,18 @@
     <t>917</t>
   </si>
   <si>
-    <t>1954</t>
-  </si>
-  <si>
-    <t>1847</t>
-  </si>
-  <si>
-    <t>729</t>
-  </si>
-  <si>
-    <t>3325</t>
-  </si>
-  <si>
-    <t>939</t>
-  </si>
-  <si>
-    <t>1164</t>
+    <t>2649</t>
   </si>
   <si>
     <t>4499</t>
   </si>
   <si>
-    <t>1359</t>
-  </si>
-  <si>
-    <t>2649</t>
+    <t>598</t>
   </si>
   <si>
     <t>3499</t>
   </si>
   <si>
-    <t>598</t>
-  </si>
-  <si>
     <t>1919</t>
   </si>
   <si>
@@ -730,22 +727,22 @@
     <t>4084</t>
   </si>
   <si>
+    <t>2124</t>
+  </si>
+  <si>
     <t>999</t>
   </si>
   <si>
-    <t>2124</t>
-  </si>
-  <si>
     <t>635</t>
   </si>
   <si>
+    <t>10169</t>
+  </si>
+  <si>
     <t>1785</t>
   </si>
   <si>
-    <t>10169</t>
-  </si>
-  <si>
-    <t>2999</t>
+    <t>1828</t>
   </si>
   <si>
     <t>2100</t>
@@ -766,45 +763,45 @@
     <t>https://i.zst.com.br/thumbs/45/39/14/-1591251808.jpg</t>
   </si>
   <si>
+    <t>https://i.zst.com.br/thumbs/45/f/35/-1597645208.jpg</t>
+  </si>
+  <si>
     <t>https://i.zst.com.br/thumbs/45/16/30/-1584401187.jpg</t>
   </si>
   <si>
-    <t>https://i.zst.com.br/thumbs/45/f/35/-1597645208.jpg</t>
-  </si>
-  <si>
     <t>https://i.zst.com.br/thumbs/45/30/14/-1591252595.jpg</t>
   </si>
   <si>
     <t>https://i.zst.com.br/thumbs/45/30/17/-1202498267.jpg</t>
   </si>
   <si>
+    <t>https://i.zst.com.br/thumbs/45/12/32/-1472883387.jpg</t>
+  </si>
+  <si>
     <t>https://i.zst.com.br/thumbs/45/16/f/-1346812222.jpg</t>
   </si>
   <si>
-    <t>https://i.zst.com.br/thumbs/45/12/32/-1472883387.jpg</t>
-  </si>
-  <si>
     <t>https://i.zst.com.br/thumbs/45/19/31/-1113972290.jpg</t>
   </si>
   <si>
     <t>https://i.zst.com.br/thumbs/45/3d/11/-1202542340.jpg</t>
   </si>
   <si>
+    <t>https://i.zst.com.br/thumbs/45/2e/2d/-1603821631.jpg</t>
+  </si>
+  <si>
     <t>https://i.zst.com.br/thumbs/45/37/2f/-1451536322.jpg</t>
   </si>
   <si>
-    <t>https://i.zst.com.br/thumbs/45/2e/2d/-1603821631.jpg</t>
-  </si>
-  <si>
     <t>https://i.zst.com.br/thumbs/45/2c/35/-1597643414.jpg</t>
   </si>
   <si>
+    <t>https://i.zst.com.br/thumbs/45/18/3d/-1449484750.jpg</t>
+  </si>
+  <si>
     <t>https://i.zst.com.br/thumbs/45/37/3b/-1449465281.jpg</t>
   </si>
   <si>
-    <t>https://i.zst.com.br/thumbs/45/18/3d/-1449484750.jpg</t>
-  </si>
-  <si>
     <t>https://i.zst.com.br/thumbs/45/24/14/-1693348668.jpg</t>
   </si>
   <si>
@@ -820,24 +817,24 @@
     <t>https://i.zst.com.br/thumbs/45/11/f/-1524507737.jpg</t>
   </si>
   <si>
+    <t>https://i.zst.com.br/thumbs/45/1c/14/-1449500134.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/2/12/-1683989765.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/1a/1c/-1529478118.jpg</t>
+  </si>
+  <si>
     <t>https://i.zst.com.br/thumbs/45/3a/3a/-1598683126.jpg</t>
   </si>
   <si>
-    <t>https://i.zst.com.br/thumbs/45/1a/1c/-1529478118.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/2/12/-1683989765.jpg</t>
+    <t>https://i.zst.com.br/thumbs/45/3f/1b/-1584074872.jpg</t>
   </si>
   <si>
     <t>https://i.zst.com.br/thumbs/45/a/13/-1114650735.jpg</t>
   </si>
   <si>
-    <t>https://i.zst.com.br/thumbs/45/1c/14/-1449500134.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/3f/1b/-1584074872.jpg</t>
-  </si>
-  <si>
     <t>https://i.zst.com.br/thumbs/45/2a/1b/-1678471943.jpg</t>
   </si>
   <si>
@@ -847,16 +844,34 @@
     <t>https://i.zst.com.br/thumbs/45/1c/37/-1347442557.jpg</t>
   </si>
   <si>
+    <t>https://i.zst.com.br/thumbs/45/30/33/-1475648263.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/5/15/-1358966033.jpg</t>
+  </si>
+  <si>
     <t>https://i.zst.com.br/thumbs/45/29/33/-1421244724.jpg</t>
   </si>
   <si>
-    <t>https://i.zst.com.br/thumbs/45/30/33/-1475648263.jpg</t>
+    <t>https://i.zst.com.br/thumbs/45/d/15/-1680059930.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/15/14/-1693349843.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/39/30/-1678916430.jpg</t>
   </si>
   <si>
     <t>https://i.zst.com.br/thumbs/45/d/13/-1500036474.jpg</t>
   </si>
   <si>
-    <t>https://i.zst.com.br/thumbs/45/5/15/-1358966033.jpg</t>
+    <t>https://i.zst.com.br/thumbs/45/31/1c/-871936652.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/14/37/-1591284000.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/35/30/-1678917590.jpg</t>
   </si>
   <si>
     <t>https://i.zst.com.br/thumbs/45/23/11/-747056146.jpg</t>
@@ -865,39 +880,21 @@
     <t>https://i.zst.com.br/thumbs/45/29/2e/-1554937995.jpg</t>
   </si>
   <si>
-    <t>https://i.zst.com.br/thumbs/45/15/14/-1693349843.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/d/15/-1680059930.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/39/30/-1678916430.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/31/1c/-871936652.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/14/37/-1591284000.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/35/30/-1678917590.jpg</t>
+    <t>https://i.zst.com.br/thumbs/45/10/30/-1532643273.jpg</t>
+  </si>
+  <si>
+    <t>https://i.zst.com.br/thumbs/45/3e/33/-1683990601.jpg</t>
   </si>
   <si>
     <t>https://i.zst.com.br/thumbs/45/11/12/-1679706169.jpg</t>
   </si>
   <si>
-    <t>https://i.zst.com.br/thumbs/45/10/30/-1532643273.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/3e/33/-1683990601.jpg</t>
+    <t>https://i.zst.com.br/thumbs/45/11/11/-1590231539.jpg</t>
   </si>
   <si>
     <t>https://i.zst.com.br/thumbs/45/d/33/-1683996479.jpg</t>
   </si>
   <si>
-    <t>https://i.zst.com.br/thumbs/45/11/11/-1590231539.jpg</t>
-  </si>
-  <si>
     <t>https://i.zst.com.br/thumbs/45/2b/3f/-1687085680.jpg</t>
   </si>
   <si>
@@ -910,22 +907,22 @@
     <t>https://i.zst.com.br/thumbs/45/12/11/-845276527.jpg</t>
   </si>
   <si>
+    <t>https://i.zst.com.br/thumbs/45/3a/1a/-1505387439.jpg</t>
+  </si>
+  <si>
     <t>https://i.zst.com.br/thumbs/45/b/14/-1533234478.jpg</t>
   </si>
   <si>
-    <t>https://i.zst.com.br/thumbs/45/3a/1a/-1505387439.jpg</t>
-  </si>
-  <si>
     <t>https://i.zst.com.br/thumbs/45/3f/15/-1206545191.jpg</t>
   </si>
   <si>
+    <t>https://i.zst.com.br/thumbs/45/3/1b/-1584070252.jpg</t>
+  </si>
+  <si>
     <t>https://i.zst.com.br/thumbs/45/1e/36/-1420399903.jpg</t>
   </si>
   <si>
-    <t>https://i.zst.com.br/thumbs/45/3/1b/-1584070252.jpg</t>
-  </si>
-  <si>
-    <t>https://i.zst.com.br/thumbs/45/2a/33/-1505424683.jpg</t>
+    <t>https://i.zst.com.br/thumbs/45/2e/16/-1459965948.jpg</t>
   </si>
   <si>
     <t>https://i.zst.com.br/thumbs/45/6/f/-1532413784.jpg</t>
@@ -1333,7 +1330,7 @@
         <v>185</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1350,7 +1347,7 @@
         <v>186</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1367,7 +1364,7 @@
         <v>187</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1384,7 +1381,7 @@
         <v>188</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1401,7 +1398,7 @@
         <v>189</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1418,7 +1415,7 @@
         <v>190</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1435,7 +1432,7 @@
         <v>191</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1452,7 +1449,7 @@
         <v>192</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1469,7 +1466,7 @@
         <v>193</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1486,7 +1483,7 @@
         <v>194</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1503,7 +1500,7 @@
         <v>195</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1520,7 +1517,7 @@
         <v>196</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1537,7 +1534,7 @@
         <v>197</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1554,7 +1551,7 @@
         <v>198</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1571,7 +1568,7 @@
         <v>199</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1588,7 +1585,7 @@
         <v>200</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1605,7 +1602,7 @@
         <v>201</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1622,7 +1619,7 @@
         <v>202</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1639,7 +1636,7 @@
         <v>203</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1656,7 +1653,7 @@
         <v>204</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1673,7 +1670,7 @@
         <v>205</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1690,7 +1687,7 @@
         <v>206</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1707,7 +1704,7 @@
         <v>207</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1724,7 +1721,7 @@
         <v>208</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1741,7 +1738,7 @@
         <v>209</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1758,7 +1755,7 @@
         <v>210</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1775,7 +1772,7 @@
         <v>211</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1792,7 +1789,7 @@
         <v>212</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1809,7 +1806,7 @@
         <v>213</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1826,7 +1823,7 @@
         <v>214</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1843,7 +1840,7 @@
         <v>215</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1860,7 +1857,7 @@
         <v>216</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1877,7 +1874,7 @@
         <v>217</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1894,7 +1891,7 @@
         <v>218</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1911,7 +1908,7 @@
         <v>219</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1928,7 +1925,7 @@
         <v>220</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1945,7 +1942,7 @@
         <v>221</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1962,7 +1959,7 @@
         <v>222</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1979,7 +1976,7 @@
         <v>223</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1996,7 +1993,7 @@
         <v>224</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2013,7 +2010,7 @@
         <v>225</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2030,7 +2027,7 @@
         <v>226</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2047,7 +2044,7 @@
         <v>227</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2064,7 +2061,7 @@
         <v>228</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2078,10 +2075,10 @@
         <v>169</v>
       </c>
       <c r="D46" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2095,10 +2092,10 @@
         <v>170</v>
       </c>
       <c r="D47" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2112,10 +2109,10 @@
         <v>171</v>
       </c>
       <c r="D48" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2129,10 +2126,10 @@
         <v>172</v>
       </c>
       <c r="D49" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2146,10 +2143,10 @@
         <v>173</v>
       </c>
       <c r="D50" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2163,10 +2160,10 @@
         <v>174</v>
       </c>
       <c r="D51" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2180,10 +2177,10 @@
         <v>175</v>
       </c>
       <c r="D52" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2197,10 +2194,10 @@
         <v>176</v>
       </c>
       <c r="D53" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2214,10 +2211,10 @@
         <v>177</v>
       </c>
       <c r="D54" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2231,10 +2228,10 @@
         <v>178</v>
       </c>
       <c r="D55" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2248,10 +2245,10 @@
         <v>179</v>
       </c>
       <c r="D56" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2265,10 +2262,10 @@
         <v>180</v>
       </c>
       <c r="D57" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2282,10 +2279,10 @@
         <v>181</v>
       </c>
       <c r="D58" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2299,10 +2296,10 @@
         <v>182</v>
       </c>
       <c r="D59" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2316,10 +2313,10 @@
         <v>183</v>
       </c>
       <c r="D60" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2333,10 +2330,10 @@
         <v>184</v>
       </c>
       <c r="D61" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
